--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEAF057E-48E3-4E4F-90A8-944563FA6BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309ABD0A-0691-47A9-87BA-7F4E93FA3BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
@@ -3256,9 +3256,6 @@
         <f t="shared" ref="AC2:AC33" si="1">IF(L2="","AG. FUNDIDO",IF(U2="AG","AG. USINAGEM","EM USINAGEM"))</f>
         <v>EM USINAGEM</v>
       </c>
-      <c r="AD2" s="10" t="s">
-        <v>110</v>
-      </c>
       <c r="AE2" s="44">
         <v>24</v>
       </c>
@@ -4740,6 +4737,9 @@
       <c r="AC15" s="10" t="str">
         <f t="shared" si="1"/>
         <v>EM USINAGEM</v>
+      </c>
+      <c r="AD15" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="AE15" s="44">
         <v>26</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309ABD0A-0691-47A9-87BA-7F4E93FA3BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0555F201-61D5-462D-B394-953A92FC63D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
@@ -22,8 +22,8 @@
     <sheet name="PLANEJADO BAGACEIRA" sheetId="5" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'VI DIVERSOS'!$A$1:$K$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Tabela1[#All]</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'VI DIVERSOS'!$A$1:$N$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BAGACEIRAS!$A$1:$AI$108</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">BAGACEIRAS!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3447" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="197">
   <si>
     <t>O.S.</t>
   </si>
@@ -459,22 +459,6 @@
     <t>Fusão</t>
   </si>
   <si>
-    <t>Prazo Fundição
-(Desbaste)</t>
-  </si>
-  <si>
-    <t>Prazo Usinagem
-(Desbaste)</t>
-  </si>
-  <si>
-    <t>Prazo Fundição
-(Acabamento)</t>
-  </si>
-  <si>
-    <t>Prazo Usinagem
-(Acabamento)</t>
-  </si>
-  <si>
     <t>Status
 Usinagem</t>
   </si>
@@ -652,6 +636,37 @@
   </si>
   <si>
     <t>BAGACEIRA 54" C/ SOLDA DURA</t>
+  </si>
+  <si>
+    <t>AG. USINAGEM</t>
+  </si>
+  <si>
+    <t>Prazo Fund. Prev.
+(Desbaste)</t>
+  </si>
+  <si>
+    <t>Prazo Fund. Real
+(Desbaste)</t>
+  </si>
+  <si>
+    <t>Prazo Usin. Prev.
+(Desbaste)</t>
+  </si>
+  <si>
+    <t>Prazo Usin. Real
+(Desbaste)</t>
+  </si>
+  <si>
+    <t>Prazo Fund. Prev.
+(Acabamento)</t>
+  </si>
+  <si>
+    <t>Prazo Usin. Prev.
+(Acabamento)</t>
+  </si>
+  <si>
+    <t>Prazo Usin. Real
+(Acabamento)</t>
   </si>
 </sst>
 </file>
@@ -3208,7 +3223,7 @@
       <c r="N2" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O2" s="42" t="str">
         <f t="shared" ref="O2:O33" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -3241,13 +3256,13 @@
         <v>77</v>
       </c>
       <c r="Y2" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z2" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AB2" s="10" t="s">
         <v>72</v>
@@ -3322,7 +3337,7 @@
       <c r="N3" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O3" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3343,7 +3358,7 @@
         <v>69</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V3" s="10" t="s">
         <v>72</v>
@@ -3368,7 +3383,7 @@
       </c>
       <c r="AC3" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE3" s="44">
         <v>24</v>
@@ -3436,7 +3451,7 @@
       <c r="N4" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O4" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3457,7 +3472,7 @@
         <v>69</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V4" s="10" t="s">
         <v>72</v>
@@ -3482,7 +3497,7 @@
       </c>
       <c r="AC4" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE4" s="44">
         <v>24</v>
@@ -3550,7 +3565,7 @@
       <c r="N5" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O5" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3571,7 +3586,7 @@
         <v>69</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V5" s="10" t="s">
         <v>72</v>
@@ -3596,7 +3611,7 @@
       </c>
       <c r="AC5" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE5" s="44">
         <v>24</v>
@@ -3664,7 +3679,7 @@
       <c r="N6" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O6" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3685,7 +3700,7 @@
         <v>69</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V6" s="10" t="s">
         <v>72</v>
@@ -3710,7 +3725,7 @@
       </c>
       <c r="AC6" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE6" s="44">
         <v>24</v>
@@ -3778,7 +3793,7 @@
       <c r="N7" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O7" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3892,7 +3907,7 @@
       <c r="N8" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O8" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3925,7 +3940,7 @@
         <v>77</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z8" s="10" t="s">
         <v>72</v>
@@ -4006,7 +4021,7 @@
       <c r="N9" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O9" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4039,7 +4054,7 @@
         <v>77</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z9" s="10" t="s">
         <v>72</v>
@@ -4120,7 +4135,7 @@
       <c r="N10" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O10" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4153,7 +4168,7 @@
         <v>77</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z10" s="10" t="s">
         <v>72</v>
@@ -4234,7 +4249,7 @@
       <c r="N11" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O11" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4270,7 +4285,7 @@
         <v>69</v>
       </c>
       <c r="Z11" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AA11" s="10" t="s">
         <v>72</v>
@@ -4348,7 +4363,7 @@
       <c r="N12" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O12" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4462,7 +4477,7 @@
       <c r="N13" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O13" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4576,7 +4591,7 @@
       <c r="N14" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O14" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4690,7 +4705,7 @@
       <c r="N15" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O15" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4807,7 +4822,7 @@
       <c r="N16" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O16" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4843,10 +4858,10 @@
         <v>69</v>
       </c>
       <c r="Z16" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA16" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="AA16" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="AB16" s="10" t="s">
         <v>72</v>
@@ -4921,7 +4936,7 @@
       <c r="N17" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O17" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4954,7 +4969,7 @@
         <v>77</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="Z17" s="10" t="s">
         <v>72</v>
@@ -5035,7 +5050,7 @@
       <c r="N18" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O18" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5149,7 +5164,7 @@
       <c r="N19" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O19" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5182,7 +5197,7 @@
         <v>77</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="Z19" s="10" t="s">
         <v>72</v>
@@ -5260,7 +5275,7 @@
       <c r="N20" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O20" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5371,7 +5386,7 @@
       <c r="N21" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O21" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5485,7 +5500,7 @@
       <c r="N22" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O22" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5499,11 +5514,11 @@
       <c r="R22" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S22" s="43">
-        <v>46203</v>
+      <c r="S22" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U22" s="10" t="s">
         <v>72</v>
@@ -5599,7 +5614,7 @@
       <c r="N23" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O23" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5614,11 +5629,11 @@
       <c r="R23" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S23" s="43">
-        <v>46203</v>
+      <c r="S23" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U23" s="10" t="s">
         <v>72</v>
@@ -5714,7 +5729,7 @@
       <c r="N24" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O24" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5738,7 +5753,7 @@
         <v>69</v>
       </c>
       <c r="V24" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W24" s="10" t="s">
         <v>72</v>
@@ -5828,7 +5843,7 @@
       <c r="N25" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O25" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5852,7 +5867,7 @@
         <v>69</v>
       </c>
       <c r="V25" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W25" s="10" t="s">
         <v>72</v>
@@ -5942,7 +5957,7 @@
       <c r="N26" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O26" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5963,7 +5978,7 @@
         <v>69</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="V26" s="10" t="s">
         <v>72</v>
@@ -6056,7 +6071,7 @@
       <c r="N27" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O27" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6077,10 +6092,10 @@
         <v>69</v>
       </c>
       <c r="U27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V27" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="V27" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="W27" s="10" t="s">
         <v>72</v>
@@ -6170,7 +6185,7 @@
       <c r="N28" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O28" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6191,10 +6206,10 @@
         <v>69</v>
       </c>
       <c r="U28" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V28" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="V28" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="W28" s="10" t="s">
         <v>72</v>
@@ -6284,7 +6299,7 @@
       <c r="N29" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O29" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6305,7 +6320,7 @@
         <v>69</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="V29" s="10" t="s">
         <v>72</v>
@@ -6398,7 +6413,7 @@
       <c r="N30" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O30" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6412,11 +6427,11 @@
       <c r="R30" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S30" s="43">
-        <v>46203</v>
+      <c r="S30" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T30" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U30" s="10" t="s">
         <v>72</v>
@@ -6512,7 +6527,7 @@
       <c r="N31" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O31" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6545,7 +6560,7 @@
         <v>77</v>
       </c>
       <c r="Y31" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="Z31" s="10" t="s">
         <v>72</v>
@@ -6626,7 +6641,7 @@
       <c r="N32" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O32" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6740,7 +6755,7 @@
       <c r="N33" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O33" s="42" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6854,7 +6869,7 @@
       <c r="N34" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O34" s="42" t="str">
         <f t="shared" ref="O34:O65" ca="1" si="2">IF(N34&lt;0,"ATRASADO",IF(N34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -6968,7 +6983,7 @@
       <c r="N35" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O35" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7082,7 +7097,7 @@
       <c r="N36" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O36" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7196,7 +7211,7 @@
       <c r="N37" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O37" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7310,7 +7325,7 @@
       <c r="N38" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O38" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7324,11 +7339,11 @@
       <c r="R38" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S38" s="43">
-        <v>46203</v>
+      <c r="S38" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T38" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>72</v>
@@ -7421,7 +7436,7 @@
       <c r="N39" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O39" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7532,7 +7547,7 @@
       <c r="N40" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O40" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7646,7 +7661,7 @@
       <c r="N41" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O41" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7760,7 +7775,7 @@
       <c r="N42" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O42" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7874,7 +7889,7 @@
       <c r="N43" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O43" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -7985,7 +8000,7 @@
       <c r="N44" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O44" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8099,7 +8114,7 @@
       <c r="N45" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O45" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8113,11 +8128,11 @@
       <c r="R45" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S45" s="43">
-        <v>46203</v>
+      <c r="S45" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T45" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U45" s="10" t="s">
         <v>72</v>
@@ -8213,7 +8228,7 @@
       <c r="N46" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O46" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8227,11 +8242,11 @@
       <c r="R46" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S46" s="43">
-        <v>46203</v>
+      <c r="S46" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T46" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U46" s="10" t="s">
         <v>72</v>
@@ -8327,7 +8342,7 @@
       <c r="N47" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O47" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8341,11 +8356,11 @@
       <c r="R47" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S47" s="43">
-        <v>46203</v>
+      <c r="S47" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T47" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U47" s="10" t="s">
         <v>72</v>
@@ -8438,7 +8453,7 @@
       <c r="N48" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O48" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8452,11 +8467,11 @@
       <c r="R48" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S48" s="43">
-        <v>46203</v>
+      <c r="S48" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T48" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U48" s="10" t="s">
         <v>72</v>
@@ -8550,7 +8565,7 @@
       <c r="N49" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O49" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8564,11 +8579,11 @@
       <c r="R49" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S49" s="43">
-        <v>46203</v>
+      <c r="S49" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T49" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U49" s="10" t="s">
         <v>72</v>
@@ -8662,7 +8677,7 @@
       <c r="N50" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O50" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8676,11 +8691,11 @@
       <c r="R50" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S50" s="43">
-        <v>46203</v>
+      <c r="S50" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T50" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U50" s="10" t="s">
         <v>72</v>
@@ -8776,7 +8791,7 @@
       <c r="N51" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O51" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8790,11 +8805,11 @@
       <c r="R51" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S51" s="43">
-        <v>46203</v>
+      <c r="S51" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T51" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U51" s="10" t="s">
         <v>72</v>
@@ -8890,7 +8905,7 @@
       <c r="N52" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O52" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8904,11 +8919,11 @@
       <c r="R52" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S52" s="43">
-        <v>46203</v>
+      <c r="S52" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T52" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>72</v>
@@ -9004,7 +9019,7 @@
       <c r="N53" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O53" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9018,11 +9033,11 @@
       <c r="R53" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S53" s="43">
-        <v>46203</v>
+      <c r="S53" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T53" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U53" s="10" t="s">
         <v>72</v>
@@ -9115,7 +9130,7 @@
       <c r="N54" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O54" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9129,11 +9144,11 @@
       <c r="R54" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S54" s="43">
-        <v>46203</v>
+      <c r="S54" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T54" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U54" s="10" t="s">
         <v>72</v>
@@ -9226,7 +9241,7 @@
       <c r="N55" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O55" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9240,11 +9255,11 @@
       <c r="R55" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S55" s="43">
-        <v>46203</v>
+      <c r="S55" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T55" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U55" s="10" t="s">
         <v>72</v>
@@ -9337,7 +9352,7 @@
       <c r="N56" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O56" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9351,11 +9366,11 @@
       <c r="R56" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S56" s="43">
-        <v>46203</v>
+      <c r="S56" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T56" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U56" s="10" t="s">
         <v>72</v>
@@ -9448,7 +9463,7 @@
       <c r="N57" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O57" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9462,11 +9477,11 @@
       <c r="R57" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S57" s="43">
-        <v>46203</v>
+      <c r="S57" s="43" t="s">
+        <v>69</v>
       </c>
       <c r="T57" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U57" s="10" t="s">
         <v>72</v>
@@ -9562,7 +9577,7 @@
       <c r="N58" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O58" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9677,7 +9692,7 @@
       <c r="N59" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O59" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9788,7 +9803,7 @@
       <c r="N60" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O60" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9894,7 +9909,7 @@
       <c r="N61" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O61" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9994,13 +10009,16 @@
 Fundido]])</f>
         <v>25</v>
       </c>
+      <c r="L62" s="11">
+        <v>46197</v>
+      </c>
       <c r="M62" s="16">
         <v>46234</v>
       </c>
       <c r="N62" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O62" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10046,7 +10064,7 @@
       </c>
       <c r="AC62" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. FUNDIDO</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE62" s="44">
         <v>30</v>
@@ -10100,13 +10118,16 @@
 Fundido]])</f>
         <v>25</v>
       </c>
+      <c r="L63" s="11">
+        <v>46197</v>
+      </c>
       <c r="M63" s="16">
         <v>46234</v>
       </c>
       <c r="N63" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O63" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10152,7 +10173,7 @@
       </c>
       <c r="AC63" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. FUNDIDO</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE63" s="44">
         <v>30</v>
@@ -10206,13 +10227,16 @@
 Fundido]])</f>
         <v>25</v>
       </c>
+      <c r="L64" s="11">
+        <v>46197</v>
+      </c>
       <c r="M64" s="16">
         <v>46234</v>
       </c>
       <c r="N64" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O64" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10258,7 +10282,7 @@
       </c>
       <c r="AC64" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. FUNDIDO</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE64" s="44">
         <v>30</v>
@@ -10318,7 +10342,7 @@
       <c r="N65" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O65" s="42" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10418,13 +10442,16 @@
 Fundido]])</f>
         <v>25</v>
       </c>
+      <c r="L66" s="11">
+        <v>46197</v>
+      </c>
       <c r="M66" s="16">
         <v>46234</v>
       </c>
       <c r="N66" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O66" s="42" t="str">
         <f t="shared" ref="O66:O89" ca="1" si="4">IF(N66&lt;0,"ATRASADO",IF(N66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -10470,7 +10497,7 @@
       </c>
       <c r="AC66" s="10" t="str">
         <f t="shared" ref="AC66:AC89" si="5">IF(L66="","AG. FUNDIDO",IF(U66="AG","AG. USINAGEM","EM USINAGEM"))</f>
-        <v>AG. FUNDIDO</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE66" s="44">
         <v>30</v>
@@ -10530,7 +10557,7 @@
       <c r="N67" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O67" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -10644,7 +10671,7 @@
       <c r="N68" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O68" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -10755,7 +10782,7 @@
       <c r="N69" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O69" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -10866,7 +10893,7 @@
       <c r="N70" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O70" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -10977,7 +11004,7 @@
       <c r="N71" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O71" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11088,7 +11115,7 @@
       <c r="N72" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O72" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11199,7 +11226,7 @@
       <c r="N73" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O73" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11310,7 +11337,7 @@
       <c r="N74" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O74" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11421,7 +11448,7 @@
       <c r="N75" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O75" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11532,7 +11559,7 @@
       <c r="N76" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O76" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11643,7 +11670,7 @@
       <c r="N77" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O77" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11754,7 +11781,7 @@
       <c r="N78" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O78" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11863,7 +11890,7 @@
       <c r="N79" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O79" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11972,7 +11999,7 @@
       <c r="N80" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O80" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12081,7 +12108,7 @@
       <c r="N81" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O81" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12190,7 +12217,7 @@
       <c r="N82" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O82" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12299,7 +12326,7 @@
       <c r="N83" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O83" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12408,7 +12435,7 @@
       <c r="N84" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O84" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12521,7 +12548,7 @@
       <c r="N85" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O85" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12634,7 +12661,7 @@
       <c r="N86" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O86" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12747,7 +12774,7 @@
       <c r="N87" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O87" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12860,7 +12887,7 @@
       <c r="N88" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O88" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12973,7 +13000,7 @@
       <c r="N89" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O89" s="42" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13086,7 +13113,7 @@
       <c r="N90" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O90" s="42" t="str">
         <f t="shared" ref="O90:O94" ca="1" si="6">IF(N90&lt;0,"ATRASADO",IF(N90&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -13192,7 +13219,7 @@
       <c r="N91" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O91" s="42" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -13298,7 +13325,7 @@
       <c r="N92" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O92" s="42" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -13404,7 +13431,7 @@
       <c r="N93" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O93" s="42" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -13510,7 +13537,7 @@
       <c r="N94" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O94" s="42" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -13616,7 +13643,7 @@
       <c r="N95" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O95" s="42" t="str">
         <f t="shared" ref="O95:O99" ca="1" si="9">IF(N95&lt;0,"ATRASADO",IF(N95&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -13712,7 +13739,7 @@
       <c r="N96" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O96" s="42" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -13808,7 +13835,7 @@
       <c r="N97" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O97" s="42" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -13904,7 +13931,7 @@
       <c r="N98" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O98" s="42" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -14000,7 +14027,7 @@
       <c r="N99" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O99" s="42" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -14068,7 +14095,7 @@
         <v>12</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F100" s="15" t="s">
         <v>77</v>
@@ -14077,7 +14104,7 @@
         <v>77</v>
       </c>
       <c r="H100" s="15" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I100" s="15">
         <v>1</v>
@@ -14096,7 +14123,7 @@
       <c r="N100" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O100" s="42" t="str">
         <f ca="1">IF(N100&lt;0,"ATRASADO",IF(N100&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -14164,7 +14191,7 @@
         <v>13</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F101" s="15" t="s">
         <v>77</v>
@@ -14173,7 +14200,7 @@
         <v>77</v>
       </c>
       <c r="H101" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I101" s="15">
         <v>1</v>
@@ -14192,7 +14219,7 @@
       <c r="N101" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O101" s="42" t="str">
         <f t="shared" ref="O101:O109" ca="1" si="11">IF(N101&lt;0,"ATRASADO",IF(N101&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -14260,7 +14287,7 @@
         <v>14</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F102" s="15" t="s">
         <v>77</v>
@@ -14269,7 +14296,7 @@
         <v>77</v>
       </c>
       <c r="H102" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I102" s="15">
         <v>1</v>
@@ -14288,7 +14315,7 @@
       <c r="N102" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O102" s="42" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -14356,7 +14383,7 @@
         <v>15</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F103" s="15" t="s">
         <v>77</v>
@@ -14365,7 +14392,7 @@
         <v>77</v>
       </c>
       <c r="H103" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I103" s="15">
         <v>1</v>
@@ -14384,7 +14411,7 @@
       <c r="N103" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O103" s="42" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -14452,7 +14479,7 @@
         <v>16</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F104" s="15" t="s">
         <v>77</v>
@@ -14461,7 +14488,7 @@
         <v>77</v>
       </c>
       <c r="H104" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I104" s="15">
         <v>1</v>
@@ -14480,7 +14507,7 @@
       <c r="N104" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O104" s="42" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -14548,7 +14575,7 @@
         <v>17</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F105" s="15" t="s">
         <v>77</v>
@@ -14557,7 +14584,7 @@
         <v>77</v>
       </c>
       <c r="H105" s="15" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I105" s="15">
         <v>1</v>
@@ -14576,7 +14603,7 @@
       <c r="N105" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O105" s="42" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -14644,7 +14671,7 @@
         <v>18</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F106" s="15" t="s">
         <v>77</v>
@@ -14653,7 +14680,7 @@
         <v>77</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I106" s="15">
         <v>1</v>
@@ -14672,7 +14699,7 @@
       <c r="N106" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O106" s="42" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -14740,7 +14767,7 @@
         <v>19</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F107" s="15" t="s">
         <v>77</v>
@@ -14749,7 +14776,7 @@
         <v>77</v>
       </c>
       <c r="H107" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I107" s="15">
         <v>1</v>
@@ -14768,7 +14795,7 @@
       <c r="N107" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O107" s="42" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -14836,7 +14863,7 @@
         <v>20</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F108" s="15" t="s">
         <v>77</v>
@@ -14845,7 +14872,7 @@
         <v>77</v>
       </c>
       <c r="H108" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I108" s="15">
         <v>1</v>
@@ -14864,7 +14891,7 @@
       <c r="N108" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O108" s="42" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -14932,7 +14959,7 @@
         <v>21</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F109" s="15" t="s">
         <v>77</v>
@@ -14941,7 +14968,7 @@
         <v>77</v>
       </c>
       <c r="H109" s="15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I109" s="15">
         <v>1</v>
@@ -14960,7 +14987,7 @@
       <c r="N109" s="42">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O109" s="42" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -15169,7 +15196,7 @@
       <c r="Q2" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R2" s="10" t="str">
         <f t="shared" ref="R2:R33" ca="1" si="0">IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -15240,7 +15267,7 @@
       <c r="Q3" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R3" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15311,7 +15338,7 @@
       <c r="Q4" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R4" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15382,7 +15409,7 @@
       <c r="Q5" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R5" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15453,7 +15480,7 @@
       <c r="Q6" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R6" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15524,7 +15551,7 @@
       <c r="Q7" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R7" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15595,7 +15622,7 @@
       <c r="Q8" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R8" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15666,7 +15693,7 @@
       <c r="Q9" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R9" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15737,7 +15764,7 @@
       <c r="Q10" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R10" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15808,7 +15835,7 @@
       <c r="Q11" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R11" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15879,7 +15906,7 @@
       <c r="Q12" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R12" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -15950,7 +15977,7 @@
       <c r="Q13" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R13" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16021,7 +16048,7 @@
       <c r="Q14" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R14" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16092,7 +16119,7 @@
       <c r="Q15" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R15" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16163,7 +16190,7 @@
       <c r="Q16" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R16" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16234,7 +16261,7 @@
       <c r="Q17" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R17" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16305,7 +16332,7 @@
       <c r="Q18" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R18" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16376,7 +16403,7 @@
       <c r="Q19" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R19" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16447,7 +16474,7 @@
       <c r="Q20" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R20" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16518,7 +16545,7 @@
       <c r="Q21" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R21" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16589,7 +16616,7 @@
       <c r="Q22" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R22" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16660,7 +16687,7 @@
       <c r="Q23" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R23" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16731,7 +16758,7 @@
       <c r="Q24" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R24" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16802,7 +16829,7 @@
       <c r="Q25" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R25" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16873,7 +16900,7 @@
       <c r="Q26" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R26" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16944,7 +16971,7 @@
       <c r="Q27" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R27" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17015,7 +17042,7 @@
       <c r="Q28" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R28" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17086,7 +17113,7 @@
       <c r="Q29" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R29" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17157,7 +17184,7 @@
       <c r="Q30" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R30" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17228,7 +17255,7 @@
       <c r="Q31" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R31" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17299,7 +17326,7 @@
       <c r="Q32" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R32" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17332,7 +17359,7 @@
         <v>77</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F33" s="10">
         <v>1202015</v>
@@ -17370,7 +17397,7 @@
       <c r="Q33" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17403,7 +17430,7 @@
         <v>77</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F34" s="10">
         <v>1202015</v>
@@ -17441,7 +17468,7 @@
       <c r="Q34" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R34" s="10" t="str">
         <f t="shared" ref="R34:R65" ca="1" si="1">IF(Q34&lt;0,"ATRASADO",IF(Q34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -17474,7 +17501,7 @@
         <v>77</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F35" s="10">
         <v>1202015</v>
@@ -17512,7 +17539,7 @@
       <c r="Q35" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R35" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -17545,7 +17572,7 @@
         <v>77</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F36" s="10">
         <v>1202015</v>
@@ -17583,7 +17610,7 @@
       <c r="Q36" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R36" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -17616,7 +17643,7 @@
         <v>77</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F37" s="10">
         <v>1202015</v>
@@ -17654,7 +17681,7 @@
       <c r="Q37" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R37" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -17725,7 +17752,7 @@
       <c r="Q38" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R38" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -17796,7 +17823,7 @@
       <c r="Q39" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R39" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -17867,7 +17894,7 @@
       <c r="Q40" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R40" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -17938,7 +17965,7 @@
       <c r="Q41" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R41" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18009,7 +18036,7 @@
       <c r="Q42" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R42" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18080,7 +18107,7 @@
       <c r="Q43" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R43" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18151,7 +18178,7 @@
       <c r="Q44" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R44" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18222,7 +18249,7 @@
       <c r="Q45" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R45" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18293,7 +18320,7 @@
       <c r="Q46" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R46" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18364,7 +18391,7 @@
       <c r="Q47" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R47" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18435,7 +18462,7 @@
       <c r="Q48" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R48" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18506,7 +18533,7 @@
       <c r="Q49" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R49" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18577,7 +18604,7 @@
       <c r="Q50" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R50" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18648,7 +18675,7 @@
       <c r="Q51" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R51" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18719,7 +18746,7 @@
       <c r="Q52" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R52" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18790,7 +18817,7 @@
       <c r="Q53" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R53" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18861,7 +18888,7 @@
       <c r="Q54" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R54" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -18932,7 +18959,7 @@
       <c r="Q55" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R55" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19003,7 +19030,7 @@
       <c r="Q56" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R56" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19074,7 +19101,7 @@
       <c r="Q57" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R57" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19145,7 +19172,7 @@
       <c r="Q58" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R58" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19216,7 +19243,7 @@
       <c r="Q59" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R59" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19287,7 +19314,7 @@
       <c r="Q60" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R60" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19358,7 +19385,7 @@
       <c r="Q61" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R61" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19429,7 +19456,7 @@
       <c r="Q62" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R62" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19500,7 +19527,7 @@
       <c r="Q63" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R63" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19571,7 +19598,7 @@
       <c r="Q64" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R64" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19642,7 +19669,7 @@
       <c r="Q65" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R65" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19713,7 +19740,7 @@
       <c r="Q66" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R66" s="10" t="str">
         <f t="shared" ref="R66:R91" ca="1" si="2">IF(Q66&lt;0,"ATRASADO",IF(Q66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -19784,7 +19811,7 @@
       <c r="Q67" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R67" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -19855,7 +19882,7 @@
       <c r="Q68" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R68" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -19926,7 +19953,7 @@
       <c r="Q69" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R69" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -19997,7 +20024,7 @@
       <c r="Q70" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R70" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20068,7 +20095,7 @@
       <c r="Q71" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R71" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20139,7 +20166,7 @@
       <c r="Q72" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R72" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20210,7 +20237,7 @@
       <c r="Q73" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R73" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20281,7 +20308,7 @@
       <c r="Q74" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R74" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20352,7 +20379,7 @@
       <c r="Q75" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R75" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20423,7 +20450,7 @@
       <c r="Q76" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R76" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20494,7 +20521,7 @@
       <c r="Q77" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R77" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20565,7 +20592,7 @@
       <c r="Q78" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R78" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20636,7 +20663,7 @@
       <c r="Q79" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R79" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20707,7 +20734,7 @@
       <c r="Q80" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R80" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20778,7 +20805,7 @@
       <c r="Q81" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R81" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20849,7 +20876,7 @@
       <c r="Q82" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R82" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20920,7 +20947,7 @@
       <c r="Q83" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R83" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -20991,7 +21018,7 @@
       <c r="Q84" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R84" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21062,7 +21089,7 @@
       <c r="Q85" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R85" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21133,7 +21160,7 @@
       <c r="Q86" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R86" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21204,7 +21231,7 @@
       <c r="Q87" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R87" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21275,7 +21302,7 @@
       <c r="Q88" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R88" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21346,7 +21373,7 @@
       <c r="Q89" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R89" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21417,7 +21444,7 @@
       <c r="Q90" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R90" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21488,7 +21515,7 @@
       <c r="Q91" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R91" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21655,7 +21682,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O2" s="13" t="str">
         <f t="shared" ref="O2:O16" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -21732,7 +21759,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O3" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21809,7 +21836,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O4" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21886,7 +21913,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O5" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -21963,7 +21990,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O6" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22040,7 +22067,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O7" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22117,7 +22144,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O8" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22194,7 +22221,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O9" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22271,7 +22298,7 @@
       <c r="N10" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O10" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22348,7 +22375,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O11" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22425,7 +22452,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O12" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22502,7 +22529,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O13" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22579,7 +22606,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O14" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22656,7 +22683,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O15" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22733,7 +22760,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O16" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -22810,7 +22837,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O17" s="13" t="str">
         <f ca="1">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -22889,7 +22916,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O18" s="13" t="str">
         <f t="shared" ref="O18:O25" ca="1" si="2">IF(N18&lt;0,"ATRASADO",IF(N18&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -22968,7 +22995,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23047,7 +23074,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23126,7 +23153,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23205,7 +23232,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23284,7 +23311,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23363,7 +23390,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23442,7 +23469,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23521,7 +23548,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O26" s="13" t="str">
         <f ca="1">IF(N26&lt;0,"ATRASADO",IF(N26&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23598,7 +23625,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O27" s="13" t="str">
         <f t="shared" ref="O27:O28" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23675,7 +23702,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O28" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -23752,7 +23779,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O29" s="13" t="str">
         <f t="shared" ref="O29:O31" ca="1" si="5">IF(N29&lt;0,"ATRASADO",IF(N29&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23831,7 +23858,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O30" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -23910,7 +23937,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O31" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -23964,7 +23991,7 @@
         <v>8</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>77</v>
@@ -23989,7 +24016,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O32" s="13" t="str">
         <f ca="1">IF(N32&lt;0,"ATRASADO",IF(N32&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -24043,7 +24070,7 @@
         <v>9</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>77</v>
@@ -24068,7 +24095,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O33" s="13" t="str">
         <f t="shared" ref="O33:O35" ca="1" si="7">IF(N33&lt;0,"ATRASADO",IF(N33&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -24122,7 +24149,7 @@
         <v>10</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>77</v>
@@ -24131,7 +24158,7 @@
         <v>77</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I34" s="14">
         <v>1</v>
@@ -24147,7 +24174,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O34" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -24201,7 +24228,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>77</v>
@@ -24210,7 +24237,7 @@
         <v>77</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I35" s="14">
         <v>1</v>
@@ -24226,7 +24253,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O35" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -25058,7 +25085,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F2" s="14">
         <v>1</v>
@@ -25070,7 +25097,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J2" s="7">
         <v>46204</v>
@@ -25081,7 +25108,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O2" t="str">
         <f t="shared" ref="O2:O9" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25114,7 +25141,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F3" s="14">
         <v>1</v>
@@ -25126,7 +25153,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J3" s="7">
         <v>46204</v>
@@ -25137,7 +25164,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25170,7 +25197,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F4" s="14">
         <v>1</v>
@@ -25182,7 +25209,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J4" s="7">
         <v>46204</v>
@@ -25193,7 +25220,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25226,7 +25253,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F5" s="14">
         <v>1</v>
@@ -25238,7 +25265,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J5" s="7">
         <v>46204</v>
@@ -25249,7 +25276,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25282,7 +25309,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F6" s="14">
         <v>1</v>
@@ -25294,7 +25321,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J6" s="7">
         <v>46204</v>
@@ -25305,7 +25332,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O6" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25338,7 +25365,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F7" s="14">
         <v>1</v>
@@ -25350,7 +25377,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J7" s="7">
         <v>46204</v>
@@ -25361,7 +25388,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25394,7 +25421,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F8" s="14">
         <v>1</v>
@@ -25406,7 +25433,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J8" s="7">
         <v>46204</v>
@@ -25417,7 +25444,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25450,7 +25477,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F9" s="14">
         <v>1</v>
@@ -25462,7 +25489,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J9" s="7">
         <v>46204</v>
@@ -25473,7 +25500,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -25506,7 +25533,7 @@
         <v>77</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F10" s="15">
         <v>1</v>
@@ -25518,7 +25545,7 @@
         <v>77</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J10" s="16" t="s">
         <v>77</v>
@@ -25535,7 +25562,7 @@
       <c r="N10" s="12">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O10" s="35" t="s">
         <v>102</v>
@@ -25579,7 +25606,7 @@
         <v>77</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>77</v>
@@ -25593,7 +25620,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O11" s="1" t="str">
         <f ca="1">IF(N11&lt;0,"ATRASADO",IF(N11&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25638,7 +25665,7 @@
         <v>77</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>77</v>
@@ -25652,7 +25679,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O12" t="str">
         <f ca="1">IF(N12&lt;0,"ATRASADO",IF(N12&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25697,7 +25724,7 @@
         <v>77</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>77</v>
@@ -25711,7 +25738,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">IF(N13&lt;0,"ATRASADO",IF(N13&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25756,7 +25783,7 @@
         <v>77</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>77</v>
@@ -25770,7 +25797,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O14" t="str">
         <f ca="1">IF(N14&lt;0,"ATRASADO",IF(N14&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25815,7 +25842,7 @@
         <v>77</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>77</v>
@@ -25829,7 +25856,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O15" t="str">
         <f t="shared" ref="O15:O16" ca="1" si="1">IF(N15&lt;0,"ATRASADO",IF(N15&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25874,7 +25901,7 @@
         <v>77</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>77</v>
@@ -25888,7 +25915,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -25933,7 +25960,7 @@
         <v>77</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J17" s="7">
         <v>46251</v>
@@ -25944,7 +25971,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" ref="O17:O18" ca="1" si="2">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25989,7 +26016,7 @@
         <v>77</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J18" s="7">
         <v>46251</v>
@@ -26000,7 +26027,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -26033,7 +26060,7 @@
         <v>77</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F19" s="14">
         <v>1</v>
@@ -26045,7 +26072,7 @@
         <v>77</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J19" s="16" t="s">
         <v>77</v>
@@ -26059,7 +26086,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O19" t="str">
         <f ca="1">IF(N19&lt;0,"ATRASADO",IF(N19&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -26092,7 +26119,7 @@
         <v>77</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F20" s="14">
         <v>1</v>
@@ -26104,7 +26131,7 @@
         <v>77</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>77</v>
@@ -26118,7 +26145,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O20" t="str">
         <f ca="1">IF(N20&lt;0,"ATRASADO",IF(N20&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -26151,7 +26178,7 @@
         <v>77</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F21" s="14">
         <v>1</v>
@@ -26163,7 +26190,7 @@
         <v>77</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J21" s="16" t="s">
         <v>77</v>
@@ -26177,7 +26204,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O21" t="str">
         <f t="shared" ref="O21:O26" ca="1" si="3">IF(N21&lt;0,"ATRASADO",IF(N21&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -26210,7 +26237,7 @@
         <v>77</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -26222,7 +26249,7 @@
         <v>77</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J22" s="16" t="s">
         <v>77</v>
@@ -26236,7 +26263,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O22" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26269,7 +26296,7 @@
         <v>77</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
@@ -26281,7 +26308,7 @@
         <v>77</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J23" s="16" t="s">
         <v>77</v>
@@ -26295,7 +26322,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26328,7 +26355,7 @@
         <v>77</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F24" s="14">
         <v>1</v>
@@ -26340,7 +26367,7 @@
         <v>77</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J24" s="16" t="s">
         <v>77</v>
@@ -26354,7 +26381,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O24" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26387,7 +26414,7 @@
         <v>77</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F25" s="14">
         <v>1</v>
@@ -26399,7 +26426,7 @@
         <v>77</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J25" s="16" t="s">
         <v>77</v>
@@ -26413,7 +26440,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O25" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26446,7 +26473,7 @@
         <v>77</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F26" s="14">
         <v>1</v>
@@ -26458,7 +26485,7 @@
         <v>77</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J26" s="16" t="s">
         <v>77</v>
@@ -26472,7 +26499,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O26" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26505,19 +26532,19 @@
         <v>77</v>
       </c>
       <c r="E27" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="J27" s="16" t="s">
         <v>77</v>
@@ -26531,7 +26558,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O27" t="str">
         <f t="shared" ref="O27:O34" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -26564,19 +26591,19 @@
         <v>77</v>
       </c>
       <c r="E28" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F28" s="14">
+        <v>1</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="F28" s="14">
-        <v>1</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="J28" s="16" t="s">
         <v>77</v>
@@ -26590,7 +26617,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O28" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -26623,19 +26650,19 @@
         <v>77</v>
       </c>
       <c r="E29" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="J29" s="16" t="s">
         <v>77</v>
@@ -26649,7 +26676,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O29" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -26682,19 +26709,19 @@
         <v>77</v>
       </c>
       <c r="E30" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="J30" s="16" t="s">
         <v>77</v>
@@ -26708,7 +26735,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O30" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -26741,19 +26768,19 @@
         <v>77</v>
       </c>
       <c r="E31" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="J31" s="16" t="s">
         <v>77</v>
@@ -26767,7 +26794,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O31" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -26800,19 +26827,19 @@
         <v>77</v>
       </c>
       <c r="E32" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F32" s="14">
+        <v>1</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="F32" s="14">
-        <v>1</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="J32" s="16" t="s">
         <v>77</v>
@@ -26826,7 +26853,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O32" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -26859,19 +26886,19 @@
         <v>77</v>
       </c>
       <c r="E33" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" s="14">
+        <v>1</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="F33" s="14">
-        <v>1</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="J33" s="16" t="s">
         <v>77</v>
@@ -26885,7 +26912,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O33" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -26918,19 +26945,19 @@
         <v>77</v>
       </c>
       <c r="E34" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" s="14">
+        <v>1</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="F34" s="14">
-        <v>1</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="J34" s="16" t="s">
         <v>77</v>
@@ -26944,7 +26971,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O34" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -26977,7 +27004,7 @@
         <v>77</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F35" s="14">
         <v>1</v>
@@ -26989,7 +27016,7 @@
         <v>77</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J35" s="16" t="s">
         <v>77</v>
@@ -27003,7 +27030,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O35" t="str">
         <f t="shared" ref="O35:O36" ca="1" si="5">IF(N35&lt;0,"ATRASADO",IF(N35&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27036,7 +27063,7 @@
         <v>77</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F36" s="14">
         <v>1</v>
@@ -27048,7 +27075,7 @@
         <v>77</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>77</v>
@@ -27062,7 +27089,7 @@
       <c r="N36" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O36" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -27095,7 +27122,7 @@
         <v>77</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F37" s="14">
         <v>1</v>
@@ -27107,7 +27134,7 @@
         <v>77</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J37" s="16" t="s">
         <v>77</v>
@@ -27121,7 +27148,7 @@
       <c r="N37" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O37" t="str">
         <f ca="1">IF(N37&lt;0,"ATRASADO",IF(N37&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27154,7 +27181,7 @@
         <v>77</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F38" s="14">
         <v>1</v>
@@ -27166,7 +27193,7 @@
         <v>77</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J38" s="16" t="s">
         <v>77</v>
@@ -27180,7 +27207,7 @@
       <c r="N38" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O38" t="str">
         <f t="shared" ref="O38:O52" ca="1" si="6">IF(N38&lt;0,"ATRASADO",IF(N38&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27213,7 +27240,7 @@
         <v>77</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F39" s="14">
         <v>1</v>
@@ -27225,7 +27252,7 @@
         <v>77</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J39" s="16" t="s">
         <v>77</v>
@@ -27239,7 +27266,7 @@
       <c r="N39" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O39" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27272,7 +27299,7 @@
         <v>77</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F40" s="14">
         <v>1</v>
@@ -27284,7 +27311,7 @@
         <v>77</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J40" s="16" t="s">
         <v>77</v>
@@ -27298,7 +27325,7 @@
       <c r="N40" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27331,7 +27358,7 @@
         <v>77</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F41" s="14">
         <v>1</v>
@@ -27343,7 +27370,7 @@
         <v>77</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J41" s="16" t="s">
         <v>77</v>
@@ -27357,7 +27384,7 @@
       <c r="N41" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O41" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27390,7 +27417,7 @@
         <v>77</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F42" s="14">
         <v>1</v>
@@ -27402,7 +27429,7 @@
         <v>77</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J42" s="16" t="s">
         <v>77</v>
@@ -27416,7 +27443,7 @@
       <c r="N42" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O42" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27449,7 +27476,7 @@
         <v>77</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F43" s="14">
         <v>1</v>
@@ -27461,7 +27488,7 @@
         <v>77</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J43" s="16" t="s">
         <v>77</v>
@@ -27475,7 +27502,7 @@
       <c r="N43" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O43" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27508,7 +27535,7 @@
         <v>77</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F44" s="14">
         <v>1</v>
@@ -27520,7 +27547,7 @@
         <v>77</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J44" s="16" t="s">
         <v>77</v>
@@ -27534,7 +27561,7 @@
       <c r="N44" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O44" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27567,7 +27594,7 @@
         <v>77</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F45" s="14">
         <v>1</v>
@@ -27579,7 +27606,7 @@
         <v>77</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J45" s="16" t="s">
         <v>77</v>
@@ -27593,7 +27620,7 @@
       <c r="N45" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O45" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27626,7 +27653,7 @@
         <v>77</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F46" s="14">
         <v>1</v>
@@ -27638,7 +27665,7 @@
         <v>77</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J46" s="16" t="s">
         <v>77</v>
@@ -27652,7 +27679,7 @@
       <c r="N46" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O46" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27685,7 +27712,7 @@
         <v>77</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F47" s="14">
         <v>1</v>
@@ -27697,7 +27724,7 @@
         <v>77</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J47" s="16" t="s">
         <v>77</v>
@@ -27711,7 +27738,7 @@
       <c r="N47" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O47" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27744,7 +27771,7 @@
         <v>77</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F48" s="14">
         <v>1</v>
@@ -27756,7 +27783,7 @@
         <v>77</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J48" s="16" t="s">
         <v>77</v>
@@ -27770,7 +27797,7 @@
       <c r="N48" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O48" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27803,7 +27830,7 @@
         <v>77</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F49" s="14">
         <v>1</v>
@@ -27815,7 +27842,7 @@
         <v>77</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J49" s="16" t="s">
         <v>77</v>
@@ -27829,7 +27856,7 @@
       <c r="N49" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O49" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27862,7 +27889,7 @@
         <v>77</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F50" s="14">
         <v>1</v>
@@ -27874,7 +27901,7 @@
         <v>77</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J50" s="16" t="s">
         <v>77</v>
@@ -27888,7 +27915,7 @@
       <c r="N50" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O50" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27921,7 +27948,7 @@
         <v>77</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F51" s="14">
         <v>1</v>
@@ -27933,7 +27960,7 @@
         <v>77</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J51" s="16" t="s">
         <v>77</v>
@@ -27947,7 +27974,7 @@
       <c r="N51" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O51" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -27980,7 +28007,7 @@
         <v>77</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F52" s="14">
         <v>1</v>
@@ -27992,7 +28019,7 @@
         <v>77</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J52" s="16" t="s">
         <v>77</v>
@@ -28006,7 +28033,7 @@
       <c r="N52" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O52" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -28046,7 +28073,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9730F04C-E101-46F3-A942-AC61D67D9938}">
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" style="10" bestFit="1" customWidth="1"/>
@@ -28056,11 +28083,11 @@
     <col min="5" max="5" width="100.85546875" style="30" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" style="10" customWidth="1"/>
     <col min="7" max="7" width="7.140625" style="10" customWidth="1"/>
-    <col min="8" max="12" width="16.7109375" style="10" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="16" width="16.7109375" style="10" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -28083,27 +28110,39 @@
         <v>129</v>
       </c>
       <c r="H1" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="P1" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="Q1" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="J1" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="M1" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="23">
         <v>27108</v>
       </c>
@@ -28111,42 +28150,46 @@
         <v>1</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D2" s="23">
         <v>299368</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F2" s="25">
         <v>45964</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H2" s="25">
         <v>46220</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="25"/>
+      <c r="J2" s="25">
         <v>46227</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K2" s="25"/>
       <c r="L2" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M2" s="23">
+      <c r="Q2" s="23">
         <v>285</v>
       </c>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>27330</v>
       </c>
@@ -28154,42 +28197,46 @@
         <v>1</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D3" s="23">
         <v>299368</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F3" s="25">
         <v>46108</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H3" s="25">
         <v>46220</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="25"/>
+      <c r="J3" s="25">
         <v>46227</v>
       </c>
-      <c r="J3" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K3" s="25"/>
       <c r="L3" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M3" s="23">
+      <c r="Q3" s="23">
         <v>285</v>
       </c>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="27">
         <v>27507</v>
       </c>
@@ -28197,42 +28244,46 @@
         <v>1</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D4" s="23">
         <v>1449018</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F4" s="25">
         <v>46195</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H4" s="25">
         <v>46196</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="25"/>
+      <c r="J4" s="25">
         <v>46202</v>
       </c>
-      <c r="J4" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K4" s="25"/>
       <c r="L4" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M4" s="23">
+      <c r="Q4" s="23">
         <v>496</v>
       </c>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="27">
         <v>27507</v>
       </c>
@@ -28240,42 +28291,46 @@
         <v>2</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D5" s="23">
         <v>1449018</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F5" s="25">
         <v>46195</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H5" s="25">
         <v>46196</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="25"/>
+      <c r="J5" s="25">
         <v>46202</v>
       </c>
-      <c r="J5" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K5" s="25"/>
       <c r="L5" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="23">
+      <c r="Q5" s="23">
         <v>496</v>
       </c>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R5" s="26"/>
+      <c r="S5" s="26"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="23">
         <v>27522</v>
       </c>
@@ -28283,42 +28338,46 @@
         <v>1</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D6" s="23">
         <v>299374</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F6" s="25">
         <v>46204</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H6" s="25">
         <v>46192</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="25"/>
+      <c r="J6" s="25">
         <v>46197</v>
       </c>
-      <c r="J6" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K6" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K6" s="25"/>
       <c r="L6" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M6" s="23">
+      <c r="Q6" s="23">
         <v>285</v>
       </c>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R6" s="26"/>
+      <c r="S6" s="26"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="23">
         <v>27473</v>
       </c>
@@ -28326,44 +28385,54 @@
         <v>1</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D7" s="23">
         <v>1281005</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F7" s="25">
         <v>46209</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H7" s="25">
         <v>46192</v>
       </c>
       <c r="I7" s="25">
+        <v>46196</v>
+      </c>
+      <c r="J7" s="25">
         <v>46199</v>
       </c>
-      <c r="J7" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K7" s="25"/>
       <c r="L7" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="M7" s="23">
+        <v>77</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q7" s="23">
         <v>493</v>
       </c>
-      <c r="N7" s="26">
+      <c r="R7" s="26">
         <v>285</v>
       </c>
-      <c r="O7" s="26"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S7" s="26"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
         <v>27473</v>
       </c>
@@ -28371,44 +28440,54 @@
         <v>2</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D8" s="23">
         <v>1281006</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F8" s="25">
         <v>46209</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H8" s="25">
         <v>46192</v>
       </c>
       <c r="I8" s="25">
+        <v>46196</v>
+      </c>
+      <c r="J8" s="25">
         <v>46199</v>
       </c>
-      <c r="J8" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K8" s="25"/>
       <c r="L8" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" s="23">
+        <v>77</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N8" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q8" s="23">
         <v>124</v>
       </c>
-      <c r="N8" s="26">
+      <c r="R8" s="26">
         <v>433</v>
       </c>
-      <c r="O8" s="26"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S8" s="26"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="23">
         <v>27473</v>
       </c>
@@ -28416,46 +28495,54 @@
         <v>3</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D9" s="23">
         <v>1281007</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F9" s="25">
         <v>46209</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H9" s="25">
         <v>46192</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="25"/>
+      <c r="J9" s="25">
         <v>46199</v>
       </c>
-      <c r="J9" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K9" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K9" s="25"/>
       <c r="L9" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M9" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O9" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="23">
+      <c r="Q9" s="23">
         <v>112</v>
       </c>
-      <c r="N9" s="26">
+      <c r="R9" s="26">
         <v>124</v>
       </c>
-      <c r="O9" s="26">
+      <c r="S9" s="26">
         <v>433</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="23">
         <v>27473</v>
       </c>
@@ -28463,46 +28550,54 @@
         <v>4</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D10" s="23">
         <v>1281007</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F10" s="25">
         <v>46209</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H10" s="25">
         <v>46192</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="25"/>
+      <c r="J10" s="25">
         <v>46199</v>
       </c>
-      <c r="J10" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K10" s="25"/>
       <c r="L10" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N10" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O10" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P10" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M10" s="23">
+      <c r="Q10" s="23">
         <v>112</v>
       </c>
-      <c r="N10" s="26">
+      <c r="R10" s="26">
         <v>124</v>
       </c>
-      <c r="O10" s="26">
+      <c r="S10" s="26">
         <v>433</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="23">
         <v>27473</v>
       </c>
@@ -28510,46 +28605,54 @@
         <v>5</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D11" s="23">
         <v>1281007</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F11" s="25">
         <v>46209</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H11" s="25">
         <v>46192</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="25"/>
+      <c r="J11" s="25">
         <v>46199</v>
       </c>
-      <c r="J11" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K11" s="25"/>
       <c r="L11" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M11" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N11" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O11" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P11" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M11" s="23">
+      <c r="Q11" s="23">
         <v>112</v>
       </c>
-      <c r="N11" s="26">
+      <c r="R11" s="26">
         <v>124</v>
       </c>
-      <c r="O11" s="26">
+      <c r="S11" s="26">
         <v>433</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="23">
         <v>27473</v>
       </c>
@@ -28557,46 +28660,54 @@
         <v>6</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D12" s="23">
         <v>1281007</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F12" s="25">
         <v>46209</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H12" s="25">
         <v>46192</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="25"/>
+      <c r="J12" s="25">
         <v>46199</v>
       </c>
-      <c r="J12" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K12" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K12" s="25"/>
       <c r="L12" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N12" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O12" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P12" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M12" s="23">
+      <c r="Q12" s="23">
         <v>112</v>
       </c>
-      <c r="N12" s="26">
+      <c r="R12" s="26">
         <v>124</v>
       </c>
-      <c r="O12" s="26">
+      <c r="S12" s="26">
         <v>433</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="23">
         <v>27473</v>
       </c>
@@ -28604,46 +28715,54 @@
         <v>7</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D13" s="23">
         <v>1281007</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F13" s="25">
         <v>46209</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H13" s="25">
         <v>46192</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="25"/>
+      <c r="J13" s="25">
         <v>46199</v>
       </c>
-      <c r="J13" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K13" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K13" s="25"/>
       <c r="L13" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M13" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O13" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P13" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M13" s="23">
+      <c r="Q13" s="23">
         <v>112</v>
       </c>
-      <c r="N13" s="26">
+      <c r="R13" s="26">
         <v>124</v>
       </c>
-      <c r="O13" s="26">
+      <c r="S13" s="26">
         <v>433</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
         <v>27473</v>
       </c>
@@ -28651,46 +28770,56 @@
         <v>8</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D14" s="23">
         <v>1281008</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F14" s="25">
         <v>46209</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H14" s="25">
         <v>46192</v>
       </c>
       <c r="I14" s="25">
+        <v>46196</v>
+      </c>
+      <c r="J14" s="25">
         <v>46199</v>
       </c>
-      <c r="J14" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K14" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K14" s="25"/>
       <c r="L14" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="M14" s="23">
+        <v>77</v>
+      </c>
+      <c r="M14" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N14" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O14" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P14" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q14" s="23">
         <v>112</v>
       </c>
-      <c r="N14" s="26">
+      <c r="R14" s="26">
         <v>124</v>
       </c>
-      <c r="O14" s="26">
+      <c r="S14" s="26">
         <v>433</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="27">
         <v>27416</v>
       </c>
@@ -28698,42 +28827,46 @@
         <v>1</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D15" s="23">
         <v>392291</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F15" s="25">
         <v>46211</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H15" s="29">
         <v>46197</v>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="29"/>
+      <c r="J15" s="29">
         <v>46204</v>
       </c>
-      <c r="J15" s="29">
+      <c r="K15" s="29"/>
+      <c r="L15" s="29">
         <v>46211</v>
       </c>
-      <c r="K15" s="29">
+      <c r="M15" s="29"/>
+      <c r="N15" s="29">
         <v>46218</v>
       </c>
-      <c r="L15" s="25" t="s">
+      <c r="O15" s="29"/>
+      <c r="P15" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M15" s="26">
+      <c r="Q15" s="26">
         <v>493</v>
       </c>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
         <v>27476</v>
       </c>
@@ -28741,44 +28874,48 @@
         <v>1</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D16" s="23">
         <v>299529</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F16" s="25">
         <v>46217</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H16" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J16" s="25">
+      <c r="I16" s="25"/>
+      <c r="J16" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25">
         <v>46205</v>
       </c>
-      <c r="K16" s="25">
+      <c r="M16" s="25"/>
+      <c r="N16" s="25">
         <v>46216</v>
       </c>
-      <c r="L16" s="25" t="s">
+      <c r="O16" s="25"/>
+      <c r="P16" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M16" s="23">
+      <c r="Q16" s="23">
         <v>285</v>
       </c>
-      <c r="N16" s="26">
+      <c r="R16" s="26">
         <v>327</v>
       </c>
-      <c r="O16" s="26"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S16" s="26"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="23">
         <v>27490</v>
       </c>
@@ -28786,42 +28923,46 @@
         <v>1</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D17" s="23">
         <v>299302</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F17" s="25">
         <v>46218</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H17" s="25">
         <v>46189</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="25"/>
+      <c r="J17" s="25">
         <v>46199</v>
       </c>
-      <c r="J17" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K17" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K17" s="25"/>
       <c r="L17" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="23">
+      <c r="Q17" s="23">
         <v>496</v>
       </c>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R17" s="26"/>
+      <c r="S17" s="26"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="27">
         <v>27416</v>
       </c>
@@ -28829,42 +28970,46 @@
         <v>2</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D18" s="23">
         <v>392292</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F18" s="25">
         <v>46218</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H18" s="25">
         <v>46204</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="25"/>
+      <c r="J18" s="25">
         <v>46211</v>
       </c>
-      <c r="J18" s="25">
+      <c r="K18" s="25"/>
+      <c r="L18" s="25">
         <v>46218</v>
       </c>
-      <c r="K18" s="25">
+      <c r="M18" s="25"/>
+      <c r="N18" s="25">
         <v>46225</v>
       </c>
-      <c r="L18" s="25" t="s">
+      <c r="O18" s="25"/>
+      <c r="P18" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M18" s="23">
+      <c r="Q18" s="23">
         <v>493</v>
       </c>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R18" s="26"/>
+      <c r="S18" s="26"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="23">
         <v>27521</v>
       </c>
@@ -28872,42 +29017,46 @@
         <v>1</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D19" s="23">
         <v>299303</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F19" s="25">
         <v>46227</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H19" s="25">
         <v>46199</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="25"/>
+      <c r="J19" s="25">
         <v>46206</v>
       </c>
-      <c r="J19" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K19" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K19" s="25"/>
       <c r="L19" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M19" s="23">
+      <c r="Q19" s="23">
         <v>496</v>
       </c>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R19" s="26"/>
+      <c r="S19" s="26"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="23">
         <v>26974</v>
       </c>
@@ -28915,42 +29064,46 @@
         <v>3</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D20" s="23">
         <v>299217</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F20" s="25">
         <v>46228</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H20" s="25">
         <v>46206</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="25"/>
+      <c r="J20" s="25">
         <v>46213</v>
       </c>
-      <c r="J20" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K20" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K20" s="25"/>
       <c r="L20" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M20" s="23">
+      <c r="Q20" s="23">
         <v>285</v>
       </c>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R20" s="26"/>
+      <c r="S20" s="26"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="23">
         <v>26970</v>
       </c>
@@ -28958,42 +29111,46 @@
         <v>3</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D21" s="23">
         <v>299209</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F21" s="25">
         <v>46228</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H21" s="25">
         <v>46213</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="25"/>
+      <c r="J21" s="25">
         <v>46220</v>
       </c>
-      <c r="J21" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K21" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K21" s="25"/>
       <c r="L21" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M21" s="23">
+      <c r="Q21" s="23">
         <v>285</v>
       </c>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R21" s="26"/>
+      <c r="S21" s="26"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="23">
         <v>26641</v>
       </c>
@@ -29001,42 +29158,46 @@
         <v>2</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D22" s="23">
         <v>299217</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F22" s="25">
         <v>46228</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H22" s="25">
         <v>46206</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="25"/>
+      <c r="J22" s="25">
         <v>46213</v>
       </c>
-      <c r="J22" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K22" s="25"/>
       <c r="L22" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M22" s="23">
+      <c r="Q22" s="23">
         <v>285</v>
       </c>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="23">
         <v>27547</v>
       </c>
@@ -29044,44 +29205,48 @@
         <v>1</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D23" s="23">
         <v>1573002</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F23" s="25">
         <v>46233</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H23" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I23" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J23" s="25">
+      <c r="I23" s="25"/>
+      <c r="J23" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25">
         <v>46220</v>
       </c>
-      <c r="K23" s="25">
+      <c r="M23" s="25"/>
+      <c r="N23" s="25">
         <v>46232</v>
       </c>
-      <c r="L23" s="25" t="s">
+      <c r="O23" s="25"/>
+      <c r="P23" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M23" s="23">
+      <c r="Q23" s="23">
         <v>493</v>
       </c>
-      <c r="N23" s="26">
+      <c r="R23" s="26">
         <v>112</v>
       </c>
-      <c r="O23" s="26"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S23" s="26"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="23">
         <v>27547</v>
       </c>
@@ -29089,44 +29254,48 @@
         <v>2</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D24" s="23">
         <v>1573001</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F24" s="25">
         <v>46233</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H24" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I24" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J24" s="25">
+      <c r="I24" s="25"/>
+      <c r="J24" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25">
         <v>46220</v>
       </c>
-      <c r="K24" s="25">
+      <c r="M24" s="25"/>
+      <c r="N24" s="25">
         <v>46232</v>
       </c>
-      <c r="L24" s="25" t="s">
+      <c r="O24" s="25"/>
+      <c r="P24" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M24" s="23">
+      <c r="Q24" s="23">
         <v>493</v>
       </c>
-      <c r="N24" s="26">
+      <c r="R24" s="26">
         <v>112</v>
       </c>
-      <c r="O24" s="26"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S24" s="26"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="23">
         <v>27575</v>
       </c>
@@ -29134,44 +29303,48 @@
         <v>1</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D25" s="23">
         <v>774016</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F25" s="25">
         <v>46239</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H25" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I25" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J25" s="25">
+      <c r="I25" s="25"/>
+      <c r="J25" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25">
         <v>46220</v>
       </c>
-      <c r="K25" s="25">
+      <c r="M25" s="25"/>
+      <c r="N25" s="25">
         <v>46238</v>
       </c>
-      <c r="L25" s="25" t="s">
+      <c r="O25" s="25"/>
+      <c r="P25" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M25" s="23">
+      <c r="Q25" s="23">
         <v>285</v>
       </c>
-      <c r="N25" s="26">
+      <c r="R25" s="26">
         <v>493</v>
       </c>
-      <c r="O25" s="26"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S25" s="26"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="23">
         <v>27575</v>
       </c>
@@ -29179,44 +29352,48 @@
         <v>2</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D26" s="23">
         <v>774016</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F26" s="25">
         <v>46239</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H26" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I26" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J26" s="25">
+      <c r="I26" s="25"/>
+      <c r="J26" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25">
         <v>46220</v>
       </c>
-      <c r="K26" s="25">
+      <c r="M26" s="25"/>
+      <c r="N26" s="25">
         <v>46238</v>
       </c>
-      <c r="L26" s="25" t="s">
+      <c r="O26" s="25"/>
+      <c r="P26" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M26" s="23">
+      <c r="Q26" s="23">
         <v>285</v>
       </c>
-      <c r="N26" s="26">
+      <c r="R26" s="26">
         <v>493</v>
       </c>
-      <c r="O26" s="26"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S26" s="26"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="23">
         <v>27575</v>
       </c>
@@ -29224,44 +29401,48 @@
         <v>3</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D27" s="23">
         <v>774017</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F27" s="25">
         <v>46239</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H27" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I27" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J27" s="25">
+      <c r="I27" s="25"/>
+      <c r="J27" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25">
         <v>46220</v>
       </c>
-      <c r="K27" s="25">
+      <c r="M27" s="25"/>
+      <c r="N27" s="25">
         <v>46238</v>
       </c>
-      <c r="L27" s="25" t="s">
+      <c r="O27" s="25"/>
+      <c r="P27" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M27" s="23">
+      <c r="Q27" s="23">
         <v>285</v>
       </c>
-      <c r="N27" s="26">
+      <c r="R27" s="26">
         <v>493</v>
       </c>
-      <c r="O27" s="26"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S27" s="26"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="23">
         <v>27575</v>
       </c>
@@ -29269,44 +29450,48 @@
         <v>4</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D28" s="23">
         <v>774017</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F28" s="25">
         <v>46239</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H28" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J28" s="25">
+      <c r="I28" s="25"/>
+      <c r="J28" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25">
         <v>46220</v>
       </c>
-      <c r="K28" s="25">
+      <c r="M28" s="25"/>
+      <c r="N28" s="25">
         <v>46238</v>
       </c>
-      <c r="L28" s="25" t="s">
+      <c r="O28" s="25"/>
+      <c r="P28" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M28" s="23">
+      <c r="Q28" s="23">
         <v>285</v>
       </c>
-      <c r="N28" s="26">
+      <c r="R28" s="26">
         <v>493</v>
       </c>
-      <c r="O28" s="26"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S28" s="26"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="23">
         <v>27524</v>
       </c>
@@ -29314,44 +29499,48 @@
         <v>1</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D29" s="23">
         <v>299528</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F29" s="25">
         <v>46245</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H29" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I29" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J29" s="25">
+      <c r="I29" s="25"/>
+      <c r="J29" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25">
         <v>46234</v>
       </c>
-      <c r="K29" s="25">
+      <c r="M29" s="25"/>
+      <c r="N29" s="25">
         <v>46244</v>
       </c>
-      <c r="L29" s="25" t="s">
+      <c r="O29" s="25"/>
+      <c r="P29" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M29" s="23">
+      <c r="Q29" s="23">
         <v>285</v>
       </c>
-      <c r="N29" s="26">
+      <c r="R29" s="26">
         <v>327</v>
       </c>
-      <c r="O29" s="26"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S29" s="26"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="23">
         <v>27587</v>
       </c>
@@ -29359,42 +29548,46 @@
         <v>1</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D30" s="23">
         <v>1608001</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F30" s="25">
         <v>46246</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H30" s="25">
         <v>46213</v>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="25"/>
+      <c r="J30" s="25">
         <v>46226</v>
       </c>
-      <c r="J30" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K30" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K30" s="25"/>
       <c r="L30" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M30" s="23">
+      <c r="Q30" s="23">
         <v>124</v>
       </c>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
         <v>27587</v>
       </c>
@@ -29402,42 +29595,46 @@
         <v>2</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D31" s="23">
         <v>1608002</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F31" s="25">
         <v>46246</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H31" s="25">
         <v>46213</v>
       </c>
-      <c r="I31" s="25">
+      <c r="I31" s="25"/>
+      <c r="J31" s="25">
         <v>46226</v>
       </c>
-      <c r="J31" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K31" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K31" s="25"/>
       <c r="L31" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M31" s="23">
+      <c r="Q31" s="23">
         <v>124</v>
       </c>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
         <v>27587</v>
       </c>
@@ -29445,42 +29642,46 @@
         <v>3</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D32" s="23">
         <v>1608002</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F32" s="25">
         <v>46246</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H32" s="25">
         <v>46213</v>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="25"/>
+      <c r="J32" s="25">
         <v>46226</v>
       </c>
-      <c r="J32" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K32" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="K32" s="25"/>
       <c r="L32" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M32" s="23">
+      <c r="Q32" s="23">
         <v>124</v>
       </c>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R32" s="26"/>
+      <c r="S32" s="26"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="23">
         <v>27593</v>
       </c>
@@ -29488,44 +29689,48 @@
         <v>1</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D33" s="23">
         <v>1609001</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F33" s="25">
         <v>46253</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H33" s="29">
         <v>46213</v>
       </c>
-      <c r="I33" s="29">
+      <c r="I33" s="29"/>
+      <c r="J33" s="29">
         <v>46228</v>
       </c>
-      <c r="J33" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="K33" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="L33" s="25" t="s">
+      <c r="K33" s="29"/>
+      <c r="L33" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O33" s="26"/>
+      <c r="P33" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M33" s="26">
+      <c r="Q33" s="26">
         <v>327</v>
       </c>
-      <c r="N33" s="26">
+      <c r="R33" s="26">
         <v>393</v>
       </c>
-      <c r="O33" s="26"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S33" s="26"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="23">
         <v>27599</v>
       </c>
@@ -29533,42 +29738,46 @@
         <v>1</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D34" s="23">
         <v>299374</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F34" s="25">
         <v>46254</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H34" s="29">
         <v>46220</v>
       </c>
-      <c r="I34" s="29">
+      <c r="I34" s="29"/>
+      <c r="J34" s="29">
         <v>46234</v>
       </c>
-      <c r="J34" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="K34" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="L34" s="25" t="s">
+      <c r="K34" s="29"/>
+      <c r="L34" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O34" s="26"/>
+      <c r="P34" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M34" s="26">
+      <c r="Q34" s="26">
         <v>285</v>
       </c>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R34" s="26"/>
+      <c r="S34" s="26"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="23">
         <v>27542</v>
       </c>
@@ -29576,44 +29785,48 @@
         <v>1</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D35" s="23">
         <v>299528</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F35" s="25">
         <v>46255</v>
       </c>
       <c r="G35" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H35" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="I35" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J35" s="29">
+      <c r="I35" s="26"/>
+      <c r="J35" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K35" s="26"/>
+      <c r="L35" s="29">
         <v>46241</v>
       </c>
-      <c r="K35" s="29">
+      <c r="M35" s="29"/>
+      <c r="N35" s="29">
         <v>46254</v>
       </c>
-      <c r="L35" s="25" t="s">
+      <c r="O35" s="29"/>
+      <c r="P35" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M35" s="26">
+      <c r="Q35" s="26">
         <v>285</v>
       </c>
-      <c r="N35" s="26">
+      <c r="R35" s="26">
         <v>327</v>
       </c>
-      <c r="O35" s="26"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="S35" s="26"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
         <v>27600</v>
       </c>
@@ -29621,42 +29834,46 @@
         <v>1</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F36" s="25">
         <v>46259</v>
       </c>
       <c r="G36" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H36" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I36" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J36" s="29">
+      <c r="I36" s="29"/>
+      <c r="J36" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K36" s="26"/>
+      <c r="L36" s="29">
         <v>46248</v>
       </c>
-      <c r="K36" s="29">
+      <c r="M36" s="29"/>
+      <c r="N36" s="29">
         <v>46255</v>
       </c>
-      <c r="L36" s="25" t="s">
+      <c r="O36" s="29"/>
+      <c r="P36" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M36" s="26">
+      <c r="Q36" s="26">
         <v>285</v>
       </c>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R36" s="26"/>
+      <c r="S36" s="26"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="23">
         <v>27600</v>
       </c>
@@ -29664,42 +29881,46 @@
         <v>5</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F37" s="25">
         <v>46259</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H37" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I37" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J37" s="29">
+      <c r="I37" s="29"/>
+      <c r="J37" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K37" s="26"/>
+      <c r="L37" s="29">
         <v>46248</v>
       </c>
-      <c r="K37" s="29">
+      <c r="M37" s="29"/>
+      <c r="N37" s="29">
         <v>46255</v>
       </c>
-      <c r="L37" s="25" t="s">
+      <c r="O37" s="29"/>
+      <c r="P37" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M37" s="26">
+      <c r="Q37" s="26">
         <v>285</v>
       </c>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R37" s="26"/>
+      <c r="S37" s="26"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="23">
         <v>27600</v>
       </c>
@@ -29707,42 +29928,46 @@
         <v>9</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F38" s="25">
         <v>46259</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H38" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I38" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J38" s="29">
+      <c r="I38" s="29"/>
+      <c r="J38" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K38" s="26"/>
+      <c r="L38" s="29">
         <v>46248</v>
       </c>
-      <c r="K38" s="29">
+      <c r="M38" s="29"/>
+      <c r="N38" s="29">
         <v>46255</v>
       </c>
-      <c r="L38" s="25" t="s">
+      <c r="O38" s="29"/>
+      <c r="P38" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M38" s="26">
+      <c r="Q38" s="26">
         <v>285</v>
       </c>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R38" s="26"/>
+      <c r="S38" s="26"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="23">
         <v>27600</v>
       </c>
@@ -29750,42 +29975,46 @@
         <v>13</v>
       </c>
       <c r="C39" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>172</v>
       </c>
       <c r="F39" s="25">
         <v>46259</v>
       </c>
       <c r="G39" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H39" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I39" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J39" s="29">
+      <c r="I39" s="29"/>
+      <c r="J39" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K39" s="26"/>
+      <c r="L39" s="29">
         <v>46248</v>
       </c>
-      <c r="K39" s="29">
+      <c r="M39" s="29"/>
+      <c r="N39" s="29">
         <v>46255</v>
       </c>
-      <c r="L39" s="25" t="s">
+      <c r="O39" s="29"/>
+      <c r="P39" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M39" s="26">
+      <c r="Q39" s="26">
         <v>285</v>
       </c>
-      <c r="N39" s="26"/>
-      <c r="O39" s="26"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R39" s="26"/>
+      <c r="S39" s="26"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="23">
         <v>27600</v>
       </c>
@@ -29793,42 +30022,46 @@
         <v>2</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F40" s="25">
         <v>46269</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H40" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I40" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J40" s="29">
+      <c r="I40" s="29"/>
+      <c r="J40" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K40" s="26"/>
+      <c r="L40" s="29">
         <v>46248</v>
       </c>
-      <c r="K40" s="29">
+      <c r="M40" s="29"/>
+      <c r="N40" s="29">
         <v>46255</v>
       </c>
-      <c r="L40" s="25" t="s">
+      <c r="O40" s="29"/>
+      <c r="P40" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M40" s="26">
+      <c r="Q40" s="26">
         <v>285</v>
       </c>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R40" s="26"/>
+      <c r="S40" s="26"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="23">
         <v>27600</v>
       </c>
@@ -29836,42 +30069,46 @@
         <v>6</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F41" s="25">
         <v>46269</v>
       </c>
       <c r="G41" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H41" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I41" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J41" s="29">
+      <c r="I41" s="29"/>
+      <c r="J41" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K41" s="26"/>
+      <c r="L41" s="29">
         <v>46248</v>
       </c>
-      <c r="K41" s="29">
+      <c r="M41" s="29"/>
+      <c r="N41" s="29">
         <v>46255</v>
       </c>
-      <c r="L41" s="25" t="s">
+      <c r="O41" s="29"/>
+      <c r="P41" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M41" s="26">
+      <c r="Q41" s="26">
         <v>285</v>
       </c>
-      <c r="N41" s="26"/>
-      <c r="O41" s="26"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R41" s="26"/>
+      <c r="S41" s="26"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="23">
         <v>27600</v>
       </c>
@@ -29879,42 +30116,46 @@
         <v>10</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F42" s="25">
         <v>46269</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H42" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I42" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J42" s="29">
+      <c r="I42" s="29"/>
+      <c r="J42" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K42" s="26"/>
+      <c r="L42" s="29">
         <v>46248</v>
       </c>
-      <c r="K42" s="29">
+      <c r="M42" s="29"/>
+      <c r="N42" s="29">
         <v>46255</v>
       </c>
-      <c r="L42" s="25" t="s">
+      <c r="O42" s="29"/>
+      <c r="P42" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M42" s="26">
+      <c r="Q42" s="26">
         <v>285</v>
       </c>
-      <c r="N42" s="26"/>
-      <c r="O42" s="26"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R42" s="26"/>
+      <c r="S42" s="26"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="23">
         <v>27600</v>
       </c>
@@ -29922,42 +30163,46 @@
         <v>14</v>
       </c>
       <c r="C43" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E43" s="24" t="s">
-        <v>172</v>
       </c>
       <c r="F43" s="25">
         <v>46269</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H43" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I43" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J43" s="29">
+      <c r="I43" s="29"/>
+      <c r="J43" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K43" s="26"/>
+      <c r="L43" s="29">
         <v>46248</v>
       </c>
-      <c r="K43" s="29">
+      <c r="M43" s="29"/>
+      <c r="N43" s="29">
         <v>46255</v>
       </c>
-      <c r="L43" s="25" t="s">
+      <c r="O43" s="29"/>
+      <c r="P43" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M43" s="26">
+      <c r="Q43" s="26">
         <v>285</v>
       </c>
-      <c r="N43" s="26"/>
-      <c r="O43" s="26"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R43" s="26"/>
+      <c r="S43" s="26"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="23">
         <v>27496</v>
       </c>
@@ -29965,42 +30210,46 @@
         <v>1</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D44" s="23">
         <v>299208</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F44" s="25">
         <v>46269</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H44" s="29">
         <v>46206</v>
       </c>
-      <c r="I44" s="29">
+      <c r="I44" s="29"/>
+      <c r="J44" s="29">
         <v>46213</v>
       </c>
-      <c r="J44" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="K44" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="L44" s="25" t="s">
+      <c r="K44" s="29"/>
+      <c r="L44" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O44" s="26"/>
+      <c r="P44" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M44" s="26">
+      <c r="Q44" s="26">
         <v>285</v>
       </c>
-      <c r="N44" s="26"/>
-      <c r="O44" s="26"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R44" s="26"/>
+      <c r="S44" s="26"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="23">
         <v>27600</v>
       </c>
@@ -30008,42 +30257,46 @@
         <v>3</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D45" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F45" s="25">
         <v>46279</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H45" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I45" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J45" s="29">
+      <c r="I45" s="29"/>
+      <c r="J45" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K45" s="26"/>
+      <c r="L45" s="29">
         <v>46248</v>
       </c>
-      <c r="K45" s="29">
+      <c r="M45" s="29"/>
+      <c r="N45" s="29">
         <v>46255</v>
       </c>
-      <c r="L45" s="25" t="s">
+      <c r="O45" s="29"/>
+      <c r="P45" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M45" s="26">
+      <c r="Q45" s="26">
         <v>285</v>
       </c>
-      <c r="N45" s="26"/>
-      <c r="O45" s="26"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R45" s="26"/>
+      <c r="S45" s="26"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="23">
         <v>27600</v>
       </c>
@@ -30051,42 +30304,46 @@
         <v>7</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D46" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F46" s="25">
         <v>46279</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H46" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I46" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J46" s="29">
+      <c r="I46" s="29"/>
+      <c r="J46" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K46" s="26"/>
+      <c r="L46" s="29">
         <v>46248</v>
       </c>
-      <c r="K46" s="29">
+      <c r="M46" s="29"/>
+      <c r="N46" s="29">
         <v>46255</v>
       </c>
-      <c r="L46" s="25" t="s">
+      <c r="O46" s="29"/>
+      <c r="P46" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M46" s="26">
+      <c r="Q46" s="26">
         <v>285</v>
       </c>
-      <c r="N46" s="26"/>
-      <c r="O46" s="26"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R46" s="26"/>
+      <c r="S46" s="26"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="23">
         <v>27600</v>
       </c>
@@ -30094,42 +30351,46 @@
         <v>11</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E47" s="24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F47" s="25">
         <v>46279</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H47" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I47" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J47" s="29">
+      <c r="I47" s="29"/>
+      <c r="J47" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K47" s="26"/>
+      <c r="L47" s="29">
         <v>46248</v>
       </c>
-      <c r="K47" s="29">
+      <c r="M47" s="29"/>
+      <c r="N47" s="29">
         <v>46255</v>
       </c>
-      <c r="L47" s="25" t="s">
+      <c r="O47" s="29"/>
+      <c r="P47" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M47" s="26">
+      <c r="Q47" s="26">
         <v>285</v>
       </c>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R47" s="26"/>
+      <c r="S47" s="26"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="23">
         <v>27600</v>
       </c>
@@ -30137,42 +30398,46 @@
         <v>15</v>
       </c>
       <c r="C48" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E48" s="24" t="s">
-        <v>172</v>
       </c>
       <c r="F48" s="25">
         <v>46279</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H48" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I48" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J48" s="29">
+      <c r="I48" s="29"/>
+      <c r="J48" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K48" s="26"/>
+      <c r="L48" s="29">
         <v>46248</v>
       </c>
-      <c r="K48" s="29">
+      <c r="M48" s="29"/>
+      <c r="N48" s="29">
         <v>46255</v>
       </c>
-      <c r="L48" s="25" t="s">
+      <c r="O48" s="29"/>
+      <c r="P48" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M48" s="26">
+      <c r="Q48" s="26">
         <v>285</v>
       </c>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R48" s="26"/>
+      <c r="S48" s="26"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="23">
         <v>27600</v>
       </c>
@@ -30180,42 +30445,46 @@
         <v>4</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F49" s="25">
         <v>46289</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H49" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I49" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J49" s="29">
+      <c r="I49" s="29"/>
+      <c r="J49" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K49" s="26"/>
+      <c r="L49" s="29">
         <v>46248</v>
       </c>
-      <c r="K49" s="29">
+      <c r="M49" s="29"/>
+      <c r="N49" s="29">
         <v>46255</v>
       </c>
-      <c r="L49" s="25" t="s">
+      <c r="O49" s="29"/>
+      <c r="P49" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M49" s="26">
+      <c r="Q49" s="26">
         <v>285</v>
       </c>
-      <c r="N49" s="26"/>
-      <c r="O49" s="26"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R49" s="26"/>
+      <c r="S49" s="26"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="23">
         <v>27600</v>
       </c>
@@ -30223,42 +30492,46 @@
         <v>8</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F50" s="25">
         <v>46289</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H50" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I50" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J50" s="29">
+      <c r="I50" s="29"/>
+      <c r="J50" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K50" s="26"/>
+      <c r="L50" s="29">
         <v>46248</v>
       </c>
-      <c r="K50" s="29">
+      <c r="M50" s="29"/>
+      <c r="N50" s="29">
         <v>46255</v>
       </c>
-      <c r="L50" s="25" t="s">
+      <c r="O50" s="29"/>
+      <c r="P50" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M50" s="26">
+      <c r="Q50" s="26">
         <v>285</v>
       </c>
-      <c r="N50" s="26"/>
-      <c r="O50" s="26"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R50" s="26"/>
+      <c r="S50" s="26"/>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="23">
         <v>27600</v>
       </c>
@@ -30266,42 +30539,46 @@
         <v>12</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>77</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F51" s="25">
         <v>46289</v>
       </c>
       <c r="G51" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H51" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I51" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J51" s="29">
+      <c r="I51" s="29"/>
+      <c r="J51" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K51" s="26"/>
+      <c r="L51" s="29">
         <v>46248</v>
       </c>
-      <c r="K51" s="29">
+      <c r="M51" s="29"/>
+      <c r="N51" s="29">
         <v>46255</v>
       </c>
-      <c r="L51" s="25" t="s">
+      <c r="O51" s="29"/>
+      <c r="P51" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M51" s="26">
+      <c r="Q51" s="26">
         <v>285</v>
       </c>
-      <c r="N51" s="26"/>
-      <c r="O51" s="26"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R51" s="26"/>
+      <c r="S51" s="26"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="23">
         <v>27600</v>
       </c>
@@ -30309,42 +30586,46 @@
         <v>16</v>
       </c>
       <c r="C52" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="24" t="s">
         <v>168</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52" s="24" t="s">
-        <v>172</v>
       </c>
       <c r="F52" s="25">
         <v>46289</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H52" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="I52" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J52" s="29">
+      <c r="I52" s="29"/>
+      <c r="J52" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K52" s="26"/>
+      <c r="L52" s="29">
         <v>46248</v>
       </c>
-      <c r="K52" s="29">
+      <c r="M52" s="29"/>
+      <c r="N52" s="29">
         <v>46255</v>
       </c>
-      <c r="L52" s="25" t="s">
+      <c r="O52" s="29"/>
+      <c r="P52" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M52" s="26">
+      <c r="Q52" s="26">
         <v>285</v>
       </c>
-      <c r="N52" s="26"/>
-      <c r="O52" s="26"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R52" s="26"/>
+      <c r="S52" s="26"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="23">
         <v>27597</v>
       </c>
@@ -30352,45 +30633,49 @@
         <v>1</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D53" s="23">
         <v>299303</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F53" s="25">
         <v>46332</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H53" s="29">
         <v>46297</v>
       </c>
-      <c r="I53" s="29">
+      <c r="I53" s="29"/>
+      <c r="J53" s="29">
         <v>46307</v>
       </c>
-      <c r="J53" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="K53" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="L53" s="25" t="s">
+      <c r="K53" s="29"/>
+      <c r="L53" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M53" s="26"/>
+      <c r="N53" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O53" s="26"/>
+      <c r="P53" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="M53" s="26">
+      <c r="Q53" s="26">
         <v>496</v>
       </c>
-      <c r="N53" s="26"/>
-      <c r="O53" s="26"/>
+      <c r="R53" s="26"/>
+      <c r="S53" s="26"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K53" xr:uid="{276B14C1-1A52-4B27-91DF-D329FDD63C7A}"/>
+  <autoFilter ref="A1:N53" xr:uid="{276B14C1-1A52-4B27-91DF-D329FDD63C7A}"/>
   <mergeCells count="1">
-    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="Q1:S1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0555F201-61D5-462D-B394-953A92FC63D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F911457-1A8B-45F8-8834-897DDC8D8F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
   <sheets>
     <sheet name="BAGACEIRAS" sheetId="2" r:id="rId1"/>
     <sheet name="PENTES" sheetId="8" r:id="rId2"/>
     <sheet name="RODETES NOVOS" sheetId="6" r:id="rId3"/>
     <sheet name="PERIFÉRICOS" sheetId="9" r:id="rId4"/>
-    <sheet name="CAMISAS NOVAS" sheetId="7" r:id="rId5"/>
+    <sheet name="CAMISAS" sheetId="7" r:id="rId5"/>
     <sheet name="VI DIVERSOS" sheetId="10" r:id="rId6"/>
     <sheet name="PLANEJADO BAGACEIRA" sheetId="5" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'VI DIVERSOS'!$A$1:$N$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BAGACEIRAS!$A$1:$AI$108</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Tabela1[#All]</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">BAGACEIRAS!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3484" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4222" uniqueCount="222">
   <si>
     <t>O.S.</t>
   </si>
@@ -668,6 +668,81 @@
     <t>Prazo Usin. Real
 (Acabamento)</t>
   </si>
+  <si>
+    <t>Santa Terezinha Terra Rica</t>
+  </si>
+  <si>
+    <t>Suporte da Bagaceira - 78"</t>
+  </si>
+  <si>
+    <t>PRONTO</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>PEÇA</t>
+  </si>
+  <si>
+    <t>Ipiranga Passos</t>
+  </si>
+  <si>
+    <t>BAGACEIRA 66"C/ SOLDA DURA</t>
+  </si>
+  <si>
+    <t>Calha Alta Drenagem Inox - 66"</t>
+  </si>
+  <si>
+    <t>Flange Rolo Sup. Alta Drenagem 66" - 1T</t>
+  </si>
+  <si>
+    <t>Flange Rolo Sup. Alta Drenagem 66" - 5T</t>
+  </si>
+  <si>
+    <t>Munhão c/ Inox - 66"</t>
+  </si>
+  <si>
+    <t>Suporte da Bagaceira - 66"</t>
+  </si>
+  <si>
+    <t>Kit Vedação Borracha SUP - 66"</t>
+  </si>
+  <si>
+    <t>Kit Vedação Borracha INF - 66"</t>
+  </si>
+  <si>
+    <t>Arruela  do Flange - 66"</t>
+  </si>
+  <si>
+    <t>Parafuso do Flange - 66"</t>
+  </si>
+  <si>
+    <t>Chaveta 63 x 38 x 400</t>
+  </si>
+  <si>
+    <t>Kit Vedação Metálica - 66"</t>
+  </si>
+  <si>
+    <t>Bucha Mancal RP - 66"</t>
+  </si>
+  <si>
+    <t>Substituição Elementos Fixações - 66"</t>
+  </si>
+  <si>
+    <t>RNC</t>
+  </si>
+  <si>
+    <t>PENTE SUPERIOR CONVENCIONAL FR 2"- 66"</t>
+  </si>
+  <si>
+    <t>PENTE INFERIOR CONVENCIONAL FR 2"- 66"</t>
+  </si>
+  <si>
+    <t>PENTE SUPERIOR CONVENCIONAL FR 1.5" - 66"</t>
+  </si>
+  <si>
+    <t>PENTE INFERIOR CONVENCIONAL FR 1.5" - 66"</t>
+  </si>
 </sst>
 </file>
 
@@ -824,7 +899,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -957,6 +1032,36 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2546,8 +2651,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI109" totalsRowShown="0" headerRowDxfId="110" dataDxfId="109">
-  <autoFilter ref="A1:AI109" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="110" dataDxfId="109">
+  <autoFilter ref="A1:AI114" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}"/>
   <tableColumns count="35">
     <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="108"/>
     <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="107"/>
@@ -2603,8 +2708,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V91" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72">
-  <autoFilter ref="A1:V91" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V131" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72">
+  <autoFilter ref="A1:V131" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="71"/>
     <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="70"/>
@@ -2687,8 +2792,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T52" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="A1:T52" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T88" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="A1:T88" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{56D3DA8E-4CA8-4DC6-8208-BAB93CDE51C0}" name="PV" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{B14AE1B6-8C05-4725-BF42-3DBDB37AA4E3}" name="item" dataDxfId="18"/>
@@ -3037,7 +3142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6140998E-DB8E-4214-BEB3-FBC60CB296CA}">
-  <dimension ref="A1:AI109"/>
+  <dimension ref="A1:AI114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="6.7109375" style="10" customWidth="1"/>
@@ -15041,6 +15146,501 @@
       <c r="AH109" s="46"/>
       <c r="AI109" s="47"/>
     </row>
+    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A110" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B110" s="15">
+        <v>58</v>
+      </c>
+      <c r="C110" s="15">
+        <v>27616</v>
+      </c>
+      <c r="D110" s="15">
+        <v>52</v>
+      </c>
+      <c r="E110" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F110" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G110" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H110" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="I110" s="15">
+        <v>1</v>
+      </c>
+      <c r="J110" s="16">
+        <v>46295</v>
+      </c>
+      <c r="K110" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Fundido]])</f>
+        <v>40</v>
+      </c>
+      <c r="L110" s="52"/>
+      <c r="M110" s="16">
+        <v>46356</v>
+      </c>
+      <c r="N110" s="42">
+        <f ca="1">Tabela1[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O110" s="42" t="str">
+        <f ca="1">IF(N110&lt;0,"ATRASADO",IF(N110&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P110" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Entrega]],1)</f>
+        <v>49</v>
+      </c>
+      <c r="Q110" s="52"/>
+      <c r="R110" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S110" s="43">
+        <v>46233</v>
+      </c>
+      <c r="T110" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="U110" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="V110" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="W110" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="X110" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y110" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z110" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA110" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB110" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC110" s="55" t="str">
+        <f>IF(L110="","AG. FUNDIDO",IF(U110="AG","AG. USINAGEM","EM USINAGEM"))</f>
+        <v>AG. FUNDIDO</v>
+      </c>
+      <c r="AD110" s="52"/>
+      <c r="AE110" s="56"/>
+      <c r="AF110" s="57"/>
+      <c r="AG110" s="57"/>
+      <c r="AH110" s="57"/>
+      <c r="AI110" s="58"/>
+    </row>
+    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A111" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B111" s="15">
+        <v>59</v>
+      </c>
+      <c r="C111" s="15">
+        <v>27616</v>
+      </c>
+      <c r="D111" s="15">
+        <v>53</v>
+      </c>
+      <c r="E111" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G111" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="I111" s="15">
+        <v>1</v>
+      </c>
+      <c r="J111" s="16">
+        <v>46295</v>
+      </c>
+      <c r="K111" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Fundido]])</f>
+        <v>40</v>
+      </c>
+      <c r="L111" s="52"/>
+      <c r="M111" s="16">
+        <v>46356</v>
+      </c>
+      <c r="N111" s="42">
+        <f ca="1">Tabela1[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O111" s="42" t="str">
+        <f t="shared" ref="O111:O114" ca="1" si="12">IF(N111&lt;0,"ATRASADO",IF(N111&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P111" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Entrega]],1)</f>
+        <v>49</v>
+      </c>
+      <c r="Q111" s="52"/>
+      <c r="R111" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S111" s="43">
+        <v>46233</v>
+      </c>
+      <c r="T111" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="U111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="V111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="W111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="X111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC111" s="55" t="str">
+        <f t="shared" ref="AC111:AC114" si="13">IF(L111="","AG. FUNDIDO",IF(U111="AG","AG. USINAGEM","EM USINAGEM"))</f>
+        <v>AG. FUNDIDO</v>
+      </c>
+      <c r="AD111" s="52"/>
+      <c r="AE111" s="56"/>
+      <c r="AF111" s="57"/>
+      <c r="AG111" s="57"/>
+      <c r="AH111" s="57"/>
+      <c r="AI111" s="58"/>
+    </row>
+    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A112" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B112" s="15">
+        <v>60</v>
+      </c>
+      <c r="C112" s="15">
+        <v>27616</v>
+      </c>
+      <c r="D112" s="15">
+        <v>54</v>
+      </c>
+      <c r="E112" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G112" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H112" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="I112" s="15">
+        <v>1</v>
+      </c>
+      <c r="J112" s="16">
+        <v>46295</v>
+      </c>
+      <c r="K112" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Fundido]])</f>
+        <v>40</v>
+      </c>
+      <c r="L112" s="52"/>
+      <c r="M112" s="16">
+        <v>46356</v>
+      </c>
+      <c r="N112" s="42">
+        <f ca="1">Tabela1[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O112" s="42" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P112" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Entrega]],1)</f>
+        <v>49</v>
+      </c>
+      <c r="Q112" s="52"/>
+      <c r="R112" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S112" s="43">
+        <v>46233</v>
+      </c>
+      <c r="T112" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="U112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="V112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="W112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="X112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC112" s="55" t="str">
+        <f t="shared" si="13"/>
+        <v>AG. FUNDIDO</v>
+      </c>
+      <c r="AD112" s="52"/>
+      <c r="AE112" s="56"/>
+      <c r="AF112" s="57"/>
+      <c r="AG112" s="57"/>
+      <c r="AH112" s="57"/>
+      <c r="AI112" s="58"/>
+    </row>
+    <row r="113" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A113" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B113" s="15">
+        <v>61</v>
+      </c>
+      <c r="C113" s="15">
+        <v>27616</v>
+      </c>
+      <c r="D113" s="15">
+        <v>55</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G113" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H113" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="I113" s="15">
+        <v>1</v>
+      </c>
+      <c r="J113" s="16">
+        <v>46295</v>
+      </c>
+      <c r="K113" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Fundido]])</f>
+        <v>40</v>
+      </c>
+      <c r="L113" s="52"/>
+      <c r="M113" s="16">
+        <v>46356</v>
+      </c>
+      <c r="N113" s="42">
+        <f ca="1">Tabela1[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O113" s="42" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P113" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Entrega]],1)</f>
+        <v>49</v>
+      </c>
+      <c r="Q113" s="52"/>
+      <c r="R113" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S113" s="43">
+        <v>46233</v>
+      </c>
+      <c r="T113" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="U113" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="V113" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="W113" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="X113" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y113" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z113" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA113" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB113" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC113" s="55" t="str">
+        <f t="shared" si="13"/>
+        <v>AG. FUNDIDO</v>
+      </c>
+      <c r="AD113" s="52"/>
+      <c r="AE113" s="56"/>
+      <c r="AF113" s="57"/>
+      <c r="AG113" s="57"/>
+      <c r="AH113" s="57"/>
+      <c r="AI113" s="58"/>
+    </row>
+    <row r="114" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A114" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B114" s="15">
+        <v>62</v>
+      </c>
+      <c r="C114" s="15">
+        <v>27616</v>
+      </c>
+      <c r="D114" s="15">
+        <v>56</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F114" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G114" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H114" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="I114" s="15">
+        <v>1</v>
+      </c>
+      <c r="J114" s="16">
+        <v>46295</v>
+      </c>
+      <c r="K114" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Fundido]])</f>
+        <v>40</v>
+      </c>
+      <c r="L114" s="52"/>
+      <c r="M114" s="16">
+        <v>46356</v>
+      </c>
+      <c r="N114" s="42">
+        <f ca="1">Tabela1[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O114" s="42" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P114" s="42">
+        <f>WEEKNUM(Tabela1[[#This Row],[Prazo
+Entrega]],1)</f>
+        <v>49</v>
+      </c>
+      <c r="Q114" s="52"/>
+      <c r="R114" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S114" s="43">
+        <v>46233</v>
+      </c>
+      <c r="T114" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="U114" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="V114" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="W114" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="X114" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y114" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z114" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA114" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB114" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC114" s="55" t="str">
+        <f t="shared" si="13"/>
+        <v>AG. FUNDIDO</v>
+      </c>
+      <c r="AD114" s="52"/>
+      <c r="AE114" s="56"/>
+      <c r="AF114" s="57"/>
+      <c r="AG114" s="57"/>
+      <c r="AH114" s="57"/>
+      <c r="AI114" s="58"/>
+    </row>
   </sheetData>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
@@ -15055,7 +15655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F053A7-2FDA-4BCA-8A08-44A595E3BEFC}">
-  <dimension ref="A1:V91"/>
+  <dimension ref="A1:V131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="1"/>
@@ -15073,7 +15673,8 @@
     <col min="18" max="19" width="9.140625" style="1"/>
     <col min="20" max="20" width="27.28515625" style="1" customWidth="1"/>
     <col min="21" max="21" width="18.28515625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="22" max="22" width="32" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="38.25" x14ac:dyDescent="0.25">
@@ -15852,7 +16453,9 @@
       <c r="U11" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="V11" s="10"/>
+      <c r="V11" s="10" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
@@ -15923,7 +16526,9 @@
       <c r="U12" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="V12" s="10"/>
+      <c r="V12" s="10" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
@@ -15994,7 +16599,9 @@
       <c r="U13" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="V13" s="10"/>
+      <c r="V13" s="10" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
@@ -21533,6 +22140,2846 @@
         <v>61</v>
       </c>
       <c r="V91" s="10"/>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A92" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B92" s="10">
+        <v>15</v>
+      </c>
+      <c r="C92" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D92" s="10">
+        <v>9</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I92" s="10">
+        <v>1</v>
+      </c>
+      <c r="J92" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K92" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L92" s="10"/>
+      <c r="M92" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N92" s="18"/>
+      <c r="O92" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P92" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q92" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R92" s="60" t="str">
+        <f ca="1">IF(Q92&lt;0,"ATRASADO",IF(Q92&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S92" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T92" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U92" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V92" s="60"/>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B93" s="10">
+        <v>16</v>
+      </c>
+      <c r="C93" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D93" s="10">
+        <v>10</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I93" s="10">
+        <v>1</v>
+      </c>
+      <c r="J93" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K93" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L93" s="10"/>
+      <c r="M93" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N93" s="18"/>
+      <c r="O93" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P93" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q93" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R93" s="60" t="str">
+        <f ca="1">IF(Q93&lt;0,"ATRASADO",IF(Q93&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S93" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T93" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U93" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V93" s="60"/>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B94" s="10">
+        <v>17</v>
+      </c>
+      <c r="C94" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D94" s="10">
+        <v>11</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I94" s="10">
+        <v>1</v>
+      </c>
+      <c r="J94" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K94" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L94" s="10"/>
+      <c r="M94" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N94" s="18"/>
+      <c r="O94" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P94" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q94" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R94" s="60" t="str">
+        <f t="shared" ref="R94:R131" ca="1" si="3">IF(Q94&lt;0,"ATRASADO",IF(Q94&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S94" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T94" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U94" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V94" s="60"/>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B95" s="10">
+        <v>18</v>
+      </c>
+      <c r="C95" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D95" s="10">
+        <v>12</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I95" s="10">
+        <v>1</v>
+      </c>
+      <c r="J95" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K95" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L95" s="10"/>
+      <c r="M95" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N95" s="18"/>
+      <c r="O95" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P95" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q95" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R95" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S95" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T95" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U95" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V95" s="60"/>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B96" s="10">
+        <v>19</v>
+      </c>
+      <c r="C96" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D96" s="10">
+        <v>13</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I96" s="10">
+        <v>1</v>
+      </c>
+      <c r="J96" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K96" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L96" s="10"/>
+      <c r="M96" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N96" s="18"/>
+      <c r="O96" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P96" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q96" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R96" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S96" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T96" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U96" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V96" s="60"/>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A97" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B97" s="10">
+        <v>20</v>
+      </c>
+      <c r="C97" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D97" s="10">
+        <v>14</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I97" s="10">
+        <v>1</v>
+      </c>
+      <c r="J97" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K97" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L97" s="10"/>
+      <c r="M97" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N97" s="18"/>
+      <c r="O97" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P97" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q97" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R97" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S97" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T97" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U97" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V97" s="60"/>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A98" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B98" s="10">
+        <v>21</v>
+      </c>
+      <c r="C98" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D98" s="10">
+        <v>15</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H98" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I98" s="10">
+        <v>1</v>
+      </c>
+      <c r="J98" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K98" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L98" s="10"/>
+      <c r="M98" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N98" s="18"/>
+      <c r="O98" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P98" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q98" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R98" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S98" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T98" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U98" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V98" s="60"/>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A99" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B99" s="10">
+        <v>22</v>
+      </c>
+      <c r="C99" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D99" s="10">
+        <v>16</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I99" s="10">
+        <v>1</v>
+      </c>
+      <c r="J99" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K99" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L99" s="10"/>
+      <c r="M99" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N99" s="18"/>
+      <c r="O99" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P99" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q99" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R99" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S99" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T99" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U99" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V99" s="60"/>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A100" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B100" s="10">
+        <v>23</v>
+      </c>
+      <c r="C100" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D100" s="10">
+        <v>17</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I100" s="10">
+        <v>1</v>
+      </c>
+      <c r="J100" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K100" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L100" s="10"/>
+      <c r="M100" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N100" s="18"/>
+      <c r="O100" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P100" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q100" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R100" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S100" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T100" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U100" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V100" s="60"/>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A101" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B101" s="10">
+        <v>24</v>
+      </c>
+      <c r="C101" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D101" s="10">
+        <v>18</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I101" s="10">
+        <v>1</v>
+      </c>
+      <c r="J101" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K101" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L101" s="10"/>
+      <c r="M101" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N101" s="18"/>
+      <c r="O101" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P101" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q101" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R101" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S101" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T101" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U101" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V101" s="60"/>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A102" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B102" s="10">
+        <v>25</v>
+      </c>
+      <c r="C102" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D102" s="10">
+        <v>19</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I102" s="10">
+        <v>1</v>
+      </c>
+      <c r="J102" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K102" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L102" s="10"/>
+      <c r="M102" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N102" s="18"/>
+      <c r="O102" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P102" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q102" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R102" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S102" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T102" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U102" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V102" s="60"/>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A103" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B103" s="10">
+        <v>26</v>
+      </c>
+      <c r="C103" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D103" s="10">
+        <v>20</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I103" s="10">
+        <v>1</v>
+      </c>
+      <c r="J103" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K103" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L103" s="10"/>
+      <c r="M103" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N103" s="18"/>
+      <c r="O103" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P103" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q103" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R103" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S103" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T103" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U103" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V103" s="60"/>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A104" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B104" s="10">
+        <v>27</v>
+      </c>
+      <c r="C104" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D104" s="10">
+        <v>21</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I104" s="10">
+        <v>1</v>
+      </c>
+      <c r="J104" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K104" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L104" s="10"/>
+      <c r="M104" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N104" s="18"/>
+      <c r="O104" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P104" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q104" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R104" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S104" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T104" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U104" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V104" s="60"/>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A105" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B105" s="10">
+        <v>28</v>
+      </c>
+      <c r="C105" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D105" s="10">
+        <v>22</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I105" s="10">
+        <v>1</v>
+      </c>
+      <c r="J105" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K105" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L105" s="10"/>
+      <c r="M105" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N105" s="18"/>
+      <c r="O105" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P105" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q105" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R105" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S105" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T105" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U105" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V105" s="60"/>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A106" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B106" s="10">
+        <v>29</v>
+      </c>
+      <c r="C106" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D106" s="10">
+        <v>23</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I106" s="10">
+        <v>1</v>
+      </c>
+      <c r="J106" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K106" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L106" s="10"/>
+      <c r="M106" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N106" s="18"/>
+      <c r="O106" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P106" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q106" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R106" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S106" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T106" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U106" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V106" s="60"/>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A107" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B107" s="10">
+        <v>30</v>
+      </c>
+      <c r="C107" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D107" s="10">
+        <v>24</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I107" s="10">
+        <v>1</v>
+      </c>
+      <c r="J107" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K107" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L107" s="10"/>
+      <c r="M107" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N107" s="18"/>
+      <c r="O107" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P107" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q107" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R107" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S107" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T107" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U107" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V107" s="60"/>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A108" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B108" s="10">
+        <v>31</v>
+      </c>
+      <c r="C108" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D108" s="10">
+        <v>25</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H108" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I108" s="10">
+        <v>1</v>
+      </c>
+      <c r="J108" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K108" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L108" s="10"/>
+      <c r="M108" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N108" s="18"/>
+      <c r="O108" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P108" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q108" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R108" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S108" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T108" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U108" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V108" s="60"/>
+    </row>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A109" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B109" s="10">
+        <v>32</v>
+      </c>
+      <c r="C109" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D109" s="10">
+        <v>26</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I109" s="10">
+        <v>1</v>
+      </c>
+      <c r="J109" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K109" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L109" s="10"/>
+      <c r="M109" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N109" s="18"/>
+      <c r="O109" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P109" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q109" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R109" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S109" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T109" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U109" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V109" s="60"/>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A110" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B110" s="10">
+        <v>33</v>
+      </c>
+      <c r="C110" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D110" s="10">
+        <v>27</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I110" s="10">
+        <v>1</v>
+      </c>
+      <c r="J110" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K110" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L110" s="10"/>
+      <c r="M110" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N110" s="18"/>
+      <c r="O110" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P110" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q110" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R110" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S110" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T110" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U110" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V110" s="60"/>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A111" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B111" s="10">
+        <v>34</v>
+      </c>
+      <c r="C111" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D111" s="10">
+        <v>28</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I111" s="10">
+        <v>1</v>
+      </c>
+      <c r="J111" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K111" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L111" s="10"/>
+      <c r="M111" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N111" s="18"/>
+      <c r="O111" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q111" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R111" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S111" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T111" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U111" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V111" s="60"/>
+    </row>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A112" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B112" s="10">
+        <v>35</v>
+      </c>
+      <c r="C112" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D112" s="10">
+        <v>29</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I112" s="10">
+        <v>1</v>
+      </c>
+      <c r="J112" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K112" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L112" s="10"/>
+      <c r="M112" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N112" s="18"/>
+      <c r="O112" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P112" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q112" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R112" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S112" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T112" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U112" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V112" s="60"/>
+    </row>
+    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A113" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B113" s="10">
+        <v>36</v>
+      </c>
+      <c r="C113" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D113" s="10">
+        <v>30</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G113" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I113" s="10">
+        <v>1</v>
+      </c>
+      <c r="J113" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K113" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L113" s="10"/>
+      <c r="M113" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N113" s="18"/>
+      <c r="O113" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P113" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q113" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R113" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S113" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T113" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U113" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V113" s="60"/>
+    </row>
+    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A114" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B114" s="10">
+        <v>37</v>
+      </c>
+      <c r="C114" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D114" s="10">
+        <v>31</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H114" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I114" s="10">
+        <v>1</v>
+      </c>
+      <c r="J114" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K114" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L114" s="10"/>
+      <c r="M114" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N114" s="18"/>
+      <c r="O114" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P114" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q114" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R114" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S114" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T114" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U114" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V114" s="60"/>
+    </row>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A115" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B115" s="10">
+        <v>38</v>
+      </c>
+      <c r="C115" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D115" s="10">
+        <v>32</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I115" s="10">
+        <v>1</v>
+      </c>
+      <c r="J115" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K115" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L115" s="10"/>
+      <c r="M115" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N115" s="18"/>
+      <c r="O115" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P115" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q115" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R115" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S115" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T115" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U115" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V115" s="60"/>
+    </row>
+    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A116" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B116" s="10">
+        <v>39</v>
+      </c>
+      <c r="C116" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D116" s="10">
+        <v>33</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F116" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I116" s="10">
+        <v>1</v>
+      </c>
+      <c r="J116" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K116" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L116" s="10"/>
+      <c r="M116" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N116" s="18"/>
+      <c r="O116" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P116" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q116" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R116" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S116" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T116" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U116" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V116" s="60"/>
+    </row>
+    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A117" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B117" s="10">
+        <v>40</v>
+      </c>
+      <c r="C117" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D117" s="10">
+        <v>34</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I117" s="10">
+        <v>1</v>
+      </c>
+      <c r="J117" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K117" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L117" s="10"/>
+      <c r="M117" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N117" s="18"/>
+      <c r="O117" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P117" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q117" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R117" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S117" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T117" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U117" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V117" s="60"/>
+    </row>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A118" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B118" s="10">
+        <v>41</v>
+      </c>
+      <c r="C118" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D118" s="10">
+        <v>35</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F118" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H118" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I118" s="10">
+        <v>1</v>
+      </c>
+      <c r="J118" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K118" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L118" s="10"/>
+      <c r="M118" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N118" s="18"/>
+      <c r="O118" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P118" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q118" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R118" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S118" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T118" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U118" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V118" s="60"/>
+    </row>
+    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A119" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B119" s="10">
+        <v>42</v>
+      </c>
+      <c r="C119" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D119" s="10">
+        <v>36</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F119" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I119" s="10">
+        <v>1</v>
+      </c>
+      <c r="J119" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K119" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L119" s="10"/>
+      <c r="M119" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N119" s="18"/>
+      <c r="O119" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P119" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q119" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R119" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S119" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T119" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U119" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V119" s="60"/>
+    </row>
+    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A120" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B120" s="10">
+        <v>43</v>
+      </c>
+      <c r="C120" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D120" s="10">
+        <v>37</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F120" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G120" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H120" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I120" s="10">
+        <v>1</v>
+      </c>
+      <c r="J120" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K120" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L120" s="10"/>
+      <c r="M120" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N120" s="18"/>
+      <c r="O120" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P120" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q120" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R120" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S120" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T120" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U120" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V120" s="60"/>
+    </row>
+    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A121" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B121" s="10">
+        <v>44</v>
+      </c>
+      <c r="C121" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D121" s="10">
+        <v>38</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F121" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I121" s="10">
+        <v>1</v>
+      </c>
+      <c r="J121" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K121" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L121" s="10"/>
+      <c r="M121" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N121" s="18"/>
+      <c r="O121" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P121" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q121" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R121" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S121" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T121" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U121" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V121" s="60"/>
+    </row>
+    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A122" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B122" s="10">
+        <v>45</v>
+      </c>
+      <c r="C122" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D122" s="10">
+        <v>39</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F122" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H122" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I122" s="10">
+        <v>1</v>
+      </c>
+      <c r="J122" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K122" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L122" s="10"/>
+      <c r="M122" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N122" s="18"/>
+      <c r="O122" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P122" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q122" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R122" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S122" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T122" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U122" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V122" s="60"/>
+    </row>
+    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A123" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B123" s="10">
+        <v>46</v>
+      </c>
+      <c r="C123" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D123" s="10">
+        <v>40</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G123" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I123" s="10">
+        <v>1</v>
+      </c>
+      <c r="J123" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K123" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L123" s="10"/>
+      <c r="M123" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N123" s="18"/>
+      <c r="O123" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P123" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q123" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R123" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S123" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T123" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U123" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V123" s="60"/>
+    </row>
+    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A124" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B124" s="10">
+        <v>47</v>
+      </c>
+      <c r="C124" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D124" s="10">
+        <v>41</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F124" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H124" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I124" s="10">
+        <v>1</v>
+      </c>
+      <c r="J124" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K124" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L124" s="10"/>
+      <c r="M124" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N124" s="18"/>
+      <c r="O124" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P124" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q124" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R124" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S124" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T124" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U124" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V124" s="60"/>
+    </row>
+    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A125" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B125" s="10">
+        <v>48</v>
+      </c>
+      <c r="C125" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D125" s="10">
+        <v>42</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F125" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G125" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H125" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I125" s="10">
+        <v>1</v>
+      </c>
+      <c r="J125" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K125" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L125" s="10"/>
+      <c r="M125" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N125" s="18"/>
+      <c r="O125" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P125" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q125" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R125" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S125" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T125" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U125" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V125" s="60"/>
+    </row>
+    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A126" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B126" s="10">
+        <v>49</v>
+      </c>
+      <c r="C126" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D126" s="10">
+        <v>43</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H126" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I126" s="10">
+        <v>1</v>
+      </c>
+      <c r="J126" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K126" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L126" s="10"/>
+      <c r="M126" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N126" s="18"/>
+      <c r="O126" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P126" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q126" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R126" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S126" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T126" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U126" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V126" s="60"/>
+    </row>
+    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A127" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B127" s="10">
+        <v>50</v>
+      </c>
+      <c r="C127" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D127" s="10">
+        <v>44</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F127" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G127" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I127" s="10">
+        <v>1</v>
+      </c>
+      <c r="J127" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K127" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L127" s="10"/>
+      <c r="M127" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N127" s="18"/>
+      <c r="O127" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P127" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q127" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R127" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S127" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T127" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U127" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V127" s="60"/>
+    </row>
+    <row r="128" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A128" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B128" s="10">
+        <v>51</v>
+      </c>
+      <c r="C128" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D128" s="10">
+        <v>45</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F128" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H128" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I128" s="10">
+        <v>1</v>
+      </c>
+      <c r="J128" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K128" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L128" s="10"/>
+      <c r="M128" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N128" s="18"/>
+      <c r="O128" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P128" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q128" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R128" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S128" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T128" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U128" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V128" s="60"/>
+    </row>
+    <row r="129" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A129" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B129" s="10">
+        <v>52</v>
+      </c>
+      <c r="C129" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D129" s="10">
+        <v>46</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F129" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I129" s="10">
+        <v>1</v>
+      </c>
+      <c r="J129" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K129" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L129" s="10"/>
+      <c r="M129" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N129" s="18"/>
+      <c r="O129" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P129" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q129" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R129" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S129" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T129" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U129" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V129" s="60"/>
+    </row>
+    <row r="130" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A130" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B130" s="10">
+        <v>53</v>
+      </c>
+      <c r="C130" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D130" s="10">
+        <v>47</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F130" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H130" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I130" s="10">
+        <v>1</v>
+      </c>
+      <c r="J130" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K130" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L130" s="10"/>
+      <c r="M130" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N130" s="18"/>
+      <c r="O130" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P130" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q130" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R130" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S130" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T130" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U130" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V130" s="60"/>
+    </row>
+    <row r="131" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A131" s="10">
+        <v>2333</v>
+      </c>
+      <c r="B131" s="10">
+        <v>54</v>
+      </c>
+      <c r="C131" s="10">
+        <v>27616</v>
+      </c>
+      <c r="D131" s="10">
+        <v>48</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F131" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G131" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H131" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I131" s="10">
+        <v>1</v>
+      </c>
+      <c r="J131" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K131" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>36</v>
+      </c>
+      <c r="L131" s="10"/>
+      <c r="M131" s="11">
+        <v>46325</v>
+      </c>
+      <c r="N131" s="18"/>
+      <c r="O131" s="11">
+        <f>Tabela3[[#This Row],[Prazo
+Fundido]]-10</f>
+        <v>46256</v>
+      </c>
+      <c r="P131" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q131" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>128</v>
+      </c>
+      <c r="R131" s="60" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S131" s="60">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>44</v>
+      </c>
+      <c r="T131" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U131" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V131" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -24992,7 +28439,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF21EC6F-EA0F-4DA9-80E1-5F0E0C8C0396}">
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="9.140625" style="1"/>
@@ -25000,8 +28447,7 @@
     <col min="6" max="6" width="9.140625" style="1"/>
     <col min="8" max="8" width="7.140625" customWidth="1"/>
     <col min="9" max="9" width="36.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.42578125" style="38" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.7109375" customWidth="1"/>
     <col min="16" max="18" width="13.5703125" customWidth="1"/>
@@ -27816,7 +31262,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="15">
         <v>2331</v>
       </c>
@@ -27875,7 +31321,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="15">
         <v>2331</v>
       </c>
@@ -27934,7 +31380,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="15">
         <v>2331</v>
       </c>
@@ -27993,7 +31439,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="15">
         <v>2331</v>
       </c>
@@ -28051,6 +31497,2197 @@
       <c r="S52" t="s">
         <v>120</v>
       </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A53" s="15">
+        <v>1798</v>
+      </c>
+      <c r="B53" s="15">
+        <v>9</v>
+      </c>
+      <c r="C53" s="15">
+        <v>27142</v>
+      </c>
+      <c r="D53" s="15">
+        <v>4</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F53" s="14">
+        <v>1</v>
+      </c>
+      <c r="G53" s="14">
+        <v>1343033</v>
+      </c>
+      <c r="H53" s="14">
+        <v>1</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="J53" s="7">
+        <v>46142</v>
+      </c>
+      <c r="K53" s="54">
+        <v>46128</v>
+      </c>
+      <c r="L53" s="7">
+        <v>46203</v>
+      </c>
+      <c r="M53" s="54">
+        <v>46197</v>
+      </c>
+      <c r="N53" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>6</v>
+      </c>
+      <c r="O53" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q53" s="52" t="s">
+        <v>69</v>
+      </c>
+      <c r="R53" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="S53" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="T53" s="49"/>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A54" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B54" s="15">
+        <v>8</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F54" s="14">
+        <v>1</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="J54" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L54" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M54" s="49"/>
+      <c r="N54" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O54" s="51" t="str">
+        <f ca="1">IF(N54&lt;0,"ATRASADO",IF(N54&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P54" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q54" s="11">
+        <v>46203</v>
+      </c>
+      <c r="R54" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S54" t="s">
+        <v>120</v>
+      </c>
+      <c r="T54" s="49"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A55" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B55" s="15">
+        <v>9</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F55" s="14">
+        <v>1</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H55" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="J55" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L55" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M55" s="49"/>
+      <c r="N55" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O55" s="51" t="str">
+        <f ca="1">IF(N55&lt;0,"ATRASADO",IF(N55&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q55" s="11">
+        <v>46203</v>
+      </c>
+      <c r="R55" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S55" t="s">
+        <v>120</v>
+      </c>
+      <c r="T55" s="49"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A56" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B56" s="15">
+        <v>11</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F56" s="14">
+        <v>1</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H56" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="J56" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L56" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M56" s="49"/>
+      <c r="N56" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O56" s="51" t="str">
+        <f ca="1">IF(N56&lt;0,"ATRASADO",IF(N56&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q56" s="11">
+        <v>46203</v>
+      </c>
+      <c r="R56" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S56" t="s">
+        <v>120</v>
+      </c>
+      <c r="T56" s="49"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A57" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B57" s="15">
+        <v>12</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F57" s="14">
+        <v>1</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="J57" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L57" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M57" s="49"/>
+      <c r="N57" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O57" s="51" t="str">
+        <f t="shared" ref="O57:O59" ca="1" si="7">IF(N57&lt;0,"ATRASADO",IF(N57&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P57" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q57" s="11">
+        <v>46203</v>
+      </c>
+      <c r="R57" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S57" t="s">
+        <v>120</v>
+      </c>
+      <c r="T57" s="49"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A58" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B58" s="15">
+        <v>13</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F58" s="14">
+        <v>1</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H58" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="J58" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L58" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M58" s="49"/>
+      <c r="N58" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O58" s="51" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P58" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q58" s="11">
+        <v>46203</v>
+      </c>
+      <c r="R58" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S58" t="s">
+        <v>120</v>
+      </c>
+      <c r="T58" s="49"/>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A59" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B59" s="15">
+        <v>14</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F59" s="14">
+        <v>1</v>
+      </c>
+      <c r="G59" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H59" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="J59" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L59" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M59" s="49"/>
+      <c r="N59" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O59" s="51" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P59" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q59" s="11">
+        <v>46203</v>
+      </c>
+      <c r="R59" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S59" t="s">
+        <v>120</v>
+      </c>
+      <c r="T59" s="49"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A60" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B60" s="15">
+        <v>55</v>
+      </c>
+      <c r="C60" s="14">
+        <v>27616</v>
+      </c>
+      <c r="D60" s="14">
+        <v>49</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F60" s="14">
+        <v>1</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H60" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="J60" s="7">
+        <v>46295</v>
+      </c>
+      <c r="K60" s="49"/>
+      <c r="L60" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M60" s="49"/>
+      <c r="N60" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O60" s="51" t="str">
+        <f t="shared" ref="O60:O62" ca="1" si="8">IF(N60&lt;0,"ATRASADO",IF(N60&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P60" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q60" s="11">
+        <v>46203</v>
+      </c>
+      <c r="R60" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S60" t="s">
+        <v>120</v>
+      </c>
+      <c r="T60" s="49"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A61" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B61" s="15">
+        <v>56</v>
+      </c>
+      <c r="C61" s="14">
+        <v>27616</v>
+      </c>
+      <c r="D61" s="14">
+        <v>50</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F61" s="14">
+        <v>1</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="J61" s="7">
+        <v>46295</v>
+      </c>
+      <c r="K61" s="49"/>
+      <c r="L61" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M61" s="49"/>
+      <c r="N61" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O61" s="51" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q61" s="11">
+        <v>46203</v>
+      </c>
+      <c r="R61" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S61" t="s">
+        <v>120</v>
+      </c>
+      <c r="T61" s="49"/>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A62" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B62" s="15">
+        <v>57</v>
+      </c>
+      <c r="C62" s="14">
+        <v>27616</v>
+      </c>
+      <c r="D62" s="14">
+        <v>51</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F62" s="14">
+        <v>1</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="J62" s="7">
+        <v>46295</v>
+      </c>
+      <c r="K62" s="49"/>
+      <c r="L62" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M62" s="49"/>
+      <c r="N62" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O62" s="51" t="str">
+        <f t="shared" ca="1" si="8"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P62" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q62" s="11">
+        <v>46203</v>
+      </c>
+      <c r="R62" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S62" t="s">
+        <v>120</v>
+      </c>
+      <c r="T62" s="49"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A63" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B63" s="15">
+        <v>63</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F63" s="14">
+        <v>1</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H63" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="J63" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L63" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M63" s="49"/>
+      <c r="N63" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O63" s="51" t="str">
+        <f ca="1">IF(N63&lt;0,"ATRASADO",IF(N63&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P63" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q63" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R63" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S63" t="s">
+        <v>120</v>
+      </c>
+      <c r="T63" s="49"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A64" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B64" s="15">
+        <v>64</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F64" s="14">
+        <v>1</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H64" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="J64" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L64" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M64" s="49"/>
+      <c r="N64" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O64" s="51" t="str">
+        <f t="shared" ref="O64:O76" ca="1" si="9">IF(N64&lt;0,"ATRASADO",IF(N64&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P64" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R64" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S64" t="s">
+        <v>120</v>
+      </c>
+      <c r="T64" s="49"/>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A65" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B65" s="15">
+        <v>65</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F65" s="14">
+        <v>1</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H65" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="J65" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L65" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M65" s="49"/>
+      <c r="N65" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O65" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P65" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R65" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S65" t="s">
+        <v>120</v>
+      </c>
+      <c r="T65" s="49"/>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A66" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B66" s="15">
+        <v>66</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F66" s="14">
+        <v>1</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="J66" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L66" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M66" s="49"/>
+      <c r="N66" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O66" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P66" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q66" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R66" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S66" t="s">
+        <v>120</v>
+      </c>
+      <c r="T66" s="49"/>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B67" s="15">
+        <v>67</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F67" s="14">
+        <v>1</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H67" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L67" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M67" s="49"/>
+      <c r="N67" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O67" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P67" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q67" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R67" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S67" t="s">
+        <v>120</v>
+      </c>
+      <c r="T67" s="49"/>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B68" s="15">
+        <v>68</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F68" s="14">
+        <v>1</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H68" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J68" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L68" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M68" s="49"/>
+      <c r="N68" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O68" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P68" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R68" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S68" t="s">
+        <v>120</v>
+      </c>
+      <c r="T68" s="49"/>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B69" s="15">
+        <v>69</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F69" s="14">
+        <v>1</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H69" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J69" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L69" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M69" s="49"/>
+      <c r="N69" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O69" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P69" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q69" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R69" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S69" t="s">
+        <v>120</v>
+      </c>
+      <c r="T69" s="49"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B70" s="15">
+        <v>70</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F70" s="14">
+        <v>1</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H70" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L70" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M70" s="49"/>
+      <c r="N70" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O70" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P70" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q70" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R70" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S70" t="s">
+        <v>120</v>
+      </c>
+      <c r="T70" s="49"/>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B71" s="15">
+        <v>71</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F71" s="14">
+        <v>1</v>
+      </c>
+      <c r="G71" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H71" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J71" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L71" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M71" s="49"/>
+      <c r="N71" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O71" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P71" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q71" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R71" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S71" t="s">
+        <v>120</v>
+      </c>
+      <c r="T71" s="49"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B72" s="15">
+        <v>72</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F72" s="14">
+        <v>1</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H72" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J72" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L72" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M72" s="49"/>
+      <c r="N72" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O72" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P72" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q72" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R72" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S72" t="s">
+        <v>120</v>
+      </c>
+      <c r="T72" s="49"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B73" s="15">
+        <v>73</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F73" s="14">
+        <v>1</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H73" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J73" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L73" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M73" s="49"/>
+      <c r="N73" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O73" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P73" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q73" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R73" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S73" t="s">
+        <v>120</v>
+      </c>
+      <c r="T73" s="49"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A74" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B74" s="15">
+        <v>74</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F74" s="14">
+        <v>1</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J74" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L74" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M74" s="49"/>
+      <c r="N74" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O74" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P74" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q74" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R74" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S74" t="s">
+        <v>120</v>
+      </c>
+      <c r="T74" s="49"/>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A75" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B75" s="15">
+        <v>75</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F75" s="14">
+        <v>1</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H75" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J75" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L75" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M75" s="49"/>
+      <c r="N75" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O75" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P75" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q75" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R75" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S75" t="s">
+        <v>120</v>
+      </c>
+      <c r="T75" s="49"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A76" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B76" s="15">
+        <v>76</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F76" s="14">
+        <v>1</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H76" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J76" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L76" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M76" s="49"/>
+      <c r="N76" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O76" s="51" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P76" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q76" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R76" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S76" t="s">
+        <v>120</v>
+      </c>
+      <c r="T76" s="49"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B77" s="15">
+        <v>77</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F77" s="14">
+        <v>1</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J77" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L77" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M77" s="49"/>
+      <c r="N77" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O77" s="51" t="str">
+        <f ca="1">IF(N77&lt;0,"ATRASADO",IF(N77&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P77" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q77" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R77" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S77" t="s">
+        <v>120</v>
+      </c>
+      <c r="T77" s="49"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A78" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B78" s="15">
+        <v>78</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F78" s="14">
+        <v>160</v>
+      </c>
+      <c r="G78" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H78" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="J78" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L78" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M78" s="49"/>
+      <c r="N78" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O78" s="51" t="str">
+        <f t="shared" ref="O78:O80" ca="1" si="10">IF(N78&lt;0,"ATRASADO",IF(N78&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P78" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q78" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R78" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S78" t="s">
+        <v>120</v>
+      </c>
+      <c r="T78" s="49"/>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A79" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B79" s="15">
+        <v>79</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F79" s="14">
+        <v>160</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H79" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J79" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L79" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M79" s="49"/>
+      <c r="N79" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O79" s="51" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P79" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q79" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R79" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S79" t="s">
+        <v>120</v>
+      </c>
+      <c r="T79" s="49"/>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A80" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B80" s="15">
+        <v>80</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F80" s="14">
+        <v>20</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H80" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="J80" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L80" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M80" s="49"/>
+      <c r="N80" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O80" s="51" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P80" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R80" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S80" t="s">
+        <v>120</v>
+      </c>
+      <c r="T80" s="49"/>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A81" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B81" s="15">
+        <v>81</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F81" s="14">
+        <v>1</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H81" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="J81" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L81" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M81" s="49"/>
+      <c r="N81" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O81" s="51" t="str">
+        <f ca="1">IF(N81&lt;0,"ATRASADO",IF(N81&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P81" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R81" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S81" t="s">
+        <v>120</v>
+      </c>
+      <c r="T81" s="49"/>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A82" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B82" s="15">
+        <v>82</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E82" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F82" s="14">
+        <v>1</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H82" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="J82" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L82" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M82" s="49"/>
+      <c r="N82" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O82" s="51" t="str">
+        <f ca="1">IF(N82&lt;0,"ATRASADO",IF(N82&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P82" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R82" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S82" t="s">
+        <v>120</v>
+      </c>
+      <c r="T82" s="49"/>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A83" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B83" s="15">
+        <v>83</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F83" s="14">
+        <v>1</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H83" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="J83" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L83" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M83" s="49"/>
+      <c r="N83" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O83" s="51" t="str">
+        <f ca="1">IF(N83&lt;0,"ATRASADO",IF(N83&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P83" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R83" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S83" t="s">
+        <v>120</v>
+      </c>
+      <c r="T83" s="49"/>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A84" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B84" s="15">
+        <v>84</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E84" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F84" s="14">
+        <v>1</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H84" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="J84" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L84" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M84" s="49"/>
+      <c r="N84" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O84" s="51" t="str">
+        <f ca="1">IF(N84&lt;0,"ATRASADO",IF(N84&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P84" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R84" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S84" t="s">
+        <v>120</v>
+      </c>
+      <c r="T84" s="49"/>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A85" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B85" s="15">
+        <v>85</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F85" s="14">
+        <v>1</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H85" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J85" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L85" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M85" s="49"/>
+      <c r="N85" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O85" s="51" t="str">
+        <f ca="1">IF(N85&lt;0,"ATRASADO",IF(N85&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P85" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R85" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S85" t="s">
+        <v>120</v>
+      </c>
+      <c r="T85" s="49"/>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A86" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B86" s="15">
+        <v>86</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F86" s="14">
+        <v>1</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H86" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J86" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K86" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L86" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M86" s="49"/>
+      <c r="N86" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O86" s="51" t="str">
+        <f ca="1">IF(N86&lt;0,"ATRASADO",IF(N86&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P86" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q86" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R86" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S86" t="s">
+        <v>120</v>
+      </c>
+      <c r="T86" s="49"/>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A87" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B87" s="15">
+        <v>87</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F87" s="14">
+        <v>1</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H87" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J87" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K87" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L87" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M87" s="49"/>
+      <c r="N87" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O87" s="51" t="str">
+        <f ca="1">IF(N87&lt;0,"ATRASADO",IF(N87&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P87" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R87" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S87" t="s">
+        <v>120</v>
+      </c>
+      <c r="T87" s="49"/>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A88" s="15">
+        <v>2333</v>
+      </c>
+      <c r="B88" s="15">
+        <v>88</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F88" s="14">
+        <v>1</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="J88" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K88" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L88" s="7">
+        <v>46356</v>
+      </c>
+      <c r="M88" s="49"/>
+      <c r="N88" s="50">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>159</v>
+      </c>
+      <c r="O88" s="51" t="str">
+        <f ca="1">IF(N88&lt;0,"ATRASADO",IF(N88&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P88" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q88" s="59">
+        <v>46233</v>
+      </c>
+      <c r="R88" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="S88" t="s">
+        <v>120</v>
+      </c>
+      <c r="T88" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -28063,9 +33700,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A7CF3D-4567-423F-9856-686FB94A96D5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212D5857-C1D5-4A23-87F7-19DD10BADC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A9A2AD-F6F2-43E5-9671-682B9C4521DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
   <sheets>
     <sheet name="BAGACEIRAS" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4560" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4560" uniqueCount="271">
   <si>
     <t>O.S.</t>
   </si>
@@ -983,6 +983,9 @@
   </si>
   <si>
     <t>Bit</t>
+  </si>
+  <si>
+    <t>Em Inspeção</t>
   </si>
 </sst>
 </file>
@@ -3684,7 +3687,13 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V131" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
-  <autoFilter ref="A1:V131" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}"/>
+  <autoFilter ref="A1:V131" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="1495052"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="79"/>
     <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="78"/>
@@ -16916,7 +16925,7 @@
         <v>43</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="V2" s="10"/>
     </row>
@@ -16987,7 +16996,7 @@
         <v>43</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="V3" s="10"/>
     </row>
@@ -17058,7 +17067,7 @@
         <v>43</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="V4" s="10"/>
     </row>
@@ -17129,7 +17138,7 @@
         <v>43</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="V5" s="10"/>
     </row>
@@ -17200,7 +17209,7 @@
         <v>43</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="V6" s="10"/>
     </row>
@@ -17271,7 +17280,7 @@
         <v>43</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="V7" s="10"/>
     </row>
@@ -17342,7 +17351,7 @@
         <v>43</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="V8" s="10"/>
     </row>
@@ -17413,7 +17422,7 @@
         <v>43</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="V9" s="10"/>
     </row>
@@ -17484,11 +17493,11 @@
         <v>43</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="V10" s="10"/>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>2226</v>
       </c>
@@ -17561,7 +17570,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>2226</v>
       </c>
@@ -17634,7 +17643,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>2226</v>
       </c>
@@ -17707,7 +17716,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>2227</v>
       </c>
@@ -17778,7 +17787,7 @@
       </c>
       <c r="V14" s="10"/>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>2227</v>
       </c>
@@ -17849,7 +17858,7 @@
       </c>
       <c r="V15" s="10"/>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>2227</v>
       </c>
@@ -17920,7 +17929,7 @@
       </c>
       <c r="V16" s="10"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>2227</v>
       </c>
@@ -17991,7 +18000,7 @@
       </c>
       <c r="V17" s="10"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>2227</v>
       </c>
@@ -18062,7 +18071,7 @@
       </c>
       <c r="V18" s="10"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>2227</v>
       </c>
@@ -18133,7 +18142,7 @@
       </c>
       <c r="V19" s="10"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>2227</v>
       </c>
@@ -18204,7 +18213,7 @@
       </c>
       <c r="V20" s="10"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>2227</v>
       </c>
@@ -18275,7 +18284,7 @@
       </c>
       <c r="V21" s="10"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>2227</v>
       </c>
@@ -18346,7 +18355,7 @@
       </c>
       <c r="V22" s="10"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>2227</v>
       </c>
@@ -18417,7 +18426,7 @@
       </c>
       <c r="V23" s="10"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>2227</v>
       </c>
@@ -18488,7 +18497,7 @@
       </c>
       <c r="V24" s="10"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>2227</v>
       </c>
@@ -18559,7 +18568,7 @@
       </c>
       <c r="V25" s="10"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>2227</v>
       </c>
@@ -18630,7 +18639,7 @@
       </c>
       <c r="V26" s="10"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>2227</v>
       </c>
@@ -18701,7 +18710,7 @@
       </c>
       <c r="V27" s="10"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>2227</v>
       </c>
@@ -18772,7 +18781,7 @@
       </c>
       <c r="V28" s="10"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>2227</v>
       </c>
@@ -18843,7 +18852,7 @@
       </c>
       <c r="V29" s="10"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>2227</v>
       </c>
@@ -18914,7 +18923,7 @@
       </c>
       <c r="V30" s="10"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>2227</v>
       </c>
@@ -18985,7 +18994,7 @@
       </c>
       <c r="V31" s="10"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>2227</v>
       </c>
@@ -19056,7 +19065,7 @@
       </c>
       <c r="V32" s="10"/>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>1951</v>
       </c>
@@ -19127,7 +19136,7 @@
       </c>
       <c r="V33" s="10"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>1951</v>
       </c>
@@ -19198,7 +19207,7 @@
       </c>
       <c r="V34" s="10"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>1951</v>
       </c>
@@ -19269,7 +19278,7 @@
       </c>
       <c r="V35" s="10"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>1951</v>
       </c>
@@ -19340,7 +19349,7 @@
       </c>
       <c r="V36" s="10"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>1951</v>
       </c>
@@ -19411,7 +19420,7 @@
       </c>
       <c r="V37" s="10"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
         <v>1031</v>
       </c>
@@ -19482,7 +19491,7 @@
       </c>
       <c r="V38" s="10"/>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
         <v>1031</v>
       </c>
@@ -19553,7 +19562,7 @@
       </c>
       <c r="V39" s="10"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
         <v>1031</v>
       </c>
@@ -19624,7 +19633,7 @@
       </c>
       <c r="V40" s="10"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
         <v>1031</v>
       </c>
@@ -19695,7 +19704,7 @@
       </c>
       <c r="V41" s="10"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
         <v>1031</v>
       </c>
@@ -19766,7 +19775,7 @@
       </c>
       <c r="V42" s="10"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
         <v>1031</v>
       </c>
@@ -19837,7 +19846,7 @@
       </c>
       <c r="V43" s="10"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
         <v>1031</v>
       </c>
@@ -19908,7 +19917,7 @@
       </c>
       <c r="V44" s="10"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
         <v>1031</v>
       </c>
@@ -19979,7 +19988,7 @@
       </c>
       <c r="V45" s="10"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
         <v>1031</v>
       </c>
@@ -20050,7 +20059,7 @@
       </c>
       <c r="V46" s="10"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <v>1031</v>
       </c>
@@ -20121,7 +20130,7 @@
       </c>
       <c r="V47" s="10"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15">
         <v>1031</v>
       </c>
@@ -20192,7 +20201,7 @@
       </c>
       <c r="V48" s="10"/>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15">
         <v>1031</v>
       </c>
@@ -20263,7 +20272,7 @@
       </c>
       <c r="V49" s="10"/>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15">
         <v>1031</v>
       </c>
@@ -20334,7 +20343,7 @@
       </c>
       <c r="V50" s="10"/>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15">
         <v>1031</v>
       </c>
@@ -20405,7 +20414,7 @@
       </c>
       <c r="V51" s="10"/>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="15">
         <v>1031</v>
       </c>
@@ -20476,7 +20485,7 @@
       </c>
       <c r="V52" s="10"/>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15">
         <v>1031</v>
       </c>
@@ -20547,7 +20556,7 @@
       </c>
       <c r="V53" s="10"/>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="15">
         <v>1031</v>
       </c>
@@ -20618,7 +20627,7 @@
       </c>
       <c r="V54" s="10"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="15">
         <v>1031</v>
       </c>
@@ -20689,7 +20698,7 @@
       </c>
       <c r="V55" s="10"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="15">
         <v>1031</v>
       </c>
@@ -20760,7 +20769,7 @@
       </c>
       <c r="V56" s="10"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="15">
         <v>1031</v>
       </c>
@@ -20831,7 +20840,7 @@
       </c>
       <c r="V57" s="10"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="15">
         <v>1031</v>
       </c>
@@ -20902,7 +20911,7 @@
       </c>
       <c r="V58" s="10"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="15">
         <v>1031</v>
       </c>
@@ -20973,7 +20982,7 @@
       </c>
       <c r="V59" s="10"/>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15">
         <v>1031</v>
       </c>
@@ -21044,7 +21053,7 @@
       </c>
       <c r="V60" s="10"/>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15">
         <v>1031</v>
       </c>
@@ -21115,7 +21124,7 @@
       </c>
       <c r="V61" s="10"/>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15">
         <v>1031</v>
       </c>
@@ -21186,7 +21195,7 @@
       </c>
       <c r="V62" s="10"/>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="15">
         <v>1031</v>
       </c>
@@ -21257,7 +21266,7 @@
       </c>
       <c r="V63" s="10"/>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15">
         <v>1031</v>
       </c>
@@ -21328,7 +21337,7 @@
       </c>
       <c r="V64" s="10"/>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15">
         <v>1031</v>
       </c>
@@ -21399,7 +21408,7 @@
       </c>
       <c r="V65" s="10"/>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="15">
         <v>1031</v>
       </c>
@@ -21470,7 +21479,7 @@
       </c>
       <c r="V66" s="10"/>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="15">
         <v>1031</v>
       </c>
@@ -21541,7 +21550,7 @@
       </c>
       <c r="V67" s="10"/>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="15">
         <v>1031</v>
       </c>
@@ -21612,7 +21621,7 @@
       </c>
       <c r="V68" s="10"/>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="15">
         <v>1031</v>
       </c>
@@ -21683,7 +21692,7 @@
       </c>
       <c r="V69" s="10"/>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="15">
         <v>1031</v>
       </c>
@@ -21754,7 +21763,7 @@
       </c>
       <c r="V70" s="10"/>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="15">
         <v>1031</v>
       </c>
@@ -21825,7 +21834,7 @@
       </c>
       <c r="V71" s="10"/>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="15">
         <v>1031</v>
       </c>
@@ -21896,7 +21905,7 @@
       </c>
       <c r="V72" s="10"/>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="15">
         <v>1031</v>
       </c>
@@ -21967,7 +21976,7 @@
       </c>
       <c r="V73" s="10"/>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="15">
         <v>1031</v>
       </c>
@@ -22038,7 +22047,7 @@
       </c>
       <c r="V74" s="10"/>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="15">
         <v>1031</v>
       </c>
@@ -22109,7 +22118,7 @@
       </c>
       <c r="V75" s="10"/>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="15">
         <v>1031</v>
       </c>
@@ -22180,7 +22189,7 @@
       </c>
       <c r="V76" s="10"/>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="15">
         <v>1031</v>
       </c>
@@ -22251,7 +22260,7 @@
       </c>
       <c r="V77" s="10"/>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="15">
         <v>1031</v>
       </c>
@@ -22322,7 +22331,7 @@
       </c>
       <c r="V78" s="10"/>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="15">
         <v>1031</v>
       </c>
@@ -22393,7 +22402,7 @@
       </c>
       <c r="V79" s="10"/>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="15">
         <v>1031</v>
       </c>
@@ -22464,7 +22473,7 @@
       </c>
       <c r="V80" s="10"/>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="15">
         <v>1031</v>
       </c>
@@ -22535,7 +22544,7 @@
       </c>
       <c r="V81" s="10"/>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="15">
         <v>1031</v>
       </c>
@@ -22606,7 +22615,7 @@
       </c>
       <c r="V82" s="10"/>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="15">
         <v>1031</v>
       </c>
@@ -22677,7 +22686,7 @@
       </c>
       <c r="V83" s="10"/>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>1031</v>
       </c>
@@ -22748,7 +22757,7 @@
       </c>
       <c r="V84" s="10"/>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>1031</v>
       </c>
@@ -22819,7 +22828,7 @@
       </c>
       <c r="V85" s="10"/>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>1031</v>
       </c>
@@ -22890,7 +22899,7 @@
       </c>
       <c r="V86" s="10"/>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>1031</v>
       </c>
@@ -22961,7 +22970,7 @@
       </c>
       <c r="V87" s="10"/>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>1031</v>
       </c>
@@ -23032,7 +23041,7 @@
       </c>
       <c r="V88" s="10"/>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>1031</v>
       </c>
@@ -23103,7 +23112,7 @@
       </c>
       <c r="V89" s="10"/>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="15">
         <v>1031</v>
       </c>
@@ -23174,7 +23183,7 @@
       </c>
       <c r="V90" s="10"/>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="15">
         <v>1031</v>
       </c>
@@ -23245,7 +23254,7 @@
       </c>
       <c r="V91" s="10"/>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>2333</v>
       </c>
@@ -23316,7 +23325,7 @@
       </c>
       <c r="V92" s="10"/>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>2333</v>
       </c>
@@ -23387,7 +23396,7 @@
       </c>
       <c r="V93" s="10"/>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>2333</v>
       </c>
@@ -23458,7 +23467,7 @@
       </c>
       <c r="V94" s="10"/>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>2333</v>
       </c>
@@ -23529,7 +23538,7 @@
       </c>
       <c r="V95" s="10"/>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>2333</v>
       </c>
@@ -23600,7 +23609,7 @@
       </c>
       <c r="V96" s="10"/>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>2333</v>
       </c>
@@ -23671,7 +23680,7 @@
       </c>
       <c r="V97" s="10"/>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>2333</v>
       </c>
@@ -23742,7 +23751,7 @@
       </c>
       <c r="V98" s="10"/>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>2333</v>
       </c>
@@ -23813,7 +23822,7 @@
       </c>
       <c r="V99" s="10"/>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>2333</v>
       </c>
@@ -23884,7 +23893,7 @@
       </c>
       <c r="V100" s="10"/>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>2333</v>
       </c>
@@ -23955,7 +23964,7 @@
       </c>
       <c r="V101" s="10"/>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="10">
         <v>2333</v>
       </c>
@@ -24026,7 +24035,7 @@
       </c>
       <c r="V102" s="10"/>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>2333</v>
       </c>
@@ -24097,7 +24106,7 @@
       </c>
       <c r="V103" s="10"/>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>2333</v>
       </c>
@@ -24168,7 +24177,7 @@
       </c>
       <c r="V104" s="10"/>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>2333</v>
       </c>
@@ -24239,7 +24248,7 @@
       </c>
       <c r="V105" s="10"/>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>2333</v>
       </c>
@@ -24310,7 +24319,7 @@
       </c>
       <c r="V106" s="10"/>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>2333</v>
       </c>
@@ -24381,7 +24390,7 @@
       </c>
       <c r="V107" s="10"/>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>2333</v>
       </c>
@@ -24452,7 +24461,7 @@
       </c>
       <c r="V108" s="10"/>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="10">
         <v>2333</v>
       </c>
@@ -24523,7 +24532,7 @@
       </c>
       <c r="V109" s="10"/>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>2333</v>
       </c>
@@ -24594,7 +24603,7 @@
       </c>
       <c r="V110" s="10"/>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>2333</v>
       </c>
@@ -24665,7 +24674,7 @@
       </c>
       <c r="V111" s="10"/>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="10">
         <v>2333</v>
       </c>
@@ -24736,7 +24745,7 @@
       </c>
       <c r="V112" s="10"/>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>2333</v>
       </c>
@@ -24807,7 +24816,7 @@
       </c>
       <c r="V113" s="10"/>
     </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="10">
         <v>2333</v>
       </c>
@@ -24878,7 +24887,7 @@
       </c>
       <c r="V114" s="10"/>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="10">
         <v>2333</v>
       </c>
@@ -24949,7 +24958,7 @@
       </c>
       <c r="V115" s="10"/>
     </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="10">
         <v>2333</v>
       </c>
@@ -25020,7 +25029,7 @@
       </c>
       <c r="V116" s="10"/>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="10">
         <v>2333</v>
       </c>
@@ -25091,7 +25100,7 @@
       </c>
       <c r="V117" s="10"/>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="10">
         <v>2333</v>
       </c>
@@ -25162,7 +25171,7 @@
       </c>
       <c r="V118" s="10"/>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10">
         <v>2333</v>
       </c>
@@ -25233,7 +25242,7 @@
       </c>
       <c r="V119" s="10"/>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="10">
         <v>2333</v>
       </c>
@@ -25304,7 +25313,7 @@
       </c>
       <c r="V120" s="10"/>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10">
         <v>2333</v>
       </c>
@@ -25375,7 +25384,7 @@
       </c>
       <c r="V121" s="10"/>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10">
         <v>2333</v>
       </c>
@@ -25446,7 +25455,7 @@
       </c>
       <c r="V122" s="10"/>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="10">
         <v>2333</v>
       </c>
@@ -25517,7 +25526,7 @@
       </c>
       <c r="V123" s="10"/>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="10">
         <v>2333</v>
       </c>
@@ -25588,7 +25597,7 @@
       </c>
       <c r="V124" s="10"/>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="10">
         <v>2333</v>
       </c>
@@ -25659,7 +25668,7 @@
       </c>
       <c r="V125" s="10"/>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="10">
         <v>2333</v>
       </c>
@@ -25730,7 +25739,7 @@
       </c>
       <c r="V126" s="10"/>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="10">
         <v>2333</v>
       </c>
@@ -25801,7 +25810,7 @@
       </c>
       <c r="V127" s="10"/>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="10">
         <v>2333</v>
       </c>
@@ -25872,7 +25881,7 @@
       </c>
       <c r="V128" s="10"/>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="10">
         <v>2333</v>
       </c>
@@ -25943,7 +25952,7 @@
       </c>
       <c r="V129" s="10"/>
     </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="10">
         <v>2333</v>
       </c>
@@ -26014,7 +26023,7 @@
       </c>
       <c r="V130" s="10"/>
     </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="10">
         <v>2333</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A9A2AD-F6F2-43E5-9671-682B9C4521DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC64E12-5707-4091-8FF9-D1A9E6092291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
   <sheets>
     <sheet name="BAGACEIRAS" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4560" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4702" uniqueCount="278">
   <si>
     <t>O.S.</t>
   </si>
@@ -987,6 +987,27 @@
   <si>
     <t>Em Inspeção</t>
   </si>
+  <si>
+    <t>EM INSPEÇÃO</t>
+  </si>
+  <si>
+    <t>PENTE INFERIOR CONVENCIONAL FR 1" - 84"</t>
+  </si>
+  <si>
+    <t>PENTE INFERIOR CONVENCIONAL FR 2" - 84"</t>
+  </si>
+  <si>
+    <t>PENTE INFERIOR CONVENCIONAL FR 1.1/2" - 84"</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>RODETE MOENDA Z15 - 66"</t>
+  </si>
+  <si>
+    <t>RODETE MOENDA Z15 - 90"</t>
+  </si>
 </sst>
 </file>
 
@@ -1179,7 +1200,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1331,6 +1352,20 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3622,12 +3657,15 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="118" dataDxfId="117">
   <autoFilter ref="A1:AI114" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}">
-    <filterColumn colId="12">
+    <filterColumn colId="0">
       <filters>
-        <dateGroupItem year="2026" month="7" day="10" dateTimeGrouping="day"/>
-        <dateGroupItem year="2026" month="7" day="17" dateTimeGrouping="day"/>
-        <dateGroupItem year="2026" month="7" day="24" dateTimeGrouping="day"/>
-        <dateGroupItem year="2026" month="7" day="31" dateTimeGrouping="day"/>
+        <filter val="2199"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="2"/>
+        <filter val="5"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3686,14 +3724,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V131" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
-  <autoFilter ref="A1:V131" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="1495052"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V143" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
+  <autoFilter ref="A1:V143" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="79"/>
     <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="78"/>
@@ -3734,8 +3766,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E9C3BD9-7BAA-49FB-9F98-CFD415149194}" name="Tabela13" displayName="Tabela13" ref="A1:Z35" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
-  <autoFilter ref="A1:Z35" xr:uid="{2AC5416C-4E1B-4478-8A2A-B698870CAB96}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E9C3BD9-7BAA-49FB-9F98-CFD415149194}" name="Tabela13" displayName="Tabela13" ref="A1:Z39" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
+  <autoFilter ref="A1:Z39" xr:uid="{2AC5416C-4E1B-4478-8A2A-B698870CAB96}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{9A983B4E-3365-4153-9B40-D7FE26E8B98F}" name="PV " dataDxfId="55"/>
     <tableColumn id="2" xr3:uid="{4F16CD54-AAD4-4149-8D48-CC3FFEA93AA5}" name="Item" dataDxfId="54"/>
@@ -4300,7 +4332,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>2199</v>
       </c>
@@ -4346,7 +4378,7 @@
       <c r="O2" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P2" s="40" t="str">
         <f t="shared" ref="P2:P33" ca="1" si="0">IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -4373,7 +4405,7 @@
         <v>69</v>
       </c>
       <c r="W2" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X2" s="10" t="s">
         <v>77</v>
@@ -4385,14 +4417,13 @@
         <v>69</v>
       </c>
       <c r="AA2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB2" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="AB2" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC2" s="10" t="str">
-        <f t="shared" ref="AC2:AC33" si="1">IF(L2="","AG. FUNDIDO",IF(U2="AG","AG. USINAGEM","EM USINAGEM"))</f>
-        <v>EM USINAGEM</v>
+      <c r="AC2" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE2" s="42">
         <v>24</v>
@@ -4461,7 +4492,7 @@
       <c r="O3" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P3" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4506,7 +4537,7 @@
         <v>72</v>
       </c>
       <c r="AC3" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="AC2:AC33" si="1">IF(L3="","AG. FUNDIDO",IF(U3="AG","AG. USINAGEM","EM USINAGEM"))</f>
         <v>EM USINAGEM</v>
       </c>
       <c r="AE3" s="42">
@@ -4530,7 +4561,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <v>2199</v>
       </c>
@@ -4576,7 +4607,7 @@
       <c r="O4" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4597,10 +4628,10 @@
         <v>69</v>
       </c>
       <c r="U4" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V4" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="V4" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="W4" s="10" t="s">
         <v>72</v>
@@ -4645,7 +4676,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <v>2199</v>
       </c>
@@ -4691,7 +4722,7 @@
       <c r="O5" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P5" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4712,10 +4743,10 @@
         <v>69</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="V5" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W5" s="10" t="s">
         <v>72</v>
@@ -4806,7 +4837,7 @@
       <c r="O6" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P6" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4875,7 +4906,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>2199</v>
       </c>
@@ -4921,7 +4952,7 @@
       <c r="O7" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P7" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4942,10 +4973,10 @@
         <v>69</v>
       </c>
       <c r="U7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="V7" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="W7" s="10" t="s">
         <v>72</v>
@@ -4990,7 +5021,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>2199</v>
       </c>
@@ -5036,7 +5067,7 @@
       <c r="O8" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P8" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5072,17 +5103,16 @@
         <v>69</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC8" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>85</v>
+      </c>
+      <c r="AC8" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE8" s="42">
         <v>23</v>
@@ -5105,7 +5135,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>2199</v>
       </c>
@@ -5151,7 +5181,7 @@
       <c r="O9" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P9" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5187,17 +5217,16 @@
         <v>69</v>
       </c>
       <c r="Z9" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB9" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC9" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>85</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE9" s="42">
         <v>23</v>
@@ -5220,7 +5249,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>2199</v>
       </c>
@@ -5266,7 +5295,7 @@
       <c r="O10" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P10" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5302,17 +5331,16 @@
         <v>69</v>
       </c>
       <c r="Z10" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB10" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC10" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>85</v>
+      </c>
+      <c r="AC10" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE10" s="42">
         <v>23</v>
@@ -5335,7 +5363,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>2199</v>
       </c>
@@ -5381,7 +5409,7 @@
       <c r="O11" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P11" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5417,17 +5445,16 @@
         <v>69</v>
       </c>
       <c r="Z11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA11" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB11" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="AA11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC11" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+      <c r="AC11" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE11" s="42">
         <v>23</v>
@@ -5450,7 +5477,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>2201</v>
       </c>
@@ -5496,7 +5523,7 @@
       <c r="O12" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P12" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5565,7 +5592,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15">
         <v>2201</v>
       </c>
@@ -5611,7 +5638,7 @@
       <c r="O13" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P13" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5680,7 +5707,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15">
         <v>2201</v>
       </c>
@@ -5726,7 +5753,7 @@
       <c r="O14" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P14" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5795,7 +5822,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15">
         <v>2199</v>
       </c>
@@ -5841,7 +5868,7 @@
       <c r="O15" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P15" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5913,7 +5940,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>2199</v>
       </c>
@@ -5959,7 +5986,7 @@
       <c r="O16" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P16" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5998,14 +6025,13 @@
         <v>69</v>
       </c>
       <c r="AA16" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB16" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="AB16" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC16" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+      <c r="AC16" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE16" s="42">
         <v>26</v>
@@ -6028,7 +6054,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>2201</v>
       </c>
@@ -6074,7 +6100,7 @@
       <c r="O17" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P17" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6107,20 +6133,19 @@
         <v>77</v>
       </c>
       <c r="Y17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB17" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="Z17" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA17" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB17" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC17" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+      <c r="AC17" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE17" s="42">
         <v>26</v>
@@ -6143,7 +6168,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <v>2201</v>
       </c>
@@ -6189,7 +6214,7 @@
       <c r="O18" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P18" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6225,17 +6250,16 @@
         <v>69</v>
       </c>
       <c r="Z18" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB18" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC18" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>85</v>
+      </c>
+      <c r="AC18" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE18" s="42">
         <v>26</v>
@@ -6258,7 +6282,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>2201</v>
       </c>
@@ -6304,7 +6328,7 @@
       <c r="O19" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P19" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6340,17 +6364,16 @@
         <v>69</v>
       </c>
       <c r="Z19" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB19" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC19" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>85</v>
+      </c>
+      <c r="AC19" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE19" s="42">
         <v>26</v>
@@ -6373,7 +6396,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15">
         <v>2201</v>
       </c>
@@ -6416,7 +6439,7 @@
       <c r="O20" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P20" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6485,7 +6508,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
         <v>2201</v>
       </c>
@@ -6528,7 +6551,7 @@
       <c r="O21" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P21" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6597,7 +6620,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>2203</v>
       </c>
@@ -6643,7 +6666,7 @@
       <c r="O22" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P22" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6712,7 +6735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <v>2203</v>
       </c>
@@ -6758,7 +6781,7 @@
       <c r="O23" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P23" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6873,7 +6896,7 @@
       <c r="O24" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P24" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6900,7 +6923,7 @@
         <v>69</v>
       </c>
       <c r="W24" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X24" s="10" t="s">
         <v>77</v>
@@ -6988,7 +7011,7 @@
       <c r="O25" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P25" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7015,7 +7038,7 @@
         <v>69</v>
       </c>
       <c r="W25" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X25" s="10" t="s">
         <v>77</v>
@@ -7103,7 +7126,7 @@
       <c r="O26" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P26" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7127,10 +7150,10 @@
         <v>69</v>
       </c>
       <c r="V26" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W26" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X26" s="10" t="s">
         <v>77</v>
@@ -7218,7 +7241,7 @@
       <c r="O27" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P27" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7242,10 +7265,10 @@
         <v>69</v>
       </c>
       <c r="V27" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="W27" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="W27" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="X27" s="10" t="s">
         <v>77</v>
@@ -7333,7 +7356,7 @@
       <c r="O28" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P28" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7357,7 +7380,7 @@
         <v>69</v>
       </c>
       <c r="V28" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="W28" s="10" t="s">
         <v>72</v>
@@ -7448,7 +7471,7 @@
       <c r="O29" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P29" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7472,7 +7495,7 @@
         <v>69</v>
       </c>
       <c r="V29" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W29" s="10" t="s">
         <v>72</v>
@@ -7517,7 +7540,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
         <v>2203</v>
       </c>
@@ -7563,7 +7586,7 @@
       <c r="O30" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P30" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7632,7 +7655,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
         <v>2202</v>
       </c>
@@ -7678,7 +7701,7 @@
       <c r="O31" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P31" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7711,20 +7734,19 @@
         <v>77</v>
       </c>
       <c r="Y31" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z31" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA31" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB31" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="Z31" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA31" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB31" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC31" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+      <c r="AC31" s="10" t="s">
+        <v>271</v>
       </c>
       <c r="AE31" s="42">
         <v>27</v>
@@ -7747,7 +7769,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
         <v>2202</v>
       </c>
@@ -7793,7 +7815,7 @@
       <c r="O32" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P32" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7862,7 +7884,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15">
         <v>2202</v>
       </c>
@@ -7908,7 +7930,7 @@
       <c r="O33" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P33" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7977,7 +7999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15">
         <v>2202</v>
       </c>
@@ -8023,7 +8045,7 @@
       <c r="O34" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P34" s="40" t="str">
         <f t="shared" ref="P34:P65" ca="1" si="2">IF(O34&lt;0,"ATRASADO",IF(O34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -8092,7 +8114,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
         <v>2202</v>
       </c>
@@ -8138,7 +8160,7 @@
       <c r="O35" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P35" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8207,7 +8229,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
         <v>2201</v>
       </c>
@@ -8253,7 +8275,7 @@
       <c r="O36" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P36" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8274,7 +8296,7 @@
         <v>69</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V36" s="10" t="s">
         <v>72</v>
@@ -8299,7 +8321,7 @@
       </c>
       <c r="AC36" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE36" s="42">
         <v>27</v>
@@ -8322,7 +8344,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
         <v>2201</v>
       </c>
@@ -8368,7 +8390,7 @@
       <c r="O37" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P37" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8437,7 +8459,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
         <v>2205</v>
       </c>
@@ -8483,7 +8505,7 @@
       <c r="O38" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P38" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8552,7 +8574,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
         <v>2204</v>
       </c>
@@ -8595,7 +8617,7 @@
       <c r="O39" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P39" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8664,7 +8686,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
         <v>2204</v>
       </c>
@@ -8707,7 +8729,7 @@
       <c r="O40" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P40" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8776,7 +8798,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
         <v>2204</v>
       </c>
@@ -8822,7 +8844,7 @@
       <c r="O41" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P41" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8891,7 +8913,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
         <v>2204</v>
       </c>
@@ -8937,7 +8959,7 @@
       <c r="O42" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P42" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9006,7 +9028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
         <v>2204</v>
       </c>
@@ -9052,7 +9074,7 @@
       <c r="O43" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P43" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9121,7 +9143,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
         <v>2204</v>
       </c>
@@ -9164,7 +9186,7 @@
       <c r="O44" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P44" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9233,7 +9255,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
         <v>2203</v>
       </c>
@@ -9279,7 +9301,7 @@
       <c r="O45" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P45" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9348,7 +9370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
         <v>2203</v>
       </c>
@@ -9394,7 +9416,7 @@
       <c r="O46" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P46" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9463,7 +9485,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <v>2203</v>
       </c>
@@ -9509,7 +9531,7 @@
       <c r="O47" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P47" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9621,7 +9643,7 @@
       <c r="O48" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P48" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9734,7 +9756,7 @@
       <c r="O49" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P49" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9847,7 +9869,7 @@
       <c r="O50" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P50" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9962,7 +9984,7 @@
       <c r="O51" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P51" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10077,7 +10099,7 @@
       <c r="O52" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P52" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10192,7 +10214,7 @@
       <c r="O53" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P53" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10304,7 +10326,7 @@
       <c r="O54" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P54" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10416,7 +10438,7 @@
       <c r="O55" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P55" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10528,7 +10550,7 @@
       <c r="O56" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P56" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10640,7 +10662,7 @@
       <c r="O57" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P57" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10755,7 +10777,7 @@
       <c r="O58" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P58" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10870,7 +10892,7 @@
       <c r="O59" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P59" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10939,7 +10961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15">
         <v>2226</v>
       </c>
@@ -10982,7 +11004,7 @@
       <c r="O60" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P60" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11046,7 +11068,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15">
         <v>2226</v>
       </c>
@@ -11089,7 +11111,7 @@
       <c r="O61" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P61" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11153,7 +11175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15">
         <v>2226</v>
       </c>
@@ -11199,7 +11221,7 @@
       <c r="O62" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P62" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11263,7 +11285,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="15">
         <v>2226</v>
       </c>
@@ -11309,7 +11331,7 @@
       <c r="O63" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P63" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11373,7 +11395,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15">
         <v>2226</v>
       </c>
@@ -11419,7 +11441,7 @@
       <c r="O64" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P64" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11483,7 +11505,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15">
         <v>2226</v>
       </c>
@@ -11526,7 +11548,7 @@
       <c r="O65" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P65" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11590,7 +11612,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="15">
         <v>2226</v>
       </c>
@@ -11636,7 +11658,7 @@
       <c r="O66" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P66" s="40" t="str">
         <f t="shared" ref="P66:P89" ca="1" si="4">IF(O66&lt;0,"ATRASADO",IF(O66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -11743,7 +11765,7 @@
       <c r="O67" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P67" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11858,7 +11880,7 @@
       <c r="O68" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P68" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11970,7 +11992,7 @@
       <c r="O69" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P69" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12082,7 +12104,7 @@
       <c r="O70" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P70" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12194,7 +12216,7 @@
       <c r="O71" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P71" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12306,7 +12328,7 @@
       <c r="O72" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P72" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12418,7 +12440,7 @@
       <c r="O73" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P73" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12530,7 +12552,7 @@
       <c r="O74" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P74" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12642,7 +12664,7 @@
       <c r="O75" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P75" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12754,7 +12776,7 @@
       <c r="O76" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P76" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12866,7 +12888,7 @@
       <c r="O77" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P77" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12978,7 +13000,7 @@
       <c r="O78" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P78" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13088,7 +13110,7 @@
       <c r="O79" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P79" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13198,7 +13220,7 @@
       <c r="O80" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P80" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13308,7 +13330,7 @@
       <c r="O81" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P81" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13418,7 +13440,7 @@
       <c r="O82" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P82" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13528,7 +13550,7 @@
       <c r="O83" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P83" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13638,7 +13660,7 @@
       <c r="O84" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P84" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13752,7 +13774,7 @@
       <c r="O85" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P85" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13866,7 +13888,7 @@
       <c r="O86" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P86" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13980,7 +14002,7 @@
       <c r="O87" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P87" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14094,7 +14116,7 @@
       <c r="O88" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P88" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14208,7 +14230,7 @@
       <c r="O89" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P89" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14322,7 +14344,7 @@
       <c r="O90" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P90" s="40" t="str">
         <f t="shared" ref="P90:P94" ca="1" si="6">IF(O90&lt;0,"ATRASADO",IF(O90&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -14429,7 +14451,7 @@
       <c r="O91" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P91" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -14536,7 +14558,7 @@
       <c r="O92" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P92" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -14643,7 +14665,7 @@
       <c r="O93" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P93" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -14750,7 +14772,7 @@
       <c r="O94" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P94" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -14857,7 +14879,7 @@
       <c r="O95" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P95" s="40" t="str">
         <f t="shared" ref="P95:P99" ca="1" si="7">IF(O95&lt;0,"ATRASADO",IF(O95&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -14954,7 +14976,7 @@
       <c r="O96" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P96" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -15051,7 +15073,7 @@
       <c r="O97" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P97" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -15148,7 +15170,7 @@
       <c r="O98" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P98" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -15245,7 +15267,7 @@
       <c r="O99" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P99" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -15342,7 +15364,7 @@
       <c r="O100" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P100" s="40" t="str">
         <f ca="1">IF(O100&lt;0,"ATRASADO",IF(O100&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -15439,7 +15461,7 @@
       <c r="O101" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P101" s="40" t="str">
         <f t="shared" ref="P101:P109" ca="1" si="9">IF(O101&lt;0,"ATRASADO",IF(O101&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -15536,7 +15558,7 @@
       <c r="O102" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P102" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -15633,7 +15655,7 @@
       <c r="O103" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P103" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -15730,7 +15752,7 @@
       <c r="O104" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P104" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -15827,7 +15849,7 @@
       <c r="O105" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P105" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -15924,7 +15946,7 @@
       <c r="O106" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P106" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -16021,7 +16043,7 @@
       <c r="O107" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P107" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -16118,7 +16140,7 @@
       <c r="O108" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P108" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -16215,7 +16237,7 @@
       <c r="O109" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P109" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -16312,7 +16334,7 @@
       <c r="O110" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P110" s="40" t="str">
         <f ca="1">IF(O110&lt;0,"ATRASADO",IF(O110&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16409,7 +16431,7 @@
       <c r="O111" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P111" s="40" t="str">
         <f t="shared" ref="P111:P114" ca="1" si="10">IF(O111&lt;0,"ATRASADO",IF(O111&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16506,7 +16528,7 @@
       <c r="O112" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P112" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -16603,7 +16625,7 @@
       <c r="O113" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P113" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -16700,7 +16722,7 @@
       <c r="O114" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P114" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -16768,7 +16790,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F053A7-2FDA-4BCA-8A08-44A595E3BEFC}">
-  <dimension ref="A1:V131"/>
+  <dimension ref="A1:V143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="1"/>
@@ -16910,7 +16932,7 @@
       <c r="Q2" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R2" s="10" t="str">
         <f t="shared" ref="R2:R33" ca="1" si="0">IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16981,7 +17003,7 @@
       <c r="Q3" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R3" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17052,7 +17074,7 @@
       <c r="Q4" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R4" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17123,7 +17145,7 @@
       <c r="Q5" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R5" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17194,7 +17216,7 @@
       <c r="Q6" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R6" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17265,7 +17287,7 @@
       <c r="Q7" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R7" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17336,7 +17358,7 @@
       <c r="Q8" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R8" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17407,7 +17429,7 @@
       <c r="Q9" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R9" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17478,7 +17500,7 @@
       <c r="Q10" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R10" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17497,7 +17519,7 @@
       </c>
       <c r="V10" s="10"/>
     </row>
-    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>2226</v>
       </c>
@@ -17549,7 +17571,7 @@
       <c r="Q11" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R11" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17570,7 +17592,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>2226</v>
       </c>
@@ -17622,7 +17644,7 @@
       <c r="Q12" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R12" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17643,7 +17665,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="13" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>2226</v>
       </c>
@@ -17695,7 +17717,7 @@
       <c r="Q13" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R13" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17716,7 +17738,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="14" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>2227</v>
       </c>
@@ -17768,7 +17790,7 @@
       <c r="Q14" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R14" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17787,7 +17809,7 @@
       </c>
       <c r="V14" s="10"/>
     </row>
-    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>2227</v>
       </c>
@@ -17839,7 +17861,7 @@
       <c r="Q15" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R15" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17858,7 +17880,7 @@
       </c>
       <c r="V15" s="10"/>
     </row>
-    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>2227</v>
       </c>
@@ -17910,7 +17932,7 @@
       <c r="Q16" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R16" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17929,7 +17951,7 @@
       </c>
       <c r="V16" s="10"/>
     </row>
-    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>2227</v>
       </c>
@@ -17981,7 +18003,7 @@
       <c r="Q17" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R17" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18000,7 +18022,7 @@
       </c>
       <c r="V17" s="10"/>
     </row>
-    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>2227</v>
       </c>
@@ -18052,7 +18074,7 @@
       <c r="Q18" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R18" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18071,7 +18093,7 @@
       </c>
       <c r="V18" s="10"/>
     </row>
-    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>2227</v>
       </c>
@@ -18123,7 +18145,7 @@
       <c r="Q19" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R19" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18142,7 +18164,7 @@
       </c>
       <c r="V19" s="10"/>
     </row>
-    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>2227</v>
       </c>
@@ -18194,7 +18216,7 @@
       <c r="Q20" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R20" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18213,7 +18235,7 @@
       </c>
       <c r="V20" s="10"/>
     </row>
-    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>2227</v>
       </c>
@@ -18265,7 +18287,7 @@
       <c r="Q21" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R21" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18284,7 +18306,7 @@
       </c>
       <c r="V21" s="10"/>
     </row>
-    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>2227</v>
       </c>
@@ -18336,7 +18358,7 @@
       <c r="Q22" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R22" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18355,7 +18377,7 @@
       </c>
       <c r="V22" s="10"/>
     </row>
-    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>2227</v>
       </c>
@@ -18407,7 +18429,7 @@
       <c r="Q23" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R23" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18426,7 +18448,7 @@
       </c>
       <c r="V23" s="10"/>
     </row>
-    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>2227</v>
       </c>
@@ -18478,7 +18500,7 @@
       <c r="Q24" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R24" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18497,7 +18519,7 @@
       </c>
       <c r="V24" s="10"/>
     </row>
-    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>2227</v>
       </c>
@@ -18549,7 +18571,7 @@
       <c r="Q25" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R25" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18568,7 +18590,7 @@
       </c>
       <c r="V25" s="10"/>
     </row>
-    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>2227</v>
       </c>
@@ -18620,7 +18642,7 @@
       <c r="Q26" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R26" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18639,7 +18661,7 @@
       </c>
       <c r="V26" s="10"/>
     </row>
-    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>2227</v>
       </c>
@@ -18691,7 +18713,7 @@
       <c r="Q27" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R27" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18710,7 +18732,7 @@
       </c>
       <c r="V27" s="10"/>
     </row>
-    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>2227</v>
       </c>
@@ -18762,7 +18784,7 @@
       <c r="Q28" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R28" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18781,7 +18803,7 @@
       </c>
       <c r="V28" s="10"/>
     </row>
-    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>2227</v>
       </c>
@@ -18833,7 +18855,7 @@
       <c r="Q29" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R29" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18852,7 +18874,7 @@
       </c>
       <c r="V29" s="10"/>
     </row>
-    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>2227</v>
       </c>
@@ -18904,7 +18926,7 @@
       <c r="Q30" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R30" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18923,7 +18945,7 @@
       </c>
       <c r="V30" s="10"/>
     </row>
-    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>2227</v>
       </c>
@@ -18975,7 +18997,7 @@
       <c r="Q31" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R31" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18994,7 +19016,7 @@
       </c>
       <c r="V31" s="10"/>
     </row>
-    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>2227</v>
       </c>
@@ -19046,7 +19068,7 @@
       <c r="Q32" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R32" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19065,7 +19087,7 @@
       </c>
       <c r="V32" s="10"/>
     </row>
-    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>1951</v>
       </c>
@@ -19117,7 +19139,7 @@
       <c r="Q33" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19136,7 +19158,7 @@
       </c>
       <c r="V33" s="10"/>
     </row>
-    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>1951</v>
       </c>
@@ -19188,7 +19210,7 @@
       <c r="Q34" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R34" s="10" t="str">
         <f t="shared" ref="R34:R65" ca="1" si="1">IF(Q34&lt;0,"ATRASADO",IF(Q34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -19207,7 +19229,7 @@
       </c>
       <c r="V34" s="10"/>
     </row>
-    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>1951</v>
       </c>
@@ -19259,7 +19281,7 @@
       <c r="Q35" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R35" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19278,7 +19300,7 @@
       </c>
       <c r="V35" s="10"/>
     </row>
-    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>1951</v>
       </c>
@@ -19330,7 +19352,7 @@
       <c r="Q36" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R36" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19349,7 +19371,7 @@
       </c>
       <c r="V36" s="10"/>
     </row>
-    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>1951</v>
       </c>
@@ -19401,7 +19423,7 @@
       <c r="Q37" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R37" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19420,7 +19442,7 @@
       </c>
       <c r="V37" s="10"/>
     </row>
-    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
         <v>1031</v>
       </c>
@@ -19472,7 +19494,7 @@
       <c r="Q38" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R38" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19491,7 +19513,7 @@
       </c>
       <c r="V38" s="10"/>
     </row>
-    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
         <v>1031</v>
       </c>
@@ -19543,7 +19565,7 @@
       <c r="Q39" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R39" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19562,7 +19584,7 @@
       </c>
       <c r="V39" s="10"/>
     </row>
-    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
         <v>1031</v>
       </c>
@@ -19614,7 +19636,7 @@
       <c r="Q40" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R40" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19633,7 +19655,7 @@
       </c>
       <c r="V40" s="10"/>
     </row>
-    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
         <v>1031</v>
       </c>
@@ -19685,7 +19707,7 @@
       <c r="Q41" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R41" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19704,7 +19726,7 @@
       </c>
       <c r="V41" s="10"/>
     </row>
-    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
         <v>1031</v>
       </c>
@@ -19756,7 +19778,7 @@
       <c r="Q42" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R42" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19775,7 +19797,7 @@
       </c>
       <c r="V42" s="10"/>
     </row>
-    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
         <v>1031</v>
       </c>
@@ -19827,7 +19849,7 @@
       <c r="Q43" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R43" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19846,7 +19868,7 @@
       </c>
       <c r="V43" s="10"/>
     </row>
-    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
         <v>1031</v>
       </c>
@@ -19898,7 +19920,7 @@
       <c r="Q44" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R44" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19917,7 +19939,7 @@
       </c>
       <c r="V44" s="10"/>
     </row>
-    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
         <v>1031</v>
       </c>
@@ -19969,7 +19991,7 @@
       <c r="Q45" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R45" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19988,7 +20010,7 @@
       </c>
       <c r="V45" s="10"/>
     </row>
-    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
         <v>1031</v>
       </c>
@@ -20040,7 +20062,7 @@
       <c r="Q46" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R46" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20059,7 +20081,7 @@
       </c>
       <c r="V46" s="10"/>
     </row>
-    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <v>1031</v>
       </c>
@@ -20111,7 +20133,7 @@
       <c r="Q47" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R47" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20130,7 +20152,7 @@
       </c>
       <c r="V47" s="10"/>
     </row>
-    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="15">
         <v>1031</v>
       </c>
@@ -20182,7 +20204,7 @@
       <c r="Q48" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R48" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20201,7 +20223,7 @@
       </c>
       <c r="V48" s="10"/>
     </row>
-    <row r="49" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="15">
         <v>1031</v>
       </c>
@@ -20253,7 +20275,7 @@
       <c r="Q49" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R49" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20272,7 +20294,7 @@
       </c>
       <c r="V49" s="10"/>
     </row>
-    <row r="50" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="15">
         <v>1031</v>
       </c>
@@ -20324,7 +20346,7 @@
       <c r="Q50" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R50" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20343,7 +20365,7 @@
       </c>
       <c r="V50" s="10"/>
     </row>
-    <row r="51" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="15">
         <v>1031</v>
       </c>
@@ -20395,7 +20417,7 @@
       <c r="Q51" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R51" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20414,7 +20436,7 @@
       </c>
       <c r="V51" s="10"/>
     </row>
-    <row r="52" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" s="15">
         <v>1031</v>
       </c>
@@ -20466,7 +20488,7 @@
       <c r="Q52" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R52" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20485,7 +20507,7 @@
       </c>
       <c r="V52" s="10"/>
     </row>
-    <row r="53" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="15">
         <v>1031</v>
       </c>
@@ -20537,7 +20559,7 @@
       <c r="Q53" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R53" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20556,7 +20578,7 @@
       </c>
       <c r="V53" s="10"/>
     </row>
-    <row r="54" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="15">
         <v>1031</v>
       </c>
@@ -20608,7 +20630,7 @@
       <c r="Q54" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R54" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20627,7 +20649,7 @@
       </c>
       <c r="V54" s="10"/>
     </row>
-    <row r="55" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="15">
         <v>1031</v>
       </c>
@@ -20679,7 +20701,7 @@
       <c r="Q55" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R55" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20698,7 +20720,7 @@
       </c>
       <c r="V55" s="10"/>
     </row>
-    <row r="56" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="15">
         <v>1031</v>
       </c>
@@ -20750,7 +20772,7 @@
       <c r="Q56" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R56" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20769,7 +20791,7 @@
       </c>
       <c r="V56" s="10"/>
     </row>
-    <row r="57" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="15">
         <v>1031</v>
       </c>
@@ -20821,7 +20843,7 @@
       <c r="Q57" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R57" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20840,7 +20862,7 @@
       </c>
       <c r="V57" s="10"/>
     </row>
-    <row r="58" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="15">
         <v>1031</v>
       </c>
@@ -20892,7 +20914,7 @@
       <c r="Q58" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R58" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20911,7 +20933,7 @@
       </c>
       <c r="V58" s="10"/>
     </row>
-    <row r="59" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="15">
         <v>1031</v>
       </c>
@@ -20963,7 +20985,7 @@
       <c r="Q59" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R59" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20982,7 +21004,7 @@
       </c>
       <c r="V59" s="10"/>
     </row>
-    <row r="60" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="15">
         <v>1031</v>
       </c>
@@ -21034,7 +21056,7 @@
       <c r="Q60" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R60" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21053,7 +21075,7 @@
       </c>
       <c r="V60" s="10"/>
     </row>
-    <row r="61" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="15">
         <v>1031</v>
       </c>
@@ -21105,7 +21127,7 @@
       <c r="Q61" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R61" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21124,7 +21146,7 @@
       </c>
       <c r="V61" s="10"/>
     </row>
-    <row r="62" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="15">
         <v>1031</v>
       </c>
@@ -21176,7 +21198,7 @@
       <c r="Q62" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R62" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21195,7 +21217,7 @@
       </c>
       <c r="V62" s="10"/>
     </row>
-    <row r="63" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="15">
         <v>1031</v>
       </c>
@@ -21247,7 +21269,7 @@
       <c r="Q63" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R63" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21266,7 +21288,7 @@
       </c>
       <c r="V63" s="10"/>
     </row>
-    <row r="64" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="15">
         <v>1031</v>
       </c>
@@ -21318,7 +21340,7 @@
       <c r="Q64" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R64" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21337,7 +21359,7 @@
       </c>
       <c r="V64" s="10"/>
     </row>
-    <row r="65" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" s="15">
         <v>1031</v>
       </c>
@@ -21389,7 +21411,7 @@
       <c r="Q65" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R65" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21408,7 +21430,7 @@
       </c>
       <c r="V65" s="10"/>
     </row>
-    <row r="66" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" s="15">
         <v>1031</v>
       </c>
@@ -21460,7 +21482,7 @@
       <c r="Q66" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R66" s="10" t="str">
         <f t="shared" ref="R66:R91" ca="1" si="2">IF(Q66&lt;0,"ATRASADO",IF(Q66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -21479,7 +21501,7 @@
       </c>
       <c r="V66" s="10"/>
     </row>
-    <row r="67" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="15">
         <v>1031</v>
       </c>
@@ -21531,7 +21553,7 @@
       <c r="Q67" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R67" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21550,7 +21572,7 @@
       </c>
       <c r="V67" s="10"/>
     </row>
-    <row r="68" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" s="15">
         <v>1031</v>
       </c>
@@ -21602,7 +21624,7 @@
       <c r="Q68" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R68" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21621,7 +21643,7 @@
       </c>
       <c r="V68" s="10"/>
     </row>
-    <row r="69" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="15">
         <v>1031</v>
       </c>
@@ -21673,7 +21695,7 @@
       <c r="Q69" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R69" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21692,7 +21714,7 @@
       </c>
       <c r="V69" s="10"/>
     </row>
-    <row r="70" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" s="15">
         <v>1031</v>
       </c>
@@ -21744,7 +21766,7 @@
       <c r="Q70" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R70" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21763,7 +21785,7 @@
       </c>
       <c r="V70" s="10"/>
     </row>
-    <row r="71" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" s="15">
         <v>1031</v>
       </c>
@@ -21815,7 +21837,7 @@
       <c r="Q71" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R71" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21834,7 +21856,7 @@
       </c>
       <c r="V71" s="10"/>
     </row>
-    <row r="72" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" s="15">
         <v>1031</v>
       </c>
@@ -21886,7 +21908,7 @@
       <c r="Q72" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R72" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21905,7 +21927,7 @@
       </c>
       <c r="V72" s="10"/>
     </row>
-    <row r="73" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" s="15">
         <v>1031</v>
       </c>
@@ -21957,7 +21979,7 @@
       <c r="Q73" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R73" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21976,7 +21998,7 @@
       </c>
       <c r="V73" s="10"/>
     </row>
-    <row r="74" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" s="15">
         <v>1031</v>
       </c>
@@ -22028,7 +22050,7 @@
       <c r="Q74" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R74" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22047,7 +22069,7 @@
       </c>
       <c r="V74" s="10"/>
     </row>
-    <row r="75" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" s="15">
         <v>1031</v>
       </c>
@@ -22099,7 +22121,7 @@
       <c r="Q75" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R75" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22118,7 +22140,7 @@
       </c>
       <c r="V75" s="10"/>
     </row>
-    <row r="76" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" s="15">
         <v>1031</v>
       </c>
@@ -22170,7 +22192,7 @@
       <c r="Q76" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R76" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22189,7 +22211,7 @@
       </c>
       <c r="V76" s="10"/>
     </row>
-    <row r="77" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" s="15">
         <v>1031</v>
       </c>
@@ -22241,7 +22263,7 @@
       <c r="Q77" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R77" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22260,7 +22282,7 @@
       </c>
       <c r="V77" s="10"/>
     </row>
-    <row r="78" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" s="15">
         <v>1031</v>
       </c>
@@ -22312,7 +22334,7 @@
       <c r="Q78" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R78" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22331,7 +22353,7 @@
       </c>
       <c r="V78" s="10"/>
     </row>
-    <row r="79" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" s="15">
         <v>1031</v>
       </c>
@@ -22383,7 +22405,7 @@
       <c r="Q79" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R79" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22402,7 +22424,7 @@
       </c>
       <c r="V79" s="10"/>
     </row>
-    <row r="80" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="15">
         <v>1031</v>
       </c>
@@ -22454,7 +22476,7 @@
       <c r="Q80" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R80" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22473,7 +22495,7 @@
       </c>
       <c r="V80" s="10"/>
     </row>
-    <row r="81" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" s="15">
         <v>1031</v>
       </c>
@@ -22525,7 +22547,7 @@
       <c r="Q81" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R81" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22544,7 +22566,7 @@
       </c>
       <c r="V81" s="10"/>
     </row>
-    <row r="82" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="15">
         <v>1031</v>
       </c>
@@ -22596,7 +22618,7 @@
       <c r="Q82" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R82" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22615,7 +22637,7 @@
       </c>
       <c r="V82" s="10"/>
     </row>
-    <row r="83" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" s="15">
         <v>1031</v>
       </c>
@@ -22667,7 +22689,7 @@
       <c r="Q83" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R83" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22686,7 +22708,7 @@
       </c>
       <c r="V83" s="10"/>
     </row>
-    <row r="84" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>1031</v>
       </c>
@@ -22738,7 +22760,7 @@
       <c r="Q84" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R84" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22757,7 +22779,7 @@
       </c>
       <c r="V84" s="10"/>
     </row>
-    <row r="85" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>1031</v>
       </c>
@@ -22809,7 +22831,7 @@
       <c r="Q85" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R85" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22828,7 +22850,7 @@
       </c>
       <c r="V85" s="10"/>
     </row>
-    <row r="86" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>1031</v>
       </c>
@@ -22880,7 +22902,7 @@
       <c r="Q86" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R86" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22899,7 +22921,7 @@
       </c>
       <c r="V86" s="10"/>
     </row>
-    <row r="87" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>1031</v>
       </c>
@@ -22951,7 +22973,7 @@
       <c r="Q87" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R87" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22970,7 +22992,7 @@
       </c>
       <c r="V87" s="10"/>
     </row>
-    <row r="88" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>1031</v>
       </c>
@@ -23022,7 +23044,7 @@
       <c r="Q88" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R88" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23041,7 +23063,7 @@
       </c>
       <c r="V88" s="10"/>
     </row>
-    <row r="89" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>1031</v>
       </c>
@@ -23093,7 +23115,7 @@
       <c r="Q89" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R89" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23112,7 +23134,7 @@
       </c>
       <c r="V89" s="10"/>
     </row>
-    <row r="90" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" s="15">
         <v>1031</v>
       </c>
@@ -23164,7 +23186,7 @@
       <c r="Q90" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R90" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23183,7 +23205,7 @@
       </c>
       <c r="V90" s="10"/>
     </row>
-    <row r="91" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" s="15">
         <v>1031</v>
       </c>
@@ -23235,7 +23257,7 @@
       <c r="Q91" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R91" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23254,7 +23276,7 @@
       </c>
       <c r="V91" s="10"/>
     </row>
-    <row r="92" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>2333</v>
       </c>
@@ -23306,7 +23328,7 @@
       <c r="Q92" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R92" s="10" t="str">
         <f ca="1">IF(Q92&lt;0,"ATRASADO",IF(Q92&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23325,7 +23347,7 @@
       </c>
       <c r="V92" s="10"/>
     </row>
-    <row r="93" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>2333</v>
       </c>
@@ -23377,7 +23399,7 @@
       <c r="Q93" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R93" s="10" t="str">
         <f ca="1">IF(Q93&lt;0,"ATRASADO",IF(Q93&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23396,7 +23418,7 @@
       </c>
       <c r="V93" s="10"/>
     </row>
-    <row r="94" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>2333</v>
       </c>
@@ -23448,7 +23470,7 @@
       <c r="Q94" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R94" s="10" t="str">
         <f t="shared" ref="R94:R131" ca="1" si="3">IF(Q94&lt;0,"ATRASADO",IF(Q94&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23467,7 +23489,7 @@
       </c>
       <c r="V94" s="10"/>
     </row>
-    <row r="95" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>2333</v>
       </c>
@@ -23519,7 +23541,7 @@
       <c r="Q95" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R95" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23538,7 +23560,7 @@
       </c>
       <c r="V95" s="10"/>
     </row>
-    <row r="96" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>2333</v>
       </c>
@@ -23590,7 +23612,7 @@
       <c r="Q96" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R96" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23609,7 +23631,7 @@
       </c>
       <c r="V96" s="10"/>
     </row>
-    <row r="97" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>2333</v>
       </c>
@@ -23661,7 +23683,7 @@
       <c r="Q97" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R97" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23680,7 +23702,7 @@
       </c>
       <c r="V97" s="10"/>
     </row>
-    <row r="98" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>2333</v>
       </c>
@@ -23732,7 +23754,7 @@
       <c r="Q98" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R98" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23751,7 +23773,7 @@
       </c>
       <c r="V98" s="10"/>
     </row>
-    <row r="99" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>2333</v>
       </c>
@@ -23803,7 +23825,7 @@
       <c r="Q99" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R99" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23822,7 +23844,7 @@
       </c>
       <c r="V99" s="10"/>
     </row>
-    <row r="100" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>2333</v>
       </c>
@@ -23874,7 +23896,7 @@
       <c r="Q100" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R100" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23893,7 +23915,7 @@
       </c>
       <c r="V100" s="10"/>
     </row>
-    <row r="101" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>2333</v>
       </c>
@@ -23945,7 +23967,7 @@
       <c r="Q101" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R101" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23964,7 +23986,7 @@
       </c>
       <c r="V101" s="10"/>
     </row>
-    <row r="102" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A102" s="10">
         <v>2333</v>
       </c>
@@ -24016,7 +24038,7 @@
       <c r="Q102" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R102" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24035,7 +24057,7 @@
       </c>
       <c r="V102" s="10"/>
     </row>
-    <row r="103" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>2333</v>
       </c>
@@ -24087,7 +24109,7 @@
       <c r="Q103" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R103" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24106,7 +24128,7 @@
       </c>
       <c r="V103" s="10"/>
     </row>
-    <row r="104" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>2333</v>
       </c>
@@ -24158,7 +24180,7 @@
       <c r="Q104" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R104" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24177,7 +24199,7 @@
       </c>
       <c r="V104" s="10"/>
     </row>
-    <row r="105" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>2333</v>
       </c>
@@ -24229,7 +24251,7 @@
       <c r="Q105" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R105" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24248,7 +24270,7 @@
       </c>
       <c r="V105" s="10"/>
     </row>
-    <row r="106" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>2333</v>
       </c>
@@ -24300,7 +24322,7 @@
       <c r="Q106" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R106" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24319,7 +24341,7 @@
       </c>
       <c r="V106" s="10"/>
     </row>
-    <row r="107" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>2333</v>
       </c>
@@ -24371,7 +24393,7 @@
       <c r="Q107" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R107" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24390,7 +24412,7 @@
       </c>
       <c r="V107" s="10"/>
     </row>
-    <row r="108" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>2333</v>
       </c>
@@ -24442,7 +24464,7 @@
       <c r="Q108" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R108" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24461,7 +24483,7 @@
       </c>
       <c r="V108" s="10"/>
     </row>
-    <row r="109" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A109" s="10">
         <v>2333</v>
       </c>
@@ -24513,7 +24535,7 @@
       <c r="Q109" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R109" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24532,7 +24554,7 @@
       </c>
       <c r="V109" s="10"/>
     </row>
-    <row r="110" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>2333</v>
       </c>
@@ -24584,7 +24606,7 @@
       <c r="Q110" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R110" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24603,7 +24625,7 @@
       </c>
       <c r="V110" s="10"/>
     </row>
-    <row r="111" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>2333</v>
       </c>
@@ -24655,7 +24677,7 @@
       <c r="Q111" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R111" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24674,7 +24696,7 @@
       </c>
       <c r="V111" s="10"/>
     </row>
-    <row r="112" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A112" s="10">
         <v>2333</v>
       </c>
@@ -24726,7 +24748,7 @@
       <c r="Q112" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R112" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24745,7 +24767,7 @@
       </c>
       <c r="V112" s="10"/>
     </row>
-    <row r="113" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>2333</v>
       </c>
@@ -24797,7 +24819,7 @@
       <c r="Q113" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R113" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24816,7 +24838,7 @@
       </c>
       <c r="V113" s="10"/>
     </row>
-    <row r="114" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A114" s="10">
         <v>2333</v>
       </c>
@@ -24868,7 +24890,7 @@
       <c r="Q114" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R114" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24887,7 +24909,7 @@
       </c>
       <c r="V114" s="10"/>
     </row>
-    <row r="115" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A115" s="10">
         <v>2333</v>
       </c>
@@ -24939,7 +24961,7 @@
       <c r="Q115" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R115" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24958,7 +24980,7 @@
       </c>
       <c r="V115" s="10"/>
     </row>
-    <row r="116" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A116" s="10">
         <v>2333</v>
       </c>
@@ -25010,7 +25032,7 @@
       <c r="Q116" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R116" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25029,7 +25051,7 @@
       </c>
       <c r="V116" s="10"/>
     </row>
-    <row r="117" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A117" s="10">
         <v>2333</v>
       </c>
@@ -25081,7 +25103,7 @@
       <c r="Q117" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R117" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25100,7 +25122,7 @@
       </c>
       <c r="V117" s="10"/>
     </row>
-    <row r="118" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A118" s="10">
         <v>2333</v>
       </c>
@@ -25152,7 +25174,7 @@
       <c r="Q118" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R118" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25171,7 +25193,7 @@
       </c>
       <c r="V118" s="10"/>
     </row>
-    <row r="119" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A119" s="10">
         <v>2333</v>
       </c>
@@ -25223,7 +25245,7 @@
       <c r="Q119" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R119" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25242,7 +25264,7 @@
       </c>
       <c r="V119" s="10"/>
     </row>
-    <row r="120" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A120" s="10">
         <v>2333</v>
       </c>
@@ -25294,7 +25316,7 @@
       <c r="Q120" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R120" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25313,7 +25335,7 @@
       </c>
       <c r="V120" s="10"/>
     </row>
-    <row r="121" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A121" s="10">
         <v>2333</v>
       </c>
@@ -25365,7 +25387,7 @@
       <c r="Q121" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R121" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25384,7 +25406,7 @@
       </c>
       <c r="V121" s="10"/>
     </row>
-    <row r="122" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A122" s="10">
         <v>2333</v>
       </c>
@@ -25436,7 +25458,7 @@
       <c r="Q122" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R122" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25455,7 +25477,7 @@
       </c>
       <c r="V122" s="10"/>
     </row>
-    <row r="123" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A123" s="10">
         <v>2333</v>
       </c>
@@ -25507,7 +25529,7 @@
       <c r="Q123" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R123" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25526,7 +25548,7 @@
       </c>
       <c r="V123" s="10"/>
     </row>
-    <row r="124" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A124" s="10">
         <v>2333</v>
       </c>
@@ -25578,7 +25600,7 @@
       <c r="Q124" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R124" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25597,7 +25619,7 @@
       </c>
       <c r="V124" s="10"/>
     </row>
-    <row r="125" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A125" s="10">
         <v>2333</v>
       </c>
@@ -25649,7 +25671,7 @@
       <c r="Q125" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R125" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25668,7 +25690,7 @@
       </c>
       <c r="V125" s="10"/>
     </row>
-    <row r="126" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A126" s="10">
         <v>2333</v>
       </c>
@@ -25720,7 +25742,7 @@
       <c r="Q126" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R126" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25739,7 +25761,7 @@
       </c>
       <c r="V126" s="10"/>
     </row>
-    <row r="127" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A127" s="10">
         <v>2333</v>
       </c>
@@ -25791,7 +25813,7 @@
       <c r="Q127" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R127" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25810,7 +25832,7 @@
       </c>
       <c r="V127" s="10"/>
     </row>
-    <row r="128" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A128" s="10">
         <v>2333</v>
       </c>
@@ -25862,7 +25884,7 @@
       <c r="Q128" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R128" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25881,7 +25903,7 @@
       </c>
       <c r="V128" s="10"/>
     </row>
-    <row r="129" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A129" s="10">
         <v>2333</v>
       </c>
@@ -25933,7 +25955,7 @@
       <c r="Q129" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R129" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25952,7 +25974,7 @@
       </c>
       <c r="V129" s="10"/>
     </row>
-    <row r="130" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A130" s="10">
         <v>2333</v>
       </c>
@@ -26004,7 +26026,7 @@
       <c r="Q130" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R130" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26023,7 +26045,7 @@
       </c>
       <c r="V130" s="10"/>
     </row>
-    <row r="131" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A131" s="10">
         <v>2333</v>
       </c>
@@ -26075,7 +26097,7 @@
       <c r="Q131" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R131" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26093,6 +26115,834 @@
         <v>61</v>
       </c>
       <c r="V131" s="10"/>
+    </row>
+    <row r="132" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A132" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B132" s="10">
+        <v>1</v>
+      </c>
+      <c r="C132" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D132" s="10">
+        <v>1</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F132" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H132" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I132" s="10">
+        <v>1</v>
+      </c>
+      <c r="J132" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K132" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L132" s="10"/>
+      <c r="M132" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N132" s="18"/>
+      <c r="O132" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P132" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q132" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>34</v>
+      </c>
+      <c r="R132" s="57" t="str">
+        <f ca="1">IF(Q132&lt;0,"ATRASADO",IF(Q132&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S132" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T132" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U132" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V132" s="57"/>
+    </row>
+    <row r="133" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A133" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B133" s="10">
+        <v>2</v>
+      </c>
+      <c r="C133" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D133" s="10">
+        <v>2</v>
+      </c>
+      <c r="E133" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F133" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G133" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I133" s="10">
+        <v>1</v>
+      </c>
+      <c r="J133" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K133" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L133" s="10"/>
+      <c r="M133" s="11">
+        <v>46248</v>
+      </c>
+      <c r="N133" s="18"/>
+      <c r="O133" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P133" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q133" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>49</v>
+      </c>
+      <c r="R133" s="57" t="str">
+        <f t="shared" ref="R133:R143" ca="1" si="4">IF(Q133&lt;0,"ATRASADO",IF(Q133&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S133" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>33</v>
+      </c>
+      <c r="T133" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U133" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V133" s="57"/>
+    </row>
+    <row r="134" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A134" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B134" s="10">
+        <v>3</v>
+      </c>
+      <c r="C134" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D134" s="10">
+        <v>3</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G134" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H134" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I134" s="10">
+        <v>1</v>
+      </c>
+      <c r="J134" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K134" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L134" s="10"/>
+      <c r="M134" s="11">
+        <v>46248</v>
+      </c>
+      <c r="N134" s="18"/>
+      <c r="O134" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P134" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q134" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>49</v>
+      </c>
+      <c r="R134" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S134" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>33</v>
+      </c>
+      <c r="T134" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U134" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V134" s="57"/>
+    </row>
+    <row r="135" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A135" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B135" s="10">
+        <v>4</v>
+      </c>
+      <c r="C135" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D135" s="10">
+        <v>4</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="I135" s="10">
+        <v>1</v>
+      </c>
+      <c r="J135" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K135" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L135" s="10"/>
+      <c r="M135" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N135" s="18"/>
+      <c r="O135" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P135" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q135" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>34</v>
+      </c>
+      <c r="R135" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S135" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T135" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U135" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V135" s="57"/>
+    </row>
+    <row r="136" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A136" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B136" s="10">
+        <v>5</v>
+      </c>
+      <c r="C136" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D136" s="10">
+        <v>5</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H136" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="I136" s="10">
+        <v>1</v>
+      </c>
+      <c r="J136" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K136" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L136" s="10"/>
+      <c r="M136" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N136" s="18"/>
+      <c r="O136" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P136" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q136" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>34</v>
+      </c>
+      <c r="R136" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S136" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T136" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U136" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V136" s="57"/>
+    </row>
+    <row r="137" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A137" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B137" s="10">
+        <v>6</v>
+      </c>
+      <c r="C137" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D137" s="10">
+        <v>6</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F137" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G137" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="I137" s="10">
+        <v>1</v>
+      </c>
+      <c r="J137" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K137" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L137" s="10"/>
+      <c r="M137" s="11">
+        <v>46248</v>
+      </c>
+      <c r="N137" s="18"/>
+      <c r="O137" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P137" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q137" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>49</v>
+      </c>
+      <c r="R137" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S137" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>33</v>
+      </c>
+      <c r="T137" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U137" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V137" s="57"/>
+    </row>
+    <row r="138" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A138" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B138" s="10">
+        <v>7</v>
+      </c>
+      <c r="C138" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D138" s="10">
+        <v>7</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H138" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="I138" s="10">
+        <v>1</v>
+      </c>
+      <c r="J138" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K138" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L138" s="10"/>
+      <c r="M138" s="11">
+        <v>46248</v>
+      </c>
+      <c r="N138" s="18"/>
+      <c r="O138" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P138" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q138" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>49</v>
+      </c>
+      <c r="R138" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S138" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>33</v>
+      </c>
+      <c r="T138" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U138" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V138" s="57"/>
+    </row>
+    <row r="139" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A139" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B139" s="10">
+        <v>8</v>
+      </c>
+      <c r="C139" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D139" s="10">
+        <v>8</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F139" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G139" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="I139" s="10">
+        <v>1</v>
+      </c>
+      <c r="J139" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K139" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L139" s="10"/>
+      <c r="M139" s="11">
+        <v>46248</v>
+      </c>
+      <c r="N139" s="18"/>
+      <c r="O139" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P139" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q139" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>49</v>
+      </c>
+      <c r="R139" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S139" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>33</v>
+      </c>
+      <c r="T139" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U139" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V139" s="57"/>
+    </row>
+    <row r="140" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A140" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B140" s="10">
+        <v>9</v>
+      </c>
+      <c r="C140" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D140" s="10">
+        <v>9</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F140" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H140" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I140" s="10">
+        <v>1</v>
+      </c>
+      <c r="J140" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K140" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L140" s="10"/>
+      <c r="M140" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N140" s="18"/>
+      <c r="O140" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P140" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q140" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>34</v>
+      </c>
+      <c r="R140" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S140" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T140" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U140" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V140" s="57"/>
+    </row>
+    <row r="141" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A141" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B141" s="10">
+        <v>10</v>
+      </c>
+      <c r="C141" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D141" s="10">
+        <v>10</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F141" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G141" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H141" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I141" s="10">
+        <v>1</v>
+      </c>
+      <c r="J141" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K141" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L141" s="10"/>
+      <c r="M141" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N141" s="18"/>
+      <c r="O141" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P141" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q141" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>34</v>
+      </c>
+      <c r="R141" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S141" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T141" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U141" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V141" s="57"/>
+    </row>
+    <row r="142" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A142" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B142" s="10">
+        <v>11</v>
+      </c>
+      <c r="C142" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D142" s="10">
+        <v>11</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F142" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G142" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H142" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I142" s="10">
+        <v>1</v>
+      </c>
+      <c r="J142" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K142" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L142" s="10"/>
+      <c r="M142" s="11">
+        <v>46248</v>
+      </c>
+      <c r="N142" s="18"/>
+      <c r="O142" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P142" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q142" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>49</v>
+      </c>
+      <c r="R142" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S142" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>33</v>
+      </c>
+      <c r="T142" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U142" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V142" s="57"/>
+    </row>
+    <row r="143" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A143" s="10">
+        <v>2335</v>
+      </c>
+      <c r="B143" s="10">
+        <v>12</v>
+      </c>
+      <c r="C143" s="10">
+        <v>27619</v>
+      </c>
+      <c r="D143" s="10">
+        <v>12</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G143" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I143" s="10">
+        <v>1</v>
+      </c>
+      <c r="J143" s="11">
+        <v>46219</v>
+      </c>
+      <c r="K143" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>29</v>
+      </c>
+      <c r="L143" s="10"/>
+      <c r="M143" s="11">
+        <v>46248</v>
+      </c>
+      <c r="N143" s="18"/>
+      <c r="O143" s="11">
+        <v>46203</v>
+      </c>
+      <c r="P143" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q143" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>49</v>
+      </c>
+      <c r="R143" s="57" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S143" s="57">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>33</v>
+      </c>
+      <c r="T143" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U143" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V143" s="57"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -26242,7 +27092,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O2" s="13" t="str">
         <f t="shared" ref="O2:O16" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -26319,7 +27169,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O3" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26396,7 +27246,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O4" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26473,7 +27323,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O5" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26550,7 +27400,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O6" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26627,7 +27477,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O7" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26704,7 +27554,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O8" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26781,7 +27631,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O9" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26858,7 +27708,7 @@
       <c r="N10" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O10" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -26935,7 +27785,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O11" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27012,7 +27862,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O12" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27089,7 +27939,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O13" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27166,7 +28016,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O14" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27243,7 +28093,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O15" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27320,7 +28170,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O16" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27397,7 +28247,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O17" s="13" t="str">
         <f ca="1">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27476,7 +28326,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O18" s="13" t="str">
         <f t="shared" ref="O18:O25" ca="1" si="2">IF(N18&lt;0,"ATRASADO",IF(N18&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27555,7 +28405,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -27634,7 +28484,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -27713,7 +28563,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -27792,7 +28642,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -27871,7 +28721,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -27950,7 +28800,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -28029,7 +28879,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -28108,7 +28958,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O26" s="13" t="str">
         <f ca="1">IF(N26&lt;0,"ATRASADO",IF(N26&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28185,7 +29035,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O27" s="13" t="str">
         <f t="shared" ref="O27:O28" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28262,7 +29112,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O28" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28339,7 +29189,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O29" s="13" t="str">
         <f t="shared" ref="O29:O31" ca="1" si="5">IF(N29&lt;0,"ATRASADO",IF(N29&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28418,7 +29268,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O30" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28497,7 +29347,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O31" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28576,7 +29426,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O32" s="13" t="str">
         <f ca="1">IF(N32&lt;0,"ATRASADO",IF(N32&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28616,7 +29466,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>2331</v>
       </c>
@@ -28655,7 +29505,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O33" s="13" t="str">
         <f t="shared" ref="O33:O35" ca="1" si="7">IF(N33&lt;0,"ATRASADO",IF(N33&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28695,7 +29545,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>2331</v>
       </c>
@@ -28734,7 +29584,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O34" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -28774,7 +29624,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>2331</v>
       </c>
@@ -28813,7 +29663,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O35" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -28853,55 +29703,351 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <v>2337</v>
+      </c>
+      <c r="B36" s="14">
+        <v>1</v>
+      </c>
+      <c r="C36" s="14">
+        <v>27620</v>
+      </c>
+      <c r="D36" s="14">
+        <v>1</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="I36" s="14">
+        <v>1</v>
+      </c>
+      <c r="J36" s="18">
+        <v>46265</v>
+      </c>
+      <c r="K36" s="58"/>
+      <c r="L36" s="18">
+        <v>46295</v>
+      </c>
+      <c r="M36" s="58"/>
+      <c r="N36" s="59">
+        <f ca="1">Tabela13[[#This Row],[Data Prev.
+Entrega]]-TODAY()</f>
+        <v>96</v>
+      </c>
+      <c r="O36" s="59" t="str">
+        <f ca="1">IF(N36&lt;0,"ATRASADO",IF(N36&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P36" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q36" s="61">
+        <v>46223</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y36" s="62" t="str">
+        <f>IF(K36="","AG. FUNDIDO",IF(X36="OK","LIBERADA","EM USINAGEM"))</f>
+        <v>AG. FUNDIDO</v>
+      </c>
+      <c r="Z36" s="60"/>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <v>2337</v>
+      </c>
+      <c r="B37" s="14">
+        <v>2</v>
+      </c>
+      <c r="C37" s="14">
+        <v>27620</v>
+      </c>
+      <c r="D37" s="14">
+        <v>2</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="I37" s="14">
+        <v>1</v>
+      </c>
+      <c r="J37" s="18">
+        <v>46265</v>
+      </c>
+      <c r="K37" s="58"/>
+      <c r="L37" s="18">
+        <v>46295</v>
+      </c>
+      <c r="M37" s="58"/>
+      <c r="N37" s="59">
+        <f ca="1">Tabela13[[#This Row],[Data Prev.
+Entrega]]-TODAY()</f>
+        <v>96</v>
+      </c>
+      <c r="O37" s="59" t="str">
+        <f t="shared" ref="O37:O39" ca="1" si="9">IF(N37&lt;0,"ATRASADO",IF(N37&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P37" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q37" s="61">
+        <v>46223</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y37" s="62" t="str">
+        <f t="shared" ref="Y37:Y39" si="10">IF(K37="","AG. FUNDIDO",IF(X37="OK","LIBERADA","EM USINAGEM"))</f>
+        <v>AG. FUNDIDO</v>
+      </c>
+      <c r="Z37" s="60"/>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <v>2337</v>
+      </c>
+      <c r="B38" s="14">
+        <v>3</v>
+      </c>
+      <c r="C38" s="14">
+        <v>27620</v>
+      </c>
+      <c r="D38" s="14">
+        <v>3</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I38" s="14">
+        <v>1</v>
+      </c>
+      <c r="J38" s="18">
+        <v>46265</v>
+      </c>
+      <c r="K38" s="58"/>
+      <c r="L38" s="18">
+        <v>46295</v>
+      </c>
+      <c r="M38" s="58"/>
+      <c r="N38" s="59">
+        <f ca="1">Tabela13[[#This Row],[Data Prev.
+Entrega]]-TODAY()</f>
+        <v>96</v>
+      </c>
+      <c r="O38" s="59" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P38" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q38" s="61">
+        <v>46223</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y38" s="62" t="str">
+        <f t="shared" si="10"/>
+        <v>AG. FUNDIDO</v>
+      </c>
+      <c r="Z38" s="60"/>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A39" s="14">
+        <v>2337</v>
+      </c>
+      <c r="B39" s="14">
+        <v>4</v>
+      </c>
+      <c r="C39" s="14">
+        <v>27620</v>
+      </c>
+      <c r="D39" s="14">
+        <v>4</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I39" s="14">
+        <v>1</v>
+      </c>
+      <c r="J39" s="18">
+        <v>46265</v>
+      </c>
+      <c r="K39" s="58"/>
+      <c r="L39" s="18">
+        <v>46295</v>
+      </c>
+      <c r="M39" s="58"/>
+      <c r="N39" s="59">
+        <f ca="1">Tabela13[[#This Row],[Data Prev.
+Entrega]]-TODAY()</f>
+        <v>96</v>
+      </c>
+      <c r="O39" s="59" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P39" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q39" s="61">
+        <v>46223</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="U39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="X39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y39" s="62" t="str">
+        <f t="shared" si="10"/>
+        <v>AG. FUNDIDO</v>
+      </c>
+      <c r="Z39" s="60"/>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N41" s="13"/>
       <c r="O41" s="13"/>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N42" s="13"/>
       <c r="O42" s="13"/>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N43" s="13"/>
       <c r="O43" s="13"/>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N44" s="13"/>
       <c r="O44" s="13"/>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N45" s="13"/>
       <c r="O45" s="13"/>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N46" s="13"/>
       <c r="O46" s="13"/>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N47" s="13"/>
       <c r="O47" s="13"/>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="N48" s="13"/>
       <c r="O48" s="13"/>
     </row>
@@ -29667,7 +30813,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O2" t="str">
         <f t="shared" ref="O2:O9" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -29723,7 +30869,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29779,7 +30925,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29835,7 +30981,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29891,7 +31037,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O6" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29947,7 +31093,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30003,7 +31149,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30059,7 +31205,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30121,7 +31267,7 @@
       <c r="N10" s="12">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O10" s="33" t="s">
         <v>102</v>
@@ -30179,7 +31325,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O11" s="1" t="str">
         <f ca="1">IF(N11&lt;0,"ATRASADO",IF(N11&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30238,7 +31384,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O12" t="str">
         <f ca="1">IF(N12&lt;0,"ATRASADO",IF(N12&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30297,7 +31443,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">IF(N13&lt;0,"ATRASADO",IF(N13&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30356,7 +31502,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O14" t="str">
         <f ca="1">IF(N14&lt;0,"ATRASADO",IF(N14&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30415,7 +31561,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O15" t="str">
         <f t="shared" ref="O15:O16" ca="1" si="1">IF(N15&lt;0,"ATRASADO",IF(N15&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30474,7 +31620,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -30530,7 +31676,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" ref="O17:O18" ca="1" si="2">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30586,7 +31732,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -30645,7 +31791,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O19" t="str">
         <f ca="1">IF(N19&lt;0,"ATRASADO",IF(N19&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30704,7 +31850,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O20" t="str">
         <f ca="1">IF(N20&lt;0,"ATRASADO",IF(N20&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30763,7 +31909,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O21" t="str">
         <f t="shared" ref="O21:O26" ca="1" si="3">IF(N21&lt;0,"ATRASADO",IF(N21&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30822,7 +31968,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O22" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -30881,7 +32027,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -30940,7 +32086,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O24" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -30999,7 +32145,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O25" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -31058,7 +32204,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O26" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -31117,7 +32263,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O27" t="str">
         <f t="shared" ref="O27:O34" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31176,7 +32322,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O28" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -31235,7 +32381,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O29" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -31294,7 +32440,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O30" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -31353,7 +32499,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O31" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -31412,7 +32558,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O32" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -31471,7 +32617,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O33" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -31530,7 +32676,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O34" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -31589,7 +32735,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O35" t="str">
         <f t="shared" ref="O35:O36" ca="1" si="5">IF(N35&lt;0,"ATRASADO",IF(N35&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31648,7 +32794,7 @@
       <c r="N36" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O36" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -31707,7 +32853,7 @@
       <c r="N37" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O37" t="str">
         <f ca="1">IF(N37&lt;0,"ATRASADO",IF(N37&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31766,7 +32912,7 @@
       <c r="N38" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O38" t="str">
         <f t="shared" ref="O38:O52" ca="1" si="6">IF(N38&lt;0,"ATRASADO",IF(N38&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31825,7 +32971,7 @@
       <c r="N39" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O39" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -31884,7 +33030,7 @@
       <c r="N40" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -31943,7 +33089,7 @@
       <c r="N41" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O41" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32002,7 +33148,7 @@
       <c r="N42" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O42" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32061,7 +33207,7 @@
       <c r="N43" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O43" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32120,7 +33266,7 @@
       <c r="N44" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O44" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32179,7 +33325,7 @@
       <c r="N45" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O45" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32238,7 +33384,7 @@
       <c r="N46" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O46" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32297,7 +33443,7 @@
       <c r="N47" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O47" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32356,7 +33502,7 @@
       <c r="N48" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O48" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32415,7 +33561,7 @@
       <c r="N49" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O49" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32474,7 +33620,7 @@
       <c r="N50" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O50" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32533,7 +33679,7 @@
       <c r="N51" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O51" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32592,7 +33738,7 @@
       <c r="N52" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O52" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -32654,7 +33800,7 @@
       <c r="N53" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O53" t="s">
         <v>154</v>
@@ -32712,7 +33858,7 @@
       <c r="N54" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O54" t="str">
         <f ca="1">IF(N54&lt;0,"ATRASADO",IF(N54&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32771,7 +33917,7 @@
       <c r="N55" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O55" t="str">
         <f ca="1">IF(N55&lt;0,"ATRASADO",IF(N55&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32830,7 +33976,7 @@
       <c r="N56" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O56" t="str">
         <f ca="1">IF(N56&lt;0,"ATRASADO",IF(N56&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32889,7 +34035,7 @@
       <c r="N57" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O57" t="str">
         <f t="shared" ref="O57:O59" ca="1" si="7">IF(N57&lt;0,"ATRASADO",IF(N57&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32948,7 +34094,7 @@
       <c r="N58" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O58" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -33007,7 +34153,7 @@
       <c r="N59" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O59" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -33063,7 +34209,7 @@
       <c r="N60" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O60" t="str">
         <f t="shared" ref="O60:O62" ca="1" si="8">IF(N60&lt;0,"ATRASADO",IF(N60&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33119,7 +34265,7 @@
       <c r="N61" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O61" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -33175,7 +34321,7 @@
       <c r="N62" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O62" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -33234,7 +34380,7 @@
       <c r="N63" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O63" t="str">
         <f ca="1">IF(N63&lt;0,"ATRASADO",IF(N63&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33293,7 +34439,7 @@
       <c r="N64" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O64" t="str">
         <f t="shared" ref="O64:O76" ca="1" si="9">IF(N64&lt;0,"ATRASADO",IF(N64&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33352,7 +34498,7 @@
       <c r="N65" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O65" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33411,7 +34557,7 @@
       <c r="N66" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O66" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33470,7 +34616,7 @@
       <c r="N67" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O67" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33529,7 +34675,7 @@
       <c r="N68" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O68" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33588,7 +34734,7 @@
       <c r="N69" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O69" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33647,7 +34793,7 @@
       <c r="N70" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O70" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33706,7 +34852,7 @@
       <c r="N71" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O71" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33765,7 +34911,7 @@
       <c r="N72" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O72" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33824,7 +34970,7 @@
       <c r="N73" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O73" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33883,7 +35029,7 @@
       <c r="N74" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O74" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33942,7 +35088,7 @@
       <c r="N75" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O75" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34001,7 +35147,7 @@
       <c r="N76" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O76" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34060,7 +35206,7 @@
       <c r="N77" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O77" t="str">
         <f ca="1">IF(N77&lt;0,"ATRASADO",IF(N77&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34119,7 +35265,7 @@
       <c r="N78" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O78" t="str">
         <f t="shared" ref="O78:O80" ca="1" si="10">IF(N78&lt;0,"ATRASADO",IF(N78&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34178,7 +35324,7 @@
       <c r="N79" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O79" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -34237,7 +35383,7 @@
       <c r="N80" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O80" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -34296,7 +35442,7 @@
       <c r="N81" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O81" t="str">
         <f t="shared" ref="O81:O88" ca="1" si="11">IF(N81&lt;0,"ATRASADO",IF(N81&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34355,7 +35501,7 @@
       <c r="N82" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O82" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -34414,7 +35560,7 @@
       <c r="N83" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O83" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -34473,7 +35619,7 @@
       <c r="N84" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O84" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -34532,7 +35678,7 @@
       <c r="N85" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O85" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -34591,7 +35737,7 @@
       <c r="N86" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O86" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -34650,7 +35796,7 @@
       <c r="N87" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O87" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -34709,7 +35855,7 @@
       <c r="N88" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O88" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -34771,7 +35917,7 @@
       <c r="N89" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O89" t="s">
         <v>154</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC64E12-5707-4091-8FF9-D1A9E6092291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88827D53-3F2E-4B18-81FB-C791794A6D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="5" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
   <sheets>
     <sheet name="BAGACEIRAS" sheetId="2" r:id="rId1"/>
@@ -32,17 +32,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
     </ext>
@@ -51,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4702" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4772" uniqueCount="292">
   <si>
     <t>O.S.</t>
   </si>
@@ -769,10 +758,6 @@
   </si>
   <si>
     <t>Recurso Usinagem
-Camisa</t>
-  </si>
-  <si>
-    <t>Recurso Usinagem
 Eixo</t>
   </si>
   <si>
@@ -786,9 +771,6 @@
 Eixo</t>
   </si>
   <si>
-    <t>Torno / Radial  / Soldar / Broq. / Encam.</t>
-  </si>
-  <si>
     <t>Cofco</t>
   </si>
   <si>
@@ -798,96 +780,7 @@
     <t>AG. BOQUILHAS - PED. 25567 - HTEC - 29/06</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>torno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>coletor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>radial</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>boquilha</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> / montagem / torno / broq / encamisar</t>
-    </r>
-  </si>
-  <si>
     <t>84"</t>
-  </si>
-  <si>
-    <t>torno / coletor / radial / boquilha / montagem / torno / broq / encamisar</t>
   </si>
   <si>
     <t>EM USINAGEM</t>
@@ -956,9 +849,6 @@
 Fund Real</t>
   </si>
   <si>
-    <t>Grafitar - Torno - Solda</t>
-  </si>
-  <si>
     <t>Rec
 Eixo</t>
   </si>
@@ -1007,6 +897,63 @@
   </si>
   <si>
     <t>RODETE MOENDA Z15 - 90"</t>
+  </si>
+  <si>
+    <t>Torno</t>
+  </si>
+  <si>
+    <t>Grafitar</t>
+  </si>
+  <si>
+    <t>Coletor</t>
+  </si>
+  <si>
+    <t>Radial</t>
+  </si>
+  <si>
+    <t>Solda</t>
+  </si>
+  <si>
+    <t>Boquilha</t>
+  </si>
+  <si>
+    <t>Montagem</t>
+  </si>
+  <si>
+    <t>Acab.</t>
+  </si>
+  <si>
+    <t>Broq.</t>
+  </si>
+  <si>
+    <t>Encam.</t>
+  </si>
+  <si>
+    <t>OP1</t>
+  </si>
+  <si>
+    <t>OP2</t>
+  </si>
+  <si>
+    <t>OP3</t>
+  </si>
+  <si>
+    <t>OP4</t>
+  </si>
+  <si>
+    <t>OP5</t>
+  </si>
+  <si>
+    <t>OP6</t>
+  </si>
+  <si>
+    <t>OP7</t>
+  </si>
+  <si>
+    <t>OP8</t>
+  </si>
+  <si>
+    <t>OP9</t>
   </si>
 </sst>
 </file>
@@ -1096,15 +1043,13 @@
       <scheme val="major"/>
     </font>
     <font>
-      <strike/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos Display"/>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1129,8 +1074,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1182,25 +1133,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1346,26 +1284,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1373,60 +1297,786 @@
   </cellStyles>
   <dxfs count="145">
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3005,642 +3655,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3655,220 +3669,222 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="118" dataDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="144" dataDxfId="143">
   <autoFilter ref="A1:AI114" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}">
-    <filterColumn colId="0">
+    <filterColumn colId="28">
       <filters>
-        <filter val="2199"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="2"/>
-        <filter val="5"/>
+        <filter val="EM INSPEÇÃO"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="114"/>
-    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="112"/>
-    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="111"/>
-    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="110"/>
-    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="109"/>
-    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="108"/>
-    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="107"/>
-    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="106">
+    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="142"/>
+    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="141"/>
+    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="140"/>
+    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="139"/>
+    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="138"/>
+    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="137"/>
+    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="136"/>
+    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="135"/>
+    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="134"/>
+    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="133"/>
+    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="132">
       <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
 Fundido]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="105"/>
-    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="104"/>
-    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="103"/>
-    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="102">
+    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="131"/>
+    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="130"/>
+    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="129"/>
+    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="128">
       <calculatedColumnFormula>Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="101">
+    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="127">
       <calculatedColumnFormula>IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="100">
+    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="126">
       <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
 Entrega]],1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="99"/>
-    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="98"/>
-    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="97"/>
-    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="96"/>
-    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="95"/>
-    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="94"/>
-    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="93"/>
-    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="92"/>
-    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="91"/>
-    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="90"/>
-    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="89"/>
-    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="88">
+    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="125"/>
+    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="124"/>
+    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="123"/>
+    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="122"/>
+    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="121"/>
+    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="120"/>
+    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="119"/>
+    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="118"/>
+    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="117"/>
+    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="116"/>
+    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="115"/>
+    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="114">
       <calculatedColumnFormula>IF(L2="","AG. FUNDIDO",IF(U2="AG","AG. USINAGEM","EM USINAGEM"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="86"/>
-    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="82"/>
+    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="113"/>
+    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="112"/>
+    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="111"/>
+    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="110"/>
+    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="109"/>
+    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="108"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V143" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V143" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
   <autoFilter ref="A1:V143" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="74"/>
-    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="73"/>
-    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="72"/>
-    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="71"/>
-    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="70"/>
-    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="69">
+    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="103"/>
+    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="101"/>
+    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="100"/>
+    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="99"/>
+    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="98"/>
+    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="97"/>
+    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="96"/>
+    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="95">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="68"/>
-    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="67"/>
-    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="66"/>
-    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="65"/>
-    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="64"/>
-    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="63">
+    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="94"/>
+    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="93"/>
+    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="92"/>
+    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="91"/>
+    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="90"/>
+    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="89">
       <calculatedColumnFormula>Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="62">
+    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="88">
       <calculatedColumnFormula>IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="61">
+    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="87">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="60"/>
-    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="59"/>
-    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="86"/>
+    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="85"/>
+    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E9C3BD9-7BAA-49FB-9F98-CFD415149194}" name="Tabela13" displayName="Tabela13" ref="A1:Z39" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E9C3BD9-7BAA-49FB-9F98-CFD415149194}" name="Tabela13" displayName="Tabela13" ref="A1:Z39" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
   <autoFilter ref="A1:Z39" xr:uid="{2AC5416C-4E1B-4478-8A2A-B698870CAB96}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{9A983B4E-3365-4153-9B40-D7FE26E8B98F}" name="PV " dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{4F16CD54-AAD4-4149-8D48-CC3FFEA93AA5}" name="Item" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{27DB1DBC-B9DA-4067-9696-8CA5ACAAA450}" name="OS" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{02C5E283-8ABF-44F8-B3B8-C3F186B4DF63}" name="Item2" dataDxfId="52"/>
-    <tableColumn id="5" xr3:uid="{B1051CBE-EA72-4A43-8721-8756F3E2C9C9}" name="Cliente" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{D81DBB81-327B-4EA3-89A3-229D33F3C14C}" name="Cod." dataDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{05B3DC4D-BFB9-401F-A18F-0D1B8527380B}" name="Seq." dataDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{9EBF401A-1F29-4CB3-BFA3-F2B326242AB0}" name="Descrição" dataDxfId="48"/>
-    <tableColumn id="14" xr3:uid="{85D3397C-7F95-49C7-BFFB-35012CA3B716}" name="Qtd." dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{0D04583C-577A-446B-9773-A173C5C1C166}" name="Data Prev._x000a_Fundido" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{935D3899-0C12-4408-89DF-490A507F79BA}" name="Data Real_x000a_Fundido" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{0F06941F-293B-4C15-9764-BB3495C5D3BD}" name="Data Prev._x000a_Entrega" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{92FF2511-5498-45BF-9B68-94DBEA588C5A}" name="Data Real_x000a_Entrega" dataDxfId="43"/>
-    <tableColumn id="25" xr3:uid="{98545C7E-9674-485C-A07D-715E8945B00E}" name="Falta_x000a_Dias" dataDxfId="42">
+    <tableColumn id="1" xr3:uid="{9A983B4E-3365-4153-9B40-D7FE26E8B98F}" name="PV " dataDxfId="81"/>
+    <tableColumn id="2" xr3:uid="{4F16CD54-AAD4-4149-8D48-CC3FFEA93AA5}" name="Item" dataDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{27DB1DBC-B9DA-4067-9696-8CA5ACAAA450}" name="OS" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{02C5E283-8ABF-44F8-B3B8-C3F186B4DF63}" name="Item2" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{B1051CBE-EA72-4A43-8721-8756F3E2C9C9}" name="Cliente" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{D81DBB81-327B-4EA3-89A3-229D33F3C14C}" name="Cod." dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{05B3DC4D-BFB9-401F-A18F-0D1B8527380B}" name="Seq." dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{9EBF401A-1F29-4CB3-BFA3-F2B326242AB0}" name="Descrição" dataDxfId="74"/>
+    <tableColumn id="14" xr3:uid="{85D3397C-7F95-49C7-BFFB-35012CA3B716}" name="Qtd." dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{0D04583C-577A-446B-9773-A173C5C1C166}" name="Data Prev._x000a_Fundido" dataDxfId="72"/>
+    <tableColumn id="10" xr3:uid="{935D3899-0C12-4408-89DF-490A507F79BA}" name="Data Real_x000a_Fundido" dataDxfId="71"/>
+    <tableColumn id="11" xr3:uid="{0F06941F-293B-4C15-9764-BB3495C5D3BD}" name="Data Prev._x000a_Entrega" dataDxfId="70"/>
+    <tableColumn id="12" xr3:uid="{92FF2511-5498-45BF-9B68-94DBEA588C5A}" name="Data Real_x000a_Entrega" dataDxfId="69"/>
+    <tableColumn id="25" xr3:uid="{98545C7E-9674-485C-A07D-715E8945B00E}" name="Falta_x000a_Dias" dataDxfId="68">
       <calculatedColumnFormula>Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{4EB63243-AA79-4695-93C8-CEA977B11387}" name="Indicador" dataDxfId="41">
+    <tableColumn id="27" xr3:uid="{4EB63243-AA79-4695-93C8-CEA977B11387}" name="Indicador" dataDxfId="67">
       <calculatedColumnFormula>IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7AB992C1-F70E-4469-85BB-EBB7763B2038}" name="Condição" dataDxfId="40"/>
-    <tableColumn id="24" xr3:uid="{B5965349-4BC8-4DF7-9EB4-857B6D471E8A}" name="Desenho_x000a_Previsão" dataDxfId="39"/>
-    <tableColumn id="13" xr3:uid="{FD827F61-5F7F-4B65-8A60-B59D23455B46}" name="Des." dataDxfId="38"/>
-    <tableColumn id="16" xr3:uid="{3D186A5F-076F-4232-B21C-37E58E5373B2}" name="Desb." dataDxfId="37"/>
-    <tableColumn id="17" xr3:uid="{6EEDF11E-F341-4B3E-8CD2-5595785C3427}" name="T.T." dataDxfId="36"/>
-    <tableColumn id="18" xr3:uid="{A84EFCF4-218F-4B17-8F46-8D5412141429}" name="Us. Final" dataDxfId="35"/>
-    <tableColumn id="19" xr3:uid="{EBD50149-594D-440E-BFBB-E73ACAF7B6F8}" name="Fundo D." dataDxfId="34"/>
-    <tableColumn id="20" xr3:uid="{91BE30ED-20C1-4F30-9041-45A50CCA04F0}" name="Acabam." dataDxfId="33"/>
-    <tableColumn id="21" xr3:uid="{A1A12DF6-FC3D-4466-8284-DBD00DEAF994}" name="Liberação" dataDxfId="32"/>
-    <tableColumn id="22" xr3:uid="{436F202D-DCF4-4376-A550-2541153BD99F}" name="Status Usinagem" dataDxfId="31">
+    <tableColumn id="15" xr3:uid="{7AB992C1-F70E-4469-85BB-EBB7763B2038}" name="Condição" dataDxfId="66"/>
+    <tableColumn id="24" xr3:uid="{B5965349-4BC8-4DF7-9EB4-857B6D471E8A}" name="Desenho_x000a_Previsão" dataDxfId="65"/>
+    <tableColumn id="13" xr3:uid="{FD827F61-5F7F-4B65-8A60-B59D23455B46}" name="Des." dataDxfId="64"/>
+    <tableColumn id="16" xr3:uid="{3D186A5F-076F-4232-B21C-37E58E5373B2}" name="Desb." dataDxfId="63"/>
+    <tableColumn id="17" xr3:uid="{6EEDF11E-F341-4B3E-8CD2-5595785C3427}" name="T.T." dataDxfId="62"/>
+    <tableColumn id="18" xr3:uid="{A84EFCF4-218F-4B17-8F46-8D5412141429}" name="Us. Final" dataDxfId="61"/>
+    <tableColumn id="19" xr3:uid="{EBD50149-594D-440E-BFBB-E73ACAF7B6F8}" name="Fundo D." dataDxfId="60"/>
+    <tableColumn id="20" xr3:uid="{91BE30ED-20C1-4F30-9041-45A50CCA04F0}" name="Acabam." dataDxfId="59"/>
+    <tableColumn id="21" xr3:uid="{A1A12DF6-FC3D-4466-8284-DBD00DEAF994}" name="Liberação" dataDxfId="58"/>
+    <tableColumn id="22" xr3:uid="{436F202D-DCF4-4376-A550-2541153BD99F}" name="Status Usinagem" dataDxfId="57">
       <calculatedColumnFormula>IF(K2="","AG. FUNDIDO",IF(X2="OK","LIBERADA","EM USINAGEM"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{F71E5739-8B79-47B3-9A24-E2E4D1DD46E6}" name="Observação" dataDxfId="30"/>
+    <tableColumn id="23" xr3:uid="{F71E5739-8B79-47B3-9A24-E2E4D1DD46E6}" name="Observação" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T89" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T89" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:T89" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{56D3DA8E-4CA8-4DC6-8208-BAB93CDE51C0}" name="PV" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{B14AE1B6-8C05-4725-BF42-3DBDB37AA4E3}" name="item" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{24FE1002-C88A-4623-8882-5F391ECAB319}" name="OS" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{4ED6249C-2003-4F3F-AE5A-67316434275E}" name="Item2" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{6CE5B2E1-F32C-4D32-93F0-A17C05267ADB}" name="Cliente" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{605F51C8-79D3-407B-8642-02F131952C62}" name="Qtd." dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{3AC59FFB-0DC5-477B-B780-880A1FD84811}" name="Peça" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{2EE377A7-B17C-442E-A107-012310DB953B}" name="Seq." dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{5366226E-7F3B-42E4-AC0C-86C659505CC8}" name="Descrição" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{B0D229C5-5F5A-4951-A0B4-FEA62AEFBB36}" name="Prazo_x000a_Fundido" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{8AE09F18-EB17-4537-8FBD-24671292144B}" name="Pz Fundido_x000a_Real" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{965E0234-7E4B-482D-8943-132C1520AD21}" name="Prazo_x000a_Entrega" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{D70BE32E-86AF-4C0F-893D-AC939E731683}" name="Pz Entrega_x000a_Real" dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{2FE637E5-62E2-4AE9-AE5A-BC264DC93D4F}" name="Falta_x000a_Dias" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{56D3DA8E-4CA8-4DC6-8208-BAB93CDE51C0}" name="PV" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{B14AE1B6-8C05-4725-BF42-3DBDB37AA4E3}" name="item" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{24FE1002-C88A-4623-8882-5F391ECAB319}" name="OS" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{4ED6249C-2003-4F3F-AE5A-67316434275E}" name="Item2" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{6CE5B2E1-F32C-4D32-93F0-A17C05267ADB}" name="Cliente" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{605F51C8-79D3-407B-8642-02F131952C62}" name="Qtd." dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{3AC59FFB-0DC5-477B-B780-880A1FD84811}" name="Peça" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{2EE377A7-B17C-442E-A107-012310DB953B}" name="Seq." dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{5366226E-7F3B-42E4-AC0C-86C659505CC8}" name="Descrição" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{B0D229C5-5F5A-4951-A0B4-FEA62AEFBB36}" name="Prazo_x000a_Fundido" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{8AE09F18-EB17-4537-8FBD-24671292144B}" name="Pz Fundido_x000a_Real" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{965E0234-7E4B-482D-8943-132C1520AD21}" name="Prazo_x000a_Entrega" dataDxfId="42"/>
+    <tableColumn id="13" xr3:uid="{D70BE32E-86AF-4C0F-893D-AC939E731683}" name="Pz Entrega_x000a_Real" dataDxfId="41"/>
+    <tableColumn id="15" xr3:uid="{2FE637E5-62E2-4AE9-AE5A-BC264DC93D4F}" name="Falta_x000a_Dias" dataDxfId="40">
       <calculatedColumnFormula>Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{23AEF4D3-817F-4A15-AFBA-EC837E4BE1AE}" name="Indicador" dataDxfId="13">
+    <tableColumn id="14" xr3:uid="{23AEF4D3-817F-4A15-AFBA-EC837E4BE1AE}" name="Indicador" dataDxfId="39">
       <calculatedColumnFormula>IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{78F55B7C-8E60-49C5-B1F7-B023E76BDA6E}" name="Condição" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{A889C1FB-2FE0-407A-B849-FEB9F2CA4F96}" name="Desenho_x000a_Previsão" dataDxfId="11"/>
-    <tableColumn id="19" xr3:uid="{FB1E21D0-A118-422F-AA5B-F56FFBA7B5E4}" name="Des." dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{C14325D6-C653-45B3-B85F-6AF107A71546}" name="Status" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{C6F7CA6A-B8B3-4E22-B3E8-05FFB1A03AB6}" name="Observação" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{78F55B7C-8E60-49C5-B1F7-B023E76BDA6E}" name="Condição" dataDxfId="38"/>
+    <tableColumn id="20" xr3:uid="{A889C1FB-2FE0-407A-B849-FEB9F2CA4F96}" name="Desenho_x000a_Previsão" dataDxfId="37"/>
+    <tableColumn id="19" xr3:uid="{FB1E21D0-A118-422F-AA5B-F56FFBA7B5E4}" name="Des." dataDxfId="36"/>
+    <tableColumn id="17" xr3:uid="{C14325D6-C653-45B3-B85F-6AF107A71546}" name="Status" dataDxfId="35"/>
+    <tableColumn id="18" xr3:uid="{C6F7CA6A-B8B3-4E22-B3E8-05FFB1A03AB6}" name="Observação" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}" name="Tabela6" displayName="Tabela6" ref="A1:X18" totalsRowShown="0" headerRowDxfId="144" dataDxfId="143">
-  <autoFilter ref="A1:X18" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}"/>
-  <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{C25E2119-68FD-4765-BAFB-8CC2FA75E790}" name="PV" dataDxfId="142"/>
-    <tableColumn id="2" xr3:uid="{39E67E43-7C76-4E6C-9319-15A91DE1C08C}" name="Item" dataDxfId="141"/>
-    <tableColumn id="4" xr3:uid="{5B6759FC-B832-438E-B60C-770FAF7723FA}" name="Cliente" dataDxfId="140"/>
-    <tableColumn id="5" xr3:uid="{20CFBF4C-4BD9-4F05-86D4-8A4AFFC243B2}" name="_x000a_O.S./Peça" dataDxfId="139"/>
-    <tableColumn id="6" xr3:uid="{3994BD48-BFFD-46D2-9740-EDD282F2590D}" name="Descrição" dataDxfId="138"/>
-    <tableColumn id="7" xr3:uid="{261AA518-FC82-431F-8839-D26554B59355}" name="Qtde." dataDxfId="137"/>
-    <tableColumn id="24" xr3:uid="{0C566A21-B9D9-4AD7-A8B3-328E480EA286}" name="Bit" dataDxfId="136"/>
-    <tableColumn id="26" xr3:uid="{C41F63A6-DC4C-42FE-A13B-3E56F237270D}" name="Terno" dataDxfId="135"/>
-    <tableColumn id="16" xr3:uid="{FF0A908E-E8EE-4CA0-96FA-38C032BFEFDE}" name="Forma" dataDxfId="134"/>
-    <tableColumn id="9" xr3:uid="{DE0283F8-D4F6-449C-A9CA-7DBCB898DFD9}" name="Prazo_x000a_Fund" dataDxfId="133"/>
-    <tableColumn id="10" xr3:uid="{663D9716-4C25-4ACC-A105-E9E7A474BCE6}" name="Prazo_x000a_Fund Real" dataDxfId="132"/>
-    <tableColumn id="11" xr3:uid="{6EF58C27-546C-4B57-B05D-BB07C2046388}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="131"/>
-    <tableColumn id="12" xr3:uid="{AC626966-9CA5-4150-82F1-50338494E847}" name="Pz Entrega_x000a_Real" dataDxfId="130"/>
-    <tableColumn id="13" xr3:uid="{506EC589-7ED2-4A3B-BED8-6CA8F57277E1}" name="Desenho_x000a_Previsão" dataDxfId="129"/>
-    <tableColumn id="14" xr3:uid="{A31AB572-7F13-4A5C-A42E-7E7A20433BDA}" name="Des." dataDxfId="128"/>
-    <tableColumn id="17" xr3:uid="{6C88AA43-E1BE-49A6-BA89-47D0A25BCB2C}" name="Recurso Usinagem_x000a_Camisa" dataDxfId="127"/>
-    <tableColumn id="18" xr3:uid="{F5387D14-C7D5-4022-901B-04E5D65304C7}" name="Status_x000a_Camisa" dataDxfId="126"/>
-    <tableColumn id="32" xr3:uid="{BEC53105-CFFD-422E-9C30-4E4BC1816678}" name="Nº Eixo2" dataDxfId="125"/>
-    <tableColumn id="31" xr3:uid="{75A53AF4-0F54-4590-BD96-F05C1573DAAA}" name="Rec_x000a_Eixo" dataDxfId="124"/>
-    <tableColumn id="21" xr3:uid="{E4F9165E-8213-4A74-8458-2B70C50F9169}" name="Recurso Usinagem_x000a_Eixo" dataDxfId="123"/>
-    <tableColumn id="22" xr3:uid="{DD97A210-9E2B-4A0B-AAFA-22D7F8571D7D}" name="Nº Laudo" dataDxfId="122"/>
-    <tableColumn id="29" xr3:uid="{9A0D9E97-0991-4A6E-8B85-EED9CC983F8A}" name="Prazo_x000a_Entrega_x000a_Eixo" dataDxfId="121"/>
-    <tableColumn id="23" xr3:uid="{28D59365-C375-479F-85A6-0CBB39E36BC5}" name="Status_x000a_Eixo" dataDxfId="120"/>
-    <tableColumn id="19" xr3:uid="{A08285BC-8B0E-4492-A6AF-090B851B036D}" name="Observação" dataDxfId="119"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}" name="Tabela6" displayName="Tabela6" ref="A1:AF18" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="A1:AF18" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}"/>
+  <tableColumns count="32">
+    <tableColumn id="1" xr3:uid="{C25E2119-68FD-4765-BAFB-8CC2FA75E790}" name="PV" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{39E67E43-7C76-4E6C-9319-15A91DE1C08C}" name="Item" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{5B6759FC-B832-438E-B60C-770FAF7723FA}" name="Cliente" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{20CFBF4C-4BD9-4F05-86D4-8A4AFFC243B2}" name="_x000a_O.S./Peça" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{3994BD48-BFFD-46D2-9740-EDD282F2590D}" name="Descrição" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{261AA518-FC82-431F-8839-D26554B59355}" name="Qtde." dataDxfId="26"/>
+    <tableColumn id="24" xr3:uid="{0C566A21-B9D9-4AD7-A8B3-328E480EA286}" name="Bit" dataDxfId="25"/>
+    <tableColumn id="26" xr3:uid="{C41F63A6-DC4C-42FE-A13B-3E56F237270D}" name="Terno" dataDxfId="24"/>
+    <tableColumn id="16" xr3:uid="{FF0A908E-E8EE-4CA0-96FA-38C032BFEFDE}" name="Forma" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{DE0283F8-D4F6-449C-A9CA-7DBCB898DFD9}" name="Prazo_x000a_Fund" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{663D9716-4C25-4ACC-A105-E9E7A474BCE6}" name="Prazo_x000a_Fund Real" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{6EF58C27-546C-4B57-B05D-BB07C2046388}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{AC626966-9CA5-4150-82F1-50338494E847}" name="Pz Entrega_x000a_Real" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{506EC589-7ED2-4A3B-BED8-6CA8F57277E1}" name="Desenho_x000a_Previsão" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{A31AB572-7F13-4A5C-A42E-7E7A20433BDA}" name="Des." dataDxfId="17"/>
+    <tableColumn id="33" xr3:uid="{9D21190D-5788-4F29-AED2-63644BCE6C32}" name="OP1" dataDxfId="1"/>
+    <tableColumn id="30" xr3:uid="{6C8FD4D3-300E-4009-A264-D6FBC780DE60}" name="OP2" dataDxfId="2"/>
+    <tableColumn id="28" xr3:uid="{533BCCB9-B72A-4E3A-BE20-626EE2E49D83}" name="OP3" dataDxfId="3"/>
+    <tableColumn id="27" xr3:uid="{58435D6B-01D7-44DD-9B21-62EB23C9AA4F}" name="OP4" dataDxfId="4"/>
+    <tableColumn id="25" xr3:uid="{B00B175A-D2BA-4783-8EBD-A000C46B6055}" name="OP5" dataDxfId="5"/>
+    <tableColumn id="20" xr3:uid="{1C48207C-2D30-42CB-BD4E-0C9B569C9BCB}" name="OP6" dataDxfId="6"/>
+    <tableColumn id="35" xr3:uid="{5857075F-D742-43D2-AD1F-F2BB8219D8E7}" name="OP7" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{46F62312-EE93-4C00-9352-8A9BF48479C9}" name="OP8" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{81AAED83-3114-4366-BECD-21F933A26FE9}" name="OP9" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{F5387D14-C7D5-4022-901B-04E5D65304C7}" name="Status_x000a_Camisa" dataDxfId="16"/>
+    <tableColumn id="32" xr3:uid="{BEC53105-CFFD-422E-9C30-4E4BC1816678}" name="Nº Eixo2" dataDxfId="15"/>
+    <tableColumn id="31" xr3:uid="{75A53AF4-0F54-4590-BD96-F05C1573DAAA}" name="Rec_x000a_Eixo" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{E4F9165E-8213-4A74-8458-2B70C50F9169}" name="Recurso Usinagem_x000a_Eixo" dataDxfId="13"/>
+    <tableColumn id="22" xr3:uid="{DD97A210-9E2B-4A0B-AAFA-22D7F8571D7D}" name="Nº Laudo" dataDxfId="12"/>
+    <tableColumn id="29" xr3:uid="{9A0D9E97-0991-4A6E-8B85-EED9CC983F8A}" name="Prazo_x000a_Entrega_x000a_Eixo" dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{28D59365-C375-479F-85A6-0CBB39E36BC5}" name="Status_x000a_Eixo" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{A08285BC-8B0E-4492-A6AF-090B851B036D}" name="Observação" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4332,7 +4348,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>2199</v>
       </c>
@@ -4374,11 +4390,13 @@
       <c r="M2" s="16">
         <v>46213</v>
       </c>
-      <c r="N2" s="16"/>
+      <c r="N2" s="16">
+        <v>46199</v>
+      </c>
       <c r="O2" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P2" s="40" t="str">
         <f t="shared" ref="P2:P33" ca="1" si="0">IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -4423,7 +4441,7 @@
         <v>85</v>
       </c>
       <c r="AC2" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE2" s="42">
         <v>24</v>
@@ -4446,7 +4464,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
         <v>2199</v>
       </c>
@@ -4492,7 +4510,7 @@
       <c r="O3" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P3" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4537,7 +4555,7 @@
         <v>72</v>
       </c>
       <c r="AC3" s="10" t="str">
-        <f t="shared" ref="AC2:AC33" si="1">IF(L3="","AG. FUNDIDO",IF(U3="AG","AG. USINAGEM","EM USINAGEM"))</f>
+        <f t="shared" ref="AC3:AC33" si="1">IF(L3="","AG. FUNDIDO",IF(U3="AG","AG. USINAGEM","EM USINAGEM"))</f>
         <v>EM USINAGEM</v>
       </c>
       <c r="AE3" s="42">
@@ -4607,7 +4625,7 @@
       <c r="O4" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P4" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4722,7 +4740,7 @@
       <c r="O5" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P5" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4791,7 +4809,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
         <v>2199</v>
       </c>
@@ -4837,7 +4855,7 @@
       <c r="O6" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P6" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4952,7 +4970,7 @@
       <c r="O7" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P7" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5021,7 +5039,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>2199</v>
       </c>
@@ -5063,11 +5081,13 @@
       <c r="M8" s="16">
         <v>46213</v>
       </c>
-      <c r="N8" s="16"/>
+      <c r="N8" s="16">
+        <v>46199</v>
+      </c>
       <c r="O8" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P8" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5112,7 +5132,7 @@
         <v>85</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE8" s="42">
         <v>23</v>
@@ -5135,7 +5155,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>2199</v>
       </c>
@@ -5177,11 +5197,13 @@
       <c r="M9" s="16">
         <v>46213</v>
       </c>
-      <c r="N9" s="16"/>
+      <c r="N9" s="16">
+        <v>46199</v>
+      </c>
       <c r="O9" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P9" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5226,7 +5248,7 @@
         <v>85</v>
       </c>
       <c r="AC9" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE9" s="42">
         <v>23</v>
@@ -5249,7 +5271,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>2199</v>
       </c>
@@ -5291,11 +5313,13 @@
       <c r="M10" s="16">
         <v>46213</v>
       </c>
-      <c r="N10" s="16"/>
+      <c r="N10" s="16">
+        <v>46199</v>
+      </c>
       <c r="O10" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P10" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5340,7 +5364,7 @@
         <v>85</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE10" s="42">
         <v>23</v>
@@ -5363,7 +5387,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>2199</v>
       </c>
@@ -5405,11 +5429,13 @@
       <c r="M11" s="16">
         <v>46213</v>
       </c>
-      <c r="N11" s="16"/>
+      <c r="N11" s="16">
+        <v>46199</v>
+      </c>
       <c r="O11" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P11" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5454,7 +5480,7 @@
         <v>85</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE11" s="42">
         <v>23</v>
@@ -5523,7 +5549,7 @@
       <c r="O12" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P12" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5638,7 +5664,7 @@
       <c r="O13" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P13" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5753,7 +5779,7 @@
       <c r="O14" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P14" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5868,7 +5894,7 @@
       <c r="O15" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P15" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -5940,7 +5966,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="15">
         <v>2199</v>
       </c>
@@ -5982,11 +6008,13 @@
       <c r="M16" s="16">
         <v>46213</v>
       </c>
-      <c r="N16" s="16"/>
+      <c r="N16" s="16">
+        <v>46199</v>
+      </c>
       <c r="O16" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P16" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6031,7 +6059,7 @@
         <v>85</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE16" s="42">
         <v>26</v>
@@ -6054,7 +6082,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="15">
         <v>2201</v>
       </c>
@@ -6096,11 +6124,13 @@
       <c r="M17" s="16">
         <v>46213</v>
       </c>
-      <c r="N17" s="16"/>
+      <c r="N17" s="16">
+        <v>46199</v>
+      </c>
       <c r="O17" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P17" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6145,7 +6175,7 @@
         <v>85</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE17" s="42">
         <v>26</v>
@@ -6168,7 +6198,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
         <v>2201</v>
       </c>
@@ -6210,11 +6240,13 @@
       <c r="M18" s="16">
         <v>46213</v>
       </c>
-      <c r="N18" s="16"/>
+      <c r="N18" s="16">
+        <v>46199</v>
+      </c>
       <c r="O18" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P18" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6259,7 +6291,7 @@
         <v>85</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE18" s="42">
         <v>26</v>
@@ -6282,7 +6314,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
         <v>2201</v>
       </c>
@@ -6324,11 +6356,13 @@
       <c r="M19" s="16">
         <v>46213</v>
       </c>
-      <c r="N19" s="16"/>
+      <c r="N19" s="16">
+        <v>46199</v>
+      </c>
       <c r="O19" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P19" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6373,7 +6407,7 @@
         <v>85</v>
       </c>
       <c r="AC19" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE19" s="42">
         <v>26</v>
@@ -6439,7 +6473,7 @@
       <c r="O20" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P20" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6551,7 +6585,7 @@
       <c r="O21" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P21" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6666,7 +6700,7 @@
       <c r="O22" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P22" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6781,7 +6815,7 @@
       <c r="O23" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P23" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6896,7 +6930,7 @@
       <c r="O24" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P24" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7011,7 +7045,7 @@
       <c r="O25" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P25" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7126,7 +7160,7 @@
       <c r="O26" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P26" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7241,7 +7275,7 @@
       <c r="O27" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P27" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7356,7 +7390,7 @@
       <c r="O28" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P28" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7471,7 +7505,7 @@
       <c r="O29" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P29" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7586,7 +7620,7 @@
       <c r="O30" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P30" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7655,7 +7689,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
         <v>2202</v>
       </c>
@@ -7697,11 +7731,13 @@
       <c r="M31" s="16">
         <v>46213</v>
       </c>
-      <c r="N31" s="16"/>
+      <c r="N31" s="16">
+        <v>46199</v>
+      </c>
       <c r="O31" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P31" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7746,7 +7782,7 @@
         <v>85</v>
       </c>
       <c r="AC31" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AE31" s="42">
         <v>27</v>
@@ -7815,7 +7851,7 @@
       <c r="O32" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P32" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7930,7 +7966,7 @@
       <c r="O33" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P33" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8045,7 +8081,7 @@
       <c r="O34" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P34" s="40" t="str">
         <f t="shared" ref="P34:P65" ca="1" si="2">IF(O34&lt;0,"ATRASADO",IF(O34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -8160,7 +8196,7 @@
       <c r="O35" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P35" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8275,7 +8311,7 @@
       <c r="O36" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P36" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8390,7 +8426,7 @@
       <c r="O37" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P37" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8505,7 +8541,7 @@
       <c r="O38" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P38" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8617,7 +8653,7 @@
       <c r="O39" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P39" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8729,7 +8765,7 @@
       <c r="O40" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P40" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8844,7 +8880,7 @@
       <c r="O41" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P41" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -8959,7 +8995,7 @@
       <c r="O42" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P42" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9074,7 +9110,7 @@
       <c r="O43" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P43" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9186,7 +9222,7 @@
       <c r="O44" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P44" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9301,7 +9337,7 @@
       <c r="O45" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P45" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9416,7 +9452,7 @@
       <c r="O46" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P46" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9531,7 +9567,7 @@
       <c r="O47" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P47" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9643,7 +9679,7 @@
       <c r="O48" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P48" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9756,7 +9792,7 @@
       <c r="O49" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P49" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9869,7 +9905,7 @@
       <c r="O50" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P50" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9984,7 +10020,7 @@
       <c r="O51" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P51" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10099,7 +10135,7 @@
       <c r="O52" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P52" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10214,7 +10250,7 @@
       <c r="O53" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P53" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10326,7 +10362,7 @@
       <c r="O54" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P54" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10438,7 +10474,7 @@
       <c r="O55" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P55" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10550,7 +10586,7 @@
       <c r="O56" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P56" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10662,7 +10698,7 @@
       <c r="O57" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P57" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10777,7 +10813,7 @@
       <c r="O58" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P58" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10892,7 +10928,7 @@
       <c r="O59" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P59" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11004,7 +11040,7 @@
       <c r="O60" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P60" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11111,7 +11147,7 @@
       <c r="O61" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P61" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11221,7 +11257,7 @@
       <c r="O62" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P62" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11331,7 +11367,7 @@
       <c r="O63" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P63" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11441,7 +11477,7 @@
       <c r="O64" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P64" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11548,7 +11584,7 @@
       <c r="O65" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P65" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11658,7 +11694,7 @@
       <c r="O66" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P66" s="40" t="str">
         <f t="shared" ref="P66:P89" ca="1" si="4">IF(O66&lt;0,"ATRASADO",IF(O66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -11765,7 +11801,7 @@
       <c r="O67" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P67" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11880,7 +11916,7 @@
       <c r="O68" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P68" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -11992,7 +12028,7 @@
       <c r="O69" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P69" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12104,7 +12140,7 @@
       <c r="O70" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P70" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12216,7 +12252,7 @@
       <c r="O71" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P71" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12328,7 +12364,7 @@
       <c r="O72" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P72" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12440,7 +12476,7 @@
       <c r="O73" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P73" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12552,7 +12588,7 @@
       <c r="O74" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P74" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12664,7 +12700,7 @@
       <c r="O75" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P75" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12776,7 +12812,7 @@
       <c r="O76" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P76" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -12888,7 +12924,7 @@
       <c r="O77" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P77" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13000,7 +13036,7 @@
       <c r="O78" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P78" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13110,7 +13146,7 @@
       <c r="O79" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P79" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13220,7 +13256,7 @@
       <c r="O80" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P80" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13330,7 +13366,7 @@
       <c r="O81" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P81" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13440,7 +13476,7 @@
       <c r="O82" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P82" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13550,7 +13586,7 @@
       <c r="O83" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P83" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13660,7 +13696,7 @@
       <c r="O84" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P84" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13774,7 +13810,7 @@
       <c r="O85" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P85" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13888,7 +13924,7 @@
       <c r="O86" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P86" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14002,7 +14038,7 @@
       <c r="O87" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P87" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14116,7 +14152,7 @@
       <c r="O88" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P88" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14230,7 +14266,7 @@
       <c r="O89" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P89" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14344,7 +14380,7 @@
       <c r="O90" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P90" s="40" t="str">
         <f t="shared" ref="P90:P94" ca="1" si="6">IF(O90&lt;0,"ATRASADO",IF(O90&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -14451,7 +14487,7 @@
       <c r="O91" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P91" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -14558,7 +14594,7 @@
       <c r="O92" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P92" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -14665,7 +14701,7 @@
       <c r="O93" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P93" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -14772,7 +14808,7 @@
       <c r="O94" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P94" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -14879,7 +14915,7 @@
       <c r="O95" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P95" s="40" t="str">
         <f t="shared" ref="P95:P99" ca="1" si="7">IF(O95&lt;0,"ATRASADO",IF(O95&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -14976,7 +15012,7 @@
       <c r="O96" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P96" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -15073,7 +15109,7 @@
       <c r="O97" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P97" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -15170,7 +15206,7 @@
       <c r="O98" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P98" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -15267,7 +15303,7 @@
       <c r="O99" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P99" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -15364,7 +15400,7 @@
       <c r="O100" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P100" s="40" t="str">
         <f ca="1">IF(O100&lt;0,"ATRASADO",IF(O100&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -15461,7 +15497,7 @@
       <c r="O101" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P101" s="40" t="str">
         <f t="shared" ref="P101:P109" ca="1" si="9">IF(O101&lt;0,"ATRASADO",IF(O101&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -15558,7 +15594,7 @@
       <c r="O102" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P102" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -15655,7 +15691,7 @@
       <c r="O103" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P103" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -15752,7 +15788,7 @@
       <c r="O104" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P104" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -15849,7 +15885,7 @@
       <c r="O105" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P105" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -15946,7 +15982,7 @@
       <c r="O106" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P106" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -16043,7 +16079,7 @@
       <c r="O107" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P107" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -16140,7 +16176,7 @@
       <c r="O108" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P108" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -16237,7 +16273,7 @@
       <c r="O109" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P109" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -16334,7 +16370,7 @@
       <c r="O110" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P110" s="40" t="str">
         <f ca="1">IF(O110&lt;0,"ATRASADO",IF(O110&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16431,7 +16467,7 @@
       <c r="O111" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P111" s="40" t="str">
         <f t="shared" ref="P111:P114" ca="1" si="10">IF(O111&lt;0,"ATRASADO",IF(O111&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16528,7 +16564,7 @@
       <c r="O112" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P112" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -16625,7 +16661,7 @@
       <c r="O113" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P113" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -16722,7 +16758,7 @@
       <c r="O114" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P114" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -16932,7 +16968,7 @@
       <c r="Q2" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R2" s="10" t="str">
         <f t="shared" ref="R2:R33" ca="1" si="0">IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16947,7 +16983,7 @@
         <v>43</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="V2" s="10"/>
     </row>
@@ -17003,7 +17039,7 @@
       <c r="Q3" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R3" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17018,7 +17054,7 @@
         <v>43</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="V3" s="10"/>
     </row>
@@ -17074,7 +17110,7 @@
       <c r="Q4" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R4" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17089,7 +17125,7 @@
         <v>43</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="V4" s="10"/>
     </row>
@@ -17145,7 +17181,7 @@
       <c r="Q5" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R5" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17160,7 +17196,7 @@
         <v>43</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="V5" s="10"/>
     </row>
@@ -17216,7 +17252,7 @@
       <c r="Q6" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R6" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17231,7 +17267,7 @@
         <v>43</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="V6" s="10"/>
     </row>
@@ -17287,7 +17323,7 @@
       <c r="Q7" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R7" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17302,7 +17338,7 @@
         <v>43</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="V7" s="10"/>
     </row>
@@ -17358,7 +17394,7 @@
       <c r="Q8" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R8" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17373,7 +17409,7 @@
         <v>43</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="V8" s="10"/>
     </row>
@@ -17429,7 +17465,7 @@
       <c r="Q9" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R9" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17444,7 +17480,7 @@
         <v>43</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="V9" s="10"/>
     </row>
@@ -17500,7 +17536,7 @@
       <c r="Q10" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R10" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17515,7 +17551,7 @@
         <v>43</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="V10" s="10"/>
     </row>
@@ -17571,7 +17607,7 @@
       <c r="Q11" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R11" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17644,7 +17680,7 @@
       <c r="Q12" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R12" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17717,7 +17753,7 @@
       <c r="Q13" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R13" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17790,7 +17826,7 @@
       <c r="Q14" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R14" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17861,7 +17897,7 @@
       <c r="Q15" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R15" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -17932,7 +17968,7 @@
       <c r="Q16" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R16" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18003,7 +18039,7 @@
       <c r="Q17" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R17" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18074,7 +18110,7 @@
       <c r="Q18" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R18" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18145,7 +18181,7 @@
       <c r="Q19" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R19" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18216,7 +18252,7 @@
       <c r="Q20" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R20" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18287,7 +18323,7 @@
       <c r="Q21" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R21" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18358,7 +18394,7 @@
       <c r="Q22" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R22" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18429,7 +18465,7 @@
       <c r="Q23" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R23" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18500,7 +18536,7 @@
       <c r="Q24" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R24" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18571,7 +18607,7 @@
       <c r="Q25" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R25" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18642,7 +18678,7 @@
       <c r="Q26" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R26" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18713,7 +18749,7 @@
       <c r="Q27" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R27" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18784,7 +18820,7 @@
       <c r="Q28" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R28" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18855,7 +18891,7 @@
       <c r="Q29" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R29" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18926,7 +18962,7 @@
       <c r="Q30" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R30" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18997,7 +19033,7 @@
       <c r="Q31" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R31" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19068,7 +19104,7 @@
       <c r="Q32" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R32" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19139,7 +19175,7 @@
       <c r="Q33" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19210,7 +19246,7 @@
       <c r="Q34" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R34" s="10" t="str">
         <f t="shared" ref="R34:R65" ca="1" si="1">IF(Q34&lt;0,"ATRASADO",IF(Q34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -19281,7 +19317,7 @@
       <c r="Q35" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R35" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19352,7 +19388,7 @@
       <c r="Q36" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R36" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19423,7 +19459,7 @@
       <c r="Q37" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R37" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19494,7 +19530,7 @@
       <c r="Q38" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R38" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19565,7 +19601,7 @@
       <c r="Q39" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R39" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19636,7 +19672,7 @@
       <c r="Q40" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R40" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19707,7 +19743,7 @@
       <c r="Q41" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R41" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19778,7 +19814,7 @@
       <c r="Q42" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R42" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19849,7 +19885,7 @@
       <c r="Q43" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R43" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19920,7 +19956,7 @@
       <c r="Q44" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R44" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -19991,7 +20027,7 @@
       <c r="Q45" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R45" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20062,7 +20098,7 @@
       <c r="Q46" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R46" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20133,7 +20169,7 @@
       <c r="Q47" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R47" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20204,7 +20240,7 @@
       <c r="Q48" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R48" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20275,7 +20311,7 @@
       <c r="Q49" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R49" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20346,7 +20382,7 @@
       <c r="Q50" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R50" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20417,7 +20453,7 @@
       <c r="Q51" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R51" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20488,7 +20524,7 @@
       <c r="Q52" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R52" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20559,7 +20595,7 @@
       <c r="Q53" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R53" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20630,7 +20666,7 @@
       <c r="Q54" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R54" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20701,7 +20737,7 @@
       <c r="Q55" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R55" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20772,7 +20808,7 @@
       <c r="Q56" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R56" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20843,7 +20879,7 @@
       <c r="Q57" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R57" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20914,7 +20950,7 @@
       <c r="Q58" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R58" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20985,7 +21021,7 @@
       <c r="Q59" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R59" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21056,7 +21092,7 @@
       <c r="Q60" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R60" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21127,7 +21163,7 @@
       <c r="Q61" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R61" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21198,7 +21234,7 @@
       <c r="Q62" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R62" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21269,7 +21305,7 @@
       <c r="Q63" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R63" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21340,7 +21376,7 @@
       <c r="Q64" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="R64" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21411,7 +21447,7 @@
       <c r="Q65" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R65" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21482,7 +21518,7 @@
       <c r="Q66" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R66" s="10" t="str">
         <f t="shared" ref="R66:R91" ca="1" si="2">IF(Q66&lt;0,"ATRASADO",IF(Q66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -21553,7 +21589,7 @@
       <c r="Q67" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R67" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21624,7 +21660,7 @@
       <c r="Q68" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R68" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21695,7 +21731,7 @@
       <c r="Q69" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R69" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21766,7 +21802,7 @@
       <c r="Q70" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R70" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21837,7 +21873,7 @@
       <c r="Q71" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R71" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21908,7 +21944,7 @@
       <c r="Q72" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R72" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -21979,7 +22015,7 @@
       <c r="Q73" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R73" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22050,7 +22086,7 @@
       <c r="Q74" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R74" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22121,7 +22157,7 @@
       <c r="Q75" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R75" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22192,7 +22228,7 @@
       <c r="Q76" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R76" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22263,7 +22299,7 @@
       <c r="Q77" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R77" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22334,7 +22370,7 @@
       <c r="Q78" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R78" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22405,7 +22441,7 @@
       <c r="Q79" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R79" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22476,7 +22512,7 @@
       <c r="Q80" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R80" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22547,7 +22583,7 @@
       <c r="Q81" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R81" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22618,7 +22654,7 @@
       <c r="Q82" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R82" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22689,7 +22725,7 @@
       <c r="Q83" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R83" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22760,7 +22796,7 @@
       <c r="Q84" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R84" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22831,7 +22867,7 @@
       <c r="Q85" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R85" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22902,7 +22938,7 @@
       <c r="Q86" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R86" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -22973,7 +23009,7 @@
       <c r="Q87" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R87" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23044,7 +23080,7 @@
       <c r="Q88" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R88" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23115,7 +23151,7 @@
       <c r="Q89" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R89" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23186,7 +23222,7 @@
       <c r="Q90" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R90" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23257,7 +23293,7 @@
       <c r="Q91" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R91" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23328,7 +23364,7 @@
       <c r="Q92" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R92" s="10" t="str">
         <f ca="1">IF(Q92&lt;0,"ATRASADO",IF(Q92&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23399,7 +23435,7 @@
       <c r="Q93" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R93" s="10" t="str">
         <f ca="1">IF(Q93&lt;0,"ATRASADO",IF(Q93&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23470,7 +23506,7 @@
       <c r="Q94" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R94" s="10" t="str">
         <f t="shared" ref="R94:R131" ca="1" si="3">IF(Q94&lt;0,"ATRASADO",IF(Q94&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23541,7 +23577,7 @@
       <c r="Q95" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R95" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23612,7 +23648,7 @@
       <c r="Q96" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R96" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23683,7 +23719,7 @@
       <c r="Q97" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R97" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23754,7 +23790,7 @@
       <c r="Q98" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R98" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23825,7 +23861,7 @@
       <c r="Q99" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R99" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23896,7 +23932,7 @@
       <c r="Q100" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R100" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -23967,7 +24003,7 @@
       <c r="Q101" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R101" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24038,7 +24074,7 @@
       <c r="Q102" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R102" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24109,7 +24145,7 @@
       <c r="Q103" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R103" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24180,7 +24216,7 @@
       <c r="Q104" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R104" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24251,7 +24287,7 @@
       <c r="Q105" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R105" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24322,7 +24358,7 @@
       <c r="Q106" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R106" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24393,7 +24429,7 @@
       <c r="Q107" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R107" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24464,7 +24500,7 @@
       <c r="Q108" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R108" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24535,7 +24571,7 @@
       <c r="Q109" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R109" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24606,7 +24642,7 @@
       <c r="Q110" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R110" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24677,7 +24713,7 @@
       <c r="Q111" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R111" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24748,7 +24784,7 @@
       <c r="Q112" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R112" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24819,7 +24855,7 @@
       <c r="Q113" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R113" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24890,7 +24926,7 @@
       <c r="Q114" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R114" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -24961,7 +24997,7 @@
       <c r="Q115" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R115" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25032,7 +25068,7 @@
       <c r="Q116" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R116" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25103,7 +25139,7 @@
       <c r="Q117" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R117" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25174,7 +25210,7 @@
       <c r="Q118" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R118" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25245,7 +25281,7 @@
       <c r="Q119" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R119" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25316,7 +25352,7 @@
       <c r="Q120" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R120" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25387,7 +25423,7 @@
       <c r="Q121" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R121" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25458,7 +25494,7 @@
       <c r="Q122" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R122" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25529,7 +25565,7 @@
       <c r="Q123" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R123" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25600,7 +25636,7 @@
       <c r="Q124" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R124" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25671,7 +25707,7 @@
       <c r="Q125" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R125" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25742,7 +25778,7 @@
       <c r="Q126" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R126" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25813,7 +25849,7 @@
       <c r="Q127" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R127" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25884,7 +25920,7 @@
       <c r="Q128" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R128" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25955,7 +25991,7 @@
       <c r="Q129" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R129" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26026,7 +26062,7 @@
       <c r="Q130" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R130" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26097,7 +26133,7 @@
       <c r="Q131" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R131" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26139,7 +26175,7 @@
         <v>77</v>
       </c>
       <c r="H132" s="10" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I132" s="10">
         <v>1</v>
@@ -26147,7 +26183,7 @@
       <c r="J132" s="11">
         <v>46219</v>
       </c>
-      <c r="K132" s="57">
+      <c r="K132" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26166,13 +26202,13 @@
       <c r="Q132" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
-      </c>
-      <c r="R132" s="57" t="str">
+        <v>32</v>
+      </c>
+      <c r="R132" s="10" t="str">
         <f ca="1">IF(Q132&lt;0,"ATRASADO",IF(Q132&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
         <v>NO PRAZO</v>
       </c>
-      <c r="S132" s="57">
+      <c r="S132" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>31</v>
@@ -26183,7 +26219,7 @@
       <c r="U132" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V132" s="57"/>
+      <c r="V132" s="10"/>
     </row>
     <row r="133" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A133" s="10">
@@ -26208,7 +26244,7 @@
         <v>77</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I133" s="10">
         <v>1</v>
@@ -26216,7 +26252,7 @@
       <c r="J133" s="11">
         <v>46219</v>
       </c>
-      <c r="K133" s="57">
+      <c r="K133" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26235,13 +26271,13 @@
       <c r="Q133" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
-      </c>
-      <c r="R133" s="57" t="str">
+        <v>47</v>
+      </c>
+      <c r="R133" s="10" t="str">
         <f t="shared" ref="R133:R143" ca="1" si="4">IF(Q133&lt;0,"ATRASADO",IF(Q133&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
         <v>NO PRAZO</v>
       </c>
-      <c r="S133" s="57">
+      <c r="S133" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>33</v>
@@ -26252,7 +26288,7 @@
       <c r="U133" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V133" s="57"/>
+      <c r="V133" s="10"/>
     </row>
     <row r="134" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A134" s="10">
@@ -26277,7 +26313,7 @@
         <v>77</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I134" s="10">
         <v>1</v>
@@ -26285,7 +26321,7 @@
       <c r="J134" s="11">
         <v>46219</v>
       </c>
-      <c r="K134" s="57">
+      <c r="K134" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26304,13 +26340,13 @@
       <c r="Q134" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
-      </c>
-      <c r="R134" s="57" t="str">
+        <v>47</v>
+      </c>
+      <c r="R134" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S134" s="57">
+      <c r="S134" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>33</v>
@@ -26321,7 +26357,7 @@
       <c r="U134" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V134" s="57"/>
+      <c r="V134" s="10"/>
     </row>
     <row r="135" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A135" s="10">
@@ -26346,7 +26382,7 @@
         <v>77</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I135" s="10">
         <v>1</v>
@@ -26354,7 +26390,7 @@
       <c r="J135" s="11">
         <v>46219</v>
       </c>
-      <c r="K135" s="57">
+      <c r="K135" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26373,13 +26409,13 @@
       <c r="Q135" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
-      </c>
-      <c r="R135" s="57" t="str">
+        <v>32</v>
+      </c>
+      <c r="R135" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S135" s="57">
+      <c r="S135" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>31</v>
@@ -26390,7 +26426,7 @@
       <c r="U135" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V135" s="57"/>
+      <c r="V135" s="10"/>
     </row>
     <row r="136" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A136" s="10">
@@ -26415,7 +26451,7 @@
         <v>77</v>
       </c>
       <c r="H136" s="10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I136" s="10">
         <v>1</v>
@@ -26423,7 +26459,7 @@
       <c r="J136" s="11">
         <v>46219</v>
       </c>
-      <c r="K136" s="57">
+      <c r="K136" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26442,13 +26478,13 @@
       <c r="Q136" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
-      </c>
-      <c r="R136" s="57" t="str">
+        <v>32</v>
+      </c>
+      <c r="R136" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S136" s="57">
+      <c r="S136" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>31</v>
@@ -26459,7 +26495,7 @@
       <c r="U136" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V136" s="57"/>
+      <c r="V136" s="10"/>
     </row>
     <row r="137" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A137" s="10">
@@ -26484,7 +26520,7 @@
         <v>77</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I137" s="10">
         <v>1</v>
@@ -26492,7 +26528,7 @@
       <c r="J137" s="11">
         <v>46219</v>
       </c>
-      <c r="K137" s="57">
+      <c r="K137" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26511,13 +26547,13 @@
       <c r="Q137" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
-      </c>
-      <c r="R137" s="57" t="str">
+        <v>47</v>
+      </c>
+      <c r="R137" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S137" s="57">
+      <c r="S137" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>33</v>
@@ -26528,7 +26564,7 @@
       <c r="U137" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V137" s="57"/>
+      <c r="V137" s="10"/>
     </row>
     <row r="138" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A138" s="10">
@@ -26553,7 +26589,7 @@
         <v>77</v>
       </c>
       <c r="H138" s="10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I138" s="10">
         <v>1</v>
@@ -26561,7 +26597,7 @@
       <c r="J138" s="11">
         <v>46219</v>
       </c>
-      <c r="K138" s="57">
+      <c r="K138" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26580,13 +26616,13 @@
       <c r="Q138" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
-      </c>
-      <c r="R138" s="57" t="str">
+        <v>47</v>
+      </c>
+      <c r="R138" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S138" s="57">
+      <c r="S138" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>33</v>
@@ -26597,7 +26633,7 @@
       <c r="U138" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V138" s="57"/>
+      <c r="V138" s="10"/>
     </row>
     <row r="139" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A139" s="10">
@@ -26622,7 +26658,7 @@
         <v>77</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="I139" s="10">
         <v>1</v>
@@ -26630,7 +26666,7 @@
       <c r="J139" s="11">
         <v>46219</v>
       </c>
-      <c r="K139" s="57">
+      <c r="K139" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26649,13 +26685,13 @@
       <c r="Q139" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
-      </c>
-      <c r="R139" s="57" t="str">
+        <v>47</v>
+      </c>
+      <c r="R139" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S139" s="57">
+      <c r="S139" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>33</v>
@@ -26666,7 +26702,7 @@
       <c r="U139" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V139" s="57"/>
+      <c r="V139" s="10"/>
     </row>
     <row r="140" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A140" s="10">
@@ -26691,7 +26727,7 @@
         <v>77</v>
       </c>
       <c r="H140" s="10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I140" s="10">
         <v>1</v>
@@ -26699,7 +26735,7 @@
       <c r="J140" s="11">
         <v>46219</v>
       </c>
-      <c r="K140" s="57">
+      <c r="K140" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26718,13 +26754,13 @@
       <c r="Q140" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
-      </c>
-      <c r="R140" s="57" t="str">
+        <v>32</v>
+      </c>
+      <c r="R140" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S140" s="57">
+      <c r="S140" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>31</v>
@@ -26735,7 +26771,7 @@
       <c r="U140" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V140" s="57"/>
+      <c r="V140" s="10"/>
     </row>
     <row r="141" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A141" s="10">
@@ -26760,7 +26796,7 @@
         <v>77</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I141" s="10">
         <v>1</v>
@@ -26768,7 +26804,7 @@
       <c r="J141" s="11">
         <v>46219</v>
       </c>
-      <c r="K141" s="57">
+      <c r="K141" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26787,13 +26823,13 @@
       <c r="Q141" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>34</v>
-      </c>
-      <c r="R141" s="57" t="str">
+        <v>32</v>
+      </c>
+      <c r="R141" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S141" s="57">
+      <c r="S141" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>31</v>
@@ -26804,7 +26840,7 @@
       <c r="U141" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V141" s="57"/>
+      <c r="V141" s="10"/>
     </row>
     <row r="142" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A142" s="10">
@@ -26829,7 +26865,7 @@
         <v>77</v>
       </c>
       <c r="H142" s="10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I142" s="10">
         <v>1</v>
@@ -26837,7 +26873,7 @@
       <c r="J142" s="11">
         <v>46219</v>
       </c>
-      <c r="K142" s="57">
+      <c r="K142" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26856,13 +26892,13 @@
       <c r="Q142" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
-      </c>
-      <c r="R142" s="57" t="str">
+        <v>47</v>
+      </c>
+      <c r="R142" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S142" s="57">
+      <c r="S142" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>33</v>
@@ -26873,7 +26909,7 @@
       <c r="U142" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V142" s="57"/>
+      <c r="V142" s="10"/>
     </row>
     <row r="143" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A143" s="10">
@@ -26898,7 +26934,7 @@
         <v>77</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I143" s="10">
         <v>1</v>
@@ -26906,7 +26942,7 @@
       <c r="J143" s="11">
         <v>46219</v>
       </c>
-      <c r="K143" s="57">
+      <c r="K143" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>29</v>
@@ -26925,13 +26961,13 @@
       <c r="Q143" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
-      </c>
-      <c r="R143" s="57" t="str">
+        <v>47</v>
+      </c>
+      <c r="R143" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S143" s="57">
+      <c r="S143" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>33</v>
@@ -26942,7 +26978,7 @@
       <c r="U143" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V143" s="57"/>
+      <c r="V143" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -27092,7 +27128,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O2" s="13" t="str">
         <f t="shared" ref="O2:O16" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27169,7 +27205,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O3" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27246,7 +27282,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O4" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27323,7 +27359,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O5" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27400,7 +27436,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O6" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27477,7 +27513,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O7" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27554,7 +27590,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O8" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27631,7 +27667,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O9" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27708,7 +27744,7 @@
       <c r="N10" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O10" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27785,7 +27821,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O11" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27862,7 +27898,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O12" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27939,7 +27975,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O13" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -28016,7 +28052,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O14" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -28093,7 +28129,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O15" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -28170,7 +28206,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O16" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -28247,7 +28283,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O17" s="13" t="str">
         <f ca="1">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28326,7 +28362,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O18" s="13" t="str">
         <f t="shared" ref="O18:O25" ca="1" si="2">IF(N18&lt;0,"ATRASADO",IF(N18&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28405,7 +28441,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -28484,7 +28520,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -28563,7 +28599,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -28642,7 +28678,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -28721,7 +28757,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -28800,7 +28836,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -28879,7 +28915,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -28958,7 +28994,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O26" s="13" t="str">
         <f ca="1">IF(N26&lt;0,"ATRASADO",IF(N26&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -29035,7 +29071,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O27" s="13" t="str">
         <f t="shared" ref="O27:O28" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -29112,7 +29148,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O28" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -29189,7 +29225,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O29" s="13" t="str">
         <f t="shared" ref="O29:O31" ca="1" si="5">IF(N29&lt;0,"ATRASADO",IF(N29&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -29268,7 +29304,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O30" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -29347,7 +29383,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="O31" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -29426,7 +29462,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O32" s="13" t="str">
         <f ca="1">IF(N32&lt;0,"ATRASADO",IF(N32&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -29466,7 +29502,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>2331</v>
       </c>
@@ -29505,7 +29541,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O33" s="13" t="str">
         <f t="shared" ref="O33:O35" ca="1" si="7">IF(N33&lt;0,"ATRASADO",IF(N33&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -29545,7 +29581,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>2331</v>
       </c>
@@ -29584,7 +29620,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O34" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -29624,7 +29660,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>2331</v>
       </c>
@@ -29663,7 +29699,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O35" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -29703,7 +29739,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>2337</v>
       </c>
@@ -29717,7 +29753,7 @@
         <v>1</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>77</v>
@@ -29726,7 +29762,7 @@
         <v>77</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I36" s="14">
         <v>1</v>
@@ -29734,24 +29770,24 @@
       <c r="J36" s="18">
         <v>46265</v>
       </c>
-      <c r="K36" s="58"/>
+      <c r="K36" s="1"/>
       <c r="L36" s="18">
         <v>46295</v>
       </c>
-      <c r="M36" s="58"/>
-      <c r="N36" s="59">
+      <c r="M36" s="1"/>
+      <c r="N36" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>96</v>
-      </c>
-      <c r="O36" s="59" t="str">
+        <v>94</v>
+      </c>
+      <c r="O36" s="13" t="str">
         <f ca="1">IF(N36&lt;0,"ATRASADO",IF(N36&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
         <v>NO PRAZO</v>
       </c>
       <c r="P36" t="s">
         <v>43</v>
       </c>
-      <c r="Q36" s="61">
+      <c r="Q36" s="32">
         <v>46223</v>
       </c>
       <c r="R36" s="1" t="s">
@@ -29775,13 +29811,12 @@
       <c r="X36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Y36" s="62" t="str">
+      <c r="Y36" t="str">
         <f>IF(K36="","AG. FUNDIDO",IF(X36="OK","LIBERADA","EM USINAGEM"))</f>
         <v>AG. FUNDIDO</v>
       </c>
-      <c r="Z36" s="60"/>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="14">
         <v>2337</v>
       </c>
@@ -29795,7 +29830,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F37" s="14" t="s">
         <v>77</v>
@@ -29804,7 +29839,7 @@
         <v>77</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="I37" s="14">
         <v>1</v>
@@ -29812,24 +29847,24 @@
       <c r="J37" s="18">
         <v>46265</v>
       </c>
-      <c r="K37" s="58"/>
+      <c r="K37" s="1"/>
       <c r="L37" s="18">
         <v>46295</v>
       </c>
-      <c r="M37" s="58"/>
-      <c r="N37" s="59">
+      <c r="M37" s="1"/>
+      <c r="N37" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>96</v>
-      </c>
-      <c r="O37" s="59" t="str">
+        <v>94</v>
+      </c>
+      <c r="O37" s="13" t="str">
         <f t="shared" ref="O37:O39" ca="1" si="9">IF(N37&lt;0,"ATRASADO",IF(N37&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
         <v>NO PRAZO</v>
       </c>
       <c r="P37" t="s">
         <v>43</v>
       </c>
-      <c r="Q37" s="61">
+      <c r="Q37" s="32">
         <v>46223</v>
       </c>
       <c r="R37" s="1" t="s">
@@ -29853,13 +29888,12 @@
       <c r="X37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Y37" s="62" t="str">
+      <c r="Y37" t="str">
         <f t="shared" ref="Y37:Y39" si="10">IF(K37="","AG. FUNDIDO",IF(X37="OK","LIBERADA","EM USINAGEM"))</f>
         <v>AG. FUNDIDO</v>
       </c>
-      <c r="Z37" s="60"/>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="14">
         <v>2337</v>
       </c>
@@ -29873,7 +29907,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F38" s="14" t="s">
         <v>77</v>
@@ -29890,24 +29924,24 @@
       <c r="J38" s="18">
         <v>46265</v>
       </c>
-      <c r="K38" s="58"/>
+      <c r="K38" s="1"/>
       <c r="L38" s="18">
         <v>46295</v>
       </c>
-      <c r="M38" s="58"/>
-      <c r="N38" s="59">
+      <c r="M38" s="1"/>
+      <c r="N38" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>96</v>
-      </c>
-      <c r="O38" s="59" t="str">
+        <v>94</v>
+      </c>
+      <c r="O38" s="13" t="str">
         <f t="shared" ca="1" si="9"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P38" t="s">
         <v>43</v>
       </c>
-      <c r="Q38" s="61">
+      <c r="Q38" s="32">
         <v>46223</v>
       </c>
       <c r="R38" s="1" t="s">
@@ -29931,13 +29965,12 @@
       <c r="X38" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Y38" s="62" t="str">
+      <c r="Y38" t="str">
         <f t="shared" si="10"/>
         <v>AG. FUNDIDO</v>
       </c>
-      <c r="Z38" s="60"/>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="14">
         <v>2337</v>
       </c>
@@ -29951,7 +29984,7 @@
         <v>4</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="F39" s="14" t="s">
         <v>77</v>
@@ -29968,24 +30001,24 @@
       <c r="J39" s="18">
         <v>46265</v>
       </c>
-      <c r="K39" s="58"/>
+      <c r="K39" s="1"/>
       <c r="L39" s="18">
         <v>46295</v>
       </c>
-      <c r="M39" s="58"/>
-      <c r="N39" s="59">
+      <c r="M39" s="1"/>
+      <c r="N39" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>96</v>
-      </c>
-      <c r="O39" s="59" t="str">
+        <v>94</v>
+      </c>
+      <c r="O39" s="13" t="str">
         <f t="shared" ca="1" si="9"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P39" t="s">
         <v>43</v>
       </c>
-      <c r="Q39" s="61">
+      <c r="Q39" s="32">
         <v>46223</v>
       </c>
       <c r="R39" s="1" t="s">
@@ -30009,45 +30042,44 @@
       <c r="X39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Y39" s="62" t="str">
+      <c r="Y39" t="str">
         <f t="shared" si="10"/>
         <v>AG. FUNDIDO</v>
       </c>
-      <c r="Z39" s="60"/>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N41" s="13"/>
       <c r="O41" s="13"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N42" s="13"/>
       <c r="O42" s="13"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N43" s="13"/>
       <c r="O43" s="13"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N44" s="13"/>
       <c r="O44" s="13"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N45" s="13"/>
       <c r="O45" s="13"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N46" s="13"/>
       <c r="O46" s="13"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N47" s="13"/>
       <c r="O47" s="13"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="N48" s="13"/>
       <c r="O48" s="13"/>
     </row>
@@ -30813,7 +30845,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O2" t="str">
         <f t="shared" ref="O2:O9" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30869,7 +30901,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30925,7 +30957,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30981,7 +31013,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31037,7 +31069,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O6" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31093,7 +31125,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31149,7 +31181,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31205,7 +31237,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31267,7 +31299,7 @@
       <c r="N10" s="12">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>-21</v>
+        <v>-23</v>
       </c>
       <c r="O10" s="33" t="s">
         <v>102</v>
@@ -31325,7 +31357,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O11" s="1" t="str">
         <f ca="1">IF(N11&lt;0,"ATRASADO",IF(N11&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31384,7 +31416,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O12" t="str">
         <f ca="1">IF(N12&lt;0,"ATRASADO",IF(N12&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31443,7 +31475,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">IF(N13&lt;0,"ATRASADO",IF(N13&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31502,7 +31534,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O14" t="str">
         <f ca="1">IF(N14&lt;0,"ATRASADO",IF(N14&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31561,7 +31593,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O15" t="str">
         <f t="shared" ref="O15:O16" ca="1" si="1">IF(N15&lt;0,"ATRASADO",IF(N15&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31620,7 +31652,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -31676,7 +31708,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" ref="O17:O18" ca="1" si="2">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31732,7 +31764,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31791,7 +31823,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O19" t="str">
         <f ca="1">IF(N19&lt;0,"ATRASADO",IF(N19&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31850,7 +31882,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O20" t="str">
         <f ca="1">IF(N20&lt;0,"ATRASADO",IF(N20&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31909,7 +31941,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O21" t="str">
         <f t="shared" ref="O21:O26" ca="1" si="3">IF(N21&lt;0,"ATRASADO",IF(N21&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31968,7 +32000,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O22" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -32027,7 +32059,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -32086,7 +32118,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O24" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -32145,7 +32177,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O25" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -32204,7 +32236,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O26" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -32263,7 +32295,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O27" t="str">
         <f t="shared" ref="O27:O34" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32322,7 +32354,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O28" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -32381,7 +32413,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O29" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -32440,7 +32472,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O30" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -32499,7 +32531,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O31" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -32558,7 +32590,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O32" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -32617,7 +32649,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O33" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -32676,7 +32708,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O34" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -32735,7 +32767,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O35" t="str">
         <f t="shared" ref="O35:O36" ca="1" si="5">IF(N35&lt;0,"ATRASADO",IF(N35&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32794,7 +32826,7 @@
       <c r="N36" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O36" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -32853,7 +32885,7 @@
       <c r="N37" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O37" t="str">
         <f ca="1">IF(N37&lt;0,"ATRASADO",IF(N37&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32912,7 +32944,7 @@
       <c r="N38" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O38" t="str">
         <f t="shared" ref="O38:O52" ca="1" si="6">IF(N38&lt;0,"ATRASADO",IF(N38&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32971,7 +33003,7 @@
       <c r="N39" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O39" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33030,7 +33062,7 @@
       <c r="N40" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33089,7 +33121,7 @@
       <c r="N41" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O41" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33148,7 +33180,7 @@
       <c r="N42" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O42" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33207,7 +33239,7 @@
       <c r="N43" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O43" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33266,7 +33298,7 @@
       <c r="N44" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O44" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33325,7 +33357,7 @@
       <c r="N45" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O45" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33384,7 +33416,7 @@
       <c r="N46" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O46" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33443,7 +33475,7 @@
       <c r="N47" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O47" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33502,7 +33534,7 @@
       <c r="N48" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O48" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33561,7 +33593,7 @@
       <c r="N49" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O49" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33620,7 +33652,7 @@
       <c r="N50" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O50" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33679,7 +33711,7 @@
       <c r="N51" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O51" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33738,7 +33770,7 @@
       <c r="N52" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O52" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -33800,7 +33832,7 @@
       <c r="N53" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O53" t="s">
         <v>154</v>
@@ -33858,7 +33890,7 @@
       <c r="N54" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O54" t="str">
         <f ca="1">IF(N54&lt;0,"ATRASADO",IF(N54&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33917,7 +33949,7 @@
       <c r="N55" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O55" t="str">
         <f ca="1">IF(N55&lt;0,"ATRASADO",IF(N55&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33976,7 +34008,7 @@
       <c r="N56" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O56" t="str">
         <f ca="1">IF(N56&lt;0,"ATRASADO",IF(N56&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34035,7 +34067,7 @@
       <c r="N57" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O57" t="str">
         <f t="shared" ref="O57:O59" ca="1" si="7">IF(N57&lt;0,"ATRASADO",IF(N57&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34094,7 +34126,7 @@
       <c r="N58" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O58" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -34153,7 +34185,7 @@
       <c r="N59" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O59" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -34209,7 +34241,7 @@
       <c r="N60" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O60" t="str">
         <f t="shared" ref="O60:O62" ca="1" si="8">IF(N60&lt;0,"ATRASADO",IF(N60&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34265,7 +34297,7 @@
       <c r="N61" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O61" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -34321,7 +34353,7 @@
       <c r="N62" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O62" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -34380,7 +34412,7 @@
       <c r="N63" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O63" t="str">
         <f ca="1">IF(N63&lt;0,"ATRASADO",IF(N63&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34439,7 +34471,7 @@
       <c r="N64" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O64" t="str">
         <f t="shared" ref="O64:O76" ca="1" si="9">IF(N64&lt;0,"ATRASADO",IF(N64&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34498,7 +34530,7 @@
       <c r="N65" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O65" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34557,7 +34589,7 @@
       <c r="N66" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O66" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34616,7 +34648,7 @@
       <c r="N67" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O67" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34675,7 +34707,7 @@
       <c r="N68" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O68" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34734,7 +34766,7 @@
       <c r="N69" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O69" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34793,7 +34825,7 @@
       <c r="N70" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O70" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34852,7 +34884,7 @@
       <c r="N71" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O71" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34911,7 +34943,7 @@
       <c r="N72" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O72" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -34970,7 +35002,7 @@
       <c r="N73" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O73" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -35029,7 +35061,7 @@
       <c r="N74" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O74" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -35088,7 +35120,7 @@
       <c r="N75" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O75" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -35147,7 +35179,7 @@
       <c r="N76" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O76" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -35206,7 +35238,7 @@
       <c r="N77" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O77" t="str">
         <f ca="1">IF(N77&lt;0,"ATRASADO",IF(N77&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35265,7 +35297,7 @@
       <c r="N78" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O78" t="str">
         <f t="shared" ref="O78:O80" ca="1" si="10">IF(N78&lt;0,"ATRASADO",IF(N78&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35324,7 +35356,7 @@
       <c r="N79" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O79" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -35383,7 +35415,7 @@
       <c r="N80" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O80" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -35442,7 +35474,7 @@
       <c r="N81" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O81" t="str">
         <f t="shared" ref="O81:O88" ca="1" si="11">IF(N81&lt;0,"ATRASADO",IF(N81&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35501,7 +35533,7 @@
       <c r="N82" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O82" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -35560,7 +35592,7 @@
       <c r="N83" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O83" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -35619,7 +35651,7 @@
       <c r="N84" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O84" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -35678,7 +35710,7 @@
       <c r="N85" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O85" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -35737,7 +35769,7 @@
       <c r="N86" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O86" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -35796,7 +35828,7 @@
       <c r="N87" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O87" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -35855,7 +35887,7 @@
       <c r="N88" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O88" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -35917,7 +35949,7 @@
       <c r="N89" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O89" t="s">
         <v>154</v>
@@ -35955,7 +35987,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A7CF3D-4567-423F-9856-686FB94A96D5}">
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:AF18"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="53"/>
@@ -35969,19 +36001,18 @@
     <col min="10" max="10" width="10.140625" style="53" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.28515625" style="53" customWidth="1"/>
     <col min="12" max="12" width="10.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="9.140625" style="53"/>
-    <col min="16" max="16" width="56.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="18.5703125" style="53" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13" style="53" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13" style="53" customWidth="1"/>
-    <col min="23" max="23" width="19.28515625" style="53" customWidth="1"/>
-    <col min="24" max="24" width="25.42578125" style="53" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="53"/>
+    <col min="13" max="24" width="9.140625" style="53"/>
+    <col min="25" max="26" width="18.5703125" style="53" customWidth="1"/>
+    <col min="27" max="27" width="9.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13" style="53" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="53" customWidth="1"/>
+    <col min="31" max="31" width="19.28515625" style="53" customWidth="1"/>
+    <col min="32" max="32" width="25.42578125" style="53" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
         <v>7</v>
       </c>
@@ -35992,7 +36023,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="52" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E1" s="51" t="s">
         <v>6</v>
@@ -36001,22 +36032,22 @@
         <v>2</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I1" s="51" t="s">
         <v>226</v>
       </c>
       <c r="J1" s="52" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="K1" s="52" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L1" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="M1" s="52" t="s">
         <v>21</v>
@@ -36028,34 +36059,58 @@
         <v>84</v>
       </c>
       <c r="P1" s="52" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q1" s="52" t="s">
+        <v>284</v>
+      </c>
+      <c r="R1" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="S1" s="52" t="s">
+        <v>286</v>
+      </c>
+      <c r="T1" s="52" t="s">
+        <v>287</v>
+      </c>
+      <c r="U1" s="52" t="s">
+        <v>288</v>
+      </c>
+      <c r="V1" s="52" t="s">
+        <v>289</v>
+      </c>
+      <c r="W1" s="52" t="s">
+        <v>290</v>
+      </c>
+      <c r="X1" s="52" t="s">
+        <v>291</v>
+      </c>
+      <c r="Y1" s="52" t="s">
+        <v>228</v>
+      </c>
+      <c r="Z1" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="AA1" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="AB1" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="Q1" s="52" t="s">
-        <v>228</v>
-      </c>
-      <c r="R1" s="52" t="s">
-        <v>251</v>
-      </c>
-      <c r="S1" s="52" t="s">
-        <v>262</v>
-      </c>
-      <c r="T1" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="U1" s="52" t="s">
+      <c r="AC1" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD1" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="AE1" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="V1" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="W1" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="X1" s="52" t="s">
+      <c r="AF1" s="52" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="54">
         <v>1015</v>
       </c>
@@ -36063,13 +36118,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="54" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D2" s="54">
         <v>6635</v>
       </c>
       <c r="E2" s="54" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F2" s="54">
         <v>1</v>
@@ -36083,11 +36138,11 @@
       <c r="I2" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="J2" s="56">
+      <c r="J2" s="55">
         <v>46233</v>
       </c>
       <c r="K2" s="54"/>
-      <c r="L2" s="56"/>
+      <c r="L2" s="55"/>
       <c r="M2" s="54"/>
       <c r="N2" s="54" t="s">
         <v>69</v>
@@ -36095,33 +36150,57 @@
       <c r="O2" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="P2" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q2" s="54" t="s">
-        <v>241</v>
-      </c>
-      <c r="R2" s="54">
+      <c r="P2" s="56" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q2" s="56" t="s">
+        <v>275</v>
+      </c>
+      <c r="R2" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="S2" s="56" t="s">
+        <v>278</v>
+      </c>
+      <c r="T2" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="U2" s="54" t="s">
+        <v>280</v>
+      </c>
+      <c r="V2" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="W2" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="X2" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y2" s="54" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z2" s="54">
         <v>2</v>
       </c>
-      <c r="S2" s="54" t="s">
+      <c r="AA2" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="T2" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U2" s="54" t="s">
+      <c r="AB2" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC2" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V2" s="54"/>
-      <c r="W2" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="X2" s="54" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="54" t="s">
+        <v>258</v>
+      </c>
+      <c r="AF2" s="54" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="54">
         <v>1027</v>
       </c>
@@ -36135,19 +36214,19 @@
         <v>77</v>
       </c>
       <c r="E3" s="54" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F3" s="54">
         <v>1</v>
       </c>
       <c r="G3" s="54" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H3" s="54" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I3" s="54" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J3" s="54" t="s">
         <v>77</v>
@@ -36155,7 +36234,7 @@
       <c r="K3" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L3" s="56">
+      <c r="L3" s="55">
         <v>46410</v>
       </c>
       <c r="M3" s="54"/>
@@ -36166,32 +36245,44 @@
         <v>72</v>
       </c>
       <c r="P3" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q3" s="54" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="R3" s="54" t="s">
-        <v>252</v>
-      </c>
-      <c r="S3" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T3" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="U3" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="54"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="54"/>
+      <c r="X3" s="54"/>
+      <c r="Y3" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z3" s="54" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA3" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB3" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC3" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V3" s="56">
+      <c r="AD3" s="55">
         <v>46410</v>
       </c>
-      <c r="W3" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X3" s="54"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE3" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF3" s="54"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="54">
         <v>1027</v>
       </c>
@@ -36205,19 +36296,19 @@
         <v>77</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F4" s="54">
         <v>1</v>
       </c>
       <c r="G4" s="54" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H4" s="54" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I4" s="54" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J4" s="54" t="s">
         <v>77</v>
@@ -36225,7 +36316,7 @@
       <c r="K4" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="56">
+      <c r="L4" s="55">
         <v>46414</v>
       </c>
       <c r="M4" s="54"/>
@@ -36236,32 +36327,44 @@
         <v>72</v>
       </c>
       <c r="P4" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q4" s="54" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="R4" s="54" t="s">
-        <v>253</v>
-      </c>
-      <c r="S4" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T4" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="U4" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S4" s="54"/>
+      <c r="T4" s="54"/>
+      <c r="U4" s="54"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="54"/>
+      <c r="X4" s="54"/>
+      <c r="Y4" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z4" s="54" t="s">
+        <v>249</v>
+      </c>
+      <c r="AA4" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB4" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC4" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V4" s="56">
+      <c r="AD4" s="55">
         <v>46414</v>
       </c>
-      <c r="W4" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X4" s="54"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE4" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF4" s="54"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="54">
         <v>1027</v>
       </c>
@@ -36275,27 +36378,27 @@
         <v>77</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F5" s="54">
         <v>1</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H5" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="I5" s="54" t="s">
-        <v>250</v>
-      </c>
       <c r="J5" s="54" t="s">
         <v>77</v>
       </c>
       <c r="K5" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L5" s="56">
+      <c r="L5" s="55">
         <v>46416</v>
       </c>
       <c r="M5" s="54"/>
@@ -36306,32 +36409,44 @@
         <v>72</v>
       </c>
       <c r="P5" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q5" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="R5" s="54">
+        <v>273</v>
+      </c>
+      <c r="R5" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S5" s="54"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="54"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="54"/>
+      <c r="X5" s="54"/>
+      <c r="Y5" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z5" s="54">
         <v>9</v>
       </c>
-      <c r="S5" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T5" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="U5" s="54" t="s">
+      <c r="AA5" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB5" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC5" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V5" s="56">
+      <c r="AD5" s="55">
         <v>46416</v>
       </c>
-      <c r="W5" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X5" s="54"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE5" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF5" s="54"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="54">
         <v>1027</v>
       </c>
@@ -36345,7 +36460,7 @@
         <v>77</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F6" s="54">
         <v>1</v>
@@ -36354,18 +36469,18 @@
         <v>1700</v>
       </c>
       <c r="H6" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="I6" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="I6" s="54" t="s">
-        <v>250</v>
-      </c>
       <c r="J6" s="54" t="s">
         <v>77</v>
       </c>
       <c r="K6" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="55">
         <v>46417</v>
       </c>
       <c r="M6" s="54"/>
@@ -36376,32 +36491,44 @@
         <v>72</v>
       </c>
       <c r="P6" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q6" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="R6" s="54">
+        <v>273</v>
+      </c>
+      <c r="R6" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S6" s="54"/>
+      <c r="T6" s="54"/>
+      <c r="U6" s="54"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="54"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z6" s="54">
         <v>17</v>
       </c>
-      <c r="S6" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T6" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="U6" s="54" t="s">
+      <c r="AA6" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB6" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC6" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V6" s="56">
+      <c r="AD6" s="55">
         <v>46417</v>
       </c>
-      <c r="W6" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X6" s="54"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE6" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF6" s="54"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="54">
         <v>1027</v>
       </c>
@@ -36415,7 +36542,7 @@
         <v>77</v>
       </c>
       <c r="E7" s="54" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F7" s="54">
         <v>1</v>
@@ -36424,10 +36551,10 @@
         <v>1700</v>
       </c>
       <c r="H7" s="54" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I7" s="54" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J7" s="54" t="s">
         <v>77</v>
@@ -36435,7 +36562,7 @@
       <c r="K7" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L7" s="56">
+      <c r="L7" s="55">
         <v>46420</v>
       </c>
       <c r="M7" s="54"/>
@@ -36446,32 +36573,44 @@
         <v>72</v>
       </c>
       <c r="P7" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q7" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="R7" s="54">
+        <v>273</v>
+      </c>
+      <c r="R7" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S7" s="54"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z7" s="54">
         <v>7</v>
       </c>
-      <c r="S7" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T7" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="U7" s="54" t="s">
+      <c r="AA7" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB7" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC7" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V7" s="56">
+      <c r="AD7" s="55">
         <v>46420</v>
       </c>
-      <c r="W7" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X7" s="54"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE7" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF7" s="54"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="54">
         <v>1027</v>
       </c>
@@ -36485,7 +36624,7 @@
         <v>6820</v>
       </c>
       <c r="E8" s="54" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F8" s="54">
         <v>1</v>
@@ -36494,16 +36633,16 @@
         <v>1700</v>
       </c>
       <c r="H8" s="54" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I8" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="J8" s="56">
+      <c r="J8" s="55">
         <v>46233</v>
       </c>
       <c r="K8" s="54"/>
-      <c r="L8" s="56">
+      <c r="L8" s="55">
         <v>46408</v>
       </c>
       <c r="M8" s="54"/>
@@ -36514,32 +36653,48 @@
         <v>72</v>
       </c>
       <c r="P8" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q8" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="R8" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S8" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="T8" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="54" t="s">
         <v>234</v>
       </c>
-      <c r="Q8" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="R8" s="54">
+      <c r="Z8" s="54">
         <v>2</v>
       </c>
-      <c r="S8" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T8" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U8" s="54" t="s">
+      <c r="AA8" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB8" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC8" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V8" s="56">
+      <c r="AD8" s="55">
         <v>46408</v>
       </c>
-      <c r="W8" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X8" s="54"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE8" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF8" s="54"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="54">
         <v>1027</v>
       </c>
@@ -36553,7 +36708,7 @@
         <v>77</v>
       </c>
       <c r="E9" s="54" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F9" s="54">
         <v>1</v>
@@ -36562,10 +36717,10 @@
         <v>1700</v>
       </c>
       <c r="H9" s="54" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I9" s="54" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J9" s="54" t="s">
         <v>77</v>
@@ -36573,7 +36728,7 @@
       <c r="K9" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L9" s="56">
+      <c r="L9" s="55">
         <v>46421</v>
       </c>
       <c r="M9" s="54"/>
@@ -36584,32 +36739,44 @@
         <v>72</v>
       </c>
       <c r="P9" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q9" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="R9" s="54">
+        <v>273</v>
+      </c>
+      <c r="R9" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z9" s="54">
         <v>3</v>
       </c>
-      <c r="S9" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T9" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U9" s="54" t="s">
+      <c r="AA9" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB9" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC9" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V9" s="56">
+      <c r="AD9" s="55">
         <v>46421</v>
       </c>
-      <c r="W9" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X9" s="54"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE9" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF9" s="54"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="54">
         <v>1027</v>
       </c>
@@ -36623,7 +36790,7 @@
         <v>6821</v>
       </c>
       <c r="E10" s="54" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F10" s="54">
         <v>1</v>
@@ -36632,16 +36799,16 @@
         <v>1700</v>
       </c>
       <c r="H10" s="54" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I10" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="J10" s="56">
+      <c r="J10" s="55">
         <v>46233</v>
       </c>
       <c r="K10" s="54"/>
-      <c r="L10" s="56">
+      <c r="L10" s="55">
         <v>46403</v>
       </c>
       <c r="M10" s="54"/>
@@ -36652,32 +36819,48 @@
         <v>72</v>
       </c>
       <c r="P10" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q10" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="R10" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S10" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="T10" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54" t="s">
         <v>234</v>
       </c>
-      <c r="Q10" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="R10" s="54">
+      <c r="Z10" s="54">
         <v>10</v>
       </c>
-      <c r="S10" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T10" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U10" s="54" t="s">
+      <c r="AA10" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB10" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC10" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V10" s="56">
+      <c r="AD10" s="55">
         <v>46403</v>
       </c>
-      <c r="W10" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X10" s="54"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE10" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF10" s="54"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="54">
         <v>1027</v>
       </c>
@@ -36691,7 +36874,7 @@
         <v>77</v>
       </c>
       <c r="E11" s="54" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F11" s="54">
         <v>1</v>
@@ -36700,10 +36883,10 @@
         <v>1700</v>
       </c>
       <c r="H11" s="54" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I11" s="54" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J11" s="54" t="s">
         <v>77</v>
@@ -36711,7 +36894,7 @@
       <c r="K11" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L11" s="56">
+      <c r="L11" s="55">
         <v>46423</v>
       </c>
       <c r="M11" s="54"/>
@@ -36722,32 +36905,44 @@
         <v>72</v>
       </c>
       <c r="P11" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q11" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="R11" s="54">
+        <v>273</v>
+      </c>
+      <c r="R11" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z11" s="54">
         <v>20</v>
       </c>
-      <c r="S11" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T11" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U11" s="54" t="s">
+      <c r="AA11" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB11" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC11" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V11" s="56">
+      <c r="AD11" s="55">
         <v>46423</v>
       </c>
-      <c r="W11" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X11" s="54"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE11" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF11" s="54"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="54">
         <v>1027</v>
       </c>
@@ -36761,7 +36956,7 @@
         <v>6822</v>
       </c>
       <c r="E12" s="54" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F12" s="54">
         <v>1</v>
@@ -36770,16 +36965,16 @@
         <v>1700</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I12" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="J12" s="56">
+      <c r="J12" s="55">
         <v>46233</v>
       </c>
       <c r="K12" s="54"/>
-      <c r="L12" s="56">
+      <c r="L12" s="55">
         <v>46406</v>
       </c>
       <c r="M12" s="54"/>
@@ -36789,33 +36984,57 @@
       <c r="O12" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="P12" s="55" t="s">
-        <v>240</v>
+      <c r="P12" s="54" t="s">
+        <v>273</v>
       </c>
       <c r="Q12" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="R12" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="S12" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="T12" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="U12" s="54" t="s">
+        <v>280</v>
+      </c>
+      <c r="V12" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="W12" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="X12" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y12" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="R12" s="54">
+      <c r="Z12" s="54">
         <v>18</v>
       </c>
-      <c r="S12" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T12" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U12" s="54" t="s">
+      <c r="AA12" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB12" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC12" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V12" s="56">
+      <c r="AD12" s="55">
         <v>46406</v>
       </c>
-      <c r="W12" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X12" s="54"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE12" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF12" s="54"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="54">
         <v>1027</v>
       </c>
@@ -36829,7 +37048,7 @@
         <v>77</v>
       </c>
       <c r="E13" s="54" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F13" s="54">
         <v>1</v>
@@ -36838,10 +37057,10 @@
         <v>1700</v>
       </c>
       <c r="H13" s="54" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I13" s="54" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J13" s="54" t="s">
         <v>77</v>
@@ -36849,7 +37068,7 @@
       <c r="K13" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L13" s="56">
+      <c r="L13" s="55">
         <v>46424</v>
       </c>
       <c r="M13" s="54"/>
@@ -36860,32 +37079,44 @@
         <v>72</v>
       </c>
       <c r="P13" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q13" s="54" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="R13" s="54" t="s">
-        <v>255</v>
-      </c>
-      <c r="S13" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T13" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U13" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S13" s="54"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="54"/>
+      <c r="V13" s="54"/>
+      <c r="W13" s="54"/>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z13" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA13" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB13" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC13" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V13" s="56">
+      <c r="AD13" s="55">
         <v>46424</v>
       </c>
-      <c r="W13" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X13" s="54"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE13" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF13" s="54"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="54">
         <v>1027</v>
       </c>
@@ -36899,27 +37130,27 @@
         <v>6010</v>
       </c>
       <c r="E14" s="54" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F14" s="54">
         <v>1</v>
       </c>
       <c r="G14" s="54" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="I14" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="J14" s="56">
+      <c r="J14" s="55">
         <v>46233</v>
       </c>
-      <c r="K14" s="56">
+      <c r="K14" s="55">
         <v>46198</v>
       </c>
-      <c r="L14" s="56">
+      <c r="L14" s="55">
         <v>46426</v>
       </c>
       <c r="M14" s="54"/>
@@ -36929,33 +37160,57 @@
       <c r="O14" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="P14" s="55" t="s">
-        <v>240</v>
+      <c r="P14" s="54" t="s">
+        <v>273</v>
       </c>
       <c r="Q14" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="R14" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="S14" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="T14" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="U14" s="54" t="s">
+        <v>280</v>
+      </c>
+      <c r="V14" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="W14" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="X14" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y14" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="R14" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="S14" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T14" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U14" s="54" t="s">
+      <c r="Z14" s="54" t="s">
+        <v>238</v>
+      </c>
+      <c r="AA14" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB14" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC14" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V14" s="56">
+      <c r="AD14" s="55">
         <v>46426</v>
       </c>
-      <c r="W14" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X14" s="54"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE14" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF14" s="54"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="54">
         <v>1027</v>
       </c>
@@ -36969,7 +37224,7 @@
         <v>77</v>
       </c>
       <c r="E15" s="54" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F15" s="54">
         <v>1</v>
@@ -36978,18 +37233,18 @@
         <v>1700</v>
       </c>
       <c r="H15" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="I15" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="I15" s="54" t="s">
-        <v>250</v>
-      </c>
       <c r="J15" s="54" t="s">
         <v>77</v>
       </c>
       <c r="K15" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L15" s="56">
+      <c r="L15" s="55">
         <v>46427</v>
       </c>
       <c r="M15" s="54"/>
@@ -37000,32 +37255,44 @@
         <v>72</v>
       </c>
       <c r="P15" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q15" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="R15" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S15" s="54"/>
+      <c r="T15" s="54"/>
+      <c r="U15" s="54"/>
+      <c r="V15" s="54"/>
+      <c r="W15" s="54"/>
+      <c r="X15" s="54"/>
+      <c r="Y15" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="R15" s="54" t="s">
-        <v>256</v>
-      </c>
-      <c r="S15" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T15" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U15" s="54" t="s">
+      <c r="Z15" s="54" t="s">
+        <v>252</v>
+      </c>
+      <c r="AA15" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB15" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC15" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V15" s="56">
+      <c r="AD15" s="55">
         <v>46427</v>
       </c>
-      <c r="W15" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X15" s="54"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE15" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF15" s="54"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="54">
         <v>1027</v>
       </c>
@@ -37039,7 +37306,7 @@
         <v>6824</v>
       </c>
       <c r="E16" s="54" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F16" s="54">
         <v>1</v>
@@ -37048,16 +37315,16 @@
         <v>1700</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="I16" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="J16" s="56">
+      <c r="J16" s="55">
         <v>46233</v>
       </c>
       <c r="K16" s="54"/>
-      <c r="L16" s="56">
+      <c r="L16" s="55">
         <v>46428</v>
       </c>
       <c r="M16" s="54"/>
@@ -37067,33 +37334,57 @@
       <c r="O16" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="P16" s="55" t="s">
-        <v>240</v>
+      <c r="P16" s="54" t="s">
+        <v>273</v>
       </c>
       <c r="Q16" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="R16" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="S16" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="T16" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="U16" s="54" t="s">
+        <v>280</v>
+      </c>
+      <c r="V16" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="W16" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="X16" s="54" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y16" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="R16" s="54">
+      <c r="Z16" s="54">
         <v>14</v>
       </c>
-      <c r="S16" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T16" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U16" s="54" t="s">
+      <c r="AA16" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB16" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC16" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V16" s="56">
+      <c r="AD16" s="55">
         <v>46428</v>
       </c>
-      <c r="W16" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X16" s="54"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE16" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF16" s="54"/>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="54">
         <v>1027</v>
       </c>
@@ -37107,7 +37398,7 @@
         <v>77</v>
       </c>
       <c r="E17" s="54" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F17" s="54">
         <v>1</v>
@@ -37116,10 +37407,10 @@
         <v>1700</v>
       </c>
       <c r="H17" s="54" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I17" s="54" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J17" s="54" t="s">
         <v>77</v>
@@ -37127,7 +37418,7 @@
       <c r="K17" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L17" s="56">
+      <c r="L17" s="55">
         <v>46430</v>
       </c>
       <c r="M17" s="54"/>
@@ -37138,32 +37429,44 @@
         <v>72</v>
       </c>
       <c r="P17" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q17" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="R17" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="54"/>
+      <c r="W17" s="54"/>
+      <c r="X17" s="54"/>
+      <c r="Y17" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="R17" s="54">
+      <c r="Z17" s="54">
         <v>15</v>
       </c>
-      <c r="S17" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T17" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U17" s="54" t="s">
+      <c r="AA17" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB17" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC17" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V17" s="56">
+      <c r="AD17" s="55">
         <v>46430</v>
       </c>
-      <c r="W17" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X17" s="54"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="AE17" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF17" s="54"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="54">
         <v>1027</v>
       </c>
@@ -37177,7 +37480,7 @@
         <v>77</v>
       </c>
       <c r="E18" s="54" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F18" s="54">
         <v>1</v>
@@ -37186,10 +37489,10 @@
         <v>1700</v>
       </c>
       <c r="H18" s="54" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I18" s="54" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J18" s="54" t="s">
         <v>77</v>
@@ -37197,7 +37500,7 @@
       <c r="K18" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="L18" s="56">
+      <c r="L18" s="55">
         <v>46431</v>
       </c>
       <c r="M18" s="54"/>
@@ -37208,64 +37511,45 @@
         <v>72</v>
       </c>
       <c r="P18" s="54" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="Q18" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="R18" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
+      <c r="U18" s="54"/>
+      <c r="V18" s="54"/>
+      <c r="W18" s="54"/>
+      <c r="X18" s="54"/>
+      <c r="Y18" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="R18" s="54">
+      <c r="Z18" s="54">
         <v>16</v>
       </c>
-      <c r="S18" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="T18" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="U18" s="54" t="s">
+      <c r="AA18" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB18" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="AC18" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="V18" s="56">
+      <c r="AD18" s="55">
         <v>46431</v>
       </c>
-      <c r="W18" s="54" t="s">
-        <v>236</v>
-      </c>
-      <c r="X18" s="54"/>
+      <c r="AE18" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="AF18" s="54"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="P2 P12 P16">
-    <cfRule type="expression" dxfId="7" priority="11">
-      <formula>$P2="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
-    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",P2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="10" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",P2)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="12">
-      <formula>#REF!="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P12 P14 P16">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",P12)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",P12)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="4">
-      <formula>#REF!="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P14">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>$P14="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6382DAA2-8EF0-4FC8-965A-77ED67BADE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2283669-2237-4CB1-9151-A1FB1DD40835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5478" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6298" uniqueCount="376">
   <si>
     <t>O.S.</t>
   </si>
@@ -1020,6 +1020,204 @@
   <si>
     <t>RP</t>
   </si>
+  <si>
+    <t>Raizen Barra</t>
+  </si>
+  <si>
+    <t>CONCLUÍDO</t>
+  </si>
+  <si>
+    <t>AG. EIXO</t>
+  </si>
+  <si>
+    <t>Raizen Bonfim</t>
+  </si>
+  <si>
+    <t>Camisa</t>
+  </si>
+  <si>
+    <t>78"</t>
+  </si>
+  <si>
+    <t>IPA41</t>
+  </si>
+  <si>
+    <t>PSO121</t>
+  </si>
+  <si>
+    <t>SH53</t>
+  </si>
+  <si>
+    <t>Raizen Ipaussu</t>
+  </si>
+  <si>
+    <t>Raizen Jatai</t>
+  </si>
+  <si>
+    <t>90"</t>
+  </si>
+  <si>
+    <t>3G</t>
+  </si>
+  <si>
+    <t>Raizen Junqueira</t>
+  </si>
+  <si>
+    <t>111F</t>
+  </si>
+  <si>
+    <t>45S</t>
+  </si>
+  <si>
+    <t>AG. Ø CLIENTE</t>
+  </si>
+  <si>
+    <t>AG. INF. CLIENTE</t>
+  </si>
+  <si>
+    <t>Raizen Mundial</t>
+  </si>
+  <si>
+    <t>54"</t>
+  </si>
+  <si>
+    <t>66"</t>
+  </si>
+  <si>
+    <t>31A</t>
+  </si>
+  <si>
+    <t>Raizen Paralcool</t>
+  </si>
+  <si>
+    <t>Raizen S. Francisco</t>
+  </si>
+  <si>
+    <t>Raizen Serra</t>
+  </si>
+  <si>
+    <t>Raizen Sta Candida</t>
+  </si>
+  <si>
+    <t>Raizen Taruma</t>
+  </si>
+  <si>
+    <t>Raizen Univalem</t>
+  </si>
+  <si>
+    <t>Raizen Vale</t>
+  </si>
+  <si>
+    <t>Raizen Zanin</t>
+  </si>
+  <si>
+    <t>2096/3</t>
+  </si>
+  <si>
+    <t>2096/1</t>
+  </si>
+  <si>
+    <t>2096/2</t>
+  </si>
+  <si>
+    <t>967/31</t>
+  </si>
+  <si>
+    <t>2087/2</t>
+  </si>
+  <si>
+    <t>2087/1</t>
+  </si>
+  <si>
+    <t>2082/3</t>
+  </si>
+  <si>
+    <t>2082/1</t>
+  </si>
+  <si>
+    <t>2082/2</t>
+  </si>
+  <si>
+    <t>2081/2</t>
+  </si>
+  <si>
+    <t>2081/1</t>
+  </si>
+  <si>
+    <t>2079/1</t>
+  </si>
+  <si>
+    <t>2079/2</t>
+  </si>
+  <si>
+    <t>2083/8</t>
+  </si>
+  <si>
+    <t>2083/3</t>
+  </si>
+  <si>
+    <t>2083/9</t>
+  </si>
+  <si>
+    <t>2083/4</t>
+  </si>
+  <si>
+    <t>2083/7</t>
+  </si>
+  <si>
+    <t>2083/6</t>
+  </si>
+  <si>
+    <t>2083/2</t>
+  </si>
+  <si>
+    <t>2083/5</t>
+  </si>
+  <si>
+    <t>1025/2</t>
+  </si>
+  <si>
+    <t>2083/1</t>
+  </si>
+  <si>
+    <t>Camisa  (Embuch)</t>
+  </si>
+  <si>
+    <t>60"</t>
+  </si>
+  <si>
+    <t>72"</t>
+  </si>
+  <si>
+    <t>P112</t>
+  </si>
+  <si>
+    <t>s/e</t>
+  </si>
+  <si>
+    <t>47D</t>
+  </si>
+  <si>
+    <t>DEP5</t>
+  </si>
+  <si>
+    <t>11PF</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>34D</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
 </sst>
 </file>
 
@@ -1029,7 +1227,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1113,8 +1311,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1145,8 +1355,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1198,12 +1414,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1355,12 +1586,577 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Vírgula 2" xfId="1" xr:uid="{8785E80A-1CD4-4609-8517-D88B418F2B05}"/>
   </cellStyles>
-  <dxfs count="174">
+  <dxfs count="247">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1398,6 +2194,660 @@
         <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3692,667 +5142,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4367,226 +5156,233 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="144" dataDxfId="143">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="246" dataDxfId="245">
   <autoFilter ref="A1:AI114" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}">
-    <filterColumn colId="4">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Aura Brazil"/>
+        <filter val="2205"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="142"/>
-    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="141"/>
-    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="140"/>
-    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="139"/>
-    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="138"/>
-    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="137"/>
-    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="136"/>
-    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="135"/>
-    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="134"/>
-    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="133"/>
-    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="132">
+    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="244"/>
+    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="243"/>
+    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="242"/>
+    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="241"/>
+    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="240"/>
+    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="239"/>
+    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="238"/>
+    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="237"/>
+    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="236"/>
+    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="235"/>
+    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="234">
       <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
 Fundido]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="131"/>
-    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="130"/>
-    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="129"/>
-    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="128">
+    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="233"/>
+    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="232"/>
+    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="231"/>
+    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="230">
       <calculatedColumnFormula>Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="127">
+    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="229">
       <calculatedColumnFormula>IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="126">
+    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="228">
       <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
 Entrega]],1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="125"/>
-    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="124"/>
-    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="123"/>
-    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="122"/>
-    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="121"/>
-    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="120"/>
-    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="119"/>
-    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="118"/>
-    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="117"/>
-    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="116"/>
-    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="115"/>
-    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="114">
+    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="227"/>
+    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="226"/>
+    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="225"/>
+    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="224"/>
+    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="223"/>
+    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="222"/>
+    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="221"/>
+    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="220"/>
+    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="219"/>
+    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="218"/>
+    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="217"/>
+    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="216">
       <calculatedColumnFormula>IF(L2="","AG. FUNDIDO",IF(U2="AG","AG. USINAGEM","EM USINAGEM"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="113"/>
-    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="112"/>
-    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="111"/>
-    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="110"/>
-    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="109"/>
-    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="108"/>
+    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="215"/>
+    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="214"/>
+    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="213"/>
+    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="212"/>
+    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="211"/>
+    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="210"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V143" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V143" totalsRowShown="0" headerRowDxfId="209" dataDxfId="208">
   <autoFilter ref="A1:V143" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="101"/>
-    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="100"/>
-    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="99"/>
-    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="98"/>
-    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="97"/>
-    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="96"/>
-    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="95">
+    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="207"/>
+    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="206"/>
+    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="205"/>
+    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="204"/>
+    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="203"/>
+    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="202"/>
+    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="201"/>
+    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="200"/>
+    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="199"/>
+    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="198"/>
+    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="197">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="94"/>
-    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="93"/>
-    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="92"/>
-    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="91"/>
-    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="90"/>
-    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="89">
+    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="196"/>
+    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="195"/>
+    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="194"/>
+    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="193"/>
+    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="192"/>
+    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="191">
       <calculatedColumnFormula>Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="88">
+    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="190">
       <calculatedColumnFormula>IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="87">
+    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="189">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="86"/>
-    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="85"/>
-    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="84"/>
+    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="188"/>
+    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="187"/>
+    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="186"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E9C3BD9-7BAA-49FB-9F98-CFD415149194}" name="Tabela13" displayName="Tabela13" ref="A1:Z39" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E9C3BD9-7BAA-49FB-9F98-CFD415149194}" name="Tabela13" displayName="Tabela13" ref="A1:Z39" totalsRowShown="0" headerRowDxfId="185" dataDxfId="184">
   <autoFilter ref="A1:Z39" xr:uid="{2AC5416C-4E1B-4478-8A2A-B698870CAB96}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{9A983B4E-3365-4153-9B40-D7FE26E8B98F}" name="PV " dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{4F16CD54-AAD4-4149-8D48-CC3FFEA93AA5}" name="Item" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{27DB1DBC-B9DA-4067-9696-8CA5ACAAA450}" name="OS" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{02C5E283-8ABF-44F8-B3B8-C3F186B4DF63}" name="Item2" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{B1051CBE-EA72-4A43-8721-8756F3E2C9C9}" name="Cliente" dataDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{D81DBB81-327B-4EA3-89A3-229D33F3C14C}" name="Cod." dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{05B3DC4D-BFB9-401F-A18F-0D1B8527380B}" name="Seq." dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{9EBF401A-1F29-4CB3-BFA3-F2B326242AB0}" name="Descrição" dataDxfId="74"/>
-    <tableColumn id="14" xr3:uid="{85D3397C-7F95-49C7-BFFB-35012CA3B716}" name="Qtd." dataDxfId="73"/>
-    <tableColumn id="9" xr3:uid="{0D04583C-577A-446B-9773-A173C5C1C166}" name="Data Prev._x000a_Fundido" dataDxfId="72"/>
-    <tableColumn id="10" xr3:uid="{935D3899-0C12-4408-89DF-490A507F79BA}" name="Data Real_x000a_Fundido" dataDxfId="71"/>
-    <tableColumn id="11" xr3:uid="{0F06941F-293B-4C15-9764-BB3495C5D3BD}" name="Data Prev._x000a_Entrega" dataDxfId="70"/>
-    <tableColumn id="12" xr3:uid="{92FF2511-5498-45BF-9B68-94DBEA588C5A}" name="Data Real_x000a_Entrega" dataDxfId="69"/>
-    <tableColumn id="25" xr3:uid="{98545C7E-9674-485C-A07D-715E8945B00E}" name="Falta_x000a_Dias" dataDxfId="68">
+    <tableColumn id="1" xr3:uid="{9A983B4E-3365-4153-9B40-D7FE26E8B98F}" name="PV " dataDxfId="183"/>
+    <tableColumn id="2" xr3:uid="{4F16CD54-AAD4-4149-8D48-CC3FFEA93AA5}" name="Item" dataDxfId="182"/>
+    <tableColumn id="3" xr3:uid="{27DB1DBC-B9DA-4067-9696-8CA5ACAAA450}" name="OS" dataDxfId="181"/>
+    <tableColumn id="4" xr3:uid="{02C5E283-8ABF-44F8-B3B8-C3F186B4DF63}" name="Item2" dataDxfId="180"/>
+    <tableColumn id="5" xr3:uid="{B1051CBE-EA72-4A43-8721-8756F3E2C9C9}" name="Cliente" dataDxfId="179"/>
+    <tableColumn id="6" xr3:uid="{D81DBB81-327B-4EA3-89A3-229D33F3C14C}" name="Cod." dataDxfId="178"/>
+    <tableColumn id="7" xr3:uid="{05B3DC4D-BFB9-401F-A18F-0D1B8527380B}" name="Seq." dataDxfId="177"/>
+    <tableColumn id="8" xr3:uid="{9EBF401A-1F29-4CB3-BFA3-F2B326242AB0}" name="Descrição" dataDxfId="176"/>
+    <tableColumn id="14" xr3:uid="{85D3397C-7F95-49C7-BFFB-35012CA3B716}" name="Qtd." dataDxfId="175"/>
+    <tableColumn id="9" xr3:uid="{0D04583C-577A-446B-9773-A173C5C1C166}" name="Data Prev._x000a_Fundido" dataDxfId="174"/>
+    <tableColumn id="10" xr3:uid="{935D3899-0C12-4408-89DF-490A507F79BA}" name="Data Real_x000a_Fundido" dataDxfId="173"/>
+    <tableColumn id="11" xr3:uid="{0F06941F-293B-4C15-9764-BB3495C5D3BD}" name="Data Prev._x000a_Entrega" dataDxfId="172"/>
+    <tableColumn id="12" xr3:uid="{92FF2511-5498-45BF-9B68-94DBEA588C5A}" name="Data Real_x000a_Entrega" dataDxfId="171"/>
+    <tableColumn id="25" xr3:uid="{98545C7E-9674-485C-A07D-715E8945B00E}" name="Falta_x000a_Dias" dataDxfId="170">
       <calculatedColumnFormula>Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{4EB63243-AA79-4695-93C8-CEA977B11387}" name="Indicador" dataDxfId="67">
+    <tableColumn id="27" xr3:uid="{4EB63243-AA79-4695-93C8-CEA977B11387}" name="Indicador" dataDxfId="169">
       <calculatedColumnFormula>IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7AB992C1-F70E-4469-85BB-EBB7763B2038}" name="Condição" dataDxfId="66"/>
-    <tableColumn id="24" xr3:uid="{B5965349-4BC8-4DF7-9EB4-857B6D471E8A}" name="Desenho_x000a_Previsão" dataDxfId="65"/>
-    <tableColumn id="13" xr3:uid="{FD827F61-5F7F-4B65-8A60-B59D23455B46}" name="Des." dataDxfId="64"/>
-    <tableColumn id="16" xr3:uid="{3D186A5F-076F-4232-B21C-37E58E5373B2}" name="Desb." dataDxfId="63"/>
-    <tableColumn id="17" xr3:uid="{6EEDF11E-F341-4B3E-8CD2-5595785C3427}" name="T.T." dataDxfId="62"/>
-    <tableColumn id="18" xr3:uid="{A84EFCF4-218F-4B17-8F46-8D5412141429}" name="Us. Final" dataDxfId="61"/>
-    <tableColumn id="19" xr3:uid="{EBD50149-594D-440E-BFBB-E73ACAF7B6F8}" name="Fundo D." dataDxfId="60"/>
-    <tableColumn id="20" xr3:uid="{91BE30ED-20C1-4F30-9041-45A50CCA04F0}" name="Acabam." dataDxfId="59"/>
-    <tableColumn id="21" xr3:uid="{A1A12DF6-FC3D-4466-8284-DBD00DEAF994}" name="Liberação" dataDxfId="58"/>
-    <tableColumn id="22" xr3:uid="{436F202D-DCF4-4376-A550-2541153BD99F}" name="Status Usinagem" dataDxfId="57">
+    <tableColumn id="15" xr3:uid="{7AB992C1-F70E-4469-85BB-EBB7763B2038}" name="Condição" dataDxfId="168"/>
+    <tableColumn id="24" xr3:uid="{B5965349-4BC8-4DF7-9EB4-857B6D471E8A}" name="Desenho_x000a_Previsão" dataDxfId="167"/>
+    <tableColumn id="13" xr3:uid="{FD827F61-5F7F-4B65-8A60-B59D23455B46}" name="Des." dataDxfId="166"/>
+    <tableColumn id="16" xr3:uid="{3D186A5F-076F-4232-B21C-37E58E5373B2}" name="Desb." dataDxfId="165"/>
+    <tableColumn id="17" xr3:uid="{6EEDF11E-F341-4B3E-8CD2-5595785C3427}" name="T.T." dataDxfId="164"/>
+    <tableColumn id="18" xr3:uid="{A84EFCF4-218F-4B17-8F46-8D5412141429}" name="Us. Final" dataDxfId="163"/>
+    <tableColumn id="19" xr3:uid="{EBD50149-594D-440E-BFBB-E73ACAF7B6F8}" name="Fundo D." dataDxfId="162"/>
+    <tableColumn id="20" xr3:uid="{91BE30ED-20C1-4F30-9041-45A50CCA04F0}" name="Acabam." dataDxfId="161"/>
+    <tableColumn id="21" xr3:uid="{A1A12DF6-FC3D-4466-8284-DBD00DEAF994}" name="Liberação" dataDxfId="160"/>
+    <tableColumn id="22" xr3:uid="{436F202D-DCF4-4376-A550-2541153BD99F}" name="Status Usinagem" dataDxfId="159">
       <calculatedColumnFormula>IF(K2="","AG. FUNDIDO",IF(X2="OK","LIBERADA","EM USINAGEM"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{F71E5739-8B79-47B3-9A24-E2E4D1DD46E6}" name="Observação" dataDxfId="56"/>
+    <tableColumn id="23" xr3:uid="{F71E5739-8B79-47B3-9A24-E2E4D1DD46E6}" name="Observação" dataDxfId="158"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T89" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T89" totalsRowShown="0" headerRowDxfId="157" dataDxfId="156">
   <autoFilter ref="A1:T89" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{56D3DA8E-4CA8-4DC6-8208-BAB93CDE51C0}" name="PV" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{B14AE1B6-8C05-4725-BF42-3DBDB37AA4E3}" name="item" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{24FE1002-C88A-4623-8882-5F391ECAB319}" name="OS" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{4ED6249C-2003-4F3F-AE5A-67316434275E}" name="Item2" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{6CE5B2E1-F32C-4D32-93F0-A17C05267ADB}" name="Cliente" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{605F51C8-79D3-407B-8642-02F131952C62}" name="Qtd." dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{3AC59FFB-0DC5-477B-B780-880A1FD84811}" name="Peça" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{2EE377A7-B17C-442E-A107-012310DB953B}" name="Seq." dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{5366226E-7F3B-42E4-AC0C-86C659505CC8}" name="Descrição" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{B0D229C5-5F5A-4951-A0B4-FEA62AEFBB36}" name="Prazo_x000a_Fundido" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{8AE09F18-EB17-4537-8FBD-24671292144B}" name="Pz Fundido_x000a_Real" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{965E0234-7E4B-482D-8943-132C1520AD21}" name="Prazo_x000a_Entrega" dataDxfId="42"/>
-    <tableColumn id="13" xr3:uid="{D70BE32E-86AF-4C0F-893D-AC939E731683}" name="Pz Entrega_x000a_Real" dataDxfId="41"/>
-    <tableColumn id="15" xr3:uid="{2FE637E5-62E2-4AE9-AE5A-BC264DC93D4F}" name="Falta_x000a_Dias" dataDxfId="40">
+    <tableColumn id="1" xr3:uid="{56D3DA8E-4CA8-4DC6-8208-BAB93CDE51C0}" name="PV" dataDxfId="155"/>
+    <tableColumn id="2" xr3:uid="{B14AE1B6-8C05-4725-BF42-3DBDB37AA4E3}" name="item" dataDxfId="154"/>
+    <tableColumn id="3" xr3:uid="{24FE1002-C88A-4623-8882-5F391ECAB319}" name="OS" dataDxfId="153"/>
+    <tableColumn id="4" xr3:uid="{4ED6249C-2003-4F3F-AE5A-67316434275E}" name="Item2" dataDxfId="152"/>
+    <tableColumn id="5" xr3:uid="{6CE5B2E1-F32C-4D32-93F0-A17C05267ADB}" name="Cliente" dataDxfId="151"/>
+    <tableColumn id="6" xr3:uid="{605F51C8-79D3-407B-8642-02F131952C62}" name="Qtd." dataDxfId="150"/>
+    <tableColumn id="7" xr3:uid="{3AC59FFB-0DC5-477B-B780-880A1FD84811}" name="Peça" dataDxfId="149"/>
+    <tableColumn id="8" xr3:uid="{2EE377A7-B17C-442E-A107-012310DB953B}" name="Seq." dataDxfId="148"/>
+    <tableColumn id="9" xr3:uid="{5366226E-7F3B-42E4-AC0C-86C659505CC8}" name="Descrição" dataDxfId="147"/>
+    <tableColumn id="10" xr3:uid="{B0D229C5-5F5A-4951-A0B4-FEA62AEFBB36}" name="Prazo_x000a_Fundido" dataDxfId="146"/>
+    <tableColumn id="11" xr3:uid="{8AE09F18-EB17-4537-8FBD-24671292144B}" name="Pz Fundido_x000a_Real" dataDxfId="145"/>
+    <tableColumn id="12" xr3:uid="{965E0234-7E4B-482D-8943-132C1520AD21}" name="Prazo_x000a_Entrega" dataDxfId="144"/>
+    <tableColumn id="13" xr3:uid="{D70BE32E-86AF-4C0F-893D-AC939E731683}" name="Pz Entrega_x000a_Real" dataDxfId="143"/>
+    <tableColumn id="15" xr3:uid="{2FE637E5-62E2-4AE9-AE5A-BC264DC93D4F}" name="Falta_x000a_Dias" dataDxfId="142">
       <calculatedColumnFormula>Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{23AEF4D3-817F-4A15-AFBA-EC837E4BE1AE}" name="Indicador" dataDxfId="39">
+    <tableColumn id="14" xr3:uid="{23AEF4D3-817F-4A15-AFBA-EC837E4BE1AE}" name="Indicador" dataDxfId="141">
       <calculatedColumnFormula>IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{78F55B7C-8E60-49C5-B1F7-B023E76BDA6E}" name="Condição" dataDxfId="38"/>
-    <tableColumn id="20" xr3:uid="{A889C1FB-2FE0-407A-B849-FEB9F2CA4F96}" name="Desenho_x000a_Previsão" dataDxfId="37"/>
-    <tableColumn id="19" xr3:uid="{FB1E21D0-A118-422F-AA5B-F56FFBA7B5E4}" name="Des." dataDxfId="36"/>
-    <tableColumn id="17" xr3:uid="{C14325D6-C653-45B3-B85F-6AF107A71546}" name="Status" dataDxfId="35"/>
-    <tableColumn id="18" xr3:uid="{C6F7CA6A-B8B3-4E22-B3E8-05FFB1A03AB6}" name="Observação" dataDxfId="34"/>
+    <tableColumn id="16" xr3:uid="{78F55B7C-8E60-49C5-B1F7-B023E76BDA6E}" name="Condição" dataDxfId="140"/>
+    <tableColumn id="20" xr3:uid="{A889C1FB-2FE0-407A-B849-FEB9F2CA4F96}" name="Desenho_x000a_Previsão" dataDxfId="139"/>
+    <tableColumn id="19" xr3:uid="{FB1E21D0-A118-422F-AA5B-F56FFBA7B5E4}" name="Des." dataDxfId="138"/>
+    <tableColumn id="17" xr3:uid="{C14325D6-C653-45B3-B85F-6AF107A71546}" name="Status" dataDxfId="137"/>
+    <tableColumn id="18" xr3:uid="{C6F7CA6A-B8B3-4E22-B3E8-05FFB1A03AB6}" name="Observação" dataDxfId="136"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}" name="Tabela6" displayName="Tabela6" ref="A1:AC29" totalsRowShown="0" headerRowDxfId="173" dataDxfId="172">
-  <autoFilter ref="A1:AC29" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}" name="Tabela6" displayName="Tabela6" ref="A1:AC77" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+  <autoFilter ref="A1:AC77" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Raizen Barra"/>
+        <filter val="Raizen Bonfim"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{C25E2119-68FD-4765-BAFB-8CC2FA75E790}" name="PV" dataDxfId="171"/>
-    <tableColumn id="2" xr3:uid="{39E67E43-7C76-4E6C-9319-15A91DE1C08C}" name="Item" dataDxfId="170"/>
-    <tableColumn id="4" xr3:uid="{5B6759FC-B832-438E-B60C-770FAF7723FA}" name="Cliente" dataDxfId="169"/>
-    <tableColumn id="5" xr3:uid="{20CFBF4C-4BD9-4F05-86D4-8A4AFFC243B2}" name="_x000a_O.S./Peça" dataDxfId="168"/>
-    <tableColumn id="6" xr3:uid="{3994BD48-BFFD-46D2-9740-EDD282F2590D}" name="Descrição" dataDxfId="167"/>
-    <tableColumn id="7" xr3:uid="{261AA518-FC82-431F-8839-D26554B59355}" name="Qtde." dataDxfId="166"/>
-    <tableColumn id="24" xr3:uid="{0C566A21-B9D9-4AD7-A8B3-328E480EA286}" name="Bit" dataDxfId="165"/>
-    <tableColumn id="17" xr3:uid="{7631FA30-8167-4961-B0E8-981A96ADEF58}" name="Tipo" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{4F794446-D6E6-4C06-B881-9408CC542675}" name="Pos." dataDxfId="1"/>
-    <tableColumn id="26" xr3:uid="{C41F63A6-DC4C-42FE-A13B-3E56F237270D}" name="Terno" dataDxfId="164"/>
-    <tableColumn id="16" xr3:uid="{FF0A908E-E8EE-4CA0-96FA-38C032BFEFDE}" name="Forma" dataDxfId="163"/>
-    <tableColumn id="9" xr3:uid="{DE0283F8-D4F6-449C-A9CA-7DBCB898DFD9}" name="Prazo_x000a_Fund" dataDxfId="162"/>
-    <tableColumn id="10" xr3:uid="{663D9716-4C25-4ACC-A105-E9E7A474BCE6}" name="Prazo_x000a_Fund Real" dataDxfId="161"/>
-    <tableColumn id="11" xr3:uid="{6EF58C27-546C-4B57-B05D-BB07C2046388}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="160"/>
-    <tableColumn id="12" xr3:uid="{AC626966-9CA5-4150-82F1-50338494E847}" name="Pz Entrega_x000a_Real" dataDxfId="159"/>
-    <tableColumn id="13" xr3:uid="{506EC589-7ED2-4A3B-BED8-6CA8F57277E1}" name="Desenho_x000a_Previsão" dataDxfId="158"/>
-    <tableColumn id="14" xr3:uid="{A31AB572-7F13-4A5C-A42E-7E7A20433BDA}" name="Des." dataDxfId="157"/>
-    <tableColumn id="33" xr3:uid="{9D21190D-5788-4F29-AED2-63644BCE6C32}" name="OP1" dataDxfId="156"/>
-    <tableColumn id="30" xr3:uid="{6C8FD4D3-300E-4009-A264-D6FBC780DE60}" name="OP2" dataDxfId="155"/>
-    <tableColumn id="28" xr3:uid="{533BCCB9-B72A-4E3A-BE20-626EE2E49D83}" name="OP3" dataDxfId="154"/>
-    <tableColumn id="27" xr3:uid="{58435D6B-01D7-44DD-9B21-62EB23C9AA4F}" name="OP4" dataDxfId="153"/>
-    <tableColumn id="25" xr3:uid="{B00B175A-D2BA-4783-8EBD-A000C46B6055}" name="OP5" dataDxfId="152"/>
-    <tableColumn id="20" xr3:uid="{1C48207C-2D30-42CB-BD4E-0C9B569C9BCB}" name="OP6" dataDxfId="151"/>
-    <tableColumn id="35" xr3:uid="{5857075F-D742-43D2-AD1F-F2BB8219D8E7}" name="OP7" dataDxfId="150"/>
-    <tableColumn id="15" xr3:uid="{46F62312-EE93-4C00-9352-8A9BF48479C9}" name="OP8" dataDxfId="149"/>
-    <tableColumn id="8" xr3:uid="{81AAED83-3114-4366-BECD-21F933A26FE9}" name="OP9" dataDxfId="148"/>
-    <tableColumn id="18" xr3:uid="{F5387D14-C7D5-4022-901B-04E5D65304C7}" name="Status_x000a_Camisa" dataDxfId="147"/>
-    <tableColumn id="32" xr3:uid="{BEC53105-CFFD-422E-9C30-4E4BC1816678}" name="Nº Eixo" dataDxfId="146"/>
-    <tableColumn id="19" xr3:uid="{A08285BC-8B0E-4492-A6AF-090B851B036D}" name="Observação" dataDxfId="145"/>
+    <tableColumn id="1" xr3:uid="{C25E2119-68FD-4765-BAFB-8CC2FA75E790}" name="PV" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{39E67E43-7C76-4E6C-9319-15A91DE1C08C}" name="Item" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{5B6759FC-B832-438E-B60C-770FAF7723FA}" name="Cliente" dataDxfId="83"/>
+    <tableColumn id="5" xr3:uid="{20CFBF4C-4BD9-4F05-86D4-8A4AFFC243B2}" name="_x000a_O.S./Peça" dataDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{3994BD48-BFFD-46D2-9740-EDD282F2590D}" name="Descrição" dataDxfId="81"/>
+    <tableColumn id="7" xr3:uid="{261AA518-FC82-431F-8839-D26554B59355}" name="Qtde." dataDxfId="80"/>
+    <tableColumn id="24" xr3:uid="{0C566A21-B9D9-4AD7-A8B3-328E480EA286}" name="Bit" dataDxfId="79"/>
+    <tableColumn id="17" xr3:uid="{7631FA30-8167-4961-B0E8-981A96ADEF58}" name="Tipo" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{4F794446-D6E6-4C06-B881-9408CC542675}" name="Pos." dataDxfId="77"/>
+    <tableColumn id="26" xr3:uid="{C41F63A6-DC4C-42FE-A13B-3E56F237270D}" name="Terno" dataDxfId="76"/>
+    <tableColumn id="16" xr3:uid="{FF0A908E-E8EE-4CA0-96FA-38C032BFEFDE}" name="Forma" dataDxfId="75"/>
+    <tableColumn id="9" xr3:uid="{DE0283F8-D4F6-449C-A9CA-7DBCB898DFD9}" name="Prazo_x000a_Fund" dataDxfId="74"/>
+    <tableColumn id="10" xr3:uid="{663D9716-4C25-4ACC-A105-E9E7A474BCE6}" name="Prazo_x000a_Fund Real" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{6EF58C27-546C-4B57-B05D-BB07C2046388}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{AC626966-9CA5-4150-82F1-50338494E847}" name="Pz Entrega_x000a_Real" dataDxfId="71"/>
+    <tableColumn id="13" xr3:uid="{506EC589-7ED2-4A3B-BED8-6CA8F57277E1}" name="Desenho_x000a_Previsão" dataDxfId="70"/>
+    <tableColumn id="14" xr3:uid="{A31AB572-7F13-4A5C-A42E-7E7A20433BDA}" name="Des." dataDxfId="69"/>
+    <tableColumn id="33" xr3:uid="{9D21190D-5788-4F29-AED2-63644BCE6C32}" name="OP1" dataDxfId="68"/>
+    <tableColumn id="30" xr3:uid="{6C8FD4D3-300E-4009-A264-D6FBC780DE60}" name="OP2" dataDxfId="67"/>
+    <tableColumn id="28" xr3:uid="{533BCCB9-B72A-4E3A-BE20-626EE2E49D83}" name="OP3" dataDxfId="66"/>
+    <tableColumn id="27" xr3:uid="{58435D6B-01D7-44DD-9B21-62EB23C9AA4F}" name="OP4" dataDxfId="65"/>
+    <tableColumn id="25" xr3:uid="{B00B175A-D2BA-4783-8EBD-A000C46B6055}" name="OP5" dataDxfId="64"/>
+    <tableColumn id="20" xr3:uid="{1C48207C-2D30-42CB-BD4E-0C9B569C9BCB}" name="OP6" dataDxfId="63"/>
+    <tableColumn id="35" xr3:uid="{5857075F-D742-43D2-AD1F-F2BB8219D8E7}" name="OP7" dataDxfId="62"/>
+    <tableColumn id="15" xr3:uid="{46F62312-EE93-4C00-9352-8A9BF48479C9}" name="OP8" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{81AAED83-3114-4366-BECD-21F933A26FE9}" name="OP9" dataDxfId="60"/>
+    <tableColumn id="18" xr3:uid="{F5387D14-C7D5-4022-901B-04E5D65304C7}" name="Status_x000a_Camisa" dataDxfId="59"/>
+    <tableColumn id="32" xr3:uid="{BEC53105-CFFD-422E-9C30-4E4BC1816678}" name="Nº Eixo" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{A08285BC-8B0E-4492-A6AF-090B851B036D}" name="Observação" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2911020D-4239-47C9-B941-F45CAD7BBE3D}" name="Tabela66" displayName="Tabela66" ref="A1:AD35" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2911020D-4239-47C9-B941-F45CAD7BBE3D}" name="Tabela66" displayName="Tabela66" ref="A1:AD35" totalsRowShown="0" headerRowDxfId="135" dataDxfId="134">
   <autoFilter ref="A1:AD35" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}">
     <filterColumn colId="0">
       <filters>
@@ -4595,36 +5391,36 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="30">
-    <tableColumn id="4" xr3:uid="{DD6014DD-F2DC-47D0-A44B-A9397730BE4E}" name="Cliente" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{59911696-06D3-45A5-970B-2AD22F609E28}" name="Descrição" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{8F359B2A-1452-4DD5-8078-A592FF1FAEDA}" name="Qtde." dataDxfId="29"/>
-    <tableColumn id="24" xr3:uid="{6ACDF30B-4FA5-46F2-B973-769AFF1A7ED5}" name="Bit" dataDxfId="28"/>
-    <tableColumn id="26" xr3:uid="{CA14875A-A13A-4CA2-81ED-1A988AD78208}" name="Terno" dataDxfId="27"/>
-    <tableColumn id="16" xr3:uid="{D3038C5E-F555-4042-A706-904B091CB790}" name="Forma" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{736BC299-01E4-44CB-8D56-905E55712437}" name="Prazo_x000a_Fund" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{714F025C-A04A-41D1-BB99-C7973DD1D6C8}" name="Prazo_x000a_Fund Real" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{2AE87132-0DBA-40D2-AB92-CEAC0877A62E}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="23"/>
-    <tableColumn id="12" xr3:uid="{CF3374FD-D85C-4F8B-BC4C-3092E3B5F31A}" name="Pz Entrega_x000a_Real" dataDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{75F62D18-9AFA-4320-9551-17D7D3F48733}" name="Desenho_x000a_Previsão" dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{0E91F17A-D1CD-4B1F-B5BA-F593FF862042}" name="Des." dataDxfId="20"/>
-    <tableColumn id="33" xr3:uid="{49915B29-1E2A-403B-BB52-E050204325AB}" name="OP1" dataDxfId="19"/>
-    <tableColumn id="30" xr3:uid="{918DBD98-C28A-4CAB-8273-DEB81CE88B05}" name="OP2" dataDxfId="18"/>
-    <tableColumn id="28" xr3:uid="{F99FDFD5-3B70-48B1-93CD-89C55B3CE706}" name="OP3" dataDxfId="17"/>
-    <tableColumn id="27" xr3:uid="{3B6FF2E7-14DF-4DBF-B5AB-5AC8D2BE1CDD}" name="OP4" dataDxfId="16"/>
-    <tableColumn id="25" xr3:uid="{0837249B-09C0-43AA-A6F1-42C6831ED1C4}" name="OP5" dataDxfId="15"/>
-    <tableColumn id="20" xr3:uid="{9AB76328-313A-4CD8-9CB1-5AB1453CAE9E}" name="OP6" dataDxfId="14"/>
-    <tableColumn id="35" xr3:uid="{B32C0B30-5F3F-42B0-8DFF-98B0B8FB2893}" name="OP7" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{AF3E8433-61CF-422E-9FA2-91C9BA8DC757}" name="OP8" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{A6F4F508-1C53-4E9B-9746-79444D0123BB}" name="OP9" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{AEDB6685-F605-437C-ABD4-65BAE59B7844}" name="Status_x000a_Camisa" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{4D106AB2-FC5C-4F08-8B0A-A966B169502D}" name="PV eixo" dataDxfId="9"/>
-    <tableColumn id="32" xr3:uid="{111EB1E4-5B59-4AC6-97B8-26DB9C34AFD4}" name="Nº Eixo2" dataDxfId="8"/>
-    <tableColumn id="31" xr3:uid="{3327FDD5-D7D9-476C-B262-F5CEDAA2C9FA}" name="Rec_x000a_Eixo" dataDxfId="7"/>
-    <tableColumn id="34" xr3:uid="{947A4EE5-7E50-4ED4-9CAE-160C8A4CBD34}" name="OP10" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{76660409-FD24-4D8E-B5EF-275B92F001A9}" name="OP11" dataDxfId="5"/>
-    <tableColumn id="29" xr3:uid="{2D48D210-14B2-4386-A519-42F0F2B7E9F5}" name="Prazo_x000a_Entrega_x000a_Eixo" dataDxfId="4"/>
-    <tableColumn id="23" xr3:uid="{4DFCA09F-8E46-42D4-9163-40353BAA4ACE}" name="Status_x000a_Eixo" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{E3D32BDE-09FA-4F17-8CE6-8B2139F9BB8A}" name="Observação" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{DD6014DD-F2DC-47D0-A44B-A9397730BE4E}" name="Cliente" dataDxfId="133"/>
+    <tableColumn id="6" xr3:uid="{59911696-06D3-45A5-970B-2AD22F609E28}" name="Descrição" dataDxfId="132"/>
+    <tableColumn id="7" xr3:uid="{8F359B2A-1452-4DD5-8078-A592FF1FAEDA}" name="Qtde." dataDxfId="131"/>
+    <tableColumn id="24" xr3:uid="{6ACDF30B-4FA5-46F2-B973-769AFF1A7ED5}" name="Bit" dataDxfId="130"/>
+    <tableColumn id="26" xr3:uid="{CA14875A-A13A-4CA2-81ED-1A988AD78208}" name="Terno" dataDxfId="129"/>
+    <tableColumn id="16" xr3:uid="{D3038C5E-F555-4042-A706-904B091CB790}" name="Forma" dataDxfId="128"/>
+    <tableColumn id="9" xr3:uid="{736BC299-01E4-44CB-8D56-905E55712437}" name="Prazo_x000a_Fund" dataDxfId="127"/>
+    <tableColumn id="10" xr3:uid="{714F025C-A04A-41D1-BB99-C7973DD1D6C8}" name="Prazo_x000a_Fund Real" dataDxfId="126"/>
+    <tableColumn id="11" xr3:uid="{2AE87132-0DBA-40D2-AB92-CEAC0877A62E}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="125"/>
+    <tableColumn id="12" xr3:uid="{CF3374FD-D85C-4F8B-BC4C-3092E3B5F31A}" name="Pz Entrega_x000a_Real" dataDxfId="124"/>
+    <tableColumn id="13" xr3:uid="{75F62D18-9AFA-4320-9551-17D7D3F48733}" name="Desenho_x000a_Previsão" dataDxfId="123"/>
+    <tableColumn id="14" xr3:uid="{0E91F17A-D1CD-4B1F-B5BA-F593FF862042}" name="Des." dataDxfId="122"/>
+    <tableColumn id="33" xr3:uid="{49915B29-1E2A-403B-BB52-E050204325AB}" name="OP1" dataDxfId="121"/>
+    <tableColumn id="30" xr3:uid="{918DBD98-C28A-4CAB-8273-DEB81CE88B05}" name="OP2" dataDxfId="120"/>
+    <tableColumn id="28" xr3:uid="{F99FDFD5-3B70-48B1-93CD-89C55B3CE706}" name="OP3" dataDxfId="119"/>
+    <tableColumn id="27" xr3:uid="{3B6FF2E7-14DF-4DBF-B5AB-5AC8D2BE1CDD}" name="OP4" dataDxfId="118"/>
+    <tableColumn id="25" xr3:uid="{0837249B-09C0-43AA-A6F1-42C6831ED1C4}" name="OP5" dataDxfId="117"/>
+    <tableColumn id="20" xr3:uid="{9AB76328-313A-4CD8-9CB1-5AB1453CAE9E}" name="OP6" dataDxfId="116"/>
+    <tableColumn id="35" xr3:uid="{B32C0B30-5F3F-42B0-8DFF-98B0B8FB2893}" name="OP7" dataDxfId="115"/>
+    <tableColumn id="15" xr3:uid="{AF3E8433-61CF-422E-9FA2-91C9BA8DC757}" name="OP8" dataDxfId="114"/>
+    <tableColumn id="8" xr3:uid="{A6F4F508-1C53-4E9B-9746-79444D0123BB}" name="OP9" dataDxfId="113"/>
+    <tableColumn id="18" xr3:uid="{AEDB6685-F605-437C-ABD4-65BAE59B7844}" name="Status_x000a_Camisa" dataDxfId="112"/>
+    <tableColumn id="3" xr3:uid="{4D106AB2-FC5C-4F08-8B0A-A966B169502D}" name="PV eixo" dataDxfId="111"/>
+    <tableColumn id="32" xr3:uid="{111EB1E4-5B59-4AC6-97B8-26DB9C34AFD4}" name="Nº Eixo2" dataDxfId="110"/>
+    <tableColumn id="31" xr3:uid="{3327FDD5-D7D9-476C-B262-F5CEDAA2C9FA}" name="Rec_x000a_Eixo" dataDxfId="109"/>
+    <tableColumn id="34" xr3:uid="{947A4EE5-7E50-4ED4-9CAE-160C8A4CBD34}" name="OP10" dataDxfId="108"/>
+    <tableColumn id="17" xr3:uid="{76660409-FD24-4D8E-B5EF-275B92F001A9}" name="OP11" dataDxfId="107"/>
+    <tableColumn id="29" xr3:uid="{2D48D210-14B2-4386-A519-42F0F2B7E9F5}" name="Prazo_x000a_Entrega_x000a_Eixo" dataDxfId="106"/>
+    <tableColumn id="23" xr3:uid="{4DFCA09F-8E46-42D4-9163-40353BAA4ACE}" name="Status_x000a_Eixo" dataDxfId="105"/>
+    <tableColumn id="19" xr3:uid="{E3D32BDE-09FA-4F17-8CE6-8B2139F9BB8A}" name="Observação" dataDxfId="104"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5271,10 +6067,10 @@
         <v>69</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W3" s="10" t="s">
         <v>72</v>
@@ -5389,10 +6185,10 @@
         <v>69</v>
       </c>
       <c r="V4" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="W4" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="X4" s="10" t="s">
         <v>77</v>
@@ -5734,7 +6530,7 @@
         <v>69</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="W7" s="10" t="s">
         <v>72</v>
@@ -6310,10 +7106,10 @@
         <v>69</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="V12" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W12" s="10" t="s">
         <v>72</v>
@@ -6425,10 +7221,10 @@
         <v>69</v>
       </c>
       <c r="U13" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V13" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="V13" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="W13" s="10" t="s">
         <v>72</v>
@@ -6540,10 +7336,10 @@
         <v>69</v>
       </c>
       <c r="U14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="V14" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="V14" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="W14" s="10" t="s">
         <v>72</v>
@@ -8042,7 +8838,7 @@
         <v>69</v>
       </c>
       <c r="W27" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="X27" s="10" t="s">
         <v>77</v>
@@ -8157,7 +8953,7 @@
         <v>69</v>
       </c>
       <c r="W28" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X28" s="10" t="s">
         <v>77</v>
@@ -8272,7 +9068,7 @@
         <v>69</v>
       </c>
       <c r="W29" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X29" s="10" t="s">
         <v>77</v>
@@ -8842,7 +9638,7 @@
         <v>69</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V34" s="10" t="s">
         <v>72</v>
@@ -8867,7 +9663,7 @@
       </c>
       <c r="AC34" s="10" t="str">
         <f t="shared" ref="AC34:AC65" si="3">IF(L34="","AG. FUNDIDO",IF(U34="AG","AG. USINAGEM","EM USINAGEM"))</f>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE34" s="42">
         <v>27</v>
@@ -9072,10 +9868,10 @@
         <v>69</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="V36" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W36" s="10" t="s">
         <v>72</v>
@@ -9235,7 +10031,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
         <v>2205</v>
       </c>
@@ -9302,7 +10098,7 @@
         <v>69</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V38" s="10" t="s">
         <v>72</v>
@@ -9327,7 +10123,7 @@
       </c>
       <c r="AC38" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE38" s="42">
         <v>27</v>
@@ -10486,7 +11282,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" s="15">
         <v>2205</v>
       </c>
@@ -10553,7 +11349,7 @@
         <v>69</v>
       </c>
       <c r="U49" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V49" s="10" t="s">
         <v>72</v>
@@ -10578,7 +11374,7 @@
       </c>
       <c r="AC49" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE49" s="42">
         <v>28</v>
@@ -10599,7 +11395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" s="15">
         <v>2205</v>
       </c>
@@ -10714,7 +11510,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" s="15">
         <v>2205</v>
       </c>
@@ -10829,7 +11625,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" s="15">
         <v>2205</v>
       </c>
@@ -11737,7 +12533,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="15">
         <v>2226</v>
       </c>
@@ -11847,7 +12643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="15">
         <v>2226</v>
       </c>
@@ -11957,7 +12753,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15">
         <v>2226</v>
       </c>
@@ -12067,7 +12863,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="15">
         <v>2226</v>
       </c>
@@ -12177,7 +12973,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="15">
         <v>2226</v>
       </c>
@@ -12287,7 +13083,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15">
         <v>2226</v>
       </c>
@@ -12397,7 +13193,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="15">
         <v>2226</v>
       </c>
@@ -36736,118 +37532,118 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A7CF3D-4567-423F-9856-686FB94A96D5}">
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC237"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="53"/>
-    <col min="3" max="3" width="16" style="53" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="53"/>
-    <col min="5" max="5" width="21.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="53" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" style="53" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.42578125" style="53" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" style="53" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="53"/>
-    <col min="12" max="12" width="10.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" style="53" customWidth="1"/>
-    <col min="14" max="14" width="10.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="15" max="26" width="9.140625" style="53"/>
-    <col min="27" max="27" width="18.5703125" style="53" customWidth="1"/>
-    <col min="28" max="28" width="12.140625" style="53" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="25.42578125" style="53" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="53"/>
+    <col min="1" max="2" width="9.140625" style="69"/>
+    <col min="3" max="3" width="16" style="69" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="69"/>
+    <col min="5" max="5" width="21.85546875" style="69" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="69" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" style="69" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.42578125" style="69" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" style="69" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="69"/>
+    <col min="12" max="12" width="10.140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" style="69" customWidth="1"/>
+    <col min="14" max="15" width="10.140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="9.140625" style="69"/>
+    <col min="27" max="27" width="18.5703125" style="69" customWidth="1"/>
+    <col min="28" max="28" width="12.140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="25.42578125" style="69" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="69"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="51" t="s">
+      <c r="B1" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="68" t="s">
         <v>257</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="67" t="s">
         <v>258</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="67" t="s">
         <v>304</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="67" t="s">
         <v>303</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="67" t="s">
         <v>236</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="L1" s="52" t="s">
+      <c r="L1" s="68" t="s">
         <v>251</v>
       </c>
-      <c r="M1" s="52" t="s">
+      <c r="M1" s="68" t="s">
         <v>252</v>
       </c>
-      <c r="N1" s="52" t="s">
+      <c r="N1" s="68" t="s">
         <v>250</v>
       </c>
-      <c r="O1" s="52" t="s">
+      <c r="O1" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="52" t="s">
+      <c r="P1" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="Q1" s="52" t="s">
+      <c r="Q1" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="R1" s="52" t="s">
+      <c r="R1" s="68" t="s">
         <v>277</v>
       </c>
-      <c r="S1" s="52" t="s">
+      <c r="S1" s="68" t="s">
         <v>278</v>
       </c>
-      <c r="T1" s="52" t="s">
+      <c r="T1" s="68" t="s">
         <v>279</v>
       </c>
-      <c r="U1" s="52" t="s">
+      <c r="U1" s="68" t="s">
         <v>280</v>
       </c>
-      <c r="V1" s="52" t="s">
+      <c r="V1" s="68" t="s">
         <v>281</v>
       </c>
-      <c r="W1" s="52" t="s">
+      <c r="W1" s="68" t="s">
         <v>282</v>
       </c>
-      <c r="X1" s="52" t="s">
+      <c r="X1" s="68" t="s">
         <v>283</v>
       </c>
-      <c r="Y1" s="52" t="s">
+      <c r="Y1" s="68" t="s">
         <v>284</v>
       </c>
-      <c r="Z1" s="52" t="s">
+      <c r="Z1" s="68" t="s">
         <v>285</v>
       </c>
-      <c r="AA1" s="52" t="s">
+      <c r="AA1" s="68" t="s">
         <v>227</v>
       </c>
-      <c r="AB1" s="52" t="s">
+      <c r="AB1" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="AC1" s="52" t="s">
+      <c r="AC1" s="68" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54">
         <v>1015</v>
       </c>
@@ -36932,7 +37728,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54">
         <v>1027</v>
       </c>
@@ -37005,7 +37801,7 @@
       </c>
       <c r="AC3" s="54"/>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="54">
         <v>1027</v>
       </c>
@@ -37078,7 +37874,7 @@
       </c>
       <c r="AC4" s="54"/>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="54">
         <v>1027</v>
       </c>
@@ -37151,7 +37947,7 @@
       </c>
       <c r="AC5" s="54"/>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54">
         <v>1027</v>
       </c>
@@ -37224,7 +38020,7 @@
       </c>
       <c r="AC6" s="54"/>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54">
         <v>1027</v>
       </c>
@@ -37297,7 +38093,7 @@
       </c>
       <c r="AC7" s="54"/>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="54">
         <v>1027</v>
       </c>
@@ -37372,7 +38168,7 @@
       </c>
       <c r="AC8" s="54"/>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="54">
         <v>1027</v>
       </c>
@@ -37445,7 +38241,7 @@
       </c>
       <c r="AC9" s="54"/>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="54">
         <v>1027</v>
       </c>
@@ -37520,7 +38316,7 @@
       </c>
       <c r="AC10" s="54"/>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="54">
         <v>1027</v>
       </c>
@@ -37593,7 +38389,7 @@
       </c>
       <c r="AC11" s="54"/>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="54">
         <v>1027</v>
       </c>
@@ -37676,7 +38472,7 @@
       </c>
       <c r="AC12" s="54"/>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="54">
         <v>1027</v>
       </c>
@@ -37749,7 +38545,7 @@
       </c>
       <c r="AC13" s="54"/>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="54">
         <v>1027</v>
       </c>
@@ -37834,7 +38630,7 @@
       </c>
       <c r="AC14" s="54"/>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="54">
         <v>1027</v>
       </c>
@@ -37907,7 +38703,7 @@
       </c>
       <c r="AC15" s="54"/>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="54">
         <v>1027</v>
       </c>
@@ -37990,7 +38786,7 @@
       </c>
       <c r="AC16" s="54"/>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54">
         <v>1027</v>
       </c>
@@ -38063,7 +38859,7 @@
       </c>
       <c r="AC17" s="54"/>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54">
         <v>1027</v>
       </c>
@@ -38136,7 +38932,7 @@
       </c>
       <c r="AC18" s="54"/>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="54">
         <v>1005</v>
       </c>
@@ -38209,7 +39005,7 @@
       </c>
       <c r="AC19" s="54"/>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54">
         <v>1005</v>
       </c>
@@ -38282,7 +39078,7 @@
       </c>
       <c r="AC20" s="54"/>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="54">
         <v>1005</v>
       </c>
@@ -38355,7 +39151,7 @@
       </c>
       <c r="AC21" s="54"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="54">
         <v>1005</v>
       </c>
@@ -38428,7 +39224,7 @@
       </c>
       <c r="AC22" s="54"/>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="54">
         <v>1005</v>
       </c>
@@ -38501,7 +39297,7 @@
       </c>
       <c r="AC23" s="54"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="54">
         <v>1005</v>
       </c>
@@ -38574,7 +39370,7 @@
       </c>
       <c r="AC24" s="54"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="54">
         <v>1005</v>
       </c>
@@ -38647,7 +39443,7 @@
       </c>
       <c r="AC25" s="54"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="54">
         <v>1005</v>
       </c>
@@ -38720,7 +39516,7 @@
       </c>
       <c r="AC26" s="54"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="54">
         <v>1005</v>
       </c>
@@ -38793,7 +39589,7 @@
       </c>
       <c r="AC27" s="54"/>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="54">
         <v>1005</v>
       </c>
@@ -38866,7 +39662,7 @@
       </c>
       <c r="AC28" s="54"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="54">
         <v>1005</v>
       </c>
@@ -38939,8 +39735,4073 @@
       </c>
       <c r="AC29" s="54"/>
     </row>
+    <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="63">
+        <v>2077</v>
+      </c>
+      <c r="B30" s="58">
+        <v>1</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="D30" s="63">
+        <v>6728</v>
+      </c>
+      <c r="E30" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" s="58">
+        <v>1</v>
+      </c>
+      <c r="G30" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="H30" s="58" t="s">
+        <v>305</v>
+      </c>
+      <c r="I30" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J30" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K30" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L30" s="65"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="59">
+        <v>46090</v>
+      </c>
+      <c r="O30" s="59">
+        <v>46090</v>
+      </c>
+      <c r="P30" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q30" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R30" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S30" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T30" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U30" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V30" s="58"/>
+      <c r="W30" s="58"/>
+      <c r="X30" s="58"/>
+      <c r="Y30" s="58"/>
+      <c r="Z30" s="58"/>
+      <c r="AA30" s="58" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB30" s="63">
+        <v>6032</v>
+      </c>
+      <c r="AC30" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="63">
+        <v>2077</v>
+      </c>
+      <c r="B31" s="58">
+        <v>2</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="D31" s="63">
+        <v>6727</v>
+      </c>
+      <c r="E31" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F31" s="58">
+        <v>1</v>
+      </c>
+      <c r="G31" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="H31" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I31" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J31" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K31" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L31" s="65"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="59">
+        <v>46192</v>
+      </c>
+      <c r="O31" s="59">
+        <v>46192</v>
+      </c>
+      <c r="P31" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q31" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R31" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S31" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T31" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U31" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V31" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W31" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X31" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y31" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z31" s="58"/>
+      <c r="AA31" s="58" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB31" s="63">
+        <v>6040</v>
+      </c>
+      <c r="AC31" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="63">
+        <v>1386</v>
+      </c>
+      <c r="B32" s="58">
+        <v>5</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="D32" s="63">
+        <v>6169</v>
+      </c>
+      <c r="E32" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F32" s="58">
+        <v>1</v>
+      </c>
+      <c r="G32" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="H32" s="58" t="s">
+        <v>305</v>
+      </c>
+      <c r="I32" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J32" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K32" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L32" s="65"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q32" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R32" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S32" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T32" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U32" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V32" s="58"/>
+      <c r="W32" s="58"/>
+      <c r="X32" s="58"/>
+      <c r="Y32" s="58"/>
+      <c r="Z32" s="58"/>
+      <c r="AA32" s="58" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB32" s="63">
+        <v>6075</v>
+      </c>
+      <c r="AC32" s="58"/>
+    </row>
+    <row r="33" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B33" s="60">
+        <v>8</v>
+      </c>
+      <c r="C33" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D33" s="63">
+        <v>6741</v>
+      </c>
+      <c r="E33" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F33" s="58">
+        <v>1</v>
+      </c>
+      <c r="G33" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H33" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I33" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J33" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K33" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L33" s="60"/>
+      <c r="M33" s="60"/>
+      <c r="N33" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O33" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P33" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q33" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R33" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S33" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T33" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U33" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V33" s="65"/>
+      <c r="W33" s="65"/>
+      <c r="X33" s="65"/>
+      <c r="Y33" s="65"/>
+      <c r="Z33" s="65"/>
+      <c r="AA33" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB33" s="63">
+        <v>123</v>
+      </c>
+      <c r="AC33" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B34" s="60">
+        <v>1</v>
+      </c>
+      <c r="C34" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D34" s="63">
+        <v>6734</v>
+      </c>
+      <c r="E34" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F34" s="58">
+        <v>1</v>
+      </c>
+      <c r="G34" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H34" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J34" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K34" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L34" s="60"/>
+      <c r="M34" s="60"/>
+      <c r="N34" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O34" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P34" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q34" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R34" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S34" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T34" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U34" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V34" s="65"/>
+      <c r="W34" s="65"/>
+      <c r="X34" s="65"/>
+      <c r="Y34" s="65"/>
+      <c r="Z34" s="65"/>
+      <c r="AA34" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB34" s="63">
+        <v>134</v>
+      </c>
+      <c r="AC34" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B35" s="60">
+        <v>4</v>
+      </c>
+      <c r="C35" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D35" s="63">
+        <v>6737</v>
+      </c>
+      <c r="E35" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F35" s="58">
+        <v>1</v>
+      </c>
+      <c r="G35" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H35" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I35" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J35" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K35" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L35" s="60"/>
+      <c r="M35" s="60"/>
+      <c r="N35" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O35" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P35" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q35" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R35" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S35" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T35" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U35" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V35" s="65"/>
+      <c r="W35" s="65"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="65"/>
+      <c r="Z35" s="65"/>
+      <c r="AA35" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB35" s="63">
+        <v>173</v>
+      </c>
+      <c r="AC35" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B36" s="60">
+        <v>9</v>
+      </c>
+      <c r="C36" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D36" s="63">
+        <v>6742</v>
+      </c>
+      <c r="E36" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F36" s="58">
+        <v>1</v>
+      </c>
+      <c r="G36" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H36" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I36" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J36" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K36" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L36" s="60"/>
+      <c r="M36" s="60"/>
+      <c r="N36" s="64">
+        <v>46127</v>
+      </c>
+      <c r="O36" s="60"/>
+      <c r="P36" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q36" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R36" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S36" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T36" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U36" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V36" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W36" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X36" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y36" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z36" s="65"/>
+      <c r="AA36" s="60" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB36" s="63">
+        <v>181</v>
+      </c>
+      <c r="AC36" s="60"/>
+    </row>
+    <row r="37" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B37" s="60">
+        <v>10</v>
+      </c>
+      <c r="C37" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D37" s="63">
+        <v>6743</v>
+      </c>
+      <c r="E37" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F37" s="58">
+        <v>1</v>
+      </c>
+      <c r="G37" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H37" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I37" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J37" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K37" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L37" s="60"/>
+      <c r="M37" s="60"/>
+      <c r="N37" s="64">
+        <v>46185</v>
+      </c>
+      <c r="O37" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P37" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q37" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R37" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S37" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T37" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U37" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V37" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W37" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X37" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y37" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z37" s="65"/>
+      <c r="AA37" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB37" s="63">
+        <v>187</v>
+      </c>
+      <c r="AC37" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B38" s="60">
+        <v>3</v>
+      </c>
+      <c r="C38" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D38" s="63">
+        <v>6736</v>
+      </c>
+      <c r="E38" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F38" s="58">
+        <v>1</v>
+      </c>
+      <c r="G38" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H38" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I38" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K38" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L38" s="60"/>
+      <c r="M38" s="60"/>
+      <c r="N38" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O38" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P38" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q38" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R38" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S38" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T38" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U38" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V38" s="65"/>
+      <c r="W38" s="65"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="65"/>
+      <c r="Z38" s="65"/>
+      <c r="AA38" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB38" s="63">
+        <v>199</v>
+      </c>
+      <c r="AC38" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B39" s="60">
+        <v>2</v>
+      </c>
+      <c r="C39" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D39" s="63">
+        <v>6735</v>
+      </c>
+      <c r="E39" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F39" s="58">
+        <v>1</v>
+      </c>
+      <c r="G39" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H39" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I39" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J39" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K39" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L39" s="60"/>
+      <c r="M39" s="60"/>
+      <c r="N39" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O39" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P39" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q39" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R39" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S39" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T39" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U39" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V39" s="65"/>
+      <c r="W39" s="65"/>
+      <c r="X39" s="65"/>
+      <c r="Y39" s="65"/>
+      <c r="Z39" s="65"/>
+      <c r="AA39" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB39" s="63">
+        <v>200</v>
+      </c>
+      <c r="AC39" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B40" s="60">
+        <v>7</v>
+      </c>
+      <c r="C40" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D40" s="63">
+        <v>6740</v>
+      </c>
+      <c r="E40" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F40" s="58">
+        <v>1</v>
+      </c>
+      <c r="G40" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H40" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I40" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J40" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K40" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L40" s="60"/>
+      <c r="M40" s="60"/>
+      <c r="N40" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O40" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P40" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q40" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R40" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S40" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T40" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U40" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V40" s="65"/>
+      <c r="W40" s="65"/>
+      <c r="X40" s="65"/>
+      <c r="Y40" s="65"/>
+      <c r="Z40" s="65"/>
+      <c r="AA40" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB40" s="63">
+        <v>201</v>
+      </c>
+      <c r="AC40" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B41" s="60">
+        <v>5</v>
+      </c>
+      <c r="C41" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D41" s="63">
+        <v>6738</v>
+      </c>
+      <c r="E41" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F41" s="58">
+        <v>1</v>
+      </c>
+      <c r="G41" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H41" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I41" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J41" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K41" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O41" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P41" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q41" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R41" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S41" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T41" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U41" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V41" s="65"/>
+      <c r="W41" s="65"/>
+      <c r="X41" s="65"/>
+      <c r="Y41" s="65"/>
+      <c r="Z41" s="65"/>
+      <c r="AA41" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB41" s="63" t="s">
+        <v>316</v>
+      </c>
+      <c r="AC41" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B42" s="60">
+        <v>11</v>
+      </c>
+      <c r="C42" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D42" s="63">
+        <v>6744</v>
+      </c>
+      <c r="E42" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F42" s="58">
+        <v>1</v>
+      </c>
+      <c r="G42" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H42" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I42" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J42" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K42" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L42" s="60"/>
+      <c r="M42" s="60"/>
+      <c r="N42" s="64">
+        <v>46127</v>
+      </c>
+      <c r="O42" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P42" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q42" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R42" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S42" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T42" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U42" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V42" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W42" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X42" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y42" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z42" s="65"/>
+      <c r="AA42" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB42" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="AC42" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="63">
+        <v>2078</v>
+      </c>
+      <c r="B43" s="60">
+        <v>6</v>
+      </c>
+      <c r="C43" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="D43" s="63">
+        <v>6739</v>
+      </c>
+      <c r="E43" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F43" s="58">
+        <v>1</v>
+      </c>
+      <c r="G43" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H43" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I43" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J43" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K43" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L43" s="60"/>
+      <c r="M43" s="60"/>
+      <c r="N43" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O43" s="64">
+        <v>46090</v>
+      </c>
+      <c r="P43" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q43" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R43" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S43" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="T43" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="U43" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="V43" s="65"/>
+      <c r="W43" s="65"/>
+      <c r="X43" s="65"/>
+      <c r="Y43" s="65"/>
+      <c r="Z43" s="65"/>
+      <c r="AA43" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB43" s="63" t="s">
+        <v>318</v>
+      </c>
+      <c r="AC43" s="58" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="60">
+        <v>2099</v>
+      </c>
+      <c r="B44" s="60">
+        <v>1</v>
+      </c>
+      <c r="C44" s="60" t="s">
+        <v>319</v>
+      </c>
+      <c r="D44" s="60">
+        <v>6745</v>
+      </c>
+      <c r="E44" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F44" s="60">
+        <v>1</v>
+      </c>
+      <c r="G44" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="H44" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I44" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J44" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K44" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L44" s="60"/>
+      <c r="M44" s="60"/>
+      <c r="N44" s="64">
+        <v>46127</v>
+      </c>
+      <c r="O44" s="60"/>
+      <c r="P44" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q44" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="R44" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S44" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T44" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U44" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V44" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W44" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X44" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y44" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z44" s="65"/>
+      <c r="AA44" s="60" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB44" s="60">
+        <v>44</v>
+      </c>
+      <c r="AC44" s="60"/>
+    </row>
+    <row r="45" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="60">
+        <v>2097</v>
+      </c>
+      <c r="B45" s="60">
+        <v>1</v>
+      </c>
+      <c r="C45" s="60" t="s">
+        <v>320</v>
+      </c>
+      <c r="D45" s="60">
+        <v>6788</v>
+      </c>
+      <c r="E45" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F45" s="60">
+        <v>1</v>
+      </c>
+      <c r="G45" s="65" t="s">
+        <v>321</v>
+      </c>
+      <c r="H45" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I45" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J45" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K45" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="L45" s="60"/>
+      <c r="M45" s="60"/>
+      <c r="N45" s="64">
+        <v>46127</v>
+      </c>
+      <c r="O45" s="60"/>
+      <c r="P45" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q45" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R45" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S45" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T45" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U45" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V45" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W45" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X45" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y45" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z45" s="65"/>
+      <c r="AA45" s="60" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB45" s="60" t="s">
+        <v>322</v>
+      </c>
+      <c r="AC45" s="60"/>
+    </row>
+    <row r="46" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="60">
+        <v>2088</v>
+      </c>
+      <c r="B46" s="60">
+        <v>3</v>
+      </c>
+      <c r="C46" s="60" t="s">
+        <v>323</v>
+      </c>
+      <c r="D46" s="60">
+        <v>6774</v>
+      </c>
+      <c r="E46" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F46" s="60">
+        <v>1</v>
+      </c>
+      <c r="G46" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="H46" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I46" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J46" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K46" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L46" s="60"/>
+      <c r="M46" s="60"/>
+      <c r="N46" s="66">
+        <v>46132</v>
+      </c>
+      <c r="O46" s="60"/>
+      <c r="P46" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q46" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R46" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S46" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T46" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U46" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V46" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W46" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X46" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y46" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z46" s="65"/>
+      <c r="AA46" s="60" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB46" s="60">
+        <v>62</v>
+      </c>
+      <c r="AC46" s="60"/>
+    </row>
+    <row r="47" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="60">
+        <v>2088</v>
+      </c>
+      <c r="B47" s="60">
+        <v>1</v>
+      </c>
+      <c r="C47" s="60" t="s">
+        <v>323</v>
+      </c>
+      <c r="D47" s="60">
+        <v>6772</v>
+      </c>
+      <c r="E47" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F47" s="60">
+        <v>1</v>
+      </c>
+      <c r="G47" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="H47" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I47" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J47" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K47" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L47" s="60"/>
+      <c r="M47" s="60"/>
+      <c r="N47" s="66">
+        <v>46132</v>
+      </c>
+      <c r="O47" s="60"/>
+      <c r="P47" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q47" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R47" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S47" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T47" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U47" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V47" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W47" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X47" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y47" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z47" s="65"/>
+      <c r="AA47" s="60" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB47" s="60" t="s">
+        <v>324</v>
+      </c>
+      <c r="AC47" s="60"/>
+    </row>
+    <row r="48" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="60">
+        <v>2088</v>
+      </c>
+      <c r="B48" s="60">
+        <v>2</v>
+      </c>
+      <c r="C48" s="60" t="s">
+        <v>323</v>
+      </c>
+      <c r="D48" s="60">
+        <v>6778</v>
+      </c>
+      <c r="E48" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F48" s="60">
+        <v>1</v>
+      </c>
+      <c r="G48" s="65">
+        <v>2200</v>
+      </c>
+      <c r="H48" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I48" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J48" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K48" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L48" s="60"/>
+      <c r="M48" s="60"/>
+      <c r="N48" s="66">
+        <v>46132</v>
+      </c>
+      <c r="O48" s="60"/>
+      <c r="P48" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q48" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R48" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S48" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T48" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U48" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V48" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W48" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X48" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y48" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z48" s="65"/>
+      <c r="AA48" s="60" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB48" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="AC48" s="60"/>
+    </row>
+    <row r="49" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="60">
+        <v>974</v>
+      </c>
+      <c r="B49" s="60">
+        <v>4</v>
+      </c>
+      <c r="C49" s="60" t="s">
+        <v>323</v>
+      </c>
+      <c r="D49" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E49" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F49" s="60">
+        <v>1</v>
+      </c>
+      <c r="G49" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="H49" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I49" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J49" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K49" s="60" t="s">
+        <v>242</v>
+      </c>
+      <c r="L49" s="60"/>
+      <c r="M49" s="60"/>
+      <c r="N49" s="66">
+        <v>46063</v>
+      </c>
+      <c r="O49" s="60"/>
+      <c r="P49" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q49" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R49" s="65" t="s">
+        <v>268</v>
+      </c>
+      <c r="S49" s="65" t="s">
+        <v>267</v>
+      </c>
+      <c r="T49" s="65"/>
+      <c r="U49" s="65"/>
+      <c r="V49" s="65"/>
+      <c r="W49" s="65"/>
+      <c r="X49" s="65"/>
+      <c r="Y49" s="65"/>
+      <c r="Z49" s="65"/>
+      <c r="AA49" s="60" t="s">
+        <v>327</v>
+      </c>
+      <c r="AB49" s="60">
+        <v>81</v>
+      </c>
+      <c r="AC49" s="60" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="60">
+        <v>1006</v>
+      </c>
+      <c r="B50" s="60">
+        <v>3</v>
+      </c>
+      <c r="C50" s="60" t="s">
+        <v>328</v>
+      </c>
+      <c r="D50" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F50" s="60">
+        <v>1</v>
+      </c>
+      <c r="G50" s="65" t="s">
+        <v>329</v>
+      </c>
+      <c r="H50" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I50" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J50" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K50" s="60" t="s">
+        <v>242</v>
+      </c>
+      <c r="L50" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="M50" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="N50" s="66">
+        <v>46191</v>
+      </c>
+      <c r="O50" s="60"/>
+      <c r="P50" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q50" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R50" s="70" t="s">
+        <v>268</v>
+      </c>
+      <c r="S50" s="70" t="s">
+        <v>267</v>
+      </c>
+      <c r="T50" s="65"/>
+      <c r="U50" s="65"/>
+      <c r="V50" s="65"/>
+      <c r="W50" s="65"/>
+      <c r="X50" s="65"/>
+      <c r="Y50" s="65"/>
+      <c r="Z50" s="65"/>
+      <c r="AA50" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB50" s="60">
+        <v>18</v>
+      </c>
+      <c r="AC50" s="60" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="60">
+        <v>1006</v>
+      </c>
+      <c r="B51" s="60">
+        <v>4</v>
+      </c>
+      <c r="C51" s="60" t="s">
+        <v>328</v>
+      </c>
+      <c r="D51" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F51" s="60">
+        <v>1</v>
+      </c>
+      <c r="G51" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="H51" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="I51" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J51" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K51" s="60" t="s">
+        <v>242</v>
+      </c>
+      <c r="L51" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="M51" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="N51" s="66">
+        <v>46191</v>
+      </c>
+      <c r="O51" s="60"/>
+      <c r="P51" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q51" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R51" s="70" t="s">
+        <v>268</v>
+      </c>
+      <c r="S51" s="70" t="s">
+        <v>267</v>
+      </c>
+      <c r="T51" s="65"/>
+      <c r="U51" s="65"/>
+      <c r="V51" s="65"/>
+      <c r="W51" s="65"/>
+      <c r="X51" s="65"/>
+      <c r="Y51" s="65"/>
+      <c r="Z51" s="65"/>
+      <c r="AA51" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB51" s="60" t="s">
+        <v>331</v>
+      </c>
+      <c r="AC51" s="60" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="60">
+        <v>2098</v>
+      </c>
+      <c r="B52" s="60">
+        <v>1</v>
+      </c>
+      <c r="C52" s="60" t="s">
+        <v>332</v>
+      </c>
+      <c r="D52" s="60">
+        <v>6746</v>
+      </c>
+      <c r="E52" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F52" s="60">
+        <v>1</v>
+      </c>
+      <c r="G52" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="H52" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I52" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J52" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K52" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L52" s="60"/>
+      <c r="M52" s="60"/>
+      <c r="N52" s="66">
+        <v>46127</v>
+      </c>
+      <c r="O52" s="60"/>
+      <c r="P52" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q52" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R52" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S52" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T52" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U52" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V52" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W52" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X52" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y52" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z52" s="65"/>
+      <c r="AA52" s="60" t="s">
+        <v>312</v>
+      </c>
+      <c r="AB52" s="60">
+        <v>22</v>
+      </c>
+      <c r="AC52" s="60"/>
+    </row>
+    <row r="53" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="60">
+        <v>2080</v>
+      </c>
+      <c r="B53" s="60">
+        <v>2</v>
+      </c>
+      <c r="C53" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D53" s="60">
+        <v>6726</v>
+      </c>
+      <c r="E53" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F53" s="60">
+        <v>1</v>
+      </c>
+      <c r="G53" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="H53" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I53" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J53" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K53" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L53" s="60"/>
+      <c r="M53" s="60"/>
+      <c r="N53" s="66">
+        <v>46195</v>
+      </c>
+      <c r="O53" s="60"/>
+      <c r="P53" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q53" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R53" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S53" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T53" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U53" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V53" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W53" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X53" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y53" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z53" s="65"/>
+      <c r="AA53" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB53" s="60">
+        <v>33</v>
+      </c>
+      <c r="AC53" s="60" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="60">
+        <v>2080</v>
+      </c>
+      <c r="B54" s="60">
+        <v>1</v>
+      </c>
+      <c r="C54" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D54" s="60">
+        <v>6725</v>
+      </c>
+      <c r="E54" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F54" s="60">
+        <v>1</v>
+      </c>
+      <c r="G54" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="H54" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I54" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J54" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K54" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L54" s="60"/>
+      <c r="M54" s="60"/>
+      <c r="N54" s="66">
+        <v>46101</v>
+      </c>
+      <c r="O54" s="60"/>
+      <c r="P54" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q54" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R54" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="S54" s="61" t="s">
+        <v>269</v>
+      </c>
+      <c r="T54" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="U54" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V54" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="W54" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="X54" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y54" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z54" s="65"/>
+      <c r="AA54" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="AB54" s="60">
+        <v>44</v>
+      </c>
+      <c r="AC54" s="60" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="63" t="s">
+        <v>340</v>
+      </c>
+      <c r="B55" s="58">
+        <v>3</v>
+      </c>
+      <c r="C55" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="D55" s="63">
+        <v>6751</v>
+      </c>
+      <c r="E55" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F55" s="58">
+        <v>1</v>
+      </c>
+      <c r="G55" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="H55" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I55" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J55" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K55" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L55" s="60"/>
+      <c r="M55" s="60"/>
+      <c r="N55" s="64">
+        <v>46127</v>
+      </c>
+      <c r="O55" s="60"/>
+      <c r="P55" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q55" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R55" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S55" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T55" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U55" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V55" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W55" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X55" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y55" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z55" s="60"/>
+      <c r="AA55" s="60"/>
+      <c r="AB55" s="57">
+        <v>78</v>
+      </c>
+      <c r="AC55" s="60"/>
+    </row>
+    <row r="56" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="63" t="s">
+        <v>341</v>
+      </c>
+      <c r="B56" s="58">
+        <v>1</v>
+      </c>
+      <c r="C56" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="D56" s="63">
+        <v>6749</v>
+      </c>
+      <c r="E56" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F56" s="58">
+        <v>1</v>
+      </c>
+      <c r="G56" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="H56" s="65" t="s">
+        <v>306</v>
+      </c>
+      <c r="I56" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J56" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K56" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L56" s="60"/>
+      <c r="M56" s="60"/>
+      <c r="N56" s="64">
+        <v>46127</v>
+      </c>
+      <c r="O56" s="60"/>
+      <c r="P56" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q56" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R56" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S56" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T56" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U56" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V56" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W56" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X56" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y56" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z56" s="60"/>
+      <c r="AA56" s="60"/>
+      <c r="AB56" s="57">
+        <v>82</v>
+      </c>
+      <c r="AC56" s="60"/>
+    </row>
+    <row r="57" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="B57" s="58">
+        <v>2</v>
+      </c>
+      <c r="C57" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="D57" s="63">
+        <v>6750</v>
+      </c>
+      <c r="E57" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F57" s="58">
+        <v>1</v>
+      </c>
+      <c r="G57" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H57" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I57" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J57" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K57" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L57" s="60"/>
+      <c r="M57" s="60"/>
+      <c r="N57" s="64">
+        <v>46127</v>
+      </c>
+      <c r="O57" s="60"/>
+      <c r="P57" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q57" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R57" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S57" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T57" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U57" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V57" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W57" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X57" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y57" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z57" s="60"/>
+      <c r="AA57" s="60"/>
+      <c r="AB57" s="57">
+        <v>85</v>
+      </c>
+      <c r="AC57" s="60"/>
+    </row>
+    <row r="58" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="B58" s="58">
+        <v>31</v>
+      </c>
+      <c r="C58" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="D58" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F58" s="58">
+        <v>1</v>
+      </c>
+      <c r="G58" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H58" s="63" t="s">
+        <v>305</v>
+      </c>
+      <c r="I58" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J58" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K58" s="60" t="s">
+        <v>242</v>
+      </c>
+      <c r="L58" s="60"/>
+      <c r="M58" s="60"/>
+      <c r="N58" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O58" s="60"/>
+      <c r="P58" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q58" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R58" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="S58" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="T58" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="U58" s="60" t="s">
+        <v>276</v>
+      </c>
+      <c r="V58" s="60"/>
+      <c r="W58" s="60"/>
+      <c r="X58" s="60"/>
+      <c r="Y58" s="60"/>
+      <c r="Z58" s="60"/>
+      <c r="AA58" s="60"/>
+      <c r="AB58" s="57">
+        <v>86</v>
+      </c>
+      <c r="AC58" s="60"/>
+    </row>
+    <row r="59" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="B59" s="58">
+        <v>2</v>
+      </c>
+      <c r="C59" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="D59" s="63">
+        <v>6731</v>
+      </c>
+      <c r="E59" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F59" s="58">
+        <v>1</v>
+      </c>
+      <c r="G59" s="71">
+        <v>2000</v>
+      </c>
+      <c r="H59" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I59" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J59" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K59" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L59" s="60"/>
+      <c r="M59" s="60"/>
+      <c r="N59" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O59" s="60"/>
+      <c r="P59" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q59" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R59" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S59" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T59" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U59" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V59" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W59" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X59" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y59" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z59" s="60"/>
+      <c r="AA59" s="60"/>
+      <c r="AB59" s="57">
+        <v>38</v>
+      </c>
+      <c r="AC59" s="60"/>
+    </row>
+    <row r="60" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="63" t="s">
+        <v>345</v>
+      </c>
+      <c r="B60" s="58">
+        <v>1</v>
+      </c>
+      <c r="C60" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="D60" s="63">
+        <v>6732</v>
+      </c>
+      <c r="E60" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F60" s="58">
+        <v>1</v>
+      </c>
+      <c r="G60" s="71">
+        <v>2000</v>
+      </c>
+      <c r="H60" s="63" t="s">
+        <v>305</v>
+      </c>
+      <c r="I60" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J60" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K60" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L60" s="60"/>
+      <c r="M60" s="60"/>
+      <c r="N60" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O60" s="60"/>
+      <c r="P60" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q60" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R60" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="S60" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="T60" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="U60" s="60" t="s">
+        <v>276</v>
+      </c>
+      <c r="V60" s="60"/>
+      <c r="W60" s="60"/>
+      <c r="X60" s="60"/>
+      <c r="Y60" s="60"/>
+      <c r="Z60" s="60"/>
+      <c r="AA60" s="60"/>
+      <c r="AB60" s="57">
+        <v>62</v>
+      </c>
+      <c r="AC60" s="60"/>
+    </row>
+    <row r="61" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="63" t="s">
+        <v>346</v>
+      </c>
+      <c r="B61" s="58">
+        <v>3</v>
+      </c>
+      <c r="C61" s="58" t="s">
+        <v>336</v>
+      </c>
+      <c r="D61" s="63">
+        <v>6775</v>
+      </c>
+      <c r="E61" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F61" s="58">
+        <v>1</v>
+      </c>
+      <c r="G61" s="72" t="s">
+        <v>315</v>
+      </c>
+      <c r="H61" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I61" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J61" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K61" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L61" s="60"/>
+      <c r="M61" s="60"/>
+      <c r="N61" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O61" s="60"/>
+      <c r="P61" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q61" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R61" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S61" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T61" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U61" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V61" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W61" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X61" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y61" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z61" s="60"/>
+      <c r="AA61" s="60"/>
+      <c r="AB61" s="57">
+        <v>114</v>
+      </c>
+      <c r="AC61" s="60"/>
+    </row>
+    <row r="62" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="63" t="s">
+        <v>347</v>
+      </c>
+      <c r="B62" s="58">
+        <v>1</v>
+      </c>
+      <c r="C62" s="58" t="s">
+        <v>336</v>
+      </c>
+      <c r="D62" s="63">
+        <v>6767</v>
+      </c>
+      <c r="E62" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F62" s="58">
+        <v>1</v>
+      </c>
+      <c r="G62" s="72" t="s">
+        <v>315</v>
+      </c>
+      <c r="H62" s="63" t="s">
+        <v>309</v>
+      </c>
+      <c r="I62" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J62" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K62" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L62" s="60"/>
+      <c r="M62" s="60"/>
+      <c r="N62" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O62" s="60"/>
+      <c r="P62" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q62" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R62" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="S62" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="T62" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="U62" s="60" t="s">
+        <v>276</v>
+      </c>
+      <c r="V62" s="60"/>
+      <c r="W62" s="60"/>
+      <c r="X62" s="60"/>
+      <c r="Y62" s="60"/>
+      <c r="Z62" s="60"/>
+      <c r="AA62" s="60"/>
+      <c r="AB62" s="57" t="s">
+        <v>366</v>
+      </c>
+      <c r="AC62" s="60"/>
+    </row>
+    <row r="63" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="63" t="s">
+        <v>348</v>
+      </c>
+      <c r="B63" s="58">
+        <v>2</v>
+      </c>
+      <c r="C63" s="58" t="s">
+        <v>336</v>
+      </c>
+      <c r="D63" s="63">
+        <v>6768</v>
+      </c>
+      <c r="E63" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F63" s="58">
+        <v>1</v>
+      </c>
+      <c r="G63" s="72" t="s">
+        <v>315</v>
+      </c>
+      <c r="H63" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I63" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J63" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K63" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L63" s="60"/>
+      <c r="M63" s="60"/>
+      <c r="N63" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O63" s="60"/>
+      <c r="P63" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q63" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R63" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S63" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T63" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U63" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V63" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W63" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X63" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y63" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z63" s="60"/>
+      <c r="AA63" s="60"/>
+      <c r="AB63" s="57" t="s">
+        <v>367</v>
+      </c>
+      <c r="AC63" s="60"/>
+    </row>
+    <row r="64" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="63" t="s">
+        <v>349</v>
+      </c>
+      <c r="B64" s="58">
+        <v>2</v>
+      </c>
+      <c r="C64" s="58" t="s">
+        <v>337</v>
+      </c>
+      <c r="D64" s="63">
+        <v>6763</v>
+      </c>
+      <c r="E64" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F64" s="58">
+        <v>1</v>
+      </c>
+      <c r="G64" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H64" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I64" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J64" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K64" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L64" s="60"/>
+      <c r="M64" s="60"/>
+      <c r="N64" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O64" s="60"/>
+      <c r="P64" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q64" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R64" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S64" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T64" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U64" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V64" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W64" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X64" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y64" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z64" s="60"/>
+      <c r="AA64" s="60"/>
+      <c r="AB64" s="57" t="s">
+        <v>368</v>
+      </c>
+      <c r="AC64" s="60"/>
+    </row>
+    <row r="65" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="63" t="s">
+        <v>350</v>
+      </c>
+      <c r="B65" s="58">
+        <v>1</v>
+      </c>
+      <c r="C65" s="58" t="s">
+        <v>337</v>
+      </c>
+      <c r="D65" s="63">
+        <v>6729</v>
+      </c>
+      <c r="E65" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F65" s="58">
+        <v>1</v>
+      </c>
+      <c r="G65" s="72" t="s">
+        <v>364</v>
+      </c>
+      <c r="H65" s="63" t="s">
+        <v>309</v>
+      </c>
+      <c r="I65" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J65" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K65" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L65" s="60"/>
+      <c r="M65" s="60"/>
+      <c r="N65" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O65" s="60"/>
+      <c r="P65" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q65" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R65" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="S65" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="T65" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="U65" s="60" t="s">
+        <v>276</v>
+      </c>
+      <c r="V65" s="60"/>
+      <c r="W65" s="60"/>
+      <c r="X65" s="60"/>
+      <c r="Y65" s="60"/>
+      <c r="Z65" s="60"/>
+      <c r="AA65" s="60"/>
+      <c r="AB65" s="57" t="s">
+        <v>369</v>
+      </c>
+      <c r="AC65" s="60"/>
+    </row>
+    <row r="66" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="63" t="s">
+        <v>351</v>
+      </c>
+      <c r="B66" s="58">
+        <v>1</v>
+      </c>
+      <c r="C66" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="D66" s="63">
+        <v>6733</v>
+      </c>
+      <c r="E66" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F66" s="58">
+        <v>1</v>
+      </c>
+      <c r="G66" s="72" t="s">
+        <v>365</v>
+      </c>
+      <c r="H66" s="63" t="s">
+        <v>309</v>
+      </c>
+      <c r="I66" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J66" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K66" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L66" s="60"/>
+      <c r="M66" s="60"/>
+      <c r="N66" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O66" s="60"/>
+      <c r="P66" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q66" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R66" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="S66" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="T66" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="U66" s="60" t="s">
+        <v>276</v>
+      </c>
+      <c r="V66" s="60"/>
+      <c r="W66" s="60"/>
+      <c r="X66" s="60"/>
+      <c r="Y66" s="60"/>
+      <c r="Z66" s="60"/>
+      <c r="AA66" s="60"/>
+      <c r="AB66" s="57" t="s">
+        <v>370</v>
+      </c>
+      <c r="AC66" s="60"/>
+    </row>
+    <row r="67" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="63" t="s">
+        <v>352</v>
+      </c>
+      <c r="B67" s="58">
+        <v>2</v>
+      </c>
+      <c r="C67" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="D67" s="63">
+        <v>6779</v>
+      </c>
+      <c r="E67" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F67" s="58">
+        <v>1</v>
+      </c>
+      <c r="G67" s="71">
+        <v>2100</v>
+      </c>
+      <c r="H67" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I67" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J67" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K67" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L67" s="60"/>
+      <c r="M67" s="60"/>
+      <c r="N67" s="64">
+        <v>46090</v>
+      </c>
+      <c r="O67" s="60"/>
+      <c r="P67" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q67" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R67" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S67" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T67" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U67" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V67" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W67" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X67" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y67" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z67" s="60"/>
+      <c r="AA67" s="60"/>
+      <c r="AB67" s="57" t="s">
+        <v>371</v>
+      </c>
+      <c r="AC67" s="60"/>
+    </row>
+    <row r="68" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="63" t="s">
+        <v>353</v>
+      </c>
+      <c r="B68" s="58">
+        <v>8</v>
+      </c>
+      <c r="C68" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D68" s="63">
+        <v>6759</v>
+      </c>
+      <c r="E68" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F68" s="58">
+        <v>1</v>
+      </c>
+      <c r="G68" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H68" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I68" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J68" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K68" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L68" s="60"/>
+      <c r="M68" s="60"/>
+      <c r="N68" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O68" s="60"/>
+      <c r="P68" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q68" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R68" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S68" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T68" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U68" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V68" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W68" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X68" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y68" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z68" s="60"/>
+      <c r="AA68" s="60"/>
+      <c r="AB68" s="57">
+        <v>22</v>
+      </c>
+      <c r="AC68" s="60"/>
+    </row>
+    <row r="69" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="63" t="s">
+        <v>354</v>
+      </c>
+      <c r="B69" s="58">
+        <v>3</v>
+      </c>
+      <c r="C69" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D69" s="63">
+        <v>6754</v>
+      </c>
+      <c r="E69" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F69" s="58">
+        <v>1</v>
+      </c>
+      <c r="G69" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H69" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I69" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J69" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K69" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L69" s="60"/>
+      <c r="M69" s="60"/>
+      <c r="N69" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O69" s="60"/>
+      <c r="P69" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q69" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R69" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S69" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T69" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U69" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V69" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W69" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X69" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y69" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z69" s="60"/>
+      <c r="AA69" s="60"/>
+      <c r="AB69" s="57">
+        <v>24</v>
+      </c>
+      <c r="AC69" s="60"/>
+    </row>
+    <row r="70" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="63" t="s">
+        <v>355</v>
+      </c>
+      <c r="B70" s="58">
+        <v>9</v>
+      </c>
+      <c r="C70" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D70" s="63">
+        <v>6760</v>
+      </c>
+      <c r="E70" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F70" s="58">
+        <v>1</v>
+      </c>
+      <c r="G70" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H70" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I70" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J70" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K70" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L70" s="60"/>
+      <c r="M70" s="60"/>
+      <c r="N70" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O70" s="60"/>
+      <c r="P70" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q70" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R70" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S70" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T70" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U70" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V70" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W70" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X70" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y70" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z70" s="60"/>
+      <c r="AA70" s="60"/>
+      <c r="AB70" s="57">
+        <v>25</v>
+      </c>
+      <c r="AC70" s="60"/>
+    </row>
+    <row r="71" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="63" t="s">
+        <v>356</v>
+      </c>
+      <c r="B71" s="58">
+        <v>4</v>
+      </c>
+      <c r="C71" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D71" s="63">
+        <v>6755</v>
+      </c>
+      <c r="E71" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F71" s="58">
+        <v>1</v>
+      </c>
+      <c r="G71" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H71" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I71" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J71" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K71" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L71" s="60"/>
+      <c r="M71" s="60"/>
+      <c r="N71" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O71" s="60"/>
+      <c r="P71" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q71" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R71" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S71" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T71" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U71" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V71" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W71" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X71" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y71" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z71" s="60"/>
+      <c r="AA71" s="60"/>
+      <c r="AB71" s="57">
+        <v>30</v>
+      </c>
+      <c r="AC71" s="60"/>
+    </row>
+    <row r="72" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="63" t="s">
+        <v>357</v>
+      </c>
+      <c r="B72" s="58">
+        <v>7</v>
+      </c>
+      <c r="C72" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D72" s="63">
+        <v>6758</v>
+      </c>
+      <c r="E72" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F72" s="58">
+        <v>1</v>
+      </c>
+      <c r="G72" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H72" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I72" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J72" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K72" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L72" s="60"/>
+      <c r="M72" s="60"/>
+      <c r="N72" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O72" s="60"/>
+      <c r="P72" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q72" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R72" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S72" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T72" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U72" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V72" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W72" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X72" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y72" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z72" s="60"/>
+      <c r="AA72" s="60"/>
+      <c r="AB72" s="57">
+        <v>32</v>
+      </c>
+      <c r="AC72" s="60"/>
+    </row>
+    <row r="73" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="63" t="s">
+        <v>358</v>
+      </c>
+      <c r="B73" s="58">
+        <v>6</v>
+      </c>
+      <c r="C73" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D73" s="63">
+        <v>6757</v>
+      </c>
+      <c r="E73" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F73" s="58">
+        <v>1</v>
+      </c>
+      <c r="G73" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H73" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I73" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J73" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K73" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L73" s="60"/>
+      <c r="M73" s="60"/>
+      <c r="N73" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O73" s="60"/>
+      <c r="P73" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q73" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R73" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S73" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T73" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U73" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V73" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W73" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X73" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y73" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z73" s="60"/>
+      <c r="AA73" s="60"/>
+      <c r="AB73" s="57">
+        <v>46</v>
+      </c>
+      <c r="AC73" s="60"/>
+    </row>
+    <row r="74" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="B74" s="58">
+        <v>2</v>
+      </c>
+      <c r="C74" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D74" s="63">
+        <v>6753</v>
+      </c>
+      <c r="E74" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F74" s="58">
+        <v>1</v>
+      </c>
+      <c r="G74" s="72" t="s">
+        <v>315</v>
+      </c>
+      <c r="H74" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I74" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J74" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K74" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L74" s="60"/>
+      <c r="M74" s="60"/>
+      <c r="N74" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O74" s="60"/>
+      <c r="P74" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q74" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R74" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S74" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T74" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U74" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V74" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W74" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X74" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y74" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z74" s="60"/>
+      <c r="AA74" s="60"/>
+      <c r="AB74" s="57" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC74" s="60"/>
+    </row>
+    <row r="75" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="63" t="s">
+        <v>360</v>
+      </c>
+      <c r="B75" s="58">
+        <v>5</v>
+      </c>
+      <c r="C75" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D75" s="63">
+        <v>6756</v>
+      </c>
+      <c r="E75" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F75" s="58">
+        <v>1</v>
+      </c>
+      <c r="G75" s="72" t="s">
+        <v>315</v>
+      </c>
+      <c r="H75" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I75" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J75" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K75" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L75" s="60"/>
+      <c r="M75" s="60"/>
+      <c r="N75" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O75" s="60"/>
+      <c r="P75" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q75" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R75" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S75" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T75" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U75" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V75" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W75" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X75" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y75" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z75" s="60"/>
+      <c r="AA75" s="60"/>
+      <c r="AB75" s="57" t="s">
+        <v>373</v>
+      </c>
+      <c r="AC75" s="60"/>
+    </row>
+    <row r="76" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="63" t="s">
+        <v>361</v>
+      </c>
+      <c r="B76" s="58">
+        <v>2</v>
+      </c>
+      <c r="C76" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D76" s="63"/>
+      <c r="E76" s="58" t="s">
+        <v>363</v>
+      </c>
+      <c r="F76" s="58">
+        <v>1</v>
+      </c>
+      <c r="G76" s="72" t="s">
+        <v>315</v>
+      </c>
+      <c r="H76" s="63" t="s">
+        <v>309</v>
+      </c>
+      <c r="I76" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J76" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K76" s="60" t="s">
+        <v>242</v>
+      </c>
+      <c r="L76" s="60"/>
+      <c r="M76" s="60"/>
+      <c r="N76" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O76" s="60"/>
+      <c r="P76" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q76" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R76" s="60" t="s">
+        <v>267</v>
+      </c>
+      <c r="S76" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="T76" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="U76" s="60" t="s">
+        <v>276</v>
+      </c>
+      <c r="V76" s="60"/>
+      <c r="W76" s="60"/>
+      <c r="X76" s="60"/>
+      <c r="Y76" s="60"/>
+      <c r="Z76" s="60"/>
+      <c r="AA76" s="60"/>
+      <c r="AB76" s="57" t="s">
+        <v>374</v>
+      </c>
+      <c r="AC76" s="60"/>
+    </row>
+    <row r="77" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="63" t="s">
+        <v>362</v>
+      </c>
+      <c r="B77" s="58">
+        <v>1</v>
+      </c>
+      <c r="C77" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="D77" s="63">
+        <v>6730</v>
+      </c>
+      <c r="E77" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="F77" s="58">
+        <v>1</v>
+      </c>
+      <c r="G77" s="72" t="s">
+        <v>330</v>
+      </c>
+      <c r="H77" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="I77" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J77" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="K77" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="L77" s="60"/>
+      <c r="M77" s="60"/>
+      <c r="N77" s="64">
+        <v>46101</v>
+      </c>
+      <c r="O77" s="60"/>
+      <c r="P77" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q77" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="R77" s="58" t="s">
+        <v>267</v>
+      </c>
+      <c r="S77" s="58" t="s">
+        <v>269</v>
+      </c>
+      <c r="T77" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="U77" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="V77" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="W77" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="X77" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y77" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z77" s="60"/>
+      <c r="AA77" s="60"/>
+      <c r="AB77" s="57" t="s">
+        <v>375</v>
+      </c>
+      <c r="AC77" s="60"/>
+    </row>
+    <row r="78" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H78" s="73"/>
+    </row>
+    <row r="79" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
+  <conditionalFormatting sqref="D30:D32">
+    <cfRule type="expression" dxfId="103" priority="64">
+      <formula>$P30="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:D32">
+    <cfRule type="containsText" dxfId="102" priority="62" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="101" priority="63" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",D30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30:A32">
+    <cfRule type="expression" dxfId="100" priority="61">
+      <formula>$P30="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30:A32">
+    <cfRule type="containsText" dxfId="99" priority="59" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",A30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="98" priority="60" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",A30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB30:AB32">
+    <cfRule type="expression" dxfId="94" priority="55">
+      <formula>$P30="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB30:AB32">
+    <cfRule type="containsText" dxfId="93" priority="53" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",AB30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="92" priority="54" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",AB30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33:A43">
+    <cfRule type="expression" dxfId="88" priority="52">
+      <formula>$P33="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33:A43">
+    <cfRule type="containsText" dxfId="87" priority="50" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",A33)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="86" priority="51" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",A33)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D33:D43">
+    <cfRule type="expression" dxfId="54" priority="49">
+      <formula>$P33="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D33:D43">
+    <cfRule type="containsText" dxfId="53" priority="47" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",D33)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="52" priority="48" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",D33)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB33:AB43">
+    <cfRule type="expression" dxfId="51" priority="46">
+      <formula>$P33="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB33:AB43">
+    <cfRule type="containsText" dxfId="50" priority="44" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",AB33)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="49" priority="45" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",AB33)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N33:N45">
+    <cfRule type="expression" dxfId="45" priority="43">
+      <formula>$P33="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N33:N45">
+    <cfRule type="containsText" dxfId="44" priority="41" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",N33)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="43" priority="42" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",N33)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O33:O35">
+    <cfRule type="expression" dxfId="42" priority="40">
+      <formula>$P33="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O33:O35">
+    <cfRule type="containsText" dxfId="41" priority="38" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",O33)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="39" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",O33)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O37:O43">
+    <cfRule type="expression" dxfId="36" priority="37">
+      <formula>$P37="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O37:O43">
+    <cfRule type="containsText" dxfId="35" priority="35" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",O37)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="36" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",O37)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C45">
+    <cfRule type="expression" dxfId="33" priority="34">
+      <formula>$P45="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C45">
+    <cfRule type="containsText" dxfId="32" priority="32" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",C45)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="33" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",C45)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C46:C49">
+    <cfRule type="expression" dxfId="30" priority="31">
+      <formula>$P46="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C46:C49">
+    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",C46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",C46)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C55">
+    <cfRule type="expression" dxfId="27" priority="27">
+      <formula>$P55="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C56:C77">
+    <cfRule type="expression" dxfId="26" priority="28">
+      <formula>$P56="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C55:C77">
+    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",C55)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D55">
+    <cfRule type="expression" dxfId="23" priority="23">
+      <formula>$P55="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D56:D77">
+    <cfRule type="expression" dxfId="22" priority="24">
+      <formula>$P56="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D55:D77">
+    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",D55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",D55)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="expression" dxfId="19" priority="19">
+      <formula>$P55="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56:A77">
+    <cfRule type="expression" dxfId="18" priority="20">
+      <formula>$P56="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55:A77">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",A55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",A55)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H58 H60 H62 H65:H66 H76">
+    <cfRule type="expression" dxfId="14" priority="16">
+      <formula>$P58="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H58 H60 H62 H65:H66 H76">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",H58)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G59:G60 G67">
+    <cfRule type="expression" dxfId="10" priority="12">
+      <formula>$P59="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G59:G60 G67">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",G59)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N55">
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>$P55="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N56:N77">
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>$P56="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N55:N77">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",N55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",N55)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB55">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$P55="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB56:AB77">
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>$P56="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB55:AB77">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",AB55)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2283669-2237-4CB1-9151-A1FB1DD40835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C976EC-4C0E-46B9-9698-EA34B1A371F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
   <sheets>
     <sheet name="BAGACEIRAS" sheetId="2" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6298" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6370" uniqueCount="384">
   <si>
     <t>O.S.</t>
   </si>
@@ -1218,6 +1218,30 @@
   <si>
     <t>P8</t>
   </si>
+  <si>
+    <t>Pagrisa</t>
+  </si>
+  <si>
+    <t>Chapa</t>
+  </si>
+  <si>
+    <t>PENTE SUP. CHAPA RETO FR 2" - 66"</t>
+  </si>
+  <si>
+    <t>PENTE SUP. CHAPA RETO FR 1.1/2" - 66"</t>
+  </si>
+  <si>
+    <t>PENTE INF. CONVENCIONAL FR 2" - 66"</t>
+  </si>
+  <si>
+    <t>PENTE INF. CONVENCIONAL FR 1.1/2" - 66"</t>
+  </si>
+  <si>
+    <t>Estoque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AG. DESENHO </t>
+  </si>
 </sst>
 </file>
 
@@ -1434,7 +1458,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1586,59 +1610,39 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Vírgula 2" xfId="1" xr:uid="{8785E80A-1CD4-4609-8517-D88B418F2B05}"/>
   </cellStyles>
-  <dxfs count="247">
+  <dxfs count="216">
     <dxf>
       <fill>
         <patternFill>
@@ -1806,922 +1810,6 @@
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -5142,6 +4230,705 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -5156,7 +4943,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="246" dataDxfId="245">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="184" dataDxfId="183">
   <autoFilter ref="A1:AI114" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}">
     <filterColumn colId="0">
       <filters>
@@ -5165,179 +4952,179 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="244"/>
-    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="243"/>
-    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="242"/>
-    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="241"/>
-    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="240"/>
-    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="239"/>
-    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="238"/>
-    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="237"/>
-    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="236"/>
-    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="235"/>
-    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="234">
+    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="182"/>
+    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="181"/>
+    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="180"/>
+    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="179"/>
+    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="178"/>
+    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="177"/>
+    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="176"/>
+    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="175"/>
+    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="174"/>
+    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="173"/>
+    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="172">
       <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
 Fundido]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="233"/>
-    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="232"/>
-    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="231"/>
-    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="230">
+    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="171"/>
+    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="170"/>
+    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="169"/>
+    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="168">
       <calculatedColumnFormula>Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="229">
+    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="167">
       <calculatedColumnFormula>IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="228">
+    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="166">
       <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
 Entrega]],1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="227"/>
-    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="226"/>
-    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="225"/>
-    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="224"/>
-    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="223"/>
-    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="222"/>
-    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="221"/>
-    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="220"/>
-    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="219"/>
-    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="218"/>
-    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="217"/>
-    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="216">
+    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="165"/>
+    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="164"/>
+    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="163"/>
+    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="162"/>
+    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="161"/>
+    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="160"/>
+    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="159"/>
+    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="158"/>
+    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="157"/>
+    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="156"/>
+    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="155"/>
+    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="154">
       <calculatedColumnFormula>IF(L2="","AG. FUNDIDO",IF(U2="AG","AG. USINAGEM","EM USINAGEM"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="215"/>
-    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="214"/>
-    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="213"/>
-    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="212"/>
-    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="211"/>
-    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="210"/>
+    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="153"/>
+    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="152"/>
+    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="151"/>
+    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="150"/>
+    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="149"/>
+    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="148"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V143" totalsRowShown="0" headerRowDxfId="209" dataDxfId="208">
-  <autoFilter ref="A1:V143" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V151" totalsRowShown="0" headerRowDxfId="147" dataDxfId="146">
+  <autoFilter ref="A1:V151" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="207"/>
-    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="206"/>
-    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="205"/>
-    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="204"/>
-    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="203"/>
-    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="202"/>
-    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="201"/>
-    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="200"/>
-    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="199"/>
-    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="198"/>
-    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="197">
+    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="140"/>
+    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="139"/>
+    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="138"/>
+    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="137"/>
+    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="136"/>
+    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="135">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="196"/>
-    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="195"/>
-    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="194"/>
-    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="193"/>
-    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="192"/>
-    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="191">
+    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="134"/>
+    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="133"/>
+    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="132"/>
+    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="131"/>
+    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="130"/>
+    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="129">
       <calculatedColumnFormula>Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="190">
+    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="128">
       <calculatedColumnFormula>IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="189">
+    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="127">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="188"/>
-    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="187"/>
-    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="186"/>
+    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="126"/>
+    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="125"/>
+    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="124"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E9C3BD9-7BAA-49FB-9F98-CFD415149194}" name="Tabela13" displayName="Tabela13" ref="A1:Z39" totalsRowShown="0" headerRowDxfId="185" dataDxfId="184">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E9C3BD9-7BAA-49FB-9F98-CFD415149194}" name="Tabela13" displayName="Tabela13" ref="A1:Z39" totalsRowShown="0" headerRowDxfId="123" dataDxfId="122">
   <autoFilter ref="A1:Z39" xr:uid="{2AC5416C-4E1B-4478-8A2A-B698870CAB96}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{9A983B4E-3365-4153-9B40-D7FE26E8B98F}" name="PV " dataDxfId="183"/>
-    <tableColumn id="2" xr3:uid="{4F16CD54-AAD4-4149-8D48-CC3FFEA93AA5}" name="Item" dataDxfId="182"/>
-    <tableColumn id="3" xr3:uid="{27DB1DBC-B9DA-4067-9696-8CA5ACAAA450}" name="OS" dataDxfId="181"/>
-    <tableColumn id="4" xr3:uid="{02C5E283-8ABF-44F8-B3B8-C3F186B4DF63}" name="Item2" dataDxfId="180"/>
-    <tableColumn id="5" xr3:uid="{B1051CBE-EA72-4A43-8721-8756F3E2C9C9}" name="Cliente" dataDxfId="179"/>
-    <tableColumn id="6" xr3:uid="{D81DBB81-327B-4EA3-89A3-229D33F3C14C}" name="Cod." dataDxfId="178"/>
-    <tableColumn id="7" xr3:uid="{05B3DC4D-BFB9-401F-A18F-0D1B8527380B}" name="Seq." dataDxfId="177"/>
-    <tableColumn id="8" xr3:uid="{9EBF401A-1F29-4CB3-BFA3-F2B326242AB0}" name="Descrição" dataDxfId="176"/>
-    <tableColumn id="14" xr3:uid="{85D3397C-7F95-49C7-BFFB-35012CA3B716}" name="Qtd." dataDxfId="175"/>
-    <tableColumn id="9" xr3:uid="{0D04583C-577A-446B-9773-A173C5C1C166}" name="Data Prev._x000a_Fundido" dataDxfId="174"/>
-    <tableColumn id="10" xr3:uid="{935D3899-0C12-4408-89DF-490A507F79BA}" name="Data Real_x000a_Fundido" dataDxfId="173"/>
-    <tableColumn id="11" xr3:uid="{0F06941F-293B-4C15-9764-BB3495C5D3BD}" name="Data Prev._x000a_Entrega" dataDxfId="172"/>
-    <tableColumn id="12" xr3:uid="{92FF2511-5498-45BF-9B68-94DBEA588C5A}" name="Data Real_x000a_Entrega" dataDxfId="171"/>
-    <tableColumn id="25" xr3:uid="{98545C7E-9674-485C-A07D-715E8945B00E}" name="Falta_x000a_Dias" dataDxfId="170">
+    <tableColumn id="1" xr3:uid="{9A983B4E-3365-4153-9B40-D7FE26E8B98F}" name="PV " dataDxfId="121"/>
+    <tableColumn id="2" xr3:uid="{4F16CD54-AAD4-4149-8D48-CC3FFEA93AA5}" name="Item" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{27DB1DBC-B9DA-4067-9696-8CA5ACAAA450}" name="OS" dataDxfId="119"/>
+    <tableColumn id="4" xr3:uid="{02C5E283-8ABF-44F8-B3B8-C3F186B4DF63}" name="Item2" dataDxfId="118"/>
+    <tableColumn id="5" xr3:uid="{B1051CBE-EA72-4A43-8721-8756F3E2C9C9}" name="Cliente" dataDxfId="117"/>
+    <tableColumn id="6" xr3:uid="{D81DBB81-327B-4EA3-89A3-229D33F3C14C}" name="Cod." dataDxfId="116"/>
+    <tableColumn id="7" xr3:uid="{05B3DC4D-BFB9-401F-A18F-0D1B8527380B}" name="Seq." dataDxfId="115"/>
+    <tableColumn id="8" xr3:uid="{9EBF401A-1F29-4CB3-BFA3-F2B326242AB0}" name="Descrição" dataDxfId="114"/>
+    <tableColumn id="14" xr3:uid="{85D3397C-7F95-49C7-BFFB-35012CA3B716}" name="Qtd." dataDxfId="113"/>
+    <tableColumn id="9" xr3:uid="{0D04583C-577A-446B-9773-A173C5C1C166}" name="Data Prev._x000a_Fundido" dataDxfId="112"/>
+    <tableColumn id="10" xr3:uid="{935D3899-0C12-4408-89DF-490A507F79BA}" name="Data Real_x000a_Fundido" dataDxfId="111"/>
+    <tableColumn id="11" xr3:uid="{0F06941F-293B-4C15-9764-BB3495C5D3BD}" name="Data Prev._x000a_Entrega" dataDxfId="110"/>
+    <tableColumn id="12" xr3:uid="{92FF2511-5498-45BF-9B68-94DBEA588C5A}" name="Data Real_x000a_Entrega" dataDxfId="109"/>
+    <tableColumn id="25" xr3:uid="{98545C7E-9674-485C-A07D-715E8945B00E}" name="Falta_x000a_Dias" dataDxfId="108">
       <calculatedColumnFormula>Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{4EB63243-AA79-4695-93C8-CEA977B11387}" name="Indicador" dataDxfId="169">
+    <tableColumn id="27" xr3:uid="{4EB63243-AA79-4695-93C8-CEA977B11387}" name="Indicador" dataDxfId="107">
       <calculatedColumnFormula>IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7AB992C1-F70E-4469-85BB-EBB7763B2038}" name="Condição" dataDxfId="168"/>
-    <tableColumn id="24" xr3:uid="{B5965349-4BC8-4DF7-9EB4-857B6D471E8A}" name="Desenho_x000a_Previsão" dataDxfId="167"/>
-    <tableColumn id="13" xr3:uid="{FD827F61-5F7F-4B65-8A60-B59D23455B46}" name="Des." dataDxfId="166"/>
-    <tableColumn id="16" xr3:uid="{3D186A5F-076F-4232-B21C-37E58E5373B2}" name="Desb." dataDxfId="165"/>
-    <tableColumn id="17" xr3:uid="{6EEDF11E-F341-4B3E-8CD2-5595785C3427}" name="T.T." dataDxfId="164"/>
-    <tableColumn id="18" xr3:uid="{A84EFCF4-218F-4B17-8F46-8D5412141429}" name="Us. Final" dataDxfId="163"/>
-    <tableColumn id="19" xr3:uid="{EBD50149-594D-440E-BFBB-E73ACAF7B6F8}" name="Fundo D." dataDxfId="162"/>
-    <tableColumn id="20" xr3:uid="{91BE30ED-20C1-4F30-9041-45A50CCA04F0}" name="Acabam." dataDxfId="161"/>
-    <tableColumn id="21" xr3:uid="{A1A12DF6-FC3D-4466-8284-DBD00DEAF994}" name="Liberação" dataDxfId="160"/>
-    <tableColumn id="22" xr3:uid="{436F202D-DCF4-4376-A550-2541153BD99F}" name="Status Usinagem" dataDxfId="159">
+    <tableColumn id="15" xr3:uid="{7AB992C1-F70E-4469-85BB-EBB7763B2038}" name="Condição" dataDxfId="106"/>
+    <tableColumn id="24" xr3:uid="{B5965349-4BC8-4DF7-9EB4-857B6D471E8A}" name="Desenho_x000a_Previsão" dataDxfId="105"/>
+    <tableColumn id="13" xr3:uid="{FD827F61-5F7F-4B65-8A60-B59D23455B46}" name="Des." dataDxfId="104"/>
+    <tableColumn id="16" xr3:uid="{3D186A5F-076F-4232-B21C-37E58E5373B2}" name="Desb." dataDxfId="103"/>
+    <tableColumn id="17" xr3:uid="{6EEDF11E-F341-4B3E-8CD2-5595785C3427}" name="T.T." dataDxfId="102"/>
+    <tableColumn id="18" xr3:uid="{A84EFCF4-218F-4B17-8F46-8D5412141429}" name="Us. Final" dataDxfId="101"/>
+    <tableColumn id="19" xr3:uid="{EBD50149-594D-440E-BFBB-E73ACAF7B6F8}" name="Fundo D." dataDxfId="100"/>
+    <tableColumn id="20" xr3:uid="{91BE30ED-20C1-4F30-9041-45A50CCA04F0}" name="Acabam." dataDxfId="99"/>
+    <tableColumn id="21" xr3:uid="{A1A12DF6-FC3D-4466-8284-DBD00DEAF994}" name="Liberação" dataDxfId="98"/>
+    <tableColumn id="22" xr3:uid="{436F202D-DCF4-4376-A550-2541153BD99F}" name="Status Usinagem" dataDxfId="97">
       <calculatedColumnFormula>IF(K2="","AG. FUNDIDO",IF(X2="OK","LIBERADA","EM USINAGEM"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{F71E5739-8B79-47B3-9A24-E2E4D1DD46E6}" name="Observação" dataDxfId="158"/>
+    <tableColumn id="23" xr3:uid="{F71E5739-8B79-47B3-9A24-E2E4D1DD46E6}" name="Observação" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T89" totalsRowShown="0" headerRowDxfId="157" dataDxfId="156">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T89" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="A1:T89" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{56D3DA8E-4CA8-4DC6-8208-BAB93CDE51C0}" name="PV" dataDxfId="155"/>
-    <tableColumn id="2" xr3:uid="{B14AE1B6-8C05-4725-BF42-3DBDB37AA4E3}" name="item" dataDxfId="154"/>
-    <tableColumn id="3" xr3:uid="{24FE1002-C88A-4623-8882-5F391ECAB319}" name="OS" dataDxfId="153"/>
-    <tableColumn id="4" xr3:uid="{4ED6249C-2003-4F3F-AE5A-67316434275E}" name="Item2" dataDxfId="152"/>
-    <tableColumn id="5" xr3:uid="{6CE5B2E1-F32C-4D32-93F0-A17C05267ADB}" name="Cliente" dataDxfId="151"/>
-    <tableColumn id="6" xr3:uid="{605F51C8-79D3-407B-8642-02F131952C62}" name="Qtd." dataDxfId="150"/>
-    <tableColumn id="7" xr3:uid="{3AC59FFB-0DC5-477B-B780-880A1FD84811}" name="Peça" dataDxfId="149"/>
-    <tableColumn id="8" xr3:uid="{2EE377A7-B17C-442E-A107-012310DB953B}" name="Seq." dataDxfId="148"/>
-    <tableColumn id="9" xr3:uid="{5366226E-7F3B-42E4-AC0C-86C659505CC8}" name="Descrição" dataDxfId="147"/>
-    <tableColumn id="10" xr3:uid="{B0D229C5-5F5A-4951-A0B4-FEA62AEFBB36}" name="Prazo_x000a_Fundido" dataDxfId="146"/>
-    <tableColumn id="11" xr3:uid="{8AE09F18-EB17-4537-8FBD-24671292144B}" name="Pz Fundido_x000a_Real" dataDxfId="145"/>
-    <tableColumn id="12" xr3:uid="{965E0234-7E4B-482D-8943-132C1520AD21}" name="Prazo_x000a_Entrega" dataDxfId="144"/>
-    <tableColumn id="13" xr3:uid="{D70BE32E-86AF-4C0F-893D-AC939E731683}" name="Pz Entrega_x000a_Real" dataDxfId="143"/>
-    <tableColumn id="15" xr3:uid="{2FE637E5-62E2-4AE9-AE5A-BC264DC93D4F}" name="Falta_x000a_Dias" dataDxfId="142">
+    <tableColumn id="1" xr3:uid="{56D3DA8E-4CA8-4DC6-8208-BAB93CDE51C0}" name="PV" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{B14AE1B6-8C05-4725-BF42-3DBDB37AA4E3}" name="item" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{24FE1002-C88A-4623-8882-5F391ECAB319}" name="OS" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{4ED6249C-2003-4F3F-AE5A-67316434275E}" name="Item2" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{6CE5B2E1-F32C-4D32-93F0-A17C05267ADB}" name="Cliente" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{605F51C8-79D3-407B-8642-02F131952C62}" name="Qtd." dataDxfId="88"/>
+    <tableColumn id="7" xr3:uid="{3AC59FFB-0DC5-477B-B780-880A1FD84811}" name="Peça" dataDxfId="87"/>
+    <tableColumn id="8" xr3:uid="{2EE377A7-B17C-442E-A107-012310DB953B}" name="Seq." dataDxfId="86"/>
+    <tableColumn id="9" xr3:uid="{5366226E-7F3B-42E4-AC0C-86C659505CC8}" name="Descrição" dataDxfId="85"/>
+    <tableColumn id="10" xr3:uid="{B0D229C5-5F5A-4951-A0B4-FEA62AEFBB36}" name="Prazo_x000a_Fundido" dataDxfId="84"/>
+    <tableColumn id="11" xr3:uid="{8AE09F18-EB17-4537-8FBD-24671292144B}" name="Pz Fundido_x000a_Real" dataDxfId="83"/>
+    <tableColumn id="12" xr3:uid="{965E0234-7E4B-482D-8943-132C1520AD21}" name="Prazo_x000a_Entrega" dataDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{D70BE32E-86AF-4C0F-893D-AC939E731683}" name="Pz Entrega_x000a_Real" dataDxfId="81"/>
+    <tableColumn id="15" xr3:uid="{2FE637E5-62E2-4AE9-AE5A-BC264DC93D4F}" name="Falta_x000a_Dias" dataDxfId="80">
       <calculatedColumnFormula>Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{23AEF4D3-817F-4A15-AFBA-EC837E4BE1AE}" name="Indicador" dataDxfId="141">
+    <tableColumn id="14" xr3:uid="{23AEF4D3-817F-4A15-AFBA-EC837E4BE1AE}" name="Indicador" dataDxfId="79">
       <calculatedColumnFormula>IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{78F55B7C-8E60-49C5-B1F7-B023E76BDA6E}" name="Condição" dataDxfId="140"/>
-    <tableColumn id="20" xr3:uid="{A889C1FB-2FE0-407A-B849-FEB9F2CA4F96}" name="Desenho_x000a_Previsão" dataDxfId="139"/>
-    <tableColumn id="19" xr3:uid="{FB1E21D0-A118-422F-AA5B-F56FFBA7B5E4}" name="Des." dataDxfId="138"/>
-    <tableColumn id="17" xr3:uid="{C14325D6-C653-45B3-B85F-6AF107A71546}" name="Status" dataDxfId="137"/>
-    <tableColumn id="18" xr3:uid="{C6F7CA6A-B8B3-4E22-B3E8-05FFB1A03AB6}" name="Observação" dataDxfId="136"/>
+    <tableColumn id="16" xr3:uid="{78F55B7C-8E60-49C5-B1F7-B023E76BDA6E}" name="Condição" dataDxfId="78"/>
+    <tableColumn id="20" xr3:uid="{A889C1FB-2FE0-407A-B849-FEB9F2CA4F96}" name="Desenho_x000a_Previsão" dataDxfId="77"/>
+    <tableColumn id="19" xr3:uid="{FB1E21D0-A118-422F-AA5B-F56FFBA7B5E4}" name="Des." dataDxfId="76"/>
+    <tableColumn id="17" xr3:uid="{C14325D6-C653-45B3-B85F-6AF107A71546}" name="Status" dataDxfId="75"/>
+    <tableColumn id="18" xr3:uid="{C6F7CA6A-B8B3-4E22-B3E8-05FFB1A03AB6}" name="Observação" dataDxfId="74"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}" name="Tabela6" displayName="Tabela6" ref="A1:AC77" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}" name="Tabela6" displayName="Tabela6" ref="A1:AC77" totalsRowShown="0" headerRowDxfId="215" dataDxfId="214">
   <autoFilter ref="A1:AC77" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}">
     <filterColumn colId="2">
       <filters>
@@ -5347,42 +5134,42 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="29">
-    <tableColumn id="1" xr3:uid="{C25E2119-68FD-4765-BAFB-8CC2FA75E790}" name="PV" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{39E67E43-7C76-4E6C-9319-15A91DE1C08C}" name="Item" dataDxfId="84"/>
-    <tableColumn id="4" xr3:uid="{5B6759FC-B832-438E-B60C-770FAF7723FA}" name="Cliente" dataDxfId="83"/>
-    <tableColumn id="5" xr3:uid="{20CFBF4C-4BD9-4F05-86D4-8A4AFFC243B2}" name="_x000a_O.S./Peça" dataDxfId="82"/>
-    <tableColumn id="6" xr3:uid="{3994BD48-BFFD-46D2-9740-EDD282F2590D}" name="Descrição" dataDxfId="81"/>
-    <tableColumn id="7" xr3:uid="{261AA518-FC82-431F-8839-D26554B59355}" name="Qtde." dataDxfId="80"/>
-    <tableColumn id="24" xr3:uid="{0C566A21-B9D9-4AD7-A8B3-328E480EA286}" name="Bit" dataDxfId="79"/>
-    <tableColumn id="17" xr3:uid="{7631FA30-8167-4961-B0E8-981A96ADEF58}" name="Tipo" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{4F794446-D6E6-4C06-B881-9408CC542675}" name="Pos." dataDxfId="77"/>
-    <tableColumn id="26" xr3:uid="{C41F63A6-DC4C-42FE-A13B-3E56F237270D}" name="Terno" dataDxfId="76"/>
-    <tableColumn id="16" xr3:uid="{FF0A908E-E8EE-4CA0-96FA-38C032BFEFDE}" name="Forma" dataDxfId="75"/>
-    <tableColumn id="9" xr3:uid="{DE0283F8-D4F6-449C-A9CA-7DBCB898DFD9}" name="Prazo_x000a_Fund" dataDxfId="74"/>
-    <tableColumn id="10" xr3:uid="{663D9716-4C25-4ACC-A105-E9E7A474BCE6}" name="Prazo_x000a_Fund Real" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{6EF58C27-546C-4B57-B05D-BB07C2046388}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="72"/>
-    <tableColumn id="12" xr3:uid="{AC626966-9CA5-4150-82F1-50338494E847}" name="Pz Entrega_x000a_Real" dataDxfId="71"/>
-    <tableColumn id="13" xr3:uid="{506EC589-7ED2-4A3B-BED8-6CA8F57277E1}" name="Desenho_x000a_Previsão" dataDxfId="70"/>
-    <tableColumn id="14" xr3:uid="{A31AB572-7F13-4A5C-A42E-7E7A20433BDA}" name="Des." dataDxfId="69"/>
-    <tableColumn id="33" xr3:uid="{9D21190D-5788-4F29-AED2-63644BCE6C32}" name="OP1" dataDxfId="68"/>
-    <tableColumn id="30" xr3:uid="{6C8FD4D3-300E-4009-A264-D6FBC780DE60}" name="OP2" dataDxfId="67"/>
-    <tableColumn id="28" xr3:uid="{533BCCB9-B72A-4E3A-BE20-626EE2E49D83}" name="OP3" dataDxfId="66"/>
-    <tableColumn id="27" xr3:uid="{58435D6B-01D7-44DD-9B21-62EB23C9AA4F}" name="OP4" dataDxfId="65"/>
-    <tableColumn id="25" xr3:uid="{B00B175A-D2BA-4783-8EBD-A000C46B6055}" name="OP5" dataDxfId="64"/>
-    <tableColumn id="20" xr3:uid="{1C48207C-2D30-42CB-BD4E-0C9B569C9BCB}" name="OP6" dataDxfId="63"/>
-    <tableColumn id="35" xr3:uid="{5857075F-D742-43D2-AD1F-F2BB8219D8E7}" name="OP7" dataDxfId="62"/>
-    <tableColumn id="15" xr3:uid="{46F62312-EE93-4C00-9352-8A9BF48479C9}" name="OP8" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{81AAED83-3114-4366-BECD-21F933A26FE9}" name="OP9" dataDxfId="60"/>
-    <tableColumn id="18" xr3:uid="{F5387D14-C7D5-4022-901B-04E5D65304C7}" name="Status_x000a_Camisa" dataDxfId="59"/>
-    <tableColumn id="32" xr3:uid="{BEC53105-CFFD-422E-9C30-4E4BC1816678}" name="Nº Eixo" dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{A08285BC-8B0E-4492-A6AF-090B851B036D}" name="Observação" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{C25E2119-68FD-4765-BAFB-8CC2FA75E790}" name="PV" dataDxfId="213"/>
+    <tableColumn id="2" xr3:uid="{39E67E43-7C76-4E6C-9319-15A91DE1C08C}" name="Item" dataDxfId="212"/>
+    <tableColumn id="4" xr3:uid="{5B6759FC-B832-438E-B60C-770FAF7723FA}" name="Cliente" dataDxfId="211"/>
+    <tableColumn id="5" xr3:uid="{20CFBF4C-4BD9-4F05-86D4-8A4AFFC243B2}" name="_x000a_O.S./Peça" dataDxfId="210"/>
+    <tableColumn id="6" xr3:uid="{3994BD48-BFFD-46D2-9740-EDD282F2590D}" name="Descrição" dataDxfId="209"/>
+    <tableColumn id="7" xr3:uid="{261AA518-FC82-431F-8839-D26554B59355}" name="Qtde." dataDxfId="208"/>
+    <tableColumn id="24" xr3:uid="{0C566A21-B9D9-4AD7-A8B3-328E480EA286}" name="Bit" dataDxfId="207"/>
+    <tableColumn id="17" xr3:uid="{7631FA30-8167-4961-B0E8-981A96ADEF58}" name="Tipo" dataDxfId="206"/>
+    <tableColumn id="3" xr3:uid="{4F794446-D6E6-4C06-B881-9408CC542675}" name="Pos." dataDxfId="205"/>
+    <tableColumn id="26" xr3:uid="{C41F63A6-DC4C-42FE-A13B-3E56F237270D}" name="Terno" dataDxfId="204"/>
+    <tableColumn id="16" xr3:uid="{FF0A908E-E8EE-4CA0-96FA-38C032BFEFDE}" name="Forma" dataDxfId="203"/>
+    <tableColumn id="9" xr3:uid="{DE0283F8-D4F6-449C-A9CA-7DBCB898DFD9}" name="Prazo_x000a_Fund" dataDxfId="202"/>
+    <tableColumn id="10" xr3:uid="{663D9716-4C25-4ACC-A105-E9E7A474BCE6}" name="Prazo_x000a_Fund Real" dataDxfId="201"/>
+    <tableColumn id="11" xr3:uid="{6EF58C27-546C-4B57-B05D-BB07C2046388}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="200"/>
+    <tableColumn id="12" xr3:uid="{AC626966-9CA5-4150-82F1-50338494E847}" name="Pz Entrega_x000a_Real" dataDxfId="199"/>
+    <tableColumn id="13" xr3:uid="{506EC589-7ED2-4A3B-BED8-6CA8F57277E1}" name="Desenho_x000a_Previsão" dataDxfId="198"/>
+    <tableColumn id="14" xr3:uid="{A31AB572-7F13-4A5C-A42E-7E7A20433BDA}" name="Des." dataDxfId="197"/>
+    <tableColumn id="33" xr3:uid="{9D21190D-5788-4F29-AED2-63644BCE6C32}" name="OP1" dataDxfId="196"/>
+    <tableColumn id="30" xr3:uid="{6C8FD4D3-300E-4009-A264-D6FBC780DE60}" name="OP2" dataDxfId="195"/>
+    <tableColumn id="28" xr3:uid="{533BCCB9-B72A-4E3A-BE20-626EE2E49D83}" name="OP3" dataDxfId="194"/>
+    <tableColumn id="27" xr3:uid="{58435D6B-01D7-44DD-9B21-62EB23C9AA4F}" name="OP4" dataDxfId="193"/>
+    <tableColumn id="25" xr3:uid="{B00B175A-D2BA-4783-8EBD-A000C46B6055}" name="OP5" dataDxfId="192"/>
+    <tableColumn id="20" xr3:uid="{1C48207C-2D30-42CB-BD4E-0C9B569C9BCB}" name="OP6" dataDxfId="191"/>
+    <tableColumn id="35" xr3:uid="{5857075F-D742-43D2-AD1F-F2BB8219D8E7}" name="OP7" dataDxfId="190"/>
+    <tableColumn id="15" xr3:uid="{46F62312-EE93-4C00-9352-8A9BF48479C9}" name="OP8" dataDxfId="189"/>
+    <tableColumn id="8" xr3:uid="{81AAED83-3114-4366-BECD-21F933A26FE9}" name="OP9" dataDxfId="188"/>
+    <tableColumn id="18" xr3:uid="{F5387D14-C7D5-4022-901B-04E5D65304C7}" name="Status_x000a_Camisa" dataDxfId="187"/>
+    <tableColumn id="32" xr3:uid="{BEC53105-CFFD-422E-9C30-4E4BC1816678}" name="Nº Eixo" dataDxfId="186"/>
+    <tableColumn id="19" xr3:uid="{A08285BC-8B0E-4492-A6AF-090B851B036D}" name="Observação" dataDxfId="185"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2911020D-4239-47C9-B941-F45CAD7BBE3D}" name="Tabela66" displayName="Tabela66" ref="A1:AD35" totalsRowShown="0" headerRowDxfId="135" dataDxfId="134">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2911020D-4239-47C9-B941-F45CAD7BBE3D}" name="Tabela66" displayName="Tabela66" ref="A1:AD35" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72">
   <autoFilter ref="A1:AD35" xr:uid="{08F50CE1-35A6-4ABA-9594-79B9C39908E8}">
     <filterColumn colId="0">
       <filters>
@@ -5391,36 +5178,36 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="30">
-    <tableColumn id="4" xr3:uid="{DD6014DD-F2DC-47D0-A44B-A9397730BE4E}" name="Cliente" dataDxfId="133"/>
-    <tableColumn id="6" xr3:uid="{59911696-06D3-45A5-970B-2AD22F609E28}" name="Descrição" dataDxfId="132"/>
-    <tableColumn id="7" xr3:uid="{8F359B2A-1452-4DD5-8078-A592FF1FAEDA}" name="Qtde." dataDxfId="131"/>
-    <tableColumn id="24" xr3:uid="{6ACDF30B-4FA5-46F2-B973-769AFF1A7ED5}" name="Bit" dataDxfId="130"/>
-    <tableColumn id="26" xr3:uid="{CA14875A-A13A-4CA2-81ED-1A988AD78208}" name="Terno" dataDxfId="129"/>
-    <tableColumn id="16" xr3:uid="{D3038C5E-F555-4042-A706-904B091CB790}" name="Forma" dataDxfId="128"/>
-    <tableColumn id="9" xr3:uid="{736BC299-01E4-44CB-8D56-905E55712437}" name="Prazo_x000a_Fund" dataDxfId="127"/>
-    <tableColumn id="10" xr3:uid="{714F025C-A04A-41D1-BB99-C7973DD1D6C8}" name="Prazo_x000a_Fund Real" dataDxfId="126"/>
-    <tableColumn id="11" xr3:uid="{2AE87132-0DBA-40D2-AB92-CEAC0877A62E}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="125"/>
-    <tableColumn id="12" xr3:uid="{CF3374FD-D85C-4F8B-BC4C-3092E3B5F31A}" name="Pz Entrega_x000a_Real" dataDxfId="124"/>
-    <tableColumn id="13" xr3:uid="{75F62D18-9AFA-4320-9551-17D7D3F48733}" name="Desenho_x000a_Previsão" dataDxfId="123"/>
-    <tableColumn id="14" xr3:uid="{0E91F17A-D1CD-4B1F-B5BA-F593FF862042}" name="Des." dataDxfId="122"/>
-    <tableColumn id="33" xr3:uid="{49915B29-1E2A-403B-BB52-E050204325AB}" name="OP1" dataDxfId="121"/>
-    <tableColumn id="30" xr3:uid="{918DBD98-C28A-4CAB-8273-DEB81CE88B05}" name="OP2" dataDxfId="120"/>
-    <tableColumn id="28" xr3:uid="{F99FDFD5-3B70-48B1-93CD-89C55B3CE706}" name="OP3" dataDxfId="119"/>
-    <tableColumn id="27" xr3:uid="{3B6FF2E7-14DF-4DBF-B5AB-5AC8D2BE1CDD}" name="OP4" dataDxfId="118"/>
-    <tableColumn id="25" xr3:uid="{0837249B-09C0-43AA-A6F1-42C6831ED1C4}" name="OP5" dataDxfId="117"/>
-    <tableColumn id="20" xr3:uid="{9AB76328-313A-4CD8-9CB1-5AB1453CAE9E}" name="OP6" dataDxfId="116"/>
-    <tableColumn id="35" xr3:uid="{B32C0B30-5F3F-42B0-8DFF-98B0B8FB2893}" name="OP7" dataDxfId="115"/>
-    <tableColumn id="15" xr3:uid="{AF3E8433-61CF-422E-9FA2-91C9BA8DC757}" name="OP8" dataDxfId="114"/>
-    <tableColumn id="8" xr3:uid="{A6F4F508-1C53-4E9B-9746-79444D0123BB}" name="OP9" dataDxfId="113"/>
-    <tableColumn id="18" xr3:uid="{AEDB6685-F605-437C-ABD4-65BAE59B7844}" name="Status_x000a_Camisa" dataDxfId="112"/>
-    <tableColumn id="3" xr3:uid="{4D106AB2-FC5C-4F08-8B0A-A966B169502D}" name="PV eixo" dataDxfId="111"/>
-    <tableColumn id="32" xr3:uid="{111EB1E4-5B59-4AC6-97B8-26DB9C34AFD4}" name="Nº Eixo2" dataDxfId="110"/>
-    <tableColumn id="31" xr3:uid="{3327FDD5-D7D9-476C-B262-F5CEDAA2C9FA}" name="Rec_x000a_Eixo" dataDxfId="109"/>
-    <tableColumn id="34" xr3:uid="{947A4EE5-7E50-4ED4-9CAE-160C8A4CBD34}" name="OP10" dataDxfId="108"/>
-    <tableColumn id="17" xr3:uid="{76660409-FD24-4D8E-B5EF-275B92F001A9}" name="OP11" dataDxfId="107"/>
-    <tableColumn id="29" xr3:uid="{2D48D210-14B2-4386-A519-42F0F2B7E9F5}" name="Prazo_x000a_Entrega_x000a_Eixo" dataDxfId="106"/>
-    <tableColumn id="23" xr3:uid="{4DFCA09F-8E46-42D4-9163-40353BAA4ACE}" name="Status_x000a_Eixo" dataDxfId="105"/>
-    <tableColumn id="19" xr3:uid="{E3D32BDE-09FA-4F17-8CE6-8B2139F9BB8A}" name="Observação" dataDxfId="104"/>
+    <tableColumn id="4" xr3:uid="{DD6014DD-F2DC-47D0-A44B-A9397730BE4E}" name="Cliente" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{59911696-06D3-45A5-970B-2AD22F609E28}" name="Descrição" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{8F359B2A-1452-4DD5-8078-A592FF1FAEDA}" name="Qtde." dataDxfId="69"/>
+    <tableColumn id="24" xr3:uid="{6ACDF30B-4FA5-46F2-B973-769AFF1A7ED5}" name="Bit" dataDxfId="68"/>
+    <tableColumn id="26" xr3:uid="{CA14875A-A13A-4CA2-81ED-1A988AD78208}" name="Terno" dataDxfId="67"/>
+    <tableColumn id="16" xr3:uid="{D3038C5E-F555-4042-A706-904B091CB790}" name="Forma" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{736BC299-01E4-44CB-8D56-905E55712437}" name="Prazo_x000a_Fund" dataDxfId="65"/>
+    <tableColumn id="10" xr3:uid="{714F025C-A04A-41D1-BB99-C7973DD1D6C8}" name="Prazo_x000a_Fund Real" dataDxfId="64"/>
+    <tableColumn id="11" xr3:uid="{2AE87132-0DBA-40D2-AB92-CEAC0877A62E}" name="Prazo_x000a_Entrega_x000a_Camisa" dataDxfId="63"/>
+    <tableColumn id="12" xr3:uid="{CF3374FD-D85C-4F8B-BC4C-3092E3B5F31A}" name="Pz Entrega_x000a_Real" dataDxfId="62"/>
+    <tableColumn id="13" xr3:uid="{75F62D18-9AFA-4320-9551-17D7D3F48733}" name="Desenho_x000a_Previsão" dataDxfId="61"/>
+    <tableColumn id="14" xr3:uid="{0E91F17A-D1CD-4B1F-B5BA-F593FF862042}" name="Des." dataDxfId="60"/>
+    <tableColumn id="33" xr3:uid="{49915B29-1E2A-403B-BB52-E050204325AB}" name="OP1" dataDxfId="59"/>
+    <tableColumn id="30" xr3:uid="{918DBD98-C28A-4CAB-8273-DEB81CE88B05}" name="OP2" dataDxfId="58"/>
+    <tableColumn id="28" xr3:uid="{F99FDFD5-3B70-48B1-93CD-89C55B3CE706}" name="OP3" dataDxfId="57"/>
+    <tableColumn id="27" xr3:uid="{3B6FF2E7-14DF-4DBF-B5AB-5AC8D2BE1CDD}" name="OP4" dataDxfId="56"/>
+    <tableColumn id="25" xr3:uid="{0837249B-09C0-43AA-A6F1-42C6831ED1C4}" name="OP5" dataDxfId="55"/>
+    <tableColumn id="20" xr3:uid="{9AB76328-313A-4CD8-9CB1-5AB1453CAE9E}" name="OP6" dataDxfId="54"/>
+    <tableColumn id="35" xr3:uid="{B32C0B30-5F3F-42B0-8DFF-98B0B8FB2893}" name="OP7" dataDxfId="53"/>
+    <tableColumn id="15" xr3:uid="{AF3E8433-61CF-422E-9FA2-91C9BA8DC757}" name="OP8" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{A6F4F508-1C53-4E9B-9746-79444D0123BB}" name="OP9" dataDxfId="51"/>
+    <tableColumn id="18" xr3:uid="{AEDB6685-F605-437C-ABD4-65BAE59B7844}" name="Status_x000a_Camisa" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{4D106AB2-FC5C-4F08-8B0A-A966B169502D}" name="PV eixo" dataDxfId="49"/>
+    <tableColumn id="32" xr3:uid="{111EB1E4-5B59-4AC6-97B8-26DB9C34AFD4}" name="Nº Eixo2" dataDxfId="48"/>
+    <tableColumn id="31" xr3:uid="{3327FDD5-D7D9-476C-B262-F5CEDAA2C9FA}" name="Rec_x000a_Eixo" dataDxfId="47"/>
+    <tableColumn id="34" xr3:uid="{947A4EE5-7E50-4ED4-9CAE-160C8A4CBD34}" name="OP10" dataDxfId="46"/>
+    <tableColumn id="17" xr3:uid="{76660409-FD24-4D8E-B5EF-275B92F001A9}" name="OP11" dataDxfId="45"/>
+    <tableColumn id="29" xr3:uid="{2D48D210-14B2-4386-A519-42F0F2B7E9F5}" name="Prazo_x000a_Entrega_x000a_Eixo" dataDxfId="44"/>
+    <tableColumn id="23" xr3:uid="{4DFCA09F-8E46-42D4-9163-40353BAA4ACE}" name="Status_x000a_Eixo" dataDxfId="43"/>
+    <tableColumn id="19" xr3:uid="{E3D32BDE-09FA-4F17-8CE6-8B2139F9BB8A}" name="Observação" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -18371,7 +18158,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F053A7-2FDA-4BCA-8A08-44A595E3BEFC}">
-  <dimension ref="A1:V143"/>
+  <dimension ref="A1:V151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="1"/>
@@ -28524,6 +28311,574 @@
         <v>61</v>
       </c>
       <c r="V143" s="10"/>
+    </row>
+    <row r="144" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A144" s="10">
+        <v>2342</v>
+      </c>
+      <c r="B144" s="10">
+        <v>1</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="I144" s="10">
+        <v>1</v>
+      </c>
+      <c r="J144" s="11">
+        <v>46203</v>
+      </c>
+      <c r="K144" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>27</v>
+      </c>
+      <c r="L144" s="11">
+        <v>46203</v>
+      </c>
+      <c r="M144" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N144" s="18"/>
+      <c r="O144" s="11">
+        <v>46204</v>
+      </c>
+      <c r="P144" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q144" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>30</v>
+      </c>
+      <c r="R144" s="65" t="str">
+        <f ca="1">IF(Q144&lt;0,"ATRASADO",IF(Q144&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S144" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T144" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U144" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="V144" s="65"/>
+    </row>
+    <row r="145" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A145" s="10">
+        <v>2342</v>
+      </c>
+      <c r="B145" s="10">
+        <v>2</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D145" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F145" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="G145" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H145" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="I145" s="10">
+        <v>1</v>
+      </c>
+      <c r="J145" s="11">
+        <v>46203</v>
+      </c>
+      <c r="K145" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>27</v>
+      </c>
+      <c r="L145" s="11">
+        <v>46203</v>
+      </c>
+      <c r="M145" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N145" s="18"/>
+      <c r="O145" s="11">
+        <v>46204</v>
+      </c>
+      <c r="P145" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q145" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>30</v>
+      </c>
+      <c r="R145" s="65" t="str">
+        <f t="shared" ref="R145:R151" ca="1" si="5">IF(Q145&lt;0,"ATRASADO",IF(Q145&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S145" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T145" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U145" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="V145" s="65"/>
+    </row>
+    <row r="146" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A146" s="10">
+        <v>2342</v>
+      </c>
+      <c r="B146" s="10">
+        <v>3</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F146" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H146" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="I146" s="10">
+        <v>1</v>
+      </c>
+      <c r="J146" s="11">
+        <v>46203</v>
+      </c>
+      <c r="K146" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>27</v>
+      </c>
+      <c r="L146" s="11">
+        <v>46203</v>
+      </c>
+      <c r="M146" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N146" s="18"/>
+      <c r="O146" s="11">
+        <v>46204</v>
+      </c>
+      <c r="P146" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q146" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>30</v>
+      </c>
+      <c r="R146" s="65" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S146" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T146" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U146" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="V146" s="65"/>
+    </row>
+    <row r="147" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A147" s="10">
+        <v>2342</v>
+      </c>
+      <c r="B147" s="10">
+        <v>4</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E147" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F147" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="I147" s="10">
+        <v>1</v>
+      </c>
+      <c r="J147" s="11">
+        <v>46203</v>
+      </c>
+      <c r="K147" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>27</v>
+      </c>
+      <c r="L147" s="11">
+        <v>46203</v>
+      </c>
+      <c r="M147" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N147" s="18"/>
+      <c r="O147" s="11">
+        <v>46204</v>
+      </c>
+      <c r="P147" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q147" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>30</v>
+      </c>
+      <c r="R147" s="65" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S147" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T147" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U147" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="V147" s="65"/>
+    </row>
+    <row r="148" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A148" s="10">
+        <v>2342</v>
+      </c>
+      <c r="B148" s="10">
+        <v>5</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E148" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F148" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H148" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="I148" s="10">
+        <v>1</v>
+      </c>
+      <c r="J148" s="11">
+        <v>46203</v>
+      </c>
+      <c r="K148" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>27</v>
+      </c>
+      <c r="L148" s="11">
+        <v>46203</v>
+      </c>
+      <c r="M148" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N148" s="18"/>
+      <c r="O148" s="11">
+        <v>46204</v>
+      </c>
+      <c r="P148" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q148" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>30</v>
+      </c>
+      <c r="R148" s="65" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S148" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T148" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U148" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="V148" s="65"/>
+    </row>
+    <row r="149" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A149" s="10">
+        <v>2342</v>
+      </c>
+      <c r="B149" s="10">
+        <v>6</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F149" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="I149" s="10">
+        <v>1</v>
+      </c>
+      <c r="J149" s="11">
+        <v>46203</v>
+      </c>
+      <c r="K149" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>27</v>
+      </c>
+      <c r="L149" s="11">
+        <v>46203</v>
+      </c>
+      <c r="M149" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N149" s="18"/>
+      <c r="O149" s="11">
+        <v>46204</v>
+      </c>
+      <c r="P149" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q149" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>30</v>
+      </c>
+      <c r="R149" s="65" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S149" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T149" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U149" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="V149" s="65"/>
+    </row>
+    <row r="150" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A150" s="10">
+        <v>2342</v>
+      </c>
+      <c r="B150" s="10">
+        <v>7</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E150" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F150" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G150" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H150" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="I150" s="10">
+        <v>1</v>
+      </c>
+      <c r="J150" s="11">
+        <v>46203</v>
+      </c>
+      <c r="K150" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>27</v>
+      </c>
+      <c r="L150" s="11">
+        <v>46203</v>
+      </c>
+      <c r="M150" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N150" s="18"/>
+      <c r="O150" s="11">
+        <v>46204</v>
+      </c>
+      <c r="P150" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q150" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>30</v>
+      </c>
+      <c r="R150" s="65" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S150" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T150" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U150" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="V150" s="65"/>
+    </row>
+    <row r="151" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A151" s="10">
+        <v>2342</v>
+      </c>
+      <c r="B151" s="10">
+        <v>8</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E151" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F151" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="I151" s="10">
+        <v>1</v>
+      </c>
+      <c r="J151" s="11">
+        <v>46203</v>
+      </c>
+      <c r="K151" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>27</v>
+      </c>
+      <c r="L151" s="11">
+        <v>46203</v>
+      </c>
+      <c r="M151" s="11">
+        <v>46233</v>
+      </c>
+      <c r="N151" s="18"/>
+      <c r="O151" s="11">
+        <v>46204</v>
+      </c>
+      <c r="P151" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q151" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>30</v>
+      </c>
+      <c r="R151" s="65" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S151" s="65">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>31</v>
+      </c>
+      <c r="T151" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="U151" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="V151" s="65"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -37535,115 +37890,115 @@
   <dimension ref="A1:AC237"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="69"/>
-    <col min="3" max="3" width="16" style="69" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="69"/>
-    <col min="5" max="5" width="21.85546875" style="69" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="69" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" style="69" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.42578125" style="69" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" style="69" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="69"/>
-    <col min="12" max="12" width="10.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" style="69" customWidth="1"/>
-    <col min="14" max="15" width="10.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="9.140625" style="69"/>
-    <col min="27" max="27" width="18.5703125" style="69" customWidth="1"/>
-    <col min="28" max="28" width="12.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="25.42578125" style="69" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="69"/>
+    <col min="1" max="2" width="9.140625" style="53"/>
+    <col min="3" max="3" width="16" style="53" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="53"/>
+    <col min="5" max="5" width="21.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.42578125" style="53" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" style="53" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="53"/>
+    <col min="12" max="12" width="10.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" style="53" customWidth="1"/>
+    <col min="14" max="15" width="10.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="9.140625" style="53"/>
+    <col min="27" max="27" width="18.5703125" style="53" customWidth="1"/>
+    <col min="28" max="28" width="12.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="25.42578125" style="53" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="53"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="67" t="s">
+      <c r="B1" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="52" t="s">
         <v>257</v>
       </c>
-      <c r="E1" s="67" t="s">
+      <c r="E1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="67" t="s">
+      <c r="F1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="51" t="s">
         <v>304</v>
       </c>
-      <c r="I1" s="67" t="s">
+      <c r="I1" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="51" t="s">
         <v>236</v>
       </c>
-      <c r="K1" s="67" t="s">
+      <c r="K1" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="L1" s="68" t="s">
+      <c r="L1" s="52" t="s">
         <v>251</v>
       </c>
-      <c r="M1" s="68" t="s">
+      <c r="M1" s="52" t="s">
         <v>252</v>
       </c>
-      <c r="N1" s="68" t="s">
+      <c r="N1" s="52" t="s">
         <v>250</v>
       </c>
-      <c r="O1" s="68" t="s">
+      <c r="O1" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="68" t="s">
+      <c r="P1" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="Q1" s="68" t="s">
+      <c r="Q1" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="R1" s="68" t="s">
+      <c r="R1" s="52" t="s">
         <v>277</v>
       </c>
-      <c r="S1" s="68" t="s">
+      <c r="S1" s="52" t="s">
         <v>278</v>
       </c>
-      <c r="T1" s="68" t="s">
+      <c r="T1" s="52" t="s">
         <v>279</v>
       </c>
-      <c r="U1" s="68" t="s">
+      <c r="U1" s="52" t="s">
         <v>280</v>
       </c>
-      <c r="V1" s="68" t="s">
+      <c r="V1" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="W1" s="68" t="s">
+      <c r="W1" s="52" t="s">
         <v>282</v>
       </c>
-      <c r="X1" s="68" t="s">
+      <c r="X1" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="Y1" s="68" t="s">
+      <c r="Y1" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="Z1" s="68" t="s">
+      <c r="Z1" s="52" t="s">
         <v>285</v>
       </c>
-      <c r="AA1" s="68" t="s">
+      <c r="AA1" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="AB1" s="68" t="s">
+      <c r="AB1" s="52" t="s">
         <v>301</v>
       </c>
-      <c r="AC1" s="68" t="s">
+      <c r="AC1" s="52" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54">
         <v>1015</v>
       </c>
@@ -37728,7 +38083,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54">
         <v>1027</v>
       </c>
@@ -37801,7 +38156,7 @@
       </c>
       <c r="AC3" s="54"/>
     </row>
-    <row r="4" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="54">
         <v>1027</v>
       </c>
@@ -37874,7 +38229,7 @@
       </c>
       <c r="AC4" s="54"/>
     </row>
-    <row r="5" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="54">
         <v>1027</v>
       </c>
@@ -37947,7 +38302,7 @@
       </c>
       <c r="AC5" s="54"/>
     </row>
-    <row r="6" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54">
         <v>1027</v>
       </c>
@@ -38020,7 +38375,7 @@
       </c>
       <c r="AC6" s="54"/>
     </row>
-    <row r="7" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="54">
         <v>1027</v>
       </c>
@@ -38093,7 +38448,7 @@
       </c>
       <c r="AC7" s="54"/>
     </row>
-    <row r="8" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="54">
         <v>1027</v>
       </c>
@@ -38168,7 +38523,7 @@
       </c>
       <c r="AC8" s="54"/>
     </row>
-    <row r="9" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="54">
         <v>1027</v>
       </c>
@@ -38241,7 +38596,7 @@
       </c>
       <c r="AC9" s="54"/>
     </row>
-    <row r="10" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="54">
         <v>1027</v>
       </c>
@@ -38316,7 +38671,7 @@
       </c>
       <c r="AC10" s="54"/>
     </row>
-    <row r="11" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="54">
         <v>1027</v>
       </c>
@@ -38389,7 +38744,7 @@
       </c>
       <c r="AC11" s="54"/>
     </row>
-    <row r="12" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="54">
         <v>1027</v>
       </c>
@@ -38472,7 +38827,7 @@
       </c>
       <c r="AC12" s="54"/>
     </row>
-    <row r="13" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="54">
         <v>1027</v>
       </c>
@@ -38545,7 +38900,7 @@
       </c>
       <c r="AC13" s="54"/>
     </row>
-    <row r="14" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="54">
         <v>1027</v>
       </c>
@@ -38630,7 +38985,7 @@
       </c>
       <c r="AC14" s="54"/>
     </row>
-    <row r="15" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="54">
         <v>1027</v>
       </c>
@@ -38703,7 +39058,7 @@
       </c>
       <c r="AC15" s="54"/>
     </row>
-    <row r="16" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="54">
         <v>1027</v>
       </c>
@@ -38786,7 +39141,7 @@
       </c>
       <c r="AC16" s="54"/>
     </row>
-    <row r="17" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54">
         <v>1027</v>
       </c>
@@ -38859,7 +39214,7 @@
       </c>
       <c r="AC17" s="54"/>
     </row>
-    <row r="18" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54">
         <v>1027</v>
       </c>
@@ -38932,7 +39287,7 @@
       </c>
       <c r="AC18" s="54"/>
     </row>
-    <row r="19" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="54">
         <v>1005</v>
       </c>
@@ -39005,7 +39360,7 @@
       </c>
       <c r="AC19" s="54"/>
     </row>
-    <row r="20" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54">
         <v>1005</v>
       </c>
@@ -39078,7 +39433,7 @@
       </c>
       <c r="AC20" s="54"/>
     </row>
-    <row r="21" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="54">
         <v>1005</v>
       </c>
@@ -39151,7 +39506,7 @@
       </c>
       <c r="AC21" s="54"/>
     </row>
-    <row r="22" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="54">
         <v>1005</v>
       </c>
@@ -39224,7 +39579,7 @@
       </c>
       <c r="AC22" s="54"/>
     </row>
-    <row r="23" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="54">
         <v>1005</v>
       </c>
@@ -39297,7 +39652,7 @@
       </c>
       <c r="AC23" s="54"/>
     </row>
-    <row r="24" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="54">
         <v>1005</v>
       </c>
@@ -39370,7 +39725,7 @@
       </c>
       <c r="AC24" s="54"/>
     </row>
-    <row r="25" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="54">
         <v>1005</v>
       </c>
@@ -39443,7 +39798,7 @@
       </c>
       <c r="AC25" s="54"/>
     </row>
-    <row r="26" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="54">
         <v>1005</v>
       </c>
@@ -39516,7 +39871,7 @@
       </c>
       <c r="AC26" s="54"/>
     </row>
-    <row r="27" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="54">
         <v>1005</v>
       </c>
@@ -39589,7 +39944,7 @@
       </c>
       <c r="AC27" s="54"/>
     </row>
-    <row r="28" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="54">
         <v>1005</v>
       </c>
@@ -39662,7 +40017,7 @@
       </c>
       <c r="AC28" s="54"/>
     </row>
-    <row r="29" spans="1:29" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="54">
         <v>1005</v>
       </c>
@@ -39736,7 +40091,7 @@
       <c r="AC29" s="54"/>
     </row>
     <row r="30" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="63">
+      <c r="A30" s="62">
         <v>2077</v>
       </c>
       <c r="B30" s="58">
@@ -39745,7 +40100,7 @@
       <c r="C30" s="58" t="s">
         <v>310</v>
       </c>
-      <c r="D30" s="63">
+      <c r="D30" s="62">
         <v>6728</v>
       </c>
       <c r="E30" s="58" t="s">
@@ -39769,8 +40124,8 @@
       <c r="K30" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="54"/>
       <c r="N30" s="59">
         <v>46090</v>
       </c>
@@ -39783,16 +40138,16 @@
       <c r="Q30" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R30" s="61" t="s">
+      <c r="R30" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S30" s="61" t="s">
+      <c r="S30" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T30" s="61" t="s">
+      <c r="T30" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U30" s="61" t="s">
+      <c r="U30" s="60" t="s">
         <v>276</v>
       </c>
       <c r="V30" s="58"/>
@@ -39803,7 +40158,7 @@
       <c r="AA30" s="58" t="s">
         <v>311</v>
       </c>
-      <c r="AB30" s="63">
+      <c r="AB30" s="62">
         <v>6032</v>
       </c>
       <c r="AC30" s="58" t="s">
@@ -39811,7 +40166,7 @@
       </c>
     </row>
     <row r="31" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="63">
+      <c r="A31" s="62">
         <v>2077</v>
       </c>
       <c r="B31" s="58">
@@ -39820,7 +40175,7 @@
       <c r="C31" s="58" t="s">
         <v>310</v>
       </c>
-      <c r="D31" s="63">
+      <c r="D31" s="62">
         <v>6727</v>
       </c>
       <c r="E31" s="58" t="s">
@@ -39844,8 +40199,8 @@
       <c r="K31" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="54"/>
       <c r="N31" s="59">
         <v>46192</v>
       </c>
@@ -39858,35 +40213,35 @@
       <c r="Q31" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R31" s="61" t="s">
+      <c r="R31" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S31" s="61" t="s">
+      <c r="S31" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T31" s="61" t="s">
+      <c r="T31" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U31" s="61" t="s">
+      <c r="U31" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V31" s="61" t="s">
+      <c r="V31" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W31" s="61" t="s">
+      <c r="W31" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X31" s="61" t="s">
+      <c r="X31" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="Y31" s="61" t="s">
+      <c r="Y31" s="60" t="s">
         <v>276</v>
       </c>
       <c r="Z31" s="58"/>
       <c r="AA31" s="58" t="s">
         <v>311</v>
       </c>
-      <c r="AB31" s="63">
+      <c r="AB31" s="62">
         <v>6040</v>
       </c>
       <c r="AC31" s="58" t="s">
@@ -39894,7 +40249,7 @@
       </c>
     </row>
     <row r="32" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="63">
+      <c r="A32" s="62">
         <v>1386</v>
       </c>
       <c r="B32" s="58">
@@ -39903,7 +40258,7 @@
       <c r="C32" s="58" t="s">
         <v>310</v>
       </c>
-      <c r="D32" s="63">
+      <c r="D32" s="62">
         <v>6169</v>
       </c>
       <c r="E32" s="58" t="s">
@@ -39927,8 +40282,8 @@
       <c r="K32" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L32" s="65"/>
-      <c r="M32" s="65"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="54"/>
       <c r="N32" s="58"/>
       <c r="O32" s="58"/>
       <c r="P32" s="58" t="s">
@@ -39937,16 +40292,16 @@
       <c r="Q32" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R32" s="61" t="s">
+      <c r="R32" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S32" s="61" t="s">
+      <c r="S32" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T32" s="61" t="s">
+      <c r="T32" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U32" s="61" t="s">
+      <c r="U32" s="60" t="s">
         <v>276</v>
       </c>
       <c r="V32" s="58"/>
@@ -39957,22 +40312,22 @@
       <c r="AA32" s="58" t="s">
         <v>312</v>
       </c>
-      <c r="AB32" s="63">
+      <c r="AB32" s="62">
         <v>6075</v>
       </c>
       <c r="AC32" s="58"/>
     </row>
     <row r="33" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="63">
+      <c r="A33" s="62">
         <v>2078</v>
       </c>
-      <c r="B33" s="60">
+      <c r="B33" s="54">
         <v>8</v>
       </c>
-      <c r="C33" s="60" t="s">
+      <c r="C33" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D33" s="63">
+      <c r="D33" s="62">
         <v>6741</v>
       </c>
       <c r="E33" s="58" t="s">
@@ -39981,10 +40336,10 @@
       <c r="F33" s="58">
         <v>1</v>
       </c>
-      <c r="G33" s="65" t="s">
+      <c r="G33" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H33" s="65" t="s">
+      <c r="H33" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I33" s="58" t="s">
@@ -39996,12 +40351,12 @@
       <c r="K33" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L33" s="60"/>
-      <c r="M33" s="60"/>
-      <c r="N33" s="64">
+      <c r="L33" s="54"/>
+      <c r="M33" s="54"/>
+      <c r="N33" s="63">
         <v>46090</v>
       </c>
-      <c r="O33" s="64">
+      <c r="O33" s="63">
         <v>46090</v>
       </c>
       <c r="P33" s="58" t="s">
@@ -40010,27 +40365,27 @@
       <c r="Q33" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R33" s="61" t="s">
+      <c r="R33" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S33" s="61" t="s">
+      <c r="S33" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T33" s="61" t="s">
+      <c r="T33" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U33" s="61" t="s">
+      <c r="U33" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="V33" s="65"/>
-      <c r="W33" s="65"/>
-      <c r="X33" s="65"/>
-      <c r="Y33" s="65"/>
-      <c r="Z33" s="65"/>
-      <c r="AA33" s="60" t="s">
+      <c r="V33" s="54"/>
+      <c r="W33" s="54"/>
+      <c r="X33" s="54"/>
+      <c r="Y33" s="54"/>
+      <c r="Z33" s="54"/>
+      <c r="AA33" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB33" s="63">
+      <c r="AB33" s="62">
         <v>123</v>
       </c>
       <c r="AC33" s="58" t="s">
@@ -40038,16 +40393,16 @@
       </c>
     </row>
     <row r="34" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="63">
+      <c r="A34" s="62">
         <v>2078</v>
       </c>
-      <c r="B34" s="60">
-        <v>1</v>
-      </c>
-      <c r="C34" s="60" t="s">
+      <c r="B34" s="54">
+        <v>1</v>
+      </c>
+      <c r="C34" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D34" s="63">
+      <c r="D34" s="62">
         <v>6734</v>
       </c>
       <c r="E34" s="58" t="s">
@@ -40056,10 +40411,10 @@
       <c r="F34" s="58">
         <v>1</v>
       </c>
-      <c r="G34" s="65" t="s">
+      <c r="G34" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H34" s="65" t="s">
+      <c r="H34" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I34" s="58" t="s">
@@ -40071,12 +40426,12 @@
       <c r="K34" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L34" s="60"/>
-      <c r="M34" s="60"/>
-      <c r="N34" s="64">
+      <c r="L34" s="54"/>
+      <c r="M34" s="54"/>
+      <c r="N34" s="63">
         <v>46090</v>
       </c>
-      <c r="O34" s="64">
+      <c r="O34" s="63">
         <v>46090</v>
       </c>
       <c r="P34" s="58" t="s">
@@ -40085,27 +40440,27 @@
       <c r="Q34" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R34" s="61" t="s">
+      <c r="R34" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S34" s="61" t="s">
+      <c r="S34" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T34" s="61" t="s">
+      <c r="T34" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U34" s="61" t="s">
+      <c r="U34" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="V34" s="65"/>
-      <c r="W34" s="65"/>
-      <c r="X34" s="65"/>
-      <c r="Y34" s="65"/>
-      <c r="Z34" s="65"/>
-      <c r="AA34" s="60" t="s">
+      <c r="V34" s="54"/>
+      <c r="W34" s="54"/>
+      <c r="X34" s="54"/>
+      <c r="Y34" s="54"/>
+      <c r="Z34" s="54"/>
+      <c r="AA34" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB34" s="63">
+      <c r="AB34" s="62">
         <v>134</v>
       </c>
       <c r="AC34" s="58" t="s">
@@ -40113,16 +40468,16 @@
       </c>
     </row>
     <row r="35" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63">
+      <c r="A35" s="62">
         <v>2078</v>
       </c>
-      <c r="B35" s="60">
+      <c r="B35" s="54">
         <v>4</v>
       </c>
-      <c r="C35" s="60" t="s">
+      <c r="C35" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D35" s="63">
+      <c r="D35" s="62">
         <v>6737</v>
       </c>
       <c r="E35" s="58" t="s">
@@ -40131,10 +40486,10 @@
       <c r="F35" s="58">
         <v>1</v>
       </c>
-      <c r="G35" s="65" t="s">
+      <c r="G35" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H35" s="65" t="s">
+      <c r="H35" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I35" s="58" t="s">
@@ -40146,12 +40501,12 @@
       <c r="K35" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L35" s="60"/>
-      <c r="M35" s="60"/>
-      <c r="N35" s="64">
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="63">
         <v>46090</v>
       </c>
-      <c r="O35" s="64">
+      <c r="O35" s="63">
         <v>46090</v>
       </c>
       <c r="P35" s="58" t="s">
@@ -40160,27 +40515,27 @@
       <c r="Q35" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R35" s="61" t="s">
+      <c r="R35" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S35" s="61" t="s">
+      <c r="S35" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T35" s="61" t="s">
+      <c r="T35" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U35" s="61" t="s">
+      <c r="U35" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="V35" s="65"/>
-      <c r="W35" s="65"/>
-      <c r="X35" s="65"/>
-      <c r="Y35" s="65"/>
-      <c r="Z35" s="65"/>
-      <c r="AA35" s="60" t="s">
+      <c r="V35" s="54"/>
+      <c r="W35" s="54"/>
+      <c r="X35" s="54"/>
+      <c r="Y35" s="54"/>
+      <c r="Z35" s="54"/>
+      <c r="AA35" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB35" s="63">
+      <c r="AB35" s="62">
         <v>173</v>
       </c>
       <c r="AC35" s="58" t="s">
@@ -40188,16 +40543,16 @@
       </c>
     </row>
     <row r="36" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="63">
+      <c r="A36" s="62">
         <v>2078</v>
       </c>
-      <c r="B36" s="60">
+      <c r="B36" s="54">
         <v>9</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D36" s="63">
+      <c r="D36" s="62">
         <v>6742</v>
       </c>
       <c r="E36" s="58" t="s">
@@ -40206,10 +40561,10 @@
       <c r="F36" s="58">
         <v>1</v>
       </c>
-      <c r="G36" s="65" t="s">
+      <c r="G36" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H36" s="65" t="s">
+      <c r="H36" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I36" s="58" t="s">
@@ -40221,62 +40576,62 @@
       <c r="K36" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L36" s="60"/>
-      <c r="M36" s="60"/>
-      <c r="N36" s="64">
+      <c r="L36" s="54"/>
+      <c r="M36" s="54"/>
+      <c r="N36" s="63">
         <v>46127</v>
       </c>
-      <c r="O36" s="60"/>
+      <c r="O36" s="54"/>
       <c r="P36" s="58" t="s">
         <v>69</v>
       </c>
       <c r="Q36" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R36" s="61" t="s">
+      <c r="R36" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S36" s="61" t="s">
+      <c r="S36" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T36" s="61" t="s">
+      <c r="T36" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U36" s="61" t="s">
+      <c r="U36" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V36" s="61" t="s">
+      <c r="V36" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W36" s="61" t="s">
+      <c r="W36" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X36" s="62" t="s">
+      <c r="X36" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="Y36" s="62" t="s">
+      <c r="Y36" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="Z36" s="65"/>
-      <c r="AA36" s="60" t="s">
+      <c r="Z36" s="54"/>
+      <c r="AA36" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="AB36" s="63">
+      <c r="AB36" s="62">
         <v>181</v>
       </c>
-      <c r="AC36" s="60"/>
+      <c r="AC36" s="54"/>
     </row>
     <row r="37" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="63">
+      <c r="A37" s="62">
         <v>2078</v>
       </c>
-      <c r="B37" s="60">
+      <c r="B37" s="54">
         <v>10</v>
       </c>
-      <c r="C37" s="60" t="s">
+      <c r="C37" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D37" s="63">
+      <c r="D37" s="62">
         <v>6743</v>
       </c>
       <c r="E37" s="58" t="s">
@@ -40285,10 +40640,10 @@
       <c r="F37" s="58">
         <v>1</v>
       </c>
-      <c r="G37" s="65" t="s">
+      <c r="G37" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H37" s="65" t="s">
+      <c r="H37" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I37" s="58" t="s">
@@ -40300,12 +40655,12 @@
       <c r="K37" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L37" s="60"/>
-      <c r="M37" s="60"/>
-      <c r="N37" s="64">
+      <c r="L37" s="54"/>
+      <c r="M37" s="54"/>
+      <c r="N37" s="63">
         <v>46185</v>
       </c>
-      <c r="O37" s="64">
+      <c r="O37" s="63">
         <v>46090</v>
       </c>
       <c r="P37" s="58" t="s">
@@ -40314,35 +40669,35 @@
       <c r="Q37" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R37" s="61" t="s">
+      <c r="R37" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S37" s="61" t="s">
+      <c r="S37" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T37" s="61" t="s">
+      <c r="T37" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U37" s="61" t="s">
+      <c r="U37" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V37" s="61" t="s">
+      <c r="V37" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W37" s="61" t="s">
+      <c r="W37" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X37" s="61" t="s">
+      <c r="X37" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="Y37" s="61" t="s">
+      <c r="Y37" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="Z37" s="65"/>
-      <c r="AA37" s="60" t="s">
+      <c r="Z37" s="54"/>
+      <c r="AA37" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB37" s="63">
+      <c r="AB37" s="62">
         <v>187</v>
       </c>
       <c r="AC37" s="58" t="s">
@@ -40350,16 +40705,16 @@
       </c>
     </row>
     <row r="38" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="63">
+      <c r="A38" s="62">
         <v>2078</v>
       </c>
-      <c r="B38" s="60">
+      <c r="B38" s="54">
         <v>3</v>
       </c>
-      <c r="C38" s="60" t="s">
+      <c r="C38" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D38" s="63">
+      <c r="D38" s="62">
         <v>6736</v>
       </c>
       <c r="E38" s="58" t="s">
@@ -40368,10 +40723,10 @@
       <c r="F38" s="58">
         <v>1</v>
       </c>
-      <c r="G38" s="65" t="s">
+      <c r="G38" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H38" s="65" t="s">
+      <c r="H38" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I38" s="58" t="s">
@@ -40383,12 +40738,12 @@
       <c r="K38" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L38" s="60"/>
-      <c r="M38" s="60"/>
-      <c r="N38" s="64">
+      <c r="L38" s="54"/>
+      <c r="M38" s="54"/>
+      <c r="N38" s="63">
         <v>46090</v>
       </c>
-      <c r="O38" s="64">
+      <c r="O38" s="63">
         <v>46090</v>
       </c>
       <c r="P38" s="58" t="s">
@@ -40397,27 +40752,27 @@
       <c r="Q38" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R38" s="61" t="s">
+      <c r="R38" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S38" s="61" t="s">
+      <c r="S38" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T38" s="61" t="s">
+      <c r="T38" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U38" s="61" t="s">
+      <c r="U38" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="V38" s="65"/>
-      <c r="W38" s="65"/>
-      <c r="X38" s="65"/>
-      <c r="Y38" s="65"/>
-      <c r="Z38" s="65"/>
-      <c r="AA38" s="60" t="s">
+      <c r="V38" s="54"/>
+      <c r="W38" s="54"/>
+      <c r="X38" s="54"/>
+      <c r="Y38" s="54"/>
+      <c r="Z38" s="54"/>
+      <c r="AA38" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB38" s="63">
+      <c r="AB38" s="62">
         <v>199</v>
       </c>
       <c r="AC38" s="58" t="s">
@@ -40425,16 +40780,16 @@
       </c>
     </row>
     <row r="39" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="63">
+      <c r="A39" s="62">
         <v>2078</v>
       </c>
-      <c r="B39" s="60">
+      <c r="B39" s="54">
         <v>2</v>
       </c>
-      <c r="C39" s="60" t="s">
+      <c r="C39" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D39" s="63">
+      <c r="D39" s="62">
         <v>6735</v>
       </c>
       <c r="E39" s="58" t="s">
@@ -40443,10 +40798,10 @@
       <c r="F39" s="58">
         <v>1</v>
       </c>
-      <c r="G39" s="65" t="s">
+      <c r="G39" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H39" s="65" t="s">
+      <c r="H39" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I39" s="58" t="s">
@@ -40458,12 +40813,12 @@
       <c r="K39" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L39" s="60"/>
-      <c r="M39" s="60"/>
-      <c r="N39" s="64">
+      <c r="L39" s="54"/>
+      <c r="M39" s="54"/>
+      <c r="N39" s="63">
         <v>46090</v>
       </c>
-      <c r="O39" s="64">
+      <c r="O39" s="63">
         <v>46090</v>
       </c>
       <c r="P39" s="58" t="s">
@@ -40472,27 +40827,27 @@
       <c r="Q39" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R39" s="61" t="s">
+      <c r="R39" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S39" s="61" t="s">
+      <c r="S39" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T39" s="61" t="s">
+      <c r="T39" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U39" s="61" t="s">
+      <c r="U39" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="V39" s="65"/>
-      <c r="W39" s="65"/>
-      <c r="X39" s="65"/>
-      <c r="Y39" s="65"/>
-      <c r="Z39" s="65"/>
-      <c r="AA39" s="60" t="s">
+      <c r="V39" s="54"/>
+      <c r="W39" s="54"/>
+      <c r="X39" s="54"/>
+      <c r="Y39" s="54"/>
+      <c r="Z39" s="54"/>
+      <c r="AA39" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB39" s="63">
+      <c r="AB39" s="62">
         <v>200</v>
       </c>
       <c r="AC39" s="58" t="s">
@@ -40500,16 +40855,16 @@
       </c>
     </row>
     <row r="40" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="63">
+      <c r="A40" s="62">
         <v>2078</v>
       </c>
-      <c r="B40" s="60">
+      <c r="B40" s="54">
         <v>7</v>
       </c>
-      <c r="C40" s="60" t="s">
+      <c r="C40" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D40" s="63">
+      <c r="D40" s="62">
         <v>6740</v>
       </c>
       <c r="E40" s="58" t="s">
@@ -40518,10 +40873,10 @@
       <c r="F40" s="58">
         <v>1</v>
       </c>
-      <c r="G40" s="65" t="s">
+      <c r="G40" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H40" s="65" t="s">
+      <c r="H40" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I40" s="58" t="s">
@@ -40533,12 +40888,12 @@
       <c r="K40" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L40" s="60"/>
-      <c r="M40" s="60"/>
-      <c r="N40" s="64">
+      <c r="L40" s="54"/>
+      <c r="M40" s="54"/>
+      <c r="N40" s="63">
         <v>46090</v>
       </c>
-      <c r="O40" s="64">
+      <c r="O40" s="63">
         <v>46090</v>
       </c>
       <c r="P40" s="58" t="s">
@@ -40547,27 +40902,27 @@
       <c r="Q40" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R40" s="61" t="s">
+      <c r="R40" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S40" s="61" t="s">
+      <c r="S40" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T40" s="61" t="s">
+      <c r="T40" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U40" s="61" t="s">
+      <c r="U40" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="V40" s="65"/>
-      <c r="W40" s="65"/>
-      <c r="X40" s="65"/>
-      <c r="Y40" s="65"/>
-      <c r="Z40" s="65"/>
-      <c r="AA40" s="60" t="s">
+      <c r="V40" s="54"/>
+      <c r="W40" s="54"/>
+      <c r="X40" s="54"/>
+      <c r="Y40" s="54"/>
+      <c r="Z40" s="54"/>
+      <c r="AA40" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB40" s="63">
+      <c r="AB40" s="62">
         <v>201</v>
       </c>
       <c r="AC40" s="58" t="s">
@@ -40575,16 +40930,16 @@
       </c>
     </row>
     <row r="41" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="63">
+      <c r="A41" s="62">
         <v>2078</v>
       </c>
-      <c r="B41" s="60">
+      <c r="B41" s="54">
         <v>5</v>
       </c>
-      <c r="C41" s="60" t="s">
+      <c r="C41" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D41" s="63">
+      <c r="D41" s="62">
         <v>6738</v>
       </c>
       <c r="E41" s="58" t="s">
@@ -40593,10 +40948,10 @@
       <c r="F41" s="58">
         <v>1</v>
       </c>
-      <c r="G41" s="65" t="s">
+      <c r="G41" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H41" s="65" t="s">
+      <c r="H41" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I41" s="58" t="s">
@@ -40608,12 +40963,12 @@
       <c r="K41" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L41" s="60"/>
-      <c r="M41" s="60"/>
-      <c r="N41" s="64">
+      <c r="L41" s="54"/>
+      <c r="M41" s="54"/>
+      <c r="N41" s="63">
         <v>46090</v>
       </c>
-      <c r="O41" s="64">
+      <c r="O41" s="63">
         <v>46090</v>
       </c>
       <c r="P41" s="58" t="s">
@@ -40622,27 +40977,27 @@
       <c r="Q41" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R41" s="61" t="s">
+      <c r="R41" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S41" s="61" t="s">
+      <c r="S41" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T41" s="61" t="s">
+      <c r="T41" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U41" s="61" t="s">
+      <c r="U41" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="V41" s="65"/>
-      <c r="W41" s="65"/>
-      <c r="X41" s="65"/>
-      <c r="Y41" s="65"/>
-      <c r="Z41" s="65"/>
-      <c r="AA41" s="60" t="s">
+      <c r="V41" s="54"/>
+      <c r="W41" s="54"/>
+      <c r="X41" s="54"/>
+      <c r="Y41" s="54"/>
+      <c r="Z41" s="54"/>
+      <c r="AA41" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB41" s="63" t="s">
+      <c r="AB41" s="62" t="s">
         <v>316</v>
       </c>
       <c r="AC41" s="58" t="s">
@@ -40650,16 +41005,16 @@
       </c>
     </row>
     <row r="42" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="63">
+      <c r="A42" s="62">
         <v>2078</v>
       </c>
-      <c r="B42" s="60">
+      <c r="B42" s="54">
         <v>11</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D42" s="63">
+      <c r="D42" s="62">
         <v>6744</v>
       </c>
       <c r="E42" s="58" t="s">
@@ -40668,10 +41023,10 @@
       <c r="F42" s="58">
         <v>1</v>
       </c>
-      <c r="G42" s="65" t="s">
+      <c r="G42" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H42" s="65" t="s">
+      <c r="H42" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I42" s="58" t="s">
@@ -40683,12 +41038,12 @@
       <c r="K42" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L42" s="60"/>
-      <c r="M42" s="60"/>
-      <c r="N42" s="64">
+      <c r="L42" s="54"/>
+      <c r="M42" s="54"/>
+      <c r="N42" s="63">
         <v>46127</v>
       </c>
-      <c r="O42" s="64">
+      <c r="O42" s="63">
         <v>46090</v>
       </c>
       <c r="P42" s="58" t="s">
@@ -40697,35 +41052,35 @@
       <c r="Q42" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R42" s="61" t="s">
+      <c r="R42" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S42" s="61" t="s">
+      <c r="S42" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T42" s="61" t="s">
+      <c r="T42" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U42" s="61" t="s">
+      <c r="U42" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V42" s="61" t="s">
+      <c r="V42" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W42" s="61" t="s">
+      <c r="W42" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X42" s="61" t="s">
+      <c r="X42" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="Y42" s="61" t="s">
+      <c r="Y42" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="Z42" s="65"/>
-      <c r="AA42" s="60" t="s">
+      <c r="Z42" s="54"/>
+      <c r="AA42" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB42" s="63" t="s">
+      <c r="AB42" s="62" t="s">
         <v>317</v>
       </c>
       <c r="AC42" s="58" t="s">
@@ -40733,16 +41088,16 @@
       </c>
     </row>
     <row r="43" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="63">
+      <c r="A43" s="62">
         <v>2078</v>
       </c>
-      <c r="B43" s="60">
+      <c r="B43" s="54">
         <v>6</v>
       </c>
-      <c r="C43" s="60" t="s">
+      <c r="C43" s="54" t="s">
         <v>313</v>
       </c>
-      <c r="D43" s="63">
+      <c r="D43" s="62">
         <v>6739</v>
       </c>
       <c r="E43" s="58" t="s">
@@ -40751,10 +41106,10 @@
       <c r="F43" s="58">
         <v>1</v>
       </c>
-      <c r="G43" s="65" t="s">
+      <c r="G43" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H43" s="65" t="s">
+      <c r="H43" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I43" s="58" t="s">
@@ -40766,12 +41121,12 @@
       <c r="K43" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L43" s="60"/>
-      <c r="M43" s="60"/>
-      <c r="N43" s="64">
+      <c r="L43" s="54"/>
+      <c r="M43" s="54"/>
+      <c r="N43" s="63">
         <v>46090</v>
       </c>
-      <c r="O43" s="64">
+      <c r="O43" s="63">
         <v>46090</v>
       </c>
       <c r="P43" s="58" t="s">
@@ -40780,27 +41135,27 @@
       <c r="Q43" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R43" s="61" t="s">
+      <c r="R43" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S43" s="61" t="s">
+      <c r="S43" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T43" s="61" t="s">
+      <c r="T43" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="U43" s="61" t="s">
+      <c r="U43" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="V43" s="65"/>
-      <c r="W43" s="65"/>
-      <c r="X43" s="65"/>
-      <c r="Y43" s="65"/>
-      <c r="Z43" s="65"/>
-      <c r="AA43" s="60" t="s">
+      <c r="V43" s="54"/>
+      <c r="W43" s="54"/>
+      <c r="X43" s="54"/>
+      <c r="Y43" s="54"/>
+      <c r="Z43" s="54"/>
+      <c r="AA43" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB43" s="63" t="s">
+      <c r="AB43" s="62" t="s">
         <v>318</v>
       </c>
       <c r="AC43" s="58" t="s">
@@ -40808,28 +41163,28 @@
       </c>
     </row>
     <row r="44" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="60">
+      <c r="A44" s="54">
         <v>2099</v>
       </c>
-      <c r="B44" s="60">
-        <v>1</v>
-      </c>
-      <c r="C44" s="60" t="s">
+      <c r="B44" s="54">
+        <v>1</v>
+      </c>
+      <c r="C44" s="54" t="s">
         <v>319</v>
       </c>
-      <c r="D44" s="60">
+      <c r="D44" s="54">
         <v>6745</v>
       </c>
       <c r="E44" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F44" s="60">
-        <v>1</v>
-      </c>
-      <c r="G44" s="65" t="s">
+      <c r="F44" s="54">
+        <v>1</v>
+      </c>
+      <c r="G44" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="H44" s="65" t="s">
+      <c r="H44" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I44" s="58" t="s">
@@ -40841,74 +41196,74 @@
       <c r="K44" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L44" s="60"/>
-      <c r="M44" s="60"/>
-      <c r="N44" s="64">
+      <c r="L44" s="54"/>
+      <c r="M44" s="54"/>
+      <c r="N44" s="63">
         <v>46127</v>
       </c>
-      <c r="O44" s="60"/>
+      <c r="O44" s="54"/>
       <c r="P44" s="58" t="s">
         <v>69</v>
       </c>
       <c r="Q44" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="R44" s="61" t="s">
+      <c r="R44" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S44" s="61" t="s">
+      <c r="S44" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T44" s="61" t="s">
+      <c r="T44" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U44" s="61" t="s">
+      <c r="U44" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V44" s="61" t="s">
+      <c r="V44" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W44" s="61" t="s">
+      <c r="W44" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X44" s="62" t="s">
+      <c r="X44" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="Y44" s="62" t="s">
+      <c r="Y44" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="Z44" s="65"/>
-      <c r="AA44" s="60" t="s">
+      <c r="Z44" s="54"/>
+      <c r="AA44" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="AB44" s="60">
+      <c r="AB44" s="54">
         <v>44</v>
       </c>
-      <c r="AC44" s="60"/>
+      <c r="AC44" s="54"/>
     </row>
     <row r="45" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="60">
+      <c r="A45" s="54">
         <v>2097</v>
       </c>
-      <c r="B45" s="60">
-        <v>1</v>
-      </c>
-      <c r="C45" s="60" t="s">
+      <c r="B45" s="54">
+        <v>1</v>
+      </c>
+      <c r="C45" s="54" t="s">
         <v>320</v>
       </c>
-      <c r="D45" s="60">
+      <c r="D45" s="54">
         <v>6788</v>
       </c>
       <c r="E45" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F45" s="60">
-        <v>1</v>
-      </c>
-      <c r="G45" s="65" t="s">
+      <c r="F45" s="54">
+        <v>1</v>
+      </c>
+      <c r="G45" s="54" t="s">
         <v>321</v>
       </c>
-      <c r="H45" s="65" t="s">
+      <c r="H45" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I45" s="58" t="s">
@@ -40920,74 +41275,74 @@
       <c r="K45" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="L45" s="60"/>
-      <c r="M45" s="60"/>
-      <c r="N45" s="64">
+      <c r="L45" s="54"/>
+      <c r="M45" s="54"/>
+      <c r="N45" s="63">
         <v>46127</v>
       </c>
-      <c r="O45" s="60"/>
-      <c r="P45" s="60" t="s">
+      <c r="O45" s="54"/>
+      <c r="P45" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q45" s="65" t="s">
+      <c r="Q45" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R45" s="61" t="s">
+      <c r="R45" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S45" s="61" t="s">
+      <c r="S45" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T45" s="61" t="s">
+      <c r="T45" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U45" s="61" t="s">
+      <c r="U45" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V45" s="61" t="s">
+      <c r="V45" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W45" s="61" t="s">
+      <c r="W45" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X45" s="62" t="s">
+      <c r="X45" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="Y45" s="62" t="s">
+      <c r="Y45" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="Z45" s="65"/>
-      <c r="AA45" s="60" t="s">
+      <c r="Z45" s="54"/>
+      <c r="AA45" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="AB45" s="60" t="s">
+      <c r="AB45" s="54" t="s">
         <v>322</v>
       </c>
-      <c r="AC45" s="60"/>
+      <c r="AC45" s="54"/>
     </row>
     <row r="46" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="60">
+      <c r="A46" s="54">
         <v>2088</v>
       </c>
-      <c r="B46" s="60">
+      <c r="B46" s="54">
         <v>3</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="54" t="s">
         <v>323</v>
       </c>
-      <c r="D46" s="60">
+      <c r="D46" s="54">
         <v>6774</v>
       </c>
       <c r="E46" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F46" s="60">
-        <v>1</v>
-      </c>
-      <c r="G46" s="65" t="s">
+      <c r="F46" s="54">
+        <v>1</v>
+      </c>
+      <c r="G46" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="H46" s="65" t="s">
+      <c r="H46" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I46" s="58" t="s">
@@ -40996,77 +41351,77 @@
       <c r="J46" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K46" s="60" t="s">
+      <c r="K46" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L46" s="60"/>
-      <c r="M46" s="60"/>
-      <c r="N46" s="66">
+      <c r="L46" s="54"/>
+      <c r="M46" s="54"/>
+      <c r="N46" s="55">
         <v>46132</v>
       </c>
-      <c r="O46" s="60"/>
-      <c r="P46" s="60" t="s">
+      <c r="O46" s="54"/>
+      <c r="P46" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q46" s="65" t="s">
+      <c r="Q46" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R46" s="61" t="s">
+      <c r="R46" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S46" s="61" t="s">
+      <c r="S46" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T46" s="61" t="s">
+      <c r="T46" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U46" s="61" t="s">
+      <c r="U46" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V46" s="61" t="s">
+      <c r="V46" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W46" s="61" t="s">
+      <c r="W46" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X46" s="62" t="s">
+      <c r="X46" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="Y46" s="62" t="s">
+      <c r="Y46" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="Z46" s="65"/>
-      <c r="AA46" s="60" t="s">
+      <c r="Z46" s="54"/>
+      <c r="AA46" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="AB46" s="60">
+      <c r="AB46" s="54">
         <v>62</v>
       </c>
-      <c r="AC46" s="60"/>
+      <c r="AC46" s="54"/>
     </row>
     <row r="47" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="60">
+      <c r="A47" s="54">
         <v>2088</v>
       </c>
-      <c r="B47" s="60">
-        <v>1</v>
-      </c>
-      <c r="C47" s="60" t="s">
+      <c r="B47" s="54">
+        <v>1</v>
+      </c>
+      <c r="C47" s="54" t="s">
         <v>323</v>
       </c>
-      <c r="D47" s="60">
+      <c r="D47" s="54">
         <v>6772</v>
       </c>
       <c r="E47" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F47" s="60">
-        <v>1</v>
-      </c>
-      <c r="G47" s="65" t="s">
+      <c r="F47" s="54">
+        <v>1</v>
+      </c>
+      <c r="G47" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="H47" s="65" t="s">
+      <c r="H47" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I47" s="58" t="s">
@@ -41075,77 +41430,77 @@
       <c r="J47" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K47" s="60" t="s">
+      <c r="K47" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L47" s="60"/>
-      <c r="M47" s="60"/>
-      <c r="N47" s="66">
+      <c r="L47" s="54"/>
+      <c r="M47" s="54"/>
+      <c r="N47" s="55">
         <v>46132</v>
       </c>
-      <c r="O47" s="60"/>
-      <c r="P47" s="60" t="s">
+      <c r="O47" s="54"/>
+      <c r="P47" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q47" s="65" t="s">
+      <c r="Q47" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R47" s="61" t="s">
+      <c r="R47" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S47" s="61" t="s">
+      <c r="S47" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T47" s="61" t="s">
+      <c r="T47" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U47" s="61" t="s">
+      <c r="U47" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V47" s="61" t="s">
+      <c r="V47" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W47" s="61" t="s">
+      <c r="W47" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X47" s="62" t="s">
+      <c r="X47" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="Y47" s="62" t="s">
+      <c r="Y47" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="Z47" s="65"/>
-      <c r="AA47" s="60" t="s">
+      <c r="Z47" s="54"/>
+      <c r="AA47" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="AB47" s="60" t="s">
+      <c r="AB47" s="54" t="s">
         <v>324</v>
       </c>
-      <c r="AC47" s="60"/>
+      <c r="AC47" s="54"/>
     </row>
     <row r="48" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="60">
+      <c r="A48" s="54">
         <v>2088</v>
       </c>
-      <c r="B48" s="60">
+      <c r="B48" s="54">
         <v>2</v>
       </c>
-      <c r="C48" s="60" t="s">
+      <c r="C48" s="54" t="s">
         <v>323</v>
       </c>
-      <c r="D48" s="60">
+      <c r="D48" s="54">
         <v>6778</v>
       </c>
       <c r="E48" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F48" s="60">
-        <v>1</v>
-      </c>
-      <c r="G48" s="65">
+      <c r="F48" s="54">
+        <v>1</v>
+      </c>
+      <c r="G48" s="54">
         <v>2200</v>
       </c>
-      <c r="H48" s="65" t="s">
+      <c r="H48" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I48" s="58" t="s">
@@ -41154,77 +41509,77 @@
       <c r="J48" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K48" s="60" t="s">
+      <c r="K48" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L48" s="60"/>
-      <c r="M48" s="60"/>
-      <c r="N48" s="66">
+      <c r="L48" s="54"/>
+      <c r="M48" s="54"/>
+      <c r="N48" s="55">
         <v>46132</v>
       </c>
-      <c r="O48" s="60"/>
-      <c r="P48" s="60" t="s">
+      <c r="O48" s="54"/>
+      <c r="P48" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q48" s="65" t="s">
+      <c r="Q48" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R48" s="61" t="s">
+      <c r="R48" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S48" s="61" t="s">
+      <c r="S48" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T48" s="61" t="s">
+      <c r="T48" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U48" s="61" t="s">
+      <c r="U48" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V48" s="61" t="s">
+      <c r="V48" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W48" s="61" t="s">
+      <c r="W48" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X48" s="62" t="s">
+      <c r="X48" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="Y48" s="62" t="s">
+      <c r="Y48" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="Z48" s="65"/>
-      <c r="AA48" s="60" t="s">
+      <c r="Z48" s="54"/>
+      <c r="AA48" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="AB48" s="60" t="s">
+      <c r="AB48" s="54" t="s">
         <v>325</v>
       </c>
-      <c r="AC48" s="60"/>
+      <c r="AC48" s="54"/>
     </row>
     <row r="49" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="60">
+      <c r="A49" s="54">
         <v>974</v>
       </c>
-      <c r="B49" s="60">
+      <c r="B49" s="54">
         <v>4</v>
       </c>
-      <c r="C49" s="60" t="s">
+      <c r="C49" s="54" t="s">
         <v>323</v>
       </c>
-      <c r="D49" s="60" t="s">
+      <c r="D49" s="54" t="s">
         <v>77</v>
       </c>
       <c r="E49" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F49" s="60">
-        <v>1</v>
-      </c>
-      <c r="G49" s="65" t="s">
+      <c r="F49" s="54">
+        <v>1</v>
+      </c>
+      <c r="G49" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="H49" s="65" t="s">
+      <c r="H49" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I49" s="58" t="s">
@@ -41233,67 +41588,67 @@
       <c r="J49" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K49" s="60" t="s">
+      <c r="K49" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="L49" s="60"/>
-      <c r="M49" s="60"/>
-      <c r="N49" s="66">
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="55">
         <v>46063</v>
       </c>
-      <c r="O49" s="60"/>
-      <c r="P49" s="60" t="s">
+      <c r="O49" s="54"/>
+      <c r="P49" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q49" s="65" t="s">
+      <c r="Q49" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R49" s="65" t="s">
+      <c r="R49" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="S49" s="65" t="s">
+      <c r="S49" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="T49" s="65"/>
-      <c r="U49" s="65"/>
-      <c r="V49" s="65"/>
-      <c r="W49" s="65"/>
-      <c r="X49" s="65"/>
-      <c r="Y49" s="65"/>
-      <c r="Z49" s="65"/>
-      <c r="AA49" s="60" t="s">
+      <c r="T49" s="54"/>
+      <c r="U49" s="54"/>
+      <c r="V49" s="54"/>
+      <c r="W49" s="54"/>
+      <c r="X49" s="54"/>
+      <c r="Y49" s="54"/>
+      <c r="Z49" s="54"/>
+      <c r="AA49" s="54" t="s">
         <v>327</v>
       </c>
-      <c r="AB49" s="60">
+      <c r="AB49" s="54">
         <v>81</v>
       </c>
-      <c r="AC49" s="60" t="s">
+      <c r="AC49" s="54" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="50" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="60">
+      <c r="A50" s="54">
         <v>1006</v>
       </c>
-      <c r="B50" s="60">
+      <c r="B50" s="54">
         <v>3</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="54" t="s">
         <v>328</v>
       </c>
-      <c r="D50" s="60" t="s">
+      <c r="D50" s="54" t="s">
         <v>77</v>
       </c>
       <c r="E50" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F50" s="60">
-        <v>1</v>
-      </c>
-      <c r="G50" s="65" t="s">
+      <c r="F50" s="54">
+        <v>1</v>
+      </c>
+      <c r="G50" s="54" t="s">
         <v>329</v>
       </c>
-      <c r="H50" s="65" t="s">
+      <c r="H50" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I50" s="58" t="s">
@@ -41302,71 +41657,71 @@
       <c r="J50" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K50" s="60" t="s">
+      <c r="K50" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="L50" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="M50" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="N50" s="66">
+      <c r="L50" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="M50" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N50" s="55">
         <v>46191</v>
       </c>
-      <c r="O50" s="60"/>
-      <c r="P50" s="60" t="s">
+      <c r="O50" s="54"/>
+      <c r="P50" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q50" s="65" t="s">
+      <c r="Q50" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R50" s="70" t="s">
+      <c r="R50" s="56" t="s">
         <v>268</v>
       </c>
-      <c r="S50" s="70" t="s">
+      <c r="S50" s="56" t="s">
         <v>267</v>
       </c>
-      <c r="T50" s="65"/>
-      <c r="U50" s="65"/>
-      <c r="V50" s="65"/>
-      <c r="W50" s="65"/>
-      <c r="X50" s="65"/>
-      <c r="Y50" s="65"/>
-      <c r="Z50" s="65"/>
-      <c r="AA50" s="60" t="s">
+      <c r="T50" s="54"/>
+      <c r="U50" s="54"/>
+      <c r="V50" s="54"/>
+      <c r="W50" s="54"/>
+      <c r="X50" s="54"/>
+      <c r="Y50" s="54"/>
+      <c r="Z50" s="54"/>
+      <c r="AA50" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB50" s="60">
+      <c r="AB50" s="54">
         <v>18</v>
       </c>
-      <c r="AC50" s="60" t="s">
+      <c r="AC50" s="54" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="60">
+      <c r="A51" s="54">
         <v>1006</v>
       </c>
-      <c r="B51" s="60">
+      <c r="B51" s="54">
         <v>4</v>
       </c>
-      <c r="C51" s="60" t="s">
+      <c r="C51" s="54" t="s">
         <v>328</v>
       </c>
-      <c r="D51" s="60" t="s">
+      <c r="D51" s="54" t="s">
         <v>77</v>
       </c>
       <c r="E51" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F51" s="60">
-        <v>1</v>
-      </c>
-      <c r="G51" s="65" t="s">
+      <c r="F51" s="54">
+        <v>1</v>
+      </c>
+      <c r="G51" s="54" t="s">
         <v>330</v>
       </c>
-      <c r="H51" s="65" t="s">
+      <c r="H51" s="54" t="s">
         <v>305</v>
       </c>
       <c r="I51" s="58" t="s">
@@ -41375,71 +41730,71 @@
       <c r="J51" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K51" s="60" t="s">
+      <c r="K51" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="L51" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="M51" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="N51" s="66">
+      <c r="L51" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="M51" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N51" s="55">
         <v>46191</v>
       </c>
-      <c r="O51" s="60"/>
-      <c r="P51" s="60" t="s">
+      <c r="O51" s="54"/>
+      <c r="P51" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q51" s="65" t="s">
+      <c r="Q51" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R51" s="70" t="s">
+      <c r="R51" s="56" t="s">
         <v>268</v>
       </c>
-      <c r="S51" s="70" t="s">
+      <c r="S51" s="56" t="s">
         <v>267</v>
       </c>
-      <c r="T51" s="65"/>
-      <c r="U51" s="65"/>
-      <c r="V51" s="65"/>
-      <c r="W51" s="65"/>
-      <c r="X51" s="65"/>
-      <c r="Y51" s="65"/>
-      <c r="Z51" s="65"/>
-      <c r="AA51" s="60" t="s">
+      <c r="T51" s="54"/>
+      <c r="U51" s="54"/>
+      <c r="V51" s="54"/>
+      <c r="W51" s="54"/>
+      <c r="X51" s="54"/>
+      <c r="Y51" s="54"/>
+      <c r="Z51" s="54"/>
+      <c r="AA51" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB51" s="60" t="s">
+      <c r="AB51" s="54" t="s">
         <v>331</v>
       </c>
-      <c r="AC51" s="60" t="s">
+      <c r="AC51" s="54" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="60">
+      <c r="A52" s="54">
         <v>2098</v>
       </c>
-      <c r="B52" s="60">
-        <v>1</v>
-      </c>
-      <c r="C52" s="60" t="s">
+      <c r="B52" s="54">
+        <v>1</v>
+      </c>
+      <c r="C52" s="54" t="s">
         <v>332</v>
       </c>
-      <c r="D52" s="60">
+      <c r="D52" s="54">
         <v>6746</v>
       </c>
       <c r="E52" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F52" s="60">
-        <v>1</v>
-      </c>
-      <c r="G52" s="65" t="s">
+      <c r="F52" s="54">
+        <v>1</v>
+      </c>
+      <c r="G52" s="54" t="s">
         <v>330</v>
       </c>
-      <c r="H52" s="65" t="s">
+      <c r="H52" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I52" s="58" t="s">
@@ -41448,77 +41803,77 @@
       <c r="J52" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K52" s="60" t="s">
+      <c r="K52" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L52" s="60"/>
-      <c r="M52" s="60"/>
-      <c r="N52" s="66">
+      <c r="L52" s="54"/>
+      <c r="M52" s="54"/>
+      <c r="N52" s="55">
         <v>46127</v>
       </c>
-      <c r="O52" s="60"/>
-      <c r="P52" s="60" t="s">
+      <c r="O52" s="54"/>
+      <c r="P52" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q52" s="65" t="s">
+      <c r="Q52" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R52" s="61" t="s">
+      <c r="R52" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S52" s="61" t="s">
+      <c r="S52" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T52" s="61" t="s">
+      <c r="T52" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U52" s="61" t="s">
+      <c r="U52" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V52" s="61" t="s">
+      <c r="V52" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W52" s="61" t="s">
+      <c r="W52" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X52" s="62" t="s">
+      <c r="X52" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="Y52" s="62" t="s">
+      <c r="Y52" s="61" t="s">
         <v>276</v>
       </c>
-      <c r="Z52" s="65"/>
-      <c r="AA52" s="60" t="s">
+      <c r="Z52" s="54"/>
+      <c r="AA52" s="54" t="s">
         <v>312</v>
       </c>
-      <c r="AB52" s="60">
+      <c r="AB52" s="54">
         <v>22</v>
       </c>
-      <c r="AC52" s="60"/>
+      <c r="AC52" s="54"/>
     </row>
     <row r="53" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="60">
+      <c r="A53" s="54">
         <v>2080</v>
       </c>
-      <c r="B53" s="60">
+      <c r="B53" s="54">
         <v>2</v>
       </c>
-      <c r="C53" s="60" t="s">
+      <c r="C53" s="54" t="s">
         <v>333</v>
       </c>
-      <c r="D53" s="60">
+      <c r="D53" s="54">
         <v>6726</v>
       </c>
       <c r="E53" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F53" s="60">
-        <v>1</v>
-      </c>
-      <c r="G53" s="65" t="s">
+      <c r="F53" s="54">
+        <v>1</v>
+      </c>
+      <c r="G53" s="54" t="s">
         <v>330</v>
       </c>
-      <c r="H53" s="65" t="s">
+      <c r="H53" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I53" s="58" t="s">
@@ -41527,79 +41882,79 @@
       <c r="J53" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K53" s="60" t="s">
+      <c r="K53" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L53" s="60"/>
-      <c r="M53" s="60"/>
-      <c r="N53" s="66">
+      <c r="L53" s="54"/>
+      <c r="M53" s="54"/>
+      <c r="N53" s="55">
         <v>46195</v>
       </c>
-      <c r="O53" s="60"/>
-      <c r="P53" s="60" t="s">
+      <c r="O53" s="54"/>
+      <c r="P53" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q53" s="65" t="s">
+      <c r="Q53" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R53" s="61" t="s">
+      <c r="R53" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S53" s="61" t="s">
+      <c r="S53" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T53" s="61" t="s">
+      <c r="T53" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U53" s="61" t="s">
+      <c r="U53" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V53" s="61" t="s">
+      <c r="V53" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W53" s="61" t="s">
+      <c r="W53" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X53" s="61" t="s">
+      <c r="X53" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="Y53" s="61" t="s">
+      <c r="Y53" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="Z53" s="65"/>
-      <c r="AA53" s="60" t="s">
+      <c r="Z53" s="54"/>
+      <c r="AA53" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB53" s="60">
+      <c r="AB53" s="54">
         <v>33</v>
       </c>
-      <c r="AC53" s="60" t="s">
+      <c r="AC53" s="54" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="60">
+      <c r="A54" s="54">
         <v>2080</v>
       </c>
-      <c r="B54" s="60">
-        <v>1</v>
-      </c>
-      <c r="C54" s="60" t="s">
+      <c r="B54" s="54">
+        <v>1</v>
+      </c>
+      <c r="C54" s="54" t="s">
         <v>333</v>
       </c>
-      <c r="D54" s="60">
+      <c r="D54" s="54">
         <v>6725</v>
       </c>
       <c r="E54" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F54" s="60">
-        <v>1</v>
-      </c>
-      <c r="G54" s="65" t="s">
+      <c r="F54" s="54">
+        <v>1</v>
+      </c>
+      <c r="G54" s="54" t="s">
         <v>330</v>
       </c>
-      <c r="H54" s="65" t="s">
+      <c r="H54" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I54" s="58" t="s">
@@ -41608,58 +41963,58 @@
       <c r="J54" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K54" s="60" t="s">
+      <c r="K54" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L54" s="60"/>
-      <c r="M54" s="60"/>
-      <c r="N54" s="66">
+      <c r="L54" s="54"/>
+      <c r="M54" s="54"/>
+      <c r="N54" s="55">
         <v>46101</v>
       </c>
-      <c r="O54" s="60"/>
-      <c r="P54" s="60" t="s">
+      <c r="O54" s="54"/>
+      <c r="P54" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q54" s="65" t="s">
+      <c r="Q54" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R54" s="61" t="s">
+      <c r="R54" s="60" t="s">
         <v>267</v>
       </c>
-      <c r="S54" s="61" t="s">
+      <c r="S54" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T54" s="61" t="s">
+      <c r="T54" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="U54" s="61" t="s">
+      <c r="U54" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="V54" s="61" t="s">
+      <c r="V54" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="W54" s="61" t="s">
+      <c r="W54" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="X54" s="61" t="s">
+      <c r="X54" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="Y54" s="61" t="s">
+      <c r="Y54" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="Z54" s="65"/>
-      <c r="AA54" s="60" t="s">
+      <c r="Z54" s="54"/>
+      <c r="AA54" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="AB54" s="60">
+      <c r="AB54" s="54">
         <v>44</v>
       </c>
-      <c r="AC54" s="60" t="s">
+      <c r="AC54" s="54" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="63" t="s">
+      <c r="A55" s="62" t="s">
         <v>340</v>
       </c>
       <c r="B55" s="58">
@@ -41668,7 +42023,7 @@
       <c r="C55" s="58" t="s">
         <v>334</v>
       </c>
-      <c r="D55" s="63">
+      <c r="D55" s="62">
         <v>6751</v>
       </c>
       <c r="E55" s="58" t="s">
@@ -41677,10 +42032,10 @@
       <c r="F55" s="58">
         <v>1</v>
       </c>
-      <c r="G55" s="65" t="s">
+      <c r="G55" s="54" t="s">
         <v>330</v>
       </c>
-      <c r="H55" s="65" t="s">
+      <c r="H55" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I55" s="58" t="s">
@@ -41689,19 +42044,19 @@
       <c r="J55" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K55" s="60" t="s">
+      <c r="K55" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L55" s="60"/>
-      <c r="M55" s="60"/>
-      <c r="N55" s="64">
+      <c r="L55" s="54"/>
+      <c r="M55" s="54"/>
+      <c r="N55" s="63">
         <v>46127</v>
       </c>
-      <c r="O55" s="60"/>
-      <c r="P55" s="60" t="s">
+      <c r="O55" s="54"/>
+      <c r="P55" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q55" s="65" t="s">
+      <c r="Q55" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R55" s="58" t="s">
@@ -41728,15 +42083,15 @@
       <c r="Y55" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z55" s="60"/>
-      <c r="AA55" s="60"/>
+      <c r="Z55" s="54"/>
+      <c r="AA55" s="54"/>
       <c r="AB55" s="57">
         <v>78</v>
       </c>
-      <c r="AC55" s="60"/>
+      <c r="AC55" s="54"/>
     </row>
     <row r="56" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="63" t="s">
+      <c r="A56" s="62" t="s">
         <v>341</v>
       </c>
       <c r="B56" s="58">
@@ -41745,7 +42100,7 @@
       <c r="C56" s="58" t="s">
         <v>334</v>
       </c>
-      <c r="D56" s="63">
+      <c r="D56" s="62">
         <v>6749</v>
       </c>
       <c r="E56" s="58" t="s">
@@ -41754,10 +42109,10 @@
       <c r="F56" s="58">
         <v>1</v>
       </c>
-      <c r="G56" s="65" t="s">
+      <c r="G56" s="54" t="s">
         <v>330</v>
       </c>
-      <c r="H56" s="65" t="s">
+      <c r="H56" s="54" t="s">
         <v>306</v>
       </c>
       <c r="I56" s="58" t="s">
@@ -41766,19 +42121,19 @@
       <c r="J56" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K56" s="60" t="s">
+      <c r="K56" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L56" s="60"/>
-      <c r="M56" s="60"/>
-      <c r="N56" s="64">
+      <c r="L56" s="54"/>
+      <c r="M56" s="54"/>
+      <c r="N56" s="63">
         <v>46127</v>
       </c>
-      <c r="O56" s="60"/>
-      <c r="P56" s="60" t="s">
+      <c r="O56" s="54"/>
+      <c r="P56" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q56" s="65" t="s">
+      <c r="Q56" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R56" s="58" t="s">
@@ -41805,15 +42160,15 @@
       <c r="Y56" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z56" s="60"/>
-      <c r="AA56" s="60"/>
+      <c r="Z56" s="54"/>
+      <c r="AA56" s="54"/>
       <c r="AB56" s="57">
         <v>82</v>
       </c>
-      <c r="AC56" s="60"/>
+      <c r="AC56" s="54"/>
     </row>
     <row r="57" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="63" t="s">
+      <c r="A57" s="62" t="s">
         <v>342</v>
       </c>
       <c r="B57" s="58">
@@ -41822,7 +42177,7 @@
       <c r="C57" s="58" t="s">
         <v>334</v>
       </c>
-      <c r="D57" s="63">
+      <c r="D57" s="62">
         <v>6750</v>
       </c>
       <c r="E57" s="58" t="s">
@@ -41831,7 +42186,7 @@
       <c r="F57" s="58">
         <v>1</v>
       </c>
-      <c r="G57" s="72" t="s">
+      <c r="G57" s="58" t="s">
         <v>330</v>
       </c>
       <c r="H57" s="58" t="s">
@@ -41843,19 +42198,19 @@
       <c r="J57" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K57" s="60" t="s">
+      <c r="K57" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L57" s="60"/>
-      <c r="M57" s="60"/>
-      <c r="N57" s="64">
+      <c r="L57" s="54"/>
+      <c r="M57" s="54"/>
+      <c r="N57" s="63">
         <v>46127</v>
       </c>
-      <c r="O57" s="60"/>
-      <c r="P57" s="60" t="s">
+      <c r="O57" s="54"/>
+      <c r="P57" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q57" s="65" t="s">
+      <c r="Q57" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R57" s="58" t="s">
@@ -41882,15 +42237,15 @@
       <c r="Y57" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z57" s="60"/>
-      <c r="AA57" s="60"/>
+      <c r="Z57" s="54"/>
+      <c r="AA57" s="54"/>
       <c r="AB57" s="57">
         <v>85</v>
       </c>
-      <c r="AC57" s="60"/>
+      <c r="AC57" s="54"/>
     </row>
     <row r="58" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="62" t="s">
         <v>343</v>
       </c>
       <c r="B58" s="58">
@@ -41899,7 +42254,7 @@
       <c r="C58" s="58" t="s">
         <v>334</v>
       </c>
-      <c r="D58" s="63" t="s">
+      <c r="D58" s="62" t="s">
         <v>77</v>
       </c>
       <c r="E58" s="58" t="s">
@@ -41908,10 +42263,10 @@
       <c r="F58" s="58">
         <v>1</v>
       </c>
-      <c r="G58" s="72" t="s">
+      <c r="G58" s="58" t="s">
         <v>330</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>305</v>
       </c>
       <c r="I58" s="58" t="s">
@@ -41920,46 +42275,46 @@
       <c r="J58" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="L58" s="60"/>
-      <c r="M58" s="60"/>
-      <c r="N58" s="64">
+      <c r="L58" s="54"/>
+      <c r="M58" s="54"/>
+      <c r="N58" s="63">
         <v>46101</v>
       </c>
-      <c r="O58" s="60"/>
-      <c r="P58" s="60" t="s">
+      <c r="O58" s="54"/>
+      <c r="P58" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q58" s="65" t="s">
+      <c r="Q58" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R58" s="60" t="s">
+      <c r="R58" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="S58" s="60" t="s">
+      <c r="S58" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="T58" s="60" t="s">
+      <c r="T58" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="U58" s="60" t="s">
+      <c r="U58" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="V58" s="60"/>
-      <c r="W58" s="60"/>
-      <c r="X58" s="60"/>
-      <c r="Y58" s="60"/>
-      <c r="Z58" s="60"/>
-      <c r="AA58" s="60"/>
+      <c r="V58" s="54"/>
+      <c r="W58" s="54"/>
+      <c r="X58" s="54"/>
+      <c r="Y58" s="54"/>
+      <c r="Z58" s="54"/>
+      <c r="AA58" s="54"/>
       <c r="AB58" s="57">
         <v>86</v>
       </c>
-      <c r="AC58" s="60"/>
+      <c r="AC58" s="54"/>
     </row>
     <row r="59" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="63" t="s">
+      <c r="A59" s="62" t="s">
         <v>344</v>
       </c>
       <c r="B59" s="58">
@@ -41968,7 +42323,7 @@
       <c r="C59" s="58" t="s">
         <v>335</v>
       </c>
-      <c r="D59" s="63">
+      <c r="D59" s="62">
         <v>6731</v>
       </c>
       <c r="E59" s="58" t="s">
@@ -41977,7 +42332,7 @@
       <c r="F59" s="58">
         <v>1</v>
       </c>
-      <c r="G59" s="71">
+      <c r="G59" s="64">
         <v>2000</v>
       </c>
       <c r="H59" s="58" t="s">
@@ -41989,19 +42344,19 @@
       <c r="J59" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K59" s="60" t="s">
+      <c r="K59" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L59" s="60"/>
-      <c r="M59" s="60"/>
-      <c r="N59" s="64">
+      <c r="L59" s="54"/>
+      <c r="M59" s="54"/>
+      <c r="N59" s="63">
         <v>46101</v>
       </c>
-      <c r="O59" s="60"/>
-      <c r="P59" s="60" t="s">
+      <c r="O59" s="54"/>
+      <c r="P59" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q59" s="65" t="s">
+      <c r="Q59" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R59" s="58" t="s">
@@ -42028,15 +42383,15 @@
       <c r="Y59" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z59" s="60"/>
-      <c r="AA59" s="60"/>
+      <c r="Z59" s="54"/>
+      <c r="AA59" s="54"/>
       <c r="AB59" s="57">
         <v>38</v>
       </c>
-      <c r="AC59" s="60"/>
+      <c r="AC59" s="54"/>
     </row>
     <row r="60" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="63" t="s">
+      <c r="A60" s="62" t="s">
         <v>345</v>
       </c>
       <c r="B60" s="58">
@@ -42045,7 +42400,7 @@
       <c r="C60" s="58" t="s">
         <v>335</v>
       </c>
-      <c r="D60" s="63">
+      <c r="D60" s="62">
         <v>6732</v>
       </c>
       <c r="E60" s="58" t="s">
@@ -42054,10 +42409,10 @@
       <c r="F60" s="58">
         <v>1</v>
       </c>
-      <c r="G60" s="71">
+      <c r="G60" s="64">
         <v>2000</v>
       </c>
-      <c r="H60" s="63" t="s">
+      <c r="H60" s="62" t="s">
         <v>305</v>
       </c>
       <c r="I60" s="58" t="s">
@@ -42066,46 +42421,46 @@
       <c r="J60" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K60" s="60" t="s">
+      <c r="K60" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L60" s="60"/>
-      <c r="M60" s="60"/>
-      <c r="N60" s="64">
+      <c r="L60" s="54"/>
+      <c r="M60" s="54"/>
+      <c r="N60" s="63">
         <v>46101</v>
       </c>
-      <c r="O60" s="60"/>
-      <c r="P60" s="60" t="s">
+      <c r="O60" s="54"/>
+      <c r="P60" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q60" s="65" t="s">
+      <c r="Q60" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R60" s="60" t="s">
+      <c r="R60" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="S60" s="60" t="s">
+      <c r="S60" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="T60" s="60" t="s">
+      <c r="T60" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="U60" s="60" t="s">
+      <c r="U60" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="V60" s="60"/>
-      <c r="W60" s="60"/>
-      <c r="X60" s="60"/>
-      <c r="Y60" s="60"/>
-      <c r="Z60" s="60"/>
-      <c r="AA60" s="60"/>
+      <c r="V60" s="54"/>
+      <c r="W60" s="54"/>
+      <c r="X60" s="54"/>
+      <c r="Y60" s="54"/>
+      <c r="Z60" s="54"/>
+      <c r="AA60" s="54"/>
       <c r="AB60" s="57">
         <v>62</v>
       </c>
-      <c r="AC60" s="60"/>
+      <c r="AC60" s="54"/>
     </row>
     <row r="61" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="63" t="s">
+      <c r="A61" s="62" t="s">
         <v>346</v>
       </c>
       <c r="B61" s="58">
@@ -42114,7 +42469,7 @@
       <c r="C61" s="58" t="s">
         <v>336</v>
       </c>
-      <c r="D61" s="63">
+      <c r="D61" s="62">
         <v>6775</v>
       </c>
       <c r="E61" s="58" t="s">
@@ -42123,7 +42478,7 @@
       <c r="F61" s="58">
         <v>1</v>
       </c>
-      <c r="G61" s="72" t="s">
+      <c r="G61" s="58" t="s">
         <v>315</v>
       </c>
       <c r="H61" s="58" t="s">
@@ -42135,19 +42490,19 @@
       <c r="J61" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K61" s="60" t="s">
+      <c r="K61" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L61" s="60"/>
-      <c r="M61" s="60"/>
-      <c r="N61" s="64">
+      <c r="L61" s="54"/>
+      <c r="M61" s="54"/>
+      <c r="N61" s="63">
         <v>46101</v>
       </c>
-      <c r="O61" s="60"/>
-      <c r="P61" s="60" t="s">
+      <c r="O61" s="54"/>
+      <c r="P61" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q61" s="65" t="s">
+      <c r="Q61" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R61" s="58" t="s">
@@ -42174,15 +42529,15 @@
       <c r="Y61" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z61" s="60"/>
-      <c r="AA61" s="60"/>
+      <c r="Z61" s="54"/>
+      <c r="AA61" s="54"/>
       <c r="AB61" s="57">
         <v>114</v>
       </c>
-      <c r="AC61" s="60"/>
+      <c r="AC61" s="54"/>
     </row>
     <row r="62" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="63" t="s">
+      <c r="A62" s="62" t="s">
         <v>347</v>
       </c>
       <c r="B62" s="58">
@@ -42191,7 +42546,7 @@
       <c r="C62" s="58" t="s">
         <v>336</v>
       </c>
-      <c r="D62" s="63">
+      <c r="D62" s="62">
         <v>6767</v>
       </c>
       <c r="E62" s="58" t="s">
@@ -42200,10 +42555,10 @@
       <c r="F62" s="58">
         <v>1</v>
       </c>
-      <c r="G62" s="72" t="s">
+      <c r="G62" s="58" t="s">
         <v>315</v>
       </c>
-      <c r="H62" s="63" t="s">
+      <c r="H62" s="62" t="s">
         <v>309</v>
       </c>
       <c r="I62" s="58" t="s">
@@ -42212,46 +42567,46 @@
       <c r="J62" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K62" s="60" t="s">
+      <c r="K62" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L62" s="60"/>
-      <c r="M62" s="60"/>
-      <c r="N62" s="64">
+      <c r="L62" s="54"/>
+      <c r="M62" s="54"/>
+      <c r="N62" s="63">
         <v>46101</v>
       </c>
-      <c r="O62" s="60"/>
-      <c r="P62" s="60" t="s">
+      <c r="O62" s="54"/>
+      <c r="P62" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q62" s="65" t="s">
+      <c r="Q62" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R62" s="60" t="s">
+      <c r="R62" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="S62" s="60" t="s">
+      <c r="S62" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="T62" s="60" t="s">
+      <c r="T62" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="U62" s="60" t="s">
+      <c r="U62" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="V62" s="60"/>
-      <c r="W62" s="60"/>
-      <c r="X62" s="60"/>
-      <c r="Y62" s="60"/>
-      <c r="Z62" s="60"/>
-      <c r="AA62" s="60"/>
+      <c r="V62" s="54"/>
+      <c r="W62" s="54"/>
+      <c r="X62" s="54"/>
+      <c r="Y62" s="54"/>
+      <c r="Z62" s="54"/>
+      <c r="AA62" s="54"/>
       <c r="AB62" s="57" t="s">
         <v>366</v>
       </c>
-      <c r="AC62" s="60"/>
+      <c r="AC62" s="54"/>
     </row>
     <row r="63" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="63" t="s">
+      <c r="A63" s="62" t="s">
         <v>348</v>
       </c>
       <c r="B63" s="58">
@@ -42260,7 +42615,7 @@
       <c r="C63" s="58" t="s">
         <v>336</v>
       </c>
-      <c r="D63" s="63">
+      <c r="D63" s="62">
         <v>6768</v>
       </c>
       <c r="E63" s="58" t="s">
@@ -42269,7 +42624,7 @@
       <c r="F63" s="58">
         <v>1</v>
       </c>
-      <c r="G63" s="72" t="s">
+      <c r="G63" s="58" t="s">
         <v>315</v>
       </c>
       <c r="H63" s="58" t="s">
@@ -42281,19 +42636,19 @@
       <c r="J63" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K63" s="60" t="s">
+      <c r="K63" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L63" s="60"/>
-      <c r="M63" s="60"/>
-      <c r="N63" s="64">
+      <c r="L63" s="54"/>
+      <c r="M63" s="54"/>
+      <c r="N63" s="63">
         <v>46101</v>
       </c>
-      <c r="O63" s="60"/>
-      <c r="P63" s="60" t="s">
+      <c r="O63" s="54"/>
+      <c r="P63" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q63" s="65" t="s">
+      <c r="Q63" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R63" s="58" t="s">
@@ -42320,15 +42675,15 @@
       <c r="Y63" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z63" s="60"/>
-      <c r="AA63" s="60"/>
+      <c r="Z63" s="54"/>
+      <c r="AA63" s="54"/>
       <c r="AB63" s="57" t="s">
         <v>367</v>
       </c>
-      <c r="AC63" s="60"/>
+      <c r="AC63" s="54"/>
     </row>
     <row r="64" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="63" t="s">
+      <c r="A64" s="62" t="s">
         <v>349</v>
       </c>
       <c r="B64" s="58">
@@ -42337,7 +42692,7 @@
       <c r="C64" s="58" t="s">
         <v>337</v>
       </c>
-      <c r="D64" s="63">
+      <c r="D64" s="62">
         <v>6763</v>
       </c>
       <c r="E64" s="58" t="s">
@@ -42346,7 +42701,7 @@
       <c r="F64" s="58">
         <v>1</v>
       </c>
-      <c r="G64" s="72" t="s">
+      <c r="G64" s="58" t="s">
         <v>330</v>
       </c>
       <c r="H64" s="58" t="s">
@@ -42358,19 +42713,19 @@
       <c r="J64" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K64" s="60" t="s">
+      <c r="K64" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L64" s="60"/>
-      <c r="M64" s="60"/>
-      <c r="N64" s="64">
+      <c r="L64" s="54"/>
+      <c r="M64" s="54"/>
+      <c r="N64" s="63">
         <v>46101</v>
       </c>
-      <c r="O64" s="60"/>
-      <c r="P64" s="60" t="s">
+      <c r="O64" s="54"/>
+      <c r="P64" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q64" s="65" t="s">
+      <c r="Q64" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R64" s="58" t="s">
@@ -42397,15 +42752,15 @@
       <c r="Y64" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z64" s="60"/>
-      <c r="AA64" s="60"/>
+      <c r="Z64" s="54"/>
+      <c r="AA64" s="54"/>
       <c r="AB64" s="57" t="s">
         <v>368</v>
       </c>
-      <c r="AC64" s="60"/>
+      <c r="AC64" s="54"/>
     </row>
     <row r="65" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="63" t="s">
+      <c r="A65" s="62" t="s">
         <v>350</v>
       </c>
       <c r="B65" s="58">
@@ -42414,7 +42769,7 @@
       <c r="C65" s="58" t="s">
         <v>337</v>
       </c>
-      <c r="D65" s="63">
+      <c r="D65" s="62">
         <v>6729</v>
       </c>
       <c r="E65" s="58" t="s">
@@ -42423,10 +42778,10 @@
       <c r="F65" s="58">
         <v>1</v>
       </c>
-      <c r="G65" s="72" t="s">
+      <c r="G65" s="58" t="s">
         <v>364</v>
       </c>
-      <c r="H65" s="63" t="s">
+      <c r="H65" s="62" t="s">
         <v>309</v>
       </c>
       <c r="I65" s="58" t="s">
@@ -42435,46 +42790,46 @@
       <c r="J65" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K65" s="60" t="s">
+      <c r="K65" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L65" s="60"/>
-      <c r="M65" s="60"/>
-      <c r="N65" s="64">
+      <c r="L65" s="54"/>
+      <c r="M65" s="54"/>
+      <c r="N65" s="63">
         <v>46101</v>
       </c>
-      <c r="O65" s="60"/>
-      <c r="P65" s="60" t="s">
+      <c r="O65" s="54"/>
+      <c r="P65" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q65" s="65" t="s">
+      <c r="Q65" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R65" s="60" t="s">
+      <c r="R65" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="S65" s="60" t="s">
+      <c r="S65" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="T65" s="60" t="s">
+      <c r="T65" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="U65" s="60" t="s">
+      <c r="U65" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="V65" s="60"/>
-      <c r="W65" s="60"/>
-      <c r="X65" s="60"/>
-      <c r="Y65" s="60"/>
-      <c r="Z65" s="60"/>
-      <c r="AA65" s="60"/>
+      <c r="V65" s="54"/>
+      <c r="W65" s="54"/>
+      <c r="X65" s="54"/>
+      <c r="Y65" s="54"/>
+      <c r="Z65" s="54"/>
+      <c r="AA65" s="54"/>
       <c r="AB65" s="57" t="s">
         <v>369</v>
       </c>
-      <c r="AC65" s="60"/>
+      <c r="AC65" s="54"/>
     </row>
     <row r="66" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="63" t="s">
+      <c r="A66" s="62" t="s">
         <v>351</v>
       </c>
       <c r="B66" s="58">
@@ -42483,7 +42838,7 @@
       <c r="C66" s="58" t="s">
         <v>338</v>
       </c>
-      <c r="D66" s="63">
+      <c r="D66" s="62">
         <v>6733</v>
       </c>
       <c r="E66" s="58" t="s">
@@ -42492,10 +42847,10 @@
       <c r="F66" s="58">
         <v>1</v>
       </c>
-      <c r="G66" s="72" t="s">
+      <c r="G66" s="58" t="s">
         <v>365</v>
       </c>
-      <c r="H66" s="63" t="s">
+      <c r="H66" s="62" t="s">
         <v>309</v>
       </c>
       <c r="I66" s="58" t="s">
@@ -42504,46 +42859,46 @@
       <c r="J66" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K66" s="60" t="s">
+      <c r="K66" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L66" s="60"/>
-      <c r="M66" s="60"/>
-      <c r="N66" s="64">
+      <c r="L66" s="54"/>
+      <c r="M66" s="54"/>
+      <c r="N66" s="63">
         <v>46090</v>
       </c>
-      <c r="O66" s="60"/>
-      <c r="P66" s="60" t="s">
+      <c r="O66" s="54"/>
+      <c r="P66" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q66" s="65" t="s">
+      <c r="Q66" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R66" s="60" t="s">
+      <c r="R66" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="S66" s="60" t="s">
+      <c r="S66" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="T66" s="60" t="s">
+      <c r="T66" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="U66" s="60" t="s">
+      <c r="U66" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="V66" s="60"/>
-      <c r="W66" s="60"/>
-      <c r="X66" s="60"/>
-      <c r="Y66" s="60"/>
-      <c r="Z66" s="60"/>
-      <c r="AA66" s="60"/>
+      <c r="V66" s="54"/>
+      <c r="W66" s="54"/>
+      <c r="X66" s="54"/>
+      <c r="Y66" s="54"/>
+      <c r="Z66" s="54"/>
+      <c r="AA66" s="54"/>
       <c r="AB66" s="57" t="s">
         <v>370</v>
       </c>
-      <c r="AC66" s="60"/>
+      <c r="AC66" s="54"/>
     </row>
     <row r="67" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="63" t="s">
+      <c r="A67" s="62" t="s">
         <v>352</v>
       </c>
       <c r="B67" s="58">
@@ -42552,7 +42907,7 @@
       <c r="C67" s="58" t="s">
         <v>338</v>
       </c>
-      <c r="D67" s="63">
+      <c r="D67" s="62">
         <v>6779</v>
       </c>
       <c r="E67" s="58" t="s">
@@ -42561,7 +42916,7 @@
       <c r="F67" s="58">
         <v>1</v>
       </c>
-      <c r="G67" s="71">
+      <c r="G67" s="64">
         <v>2100</v>
       </c>
       <c r="H67" s="58" t="s">
@@ -42573,19 +42928,19 @@
       <c r="J67" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K67" s="60" t="s">
+      <c r="K67" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L67" s="60"/>
-      <c r="M67" s="60"/>
-      <c r="N67" s="64">
+      <c r="L67" s="54"/>
+      <c r="M67" s="54"/>
+      <c r="N67" s="63">
         <v>46090</v>
       </c>
-      <c r="O67" s="60"/>
-      <c r="P67" s="60" t="s">
+      <c r="O67" s="54"/>
+      <c r="P67" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q67" s="65" t="s">
+      <c r="Q67" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R67" s="58" t="s">
@@ -42612,15 +42967,15 @@
       <c r="Y67" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z67" s="60"/>
-      <c r="AA67" s="60"/>
+      <c r="Z67" s="54"/>
+      <c r="AA67" s="54"/>
       <c r="AB67" s="57" t="s">
         <v>371</v>
       </c>
-      <c r="AC67" s="60"/>
+      <c r="AC67" s="54"/>
     </row>
     <row r="68" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="63" t="s">
+      <c r="A68" s="62" t="s">
         <v>353</v>
       </c>
       <c r="B68" s="58">
@@ -42629,7 +42984,7 @@
       <c r="C68" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D68" s="63">
+      <c r="D68" s="62">
         <v>6759</v>
       </c>
       <c r="E68" s="58" t="s">
@@ -42638,7 +42993,7 @@
       <c r="F68" s="58">
         <v>1</v>
       </c>
-      <c r="G68" s="72" t="s">
+      <c r="G68" s="58" t="s">
         <v>330</v>
       </c>
       <c r="H68" s="58" t="s">
@@ -42650,19 +43005,19 @@
       <c r="J68" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K68" s="60" t="s">
+      <c r="K68" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L68" s="60"/>
-      <c r="M68" s="60"/>
-      <c r="N68" s="64">
+      <c r="L68" s="54"/>
+      <c r="M68" s="54"/>
+      <c r="N68" s="63">
         <v>46101</v>
       </c>
-      <c r="O68" s="60"/>
-      <c r="P68" s="60" t="s">
+      <c r="O68" s="54"/>
+      <c r="P68" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q68" s="65" t="s">
+      <c r="Q68" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R68" s="58" t="s">
@@ -42689,15 +43044,15 @@
       <c r="Y68" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z68" s="60"/>
-      <c r="AA68" s="60"/>
+      <c r="Z68" s="54"/>
+      <c r="AA68" s="54"/>
       <c r="AB68" s="57">
         <v>22</v>
       </c>
-      <c r="AC68" s="60"/>
+      <c r="AC68" s="54"/>
     </row>
     <row r="69" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="63" t="s">
+      <c r="A69" s="62" t="s">
         <v>354</v>
       </c>
       <c r="B69" s="58">
@@ -42706,7 +43061,7 @@
       <c r="C69" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D69" s="63">
+      <c r="D69" s="62">
         <v>6754</v>
       </c>
       <c r="E69" s="58" t="s">
@@ -42715,7 +43070,7 @@
       <c r="F69" s="58">
         <v>1</v>
       </c>
-      <c r="G69" s="72" t="s">
+      <c r="G69" s="58" t="s">
         <v>330</v>
       </c>
       <c r="H69" s="58" t="s">
@@ -42727,19 +43082,19 @@
       <c r="J69" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K69" s="60" t="s">
+      <c r="K69" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L69" s="60"/>
-      <c r="M69" s="60"/>
-      <c r="N69" s="64">
+      <c r="L69" s="54"/>
+      <c r="M69" s="54"/>
+      <c r="N69" s="63">
         <v>46101</v>
       </c>
-      <c r="O69" s="60"/>
-      <c r="P69" s="60" t="s">
+      <c r="O69" s="54"/>
+      <c r="P69" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q69" s="65" t="s">
+      <c r="Q69" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R69" s="58" t="s">
@@ -42766,15 +43121,15 @@
       <c r="Y69" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z69" s="60"/>
-      <c r="AA69" s="60"/>
+      <c r="Z69" s="54"/>
+      <c r="AA69" s="54"/>
       <c r="AB69" s="57">
         <v>24</v>
       </c>
-      <c r="AC69" s="60"/>
+      <c r="AC69" s="54"/>
     </row>
     <row r="70" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="63" t="s">
+      <c r="A70" s="62" t="s">
         <v>355</v>
       </c>
       <c r="B70" s="58">
@@ -42783,7 +43138,7 @@
       <c r="C70" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D70" s="63">
+      <c r="D70" s="62">
         <v>6760</v>
       </c>
       <c r="E70" s="58" t="s">
@@ -42792,7 +43147,7 @@
       <c r="F70" s="58">
         <v>1</v>
       </c>
-      <c r="G70" s="72" t="s">
+      <c r="G70" s="58" t="s">
         <v>330</v>
       </c>
       <c r="H70" s="58" t="s">
@@ -42804,19 +43159,19 @@
       <c r="J70" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K70" s="60" t="s">
+      <c r="K70" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L70" s="60"/>
-      <c r="M70" s="60"/>
-      <c r="N70" s="64">
+      <c r="L70" s="54"/>
+      <c r="M70" s="54"/>
+      <c r="N70" s="63">
         <v>46101</v>
       </c>
-      <c r="O70" s="60"/>
-      <c r="P70" s="60" t="s">
+      <c r="O70" s="54"/>
+      <c r="P70" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q70" s="65" t="s">
+      <c r="Q70" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R70" s="58" t="s">
@@ -42843,15 +43198,15 @@
       <c r="Y70" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z70" s="60"/>
-      <c r="AA70" s="60"/>
+      <c r="Z70" s="54"/>
+      <c r="AA70" s="54"/>
       <c r="AB70" s="57">
         <v>25</v>
       </c>
-      <c r="AC70" s="60"/>
+      <c r="AC70" s="54"/>
     </row>
     <row r="71" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="63" t="s">
+      <c r="A71" s="62" t="s">
         <v>356</v>
       </c>
       <c r="B71" s="58">
@@ -42860,7 +43215,7 @@
       <c r="C71" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D71" s="63">
+      <c r="D71" s="62">
         <v>6755</v>
       </c>
       <c r="E71" s="58" t="s">
@@ -42869,7 +43224,7 @@
       <c r="F71" s="58">
         <v>1</v>
       </c>
-      <c r="G71" s="72" t="s">
+      <c r="G71" s="58" t="s">
         <v>330</v>
       </c>
       <c r="H71" s="58" t="s">
@@ -42881,19 +43236,19 @@
       <c r="J71" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K71" s="60" t="s">
+      <c r="K71" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L71" s="60"/>
-      <c r="M71" s="60"/>
-      <c r="N71" s="64">
+      <c r="L71" s="54"/>
+      <c r="M71" s="54"/>
+      <c r="N71" s="63">
         <v>46101</v>
       </c>
-      <c r="O71" s="60"/>
-      <c r="P71" s="60" t="s">
+      <c r="O71" s="54"/>
+      <c r="P71" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q71" s="65" t="s">
+      <c r="Q71" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R71" s="58" t="s">
@@ -42920,15 +43275,15 @@
       <c r="Y71" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z71" s="60"/>
-      <c r="AA71" s="60"/>
+      <c r="Z71" s="54"/>
+      <c r="AA71" s="54"/>
       <c r="AB71" s="57">
         <v>30</v>
       </c>
-      <c r="AC71" s="60"/>
+      <c r="AC71" s="54"/>
     </row>
     <row r="72" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="63" t="s">
+      <c r="A72" s="62" t="s">
         <v>357</v>
       </c>
       <c r="B72" s="58">
@@ -42937,7 +43292,7 @@
       <c r="C72" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D72" s="63">
+      <c r="D72" s="62">
         <v>6758</v>
       </c>
       <c r="E72" s="58" t="s">
@@ -42946,7 +43301,7 @@
       <c r="F72" s="58">
         <v>1</v>
       </c>
-      <c r="G72" s="72" t="s">
+      <c r="G72" s="58" t="s">
         <v>330</v>
       </c>
       <c r="H72" s="58" t="s">
@@ -42958,19 +43313,19 @@
       <c r="J72" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K72" s="60" t="s">
+      <c r="K72" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L72" s="60"/>
-      <c r="M72" s="60"/>
-      <c r="N72" s="64">
+      <c r="L72" s="54"/>
+      <c r="M72" s="54"/>
+      <c r="N72" s="63">
         <v>46101</v>
       </c>
-      <c r="O72" s="60"/>
-      <c r="P72" s="60" t="s">
+      <c r="O72" s="54"/>
+      <c r="P72" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q72" s="65" t="s">
+      <c r="Q72" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R72" s="58" t="s">
@@ -42997,15 +43352,15 @@
       <c r="Y72" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z72" s="60"/>
-      <c r="AA72" s="60"/>
+      <c r="Z72" s="54"/>
+      <c r="AA72" s="54"/>
       <c r="AB72" s="57">
         <v>32</v>
       </c>
-      <c r="AC72" s="60"/>
+      <c r="AC72" s="54"/>
     </row>
     <row r="73" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="63" t="s">
+      <c r="A73" s="62" t="s">
         <v>358</v>
       </c>
       <c r="B73" s="58">
@@ -43014,7 +43369,7 @@
       <c r="C73" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D73" s="63">
+      <c r="D73" s="62">
         <v>6757</v>
       </c>
       <c r="E73" s="58" t="s">
@@ -43023,7 +43378,7 @@
       <c r="F73" s="58">
         <v>1</v>
       </c>
-      <c r="G73" s="72" t="s">
+      <c r="G73" s="58" t="s">
         <v>330</v>
       </c>
       <c r="H73" s="58" t="s">
@@ -43035,19 +43390,19 @@
       <c r="J73" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K73" s="60" t="s">
+      <c r="K73" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L73" s="60"/>
-      <c r="M73" s="60"/>
-      <c r="N73" s="64">
+      <c r="L73" s="54"/>
+      <c r="M73" s="54"/>
+      <c r="N73" s="63">
         <v>46101</v>
       </c>
-      <c r="O73" s="60"/>
-      <c r="P73" s="60" t="s">
+      <c r="O73" s="54"/>
+      <c r="P73" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q73" s="65" t="s">
+      <c r="Q73" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R73" s="58" t="s">
@@ -43074,15 +43429,15 @@
       <c r="Y73" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z73" s="60"/>
-      <c r="AA73" s="60"/>
+      <c r="Z73" s="54"/>
+      <c r="AA73" s="54"/>
       <c r="AB73" s="57">
         <v>46</v>
       </c>
-      <c r="AC73" s="60"/>
+      <c r="AC73" s="54"/>
     </row>
     <row r="74" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="63" t="s">
+      <c r="A74" s="62" t="s">
         <v>359</v>
       </c>
       <c r="B74" s="58">
@@ -43091,7 +43446,7 @@
       <c r="C74" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D74" s="63">
+      <c r="D74" s="62">
         <v>6753</v>
       </c>
       <c r="E74" s="58" t="s">
@@ -43100,7 +43455,7 @@
       <c r="F74" s="58">
         <v>1</v>
       </c>
-      <c r="G74" s="72" t="s">
+      <c r="G74" s="58" t="s">
         <v>315</v>
       </c>
       <c r="H74" s="58" t="s">
@@ -43112,19 +43467,19 @@
       <c r="J74" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K74" s="60" t="s">
+      <c r="K74" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L74" s="60"/>
-      <c r="M74" s="60"/>
-      <c r="N74" s="64">
+      <c r="L74" s="54"/>
+      <c r="M74" s="54"/>
+      <c r="N74" s="63">
         <v>46101</v>
       </c>
-      <c r="O74" s="60"/>
-      <c r="P74" s="60" t="s">
+      <c r="O74" s="54"/>
+      <c r="P74" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q74" s="65" t="s">
+      <c r="Q74" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R74" s="58" t="s">
@@ -43151,15 +43506,15 @@
       <c r="Y74" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z74" s="60"/>
-      <c r="AA74" s="60"/>
+      <c r="Z74" s="54"/>
+      <c r="AA74" s="54"/>
       <c r="AB74" s="57" t="s">
         <v>372</v>
       </c>
-      <c r="AC74" s="60"/>
+      <c r="AC74" s="54"/>
     </row>
     <row r="75" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="63" t="s">
+      <c r="A75" s="62" t="s">
         <v>360</v>
       </c>
       <c r="B75" s="58">
@@ -43168,7 +43523,7 @@
       <c r="C75" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D75" s="63">
+      <c r="D75" s="62">
         <v>6756</v>
       </c>
       <c r="E75" s="58" t="s">
@@ -43177,7 +43532,7 @@
       <c r="F75" s="58">
         <v>1</v>
       </c>
-      <c r="G75" s="72" t="s">
+      <c r="G75" s="58" t="s">
         <v>315</v>
       </c>
       <c r="H75" s="58" t="s">
@@ -43189,19 +43544,19 @@
       <c r="J75" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K75" s="60" t="s">
+      <c r="K75" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L75" s="60"/>
-      <c r="M75" s="60"/>
-      <c r="N75" s="64">
+      <c r="L75" s="54"/>
+      <c r="M75" s="54"/>
+      <c r="N75" s="63">
         <v>46101</v>
       </c>
-      <c r="O75" s="60"/>
-      <c r="P75" s="60" t="s">
+      <c r="O75" s="54"/>
+      <c r="P75" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q75" s="65" t="s">
+      <c r="Q75" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R75" s="58" t="s">
@@ -43228,15 +43583,15 @@
       <c r="Y75" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z75" s="60"/>
-      <c r="AA75" s="60"/>
+      <c r="Z75" s="54"/>
+      <c r="AA75" s="54"/>
       <c r="AB75" s="57" t="s">
         <v>373</v>
       </c>
-      <c r="AC75" s="60"/>
+      <c r="AC75" s="54"/>
     </row>
     <row r="76" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="63" t="s">
+      <c r="A76" s="62" t="s">
         <v>361</v>
       </c>
       <c r="B76" s="58">
@@ -43245,17 +43600,17 @@
       <c r="C76" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D76" s="63"/>
+      <c r="D76" s="62"/>
       <c r="E76" s="58" t="s">
         <v>363</v>
       </c>
       <c r="F76" s="58">
         <v>1</v>
       </c>
-      <c r="G76" s="72" t="s">
+      <c r="G76" s="58" t="s">
         <v>315</v>
       </c>
-      <c r="H76" s="63" t="s">
+      <c r="H76" s="62" t="s">
         <v>309</v>
       </c>
       <c r="I76" s="58" t="s">
@@ -43264,46 +43619,46 @@
       <c r="J76" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K76" s="60" t="s">
+      <c r="K76" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="L76" s="60"/>
-      <c r="M76" s="60"/>
-      <c r="N76" s="64">
+      <c r="L76" s="54"/>
+      <c r="M76" s="54"/>
+      <c r="N76" s="63">
         <v>46101</v>
       </c>
-      <c r="O76" s="60"/>
-      <c r="P76" s="60" t="s">
+      <c r="O76" s="54"/>
+      <c r="P76" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q76" s="65" t="s">
+      <c r="Q76" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="R76" s="60" t="s">
+      <c r="R76" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="S76" s="60" t="s">
+      <c r="S76" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="T76" s="60" t="s">
+      <c r="T76" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="U76" s="60" t="s">
+      <c r="U76" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="V76" s="60"/>
-      <c r="W76" s="60"/>
-      <c r="X76" s="60"/>
-      <c r="Y76" s="60"/>
-      <c r="Z76" s="60"/>
-      <c r="AA76" s="60"/>
+      <c r="V76" s="54"/>
+      <c r="W76" s="54"/>
+      <c r="X76" s="54"/>
+      <c r="Y76" s="54"/>
+      <c r="Z76" s="54"/>
+      <c r="AA76" s="54"/>
       <c r="AB76" s="57" t="s">
         <v>374</v>
       </c>
-      <c r="AC76" s="60"/>
+      <c r="AC76" s="54"/>
     </row>
     <row r="77" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="63" t="s">
+      <c r="A77" s="62" t="s">
         <v>362</v>
       </c>
       <c r="B77" s="58">
@@ -43312,7 +43667,7 @@
       <c r="C77" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D77" s="63">
+      <c r="D77" s="62">
         <v>6730</v>
       </c>
       <c r="E77" s="58" t="s">
@@ -43321,7 +43676,7 @@
       <c r="F77" s="58">
         <v>1</v>
       </c>
-      <c r="G77" s="72" t="s">
+      <c r="G77" s="58" t="s">
         <v>330</v>
       </c>
       <c r="H77" s="58" t="s">
@@ -43333,19 +43688,19 @@
       <c r="J77" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="K77" s="60" t="s">
+      <c r="K77" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="L77" s="60"/>
-      <c r="M77" s="60"/>
-      <c r="N77" s="64">
+      <c r="L77" s="54"/>
+      <c r="M77" s="54"/>
+      <c r="N77" s="63">
         <v>46101</v>
       </c>
-      <c r="O77" s="60"/>
-      <c r="P77" s="60" t="s">
+      <c r="O77" s="54"/>
+      <c r="P77" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="Q77" s="65" t="s">
+      <c r="Q77" s="54" t="s">
         <v>69</v>
       </c>
       <c r="R77" s="58" t="s">
@@ -43372,434 +43727,327 @@
       <c r="Y77" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="Z77" s="60"/>
-      <c r="AA77" s="60"/>
+      <c r="Z77" s="54"/>
+      <c r="AA77" s="54"/>
       <c r="AB77" s="57" t="s">
         <v>375</v>
       </c>
-      <c r="AC77" s="60"/>
-    </row>
-    <row r="78" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H78" s="73"/>
-    </row>
+      <c r="AC77" s="54"/>
+    </row>
+    <row r="78" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
-  <conditionalFormatting sqref="D30:D32">
-    <cfRule type="expression" dxfId="103" priority="64">
+  <conditionalFormatting sqref="A30:A43">
+    <cfRule type="containsText" dxfId="41" priority="50" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",A30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="51" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",A30)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="52">
       <formula>$P30="s"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D30:D32">
-    <cfRule type="containsText" dxfId="102" priority="62" operator="containsText" text="encamisado">
+  <conditionalFormatting sqref="A55:A77">
+    <cfRule type="containsText" dxfId="38" priority="17" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",A55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="37" priority="18" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",A55)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="19">
+      <formula>$P55="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C45:C49">
+    <cfRule type="containsText" dxfId="35" priority="29" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",C45)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="30" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",C45)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="31">
+      <formula>$P45="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C55:C77">
+    <cfRule type="containsText" dxfId="32" priority="25" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="26" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",C55)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="27">
+      <formula>$P55="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:D43">
+    <cfRule type="containsText" dxfId="29" priority="47" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",D30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="101" priority="63" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="28" priority="48" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",D30)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30:A32">
-    <cfRule type="expression" dxfId="100" priority="61">
+    <cfRule type="expression" dxfId="27" priority="49">
       <formula>$P30="s"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A30:A32">
-    <cfRule type="containsText" dxfId="99" priority="59" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",A30)))</formula>
+  <conditionalFormatting sqref="D55:D77">
+    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",D55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="60" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",A30)))</formula>
+    <cfRule type="containsText" dxfId="25" priority="22" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",D55)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="23">
+      <formula>$P55="s"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB30:AB32">
-    <cfRule type="expression" dxfId="94" priority="55">
+  <conditionalFormatting sqref="G59:G60 G67">
+    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="10" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",G59)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="12">
+      <formula>$P59="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H58 H60 H62 H65:H66 H76">
+    <cfRule type="containsText" dxfId="20" priority="13" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="14" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",H58)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="16">
+      <formula>$P58="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N33:N45">
+    <cfRule type="containsText" dxfId="17" priority="41" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",N33)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="42" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",N33)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="43">
+      <formula>$P33="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N55:N77">
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",N55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",N55)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="7">
+      <formula>$P55="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O33:O35">
+    <cfRule type="containsText" dxfId="11" priority="38" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",O33)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="39" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",O33)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="40">
+      <formula>$P33="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O37:O43">
+    <cfRule type="containsText" dxfId="8" priority="35" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",O37)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="36" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",O37)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="37">
+      <formula>$P37="s"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB30:AB43">
+    <cfRule type="containsText" dxfId="5" priority="44" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",AB30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="45" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",AB30)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="46">
       <formula>$P30="s"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB30:AB32">
-    <cfRule type="containsText" dxfId="93" priority="53" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",AB30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="54" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",AB30)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A33:A43">
-    <cfRule type="expression" dxfId="88" priority="52">
-      <formula>$P33="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A33:A43">
-    <cfRule type="containsText" dxfId="87" priority="50" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",A33)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="51" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",A33)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D33:D43">
-    <cfRule type="expression" dxfId="54" priority="49">
-      <formula>$P33="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D33:D43">
-    <cfRule type="containsText" dxfId="53" priority="47" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",D33)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="48" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",D33)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB33:AB43">
-    <cfRule type="expression" dxfId="51" priority="46">
-      <formula>$P33="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB33:AB43">
-    <cfRule type="containsText" dxfId="50" priority="44" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",AB33)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="49" priority="45" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",AB33)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N33:N45">
-    <cfRule type="expression" dxfId="45" priority="43">
-      <formula>$P33="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N33:N45">
-    <cfRule type="containsText" dxfId="44" priority="41" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",N33)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="42" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",N33)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O33:O35">
-    <cfRule type="expression" dxfId="42" priority="40">
-      <formula>$P33="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O33:O35">
-    <cfRule type="containsText" dxfId="41" priority="38" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",O33)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="39" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",O33)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O37:O43">
-    <cfRule type="expression" dxfId="36" priority="37">
-      <formula>$P37="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O37:O43">
-    <cfRule type="containsText" dxfId="35" priority="35" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",O37)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="36" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",O37)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C45">
-    <cfRule type="expression" dxfId="33" priority="34">
-      <formula>$P45="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C45">
-    <cfRule type="containsText" dxfId="32" priority="32" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",C45)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="33" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",C45)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C46:C49">
-    <cfRule type="expression" dxfId="30" priority="31">
-      <formula>$P46="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C46:C49">
-    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",C46)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",C46)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C55">
-    <cfRule type="expression" dxfId="27" priority="27">
-      <formula>$P55="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C56:C77">
-    <cfRule type="expression" dxfId="26" priority="28">
-      <formula>$P56="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C55:C77">
-    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",C55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D55">
-    <cfRule type="expression" dxfId="23" priority="23">
-      <formula>$P55="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D56:D77">
-    <cfRule type="expression" dxfId="22" priority="24">
-      <formula>$P56="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D55:D77">
-    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",D55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",D55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55">
-    <cfRule type="expression" dxfId="19" priority="19">
-      <formula>$P55="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A56:A77">
-    <cfRule type="expression" dxfId="18" priority="20">
-      <formula>$P56="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A55:A77">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",A55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",A55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H58 H60 H62 H65:H66 H76">
-    <cfRule type="expression" dxfId="14" priority="16">
-      <formula>$P58="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H58 H60 H62 H65:H66 H76">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",H58)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G59:G60 G67">
-    <cfRule type="expression" dxfId="10" priority="12">
-      <formula>$P59="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G59:G60 G67">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",G59)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N55">
-    <cfRule type="expression" dxfId="7" priority="7">
-      <formula>$P55="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N56:N77">
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>$P56="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N55:N77">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",N55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",N55)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB55">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>$P55="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB56:AB77">
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>$P56="s"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AB55:AB77">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="encamisado">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",AB55)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>$P55="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2663E33C-4698-4785-960F-15AD9DE32B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B196FF6-42DF-4DAA-80DD-63CE49BD0E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
@@ -4999,9 +4999,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="215" dataDxfId="214">
   <autoFilter ref="A1:AI114" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}">
-    <filterColumn colId="0">
+    <filterColumn colId="4">
       <filters>
-        <filter val="2202"/>
+        <filter val="MS Internacional"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8270,7 +8270,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>2227</v>
       </c>
@@ -8349,10 +8349,10 @@
         <v>77</v>
       </c>
       <c r="Y24" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z24" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AA24" s="10" t="s">
         <v>72</v>
@@ -8385,7 +8385,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>2227</v>
       </c>
@@ -8464,10 +8464,10 @@
         <v>77</v>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z25" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AA25" s="10" t="s">
         <v>72</v>
@@ -8500,7 +8500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <v>2227</v>
       </c>
@@ -8579,10 +8579,10 @@
         <v>77</v>
       </c>
       <c r="Y26" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z26" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AA26" s="10" t="s">
         <v>72</v>
@@ -8615,7 +8615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <v>2227</v>
       </c>
@@ -8694,10 +8694,10 @@
         <v>77</v>
       </c>
       <c r="Y27" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z27" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AA27" s="10" t="s">
         <v>72</v>
@@ -8730,7 +8730,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>2227</v>
       </c>
@@ -8809,10 +8809,10 @@
         <v>77</v>
       </c>
       <c r="Y28" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z28" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AA28" s="10" t="s">
         <v>72</v>
@@ -8845,7 +8845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="15">
         <v>2227</v>
       </c>
@@ -8924,10 +8924,10 @@
         <v>77</v>
       </c>
       <c r="Y29" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z29" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AA29" s="10" t="s">
         <v>72</v>
@@ -9075,7 +9075,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
         <v>2202</v>
       </c>
@@ -9191,7 +9191,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
         <v>2202</v>
       </c>
@@ -9306,7 +9306,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15">
         <v>2202</v>
       </c>
@@ -9421,7 +9421,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15">
         <v>2202</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
         <v>2202</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="75" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75" s="15">
         <v>2290</v>
       </c>
@@ -14167,7 +14167,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76" s="15">
         <v>2290</v>
       </c>
@@ -14279,7 +14279,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="77" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77" s="15">
         <v>2290</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B196FF6-42DF-4DAA-80DD-63CE49BD0E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F68BAA-E522-4AA5-B195-6A442D05619B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
   <sheets>
     <sheet name="BAGACEIRAS" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'VI DIVERSOS'!$A$1:$N$52</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Tabela1[#All]</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BAGACEIRAS!$A$1:$AI$113</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">BAGACEIRAS!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6385" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6801" uniqueCount="413">
   <si>
     <t>O.S.</t>
   </si>
@@ -1260,16 +1260,86 @@
   <si>
     <t>RNC 13891 - EXCESSO DE SOBREMETAL</t>
   </si>
+  <si>
+    <t>AG. INFORMAÇÃO DO CLIENTE</t>
+  </si>
+  <si>
+    <t>FUNDIDO ATRASOU - ERA 01/07/26</t>
+  </si>
+  <si>
+    <t>ANDAMENTO</t>
+  </si>
+  <si>
+    <t>SOLICITAÇÃO 65063 - PRZ 30/08</t>
+  </si>
+  <si>
+    <t>AG. MP</t>
+  </si>
+  <si>
+    <t>SOL. CHAPA 65105 - PRZ 20/07</t>
+  </si>
+  <si>
+    <t>SOL. CHAPA 65106 - PRZ 20/07</t>
+  </si>
+  <si>
+    <t>SOL. CHAPA 65107 - PRZ 20/07</t>
+  </si>
+  <si>
+    <t>Flange Sup. De Alta Drenagem</t>
+  </si>
+  <si>
+    <t>Calha Em Chapa Inferior (AISI 304)</t>
+  </si>
+  <si>
+    <t>Chapa De Vedação Ø1330</t>
+  </si>
+  <si>
+    <t>Arruela Esférica</t>
+  </si>
+  <si>
+    <t>Parafuso De Flange</t>
+  </si>
+  <si>
+    <t>CHAVETA RODETE DE MOENDA - 54"</t>
+  </si>
+  <si>
+    <t>FLANGE SUP. DE ALTA DRENAGEM -54"</t>
+  </si>
+  <si>
+    <t>CALHA ROLO INFERIOR AISI 304 - 54"</t>
+  </si>
+  <si>
+    <t>Santa Terezinha Iguatemi</t>
+  </si>
+  <si>
+    <t>CALHA ROLO INFERIOR - MDA 54"</t>
+  </si>
+  <si>
+    <t>CALHA ROLO INFERIOR - MDA 78"</t>
+  </si>
+  <si>
+    <t>FLANGE SUPERIOR EM CHAPA - 54"</t>
+  </si>
+  <si>
+    <t>SUPORTE DA BAlANÇA (MUNHÃO) - 54"</t>
+  </si>
+  <si>
+    <t>PENTE INF/SUP TIPO CONVENCIONAL - MDA 90"</t>
+  </si>
+  <si>
+    <t>PENTE INF/SUP TIPO CONVENCIONAL - 2000</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="167" formatCode="##0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1388,6 +1458,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1505,7 +1597,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1689,6 +1781,79 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4185,118 +4350,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF080000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -4983,6 +5036,118 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF080000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4997,111 +5162,111 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="215" dataDxfId="214">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="191" dataDxfId="190">
   <autoFilter ref="A1:AI114" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Atvos Santa Luzia"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="35">
+    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="189"/>
+    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="188"/>
+    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="187"/>
+    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="186"/>
+    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="185"/>
+    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="184"/>
+    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="183"/>
+    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="182"/>
+    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="181"/>
+    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="180"/>
+    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="179">
+      <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
+Fundido]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="178"/>
+    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="177"/>
+    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="176"/>
+    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="175">
+      <calculatedColumnFormula>Tabela1[[#This Row],[Prazo
+Entrega]]-TODAY()</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="174">
+      <calculatedColumnFormula>IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="173">
+      <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
+Entrega]],1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="172"/>
+    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="171"/>
+    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="170"/>
+    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="169"/>
+    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="168"/>
+    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="167"/>
+    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="166"/>
+    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="165"/>
+    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="164"/>
+    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="163"/>
+    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="162"/>
+    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="161">
+      <calculatedColumnFormula>IF(L2="","AG. FUNDIDO",IF(U2="AG","AG. USINAGEM","EM USINAGEM"))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="160"/>
+    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="159"/>
+    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="158"/>
+    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="157"/>
+    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="156"/>
+    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="155"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V163" totalsRowShown="0" headerRowDxfId="215" dataDxfId="214">
+  <autoFilter ref="A1:V163" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}">
     <filterColumn colId="4">
       <filters>
         <filter val="MS Internacional"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="213"/>
-    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="212"/>
-    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="211"/>
-    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="210"/>
-    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="209"/>
-    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="208"/>
-    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="207"/>
-    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="206"/>
-    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="205"/>
-    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="204"/>
-    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="203">
-      <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
-Fundido]])</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="202"/>
-    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="201"/>
-    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="200"/>
-    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="199">
-      <calculatedColumnFormula>Tabela1[[#This Row],[Prazo
-Entrega]]-TODAY()</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="198">
-      <calculatedColumnFormula>IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="197">
-      <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
-Entrega]],1)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="196"/>
-    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="195"/>
-    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="194"/>
-    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="193"/>
-    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="192"/>
-    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="191"/>
-    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="190"/>
-    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="189"/>
-    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="188"/>
-    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="187"/>
-    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="186"/>
-    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="185">
-      <calculatedColumnFormula>IF(L2="","AG. FUNDIDO",IF(U2="AG","AG. USINAGEM","EM USINAGEM"))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="184"/>
-    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="183"/>
-    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="182"/>
-    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="181"/>
-    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="180"/>
-    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="179"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V156" totalsRowShown="0" headerRowDxfId="178" dataDxfId="177">
-  <autoFilter ref="A1:V156" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="São João Araras"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="176"/>
-    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="175"/>
-    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="174"/>
-    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="173"/>
-    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="172"/>
-    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="171"/>
-    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="170"/>
-    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="169"/>
-    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="168"/>
-    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="167"/>
-    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="166">
+    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="213"/>
+    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="212"/>
+    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="211"/>
+    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="210"/>
+    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="209"/>
+    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="208"/>
+    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="207"/>
+    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="206"/>
+    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="205"/>
+    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="204"/>
+    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="203">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="165"/>
-    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="164"/>
-    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="163"/>
-    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="162"/>
-    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="161"/>
-    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="160">
+    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="202"/>
+    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="201"/>
+    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="200"/>
+    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="199"/>
+    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="198"/>
+    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="197">
       <calculatedColumnFormula>Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="159">
+    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="196">
       <calculatedColumnFormula>IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="158">
+    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="195">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="157"/>
-    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="156"/>
-    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="155"/>
+    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="194"/>
+    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="193"/>
+    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="192"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5150,8 +5315,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T89" totalsRowShown="0" headerRowDxfId="126" dataDxfId="125">
-  <autoFilter ref="A1:T89" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}" name="Tabela4" displayName="Tabela4" ref="A1:T123" totalsRowShown="0" headerRowDxfId="126" dataDxfId="125">
+  <autoFilter ref="A1:T123" xr:uid="{8F2F252D-0322-4579-B9EF-622E98B5994C}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{56D3DA8E-4CA8-4DC6-8208-BAB93CDE51C0}" name="PV" dataDxfId="124"/>
     <tableColumn id="2" xr3:uid="{B14AE1B6-8C05-4725-BF42-3DBDB37AA4E3}" name="item" dataDxfId="123"/>
@@ -5779,7 +5944,7 @@
       <c r="O2" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P2" s="40" t="str">
         <f t="shared" ref="P2:P33" ca="1" si="0">IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -5893,7 +6058,7 @@
       <c r="O3" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P3" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6008,7 +6173,7 @@
       <c r="O4" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P4" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6123,7 +6288,7 @@
       <c r="O5" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P5" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6238,7 +6403,7 @@
       <c r="O6" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P6" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6356,7 +6521,7 @@
       <c r="O7" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P7" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6473,7 +6638,7 @@
       <c r="O8" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P8" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6589,7 +6754,7 @@
       <c r="O9" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P9" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6705,7 +6870,7 @@
       <c r="O10" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P10" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6821,7 +6986,7 @@
       <c r="O11" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P11" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6935,7 +7100,7 @@
       <c r="O12" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P12" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7050,7 +7215,7 @@
       <c r="O13" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P13" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7165,7 +7330,7 @@
       <c r="O14" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P14" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7280,7 +7445,7 @@
       <c r="O15" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P15" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7400,7 +7565,7 @@
       <c r="O16" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P16" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7516,7 +7681,7 @@
       <c r="O17" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P17" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7632,7 +7797,7 @@
       <c r="O18" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P18" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7748,7 +7913,7 @@
       <c r="O19" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P19" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7852,6 +8017,9 @@
 Fundido]])</f>
         <v>24</v>
       </c>
+      <c r="L20" s="11">
+        <v>46206</v>
+      </c>
       <c r="M20" s="16">
         <v>46227</v>
       </c>
@@ -7859,7 +8027,7 @@
       <c r="O20" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P20" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7905,7 +8073,7 @@
       </c>
       <c r="AC20" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>AG. FUNDIDO</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE20" s="42">
         <v>26</v>
@@ -7964,6 +8132,9 @@
 Fundido]])</f>
         <v>24</v>
       </c>
+      <c r="L21" s="11">
+        <v>46206</v>
+      </c>
       <c r="M21" s="16">
         <v>46220</v>
       </c>
@@ -7971,7 +8142,7 @@
       <c r="O21" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P21" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8017,7 +8188,7 @@
       </c>
       <c r="AC21" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>AG. FUNDIDO</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE21" s="42">
         <v>26</v>
@@ -8086,7 +8257,7 @@
       <c r="O22" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P22" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8201,7 +8372,7 @@
       <c r="O23" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P23" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8270,7 +8441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>2227</v>
       </c>
@@ -8316,7 +8487,7 @@
       <c r="O24" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P24" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8385,7 +8556,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>2227</v>
       </c>
@@ -8431,7 +8602,7 @@
       <c r="O25" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P25" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8500,7 +8671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <v>2227</v>
       </c>
@@ -8546,7 +8717,7 @@
       <c r="O26" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P26" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8615,7 +8786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <v>2227</v>
       </c>
@@ -8661,7 +8832,7 @@
       <c r="O27" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P27" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8730,7 +8901,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>2227</v>
       </c>
@@ -8776,7 +8947,7 @@
       <c r="O28" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P28" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8845,7 +9016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15">
         <v>2227</v>
       </c>
@@ -8891,7 +9062,7 @@
       <c r="O29" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P29" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9006,7 +9177,7 @@
       <c r="O30" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P30" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9123,7 +9294,7 @@
       <c r="O31" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P31" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9237,7 +9408,7 @@
       <c r="O32" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P32" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9352,7 +9523,7 @@
       <c r="O33" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P33" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9467,7 +9638,7 @@
       <c r="O34" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P34" s="40" t="str">
         <f t="shared" ref="P34:P65" ca="1" si="2">IF(O34&lt;0,"ATRASADO",IF(O34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -9582,7 +9753,7 @@
       <c r="O35" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P35" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9697,7 +9868,7 @@
       <c r="O36" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P36" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9812,7 +9983,7 @@
       <c r="O37" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P37" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9930,7 +10101,7 @@
       <c r="O38" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P38" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10038,11 +10209,13 @@
       <c r="M39" s="16">
         <v>46234</v>
       </c>
-      <c r="N39" s="16"/>
+      <c r="N39" s="16">
+        <v>46206</v>
+      </c>
       <c r="O39" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P39" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10086,9 +10259,8 @@
       <c r="AB39" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AC39" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v>AG. FUNDIDO</v>
+      <c r="AC39" s="10" t="s">
+        <v>151</v>
       </c>
       <c r="AE39" s="42">
         <v>27</v>
@@ -10154,7 +10326,7 @@
       <c r="O40" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P40" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10269,7 +10441,7 @@
       <c r="O41" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P41" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10384,7 +10556,7 @@
       <c r="O42" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P42" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10499,7 +10671,7 @@
       <c r="O43" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P43" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10611,7 +10783,7 @@
       <c r="O44" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P44" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10726,7 +10898,7 @@
       <c r="O45" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P45" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10841,7 +11013,7 @@
       <c r="O46" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P46" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10956,7 +11128,7 @@
       <c r="O47" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P47" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11061,6 +11233,9 @@
 Fundido]])</f>
         <v>25</v>
       </c>
+      <c r="L48" s="11">
+        <v>46206</v>
+      </c>
       <c r="M48" s="16">
         <v>46241</v>
       </c>
@@ -11068,7 +11243,7 @@
       <c r="O48" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P48" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11114,7 +11289,7 @@
       </c>
       <c r="AC48" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. FUNDIDO</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE48" s="42">
         <v>28</v>
@@ -11181,7 +11356,7 @@
       <c r="O49" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P49" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11294,7 +11469,7 @@
       <c r="O50" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P50" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11409,7 +11584,7 @@
       <c r="O51" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P51" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11524,7 +11699,7 @@
       <c r="O52" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P52" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11639,7 +11814,7 @@
       <c r="O53" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P53" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11744,6 +11919,9 @@
 Fundido]])</f>
         <v>26</v>
       </c>
+      <c r="L54" s="11">
+        <v>46206</v>
+      </c>
       <c r="M54" s="16">
         <v>46241</v>
       </c>
@@ -11751,7 +11929,7 @@
       <c r="O54" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P54" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11797,7 +11975,7 @@
       </c>
       <c r="AC54" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. FUNDIDO</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE54" s="42">
         <v>29</v>
@@ -11863,7 +12041,7 @@
       <c r="O55" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P55" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11968,6 +12146,9 @@
 Fundido]])</f>
         <v>26</v>
       </c>
+      <c r="L56" s="11">
+        <v>46206</v>
+      </c>
       <c r="M56" s="16">
         <v>46241</v>
       </c>
@@ -11975,7 +12156,7 @@
       <c r="O56" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P56" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12021,7 +12202,7 @@
       </c>
       <c r="AC56" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. FUNDIDO</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE56" s="42">
         <v>29</v>
@@ -12087,7 +12268,7 @@
       <c r="O57" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="P57" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12202,7 +12383,7 @@
       <c r="O58" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P58" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12317,7 +12498,7 @@
       <c r="O59" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P59" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12432,7 +12613,7 @@
       <c r="O60" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P60" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12542,7 +12723,7 @@
       <c r="O61" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P61" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12652,7 +12833,7 @@
       <c r="O62" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P62" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12762,7 +12943,7 @@
       <c r="O63" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P63" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12872,7 +13053,7 @@
       <c r="O64" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P64" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12982,7 +13163,7 @@
       <c r="O65" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P65" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -13092,7 +13273,7 @@
       <c r="O66" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P66" s="40" t="str">
         <f t="shared" ref="P66:P89" ca="1" si="4">IF(O66&lt;0,"ATRASADO",IF(O66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -13199,7 +13380,7 @@
       <c r="O67" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P67" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13314,7 +13495,7 @@
       <c r="O68" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P68" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13426,7 +13607,7 @@
       <c r="O69" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P69" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13538,7 +13719,7 @@
       <c r="O70" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P70" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13650,7 +13831,7 @@
       <c r="O71" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P71" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13762,7 +13943,7 @@
       <c r="O72" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P72" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13874,7 +14055,7 @@
       <c r="O73" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P73" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13986,7 +14167,7 @@
       <c r="O74" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P74" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14055,7 +14236,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="15">
         <v>2290</v>
       </c>
@@ -14098,7 +14279,7 @@
       <c r="O75" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P75" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14167,7 +14348,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="15">
         <v>2290</v>
       </c>
@@ -14210,7 +14391,7 @@
       <c r="O76" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P76" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14279,7 +14460,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="15">
         <v>2290</v>
       </c>
@@ -14322,7 +14503,7 @@
       <c r="O77" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P77" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14434,7 +14615,7 @@
       <c r="O78" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P78" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14544,7 +14725,7 @@
       <c r="O79" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P79" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14654,7 +14835,7 @@
       <c r="O80" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P80" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14764,7 +14945,7 @@
       <c r="O81" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P81" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14874,7 +15055,7 @@
       <c r="O82" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P82" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14984,7 +15165,7 @@
       <c r="O83" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P83" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15051,7 +15232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>2263</v>
       </c>
@@ -15094,7 +15275,7 @@
       <c r="O84" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P84" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15165,7 +15346,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>2263</v>
       </c>
@@ -15208,7 +15389,7 @@
       <c r="O85" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P85" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15279,7 +15460,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>2263</v>
       </c>
@@ -15322,7 +15503,7 @@
       <c r="O86" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P86" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15393,7 +15574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>2263</v>
       </c>
@@ -15436,7 +15617,7 @@
       <c r="O87" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P87" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15507,7 +15688,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>2263</v>
       </c>
@@ -15550,7 +15731,7 @@
       <c r="O88" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P88" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15621,7 +15802,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>2263</v>
       </c>
@@ -15664,7 +15845,7 @@
       <c r="O89" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P89" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15778,7 +15959,7 @@
       <c r="O90" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P90" s="40" t="str">
         <f t="shared" ref="P90:P94" ca="1" si="6">IF(O90&lt;0,"ATRASADO",IF(O90&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -15885,7 +16066,7 @@
       <c r="O91" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P91" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -15992,7 +16173,7 @@
       <c r="O92" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P92" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16099,7 +16280,7 @@
       <c r="O93" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P93" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16206,7 +16387,7 @@
       <c r="O94" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P94" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16313,7 +16494,7 @@
       <c r="O95" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P95" s="40" t="str">
         <f t="shared" ref="P95:P99" ca="1" si="7">IF(O95&lt;0,"ATRASADO",IF(O95&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16410,7 +16591,7 @@
       <c r="O96" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P96" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -16507,7 +16688,7 @@
       <c r="O97" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P97" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -16604,7 +16785,7 @@
       <c r="O98" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P98" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -16701,7 +16882,7 @@
       <c r="O99" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P99" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -16798,7 +16979,7 @@
       <c r="O100" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P100" s="40" t="str">
         <f ca="1">IF(O100&lt;0,"ATRASADO",IF(O100&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16895,7 +17076,7 @@
       <c r="O101" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P101" s="40" t="str">
         <f t="shared" ref="P101:P109" ca="1" si="9">IF(O101&lt;0,"ATRASADO",IF(O101&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16992,7 +17173,7 @@
       <c r="O102" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P102" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17089,7 +17270,7 @@
       <c r="O103" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P103" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17186,7 +17367,7 @@
       <c r="O104" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P104" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17283,7 +17464,7 @@
       <c r="O105" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P105" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17380,7 +17561,7 @@
       <c r="O106" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P106" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17477,7 +17658,7 @@
       <c r="O107" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P107" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17574,7 +17755,7 @@
       <c r="O108" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P108" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17671,7 +17852,7 @@
       <c r="O109" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P109" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17754,21 +17935,21 @@
         <v>1</v>
       </c>
       <c r="J110" s="16">
-        <v>46295</v>
+        <v>46269</v>
       </c>
       <c r="K110" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Fundido]])</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M110" s="16">
-        <v>46356</v>
+        <v>46325</v>
       </c>
       <c r="N110" s="16"/>
       <c r="O110" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="P110" s="40" t="str">
         <f ca="1">IF(O110&lt;0,"ATRASADO",IF(O110&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -17777,7 +17958,7 @@
       <c r="Q110" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Entrega]],1)</f>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="R110" s="10" t="s">
         <v>43</v>
@@ -17851,21 +18032,21 @@
         <v>1</v>
       </c>
       <c r="J111" s="16">
-        <v>46295</v>
+        <v>46269</v>
       </c>
       <c r="K111" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Fundido]])</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M111" s="16">
-        <v>46356</v>
+        <v>46325</v>
       </c>
       <c r="N111" s="16"/>
       <c r="O111" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="P111" s="40" t="str">
         <f t="shared" ref="P111:P114" ca="1" si="10">IF(O111&lt;0,"ATRASADO",IF(O111&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -17874,7 +18055,7 @@
       <c r="Q111" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Entrega]],1)</f>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="R111" s="10" t="s">
         <v>43</v>
@@ -17948,21 +18129,21 @@
         <v>1</v>
       </c>
       <c r="J112" s="16">
-        <v>46295</v>
+        <v>46269</v>
       </c>
       <c r="K112" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Fundido]])</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M112" s="16">
-        <v>46356</v>
+        <v>46325</v>
       </c>
       <c r="N112" s="16"/>
       <c r="O112" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="P112" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -17971,7 +18152,7 @@
       <c r="Q112" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Entrega]],1)</f>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="R112" s="10" t="s">
         <v>43</v>
@@ -18045,21 +18226,21 @@
         <v>1</v>
       </c>
       <c r="J113" s="16">
-        <v>46295</v>
+        <v>46269</v>
       </c>
       <c r="K113" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Fundido]])</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M113" s="16">
-        <v>46356</v>
+        <v>46325</v>
       </c>
       <c r="N113" s="16"/>
       <c r="O113" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="P113" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -18068,7 +18249,7 @@
       <c r="Q113" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Entrega]],1)</f>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="R113" s="10" t="s">
         <v>43</v>
@@ -18142,21 +18323,21 @@
         <v>1</v>
       </c>
       <c r="J114" s="16">
-        <v>46295</v>
+        <v>46269</v>
       </c>
       <c r="K114" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Fundido]])</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M114" s="16">
-        <v>46356</v>
+        <v>46325</v>
       </c>
       <c r="N114" s="16"/>
       <c r="O114" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="P114" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -18165,7 +18346,7 @@
       <c r="Q114" s="40">
         <f>WEEKNUM(Tabela1[[#This Row],[Prazo
 Entrega]],1)</f>
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="R114" s="10" t="s">
         <v>43</v>
@@ -18224,7 +18405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F053A7-2FDA-4BCA-8A08-44A595E3BEFC}">
-  <dimension ref="A1:V156"/>
+  <dimension ref="A1:V163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="1"/>
@@ -18366,7 +18547,7 @@
       <c r="Q2" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R2" s="10" t="str">
         <f t="shared" ref="R2:R33" ca="1" si="0">IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -18437,7 +18618,7 @@
       <c r="Q3" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R3" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18508,7 +18689,7 @@
       <c r="Q4" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R4" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18579,7 +18760,7 @@
       <c r="Q5" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R5" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18650,7 +18831,7 @@
       <c r="Q6" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R6" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18721,7 +18902,7 @@
       <c r="Q7" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R7" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18792,7 +18973,7 @@
       <c r="Q8" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R8" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18863,7 +19044,7 @@
       <c r="Q9" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R9" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18934,7 +19115,7 @@
       <c r="Q10" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R10" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19005,7 +19186,7 @@
       <c r="Q11" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R11" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19078,7 +19259,7 @@
       <c r="Q12" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R12" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19151,7 +19332,7 @@
       <c r="Q13" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R13" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19172,7 +19353,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="14" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>2227</v>
       </c>
@@ -19224,7 +19405,7 @@
       <c r="Q14" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R14" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19239,11 +19420,11 @@
         <v>43</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V14" s="10"/>
     </row>
-    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>2227</v>
       </c>
@@ -19295,7 +19476,7 @@
       <c r="Q15" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R15" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19310,11 +19491,11 @@
         <v>43</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V15" s="10"/>
     </row>
-    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>2227</v>
       </c>
@@ -19366,7 +19547,7 @@
       <c r="Q16" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R16" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19381,11 +19562,11 @@
         <v>43</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V16" s="10"/>
     </row>
-    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>2227</v>
       </c>
@@ -19437,7 +19618,7 @@
       <c r="Q17" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R17" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19452,11 +19633,11 @@
         <v>43</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V17" s="10"/>
     </row>
-    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>2227</v>
       </c>
@@ -19508,7 +19689,7 @@
       <c r="Q18" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R18" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19523,11 +19704,11 @@
         <v>43</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V18" s="10"/>
     </row>
-    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>2227</v>
       </c>
@@ -19579,7 +19760,7 @@
       <c r="Q19" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R19" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19594,11 +19775,11 @@
         <v>43</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V19" s="10"/>
     </row>
-    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>2227</v>
       </c>
@@ -19650,7 +19831,7 @@
       <c r="Q20" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R20" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19665,11 +19846,11 @@
         <v>43</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V20" s="10"/>
     </row>
-    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>2227</v>
       </c>
@@ -19721,7 +19902,7 @@
       <c r="Q21" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R21" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19736,11 +19917,11 @@
         <v>43</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V21" s="10"/>
     </row>
-    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>2227</v>
       </c>
@@ -19792,7 +19973,7 @@
       <c r="Q22" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R22" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19807,11 +19988,11 @@
         <v>43</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V22" s="10"/>
     </row>
-    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>2227</v>
       </c>
@@ -19863,7 +20044,7 @@
       <c r="Q23" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R23" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19878,11 +20059,11 @@
         <v>43</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V23" s="10"/>
     </row>
-    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>2227</v>
       </c>
@@ -19934,7 +20115,7 @@
       <c r="Q24" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R24" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19949,11 +20130,11 @@
         <v>43</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V24" s="10"/>
     </row>
-    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>2227</v>
       </c>
@@ -20005,7 +20186,7 @@
       <c r="Q25" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R25" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20024,7 +20205,7 @@
       </c>
       <c r="V25" s="10"/>
     </row>
-    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>2227</v>
       </c>
@@ -20076,7 +20257,7 @@
       <c r="Q26" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R26" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20091,11 +20272,11 @@
         <v>43</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>71</v>
+        <v>258</v>
       </c>
       <c r="V26" s="10"/>
     </row>
-    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>2227</v>
       </c>
@@ -20147,7 +20328,7 @@
       <c r="Q27" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R27" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20166,7 +20347,7 @@
       </c>
       <c r="V27" s="10"/>
     </row>
-    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>2227</v>
       </c>
@@ -20218,7 +20399,7 @@
       <c r="Q28" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R28" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20237,7 +20418,7 @@
       </c>
       <c r="V28" s="10"/>
     </row>
-    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>2227</v>
       </c>
@@ -20289,7 +20470,7 @@
       <c r="Q29" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R29" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20308,7 +20489,7 @@
       </c>
       <c r="V29" s="10"/>
     </row>
-    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>2227</v>
       </c>
@@ -20360,7 +20541,7 @@
       <c r="Q30" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R30" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20379,7 +20560,7 @@
       </c>
       <c r="V30" s="10"/>
     </row>
-    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>2227</v>
       </c>
@@ -20431,7 +20612,7 @@
       <c r="Q31" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R31" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20450,7 +20631,7 @@
       </c>
       <c r="V31" s="10"/>
     </row>
-    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>2227</v>
       </c>
@@ -20502,7 +20683,7 @@
       <c r="Q32" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R32" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20573,7 +20754,7 @@
       <c r="Q33" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20646,7 +20827,7 @@
       <c r="Q34" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R34" s="10" t="str">
         <f t="shared" ref="R34:R65" ca="1" si="1">IF(Q34&lt;0,"ATRASADO",IF(Q34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -20719,7 +20900,7 @@
       <c r="Q35" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R35" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20792,7 +20973,7 @@
       <c r="Q36" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R36" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20865,7 +21046,7 @@
       <c r="Q37" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R37" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20938,7 +21119,7 @@
       <c r="Q38" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R38" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21009,7 +21190,7 @@
       <c r="Q39" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R39" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21080,7 +21261,7 @@
       <c r="Q40" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R40" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21151,7 +21332,7 @@
       <c r="Q41" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R41" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21222,7 +21403,7 @@
       <c r="Q42" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R42" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21293,7 +21474,7 @@
       <c r="Q43" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R43" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21364,7 +21545,7 @@
       <c r="Q44" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R44" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21435,7 +21616,7 @@
       <c r="Q45" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R45" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21506,7 +21687,7 @@
       <c r="Q46" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R46" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21577,7 +21758,7 @@
       <c r="Q47" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R47" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21648,7 +21829,7 @@
       <c r="Q48" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R48" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21719,7 +21900,7 @@
       <c r="Q49" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R49" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21790,7 +21971,7 @@
       <c r="Q50" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R50" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21861,7 +22042,7 @@
       <c r="Q51" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R51" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21932,7 +22113,7 @@
       <c r="Q52" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R52" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22003,7 +22184,7 @@
       <c r="Q53" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R53" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22074,7 +22255,7 @@
       <c r="Q54" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R54" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22145,7 +22326,7 @@
       <c r="Q55" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R55" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22216,7 +22397,7 @@
       <c r="Q56" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R56" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22287,7 +22468,7 @@
       <c r="Q57" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R57" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22358,7 +22539,7 @@
       <c r="Q58" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R58" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22429,7 +22610,7 @@
       <c r="Q59" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R59" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22500,7 +22681,7 @@
       <c r="Q60" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R60" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22571,7 +22752,7 @@
       <c r="Q61" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R61" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22642,7 +22823,7 @@
       <c r="Q62" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R62" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22713,7 +22894,7 @@
       <c r="Q63" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R63" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22784,7 +22965,7 @@
       <c r="Q64" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R64" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22855,7 +23036,7 @@
       <c r="Q65" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R65" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22926,7 +23107,7 @@
       <c r="Q66" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R66" s="10" t="str">
         <f t="shared" ref="R66:R91" ca="1" si="2">IF(Q66&lt;0,"ATRASADO",IF(Q66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -22997,7 +23178,7 @@
       <c r="Q67" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R67" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23068,7 +23249,7 @@
       <c r="Q68" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R68" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23139,7 +23320,7 @@
       <c r="Q69" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R69" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23210,7 +23391,7 @@
       <c r="Q70" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R70" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23281,7 +23462,7 @@
       <c r="Q71" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R71" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23352,7 +23533,7 @@
       <c r="Q72" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R72" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23423,7 +23604,7 @@
       <c r="Q73" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R73" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23494,7 +23675,7 @@
       <c r="Q74" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R74" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23565,7 +23746,7 @@
       <c r="Q75" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R75" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23636,7 +23817,7 @@
       <c r="Q76" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R76" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23707,7 +23888,7 @@
       <c r="Q77" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R77" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23778,7 +23959,7 @@
       <c r="Q78" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R78" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23849,7 +24030,7 @@
       <c r="Q79" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="R79" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23920,7 +24101,7 @@
       <c r="Q80" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R80" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23991,7 +24172,7 @@
       <c r="Q81" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R81" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24062,7 +24243,7 @@
       <c r="Q82" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="R82" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24133,7 +24314,7 @@
       <c r="Q83" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R83" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24204,7 +24385,7 @@
       <c r="Q84" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R84" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24275,7 +24456,7 @@
       <c r="Q85" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R85" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24346,7 +24527,7 @@
       <c r="Q86" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R86" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24417,7 +24598,7 @@
       <c r="Q87" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R87" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24488,7 +24669,7 @@
       <c r="Q88" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R88" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24559,7 +24740,7 @@
       <c r="Q89" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R89" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24630,7 +24811,7 @@
       <c r="Q90" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R90" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24701,7 +24882,7 @@
       <c r="Q91" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="R91" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24749,7 +24930,7 @@
         <v>1</v>
       </c>
       <c r="J92" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K92" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -24764,7 +24945,7 @@
       <c r="O92" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P92" s="10" t="s">
         <v>72</v>
@@ -24772,7 +24953,7 @@
       <c r="Q92" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R92" s="10" t="str">
         <f ca="1">IF(Q92&lt;0,"ATRASADO",IF(Q92&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -24820,7 +25001,7 @@
         <v>1</v>
       </c>
       <c r="J93" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K93" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -24835,7 +25016,7 @@
       <c r="O93" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>72</v>
@@ -24843,7 +25024,7 @@
       <c r="Q93" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R93" s="10" t="str">
         <f ca="1">IF(Q93&lt;0,"ATRASADO",IF(Q93&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -24891,7 +25072,7 @@
         <v>1</v>
       </c>
       <c r="J94" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K94" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -24906,7 +25087,7 @@
       <c r="O94" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P94" s="10" t="s">
         <v>72</v>
@@ -24914,7 +25095,7 @@
       <c r="Q94" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R94" s="10" t="str">
         <f t="shared" ref="R94:R131" ca="1" si="3">IF(Q94&lt;0,"ATRASADO",IF(Q94&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -24962,7 +25143,7 @@
         <v>1</v>
       </c>
       <c r="J95" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K95" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -24977,7 +25158,7 @@
       <c r="O95" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>72</v>
@@ -24985,7 +25166,7 @@
       <c r="Q95" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R95" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25033,7 +25214,7 @@
         <v>1</v>
       </c>
       <c r="J96" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K96" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25048,7 +25229,7 @@
       <c r="O96" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P96" s="10" t="s">
         <v>72</v>
@@ -25056,7 +25237,7 @@
       <c r="Q96" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R96" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25104,7 +25285,7 @@
         <v>1</v>
       </c>
       <c r="J97" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K97" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25119,7 +25300,7 @@
       <c r="O97" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>72</v>
@@ -25127,7 +25308,7 @@
       <c r="Q97" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R97" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25175,7 +25356,7 @@
         <v>1</v>
       </c>
       <c r="J98" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K98" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25190,7 +25371,7 @@
       <c r="O98" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P98" s="10" t="s">
         <v>72</v>
@@ -25198,7 +25379,7 @@
       <c r="Q98" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R98" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25246,7 +25427,7 @@
         <v>1</v>
       </c>
       <c r="J99" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K99" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25261,7 +25442,7 @@
       <c r="O99" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>72</v>
@@ -25269,7 +25450,7 @@
       <c r="Q99" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R99" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25317,7 +25498,7 @@
         <v>1</v>
       </c>
       <c r="J100" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K100" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25332,7 +25513,7 @@
       <c r="O100" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P100" s="10" t="s">
         <v>72</v>
@@ -25340,7 +25521,7 @@
       <c r="Q100" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R100" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25388,7 +25569,7 @@
         <v>1</v>
       </c>
       <c r="J101" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K101" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25403,7 +25584,7 @@
       <c r="O101" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>72</v>
@@ -25411,7 +25592,7 @@
       <c r="Q101" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R101" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25459,7 +25640,7 @@
         <v>1</v>
       </c>
       <c r="J102" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K102" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25474,7 +25655,7 @@
       <c r="O102" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P102" s="10" t="s">
         <v>72</v>
@@ -25482,7 +25663,7 @@
       <c r="Q102" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R102" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25530,7 +25711,7 @@
         <v>1</v>
       </c>
       <c r="J103" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K103" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25545,7 +25726,7 @@
       <c r="O103" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>72</v>
@@ -25553,7 +25734,7 @@
       <c r="Q103" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R103" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25601,7 +25782,7 @@
         <v>1</v>
       </c>
       <c r="J104" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K104" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25616,7 +25797,7 @@
       <c r="O104" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P104" s="10" t="s">
         <v>72</v>
@@ -25624,7 +25805,7 @@
       <c r="Q104" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R104" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25672,7 +25853,7 @@
         <v>1</v>
       </c>
       <c r="J105" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K105" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25687,7 +25868,7 @@
       <c r="O105" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>72</v>
@@ -25695,7 +25876,7 @@
       <c r="Q105" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R105" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25743,7 +25924,7 @@
         <v>1</v>
       </c>
       <c r="J106" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K106" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25758,7 +25939,7 @@
       <c r="O106" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P106" s="10" t="s">
         <v>72</v>
@@ -25766,7 +25947,7 @@
       <c r="Q106" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R106" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25814,7 +25995,7 @@
         <v>1</v>
       </c>
       <c r="J107" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K107" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25829,7 +26010,7 @@
       <c r="O107" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>72</v>
@@ -25837,7 +26018,7 @@
       <c r="Q107" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R107" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25885,7 +26066,7 @@
         <v>1</v>
       </c>
       <c r="J108" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K108" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25900,7 +26081,7 @@
       <c r="O108" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P108" s="10" t="s">
         <v>72</v>
@@ -25908,7 +26089,7 @@
       <c r="Q108" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R108" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25956,7 +26137,7 @@
         <v>1</v>
       </c>
       <c r="J109" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K109" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -25971,7 +26152,7 @@
       <c r="O109" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>72</v>
@@ -25979,7 +26160,7 @@
       <c r="Q109" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R109" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26027,7 +26208,7 @@
         <v>1</v>
       </c>
       <c r="J110" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K110" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26042,7 +26223,7 @@
       <c r="O110" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P110" s="10" t="s">
         <v>72</v>
@@ -26050,7 +26231,7 @@
       <c r="Q110" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R110" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26098,7 +26279,7 @@
         <v>1</v>
       </c>
       <c r="J111" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K111" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26113,7 +26294,7 @@
       <c r="O111" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>72</v>
@@ -26121,7 +26302,7 @@
       <c r="Q111" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R111" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26169,7 +26350,7 @@
         <v>1</v>
       </c>
       <c r="J112" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K112" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26184,7 +26365,7 @@
       <c r="O112" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P112" s="10" t="s">
         <v>72</v>
@@ -26192,7 +26373,7 @@
       <c r="Q112" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R112" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26240,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="J113" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K113" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26255,7 +26436,7 @@
       <c r="O113" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>72</v>
@@ -26263,7 +26444,7 @@
       <c r="Q113" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R113" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26311,7 +26492,7 @@
         <v>1</v>
       </c>
       <c r="J114" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K114" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26326,7 +26507,7 @@
       <c r="O114" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P114" s="10" t="s">
         <v>72</v>
@@ -26334,7 +26515,7 @@
       <c r="Q114" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R114" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26382,7 +26563,7 @@
         <v>1</v>
       </c>
       <c r="J115" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K115" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26397,7 +26578,7 @@
       <c r="O115" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>72</v>
@@ -26405,7 +26586,7 @@
       <c r="Q115" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R115" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26453,7 +26634,7 @@
         <v>1</v>
       </c>
       <c r="J116" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K116" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26468,7 +26649,7 @@
       <c r="O116" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P116" s="10" t="s">
         <v>72</v>
@@ -26476,7 +26657,7 @@
       <c r="Q116" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R116" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26524,7 +26705,7 @@
         <v>1</v>
       </c>
       <c r="J117" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K117" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26539,7 +26720,7 @@
       <c r="O117" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>72</v>
@@ -26547,7 +26728,7 @@
       <c r="Q117" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R117" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26595,7 +26776,7 @@
         <v>1</v>
       </c>
       <c r="J118" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K118" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26610,7 +26791,7 @@
       <c r="O118" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P118" s="10" t="s">
         <v>72</v>
@@ -26618,7 +26799,7 @@
       <c r="Q118" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R118" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26666,7 +26847,7 @@
         <v>1</v>
       </c>
       <c r="J119" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K119" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26681,7 +26862,7 @@
       <c r="O119" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>72</v>
@@ -26689,7 +26870,7 @@
       <c r="Q119" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R119" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26737,7 +26918,7 @@
         <v>1</v>
       </c>
       <c r="J120" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K120" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26752,7 +26933,7 @@
       <c r="O120" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P120" s="10" t="s">
         <v>72</v>
@@ -26760,7 +26941,7 @@
       <c r="Q120" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R120" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26808,7 +26989,7 @@
         <v>1</v>
       </c>
       <c r="J121" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K121" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26823,7 +27004,7 @@
       <c r="O121" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>72</v>
@@ -26831,7 +27012,7 @@
       <c r="Q121" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R121" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26879,7 +27060,7 @@
         <v>1</v>
       </c>
       <c r="J122" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K122" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26894,7 +27075,7 @@
       <c r="O122" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P122" s="10" t="s">
         <v>72</v>
@@ -26902,7 +27083,7 @@
       <c r="Q122" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R122" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26950,7 +27131,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K123" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -26965,7 +27146,7 @@
       <c r="O123" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>72</v>
@@ -26973,7 +27154,7 @@
       <c r="Q123" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R123" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27021,7 +27202,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K124" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -27036,7 +27217,7 @@
       <c r="O124" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P124" s="10" t="s">
         <v>72</v>
@@ -27044,7 +27225,7 @@
       <c r="Q124" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R124" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27092,7 +27273,7 @@
         <v>1</v>
       </c>
       <c r="J125" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K125" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -27107,7 +27288,7 @@
       <c r="O125" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>72</v>
@@ -27115,7 +27296,7 @@
       <c r="Q125" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R125" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27163,7 +27344,7 @@
         <v>1</v>
       </c>
       <c r="J126" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K126" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -27178,7 +27359,7 @@
       <c r="O126" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P126" s="10" t="s">
         <v>72</v>
@@ -27186,7 +27367,7 @@
       <c r="Q126" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R126" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27234,7 +27415,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K127" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -27249,7 +27430,7 @@
       <c r="O127" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>72</v>
@@ -27257,7 +27438,7 @@
       <c r="Q127" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R127" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27305,7 +27486,7 @@
         <v>1</v>
       </c>
       <c r="J128" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K128" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -27320,7 +27501,7 @@
       <c r="O128" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P128" s="10" t="s">
         <v>72</v>
@@ -27328,7 +27509,7 @@
       <c r="Q128" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R128" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27376,7 +27557,7 @@
         <v>1</v>
       </c>
       <c r="J129" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K129" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -27391,7 +27572,7 @@
       <c r="O129" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>72</v>
@@ -27399,7 +27580,7 @@
       <c r="Q129" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R129" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27447,7 +27628,7 @@
         <v>1</v>
       </c>
       <c r="J130" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K130" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -27462,7 +27643,7 @@
       <c r="O130" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P130" s="10" t="s">
         <v>72</v>
@@ -27470,7 +27651,7 @@
       <c r="Q130" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R130" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27518,7 +27699,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="11">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="K131" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
@@ -27533,7 +27714,7 @@
       <c r="O131" s="11">
         <f>Tabela3[[#This Row],[Prazo
 Fundido]]-10</f>
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>72</v>
@@ -27541,7 +27722,7 @@
       <c r="Q131" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="R131" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27560,7 +27741,7 @@
       </c>
       <c r="V131" s="10"/>
     </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="10">
         <v>2335</v>
       </c>
@@ -27612,7 +27793,7 @@
       <c r="Q132" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R132" s="10" t="str">
         <f ca="1">IF(Q132&lt;0,"ATRASADO",IF(Q132&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27633,7 +27814,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="10">
         <v>2335</v>
       </c>
@@ -27685,7 +27866,7 @@
       <c r="Q133" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R133" s="10" t="str">
         <f t="shared" ref="R133:R143" ca="1" si="4">IF(Q133&lt;0,"ATRASADO",IF(Q133&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27706,7 +27887,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="10">
         <v>2335</v>
       </c>
@@ -27758,7 +27939,7 @@
       <c r="Q134" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R134" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -27779,7 +27960,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="10">
         <v>2335</v>
       </c>
@@ -27831,7 +28012,7 @@
       <c r="Q135" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R135" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -27852,7 +28033,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="10">
         <v>2335</v>
       </c>
@@ -27904,7 +28085,7 @@
       <c r="Q136" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R136" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -27925,7 +28106,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="10">
         <v>2335</v>
       </c>
@@ -27973,7 +28154,7 @@
       <c r="Q137" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R137" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -27992,7 +28173,7 @@
       </c>
       <c r="V137" s="10"/>
     </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="10">
         <v>2335</v>
       </c>
@@ -28040,7 +28221,7 @@
       <c r="Q138" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R138" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28059,7 +28240,7 @@
       </c>
       <c r="V138" s="10"/>
     </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="10">
         <v>2335</v>
       </c>
@@ -28107,7 +28288,7 @@
       <c r="Q139" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R139" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28126,7 +28307,7 @@
       </c>
       <c r="V139" s="10"/>
     </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="10">
         <v>2335</v>
       </c>
@@ -28174,7 +28355,7 @@
       <c r="Q140" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R140" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28193,7 +28374,7 @@
       </c>
       <c r="V140" s="10"/>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="10">
         <v>2335</v>
       </c>
@@ -28241,7 +28422,7 @@
       <c r="Q141" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R141" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28260,7 +28441,7 @@
       </c>
       <c r="V141" s="10"/>
     </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="10">
         <v>2335</v>
       </c>
@@ -28308,7 +28489,7 @@
       <c r="Q142" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R142" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28327,7 +28508,7 @@
       </c>
       <c r="V142" s="10"/>
     </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="10">
         <v>2335</v>
       </c>
@@ -28375,7 +28556,7 @@
       <c r="Q143" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R143" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28446,7 +28627,7 @@
       <c r="Q144" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R144" s="10" t="str">
         <f ca="1">IF(Q144&lt;0,"ATRASADO",IF(Q144&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28519,7 +28700,7 @@
       <c r="Q145" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R145" s="10" t="str">
         <f t="shared" ref="R145:R151" ca="1" si="5">IF(Q145&lt;0,"ATRASADO",IF(Q145&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28592,7 +28773,7 @@
       <c r="Q146" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R146" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28665,7 +28846,7 @@
       <c r="Q147" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R147" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28738,7 +28919,7 @@
       <c r="Q148" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R148" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28811,7 +28992,7 @@
       <c r="Q149" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R149" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28884,7 +29065,7 @@
       <c r="Q150" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R150" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28957,7 +29138,7 @@
       <c r="Q151" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R151" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28978,7 +29159,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="10">
         <v>2335</v>
       </c>
@@ -29024,7 +29205,7 @@
       <c r="Q152" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R152" s="10" t="str">
         <f t="shared" ref="R152:R156" ca="1" si="6">IF(Q152&lt;0,"ATRASADO",IF(Q152&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -29043,7 +29224,7 @@
       </c>
       <c r="V152" s="10"/>
     </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="10">
         <v>2335</v>
       </c>
@@ -29089,7 +29270,7 @@
       <c r="Q153" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R153" s="10" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -29108,7 +29289,7 @@
       </c>
       <c r="V153" s="10"/>
     </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="10">
         <v>2335</v>
       </c>
@@ -29154,7 +29335,7 @@
       <c r="Q154" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R154" s="10" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -29173,7 +29354,7 @@
       </c>
       <c r="V154" s="10"/>
     </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="10">
         <v>2335</v>
       </c>
@@ -29219,7 +29400,7 @@
       <c r="Q155" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R155" s="10" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -29238,7 +29419,7 @@
       </c>
       <c r="V155" s="10"/>
     </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="10">
         <v>2335</v>
       </c>
@@ -29284,7 +29465,7 @@
       <c r="Q156" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R156" s="10" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -29302,6 +29483,461 @@
         <v>61</v>
       </c>
       <c r="V156" s="10"/>
+    </row>
+    <row r="157" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A157" s="10">
+        <v>2352</v>
+      </c>
+      <c r="B157" s="10">
+        <v>1</v>
+      </c>
+      <c r="C157" s="10">
+        <v>27635</v>
+      </c>
+      <c r="D157" s="10">
+        <v>1</v>
+      </c>
+      <c r="E157" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F157" s="10"/>
+      <c r="G157" s="10"/>
+      <c r="H157" s="97" t="s">
+        <v>412</v>
+      </c>
+      <c r="I157" s="10">
+        <v>1</v>
+      </c>
+      <c r="J157" s="11">
+        <v>46241</v>
+      </c>
+      <c r="K157" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>32</v>
+      </c>
+      <c r="L157" s="10"/>
+      <c r="M157" s="11">
+        <v>46241</v>
+      </c>
+      <c r="N157" s="18"/>
+      <c r="O157" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P157" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q157" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>32</v>
+      </c>
+      <c r="R157" s="92" t="str">
+        <f t="shared" ref="R157:R163" ca="1" si="7">IF(Q157&lt;0,"ATRASADO",IF(Q157&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S157" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>32</v>
+      </c>
+      <c r="T157" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="U157" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V157" s="92"/>
+    </row>
+    <row r="158" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A158" s="10">
+        <v>2352</v>
+      </c>
+      <c r="B158" s="10">
+        <v>2</v>
+      </c>
+      <c r="C158" s="10">
+        <v>27635</v>
+      </c>
+      <c r="D158" s="10">
+        <v>2</v>
+      </c>
+      <c r="E158" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F158" s="10"/>
+      <c r="G158" s="10"/>
+      <c r="H158" s="97" t="s">
+        <v>412</v>
+      </c>
+      <c r="I158" s="10">
+        <v>1</v>
+      </c>
+      <c r="J158" s="11">
+        <v>46241</v>
+      </c>
+      <c r="K158" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>32</v>
+      </c>
+      <c r="L158" s="10"/>
+      <c r="M158" s="11">
+        <v>46241</v>
+      </c>
+      <c r="N158" s="18"/>
+      <c r="O158" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P158" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q158" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>32</v>
+      </c>
+      <c r="R158" s="92" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S158" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>32</v>
+      </c>
+      <c r="T158" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="U158" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V158" s="92"/>
+    </row>
+    <row r="159" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A159" s="10">
+        <v>2352</v>
+      </c>
+      <c r="B159" s="10">
+        <v>3</v>
+      </c>
+      <c r="C159" s="10">
+        <v>27635</v>
+      </c>
+      <c r="D159" s="10">
+        <v>3</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F159" s="10"/>
+      <c r="G159" s="10"/>
+      <c r="H159" s="97" t="s">
+        <v>412</v>
+      </c>
+      <c r="I159" s="10">
+        <v>1</v>
+      </c>
+      <c r="J159" s="11">
+        <v>46241</v>
+      </c>
+      <c r="K159" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>32</v>
+      </c>
+      <c r="L159" s="10"/>
+      <c r="M159" s="11">
+        <v>46241</v>
+      </c>
+      <c r="N159" s="18"/>
+      <c r="O159" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P159" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q159" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>32</v>
+      </c>
+      <c r="R159" s="92" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S159" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>32</v>
+      </c>
+      <c r="T159" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="U159" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V159" s="92"/>
+    </row>
+    <row r="160" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A160" s="10">
+        <v>2352</v>
+      </c>
+      <c r="B160" s="10">
+        <v>4</v>
+      </c>
+      <c r="C160" s="10">
+        <v>27635</v>
+      </c>
+      <c r="D160" s="10">
+        <v>4</v>
+      </c>
+      <c r="E160" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F160" s="10"/>
+      <c r="G160" s="10"/>
+      <c r="H160" s="97" t="s">
+        <v>412</v>
+      </c>
+      <c r="I160" s="10">
+        <v>1</v>
+      </c>
+      <c r="J160" s="11">
+        <v>46241</v>
+      </c>
+      <c r="K160" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>32</v>
+      </c>
+      <c r="L160" s="10"/>
+      <c r="M160" s="11">
+        <v>46241</v>
+      </c>
+      <c r="N160" s="18"/>
+      <c r="O160" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P160" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q160" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>32</v>
+      </c>
+      <c r="R160" s="92" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S160" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>32</v>
+      </c>
+      <c r="T160" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="U160" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V160" s="92"/>
+    </row>
+    <row r="161" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A161" s="10">
+        <v>2352</v>
+      </c>
+      <c r="B161" s="10">
+        <v>5</v>
+      </c>
+      <c r="C161" s="10">
+        <v>27635</v>
+      </c>
+      <c r="D161" s="10">
+        <v>5</v>
+      </c>
+      <c r="E161" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F161" s="10"/>
+      <c r="G161" s="10"/>
+      <c r="H161" s="97" t="s">
+        <v>412</v>
+      </c>
+      <c r="I161" s="10">
+        <v>1</v>
+      </c>
+      <c r="J161" s="11">
+        <v>46241</v>
+      </c>
+      <c r="K161" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>32</v>
+      </c>
+      <c r="L161" s="10"/>
+      <c r="M161" s="11">
+        <v>46241</v>
+      </c>
+      <c r="N161" s="18"/>
+      <c r="O161" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P161" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q161" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>32</v>
+      </c>
+      <c r="R161" s="92" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S161" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>32</v>
+      </c>
+      <c r="T161" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="U161" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V161" s="92"/>
+    </row>
+    <row r="162" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A162" s="10">
+        <v>2352</v>
+      </c>
+      <c r="B162" s="10">
+        <v>6</v>
+      </c>
+      <c r="C162" s="10">
+        <v>27635</v>
+      </c>
+      <c r="D162" s="10">
+        <v>6</v>
+      </c>
+      <c r="E162" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F162" s="10"/>
+      <c r="G162" s="10"/>
+      <c r="H162" s="97" t="s">
+        <v>412</v>
+      </c>
+      <c r="I162" s="10">
+        <v>1</v>
+      </c>
+      <c r="J162" s="11">
+        <v>46241</v>
+      </c>
+      <c r="K162" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>32</v>
+      </c>
+      <c r="L162" s="10"/>
+      <c r="M162" s="11">
+        <v>46241</v>
+      </c>
+      <c r="N162" s="18"/>
+      <c r="O162" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P162" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q162" s="12">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>32</v>
+      </c>
+      <c r="R162" s="92" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S162" s="92">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>32</v>
+      </c>
+      <c r="T162" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="U162" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V162" s="92"/>
+    </row>
+    <row r="163" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A163" s="10">
+        <v>2352</v>
+      </c>
+      <c r="B163" s="93">
+        <v>7</v>
+      </c>
+      <c r="C163" s="10">
+        <v>27635</v>
+      </c>
+      <c r="D163" s="93">
+        <v>7</v>
+      </c>
+      <c r="E163" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F163" s="93"/>
+      <c r="G163" s="93"/>
+      <c r="H163" s="97" t="s">
+        <v>411</v>
+      </c>
+      <c r="I163" s="10">
+        <v>1</v>
+      </c>
+      <c r="J163" s="11">
+        <v>46241</v>
+      </c>
+      <c r="K163" s="94">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Fundido]])</f>
+        <v>32</v>
+      </c>
+      <c r="L163" s="93"/>
+      <c r="M163" s="11">
+        <v>46241</v>
+      </c>
+      <c r="N163" s="95"/>
+      <c r="O163" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P163" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q163" s="96">
+        <f ca="1">Tabela3[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>32</v>
+      </c>
+      <c r="R163" s="94" t="str">
+        <f t="shared" ca="1" si="7"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="S163" s="94">
+        <f>WEEKNUM(Tabela3[[#This Row],[Prazo
+Entrega]])</f>
+        <v>32</v>
+      </c>
+      <c r="T163" s="94" t="s">
+        <v>90</v>
+      </c>
+      <c r="U163" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="V163" s="94"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -29451,7 +30087,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="O2" s="13" t="str">
         <f t="shared" ref="O2:O16" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -29528,7 +30164,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="O3" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29605,7 +30241,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O4" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29682,7 +30318,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O5" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29759,7 +30395,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O6" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29836,7 +30472,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O7" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29913,7 +30549,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O8" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29990,7 +30626,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O9" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30067,7 +30703,7 @@
       <c r="N10" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O10" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30144,7 +30780,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O11" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30221,7 +30857,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O12" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30298,7 +30934,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="O13" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30375,7 +31011,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O14" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30452,7 +31088,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O15" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30529,7 +31165,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O16" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30606,7 +31242,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O17" s="13" t="str">
         <f ca="1">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30685,7 +31321,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O18" s="13" t="str">
         <f t="shared" ref="O18:O25" ca="1" si="2">IF(N18&lt;0,"ATRASADO",IF(N18&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30764,7 +31400,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -30843,7 +31479,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -30922,7 +31558,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31001,7 +31637,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31080,7 +31716,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31159,7 +31795,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31238,7 +31874,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31317,7 +31953,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O26" s="13" t="str">
         <f ca="1">IF(N26&lt;0,"ATRASADO",IF(N26&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31394,7 +32030,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O27" s="13" t="str">
         <f t="shared" ref="O27:O28" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31471,7 +32107,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O28" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -31548,7 +32184,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O29" s="13" t="str">
         <f t="shared" ref="O29:O31" ca="1" si="5">IF(N29&lt;0,"ATRASADO",IF(N29&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31627,7 +32263,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O30" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -31706,7 +32342,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O31" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -31785,7 +32421,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O32" s="13" t="str">
         <f ca="1">IF(N32&lt;0,"ATRASADO",IF(N32&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31864,7 +32500,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O33" s="13" t="str">
         <f t="shared" ref="O33:O35" ca="1" si="7">IF(N33&lt;0,"ATRASADO",IF(N33&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31943,7 +32579,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O34" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -32022,7 +32658,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O35" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -32101,7 +32737,7 @@
       <c r="N36" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O36" s="13" t="str">
         <f ca="1">IF(N36&lt;0,"ATRASADO",IF(N36&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32178,7 +32814,7 @@
       <c r="N37" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O37" s="13" t="str">
         <f t="shared" ref="O37:O39" ca="1" si="9">IF(N37&lt;0,"ATRASADO",IF(N37&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32255,7 +32891,7 @@
       <c r="N38" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O38" s="13" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -32332,7 +32968,7 @@
       <c r="N39" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O39" s="13" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33053,7 +33689,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF21EC6F-EA0F-4DA9-80E1-5F0E0C8C0396}">
-  <dimension ref="A1:T89"/>
+  <dimension ref="A1:T123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="9.140625" style="1"/>
@@ -33160,7 +33796,7 @@
         <v>141</v>
       </c>
       <c r="J2" s="7">
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="L2" s="7">
         <v>46254</v>
@@ -33168,7 +33804,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O2" t="str">
         <f t="shared" ref="O2:O9" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33186,6 +33822,9 @@
       <c r="S2" t="s">
         <v>61</v>
       </c>
+      <c r="T2" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
@@ -33216,7 +33855,7 @@
         <v>141</v>
       </c>
       <c r="J3" s="7">
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="L3" s="7">
         <v>46254</v>
@@ -33224,7 +33863,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33242,6 +33881,9 @@
       <c r="S3" t="s">
         <v>61</v>
       </c>
+      <c r="T3" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
@@ -33272,7 +33914,7 @@
         <v>141</v>
       </c>
       <c r="J4" s="7">
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="L4" s="7">
         <v>46254</v>
@@ -33280,7 +33922,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33298,6 +33940,9 @@
       <c r="S4" t="s">
         <v>61</v>
       </c>
+      <c r="T4" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
@@ -33328,7 +33973,7 @@
         <v>141</v>
       </c>
       <c r="J5" s="7">
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="L5" s="7">
         <v>46254</v>
@@ -33336,7 +33981,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33354,6 +33999,9 @@
       <c r="S5" t="s">
         <v>61</v>
       </c>
+      <c r="T5" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
@@ -33384,7 +34032,7 @@
         <v>141</v>
       </c>
       <c r="J6" s="7">
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="L6" s="7">
         <v>46254</v>
@@ -33392,7 +34040,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O6" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33410,6 +34058,9 @@
       <c r="S6" t="s">
         <v>61</v>
       </c>
+      <c r="T6" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
@@ -33440,7 +34091,7 @@
         <v>141</v>
       </c>
       <c r="J7" s="7">
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="L7" s="7">
         <v>46254</v>
@@ -33448,7 +34099,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33466,6 +34117,9 @@
       <c r="S7" t="s">
         <v>61</v>
       </c>
+      <c r="T7" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
@@ -33496,7 +34150,7 @@
         <v>141</v>
       </c>
       <c r="J8" s="7">
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="L8" s="7">
         <v>46254</v>
@@ -33504,7 +34158,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33522,6 +34176,9 @@
       <c r="S8" t="s">
         <v>61</v>
       </c>
+      <c r="T8" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
@@ -33552,7 +34209,7 @@
         <v>141</v>
       </c>
       <c r="J9" s="7">
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="L9" s="7">
         <v>46254</v>
@@ -33560,7 +34217,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33578,6 +34235,9 @@
       <c r="S9" t="s">
         <v>61</v>
       </c>
+      <c r="T9" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="10" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
@@ -33622,7 +34282,7 @@
       <c r="N10" s="12">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>-28</v>
+        <v>-31</v>
       </c>
       <c r="O10" s="33" t="s">
         <v>102</v>
@@ -33680,7 +34340,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O11" s="1" t="str">
         <f ca="1">IF(N11&lt;0,"ATRASADO",IF(N11&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33689,14 +34349,17 @@
       <c r="P11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Q11" s="11">
-        <v>46203</v>
+      <c r="Q11" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S11" t="s">
-        <v>120</v>
+        <v>394</v>
+      </c>
+      <c r="T11" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -33739,7 +34402,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O12" t="str">
         <f ca="1">IF(N12&lt;0,"ATRASADO",IF(N12&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33748,14 +34411,17 @@
       <c r="P12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Q12" s="11">
-        <v>46203</v>
+      <c r="Q12" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S12" t="s">
-        <v>120</v>
+        <v>394</v>
+      </c>
+      <c r="T12" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -33798,7 +34464,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">IF(N13&lt;0,"ATRASADO",IF(N13&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33807,14 +34473,17 @@
       <c r="P13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Q13" s="11">
-        <v>46203</v>
+      <c r="Q13" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S13" t="s">
-        <v>120</v>
+        <v>394</v>
+      </c>
+      <c r="T13" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -33857,7 +34526,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O14" t="str">
         <f ca="1">IF(N14&lt;0,"ATRASADO",IF(N14&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33866,14 +34535,17 @@
       <c r="P14" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Q14" s="11">
-        <v>46203</v>
+      <c r="Q14" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S14" t="s">
-        <v>120</v>
+        <v>392</v>
+      </c>
+      <c r="T14" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -33916,7 +34588,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O15" t="str">
         <f t="shared" ref="O15:O16" ca="1" si="1">IF(N15&lt;0,"ATRASADO",IF(N15&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33925,14 +34597,17 @@
       <c r="P15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Q15" s="11">
-        <v>46203</v>
+      <c r="Q15" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S15" t="s">
-        <v>120</v>
+        <v>392</v>
+      </c>
+      <c r="T15" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -33975,7 +34650,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -33984,14 +34659,17 @@
       <c r="P16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Q16" s="11">
-        <v>46203</v>
+      <c r="Q16" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S16" t="s">
-        <v>120</v>
+        <v>392</v>
+      </c>
+      <c r="T16" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
@@ -34031,7 +34709,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" ref="O17:O18" ca="1" si="2">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34087,7 +34765,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -34146,7 +34824,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O19" t="str">
         <f ca="1">IF(N19&lt;0,"ATRASADO",IF(N19&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34205,7 +34883,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O20" t="str">
         <f ca="1">IF(N20&lt;0,"ATRASADO",IF(N20&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34264,7 +34942,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O21" t="str">
         <f t="shared" ref="O21:O26" ca="1" si="3">IF(N21&lt;0,"ATRASADO",IF(N21&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34323,7 +35001,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O22" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -34382,7 +35060,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -34441,7 +35119,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O24" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -34500,7 +35178,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O25" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -34559,7 +35237,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O26" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -34618,7 +35296,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O27" t="str">
         <f t="shared" ref="O27:O34" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34677,7 +35355,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O28" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -34736,7 +35414,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O29" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -34795,7 +35473,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O30" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -34854,7 +35532,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O31" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -34913,7 +35591,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O32" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -34972,7 +35650,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O33" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -35031,7 +35709,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O34" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -35090,7 +35768,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O35" t="str">
         <f t="shared" ref="O35:O36" ca="1" si="5">IF(N35&lt;0,"ATRASADO",IF(N35&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35149,7 +35827,7 @@
       <c r="N36" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O36" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -35208,7 +35886,7 @@
       <c r="N37" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O37" t="str">
         <f ca="1">IF(N37&lt;0,"ATRASADO",IF(N37&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35267,7 +35945,7 @@
       <c r="N38" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O38" t="str">
         <f t="shared" ref="O38:O52" ca="1" si="6">IF(N38&lt;0,"ATRASADO",IF(N38&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35326,7 +36004,7 @@
       <c r="N39" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O39" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35385,7 +36063,7 @@
       <c r="N40" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35444,7 +36122,7 @@
       <c r="N41" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O41" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35503,7 +36181,7 @@
       <c r="N42" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O42" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35562,7 +36240,7 @@
       <c r="N43" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O43" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35621,7 +36299,7 @@
       <c r="N44" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O44" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35680,7 +36358,7 @@
       <c r="N45" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O45" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35739,7 +36417,7 @@
       <c r="N46" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O46" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35798,7 +36476,7 @@
       <c r="N47" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O47" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35857,7 +36535,7 @@
       <c r="N48" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O48" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35876,7 +36554,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="15">
         <v>2331</v>
       </c>
@@ -35916,7 +36594,7 @@
       <c r="N49" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O49" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35935,7 +36613,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" s="15">
         <v>2331</v>
       </c>
@@ -35975,7 +36653,7 @@
       <c r="N50" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O50" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -35994,7 +36672,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" s="15">
         <v>2331</v>
       </c>
@@ -36034,7 +36712,7 @@
       <c r="N51" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O51" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36053,7 +36731,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A52" s="15">
         <v>2331</v>
       </c>
@@ -36093,7 +36771,7 @@
       <c r="N52" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O52" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36112,7 +36790,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A53" s="15">
         <v>1798</v>
       </c>
@@ -36155,7 +36833,7 @@
       <c r="N53" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="O53" t="s">
         <v>154</v>
@@ -36173,7 +36851,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A54" s="15">
         <v>2333</v>
       </c>
@@ -36213,7 +36891,7 @@
       <c r="N54" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O54" t="str">
         <f ca="1">IF(N54&lt;0,"ATRASADO",IF(N54&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -36232,7 +36910,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A55" s="15">
         <v>2333</v>
       </c>
@@ -36272,7 +36950,7 @@
       <c r="N55" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O55" t="str">
         <f ca="1">IF(N55&lt;0,"ATRASADO",IF(N55&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -36291,7 +36969,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A56" s="15">
         <v>2333</v>
       </c>
@@ -36331,7 +37009,7 @@
       <c r="N56" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O56" t="str">
         <f ca="1">IF(N56&lt;0,"ATRASADO",IF(N56&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -36350,7 +37028,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A57" s="15">
         <v>2333</v>
       </c>
@@ -36390,7 +37068,7 @@
       <c r="N57" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O57" t="str">
         <f t="shared" ref="O57:O59" ca="1" si="7">IF(N57&lt;0,"ATRASADO",IF(N57&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -36409,7 +37087,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A58" s="15">
         <v>2333</v>
       </c>
@@ -36449,7 +37127,7 @@
       <c r="N58" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O58" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -36468,7 +37146,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A59" s="15">
         <v>2333</v>
       </c>
@@ -36508,7 +37186,7 @@
       <c r="N59" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O59" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -36527,7 +37205,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A60" s="15">
         <v>2333</v>
       </c>
@@ -36564,7 +37242,7 @@
       <c r="N60" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O60" t="str">
         <f t="shared" ref="O60:O62" ca="1" si="8">IF(N60&lt;0,"ATRASADO",IF(N60&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -36582,8 +37260,11 @@
       <c r="S60" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T60" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A61" s="15">
         <v>2333</v>
       </c>
@@ -36620,7 +37301,7 @@
       <c r="N61" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O61" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -36638,8 +37319,11 @@
       <c r="S61" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T61" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A62" s="15">
         <v>2333</v>
       </c>
@@ -36676,7 +37360,7 @@
       <c r="N62" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O62" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -36694,8 +37378,11 @@
       <c r="S62" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T62" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A63" s="15">
         <v>2333</v>
       </c>
@@ -36735,7 +37422,7 @@
       <c r="N63" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O63" t="str">
         <f ca="1">IF(N63&lt;0,"ATRASADO",IF(N63&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -36754,7 +37441,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A64" s="15">
         <v>2333</v>
       </c>
@@ -36794,7 +37481,7 @@
       <c r="N64" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O64" t="str">
         <f t="shared" ref="O64:O76" ca="1" si="9">IF(N64&lt;0,"ATRASADO",IF(N64&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -36853,7 +37540,7 @@
       <c r="N65" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O65" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -36912,7 +37599,7 @@
       <c r="N66" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O66" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -36971,7 +37658,7 @@
       <c r="N67" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O67" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37030,7 +37717,7 @@
       <c r="N68" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O68" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37089,7 +37776,7 @@
       <c r="N69" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O69" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37148,7 +37835,7 @@
       <c r="N70" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O70" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37207,7 +37894,7 @@
       <c r="N71" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O71" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37266,7 +37953,7 @@
       <c r="N72" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O72" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37325,7 +38012,7 @@
       <c r="N73" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O73" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37384,7 +38071,7 @@
       <c r="N74" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O74" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37443,7 +38130,7 @@
       <c r="N75" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O75" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37502,7 +38189,7 @@
       <c r="N76" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O76" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37561,7 +38248,7 @@
       <c r="N77" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O77" t="str">
         <f ca="1">IF(N77&lt;0,"ATRASADO",IF(N77&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -37620,7 +38307,7 @@
       <c r="N78" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O78" t="str">
         <f t="shared" ref="O78:O80" ca="1" si="10">IF(N78&lt;0,"ATRASADO",IF(N78&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -37679,7 +38366,7 @@
       <c r="N79" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O79" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -37738,7 +38425,7 @@
       <c r="N80" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O80" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -37757,7 +38444,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A81" s="15">
         <v>2333</v>
       </c>
@@ -37797,7 +38484,7 @@
       <c r="N81" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O81" t="str">
         <f t="shared" ref="O81:O88" ca="1" si="11">IF(N81&lt;0,"ATRASADO",IF(N81&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -37816,7 +38503,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A82" s="15">
         <v>2333</v>
       </c>
@@ -37856,7 +38543,7 @@
       <c r="N82" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O82" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -37875,7 +38562,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A83" s="15">
         <v>2333</v>
       </c>
@@ -37915,7 +38602,7 @@
       <c r="N83" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O83" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -37934,7 +38621,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>2333</v>
       </c>
@@ -37974,7 +38661,7 @@
       <c r="N84" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O84" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -37993,7 +38680,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>2333</v>
       </c>
@@ -38033,7 +38720,7 @@
       <c r="N85" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O85" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38052,7 +38739,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>2333</v>
       </c>
@@ -38092,7 +38779,7 @@
       <c r="N86" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O86" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38111,7 +38798,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>2333</v>
       </c>
@@ -38151,7 +38838,7 @@
       <c r="N87" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O87" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38170,7 +38857,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>2333</v>
       </c>
@@ -38210,7 +38897,7 @@
       <c r="N88" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O88" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38229,7 +38916,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>1945</v>
       </c>
@@ -38272,7 +38959,7 @@
       <c r="N89" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="O89" t="s">
         <v>154</v>
@@ -38289,6 +38976,2032 @@
       <c r="S89" t="s">
         <v>101</v>
       </c>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A90" s="15">
+        <v>2345</v>
+      </c>
+      <c r="B90" s="15">
+        <v>2</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E90" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F90" s="14">
+        <v>1</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I90" s="79" t="s">
+        <v>398</v>
+      </c>
+      <c r="J90" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K90" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L90" s="7">
+        <v>46371</v>
+      </c>
+      <c r="M90" s="69"/>
+      <c r="N90" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>162</v>
+      </c>
+      <c r="O90" s="71" t="str">
+        <f t="shared" ref="O90:O97" ca="1" si="12">IF(N90&lt;0,"ATRASADO",IF(N90&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P90" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q90" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R90" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="S90" t="s">
+        <v>120</v>
+      </c>
+      <c r="T90" s="69"/>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A91" s="15">
+        <v>2345</v>
+      </c>
+      <c r="B91" s="15">
+        <v>3</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E91" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F91" s="14">
+        <v>1</v>
+      </c>
+      <c r="G91" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H91" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I91" s="79" t="s">
+        <v>398</v>
+      </c>
+      <c r="J91" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K91" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L91" s="7">
+        <v>46371</v>
+      </c>
+      <c r="M91" s="69"/>
+      <c r="N91" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>162</v>
+      </c>
+      <c r="O91" s="71" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P91" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q91" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R91" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="S91" t="s">
+        <v>120</v>
+      </c>
+      <c r="T91" s="69"/>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A92" s="15">
+        <v>2345</v>
+      </c>
+      <c r="B92" s="15">
+        <v>4</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E92" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F92" s="14">
+        <v>1</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H92" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I92" s="79" t="s">
+        <v>399</v>
+      </c>
+      <c r="J92" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K92" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L92" s="7">
+        <v>46371</v>
+      </c>
+      <c r="M92" s="69"/>
+      <c r="N92" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>162</v>
+      </c>
+      <c r="O92" s="71" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P92" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q92" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R92" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="S92" t="s">
+        <v>120</v>
+      </c>
+      <c r="T92" s="69"/>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A93" s="15">
+        <v>2345</v>
+      </c>
+      <c r="B93" s="15">
+        <v>5</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E93" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F93" s="14">
+        <v>1</v>
+      </c>
+      <c r="G93" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H93" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I93" s="79" t="s">
+        <v>399</v>
+      </c>
+      <c r="J93" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K93" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L93" s="7">
+        <v>46371</v>
+      </c>
+      <c r="M93" s="69"/>
+      <c r="N93" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>162</v>
+      </c>
+      <c r="O93" s="71" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P93" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q93" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R93" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="S93" t="s">
+        <v>120</v>
+      </c>
+      <c r="T93" s="69"/>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A94" s="15">
+        <v>2345</v>
+      </c>
+      <c r="B94" s="15">
+        <v>6</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E94" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F94" s="14">
+        <v>1</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H94" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I94" s="79" t="s">
+        <v>400</v>
+      </c>
+      <c r="J94" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K94" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L94" s="7">
+        <v>46371</v>
+      </c>
+      <c r="M94" s="69"/>
+      <c r="N94" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>162</v>
+      </c>
+      <c r="O94" s="71" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P94" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q94" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R94" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="S94" t="s">
+        <v>120</v>
+      </c>
+      <c r="T94" s="69"/>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A95" s="15">
+        <v>2345</v>
+      </c>
+      <c r="B95" s="15">
+        <v>7</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E95" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F95" s="14">
+        <v>1</v>
+      </c>
+      <c r="G95" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H95" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I95" s="79" t="s">
+        <v>400</v>
+      </c>
+      <c r="J95" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K95" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L95" s="7">
+        <v>46371</v>
+      </c>
+      <c r="M95" s="69"/>
+      <c r="N95" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>162</v>
+      </c>
+      <c r="O95" s="71" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P95" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q95" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R95" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="S95" t="s">
+        <v>120</v>
+      </c>
+      <c r="T95" s="69"/>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A96" s="15">
+        <v>2345</v>
+      </c>
+      <c r="B96" s="15">
+        <v>8</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E96" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F96" s="14">
+        <v>36</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I96" s="79" t="s">
+        <v>401</v>
+      </c>
+      <c r="J96" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K96" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L96" s="7">
+        <v>46371</v>
+      </c>
+      <c r="M96" s="69"/>
+      <c r="N96" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>162</v>
+      </c>
+      <c r="O96" s="71" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P96" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q96" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R96" s="72" t="s">
+        <v>100</v>
+      </c>
+      <c r="S96" t="s">
+        <v>120</v>
+      </c>
+      <c r="T96" s="69"/>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A97" s="15">
+        <v>2345</v>
+      </c>
+      <c r="B97" s="73">
+        <v>9</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E97" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F97" s="74">
+        <v>36</v>
+      </c>
+      <c r="G97" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I97" s="79" t="s">
+        <v>402</v>
+      </c>
+      <c r="J97" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K97" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L97" s="7">
+        <v>46371</v>
+      </c>
+      <c r="M97" s="75"/>
+      <c r="N97" s="76">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>162</v>
+      </c>
+      <c r="O97" s="77" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P97" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q97" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R97" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S97" t="s">
+        <v>120</v>
+      </c>
+      <c r="T97" s="75"/>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A98" s="15">
+        <v>2348</v>
+      </c>
+      <c r="B98" s="15">
+        <v>9</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="F98" s="81">
+        <v>2</v>
+      </c>
+      <c r="G98" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H98" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I98" s="79" t="s">
+        <v>404</v>
+      </c>
+      <c r="J98" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K98" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L98" s="7">
+        <v>46325</v>
+      </c>
+      <c r="M98" s="69"/>
+      <c r="N98" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>116</v>
+      </c>
+      <c r="O98" s="71" t="str">
+        <f t="shared" ref="O98:O103" ca="1" si="13">IF(N98&lt;0,"ATRASADO",IF(N98&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P98" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q98" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R98" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S98" t="s">
+        <v>120</v>
+      </c>
+      <c r="T98" s="69"/>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A99" s="15">
+        <v>2348</v>
+      </c>
+      <c r="B99" s="15">
+        <v>10</v>
+      </c>
+      <c r="C99" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="F99" s="81">
+        <v>2</v>
+      </c>
+      <c r="G99" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H99" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I99" s="79" t="s">
+        <v>404</v>
+      </c>
+      <c r="J99" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K99" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L99" s="7">
+        <v>46325</v>
+      </c>
+      <c r="M99" s="69"/>
+      <c r="N99" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>116</v>
+      </c>
+      <c r="O99" s="71" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P99" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q99" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R99" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S99" t="s">
+        <v>120</v>
+      </c>
+      <c r="T99" s="69"/>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A100" s="15">
+        <v>2348</v>
+      </c>
+      <c r="B100" s="15">
+        <v>11</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="F100" s="81">
+        <v>2</v>
+      </c>
+      <c r="G100" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H100" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I100" s="79" t="s">
+        <v>404</v>
+      </c>
+      <c r="J100" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K100" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L100" s="7">
+        <v>46325</v>
+      </c>
+      <c r="M100" s="69"/>
+      <c r="N100" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>116</v>
+      </c>
+      <c r="O100" s="71" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P100" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q100" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R100" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S100" t="s">
+        <v>120</v>
+      </c>
+      <c r="T100" s="69"/>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A101" s="15">
+        <v>2348</v>
+      </c>
+      <c r="B101" s="15">
+        <v>12</v>
+      </c>
+      <c r="C101" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="F101" s="81">
+        <v>1</v>
+      </c>
+      <c r="G101" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H101" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I101" s="79" t="s">
+        <v>405</v>
+      </c>
+      <c r="J101" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K101" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L101" s="7">
+        <v>46325</v>
+      </c>
+      <c r="M101" s="69"/>
+      <c r="N101" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>116</v>
+      </c>
+      <c r="O101" s="71" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P101" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q101" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R101" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S101" t="s">
+        <v>120</v>
+      </c>
+      <c r="T101" s="69"/>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A102" s="15">
+        <v>2348</v>
+      </c>
+      <c r="B102" s="15">
+        <v>13</v>
+      </c>
+      <c r="C102" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="F102" s="81">
+        <v>1</v>
+      </c>
+      <c r="G102" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H102" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I102" s="79" t="s">
+        <v>405</v>
+      </c>
+      <c r="J102" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K102" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L102" s="7">
+        <v>46325</v>
+      </c>
+      <c r="M102" s="69"/>
+      <c r="N102" s="70">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>116</v>
+      </c>
+      <c r="O102" s="71" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P102" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q102" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R102" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S102" t="s">
+        <v>120</v>
+      </c>
+      <c r="T102" s="69"/>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A103" s="15">
+        <v>2348</v>
+      </c>
+      <c r="B103" s="73">
+        <v>14</v>
+      </c>
+      <c r="C103" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E103" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="F103" s="81">
+        <v>8</v>
+      </c>
+      <c r="G103" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H103" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I103" s="79" t="s">
+        <v>403</v>
+      </c>
+      <c r="J103" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K103" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L103" s="7">
+        <v>46325</v>
+      </c>
+      <c r="M103" s="75"/>
+      <c r="N103" s="76">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>116</v>
+      </c>
+      <c r="O103" s="77" t="str">
+        <f t="shared" ca="1" si="13"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P103" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q103" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R103" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S103" t="s">
+        <v>120</v>
+      </c>
+      <c r="T103" s="75"/>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A104" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B104" s="83">
+        <v>6</v>
+      </c>
+      <c r="C104" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D104" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E104" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F104" s="86">
+        <v>1</v>
+      </c>
+      <c r="G104" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H104" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I104" s="87" t="s">
+        <v>409</v>
+      </c>
+      <c r="J104" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K104" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L104" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M104" s="89"/>
+      <c r="N104" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O104" s="91" t="str">
+        <f t="shared" ref="O104:O123" ca="1" si="14">IF(N104&lt;0,"ATRASADO",IF(N104&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P104" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q104" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R104" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S104" t="s">
+        <v>120</v>
+      </c>
+      <c r="T104" s="69"/>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A105" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B105" s="83">
+        <v>7</v>
+      </c>
+      <c r="C105" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D105" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E105" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F105" s="86">
+        <v>1</v>
+      </c>
+      <c r="G105" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H105" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I105" s="87" t="s">
+        <v>409</v>
+      </c>
+      <c r="J105" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K105" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L105" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M105" s="89"/>
+      <c r="N105" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O105" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P105" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q105" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R105" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S105" t="s">
+        <v>120</v>
+      </c>
+      <c r="T105" s="69"/>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A106" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B106" s="83">
+        <v>8</v>
+      </c>
+      <c r="C106" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D106" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E106" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F106" s="86">
+        <v>1</v>
+      </c>
+      <c r="G106" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H106" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I106" s="87" t="s">
+        <v>409</v>
+      </c>
+      <c r="J106" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K106" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L106" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M106" s="89"/>
+      <c r="N106" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O106" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P106" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q106" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R106" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S106" t="s">
+        <v>120</v>
+      </c>
+      <c r="T106" s="69"/>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A107" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B107" s="83">
+        <v>9</v>
+      </c>
+      <c r="C107" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D107" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E107" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F107" s="86">
+        <v>1</v>
+      </c>
+      <c r="G107" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H107" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107" s="87" t="s">
+        <v>409</v>
+      </c>
+      <c r="J107" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K107" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L107" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M107" s="89"/>
+      <c r="N107" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O107" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P107" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q107" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R107" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S107" t="s">
+        <v>120</v>
+      </c>
+      <c r="T107" s="69"/>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A108" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B108" s="83">
+        <v>10</v>
+      </c>
+      <c r="C108" s="84"/>
+      <c r="D108" s="84"/>
+      <c r="E108" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F108" s="86">
+        <v>1</v>
+      </c>
+      <c r="G108" s="82"/>
+      <c r="H108" s="82"/>
+      <c r="I108" s="87" t="s">
+        <v>410</v>
+      </c>
+      <c r="J108" s="88"/>
+      <c r="K108" s="89"/>
+      <c r="L108" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M108" s="89"/>
+      <c r="N108" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O108" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P108" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q108" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R108" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S108" t="s">
+        <v>61</v>
+      </c>
+      <c r="T108" s="69"/>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A109" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B109" s="83">
+        <v>11</v>
+      </c>
+      <c r="C109" s="84"/>
+      <c r="D109" s="84"/>
+      <c r="E109" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F109" s="86">
+        <v>1</v>
+      </c>
+      <c r="G109" s="82"/>
+      <c r="H109" s="82"/>
+      <c r="I109" s="87" t="s">
+        <v>410</v>
+      </c>
+      <c r="J109" s="88"/>
+      <c r="K109" s="89"/>
+      <c r="L109" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M109" s="89"/>
+      <c r="N109" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O109" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P109" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q109" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R109" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S109" t="s">
+        <v>61</v>
+      </c>
+      <c r="T109" s="69"/>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A110" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B110" s="83">
+        <v>12</v>
+      </c>
+      <c r="C110" s="84"/>
+      <c r="D110" s="84"/>
+      <c r="E110" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F110" s="86">
+        <v>1</v>
+      </c>
+      <c r="G110" s="82"/>
+      <c r="H110" s="82"/>
+      <c r="I110" s="87" t="s">
+        <v>410</v>
+      </c>
+      <c r="J110" s="88"/>
+      <c r="K110" s="89"/>
+      <c r="L110" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M110" s="89"/>
+      <c r="N110" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O110" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P110" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q110" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R110" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S110" t="s">
+        <v>61</v>
+      </c>
+      <c r="T110" s="69"/>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A111" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B111" s="83">
+        <v>13</v>
+      </c>
+      <c r="C111" s="84"/>
+      <c r="D111" s="84"/>
+      <c r="E111" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F111" s="86">
+        <v>1</v>
+      </c>
+      <c r="G111" s="82"/>
+      <c r="H111" s="82"/>
+      <c r="I111" s="87" t="s">
+        <v>410</v>
+      </c>
+      <c r="J111" s="88"/>
+      <c r="K111" s="89"/>
+      <c r="L111" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M111" s="89"/>
+      <c r="N111" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O111" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P111" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q111" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R111" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S111" t="s">
+        <v>61</v>
+      </c>
+      <c r="T111" s="69"/>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A112" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B112" s="83">
+        <v>14</v>
+      </c>
+      <c r="C112" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D112" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E112" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F112" s="86">
+        <v>1</v>
+      </c>
+      <c r="G112" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H112" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I112" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="J112" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K112" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L112" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M112" s="89"/>
+      <c r="N112" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O112" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P112" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q112" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R112" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S112" t="s">
+        <v>120</v>
+      </c>
+      <c r="T112" s="69"/>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A113" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B113" s="83">
+        <v>15</v>
+      </c>
+      <c r="C113" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D113" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E113" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F113" s="86">
+        <v>1</v>
+      </c>
+      <c r="G113" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H113" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I113" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="J113" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K113" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L113" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M113" s="89"/>
+      <c r="N113" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O113" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P113" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q113" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R113" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S113" t="s">
+        <v>120</v>
+      </c>
+      <c r="T113" s="69"/>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A114" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B114" s="83">
+        <v>16</v>
+      </c>
+      <c r="C114" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D114" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E114" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F114" s="86">
+        <v>1</v>
+      </c>
+      <c r="G114" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H114" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I114" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="J114" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K114" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L114" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M114" s="89"/>
+      <c r="N114" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O114" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P114" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q114" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R114" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S114" t="s">
+        <v>120</v>
+      </c>
+      <c r="T114" s="69"/>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A115" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B115" s="83">
+        <v>17</v>
+      </c>
+      <c r="C115" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D115" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E115" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F115" s="86">
+        <v>1</v>
+      </c>
+      <c r="G115" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H115" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I115" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="J115" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K115" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L115" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M115" s="89"/>
+      <c r="N115" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O115" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P115" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q115" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R115" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S115" t="s">
+        <v>120</v>
+      </c>
+      <c r="T115" s="69"/>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A116" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B116" s="83">
+        <v>18</v>
+      </c>
+      <c r="C116" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D116" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E116" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F116" s="86">
+        <v>1</v>
+      </c>
+      <c r="G116" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H116" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I116" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="J116" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K116" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L116" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M116" s="89"/>
+      <c r="N116" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O116" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P116" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q116" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R116" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S116" t="s">
+        <v>120</v>
+      </c>
+      <c r="T116" s="69"/>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A117" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B117" s="83">
+        <v>19</v>
+      </c>
+      <c r="C117" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D117" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E117" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F117" s="86">
+        <v>1</v>
+      </c>
+      <c r="G117" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H117" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I117" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="J117" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K117" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L117" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M117" s="89"/>
+      <c r="N117" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O117" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P117" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q117" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R117" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S117" t="s">
+        <v>120</v>
+      </c>
+      <c r="T117" s="69"/>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A118" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B118" s="83">
+        <v>20</v>
+      </c>
+      <c r="C118" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D118" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E118" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F118" s="86">
+        <v>1</v>
+      </c>
+      <c r="G118" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H118" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I118" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="J118" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K118" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L118" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M118" s="89"/>
+      <c r="N118" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O118" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P118" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q118" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R118" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S118" t="s">
+        <v>120</v>
+      </c>
+      <c r="T118" s="69"/>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A119" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B119" s="83">
+        <v>21</v>
+      </c>
+      <c r="C119" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D119" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E119" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F119" s="86">
+        <v>1</v>
+      </c>
+      <c r="G119" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H119" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I119" s="87" t="s">
+        <v>407</v>
+      </c>
+      <c r="J119" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K119" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L119" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M119" s="89"/>
+      <c r="N119" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O119" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P119" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q119" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R119" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S119" t="s">
+        <v>120</v>
+      </c>
+      <c r="T119" s="69"/>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A120" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B120" s="83">
+        <v>23</v>
+      </c>
+      <c r="C120" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D120" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E120" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F120" s="86">
+        <v>1</v>
+      </c>
+      <c r="G120" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H120" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I120" s="87" t="s">
+        <v>408</v>
+      </c>
+      <c r="J120" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K120" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L120" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M120" s="89"/>
+      <c r="N120" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O120" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P120" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q120" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R120" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S120" t="s">
+        <v>120</v>
+      </c>
+      <c r="T120" s="69"/>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A121" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B121" s="83">
+        <v>24</v>
+      </c>
+      <c r="C121" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D121" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E121" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F121" s="86">
+        <v>1</v>
+      </c>
+      <c r="G121" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H121" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I121" s="87" t="s">
+        <v>408</v>
+      </c>
+      <c r="J121" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K121" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L121" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M121" s="89"/>
+      <c r="N121" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O121" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P121" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q121" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R121" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S121" t="s">
+        <v>120</v>
+      </c>
+      <c r="T121" s="69"/>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A122" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B122" s="83">
+        <v>25</v>
+      </c>
+      <c r="C122" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D122" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E122" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F122" s="86">
+        <v>1</v>
+      </c>
+      <c r="G122" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H122" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I122" s="87" t="s">
+        <v>408</v>
+      </c>
+      <c r="J122" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K122" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L122" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M122" s="89"/>
+      <c r="N122" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O122" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P122" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q122" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R122" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S122" t="s">
+        <v>120</v>
+      </c>
+      <c r="T122" s="69"/>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A123" s="15">
+        <v>2349</v>
+      </c>
+      <c r="B123" s="83">
+        <v>26</v>
+      </c>
+      <c r="C123" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="D123" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="E123" s="85" t="s">
+        <v>152</v>
+      </c>
+      <c r="F123" s="86">
+        <v>1</v>
+      </c>
+      <c r="G123" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="H123" s="82" t="s">
+        <v>77</v>
+      </c>
+      <c r="I123" s="87" t="s">
+        <v>408</v>
+      </c>
+      <c r="J123" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K123" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L123" s="88">
+        <v>46356</v>
+      </c>
+      <c r="M123" s="89"/>
+      <c r="N123" s="90">
+        <f ca="1">Tabela4[[#This Row],[Prazo
+Entrega]]-TODAY()</f>
+        <v>147</v>
+      </c>
+      <c r="O123" s="91" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v>NO PRAZO</v>
+      </c>
+      <c r="P123" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q123" s="80">
+        <v>46264</v>
+      </c>
+      <c r="R123" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="S123" t="s">
+        <v>120</v>
+      </c>
+      <c r="T123" s="69"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -44320,11 +47033,11 @@
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="A30:A43">
-    <cfRule type="containsText" dxfId="41" priority="51" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="41" priority="50" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",A30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="51" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",A30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="50" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",A30)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="39" priority="52">
       <formula>$P30="s"</formula>
@@ -44345,88 +47058,88 @@
     <cfRule type="containsText" dxfId="35" priority="29" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",C45)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="31">
+    <cfRule type="containsText" dxfId="34" priority="30" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",C45)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="31">
       <formula>$P45="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="30" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",C45)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C55:C77">
-    <cfRule type="containsText" dxfId="32" priority="26" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="32" priority="25" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="26" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",C55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="27">
+    <cfRule type="expression" dxfId="30" priority="27">
       <formula>$P55="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="25" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:D43">
     <cfRule type="containsText" dxfId="29" priority="47" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",D30)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="49">
+    <cfRule type="containsText" dxfId="28" priority="48" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",D30)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="49">
       <formula>$P30="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="48" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",D30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D77">
-    <cfRule type="containsText" dxfId="26" priority="22" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",D55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="22" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",D55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="21" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",D55)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="23">
       <formula>$P55="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59:G60 G67">
-    <cfRule type="expression" dxfId="23" priority="12">
-      <formula>$P59="s"</formula>
+    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="22" priority="10" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",G59)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
+    <cfRule type="expression" dxfId="21" priority="12">
+      <formula>$P59="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58 H60 H62 H65:H66 H76">
-    <cfRule type="containsText" dxfId="20" priority="14" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="20" priority="13" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="14" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",H58)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="16">
+    <cfRule type="expression" dxfId="18" priority="16">
       <formula>$P58="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:N45">
     <cfRule type="containsText" dxfId="17" priority="41" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",N33)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="43">
+    <cfRule type="containsText" dxfId="16" priority="42" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",N33)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="43">
       <formula>$P33="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="42" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",N33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N55:N77">
     <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",N55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",N55)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>$P55="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",N55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O33:O35">
@@ -44463,14 +47176,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB55:AB77">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",AB55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>$P55="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F68BAA-E522-4AA5-B195-6A442D05619B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB854C81-6B01-4AF6-AAB2-0AF41CD41F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
   <sheets>
     <sheet name="BAGACEIRAS" sheetId="2" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6801" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6803" uniqueCount="417">
   <si>
     <t>O.S.</t>
   </si>
@@ -1329,6 +1329,18 @@
   <si>
     <t>PENTE INF/SUP TIPO CONVENCIONAL - 2000</t>
   </si>
+  <si>
+    <t>EXPEDIDO</t>
+  </si>
+  <si>
+    <t>RECUPERANDO</t>
+  </si>
+  <si>
+    <t>11/07/206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECISA RETORNAR PARA USINAGEM </t>
+  </si>
 </sst>
 </file>
 
@@ -1337,7 +1349,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="167" formatCode="##0"/>
+    <numFmt numFmtId="165" formatCode="##0"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -1597,7 +1609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1783,53 +1795,25 @@
     <xf numFmtId="14" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1837,23 +1821,10 @@
     <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5944,7 +5915,7 @@
       <c r="O2" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P2" s="40" t="str">
         <f t="shared" ref="P2:P33" ca="1" si="0">IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -6058,7 +6029,7 @@
       <c r="O3" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P3" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6173,7 +6144,7 @@
       <c r="O4" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P4" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6288,7 +6259,7 @@
       <c r="O5" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P5" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6403,7 +6374,7 @@
       <c r="O6" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P6" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6521,7 +6492,7 @@
       <c r="O7" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P7" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6638,7 +6609,7 @@
       <c r="O8" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P8" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6754,7 +6725,7 @@
       <c r="O9" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P9" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6870,7 +6841,7 @@
       <c r="O10" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -6986,7 +6957,7 @@
       <c r="O11" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7100,7 +7071,7 @@
       <c r="O12" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P12" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7215,7 +7186,7 @@
       <c r="O13" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P13" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7330,7 +7301,7 @@
       <c r="O14" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P14" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7445,7 +7416,7 @@
       <c r="O15" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P15" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7565,7 +7536,7 @@
       <c r="O16" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P16" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7681,7 +7652,7 @@
       <c r="O17" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P17" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7797,7 +7768,7 @@
       <c r="O18" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P18" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -7913,7 +7884,7 @@
       <c r="O19" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P19" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8027,7 +7998,7 @@
       <c r="O20" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P20" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8142,7 +8113,7 @@
       <c r="O21" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P21" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8257,7 +8228,7 @@
       <c r="O22" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P22" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8372,7 +8343,7 @@
       <c r="O23" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P23" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8487,7 +8458,7 @@
       <c r="O24" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8602,7 +8573,7 @@
       <c r="O25" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8717,7 +8688,7 @@
       <c r="O26" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8832,7 +8803,7 @@
       <c r="O27" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -8947,7 +8918,7 @@
       <c r="O28" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9062,7 +9033,7 @@
       <c r="O29" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9177,7 +9148,7 @@
       <c r="O30" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P30" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9294,7 +9265,7 @@
       <c r="O31" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P31" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9408,7 +9379,7 @@
       <c r="O32" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P32" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9523,7 +9494,7 @@
       <c r="O33" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P33" s="40" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -9638,7 +9609,7 @@
       <c r="O34" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P34" s="40" t="str">
         <f t="shared" ref="P34:P65" ca="1" si="2">IF(O34&lt;0,"ATRASADO",IF(O34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -9753,7 +9724,7 @@
       <c r="O35" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P35" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9868,7 +9839,7 @@
       <c r="O36" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P36" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -9983,7 +9954,7 @@
       <c r="O37" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P37" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10101,7 +10072,7 @@
       <c r="O38" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P38" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10215,7 +10186,7 @@
       <c r="O39" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P39" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10326,7 +10297,7 @@
       <c r="O40" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P40" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10441,7 +10412,7 @@
       <c r="O41" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P41" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10556,7 +10527,7 @@
       <c r="O42" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P42" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10671,7 +10642,7 @@
       <c r="O43" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P43" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10783,7 +10754,7 @@
       <c r="O44" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P44" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -10898,7 +10869,7 @@
       <c r="O45" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P45" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11013,7 +10984,7 @@
       <c r="O46" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P46" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11128,7 +11099,7 @@
       <c r="O47" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P47" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11243,7 +11214,7 @@
       <c r="O48" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P48" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11356,7 +11327,7 @@
       <c r="O49" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P49" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11469,7 +11440,7 @@
       <c r="O50" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P50" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11584,7 +11555,7 @@
       <c r="O51" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P51" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11699,7 +11670,7 @@
       <c r="O52" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P52" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11814,7 +11785,7 @@
       <c r="O53" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P53" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -11929,7 +11900,7 @@
       <c r="O54" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P54" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12041,7 +12012,7 @@
       <c r="O55" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P55" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12156,7 +12127,7 @@
       <c r="O56" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P56" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12268,7 +12239,7 @@
       <c r="O57" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P57" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12383,7 +12354,7 @@
       <c r="O58" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P58" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12498,7 +12469,7 @@
       <c r="O59" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P59" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12613,7 +12584,7 @@
       <c r="O60" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P60" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12723,7 +12694,7 @@
       <c r="O61" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P61" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12833,7 +12804,7 @@
       <c r="O62" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P62" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -12943,7 +12914,7 @@
       <c r="O63" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P63" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -13053,7 +13024,7 @@
       <c r="O64" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P64" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -13163,7 +13134,7 @@
       <c r="O65" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P65" s="40" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -13273,7 +13244,7 @@
       <c r="O66" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P66" s="40" t="str">
         <f t="shared" ref="P66:P89" ca="1" si="4">IF(O66&lt;0,"ATRASADO",IF(O66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -13380,7 +13351,7 @@
       <c r="O67" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P67" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13495,7 +13466,7 @@
       <c r="O68" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P68" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13607,7 +13578,7 @@
       <c r="O69" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P69" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13719,7 +13690,7 @@
       <c r="O70" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P70" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13831,7 +13802,7 @@
       <c r="O71" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P71" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -13943,7 +13914,7 @@
       <c r="O72" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P72" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14055,7 +14026,7 @@
       <c r="O73" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P73" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14167,7 +14138,7 @@
       <c r="O74" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P74" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14279,7 +14250,7 @@
       <c r="O75" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P75" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14391,7 +14362,7 @@
       <c r="O76" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P76" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14503,7 +14474,7 @@
       <c r="O77" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P77" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14615,7 +14586,7 @@
       <c r="O78" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P78" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14725,7 +14696,7 @@
       <c r="O79" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P79" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14835,7 +14806,7 @@
       <c r="O80" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P80" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -14945,7 +14916,7 @@
       <c r="O81" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P81" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15055,7 +15026,7 @@
       <c r="O82" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P82" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15165,7 +15136,7 @@
       <c r="O83" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P83" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15275,7 +15246,7 @@
       <c r="O84" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P84" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15389,7 +15360,7 @@
       <c r="O85" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P85" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15503,7 +15474,7 @@
       <c r="O86" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P86" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15617,7 +15588,7 @@
       <c r="O87" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P87" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15731,7 +15702,7 @@
       <c r="O88" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P88" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15845,7 +15816,7 @@
       <c r="O89" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P89" s="40" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -15959,7 +15930,7 @@
       <c r="O90" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P90" s="40" t="str">
         <f t="shared" ref="P90:P94" ca="1" si="6">IF(O90&lt;0,"ATRASADO",IF(O90&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16066,7 +16037,7 @@
       <c r="O91" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P91" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16173,7 +16144,7 @@
       <c r="O92" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P92" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16280,7 +16251,7 @@
       <c r="O93" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P93" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16387,7 +16358,7 @@
       <c r="O94" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P94" s="40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -16494,7 +16465,7 @@
       <c r="O95" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P95" s="40" t="str">
         <f t="shared" ref="P95:P99" ca="1" si="7">IF(O95&lt;0,"ATRASADO",IF(O95&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -16591,7 +16562,7 @@
       <c r="O96" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P96" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -16688,7 +16659,7 @@
       <c r="O97" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P97" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -16785,7 +16756,7 @@
       <c r="O98" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P98" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -16882,7 +16853,7 @@
       <c r="O99" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P99" s="40" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -16979,7 +16950,7 @@
       <c r="O100" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P100" s="40" t="str">
         <f ca="1">IF(O100&lt;0,"ATRASADO",IF(O100&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -17076,7 +17047,7 @@
       <c r="O101" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P101" s="40" t="str">
         <f t="shared" ref="P101:P109" ca="1" si="9">IF(O101&lt;0,"ATRASADO",IF(O101&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -17173,7 +17144,7 @@
       <c r="O102" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P102" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17270,7 +17241,7 @@
       <c r="O103" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P103" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17367,7 +17338,7 @@
       <c r="O104" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P104" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17464,7 +17435,7 @@
       <c r="O105" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P105" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17561,7 +17532,7 @@
       <c r="O106" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P106" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17658,7 +17629,7 @@
       <c r="O107" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P107" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17755,7 +17726,7 @@
       <c r="O108" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P108" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17852,7 +17823,7 @@
       <c r="O109" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P109" s="40" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -17949,7 +17920,7 @@
       <c r="O110" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P110" s="40" t="str">
         <f ca="1">IF(O110&lt;0,"ATRASADO",IF(O110&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -18046,7 +18017,7 @@
       <c r="O111" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P111" s="40" t="str">
         <f t="shared" ref="P111:P114" ca="1" si="10">IF(O111&lt;0,"ATRASADO",IF(O111&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -18143,7 +18114,7 @@
       <c r="O112" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P112" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -18240,7 +18211,7 @@
       <c r="O113" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P113" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -18337,7 +18308,7 @@
       <c r="O114" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P114" s="40" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -18547,7 +18518,7 @@
       <c r="Q2" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R2" s="10" t="str">
         <f t="shared" ref="R2:R33" ca="1" si="0">IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -18618,7 +18589,7 @@
       <c r="Q3" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18689,7 +18660,7 @@
       <c r="Q4" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18760,7 +18731,7 @@
       <c r="Q5" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18831,7 +18802,7 @@
       <c r="Q6" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18902,7 +18873,7 @@
       <c r="Q7" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -18973,7 +18944,7 @@
       <c r="Q8" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19044,7 +19015,7 @@
       <c r="Q9" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19115,7 +19086,7 @@
       <c r="Q10" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19186,7 +19157,7 @@
       <c r="Q11" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19259,7 +19230,7 @@
       <c r="Q12" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R12" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19332,7 +19303,7 @@
       <c r="Q13" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R13" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19405,7 +19376,7 @@
       <c r="Q14" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19476,7 +19447,7 @@
       <c r="Q15" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19547,7 +19518,7 @@
       <c r="Q16" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19618,7 +19589,7 @@
       <c r="Q17" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19689,7 +19660,7 @@
       <c r="Q18" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19760,7 +19731,7 @@
       <c r="Q19" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19831,7 +19802,7 @@
       <c r="Q20" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R20" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19902,7 +19873,7 @@
       <c r="Q21" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -19973,7 +19944,7 @@
       <c r="Q22" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R22" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20044,7 +20015,7 @@
       <c r="Q23" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20115,7 +20086,7 @@
       <c r="Q24" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R24" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20186,7 +20157,7 @@
       <c r="Q25" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R25" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20257,7 +20228,7 @@
       <c r="Q26" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20328,7 +20299,7 @@
       <c r="Q27" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20399,7 +20370,7 @@
       <c r="Q28" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20470,7 +20441,7 @@
       <c r="Q29" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20541,7 +20512,7 @@
       <c r="Q30" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20612,7 +20583,7 @@
       <c r="Q31" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R31" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20683,7 +20654,7 @@
       <c r="Q32" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R32" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20754,7 +20725,7 @@
       <c r="Q33" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R33" s="10" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -20827,7 +20798,7 @@
       <c r="Q34" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R34" s="10" t="str">
         <f t="shared" ref="R34:R65" ca="1" si="1">IF(Q34&lt;0,"ATRASADO",IF(Q34&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -20900,7 +20871,7 @@
       <c r="Q35" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R35" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -20973,7 +20944,7 @@
       <c r="Q36" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R36" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21046,7 +21017,7 @@
       <c r="Q37" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R37" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21119,7 +21090,7 @@
       <c r="Q38" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R38" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21190,7 +21161,7 @@
       <c r="Q39" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R39" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21261,7 +21232,7 @@
       <c r="Q40" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R40" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21332,7 +21303,7 @@
       <c r="Q41" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R41" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21403,7 +21374,7 @@
       <c r="Q42" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R42" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21474,7 +21445,7 @@
       <c r="Q43" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R43" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21545,7 +21516,7 @@
       <c r="Q44" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R44" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21616,7 +21587,7 @@
       <c r="Q45" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R45" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21687,7 +21658,7 @@
       <c r="Q46" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R46" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21758,7 +21729,7 @@
       <c r="Q47" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R47" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21829,7 +21800,7 @@
       <c r="Q48" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R48" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21900,7 +21871,7 @@
       <c r="Q49" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R49" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -21971,7 +21942,7 @@
       <c r="Q50" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R50" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22042,7 +22013,7 @@
       <c r="Q51" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R51" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22113,7 +22084,7 @@
       <c r="Q52" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R52" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22184,7 +22155,7 @@
       <c r="Q53" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R53" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22255,7 +22226,7 @@
       <c r="Q54" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R54" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22326,7 +22297,7 @@
       <c r="Q55" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R55" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22397,7 +22368,7 @@
       <c r="Q56" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R56" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22468,7 +22439,7 @@
       <c r="Q57" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R57" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22539,7 +22510,7 @@
       <c r="Q58" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R58" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22610,7 +22581,7 @@
       <c r="Q59" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R59" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22681,7 +22652,7 @@
       <c r="Q60" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R60" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22752,7 +22723,7 @@
       <c r="Q61" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R61" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22823,7 +22794,7 @@
       <c r="Q62" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R62" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22894,7 +22865,7 @@
       <c r="Q63" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R63" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -22965,7 +22936,7 @@
       <c r="Q64" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R64" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -23036,7 +23007,7 @@
       <c r="Q65" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R65" s="10" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -23107,7 +23078,7 @@
       <c r="Q66" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R66" s="10" t="str">
         <f t="shared" ref="R66:R91" ca="1" si="2">IF(Q66&lt;0,"ATRASADO",IF(Q66&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -23178,7 +23149,7 @@
       <c r="Q67" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R67" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23249,7 +23220,7 @@
       <c r="Q68" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R68" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23320,7 +23291,7 @@
       <c r="Q69" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R69" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23391,7 +23362,7 @@
       <c r="Q70" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R70" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23462,7 +23433,7 @@
       <c r="Q71" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R71" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23533,7 +23504,7 @@
       <c r="Q72" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R72" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23604,7 +23575,7 @@
       <c r="Q73" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R73" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23675,7 +23646,7 @@
       <c r="Q74" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R74" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23746,7 +23717,7 @@
       <c r="Q75" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R75" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23817,7 +23788,7 @@
       <c r="Q76" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R76" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23888,7 +23859,7 @@
       <c r="Q77" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R77" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -23959,7 +23930,7 @@
       <c r="Q78" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R78" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24030,7 +24001,7 @@
       <c r="Q79" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R79" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24101,7 +24072,7 @@
       <c r="Q80" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R80" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24172,7 +24143,7 @@
       <c r="Q81" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R81" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24243,7 +24214,7 @@
       <c r="Q82" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R82" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24314,7 +24285,7 @@
       <c r="Q83" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R83" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24385,7 +24356,7 @@
       <c r="Q84" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R84" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24456,7 +24427,7 @@
       <c r="Q85" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R85" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24527,7 +24498,7 @@
       <c r="Q86" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R86" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24598,7 +24569,7 @@
       <c r="Q87" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R87" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24669,7 +24640,7 @@
       <c r="Q88" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R88" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24740,7 +24711,7 @@
       <c r="Q89" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R89" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24811,7 +24782,7 @@
       <c r="Q90" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R90" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24882,7 +24853,7 @@
       <c r="Q91" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R91" s="10" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -24953,7 +24924,7 @@
       <c r="Q92" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R92" s="10" t="str">
         <f ca="1">IF(Q92&lt;0,"ATRASADO",IF(Q92&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25024,7 +24995,7 @@
       <c r="Q93" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R93" s="10" t="str">
         <f ca="1">IF(Q93&lt;0,"ATRASADO",IF(Q93&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25095,7 +25066,7 @@
       <c r="Q94" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R94" s="10" t="str">
         <f t="shared" ref="R94:R131" ca="1" si="3">IF(Q94&lt;0,"ATRASADO",IF(Q94&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -25166,7 +25137,7 @@
       <c r="Q95" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R95" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25237,7 +25208,7 @@
       <c r="Q96" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R96" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25308,7 +25279,7 @@
       <c r="Q97" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R97" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25379,7 +25350,7 @@
       <c r="Q98" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R98" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25450,7 +25421,7 @@
       <c r="Q99" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R99" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25521,7 +25492,7 @@
       <c r="Q100" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R100" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25592,7 +25563,7 @@
       <c r="Q101" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R101" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25663,7 +25634,7 @@
       <c r="Q102" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R102" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25734,7 +25705,7 @@
       <c r="Q103" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R103" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25805,7 +25776,7 @@
       <c r="Q104" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R104" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25876,7 +25847,7 @@
       <c r="Q105" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R105" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -25947,7 +25918,7 @@
       <c r="Q106" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R106" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26018,7 +25989,7 @@
       <c r="Q107" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R107" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26089,7 +26060,7 @@
       <c r="Q108" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R108" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26160,7 +26131,7 @@
       <c r="Q109" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R109" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26231,7 +26202,7 @@
       <c r="Q110" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R110" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26302,7 +26273,7 @@
       <c r="Q111" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R111" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26373,7 +26344,7 @@
       <c r="Q112" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R112" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26444,7 +26415,7 @@
       <c r="Q113" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R113" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26515,7 +26486,7 @@
       <c r="Q114" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R114" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26586,7 +26557,7 @@
       <c r="Q115" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R115" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26657,7 +26628,7 @@
       <c r="Q116" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R116" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26728,7 +26699,7 @@
       <c r="Q117" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R117" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26799,7 +26770,7 @@
       <c r="Q118" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R118" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26870,7 +26841,7 @@
       <c r="Q119" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R119" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -26941,7 +26912,7 @@
       <c r="Q120" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R120" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27012,7 +26983,7 @@
       <c r="Q121" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R121" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27083,7 +27054,7 @@
       <c r="Q122" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R122" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27154,7 +27125,7 @@
       <c r="Q123" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R123" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27225,7 +27196,7 @@
       <c r="Q124" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R124" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27296,7 +27267,7 @@
       <c r="Q125" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R125" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27367,7 +27338,7 @@
       <c r="Q126" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R126" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27438,7 +27409,7 @@
       <c r="Q127" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R127" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27509,7 +27480,7 @@
       <c r="Q128" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R128" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27580,7 +27551,7 @@
       <c r="Q129" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R129" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27651,7 +27622,7 @@
       <c r="Q130" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R130" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27722,7 +27693,7 @@
       <c r="Q131" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R131" s="10" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -27793,7 +27764,7 @@
       <c r="Q132" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R132" s="10" t="str">
         <f ca="1">IF(Q132&lt;0,"ATRASADO",IF(Q132&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27866,7 +27837,7 @@
       <c r="Q133" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R133" s="10" t="str">
         <f t="shared" ref="R133:R143" ca="1" si="4">IF(Q133&lt;0,"ATRASADO",IF(Q133&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -27939,7 +27910,7 @@
       <c r="Q134" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R134" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28012,7 +27983,7 @@
       <c r="Q135" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R135" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28085,7 +28056,7 @@
       <c r="Q136" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R136" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28154,7 +28125,7 @@
       <c r="Q137" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R137" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28221,7 +28192,7 @@
       <c r="Q138" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R138" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28288,7 +28259,7 @@
       <c r="Q139" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R139" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28355,7 +28326,7 @@
       <c r="Q140" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R140" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28422,7 +28393,7 @@
       <c r="Q141" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R141" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28489,7 +28460,7 @@
       <c r="Q142" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R142" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28556,7 +28527,7 @@
       <c r="Q143" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R143" s="10" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28627,7 +28598,7 @@
       <c r="Q144" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R144" s="10" t="str">
         <f ca="1">IF(Q144&lt;0,"ATRASADO",IF(Q144&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28700,7 +28671,7 @@
       <c r="Q145" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R145" s="10" t="str">
         <f t="shared" ref="R145:R151" ca="1" si="5">IF(Q145&lt;0,"ATRASADO",IF(Q145&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -28773,7 +28744,7 @@
       <c r="Q146" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R146" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28846,7 +28817,7 @@
       <c r="Q147" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R147" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28919,7 +28890,7 @@
       <c r="Q148" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R148" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -28992,7 +28963,7 @@
       <c r="Q149" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R149" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -29065,7 +29036,7 @@
       <c r="Q150" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R150" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -29138,7 +29109,7 @@
       <c r="Q151" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R151" s="10" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -29205,7 +29176,7 @@
       <c r="Q152" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R152" s="10" t="str">
         <f t="shared" ref="R152:R156" ca="1" si="6">IF(Q152&lt;0,"ATRASADO",IF(Q152&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -29270,7 +29241,7 @@
       <c r="Q153" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R153" s="10" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -29335,7 +29306,7 @@
       <c r="Q154" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R154" s="10" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -29400,7 +29371,7 @@
       <c r="Q155" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R155" s="10" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -29465,7 +29436,7 @@
       <c r="Q156" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R156" s="10" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -29502,7 +29473,7 @@
       </c>
       <c r="F157" s="10"/>
       <c r="G157" s="10"/>
-      <c r="H157" s="97" t="s">
+      <c r="H157" s="79" t="s">
         <v>412</v>
       </c>
       <c r="I157" s="10">
@@ -29511,7 +29482,7 @@
       <c r="J157" s="11">
         <v>46241</v>
       </c>
-      <c r="K157" s="92">
+      <c r="K157" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>32</v>
@@ -29530,24 +29501,24 @@
       <c r="Q157" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
-      </c>
-      <c r="R157" s="92" t="str">
+        <v>31</v>
+      </c>
+      <c r="R157" s="10" t="str">
         <f t="shared" ref="R157:R163" ca="1" si="7">IF(Q157&lt;0,"ATRASADO",IF(Q157&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
         <v>NO PRAZO</v>
       </c>
-      <c r="S157" s="92">
+      <c r="S157" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>32</v>
       </c>
-      <c r="T157" s="92" t="s">
+      <c r="T157" s="10" t="s">
         <v>90</v>
       </c>
       <c r="U157" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V157" s="92"/>
+      <c r="V157" s="10"/>
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A158" s="10">
@@ -29567,7 +29538,7 @@
       </c>
       <c r="F158" s="10"/>
       <c r="G158" s="10"/>
-      <c r="H158" s="97" t="s">
+      <c r="H158" s="79" t="s">
         <v>412</v>
       </c>
       <c r="I158" s="10">
@@ -29576,7 +29547,7 @@
       <c r="J158" s="11">
         <v>46241</v>
       </c>
-      <c r="K158" s="92">
+      <c r="K158" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>32</v>
@@ -29595,24 +29566,24 @@
       <c r="Q158" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
-      </c>
-      <c r="R158" s="92" t="str">
+        <v>31</v>
+      </c>
+      <c r="R158" s="10" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S158" s="92">
+      <c r="S158" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>32</v>
       </c>
-      <c r="T158" s="92" t="s">
+      <c r="T158" s="10" t="s">
         <v>90</v>
       </c>
       <c r="U158" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V158" s="92"/>
+      <c r="V158" s="10"/>
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A159" s="10">
@@ -29632,7 +29603,7 @@
       </c>
       <c r="F159" s="10"/>
       <c r="G159" s="10"/>
-      <c r="H159" s="97" t="s">
+      <c r="H159" s="79" t="s">
         <v>412</v>
       </c>
       <c r="I159" s="10">
@@ -29641,7 +29612,7 @@
       <c r="J159" s="11">
         <v>46241</v>
       </c>
-      <c r="K159" s="92">
+      <c r="K159" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>32</v>
@@ -29660,24 +29631,24 @@
       <c r="Q159" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
-      </c>
-      <c r="R159" s="92" t="str">
+        <v>31</v>
+      </c>
+      <c r="R159" s="10" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S159" s="92">
+      <c r="S159" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>32</v>
       </c>
-      <c r="T159" s="92" t="s">
+      <c r="T159" s="10" t="s">
         <v>90</v>
       </c>
       <c r="U159" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V159" s="92"/>
+      <c r="V159" s="10"/>
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A160" s="10">
@@ -29697,7 +29668,7 @@
       </c>
       <c r="F160" s="10"/>
       <c r="G160" s="10"/>
-      <c r="H160" s="97" t="s">
+      <c r="H160" s="79" t="s">
         <v>412</v>
       </c>
       <c r="I160" s="10">
@@ -29706,7 +29677,7 @@
       <c r="J160" s="11">
         <v>46241</v>
       </c>
-      <c r="K160" s="92">
+      <c r="K160" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>32</v>
@@ -29725,24 +29696,24 @@
       <c r="Q160" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
-      </c>
-      <c r="R160" s="92" t="str">
+        <v>31</v>
+      </c>
+      <c r="R160" s="10" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S160" s="92">
+      <c r="S160" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>32</v>
       </c>
-      <c r="T160" s="92" t="s">
+      <c r="T160" s="10" t="s">
         <v>90</v>
       </c>
       <c r="U160" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V160" s="92"/>
+      <c r="V160" s="10"/>
     </row>
     <row r="161" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A161" s="10">
@@ -29762,7 +29733,7 @@
       </c>
       <c r="F161" s="10"/>
       <c r="G161" s="10"/>
-      <c r="H161" s="97" t="s">
+      <c r="H161" s="79" t="s">
         <v>412</v>
       </c>
       <c r="I161" s="10">
@@ -29771,7 +29742,7 @@
       <c r="J161" s="11">
         <v>46241</v>
       </c>
-      <c r="K161" s="92">
+      <c r="K161" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>32</v>
@@ -29790,24 +29761,24 @@
       <c r="Q161" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
-      </c>
-      <c r="R161" s="92" t="str">
+        <v>31</v>
+      </c>
+      <c r="R161" s="10" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S161" s="92">
+      <c r="S161" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>32</v>
       </c>
-      <c r="T161" s="92" t="s">
+      <c r="T161" s="10" t="s">
         <v>90</v>
       </c>
       <c r="U161" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V161" s="92"/>
+      <c r="V161" s="10"/>
     </row>
     <row r="162" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A162" s="10">
@@ -29827,7 +29798,7 @@
       </c>
       <c r="F162" s="10"/>
       <c r="G162" s="10"/>
-      <c r="H162" s="97" t="s">
+      <c r="H162" s="79" t="s">
         <v>412</v>
       </c>
       <c r="I162" s="10">
@@ -29836,7 +29807,7 @@
       <c r="J162" s="11">
         <v>46241</v>
       </c>
-      <c r="K162" s="92">
+      <c r="K162" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>32</v>
@@ -29855,44 +29826,44 @@
       <c r="Q162" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
-      </c>
-      <c r="R162" s="92" t="str">
+        <v>31</v>
+      </c>
+      <c r="R162" s="10" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S162" s="92">
+      <c r="S162" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>32</v>
       </c>
-      <c r="T162" s="92" t="s">
+      <c r="T162" s="10" t="s">
         <v>90</v>
       </c>
       <c r="U162" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V162" s="92"/>
+      <c r="V162" s="10"/>
     </row>
     <row r="163" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A163" s="10">
         <v>2352</v>
       </c>
-      <c r="B163" s="93">
+      <c r="B163" s="10">
         <v>7</v>
       </c>
       <c r="C163" s="10">
         <v>27635</v>
       </c>
-      <c r="D163" s="93">
+      <c r="D163" s="10">
         <v>7</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F163" s="93"/>
-      <c r="G163" s="93"/>
-      <c r="H163" s="97" t="s">
+      <c r="F163" s="10"/>
+      <c r="G163" s="10"/>
+      <c r="H163" s="79" t="s">
         <v>411</v>
       </c>
       <c r="I163" s="10">
@@ -29901,43 +29872,43 @@
       <c r="J163" s="11">
         <v>46241</v>
       </c>
-      <c r="K163" s="94">
+      <c r="K163" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</f>
         <v>32</v>
       </c>
-      <c r="L163" s="93"/>
+      <c r="L163" s="10"/>
       <c r="M163" s="11">
         <v>46241</v>
       </c>
-      <c r="N163" s="95"/>
+      <c r="N163" s="18"/>
       <c r="O163" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P163" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="Q163" s="96">
+      <c r="Q163" s="12">
         <f ca="1">Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>32</v>
-      </c>
-      <c r="R163" s="94" t="str">
+        <v>31</v>
+      </c>
+      <c r="R163" s="10" t="str">
         <f t="shared" ca="1" si="7"/>
         <v>NO PRAZO</v>
       </c>
-      <c r="S163" s="94">
+      <c r="S163" s="10">
         <f>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</f>
         <v>32</v>
       </c>
-      <c r="T163" s="94" t="s">
+      <c r="T163" s="10" t="s">
         <v>90</v>
       </c>
       <c r="U163" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="V163" s="94"/>
+      <c r="V163" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -30087,7 +30058,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O2" s="13" t="str">
         <f t="shared" ref="O2:O16" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -30164,7 +30135,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O3" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30241,7 +30212,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O4" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30318,7 +30289,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O5" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30395,7 +30366,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O6" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30472,7 +30443,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O7" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30549,7 +30520,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O8" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30626,7 +30597,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O9" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30703,7 +30674,7 @@
       <c r="N10" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O10" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30780,7 +30751,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O11" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30857,7 +30828,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O12" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -30934,7 +30905,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O13" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31011,7 +30982,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O14" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31088,7 +31059,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O15" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31165,7 +31136,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O16" s="13" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -31242,7 +31213,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O17" s="13" t="str">
         <f ca="1">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31321,7 +31292,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O18" s="13" t="str">
         <f t="shared" ref="O18:O25" ca="1" si="2">IF(N18&lt;0,"ATRASADO",IF(N18&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -31400,7 +31371,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O19" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31479,7 +31450,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O20" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31558,7 +31529,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O21" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31637,7 +31608,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O22" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31716,7 +31687,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O23" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31795,7 +31766,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O24" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31874,7 +31845,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O25" s="13" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -31953,7 +31924,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O26" s="13" t="str">
         <f ca="1">IF(N26&lt;0,"ATRASADO",IF(N26&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32030,7 +32001,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O27" s="13" t="str">
         <f t="shared" ref="O27:O28" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32107,7 +32078,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O28" s="13" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -32184,7 +32155,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O29" s="13" t="str">
         <f t="shared" ref="O29:O31" ca="1" si="5">IF(N29&lt;0,"ATRASADO",IF(N29&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32263,7 +32234,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O30" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -32342,7 +32313,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O31" s="13" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -32421,7 +32392,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O32" s="13" t="str">
         <f ca="1">IF(N32&lt;0,"ATRASADO",IF(N32&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32500,7 +32471,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O33" s="13" t="str">
         <f t="shared" ref="O33:O35" ca="1" si="7">IF(N33&lt;0,"ATRASADO",IF(N33&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32579,7 +32550,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O34" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -32658,7 +32629,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O35" s="13" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -32737,7 +32708,7 @@
       <c r="N36" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O36" s="13" t="str">
         <f ca="1">IF(N36&lt;0,"ATRASADO",IF(N36&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32814,7 +32785,7 @@
       <c r="N37" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O37" s="13" t="str">
         <f t="shared" ref="O37:O39" ca="1" si="9">IF(N37&lt;0,"ATRASADO",IF(N37&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -32891,7 +32862,7 @@
       <c r="N38" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O38" s="13" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -32968,7 +32939,7 @@
       <c r="N39" s="13">
         <f ca="1">Tabela13[[#This Row],[Data Prev.
 Entrega]]-TODAY()</f>
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O39" s="13" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -33804,7 +33775,7 @@
       <c r="N2" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O2" t="str">
         <f t="shared" ref="O2:O9" ca="1" si="0">IF(N2&lt;0,"ATRASADO",IF(N2&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -33863,7 +33834,7 @@
       <c r="N3" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O3" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33922,7 +33893,7 @@
       <c r="N4" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O4" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -33981,7 +33952,7 @@
       <c r="N5" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O5" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34040,7 +34011,7 @@
       <c r="N6" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O6" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34099,7 +34070,7 @@
       <c r="N7" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34158,7 +34129,7 @@
       <c r="N8" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O8" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34217,7 +34188,7 @@
       <c r="N9" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34282,7 +34253,7 @@
       <c r="N10" s="12">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="O10" s="33" t="s">
         <v>102</v>
@@ -34340,7 +34311,7 @@
       <c r="N11" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O11" s="1" t="str">
         <f ca="1">IF(N11&lt;0,"ATRASADO",IF(N11&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34402,7 +34373,7 @@
       <c r="N12" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O12" t="str">
         <f ca="1">IF(N12&lt;0,"ATRASADO",IF(N12&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34464,7 +34435,7 @@
       <c r="N13" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">IF(N13&lt;0,"ATRASADO",IF(N13&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34526,7 +34497,7 @@
       <c r="N14" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O14" t="str">
         <f ca="1">IF(N14&lt;0,"ATRASADO",IF(N14&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34588,7 +34559,7 @@
       <c r="N15" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O15" t="str">
         <f t="shared" ref="O15:O16" ca="1" si="1">IF(N15&lt;0,"ATRASADO",IF(N15&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34650,7 +34621,7 @@
       <c r="N16" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -34709,7 +34680,7 @@
       <c r="N17" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O17" t="str">
         <f t="shared" ref="O17:O18" ca="1" si="2">IF(N17&lt;0,"ATRASADO",IF(N17&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34765,7 +34736,7 @@
       <c r="N18" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -34824,7 +34795,7 @@
       <c r="N19" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O19" t="str">
         <f ca="1">IF(N19&lt;0,"ATRASADO",IF(N19&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34883,7 +34854,7 @@
       <c r="N20" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O20" t="str">
         <f ca="1">IF(N20&lt;0,"ATRASADO",IF(N20&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -34942,7 +34913,7 @@
       <c r="N21" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O21" t="str">
         <f t="shared" ref="O21:O26" ca="1" si="3">IF(N21&lt;0,"ATRASADO",IF(N21&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35001,7 +34972,7 @@
       <c r="N22" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O22" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -35060,7 +35031,7 @@
       <c r="N23" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O23" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -35119,7 +35090,7 @@
       <c r="N24" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O24" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -35178,7 +35149,7 @@
       <c r="N25" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O25" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -35237,7 +35208,7 @@
       <c r="N26" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O26" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -35296,7 +35267,7 @@
       <c r="N27" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O27" t="str">
         <f t="shared" ref="O27:O34" ca="1" si="4">IF(N27&lt;0,"ATRASADO",IF(N27&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35355,7 +35326,7 @@
       <c r="N28" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O28" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -35414,7 +35385,7 @@
       <c r="N29" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O29" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -35473,7 +35444,7 @@
       <c r="N30" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O30" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -35532,7 +35503,7 @@
       <c r="N31" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O31" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -35591,7 +35562,7 @@
       <c r="N32" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O32" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -35650,7 +35621,7 @@
       <c r="N33" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O33" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -35709,7 +35680,7 @@
       <c r="N34" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O34" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -35768,7 +35739,7 @@
       <c r="N35" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O35" t="str">
         <f t="shared" ref="O35:O36" ca="1" si="5">IF(N35&lt;0,"ATRASADO",IF(N35&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35827,7 +35798,7 @@
       <c r="N36" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O36" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -35886,7 +35857,7 @@
       <c r="N37" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O37" t="str">
         <f ca="1">IF(N37&lt;0,"ATRASADO",IF(N37&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -35945,7 +35916,7 @@
       <c r="N38" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O38" t="str">
         <f t="shared" ref="O38:O52" ca="1" si="6">IF(N38&lt;0,"ATRASADO",IF(N38&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -36004,7 +35975,7 @@
       <c r="N39" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O39" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36063,7 +36034,7 @@
       <c r="N40" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O40" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36122,7 +36093,7 @@
       <c r="N41" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O41" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36181,7 +36152,7 @@
       <c r="N42" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O42" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36240,7 +36211,7 @@
       <c r="N43" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O43" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36299,7 +36270,7 @@
       <c r="N44" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O44" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36358,7 +36329,7 @@
       <c r="N45" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O45" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36417,7 +36388,7 @@
       <c r="N46" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O46" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36476,7 +36447,7 @@
       <c r="N47" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O47" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36535,7 +36506,7 @@
       <c r="N48" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O48" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36594,7 +36565,7 @@
       <c r="N49" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O49" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36653,7 +36624,7 @@
       <c r="N50" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O50" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36712,7 +36683,7 @@
       <c r="N51" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O51" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36771,7 +36742,7 @@
       <c r="N52" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O52" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -36833,7 +36804,7 @@
       <c r="N53" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O53" t="s">
         <v>154</v>
@@ -36891,7 +36862,7 @@
       <c r="N54" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O54" t="str">
         <f ca="1">IF(N54&lt;0,"ATRASADO",IF(N54&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -36950,7 +36921,7 @@
       <c r="N55" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O55" t="str">
         <f ca="1">IF(N55&lt;0,"ATRASADO",IF(N55&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -37009,7 +36980,7 @@
       <c r="N56" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O56" t="str">
         <f ca="1">IF(N56&lt;0,"ATRASADO",IF(N56&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -37068,7 +37039,7 @@
       <c r="N57" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O57" t="str">
         <f t="shared" ref="O57:O59" ca="1" si="7">IF(N57&lt;0,"ATRASADO",IF(N57&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -37127,7 +37098,7 @@
       <c r="N58" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O58" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -37186,7 +37157,7 @@
       <c r="N59" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O59" t="str">
         <f t="shared" ca="1" si="7"/>
@@ -37242,7 +37213,7 @@
       <c r="N60" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O60" t="str">
         <f t="shared" ref="O60:O62" ca="1" si="8">IF(N60&lt;0,"ATRASADO",IF(N60&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -37301,7 +37272,7 @@
       <c r="N61" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O61" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -37360,7 +37331,7 @@
       <c r="N62" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O62" t="str">
         <f t="shared" ca="1" si="8"/>
@@ -37422,7 +37393,7 @@
       <c r="N63" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O63" t="str">
         <f ca="1">IF(N63&lt;0,"ATRASADO",IF(N63&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -37481,7 +37452,7 @@
       <c r="N64" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O64" t="str">
         <f t="shared" ref="O64:O76" ca="1" si="9">IF(N64&lt;0,"ATRASADO",IF(N64&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -37540,7 +37511,7 @@
       <c r="N65" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O65" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37599,7 +37570,7 @@
       <c r="N66" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O66" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37658,7 +37629,7 @@
       <c r="N67" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O67" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37717,7 +37688,7 @@
       <c r="N68" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O68" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37776,7 +37747,7 @@
       <c r="N69" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O69" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37835,7 +37806,7 @@
       <c r="N70" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O70" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37894,7 +37865,7 @@
       <c r="N71" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O71" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -37953,7 +37924,7 @@
       <c r="N72" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O72" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -38012,7 +37983,7 @@
       <c r="N73" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O73" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -38071,7 +38042,7 @@
       <c r="N74" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O74" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -38130,7 +38101,7 @@
       <c r="N75" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O75" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -38189,7 +38160,7 @@
       <c r="N76" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O76" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -38248,7 +38219,7 @@
       <c r="N77" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O77" t="str">
         <f ca="1">IF(N77&lt;0,"ATRASADO",IF(N77&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -38307,7 +38278,7 @@
       <c r="N78" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O78" t="str">
         <f t="shared" ref="O78:O80" ca="1" si="10">IF(N78&lt;0,"ATRASADO",IF(N78&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -38366,7 +38337,7 @@
       <c r="N79" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O79" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -38425,7 +38396,7 @@
       <c r="N80" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O80" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -38444,7 +38415,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="15">
         <v>2333</v>
       </c>
@@ -38484,7 +38455,7 @@
       <c r="N81" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O81" t="str">
         <f t="shared" ref="O81:O88" ca="1" si="11">IF(N81&lt;0,"ATRASADO",IF(N81&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
@@ -38503,7 +38474,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="15">
         <v>2333</v>
       </c>
@@ -38543,7 +38514,7 @@
       <c r="N82" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O82" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38562,7 +38533,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="15">
         <v>2333</v>
       </c>
@@ -38602,7 +38573,7 @@
       <c r="N83" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O83" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38621,7 +38592,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>2333</v>
       </c>
@@ -38661,7 +38632,7 @@
       <c r="N84" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O84" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38680,7 +38651,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>2333</v>
       </c>
@@ -38720,7 +38691,7 @@
       <c r="N85" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O85" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38739,7 +38710,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>2333</v>
       </c>
@@ -38779,7 +38750,7 @@
       <c r="N86" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O86" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38798,7 +38769,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>2333</v>
       </c>
@@ -38838,7 +38809,7 @@
       <c r="N87" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O87" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38857,7 +38828,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>2333</v>
       </c>
@@ -38897,7 +38868,7 @@
       <c r="N88" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O88" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -38916,7 +38887,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>1945</v>
       </c>
@@ -38959,7 +38930,7 @@
       <c r="N89" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O89" t="s">
         <v>154</v>
@@ -38977,7 +38948,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="15">
         <v>2345</v>
       </c>
@@ -39002,7 +38973,7 @@
       <c r="H90" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I90" s="79" t="s">
+      <c r="I90" s="69" t="s">
         <v>398</v>
       </c>
       <c r="J90" s="16" t="s">
@@ -39014,31 +38985,29 @@
       <c r="L90" s="7">
         <v>46371</v>
       </c>
-      <c r="M90" s="69"/>
-      <c r="N90" s="70">
+      <c r="N90" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>162</v>
-      </c>
-      <c r="O90" s="71" t="str">
+        <v>161</v>
+      </c>
+      <c r="O90" t="str">
         <f t="shared" ref="O90:O97" ca="1" si="12">IF(N90&lt;0,"ATRASADO",IF(N90&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
         <v>NO PRAZO</v>
       </c>
       <c r="P90" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q90" s="80">
+      <c r="Q90" s="11">
         <v>46264</v>
       </c>
-      <c r="R90" s="72" t="s">
+      <c r="R90" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S90" t="s">
         <v>120</v>
       </c>
-      <c r="T90" s="69"/>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="15">
         <v>2345</v>
       </c>
@@ -39063,7 +39032,7 @@
       <c r="H91" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I91" s="79" t="s">
+      <c r="I91" s="69" t="s">
         <v>398</v>
       </c>
       <c r="J91" s="16" t="s">
@@ -39075,31 +39044,29 @@
       <c r="L91" s="7">
         <v>46371</v>
       </c>
-      <c r="M91" s="69"/>
-      <c r="N91" s="70">
+      <c r="N91" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>162</v>
-      </c>
-      <c r="O91" s="71" t="str">
+        <v>161</v>
+      </c>
+      <c r="O91" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P91" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q91" s="80">
+      <c r="Q91" s="11">
         <v>46264</v>
       </c>
-      <c r="R91" s="72" t="s">
+      <c r="R91" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S91" t="s">
         <v>120</v>
       </c>
-      <c r="T91" s="69"/>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="15">
         <v>2345</v>
       </c>
@@ -39124,7 +39091,7 @@
       <c r="H92" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I92" s="79" t="s">
+      <c r="I92" s="69" t="s">
         <v>399</v>
       </c>
       <c r="J92" s="16" t="s">
@@ -39136,31 +39103,29 @@
       <c r="L92" s="7">
         <v>46371</v>
       </c>
-      <c r="M92" s="69"/>
-      <c r="N92" s="70">
+      <c r="N92" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>162</v>
-      </c>
-      <c r="O92" s="71" t="str">
+        <v>161</v>
+      </c>
+      <c r="O92" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P92" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q92" s="80">
+      <c r="Q92" s="11">
         <v>46264</v>
       </c>
-      <c r="R92" s="72" t="s">
+      <c r="R92" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S92" t="s">
         <v>120</v>
       </c>
-      <c r="T92" s="69"/>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="15">
         <v>2345</v>
       </c>
@@ -39185,7 +39150,7 @@
       <c r="H93" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I93" s="79" t="s">
+      <c r="I93" s="69" t="s">
         <v>399</v>
       </c>
       <c r="J93" s="16" t="s">
@@ -39197,31 +39162,29 @@
       <c r="L93" s="7">
         <v>46371</v>
       </c>
-      <c r="M93" s="69"/>
-      <c r="N93" s="70">
+      <c r="N93" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>162</v>
-      </c>
-      <c r="O93" s="71" t="str">
+        <v>161</v>
+      </c>
+      <c r="O93" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P93" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q93" s="80">
+      <c r="Q93" s="11">
         <v>46264</v>
       </c>
-      <c r="R93" s="72" t="s">
+      <c r="R93" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S93" t="s">
         <v>120</v>
       </c>
-      <c r="T93" s="69"/>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="15">
         <v>2345</v>
       </c>
@@ -39246,7 +39209,7 @@
       <c r="H94" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I94" s="79" t="s">
+      <c r="I94" s="69" t="s">
         <v>400</v>
       </c>
       <c r="J94" s="16" t="s">
@@ -39258,31 +39221,29 @@
       <c r="L94" s="7">
         <v>46371</v>
       </c>
-      <c r="M94" s="69"/>
-      <c r="N94" s="70">
+      <c r="N94" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>162</v>
-      </c>
-      <c r="O94" s="71" t="str">
+        <v>161</v>
+      </c>
+      <c r="O94" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P94" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q94" s="80">
+      <c r="Q94" s="11">
         <v>46264</v>
       </c>
-      <c r="R94" s="72" t="s">
+      <c r="R94" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S94" t="s">
         <v>120</v>
       </c>
-      <c r="T94" s="69"/>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="15">
         <v>2345</v>
       </c>
@@ -39307,7 +39268,7 @@
       <c r="H95" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I95" s="79" t="s">
+      <c r="I95" s="69" t="s">
         <v>400</v>
       </c>
       <c r="J95" s="16" t="s">
@@ -39319,31 +39280,29 @@
       <c r="L95" s="7">
         <v>46371</v>
       </c>
-      <c r="M95" s="69"/>
-      <c r="N95" s="70">
+      <c r="N95" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>162</v>
-      </c>
-      <c r="O95" s="71" t="str">
+        <v>161</v>
+      </c>
+      <c r="O95" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P95" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q95" s="80">
+      <c r="Q95" s="11">
         <v>46264</v>
       </c>
-      <c r="R95" s="72" t="s">
+      <c r="R95" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S95" t="s">
         <v>120</v>
       </c>
-      <c r="T95" s="69"/>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="15">
         <v>2345</v>
       </c>
@@ -39368,7 +39327,7 @@
       <c r="H96" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I96" s="79" t="s">
+      <c r="I96" s="69" t="s">
         <v>401</v>
       </c>
       <c r="J96" s="16" t="s">
@@ -39380,35 +39339,33 @@
       <c r="L96" s="7">
         <v>46371</v>
       </c>
-      <c r="M96" s="69"/>
-      <c r="N96" s="70">
+      <c r="N96" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>162</v>
-      </c>
-      <c r="O96" s="71" t="str">
+        <v>161</v>
+      </c>
+      <c r="O96" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P96" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q96" s="80">
+      <c r="Q96" s="11">
         <v>46264</v>
       </c>
-      <c r="R96" s="72" t="s">
+      <c r="R96" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S96" t="s">
         <v>120</v>
       </c>
-      <c r="T96" s="69"/>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="15">
         <v>2345</v>
       </c>
-      <c r="B97" s="73">
+      <c r="B97" s="15">
         <v>9</v>
       </c>
       <c r="C97" s="15" t="s">
@@ -39420,7 +39377,7 @@
       <c r="E97" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F97" s="74">
+      <c r="F97" s="14">
         <v>36</v>
       </c>
       <c r="G97" s="14" t="s">
@@ -39429,7 +39386,7 @@
       <c r="H97" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="I97" s="79" t="s">
+      <c r="I97" s="69" t="s">
         <v>402</v>
       </c>
       <c r="J97" s="16" t="s">
@@ -39441,31 +39398,29 @@
       <c r="L97" s="7">
         <v>46371</v>
       </c>
-      <c r="M97" s="75"/>
-      <c r="N97" s="76">
+      <c r="N97" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>162</v>
-      </c>
-      <c r="O97" s="77" t="str">
+        <v>161</v>
+      </c>
+      <c r="O97" t="str">
         <f t="shared" ca="1" si="12"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P97" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q97" s="80">
+      <c r="Q97" s="11">
         <v>46264</v>
       </c>
-      <c r="R97" s="78" t="s">
+      <c r="R97" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S97" t="s">
         <v>120</v>
       </c>
-      <c r="T97" s="75"/>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="15">
         <v>2348</v>
       </c>
@@ -39481,16 +39436,16 @@
       <c r="E98" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="F98" s="81">
+      <c r="F98" s="70">
         <v>2</v>
       </c>
-      <c r="G98" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H98" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I98" s="79" t="s">
+      <c r="G98" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H98" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I98" s="69" t="s">
         <v>404</v>
       </c>
       <c r="J98" s="16" t="s">
@@ -39502,31 +39457,29 @@
       <c r="L98" s="7">
         <v>46325</v>
       </c>
-      <c r="M98" s="69"/>
-      <c r="N98" s="70">
+      <c r="N98" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
-      </c>
-      <c r="O98" s="71" t="str">
+        <v>115</v>
+      </c>
+      <c r="O98" t="str">
         <f t="shared" ref="O98:O103" ca="1" si="13">IF(N98&lt;0,"ATRASADO",IF(N98&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
         <v>NO PRAZO</v>
       </c>
       <c r="P98" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q98" s="80">
+      <c r="Q98" s="11">
         <v>46264</v>
       </c>
-      <c r="R98" s="78" t="s">
+      <c r="R98" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S98" t="s">
         <v>120</v>
       </c>
-      <c r="T98" s="69"/>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="15">
         <v>2348</v>
       </c>
@@ -39542,16 +39495,16 @@
       <c r="E99" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="F99" s="81">
+      <c r="F99" s="70">
         <v>2</v>
       </c>
-      <c r="G99" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H99" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I99" s="79" t="s">
+      <c r="G99" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H99" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I99" s="69" t="s">
         <v>404</v>
       </c>
       <c r="J99" s="16" t="s">
@@ -39563,31 +39516,29 @@
       <c r="L99" s="7">
         <v>46325</v>
       </c>
-      <c r="M99" s="69"/>
-      <c r="N99" s="70">
+      <c r="N99" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
-      </c>
-      <c r="O99" s="71" t="str">
+        <v>115</v>
+      </c>
+      <c r="O99" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P99" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q99" s="80">
+      <c r="Q99" s="11">
         <v>46264</v>
       </c>
-      <c r="R99" s="78" t="s">
+      <c r="R99" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S99" t="s">
         <v>120</v>
       </c>
-      <c r="T99" s="69"/>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="15">
         <v>2348</v>
       </c>
@@ -39603,16 +39554,16 @@
       <c r="E100" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="F100" s="81">
+      <c r="F100" s="70">
         <v>2</v>
       </c>
-      <c r="G100" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H100" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I100" s="79" t="s">
+      <c r="G100" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H100" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I100" s="69" t="s">
         <v>404</v>
       </c>
       <c r="J100" s="16" t="s">
@@ -39624,31 +39575,29 @@
       <c r="L100" s="7">
         <v>46325</v>
       </c>
-      <c r="M100" s="69"/>
-      <c r="N100" s="70">
+      <c r="N100" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
-      </c>
-      <c r="O100" s="71" t="str">
+        <v>115</v>
+      </c>
+      <c r="O100" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P100" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q100" s="80">
+      <c r="Q100" s="11">
         <v>46264</v>
       </c>
-      <c r="R100" s="78" t="s">
+      <c r="R100" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S100" t="s">
         <v>120</v>
       </c>
-      <c r="T100" s="69"/>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="15">
         <v>2348</v>
       </c>
@@ -39664,16 +39613,16 @@
       <c r="E101" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="F101" s="81">
-        <v>1</v>
-      </c>
-      <c r="G101" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H101" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I101" s="79" t="s">
+      <c r="F101" s="70">
+        <v>1</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H101" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I101" s="69" t="s">
         <v>405</v>
       </c>
       <c r="J101" s="16" t="s">
@@ -39685,31 +39634,29 @@
       <c r="L101" s="7">
         <v>46325</v>
       </c>
-      <c r="M101" s="69"/>
-      <c r="N101" s="70">
+      <c r="N101" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
-      </c>
-      <c r="O101" s="71" t="str">
+        <v>115</v>
+      </c>
+      <c r="O101" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P101" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q101" s="80">
+      <c r="Q101" s="11">
         <v>46264</v>
       </c>
-      <c r="R101" s="78" t="s">
+      <c r="R101" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S101" t="s">
         <v>120</v>
       </c>
-      <c r="T101" s="69"/>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="15">
         <v>2348</v>
       </c>
@@ -39725,16 +39672,16 @@
       <c r="E102" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="F102" s="81">
-        <v>1</v>
-      </c>
-      <c r="G102" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H102" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I102" s="79" t="s">
+      <c r="F102" s="70">
+        <v>1</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I102" s="69" t="s">
         <v>405</v>
       </c>
       <c r="J102" s="16" t="s">
@@ -39746,35 +39693,33 @@
       <c r="L102" s="7">
         <v>46325</v>
       </c>
-      <c r="M102" s="69"/>
-      <c r="N102" s="70">
+      <c r="N102" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
-      </c>
-      <c r="O102" s="71" t="str">
+        <v>115</v>
+      </c>
+      <c r="O102" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P102" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q102" s="80">
+      <c r="Q102" s="11">
         <v>46264</v>
       </c>
-      <c r="R102" s="78" t="s">
+      <c r="R102" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S102" t="s">
         <v>120</v>
       </c>
-      <c r="T102" s="69"/>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="15">
         <v>2348</v>
       </c>
-      <c r="B103" s="73">
+      <c r="B103" s="15">
         <v>14</v>
       </c>
       <c r="C103" s="15" t="s">
@@ -39786,16 +39731,16 @@
       <c r="E103" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="F103" s="81">
+      <c r="F103" s="70">
         <v>8</v>
       </c>
-      <c r="G103" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H103" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I103" s="79" t="s">
+      <c r="G103" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H103" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I103" s="69" t="s">
         <v>403</v>
       </c>
       <c r="J103" s="16" t="s">
@@ -39807,56 +39752,54 @@
       <c r="L103" s="7">
         <v>46325</v>
       </c>
-      <c r="M103" s="75"/>
-      <c r="N103" s="76">
+      <c r="N103" s="13">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>116</v>
-      </c>
-      <c r="O103" s="77" t="str">
+        <v>115</v>
+      </c>
+      <c r="O103" t="str">
         <f t="shared" ca="1" si="13"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P103" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q103" s="80">
+      <c r="Q103" s="11">
         <v>46264</v>
       </c>
-      <c r="R103" s="78" t="s">
+      <c r="R103" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S103" t="s">
         <v>120</v>
       </c>
-      <c r="T103" s="75"/>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="15">
         <v>2349</v>
       </c>
-      <c r="B104" s="83">
+      <c r="B104" s="71">
         <v>6</v>
       </c>
-      <c r="C104" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D104" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E104" s="85" t="s">
+      <c r="C104" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D104" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E104" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F104" s="86">
-        <v>1</v>
-      </c>
-      <c r="G104" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H104" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I104" s="87" t="s">
+      <c r="F104" s="74">
+        <v>1</v>
+      </c>
+      <c r="G104" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I104" s="75" t="s">
         <v>409</v>
       </c>
       <c r="J104" s="16" t="s">
@@ -39865,59 +39808,58 @@
       <c r="K104" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L104" s="88">
+      <c r="L104" s="76">
         <v>46356</v>
       </c>
-      <c r="M104" s="89"/>
-      <c r="N104" s="90">
+      <c r="M104" s="77"/>
+      <c r="N104" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O104" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O104" s="77" t="str">
         <f t="shared" ref="O104:O123" ca="1" si="14">IF(N104&lt;0,"ATRASADO",IF(N104&lt;=15,"ATENÇÃO","NO PRAZO"))</f>
         <v>NO PRAZO</v>
       </c>
       <c r="P104" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q104" s="80">
+      <c r="Q104" s="11">
         <v>46264</v>
       </c>
-      <c r="R104" s="78" t="s">
+      <c r="R104" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S104" t="s">
         <v>120</v>
       </c>
-      <c r="T104" s="69"/>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="15">
         <v>2349</v>
       </c>
-      <c r="B105" s="83">
+      <c r="B105" s="71">
         <v>7</v>
       </c>
-      <c r="C105" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D105" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E105" s="85" t="s">
+      <c r="C105" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D105" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E105" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F105" s="86">
-        <v>1</v>
-      </c>
-      <c r="G105" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H105" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I105" s="87" t="s">
+      <c r="F105" s="74">
+        <v>1</v>
+      </c>
+      <c r="G105" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H105" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I105" s="75" t="s">
         <v>409</v>
       </c>
       <c r="J105" s="16" t="s">
@@ -39926,59 +39868,58 @@
       <c r="K105" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L105" s="88">
+      <c r="L105" s="76">
         <v>46356</v>
       </c>
-      <c r="M105" s="89"/>
-      <c r="N105" s="90">
+      <c r="M105" s="77"/>
+      <c r="N105" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O105" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O105" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P105" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q105" s="80">
+      <c r="Q105" s="11">
         <v>46264</v>
       </c>
-      <c r="R105" s="78" t="s">
+      <c r="R105" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S105" t="s">
         <v>120</v>
       </c>
-      <c r="T105" s="69"/>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="15">
         <v>2349</v>
       </c>
-      <c r="B106" s="83">
+      <c r="B106" s="71">
         <v>8</v>
       </c>
-      <c r="C106" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D106" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E106" s="85" t="s">
+      <c r="C106" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D106" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E106" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F106" s="86">
-        <v>1</v>
-      </c>
-      <c r="G106" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H106" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I106" s="87" t="s">
+      <c r="F106" s="74">
+        <v>1</v>
+      </c>
+      <c r="G106" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H106" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I106" s="75" t="s">
         <v>409</v>
       </c>
       <c r="J106" s="16" t="s">
@@ -39987,59 +39928,58 @@
       <c r="K106" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L106" s="88">
+      <c r="L106" s="76">
         <v>46356</v>
       </c>
-      <c r="M106" s="89"/>
-      <c r="N106" s="90">
+      <c r="M106" s="77"/>
+      <c r="N106" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O106" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O106" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P106" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q106" s="80">
+      <c r="Q106" s="11">
         <v>46264</v>
       </c>
-      <c r="R106" s="78" t="s">
+      <c r="R106" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S106" t="s">
         <v>120</v>
       </c>
-      <c r="T106" s="69"/>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="15">
         <v>2349</v>
       </c>
-      <c r="B107" s="83">
+      <c r="B107" s="71">
         <v>9</v>
       </c>
-      <c r="C107" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D107" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E107" s="85" t="s">
+      <c r="C107" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D107" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E107" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F107" s="86">
-        <v>1</v>
-      </c>
-      <c r="G107" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H107" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I107" s="87" t="s">
+      <c r="F107" s="74">
+        <v>1</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H107" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107" s="75" t="s">
         <v>409</v>
       </c>
       <c r="J107" s="16" t="s">
@@ -40048,255 +39988,250 @@
       <c r="K107" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L107" s="88">
+      <c r="L107" s="76">
         <v>46356</v>
       </c>
-      <c r="M107" s="89"/>
-      <c r="N107" s="90">
+      <c r="M107" s="77"/>
+      <c r="N107" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O107" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O107" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P107" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q107" s="80">
+      <c r="Q107" s="11">
         <v>46264</v>
       </c>
-      <c r="R107" s="78" t="s">
+      <c r="R107" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S107" t="s">
         <v>120</v>
       </c>
-      <c r="T107" s="69"/>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="15">
         <v>2349</v>
       </c>
-      <c r="B108" s="83">
+      <c r="B108" s="71">
         <v>10</v>
       </c>
-      <c r="C108" s="84"/>
-      <c r="D108" s="84"/>
-      <c r="E108" s="85" t="s">
+      <c r="C108" s="72"/>
+      <c r="D108" s="72"/>
+      <c r="E108" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F108" s="86">
-        <v>1</v>
-      </c>
-      <c r="G108" s="82"/>
-      <c r="H108" s="82"/>
-      <c r="I108" s="87" t="s">
+      <c r="F108" s="74">
+        <v>1</v>
+      </c>
+      <c r="G108" s="14"/>
+      <c r="H108" s="14"/>
+      <c r="I108" s="75" t="s">
         <v>410</v>
       </c>
-      <c r="J108" s="88"/>
-      <c r="K108" s="89"/>
-      <c r="L108" s="88">
+      <c r="J108" s="76"/>
+      <c r="K108" s="77"/>
+      <c r="L108" s="76">
         <v>46356</v>
       </c>
-      <c r="M108" s="89"/>
-      <c r="N108" s="90">
+      <c r="M108" s="77"/>
+      <c r="N108" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O108" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O108" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P108" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q108" s="80">
+      <c r="Q108" s="11">
         <v>46264</v>
       </c>
-      <c r="R108" s="78" t="s">
+      <c r="R108" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S108" t="s">
         <v>61</v>
       </c>
-      <c r="T108" s="69"/>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="15">
         <v>2349</v>
       </c>
-      <c r="B109" s="83">
+      <c r="B109" s="71">
         <v>11</v>
       </c>
-      <c r="C109" s="84"/>
-      <c r="D109" s="84"/>
-      <c r="E109" s="85" t="s">
+      <c r="C109" s="72"/>
+      <c r="D109" s="72"/>
+      <c r="E109" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F109" s="86">
-        <v>1</v>
-      </c>
-      <c r="G109" s="82"/>
-      <c r="H109" s="82"/>
-      <c r="I109" s="87" t="s">
+      <c r="F109" s="74">
+        <v>1</v>
+      </c>
+      <c r="G109" s="14"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="75" t="s">
         <v>410</v>
       </c>
-      <c r="J109" s="88"/>
-      <c r="K109" s="89"/>
-      <c r="L109" s="88">
+      <c r="J109" s="76"/>
+      <c r="K109" s="77"/>
+      <c r="L109" s="76">
         <v>46356</v>
       </c>
-      <c r="M109" s="89"/>
-      <c r="N109" s="90">
+      <c r="M109" s="77"/>
+      <c r="N109" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O109" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O109" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P109" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q109" s="80">
+      <c r="Q109" s="11">
         <v>46264</v>
       </c>
-      <c r="R109" s="78" t="s">
+      <c r="R109" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S109" t="s">
         <v>61</v>
       </c>
-      <c r="T109" s="69"/>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="15">
         <v>2349</v>
       </c>
-      <c r="B110" s="83">
+      <c r="B110" s="71">
         <v>12</v>
       </c>
-      <c r="C110" s="84"/>
-      <c r="D110" s="84"/>
-      <c r="E110" s="85" t="s">
+      <c r="C110" s="72"/>
+      <c r="D110" s="72"/>
+      <c r="E110" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F110" s="86">
-        <v>1</v>
-      </c>
-      <c r="G110" s="82"/>
-      <c r="H110" s="82"/>
-      <c r="I110" s="87" t="s">
+      <c r="F110" s="74">
+        <v>1</v>
+      </c>
+      <c r="G110" s="14"/>
+      <c r="H110" s="14"/>
+      <c r="I110" s="75" t="s">
         <v>410</v>
       </c>
-      <c r="J110" s="88"/>
-      <c r="K110" s="89"/>
-      <c r="L110" s="88">
+      <c r="J110" s="76"/>
+      <c r="K110" s="77"/>
+      <c r="L110" s="76">
         <v>46356</v>
       </c>
-      <c r="M110" s="89"/>
-      <c r="N110" s="90">
+      <c r="M110" s="77"/>
+      <c r="N110" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O110" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O110" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P110" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q110" s="80">
+      <c r="Q110" s="11">
         <v>46264</v>
       </c>
-      <c r="R110" s="78" t="s">
+      <c r="R110" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S110" t="s">
         <v>61</v>
       </c>
-      <c r="T110" s="69"/>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="15">
         <v>2349</v>
       </c>
-      <c r="B111" s="83">
+      <c r="B111" s="71">
         <v>13</v>
       </c>
-      <c r="C111" s="84"/>
-      <c r="D111" s="84"/>
-      <c r="E111" s="85" t="s">
+      <c r="C111" s="72"/>
+      <c r="D111" s="72"/>
+      <c r="E111" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F111" s="86">
-        <v>1</v>
-      </c>
-      <c r="G111" s="82"/>
-      <c r="H111" s="82"/>
-      <c r="I111" s="87" t="s">
+      <c r="F111" s="74">
+        <v>1</v>
+      </c>
+      <c r="G111" s="14"/>
+      <c r="H111" s="14"/>
+      <c r="I111" s="75" t="s">
         <v>410</v>
       </c>
-      <c r="J111" s="88"/>
-      <c r="K111" s="89"/>
-      <c r="L111" s="88">
+      <c r="J111" s="76"/>
+      <c r="K111" s="77"/>
+      <c r="L111" s="76">
         <v>46356</v>
       </c>
-      <c r="M111" s="89"/>
-      <c r="N111" s="90">
+      <c r="M111" s="77"/>
+      <c r="N111" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O111" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O111" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P111" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q111" s="80">
+      <c r="Q111" s="11">
         <v>46264</v>
       </c>
-      <c r="R111" s="78" t="s">
+      <c r="R111" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S111" t="s">
         <v>61</v>
       </c>
-      <c r="T111" s="69"/>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="15">
         <v>2349</v>
       </c>
-      <c r="B112" s="83">
+      <c r="B112" s="71">
         <v>14</v>
       </c>
-      <c r="C112" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D112" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E112" s="85" t="s">
+      <c r="C112" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D112" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E112" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F112" s="86">
-        <v>1</v>
-      </c>
-      <c r="G112" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H112" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I112" s="87" t="s">
+      <c r="F112" s="74">
+        <v>1</v>
+      </c>
+      <c r="G112" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H112" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I112" s="75" t="s">
         <v>407</v>
       </c>
       <c r="J112" s="16" t="s">
@@ -40305,59 +40240,58 @@
       <c r="K112" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L112" s="88">
+      <c r="L112" s="76">
         <v>46356</v>
       </c>
-      <c r="M112" s="89"/>
-      <c r="N112" s="90">
+      <c r="M112" s="77"/>
+      <c r="N112" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O112" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O112" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P112" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q112" s="80">
+      <c r="Q112" s="11">
         <v>46264</v>
       </c>
-      <c r="R112" s="78" t="s">
+      <c r="R112" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S112" t="s">
         <v>120</v>
       </c>
-      <c r="T112" s="69"/>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="15">
         <v>2349</v>
       </c>
-      <c r="B113" s="83">
+      <c r="B113" s="71">
         <v>15</v>
       </c>
-      <c r="C113" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D113" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E113" s="85" t="s">
+      <c r="C113" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D113" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E113" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F113" s="86">
-        <v>1</v>
-      </c>
-      <c r="G113" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H113" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I113" s="87" t="s">
+      <c r="F113" s="74">
+        <v>1</v>
+      </c>
+      <c r="G113" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H113" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I113" s="75" t="s">
         <v>407</v>
       </c>
       <c r="J113" s="16" t="s">
@@ -40366,59 +40300,58 @@
       <c r="K113" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L113" s="88">
+      <c r="L113" s="76">
         <v>46356</v>
       </c>
-      <c r="M113" s="89"/>
-      <c r="N113" s="90">
+      <c r="M113" s="77"/>
+      <c r="N113" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O113" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O113" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P113" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q113" s="80">
+      <c r="Q113" s="11">
         <v>46264</v>
       </c>
-      <c r="R113" s="78" t="s">
+      <c r="R113" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S113" t="s">
         <v>120</v>
       </c>
-      <c r="T113" s="69"/>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="15">
         <v>2349</v>
       </c>
-      <c r="B114" s="83">
+      <c r="B114" s="71">
         <v>16</v>
       </c>
-      <c r="C114" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D114" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E114" s="85" t="s">
+      <c r="C114" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D114" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E114" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F114" s="86">
-        <v>1</v>
-      </c>
-      <c r="G114" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H114" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I114" s="87" t="s">
+      <c r="F114" s="74">
+        <v>1</v>
+      </c>
+      <c r="G114" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H114" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I114" s="75" t="s">
         <v>407</v>
       </c>
       <c r="J114" s="16" t="s">
@@ -40427,59 +40360,58 @@
       <c r="K114" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L114" s="88">
+      <c r="L114" s="76">
         <v>46356</v>
       </c>
-      <c r="M114" s="89"/>
-      <c r="N114" s="90">
+      <c r="M114" s="77"/>
+      <c r="N114" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O114" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O114" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P114" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q114" s="80">
+      <c r="Q114" s="11">
         <v>46264</v>
       </c>
-      <c r="R114" s="78" t="s">
+      <c r="R114" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S114" t="s">
         <v>120</v>
       </c>
-      <c r="T114" s="69"/>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="15">
         <v>2349</v>
       </c>
-      <c r="B115" s="83">
+      <c r="B115" s="71">
         <v>17</v>
       </c>
-      <c r="C115" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D115" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E115" s="85" t="s">
+      <c r="C115" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D115" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E115" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F115" s="86">
-        <v>1</v>
-      </c>
-      <c r="G115" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H115" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I115" s="87" t="s">
+      <c r="F115" s="74">
+        <v>1</v>
+      </c>
+      <c r="G115" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H115" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I115" s="75" t="s">
         <v>407</v>
       </c>
       <c r="J115" s="16" t="s">
@@ -40488,59 +40420,58 @@
       <c r="K115" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L115" s="88">
+      <c r="L115" s="76">
         <v>46356</v>
       </c>
-      <c r="M115" s="89"/>
-      <c r="N115" s="90">
+      <c r="M115" s="77"/>
+      <c r="N115" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O115" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O115" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P115" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q115" s="80">
+      <c r="Q115" s="11">
         <v>46264</v>
       </c>
-      <c r="R115" s="78" t="s">
+      <c r="R115" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S115" t="s">
         <v>120</v>
       </c>
-      <c r="T115" s="69"/>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="15">
         <v>2349</v>
       </c>
-      <c r="B116" s="83">
+      <c r="B116" s="71">
         <v>18</v>
       </c>
-      <c r="C116" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D116" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E116" s="85" t="s">
+      <c r="C116" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D116" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E116" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F116" s="86">
-        <v>1</v>
-      </c>
-      <c r="G116" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H116" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I116" s="87" t="s">
+      <c r="F116" s="74">
+        <v>1</v>
+      </c>
+      <c r="G116" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H116" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I116" s="75" t="s">
         <v>407</v>
       </c>
       <c r="J116" s="16" t="s">
@@ -40549,59 +40480,58 @@
       <c r="K116" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L116" s="88">
+      <c r="L116" s="76">
         <v>46356</v>
       </c>
-      <c r="M116" s="89"/>
-      <c r="N116" s="90">
+      <c r="M116" s="77"/>
+      <c r="N116" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O116" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O116" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P116" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q116" s="80">
+      <c r="Q116" s="11">
         <v>46264</v>
       </c>
-      <c r="R116" s="78" t="s">
+      <c r="R116" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S116" t="s">
         <v>120</v>
       </c>
-      <c r="T116" s="69"/>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="15">
         <v>2349</v>
       </c>
-      <c r="B117" s="83">
+      <c r="B117" s="71">
         <v>19</v>
       </c>
-      <c r="C117" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D117" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E117" s="85" t="s">
+      <c r="C117" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D117" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E117" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F117" s="86">
-        <v>1</v>
-      </c>
-      <c r="G117" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H117" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I117" s="87" t="s">
+      <c r="F117" s="74">
+        <v>1</v>
+      </c>
+      <c r="G117" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H117" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I117" s="75" t="s">
         <v>407</v>
       </c>
       <c r="J117" s="16" t="s">
@@ -40610,59 +40540,58 @@
       <c r="K117" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L117" s="88">
+      <c r="L117" s="76">
         <v>46356</v>
       </c>
-      <c r="M117" s="89"/>
-      <c r="N117" s="90">
+      <c r="M117" s="77"/>
+      <c r="N117" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O117" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O117" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P117" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q117" s="80">
+      <c r="Q117" s="11">
         <v>46264</v>
       </c>
-      <c r="R117" s="78" t="s">
+      <c r="R117" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S117" t="s">
         <v>120</v>
       </c>
-      <c r="T117" s="69"/>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="15">
         <v>2349</v>
       </c>
-      <c r="B118" s="83">
+      <c r="B118" s="71">
         <v>20</v>
       </c>
-      <c r="C118" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D118" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E118" s="85" t="s">
+      <c r="C118" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D118" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E118" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F118" s="86">
-        <v>1</v>
-      </c>
-      <c r="G118" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H118" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I118" s="87" t="s">
+      <c r="F118" s="74">
+        <v>1</v>
+      </c>
+      <c r="G118" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H118" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I118" s="75" t="s">
         <v>407</v>
       </c>
       <c r="J118" s="16" t="s">
@@ -40671,59 +40600,58 @@
       <c r="K118" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L118" s="88">
+      <c r="L118" s="76">
         <v>46356</v>
       </c>
-      <c r="M118" s="89"/>
-      <c r="N118" s="90">
+      <c r="M118" s="77"/>
+      <c r="N118" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O118" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O118" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P118" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q118" s="80">
+      <c r="Q118" s="11">
         <v>46264</v>
       </c>
-      <c r="R118" s="78" t="s">
+      <c r="R118" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S118" t="s">
         <v>120</v>
       </c>
-      <c r="T118" s="69"/>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="15">
         <v>2349</v>
       </c>
-      <c r="B119" s="83">
+      <c r="B119" s="71">
         <v>21</v>
       </c>
-      <c r="C119" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D119" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E119" s="85" t="s">
+      <c r="C119" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D119" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E119" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F119" s="86">
-        <v>1</v>
-      </c>
-      <c r="G119" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H119" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I119" s="87" t="s">
+      <c r="F119" s="74">
+        <v>1</v>
+      </c>
+      <c r="G119" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H119" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I119" s="75" t="s">
         <v>407</v>
       </c>
       <c r="J119" s="16" t="s">
@@ -40732,59 +40660,58 @@
       <c r="K119" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L119" s="88">
+      <c r="L119" s="76">
         <v>46356</v>
       </c>
-      <c r="M119" s="89"/>
-      <c r="N119" s="90">
+      <c r="M119" s="77"/>
+      <c r="N119" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O119" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O119" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P119" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q119" s="80">
+      <c r="Q119" s="11">
         <v>46264</v>
       </c>
-      <c r="R119" s="78" t="s">
+      <c r="R119" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S119" t="s">
         <v>120</v>
       </c>
-      <c r="T119" s="69"/>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="15">
         <v>2349</v>
       </c>
-      <c r="B120" s="83">
+      <c r="B120" s="71">
         <v>23</v>
       </c>
-      <c r="C120" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D120" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E120" s="85" t="s">
+      <c r="C120" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D120" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E120" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F120" s="86">
-        <v>1</v>
-      </c>
-      <c r="G120" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H120" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I120" s="87" t="s">
+      <c r="F120" s="74">
+        <v>1</v>
+      </c>
+      <c r="G120" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H120" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I120" s="75" t="s">
         <v>408</v>
       </c>
       <c r="J120" s="16" t="s">
@@ -40793,59 +40720,58 @@
       <c r="K120" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L120" s="88">
+      <c r="L120" s="76">
         <v>46356</v>
       </c>
-      <c r="M120" s="89"/>
-      <c r="N120" s="90">
+      <c r="M120" s="77"/>
+      <c r="N120" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O120" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O120" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P120" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q120" s="80">
+      <c r="Q120" s="11">
         <v>46264</v>
       </c>
-      <c r="R120" s="78" t="s">
+      <c r="R120" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S120" t="s">
         <v>120</v>
       </c>
-      <c r="T120" s="69"/>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="15">
         <v>2349</v>
       </c>
-      <c r="B121" s="83">
+      <c r="B121" s="71">
         <v>24</v>
       </c>
-      <c r="C121" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D121" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E121" s="85" t="s">
+      <c r="C121" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D121" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E121" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F121" s="86">
-        <v>1</v>
-      </c>
-      <c r="G121" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H121" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I121" s="87" t="s">
+      <c r="F121" s="74">
+        <v>1</v>
+      </c>
+      <c r="G121" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H121" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I121" s="75" t="s">
         <v>408</v>
       </c>
       <c r="J121" s="16" t="s">
@@ -40854,59 +40780,58 @@
       <c r="K121" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L121" s="88">
+      <c r="L121" s="76">
         <v>46356</v>
       </c>
-      <c r="M121" s="89"/>
-      <c r="N121" s="90">
+      <c r="M121" s="77"/>
+      <c r="N121" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O121" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O121" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P121" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q121" s="80">
+      <c r="Q121" s="11">
         <v>46264</v>
       </c>
-      <c r="R121" s="78" t="s">
+      <c r="R121" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S121" t="s">
         <v>120</v>
       </c>
-      <c r="T121" s="69"/>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="15">
         <v>2349</v>
       </c>
-      <c r="B122" s="83">
+      <c r="B122" s="71">
         <v>25</v>
       </c>
-      <c r="C122" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D122" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E122" s="85" t="s">
+      <c r="C122" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D122" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E122" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F122" s="86">
-        <v>1</v>
-      </c>
-      <c r="G122" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H122" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I122" s="87" t="s">
+      <c r="F122" s="74">
+        <v>1</v>
+      </c>
+      <c r="G122" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H122" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I122" s="75" t="s">
         <v>408</v>
       </c>
       <c r="J122" s="16" t="s">
@@ -40915,59 +40840,58 @@
       <c r="K122" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L122" s="88">
+      <c r="L122" s="76">
         <v>46356</v>
       </c>
-      <c r="M122" s="89"/>
-      <c r="N122" s="90">
+      <c r="M122" s="77"/>
+      <c r="N122" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O122" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O122" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P122" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q122" s="80">
+      <c r="Q122" s="11">
         <v>46264</v>
       </c>
-      <c r="R122" s="78" t="s">
+      <c r="R122" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S122" t="s">
         <v>120</v>
       </c>
-      <c r="T122" s="69"/>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="15">
         <v>2349</v>
       </c>
-      <c r="B123" s="83">
+      <c r="B123" s="71">
         <v>26</v>
       </c>
-      <c r="C123" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="D123" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="E123" s="85" t="s">
+      <c r="C123" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D123" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="E123" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="F123" s="86">
-        <v>1</v>
-      </c>
-      <c r="G123" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="H123" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="I123" s="87" t="s">
+      <c r="F123" s="74">
+        <v>1</v>
+      </c>
+      <c r="G123" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H123" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="I123" s="75" t="s">
         <v>408</v>
       </c>
       <c r="J123" s="16" t="s">
@@ -40976,32 +40900,31 @@
       <c r="K123" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L123" s="88">
+      <c r="L123" s="76">
         <v>46356</v>
       </c>
-      <c r="M123" s="89"/>
-      <c r="N123" s="90">
+      <c r="M123" s="77"/>
+      <c r="N123" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>147</v>
-      </c>
-      <c r="O123" s="91" t="str">
+        <v>146</v>
+      </c>
+      <c r="O123" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
         <v>NO PRAZO</v>
       </c>
       <c r="P123" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q123" s="80">
+      <c r="Q123" s="11">
         <v>46264</v>
       </c>
-      <c r="R123" s="78" t="s">
+      <c r="R123" s="1" t="s">
         <v>100</v>
       </c>
       <c r="S123" t="s">
         <v>120</v>
       </c>
-      <c r="T123" s="69"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -47033,11 +46956,11 @@
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="A30:A43">
-    <cfRule type="containsText" dxfId="41" priority="50" operator="containsText" text="encamisado">
+    <cfRule type="containsText" dxfId="41" priority="51" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",A30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="50" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",A30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="51" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",A30)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="39" priority="52">
       <formula>$P30="s"</formula>
@@ -47058,88 +46981,88 @@
     <cfRule type="containsText" dxfId="35" priority="29" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",C45)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="30" operator="containsText" text="pronto">
+    <cfRule type="expression" dxfId="34" priority="31">
+      <formula>$P45="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="30" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",C45)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="31">
-      <formula>$P45="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C55:C77">
-    <cfRule type="containsText" dxfId="32" priority="25" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="26" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="32" priority="26" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",C55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="27">
+    <cfRule type="expression" dxfId="31" priority="27">
       <formula>$P55="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="25" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:D43">
     <cfRule type="containsText" dxfId="29" priority="47" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",D30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="48" operator="containsText" text="pronto">
+    <cfRule type="expression" dxfId="28" priority="49">
+      <formula>$P30="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="27" priority="48" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",D30)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="49">
-      <formula>$P30="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D77">
-    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="encamisado">
+    <cfRule type="containsText" dxfId="26" priority="22" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",D55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="21" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",D55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="22" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",D55)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="23">
       <formula>$P55="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59:G60 G67">
-    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
+    <cfRule type="expression" dxfId="23" priority="12">
+      <formula>$P59="s"</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="22" priority="10" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",G59)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="12">
-      <formula>$P59="s"</formula>
+    <cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58 H60 H62 H65:H66 H76">
-    <cfRule type="containsText" dxfId="20" priority="13" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="14" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="20" priority="14" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",H58)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="16">
+    <cfRule type="expression" dxfId="19" priority="16">
       <formula>$P58="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:N45">
     <cfRule type="containsText" dxfId="17" priority="41" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",N33)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="42" operator="containsText" text="pronto">
+    <cfRule type="expression" dxfId="16" priority="43">
+      <formula>$P33="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="42" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",N33)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="43">
-      <formula>$P33="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N55:N77">
     <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",N55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="pronto">
+    <cfRule type="expression" dxfId="13" priority="7">
+      <formula>$P55="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",N55)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="7">
-      <formula>$P55="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O33:O35">
@@ -47176,14 +47099,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB55:AB77">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",AB55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$P55="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -50053,13 +49976,17 @@
       <c r="L4" s="25">
         <v>46202</v>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="25">
+        <v>46205</v>
+      </c>
       <c r="N4" s="25">
         <v>46209</v>
       </c>
-      <c r="O4" s="25"/>
+      <c r="O4" s="25">
+        <v>46206</v>
+      </c>
       <c r="P4" s="25" t="s">
-        <v>61</v>
+        <v>413</v>
       </c>
       <c r="Q4" s="23">
         <v>496</v>
@@ -50103,9 +50030,11 @@
       <c r="L5" s="25">
         <v>46202</v>
       </c>
-      <c r="M5" s="25"/>
+      <c r="M5" s="25">
+        <v>46209</v>
+      </c>
       <c r="N5" s="25">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="O5" s="25"/>
       <c r="P5" s="25" t="s">
@@ -50145,7 +50074,7 @@
         <v>46196</v>
       </c>
       <c r="J6" s="25">
-        <v>46199</v>
+        <v>46219</v>
       </c>
       <c r="K6" s="25"/>
       <c r="L6" s="25" t="s">
@@ -50161,12 +50090,14 @@
         <v>77</v>
       </c>
       <c r="P6" s="25" t="s">
-        <v>232</v>
+        <v>414</v>
       </c>
       <c r="Q6" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="R6" s="50"/>
+      <c r="R6" s="50" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="47">
@@ -50197,9 +50128,11 @@
         <v>46196</v>
       </c>
       <c r="J7" s="25">
-        <v>46199</v>
-      </c>
-      <c r="K7" s="25"/>
+        <v>46219</v>
+      </c>
+      <c r="K7" s="25">
+        <v>46206</v>
+      </c>
       <c r="L7" s="25" t="s">
         <v>77</v>
       </c>
@@ -50249,9 +50182,11 @@
         <v>46196</v>
       </c>
       <c r="J8" s="25">
-        <v>46199</v>
-      </c>
-      <c r="K8" s="25"/>
+        <v>46219</v>
+      </c>
+      <c r="K8" s="25">
+        <v>46206</v>
+      </c>
       <c r="L8" s="25" t="s">
         <v>77</v>
       </c>
@@ -50301,9 +50236,11 @@
         <v>46196</v>
       </c>
       <c r="J9" s="25">
-        <v>46199</v>
-      </c>
-      <c r="K9" s="25"/>
+        <v>46219</v>
+      </c>
+      <c r="K9" s="25">
+        <v>46206</v>
+      </c>
       <c r="L9" s="25" t="s">
         <v>77</v>
       </c>
@@ -50353,9 +50290,11 @@
         <v>46196</v>
       </c>
       <c r="J10" s="25">
-        <v>46199</v>
-      </c>
-      <c r="K10" s="25"/>
+        <v>46219</v>
+      </c>
+      <c r="K10" s="25">
+        <v>46206</v>
+      </c>
       <c r="L10" s="25" t="s">
         <v>77</v>
       </c>
@@ -50405,9 +50344,11 @@
         <v>46196</v>
       </c>
       <c r="J11" s="25">
-        <v>46199</v>
-      </c>
-      <c r="K11" s="25"/>
+        <v>46219</v>
+      </c>
+      <c r="K11" s="25">
+        <v>46206</v>
+      </c>
       <c r="L11" s="25" t="s">
         <v>77</v>
       </c>
@@ -50457,9 +50398,11 @@
         <v>46196</v>
       </c>
       <c r="J12" s="25">
-        <v>46199</v>
-      </c>
-      <c r="K12" s="25"/>
+        <v>46219</v>
+      </c>
+      <c r="K12" s="25">
+        <v>46206</v>
+      </c>
       <c r="L12" s="25" t="s">
         <v>77</v>
       </c>
@@ -50509,7 +50452,7 @@
         <v>46196</v>
       </c>
       <c r="J13" s="25">
-        <v>46199</v>
+        <v>46219</v>
       </c>
       <c r="K13" s="25"/>
       <c r="L13" s="25" t="s">
@@ -50554,20 +50497,20 @@
       <c r="G14" s="65">
         <v>46211</v>
       </c>
-      <c r="H14" s="27">
-        <v>46197</v>
+      <c r="H14" s="27" t="s">
+        <v>415</v>
       </c>
       <c r="I14" s="27"/>
       <c r="J14" s="27">
-        <v>46204</v>
+        <v>46218</v>
       </c>
       <c r="K14" s="27"/>
       <c r="L14" s="27">
-        <v>46211</v>
+        <v>46232</v>
       </c>
       <c r="M14" s="27"/>
       <c r="N14" s="27">
-        <v>46218</v>
+        <v>46236</v>
       </c>
       <c r="O14" s="27"/>
       <c r="P14" s="25" t="s">
@@ -50653,11 +50596,15 @@
       <c r="H16" s="25">
         <v>46189</v>
       </c>
-      <c r="I16" s="25"/>
+      <c r="I16" s="25">
+        <v>46189</v>
+      </c>
       <c r="J16" s="25">
         <v>46199</v>
       </c>
-      <c r="K16" s="25"/>
+      <c r="K16" s="25">
+        <v>46199</v>
+      </c>
       <c r="L16" s="25" t="s">
         <v>77</v>
       </c>
@@ -50671,7 +50618,7 @@
         <v>77</v>
       </c>
       <c r="P16" s="25" t="s">
-        <v>61</v>
+        <v>413</v>
       </c>
       <c r="Q16" s="23">
         <v>496</v>
@@ -50701,19 +50648,19 @@
         <v>46218</v>
       </c>
       <c r="H17" s="25">
-        <v>46204</v>
+        <v>46219</v>
       </c>
       <c r="I17" s="25"/>
       <c r="J17" s="68">
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="K17" s="25"/>
       <c r="L17" s="25">
-        <v>46218</v>
+        <v>46237</v>
       </c>
       <c r="M17" s="25"/>
       <c r="N17" s="25">
-        <v>46225</v>
+        <v>46241</v>
       </c>
       <c r="O17" s="25"/>
       <c r="P17" s="25" t="s">
@@ -50751,7 +50698,7 @@
       </c>
       <c r="I18" s="25"/>
       <c r="J18" s="25">
-        <v>46206</v>
+        <v>46220</v>
       </c>
       <c r="K18" s="25"/>
       <c r="L18" s="25" t="s">
@@ -51296,7 +51243,7 @@
       <c r="G29" s="25">
         <v>46246</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="80">
         <v>46213</v>
       </c>
       <c r="I29" s="25"/>
@@ -51346,7 +51293,7 @@
       <c r="G30" s="25">
         <v>46246</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="80">
         <v>46213</v>
       </c>
       <c r="I30" s="25"/>
@@ -51396,7 +51343,7 @@
       <c r="G31" s="25">
         <v>46246</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="80">
         <v>46213</v>
       </c>
       <c r="I31" s="25"/>
@@ -51446,7 +51393,7 @@
       <c r="G32" s="25">
         <v>46253</v>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="80">
         <v>46213</v>
       </c>
       <c r="I32" s="27"/>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB854C81-6B01-4AF6-AAB2-0AF41CD41F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094AC9D9-1AAE-4A1C-AB74-2208A1716180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <sheet name="PLANEJADO BAGACEIRA" sheetId="5" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'VI DIVERSOS'!$A$1:$N$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'VI DIVERSOS'!$A$1:$N$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BAGACEIRAS!$A$1:$AI$113</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">BAGACEIRAS!$1:$1</definedName>
   </definedNames>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6803" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6833" uniqueCount="423">
   <si>
     <t>O.S.</t>
   </si>
@@ -1341,6 +1341,24 @@
   <si>
     <t xml:space="preserve">PRECISA RETORNAR PARA USINAGEM </t>
   </si>
+  <si>
+    <t>Sandivk</t>
+  </si>
+  <si>
+    <t>CARCAÇA  SUPERIOR CS430 C/ USIN.</t>
+  </si>
+  <si>
+    <t>285 - 327 - 112</t>
+  </si>
+  <si>
+    <t>REPOSIÇÃO METSO</t>
+  </si>
+  <si>
+    <t>Sertmax</t>
+  </si>
+  <si>
+    <t>USINAGEM ACABEMENTO CARCAÇA INF</t>
+  </si>
 </sst>
 </file>
 
@@ -1609,7 +1627,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1825,6 +1843,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4321,6 +4342,118 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF080000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -5007,118 +5140,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF080000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -5133,70 +5154,70 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="191" dataDxfId="190">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="215" dataDxfId="214">
   <autoFilter ref="A1:AI114" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}">
-    <filterColumn colId="4">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Atvos Santa Luzia"/>
+        <filter val="2203"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="35">
-    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="189"/>
-    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="188"/>
-    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="187"/>
-    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="186"/>
-    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="185"/>
-    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="184"/>
-    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="183"/>
-    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="182"/>
-    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="181"/>
-    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="180"/>
-    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="179">
+    <tableColumn id="1" xr3:uid="{2AE87B23-57FB-4D7F-8BFD-D65EC0053BA3}" name="PV" dataDxfId="213"/>
+    <tableColumn id="2" xr3:uid="{81052488-0765-4420-B185-DA73AE55FD88}" name="Item" dataDxfId="212"/>
+    <tableColumn id="3" xr3:uid="{0E7DB960-0044-4341-ADB4-2A033B27B993}" name="O.S." dataDxfId="211"/>
+    <tableColumn id="4" xr3:uid="{B0F20CBE-FFF4-445B-B0BF-7A9C6A140189}" name="Item2" dataDxfId="210"/>
+    <tableColumn id="5" xr3:uid="{D1656E30-4AB0-4CD0-BF13-6D5A49C6E4A0}" name="Cliente" dataDxfId="209"/>
+    <tableColumn id="6" xr3:uid="{71A11213-5711-429D-A6E0-A2F44677AD5D}" name="Peça" dataDxfId="208"/>
+    <tableColumn id="7" xr3:uid="{3F7FD9F6-0726-4021-82B3-E31575A97A46}" name="Seq." dataDxfId="207"/>
+    <tableColumn id="8" xr3:uid="{0D871CDA-AC7B-4365-B4FD-95C8967CF254}" name="Descrição" dataDxfId="206"/>
+    <tableColumn id="9" xr3:uid="{9C6311D3-DE8E-4A12-8716-11D7CF745EA9}" name="Qtde." dataDxfId="205"/>
+    <tableColumn id="10" xr3:uid="{0D119764-5D6A-44D7-A0C6-EAAE37326AEF}" name="Prazo_x000a_Fundido" dataDxfId="204"/>
+    <tableColumn id="20" xr3:uid="{2835FDBA-B893-4E1E-9252-D088967B6B9B}" name="Semana_x000a_Fundido" dataDxfId="203">
       <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
 Fundido]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="178"/>
-    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="177"/>
-    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="176"/>
-    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="175">
+    <tableColumn id="11" xr3:uid="{357F67DE-6B6F-4353-906F-4FBB26ED7226}" name="Pz Fundido_x000a_Real" dataDxfId="202"/>
+    <tableColumn id="12" xr3:uid="{5CF37CA2-8EC2-4A06-8A50-1305C1129D14}" name="Prazo_x000a_Entrega" dataDxfId="201"/>
+    <tableColumn id="36" xr3:uid="{903E641C-0F4A-465E-9B87-4C77A3724350}" name="Pz Entrega_x000a_Real" dataDxfId="200"/>
+    <tableColumn id="14" xr3:uid="{49E3A48F-4FBA-45ED-9BE5-0D3F2C039F64}" name="Dias_x000a_Falta2" dataDxfId="199">
       <calculatedColumnFormula>Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="174">
+    <tableColumn id="24" xr3:uid="{FE82CCB3-C196-4A10-9CDF-EC3AAB610284}" name="Indicador" dataDxfId="198">
       <calculatedColumnFormula>IF(O2&lt;0,"ATRASADO",IF(O2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="173">
+    <tableColumn id="21" xr3:uid="{0E3EA19A-D149-4026-9EFA-582C442CDE24}" name="Semana_x000a_Entrega" dataDxfId="197">
       <calculatedColumnFormula>WEEKNUM(Tabela1[[#This Row],[Prazo
 Entrega]],1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="172"/>
-    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="171"/>
-    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="170"/>
-    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="169"/>
-    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="168"/>
-    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="167"/>
-    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="166"/>
-    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="165"/>
-    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="164"/>
-    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="163"/>
-    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="162"/>
-    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="161">
+    <tableColumn id="22" xr3:uid="{8BBF8940-A612-415C-B30B-5BED69C42E59}" name="CONDIÇÃO" dataDxfId="196"/>
+    <tableColumn id="35" xr3:uid="{DF0F32C7-2632-41CB-B20E-BE67D32DDFF8}" name="Desenho_x000a_Previsão" dataDxfId="195"/>
+    <tableColumn id="33" xr3:uid="{B0C0F319-983E-42D8-8584-16523AED9BC7}" name="Des." dataDxfId="194"/>
+    <tableColumn id="32" xr3:uid="{BB84EAAB-24E7-433E-8DE8-B7705F525D65}" name="Plainar" dataDxfId="193"/>
+    <tableColumn id="31" xr3:uid="{811011C2-9E33-4F8A-BCD2-260DDF4CC060}" name="Facear" dataDxfId="192"/>
+    <tableColumn id="30" xr3:uid="{EFE986D2-325F-4223-A6FC-89AFC0782517}" name="Serrar" dataDxfId="191"/>
+    <tableColumn id="29" xr3:uid="{806CC413-43AC-4EDE-9413-A2852780B283}" name="Solda Dura" dataDxfId="190"/>
+    <tableColumn id="28" xr3:uid="{669E3B74-6C47-4551-B95C-DE764412CB09}" name="Encaixe" dataDxfId="189"/>
+    <tableColumn id="27" xr3:uid="{33B1427B-026C-4955-BEDC-C39ECFB35542}" name="Furação" dataDxfId="188"/>
+    <tableColumn id="34" xr3:uid="{2004DA6B-65E8-4CFF-8DD6-03937C8E23A7}" name="Acabam." dataDxfId="187"/>
+    <tableColumn id="25" xr3:uid="{94AD153B-B1BE-422C-9B64-A3F125946AE5}" name="Liberação" dataDxfId="186"/>
+    <tableColumn id="23" xr3:uid="{6FFD36BA-4C85-4732-ACA9-BC9D46F4C26B}" name="Status Usinagem" dataDxfId="185">
       <calculatedColumnFormula>IF(L2="","AG. FUNDIDO",IF(U2="AG","AG. USINAGEM","EM USINAGEM"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="160"/>
-    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="159"/>
-    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="158"/>
-    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="157"/>
-    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="156"/>
-    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="155"/>
+    <tableColumn id="26" xr3:uid="{DF8CD1DA-6F25-4291-9F78-DB8D5E9AF463}" name="Observação" dataDxfId="184"/>
+    <tableColumn id="15" xr3:uid="{8F53CFFE-8E1C-41F5-9090-488AE701829C}" name="Plainar_x000a_Facear" dataDxfId="183"/>
+    <tableColumn id="16" xr3:uid="{EB12A620-BA24-453B-B639-A28F83CF7950}" name="Serrar2" dataDxfId="182"/>
+    <tableColumn id="17" xr3:uid="{46D65A07-940A-4560-AFE5-056D37171937}" name="Solda_x000a_Dura2" dataDxfId="181"/>
+    <tableColumn id="18" xr3:uid="{97823986-0C6D-4D6F-9BEE-2E43C2286AB2}" name="Encaixe /_x000a_Furação" dataDxfId="180"/>
+    <tableColumn id="19" xr3:uid="{6F1924AE-480F-421A-BD70-FA16D1D4E641}" name="Acabam./_x000a_Inspeção" dataDxfId="179"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V163" totalsRowShown="0" headerRowDxfId="215" dataDxfId="214">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}" name="Tabela3" displayName="Tabela3" ref="A1:V163" totalsRowShown="0" headerRowDxfId="178" dataDxfId="177">
   <autoFilter ref="A1:V163" xr:uid="{71E71FAB-CF6D-4765-90BA-ABDE8C3299DB}">
     <filterColumn colId="4">
       <filters>
@@ -5205,39 +5226,39 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="213"/>
-    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="212"/>
-    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="211"/>
-    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="210"/>
-    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="209"/>
-    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="208"/>
-    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="207"/>
-    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="206"/>
-    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="205"/>
-    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="204"/>
-    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="203">
+    <tableColumn id="1" xr3:uid="{8F000DF9-1B1A-450A-B138-9EDBA7F17698}" name="PV" dataDxfId="176"/>
+    <tableColumn id="2" xr3:uid="{4269DD7F-E557-42AF-949B-69AB74B45D7E}" name="Item" dataDxfId="175"/>
+    <tableColumn id="3" xr3:uid="{B8E3D127-9007-43BC-9B71-611446984BAE}" name="O.S." dataDxfId="174"/>
+    <tableColumn id="4" xr3:uid="{8A9FBC4E-431D-4132-B7C4-86DD1CC31C1D}" name="Item2" dataDxfId="173"/>
+    <tableColumn id="5" xr3:uid="{E43CCBA4-A724-44DA-9BFB-2AD45322EC54}" name="Cliente" dataDxfId="172"/>
+    <tableColumn id="6" xr3:uid="{301560AA-7C28-4FE5-AC00-2A14532B12A0}" name="Peça" dataDxfId="171"/>
+    <tableColumn id="7" xr3:uid="{864BB541-5CD2-4DAB-AEC1-ADDD341A77F2}" name="Seq." dataDxfId="170"/>
+    <tableColumn id="8" xr3:uid="{39F09B1D-71EC-461C-93C5-C5FCECCA0EC0}" name="Descrição" dataDxfId="169"/>
+    <tableColumn id="9" xr3:uid="{0CC8781A-4370-473C-AD18-F562622EB79C}" name="Qtde." dataDxfId="168"/>
+    <tableColumn id="10" xr3:uid="{8FC48674-090B-441A-B05D-5E7E4AB5177C}" name="Prazo_x000a_Fundido" dataDxfId="167"/>
+    <tableColumn id="11" xr3:uid="{2B85402B-261F-4CF1-8AC4-DE439E438480}" name="Semana_x000a_Fundido" dataDxfId="166">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Fundido]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="202"/>
-    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="201"/>
-    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="200"/>
-    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="199"/>
-    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="198"/>
-    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="197">
+    <tableColumn id="12" xr3:uid="{F410DF31-AFC5-4525-B8D3-A2AB464611B3}" name="Pz Fundido_x000a_Real" dataDxfId="165"/>
+    <tableColumn id="13" xr3:uid="{7330A8B8-B0FE-4571-921F-35503842576A}" name="Prazo_x000a_Entrega" dataDxfId="164"/>
+    <tableColumn id="23" xr3:uid="{050BF892-6E0A-4C1A-85E3-06353D54D7AC}" name="Pz Entrega_x000a_Real" dataDxfId="163"/>
+    <tableColumn id="22" xr3:uid="{07396B9E-F2A0-47CC-B1C1-8D6A8D782E82}" name="Desenho_x000a_Previsão" dataDxfId="162"/>
+    <tableColumn id="14" xr3:uid="{98904960-EE6F-4F44-87C3-8646B8C2D461}" name="Des." dataDxfId="161"/>
+    <tableColumn id="15" xr3:uid="{4C38D84D-3A40-493A-A007-3826C38C0F9D}" name="Dias_x000a_Falta2" dataDxfId="160">
       <calculatedColumnFormula>Tabela3[[#This Row],[Prazo
 Entrega]]-TODAY()</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="196">
+    <tableColumn id="16" xr3:uid="{431C9D70-8530-4071-911B-7AAC65DE848C}" name="Indicador" dataDxfId="159">
       <calculatedColumnFormula>IF(Q2&lt;0,"ATRASADO",IF(Q2&lt;=15,"ATENÇÃO","NO PRAZO"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="195">
+    <tableColumn id="17" xr3:uid="{37B1BAB9-4A72-4AB5-85A7-CFF0F27D94A6}" name="Semana_x000a_Entrega" dataDxfId="158">
       <calculatedColumnFormula>WEEKNUM(Tabela3[[#This Row],[Prazo
 Entrega]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="194"/>
-    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="193"/>
-    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="192"/>
+    <tableColumn id="19" xr3:uid="{A127FC22-0D53-4D0F-B783-28394B3FD90C}" name="CONDIÇÃO" dataDxfId="157"/>
+    <tableColumn id="20" xr3:uid="{F610A49E-78E2-480E-B901-6B99A41E5174}" name="Status Usinagem" dataDxfId="156"/>
+    <tableColumn id="21" xr3:uid="{FA7288EB-0143-4C36-8591-BF7231A8226E}" name="Observação" dataDxfId="155"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5245,7 +5266,13 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6E9C3BD9-7BAA-49FB-9F98-CFD415149194}" name="Tabela13" displayName="Tabela13" ref="A1:Z39" totalsRowShown="0" headerRowDxfId="154" dataDxfId="153">
-  <autoFilter ref="A1:Z39" xr:uid="{2AC5416C-4E1B-4478-8A2A-B698870CAB96}"/>
+  <autoFilter ref="A1:Z39" xr:uid="{2AC5416C-4E1B-4478-8A2A-B698870CAB96}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="São Domingos"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{9A983B4E-3365-4153-9B40-D7FE26E8B98F}" name="PV " dataDxfId="152"/>
     <tableColumn id="2" xr3:uid="{4F16CD54-AAD4-4149-8D48-CC3FFEA93AA5}" name="Item" dataDxfId="151"/>
@@ -5957,10 +5984,10 @@
         <v>69</v>
       </c>
       <c r="AB2" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AC2" s="10" t="s">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="AE2" s="42">
         <v>24</v>
@@ -6056,13 +6083,13 @@
         <v>69</v>
       </c>
       <c r="W3" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X3" s="10" t="s">
         <v>77</v>
       </c>
       <c r="Y3" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z3" s="10" t="s">
         <v>72</v>
@@ -6177,20 +6204,19 @@
         <v>77</v>
       </c>
       <c r="Y4" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AA4" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB4" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AC4" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+      <c r="AC4" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="AE4" s="42">
         <v>24</v>
@@ -6398,7 +6424,7 @@
         <v>69</v>
       </c>
       <c r="V6" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W6" s="10" t="s">
         <v>72</v>
@@ -6883,10 +6909,10 @@
         <v>69</v>
       </c>
       <c r="AB10" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="AE10" s="42">
         <v>23</v>
@@ -7098,16 +7124,16 @@
         <v>69</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X12" s="10" t="s">
         <v>77</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Z12" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="AA12" s="10" t="s">
         <v>72</v>
@@ -7328,7 +7354,7 @@
         <v>69</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="X14" s="10" t="s">
         <v>77</v>
@@ -7694,10 +7720,10 @@
         <v>69</v>
       </c>
       <c r="AB17" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="AE17" s="42">
         <v>26</v>
@@ -7810,10 +7836,10 @@
         <v>69</v>
       </c>
       <c r="AB18" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="AE18" s="42">
         <v>26</v>
@@ -8019,7 +8045,7 @@
         <v>69</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V20" s="10" t="s">
         <v>72</v>
@@ -8044,7 +8070,7 @@
       </c>
       <c r="AC20" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE20" s="42">
         <v>26</v>
@@ -8134,7 +8160,7 @@
         <v>69</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V21" s="10" t="s">
         <v>72</v>
@@ -8159,7 +8185,7 @@
       </c>
       <c r="AC21" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE21" s="42">
         <v>26</v>
@@ -8182,7 +8208,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>2203</v>
       </c>
@@ -8249,7 +8275,7 @@
         <v>69</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="V22" s="10" t="s">
         <v>72</v>
@@ -8274,7 +8300,7 @@
       </c>
       <c r="AC22" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE22" s="42">
         <v>25</v>
@@ -8297,7 +8323,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <v>2203</v>
       </c>
@@ -8364,7 +8390,7 @@
         <v>69</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="V23" s="10" t="s">
         <v>72</v>
@@ -8389,7 +8415,7 @@
       </c>
       <c r="AC23" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE23" s="42">
         <v>25</v>
@@ -8497,14 +8523,13 @@
         <v>85</v>
       </c>
       <c r="AA24" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB24" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC24" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>69</v>
+      </c>
+      <c r="AC24" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="AE24" s="42">
         <v>25</v>
@@ -8612,14 +8637,13 @@
         <v>85</v>
       </c>
       <c r="AA25" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB25" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC25" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>69</v>
+      </c>
+      <c r="AC25" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="AE25" s="42">
         <v>25</v>
@@ -8727,14 +8751,13 @@
         <v>85</v>
       </c>
       <c r="AA26" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB26" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC26" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>69</v>
+      </c>
+      <c r="AC26" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="AE26" s="42">
         <v>25</v>
@@ -8842,14 +8865,13 @@
         <v>85</v>
       </c>
       <c r="AA27" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB27" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC27" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>69</v>
+      </c>
+      <c r="AC27" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="AE27" s="42">
         <v>25</v>
@@ -8957,14 +8979,13 @@
         <v>85</v>
       </c>
       <c r="AA28" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB28" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC28" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>69</v>
+      </c>
+      <c r="AC28" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="AE28" s="42">
         <v>25</v>
@@ -9072,14 +9093,13 @@
         <v>85</v>
       </c>
       <c r="AA29" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AB29" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC29" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>69</v>
+      </c>
+      <c r="AC29" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="AE29" s="42">
         <v>25</v>
@@ -9102,7 +9122,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
         <v>2203</v>
       </c>
@@ -9169,7 +9189,7 @@
         <v>69</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="V30" s="10" t="s">
         <v>72</v>
@@ -9194,7 +9214,7 @@
       </c>
       <c r="AC30" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>EM USINAGEM</v>
+        <v>AG. USINAGEM</v>
       </c>
       <c r="AE30" s="42">
         <v>27</v>
@@ -9307,10 +9327,10 @@
         <v>69</v>
       </c>
       <c r="AB31" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AC31" s="10" t="s">
-        <v>258</v>
+        <v>101</v>
       </c>
       <c r="AE31" s="42">
         <v>27</v>
@@ -9400,10 +9420,10 @@
         <v>69</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="V32" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W32" s="10" t="s">
         <v>72</v>
@@ -9425,7 +9445,7 @@
       </c>
       <c r="AC32" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE32" s="42">
         <v>27</v>
@@ -9518,7 +9538,7 @@
         <v>69</v>
       </c>
       <c r="V33" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="W33" s="10" t="s">
         <v>72</v>
@@ -9636,7 +9656,7 @@
         <v>69</v>
       </c>
       <c r="W34" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="X34" s="10" t="s">
         <v>77</v>
@@ -9745,10 +9765,10 @@
         <v>69</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="V35" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W35" s="10" t="s">
         <v>72</v>
@@ -9770,7 +9790,7 @@
       </c>
       <c r="AC35" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE35" s="42">
         <v>27</v>
@@ -10177,12 +10197,13 @@
 Fundido]])</f>
         <v>25</v>
       </c>
+      <c r="L39" s="11">
+        <v>46233</v>
+      </c>
       <c r="M39" s="16">
         <v>46234</v>
       </c>
-      <c r="N39" s="16">
-        <v>46206</v>
-      </c>
+      <c r="N39" s="16"/>
       <c r="O39" s="40">
         <f ca="1">Tabela1[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
@@ -10200,11 +10221,11 @@
       <c r="R39" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S39" s="41">
-        <v>46203</v>
+      <c r="S39" s="41" t="s">
+        <v>69</v>
       </c>
       <c r="T39" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U39" s="10" t="s">
         <v>72</v>
@@ -10311,11 +10332,11 @@
       <c r="R40" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S40" s="41">
-        <v>46203</v>
+      <c r="S40" s="41" t="s">
+        <v>69</v>
       </c>
       <c r="T40" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>72</v>
@@ -10426,11 +10447,11 @@
       <c r="R41" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S41" s="41">
-        <v>46203</v>
+      <c r="S41" s="41" t="s">
+        <v>69</v>
       </c>
       <c r="T41" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>72</v>
@@ -10541,11 +10562,11 @@
       <c r="R42" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S42" s="41">
-        <v>46203</v>
+      <c r="S42" s="41" t="s">
+        <v>69</v>
       </c>
       <c r="T42" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>72</v>
@@ -10656,11 +10677,11 @@
       <c r="R43" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S43" s="41">
-        <v>46203</v>
+      <c r="S43" s="41" t="s">
+        <v>69</v>
       </c>
       <c r="T43" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>72</v>
@@ -10768,11 +10789,11 @@
       <c r="R44" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="S44" s="41">
-        <v>46203</v>
+      <c r="S44" s="41" t="s">
+        <v>69</v>
       </c>
       <c r="T44" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>72</v>
@@ -10823,7 +10844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
         <v>2203</v>
       </c>
@@ -10938,7 +10959,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
         <v>2203</v>
       </c>
@@ -11053,7 +11074,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <v>2203</v>
       </c>
@@ -11120,7 +11141,7 @@
         <v>69</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="V47" s="10" t="s">
         <v>72</v>
@@ -11145,7 +11166,7 @@
       </c>
       <c r="AC47" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>AG. USINAGEM</v>
+        <v>EM USINAGEM</v>
       </c>
       <c r="AE47" s="42">
         <v>28</v>
@@ -11576,10 +11597,10 @@
         <v>69</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="V51" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W51" s="10" t="s">
         <v>72</v>
@@ -11691,10 +11712,10 @@
         <v>69</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="V52" s="10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="W52" s="10" t="s">
         <v>72</v>
@@ -15203,7 +15224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="15">
         <v>2263</v>
       </c>
@@ -15317,7 +15338,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15">
         <v>2263</v>
       </c>
@@ -15431,7 +15452,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="15">
         <v>2263</v>
       </c>
@@ -15545,7 +15566,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
         <v>2263</v>
       </c>
@@ -15659,7 +15680,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15">
         <v>2263</v>
       </c>
@@ -15773,7 +15794,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
         <v>2263</v>
       </c>
@@ -30019,7 +30040,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>2233</v>
       </c>
@@ -30096,7 +30117,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>2233</v>
       </c>
@@ -30173,7 +30194,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>2284</v>
       </c>
@@ -30250,7 +30271,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>2284</v>
       </c>
@@ -30327,7 +30348,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>2284</v>
       </c>
@@ -30404,7 +30425,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>2284</v>
       </c>
@@ -30481,7 +30502,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>2284</v>
       </c>
@@ -30558,7 +30579,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>2284</v>
       </c>
@@ -30635,7 +30656,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>2284</v>
       </c>
@@ -30712,7 +30733,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>2284</v>
       </c>
@@ -30789,7 +30810,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>2284</v>
       </c>
@@ -30866,7 +30887,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>2284</v>
       </c>
@@ -30943,7 +30964,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>2284</v>
       </c>
@@ -31020,7 +31041,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>2284</v>
       </c>
@@ -31097,7 +31118,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>2284</v>
       </c>
@@ -31174,7 +31195,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>2320</v>
       </c>
@@ -31253,7 +31274,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>2320</v>
       </c>
@@ -31332,7 +31353,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>2320</v>
       </c>
@@ -31411,7 +31432,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>2320</v>
       </c>
@@ -31490,7 +31511,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>2320</v>
       </c>
@@ -31569,7 +31590,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>2320</v>
       </c>
@@ -31648,7 +31669,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>2320</v>
       </c>
@@ -31727,7 +31748,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>2320</v>
       </c>
@@ -31806,7 +31827,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>2320</v>
       </c>
@@ -31885,7 +31906,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>1027</v>
       </c>
@@ -31962,7 +31983,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>1027</v>
       </c>
@@ -32039,7 +32060,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>1027</v>
       </c>
@@ -32132,12 +32153,10 @@
       <c r="E29" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F29" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>77</v>
-      </c>
+      <c r="F29" s="14">
+        <v>187095</v>
+      </c>
+      <c r="G29" s="14"/>
       <c r="H29" s="6" t="s">
         <v>125</v>
       </c>
@@ -32170,7 +32189,7 @@
         <v>46246</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>72</v>
@@ -32211,12 +32230,10 @@
       <c r="E30" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F30" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>77</v>
-      </c>
+      <c r="F30" s="14">
+        <v>187095</v>
+      </c>
+      <c r="G30" s="14"/>
       <c r="H30" s="6" t="s">
         <v>125</v>
       </c>
@@ -32249,7 +32266,7 @@
         <v>46246</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>72</v>
@@ -32290,12 +32307,10 @@
       <c r="E31" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F31" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>77</v>
-      </c>
+      <c r="F31" s="14">
+        <v>187095</v>
+      </c>
+      <c r="G31" s="14"/>
       <c r="H31" s="6" t="s">
         <v>125</v>
       </c>
@@ -32328,7 +32343,7 @@
         <v>46246</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>72</v>
@@ -32353,7 +32368,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>2331</v>
       </c>
@@ -32432,7 +32447,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>2331</v>
       </c>
@@ -32511,7 +32526,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>2331</v>
       </c>
@@ -32590,7 +32605,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>2331</v>
       </c>
@@ -32669,7 +32684,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>2337</v>
       </c>
@@ -32746,7 +32761,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14">
         <v>2337</v>
       </c>
@@ -32823,7 +32838,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14">
         <v>2337</v>
       </c>
@@ -32900,7 +32915,7 @@
         <v>AG. FUNDIDO</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14">
         <v>2337</v>
       </c>
@@ -40021,29 +40036,37 @@
       <c r="B108" s="71">
         <v>10</v>
       </c>
-      <c r="C108" s="72"/>
-      <c r="D108" s="72"/>
+      <c r="C108" s="72">
+        <v>27633</v>
+      </c>
+      <c r="D108" s="72">
+        <v>8</v>
+      </c>
       <c r="E108" s="73" t="s">
         <v>152</v>
       </c>
       <c r="F108" s="74">
         <v>1</v>
       </c>
-      <c r="G108" s="14"/>
+      <c r="G108" s="14">
+        <v>1343012</v>
+      </c>
       <c r="H108" s="14"/>
       <c r="I108" s="75" t="s">
         <v>410</v>
       </c>
-      <c r="J108" s="76"/>
+      <c r="J108" s="76">
+        <v>46235</v>
+      </c>
       <c r="K108" s="77"/>
       <c r="L108" s="76">
-        <v>46356</v>
+        <v>46386</v>
       </c>
       <c r="M108" s="77"/>
       <c r="N108" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="O108" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -40052,11 +40075,11 @@
       <c r="P108" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q108" s="11">
-        <v>46264</v>
+      <c r="Q108" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S108" t="s">
         <v>61</v>
@@ -40069,29 +40092,37 @@
       <c r="B109" s="71">
         <v>11</v>
       </c>
-      <c r="C109" s="72"/>
-      <c r="D109" s="72"/>
+      <c r="C109" s="72">
+        <v>27633</v>
+      </c>
+      <c r="D109" s="72">
+        <v>9</v>
+      </c>
       <c r="E109" s="73" t="s">
         <v>152</v>
       </c>
       <c r="F109" s="74">
         <v>1</v>
       </c>
-      <c r="G109" s="14"/>
+      <c r="G109" s="14">
+        <v>1343012</v>
+      </c>
       <c r="H109" s="14"/>
       <c r="I109" s="75" t="s">
         <v>410</v>
       </c>
-      <c r="J109" s="76"/>
+      <c r="J109" s="76">
+        <v>46235</v>
+      </c>
       <c r="K109" s="77"/>
       <c r="L109" s="76">
-        <v>46356</v>
+        <v>46386</v>
       </c>
       <c r="M109" s="77"/>
       <c r="N109" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="O109" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -40100,11 +40131,11 @@
       <c r="P109" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q109" s="11">
-        <v>46264</v>
+      <c r="Q109" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S109" t="s">
         <v>61</v>
@@ -40117,29 +40148,37 @@
       <c r="B110" s="71">
         <v>12</v>
       </c>
-      <c r="C110" s="72"/>
-      <c r="D110" s="72"/>
+      <c r="C110" s="72">
+        <v>27633</v>
+      </c>
+      <c r="D110" s="72">
+        <v>10</v>
+      </c>
       <c r="E110" s="73" t="s">
         <v>152</v>
       </c>
       <c r="F110" s="74">
         <v>1</v>
       </c>
-      <c r="G110" s="14"/>
+      <c r="G110" s="14">
+        <v>1343012</v>
+      </c>
       <c r="H110" s="14"/>
       <c r="I110" s="75" t="s">
         <v>410</v>
       </c>
-      <c r="J110" s="76"/>
+      <c r="J110" s="76">
+        <v>46235</v>
+      </c>
       <c r="K110" s="77"/>
       <c r="L110" s="76">
-        <v>46356</v>
+        <v>46386</v>
       </c>
       <c r="M110" s="77"/>
       <c r="N110" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="O110" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -40148,11 +40187,11 @@
       <c r="P110" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q110" s="11">
-        <v>46264</v>
+      <c r="Q110" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S110" t="s">
         <v>61</v>
@@ -40165,29 +40204,37 @@
       <c r="B111" s="71">
         <v>13</v>
       </c>
-      <c r="C111" s="72"/>
-      <c r="D111" s="72"/>
+      <c r="C111" s="72">
+        <v>27633</v>
+      </c>
+      <c r="D111" s="72">
+        <v>11</v>
+      </c>
       <c r="E111" s="73" t="s">
         <v>152</v>
       </c>
       <c r="F111" s="74">
         <v>1</v>
       </c>
-      <c r="G111" s="14"/>
+      <c r="G111" s="14">
+        <v>1343012</v>
+      </c>
       <c r="H111" s="14"/>
       <c r="I111" s="75" t="s">
         <v>410</v>
       </c>
-      <c r="J111" s="76"/>
+      <c r="J111" s="76">
+        <v>46235</v>
+      </c>
       <c r="K111" s="77"/>
       <c r="L111" s="76">
-        <v>46356</v>
+        <v>46386</v>
       </c>
       <c r="M111" s="77"/>
       <c r="N111" s="78">
         <f ca="1">Tabela4[[#This Row],[Prazo
 Entrega]]-TODAY()</f>
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="O111" s="77" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -40196,11 +40243,11 @@
       <c r="P111" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Q111" s="11">
-        <v>46264</v>
+      <c r="Q111" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S111" t="s">
         <v>61</v>
@@ -46956,11 +47003,11 @@
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="A30:A43">
-    <cfRule type="containsText" dxfId="41" priority="51" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="41" priority="50" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",A30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="51" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",A30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="50" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",A30)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="39" priority="52">
       <formula>$P30="s"</formula>
@@ -46981,88 +47028,88 @@
     <cfRule type="containsText" dxfId="35" priority="29" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",C45)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="31">
+    <cfRule type="containsText" dxfId="34" priority="30" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",C45)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="31">
       <formula>$P45="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="30" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",C45)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C55:C77">
-    <cfRule type="containsText" dxfId="32" priority="26" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="32" priority="25" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="31" priority="26" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",C55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="27">
+    <cfRule type="expression" dxfId="30" priority="27">
       <formula>$P55="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="25" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:D43">
     <cfRule type="containsText" dxfId="29" priority="47" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",D30)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="49">
+    <cfRule type="containsText" dxfId="28" priority="48" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",D30)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="49">
       <formula>$P30="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="48" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",D30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D77">
-    <cfRule type="containsText" dxfId="26" priority="22" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",D55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="22" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",D55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="21" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",D55)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="23">
       <formula>$P55="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59:G60 G67">
-    <cfRule type="expression" dxfId="23" priority="12">
-      <formula>$P59="s"</formula>
+    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="22" priority="10" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",G59)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
+    <cfRule type="expression" dxfId="21" priority="12">
+      <formula>$P59="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58 H60 H62 H65:H66 H76">
-    <cfRule type="containsText" dxfId="20" priority="14" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="20" priority="13" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="14" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",H58)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="16">
+    <cfRule type="expression" dxfId="18" priority="16">
       <formula>$P58="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:N45">
     <cfRule type="containsText" dxfId="17" priority="41" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",N33)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="43">
+    <cfRule type="containsText" dxfId="16" priority="42" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",N33)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="43">
       <formula>$P33="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="42" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",N33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N55:N77">
     <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",N55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",N55)))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>$P55="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",N55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O33:O35">
@@ -47099,14 +47146,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB55:AB77">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",AB55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>$P55="s"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -49766,7 +49813,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9730F04C-E101-46F3-A942-AC61D67D9938}">
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="10" customWidth="1"/>
@@ -49887,7 +49934,9 @@
       <c r="Q2" s="23">
         <v>285</v>
       </c>
-      <c r="R2" s="50"/>
+      <c r="R2" s="50" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
@@ -49937,7 +49986,9 @@
       <c r="Q3" s="23">
         <v>285</v>
       </c>
-      <c r="R3" s="50"/>
+      <c r="R3" s="50" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="47">
@@ -50146,7 +50197,7 @@
         <v>77</v>
       </c>
       <c r="P7" s="25" t="s">
-        <v>232</v>
+        <v>413</v>
       </c>
       <c r="Q7" s="23" t="s">
         <v>186</v>
@@ -50200,7 +50251,7 @@
         <v>77</v>
       </c>
       <c r="P8" s="25" t="s">
-        <v>232</v>
+        <v>413</v>
       </c>
       <c r="Q8" s="23" t="s">
         <v>187</v>
@@ -50254,7 +50305,7 @@
         <v>77</v>
       </c>
       <c r="P9" s="25" t="s">
-        <v>232</v>
+        <v>413</v>
       </c>
       <c r="Q9" s="23" t="s">
         <v>187</v>
@@ -50308,7 +50359,7 @@
         <v>77</v>
       </c>
       <c r="P10" s="25" t="s">
-        <v>232</v>
+        <v>413</v>
       </c>
       <c r="Q10" s="23" t="s">
         <v>187</v>
@@ -50362,7 +50413,7 @@
         <v>77</v>
       </c>
       <c r="P11" s="25" t="s">
-        <v>232</v>
+        <v>413</v>
       </c>
       <c r="Q11" s="23" t="s">
         <v>187</v>
@@ -50416,7 +50467,7 @@
         <v>77</v>
       </c>
       <c r="P12" s="25" t="s">
-        <v>232</v>
+        <v>413</v>
       </c>
       <c r="Q12" s="23" t="s">
         <v>187</v>
@@ -50523,25 +50574,23 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="47">
-        <v>27476</v>
-      </c>
-      <c r="B15" s="47">
-        <v>1</v>
-      </c>
+        <v>27618</v>
+      </c>
+      <c r="B15" s="47"/>
       <c r="C15" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="D15" s="23">
-        <v>299529</v>
+        <v>421</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>208</v>
+        <v>422</v>
       </c>
       <c r="F15" s="49">
         <v>1</v>
       </c>
-      <c r="G15" s="25">
-        <v>46217</v>
+      <c r="G15" s="81">
+        <v>46216</v>
       </c>
       <c r="H15" s="25" t="s">
         <v>77</v>
@@ -50555,16 +50604,16 @@
       <c r="K15" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="L15" s="67">
-        <v>46205</v>
-      </c>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25">
+      <c r="L15" s="27">
+        <v>46202</v>
+      </c>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27">
         <v>46216</v>
       </c>
-      <c r="O15" s="25"/>
+      <c r="O15" s="27"/>
       <c r="P15" s="25" t="s">
-        <v>61</v>
+        <v>232</v>
       </c>
       <c r="Q15" s="23" t="s">
         <v>188</v>
@@ -50573,7 +50622,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="47">
-        <v>27490</v>
+        <v>27476</v>
       </c>
       <c r="B16" s="47">
         <v>1</v>
@@ -50582,173 +50631,173 @@
         <v>174</v>
       </c>
       <c r="D16" s="23">
-        <v>299302</v>
+        <v>299529</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F16" s="49">
         <v>1</v>
       </c>
       <c r="G16" s="25">
-        <v>46218</v>
-      </c>
-      <c r="H16" s="25">
-        <v>46189</v>
-      </c>
-      <c r="I16" s="25">
-        <v>46189</v>
-      </c>
-      <c r="J16" s="25">
-        <v>46199</v>
-      </c>
-      <c r="K16" s="25">
-        <v>46199</v>
-      </c>
-      <c r="L16" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="M16" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N16" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="O16" s="25" t="s">
-        <v>77</v>
-      </c>
+        <v>46217</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="L16" s="67">
+        <v>46205</v>
+      </c>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25">
+        <v>46216</v>
+      </c>
+      <c r="O16" s="25"/>
       <c r="P16" s="25" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q16" s="23">
-        <v>496</v>
+        <v>61</v>
+      </c>
+      <c r="Q16" s="23" t="s">
+        <v>188</v>
       </c>
       <c r="R16" s="50"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="47">
+        <v>27490</v>
+      </c>
+      <c r="B17" s="47">
+        <v>1</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="23">
+        <v>299302</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="F17" s="49">
+        <v>1</v>
+      </c>
+      <c r="G17" s="25">
+        <v>46218</v>
+      </c>
+      <c r="H17" s="25">
+        <v>46189</v>
+      </c>
+      <c r="I17" s="25">
+        <v>46189</v>
+      </c>
+      <c r="J17" s="25">
+        <v>46199</v>
+      </c>
+      <c r="K17" s="25">
+        <v>46199</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M17" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N17" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O17" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="P17" s="25" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q17" s="23">
+        <v>496</v>
+      </c>
+      <c r="R17" s="50"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="47">
         <v>27416</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B18" s="47">
         <v>2</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C18" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D18" s="23">
         <v>392292</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E18" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="F17" s="49">
-        <v>1</v>
-      </c>
-      <c r="G17" s="65">
+      <c r="F18" s="49">
+        <v>1</v>
+      </c>
+      <c r="G18" s="65">
         <v>46218</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H18" s="25">
         <v>46219</v>
       </c>
-      <c r="I17" s="25"/>
-      <c r="J17" s="68">
+      <c r="I18" s="25"/>
+      <c r="J18" s="68">
         <v>46223</v>
       </c>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25">
+      <c r="K18" s="25"/>
+      <c r="L18" s="25">
         <v>46237</v>
       </c>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25">
+      <c r="M18" s="25"/>
+      <c r="N18" s="25">
         <v>46241</v>
       </c>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q17" s="23">
-        <v>493</v>
-      </c>
-      <c r="R17" s="50"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="23">
-        <v>27521</v>
-      </c>
-      <c r="B18" s="23">
-        <v>1</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="D18" s="23">
-        <v>299303</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="F18" s="49">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25">
-        <v>46227</v>
-      </c>
-      <c r="H18" s="25">
-        <v>46211</v>
-      </c>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25">
-        <v>46220</v>
-      </c>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="M18" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N18" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="O18" s="25" t="s">
-        <v>77</v>
-      </c>
+      <c r="O18" s="25"/>
       <c r="P18" s="25" t="s">
         <v>61</v>
       </c>
       <c r="Q18" s="23">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="R18" s="50"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="23">
-        <v>26974</v>
+        <v>27521</v>
       </c>
       <c r="B19" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" s="24" t="s">
         <v>174</v>
       </c>
       <c r="D19" s="23">
-        <v>299217</v>
-      </c>
-      <c r="E19" s="66" t="s">
-        <v>212</v>
+        <v>299303</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>211</v>
       </c>
       <c r="F19" s="49">
         <v>1</v>
       </c>
       <c r="G19" s="25">
-        <v>46228</v>
+        <v>46227</v>
       </c>
       <c r="H19" s="25">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="I19" s="25"/>
       <c r="J19" s="25">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="K19" s="25"/>
       <c r="L19" s="25" t="s">
@@ -50767,13 +50816,13 @@
         <v>61</v>
       </c>
       <c r="Q19" s="23">
-        <v>285</v>
+        <v>496</v>
       </c>
       <c r="R19" s="50"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="23">
-        <v>26970</v>
+        <v>26974</v>
       </c>
       <c r="B20" s="23">
         <v>3</v>
@@ -50782,10 +50831,10 @@
         <v>174</v>
       </c>
       <c r="D20" s="23">
-        <v>299209</v>
+        <v>299217</v>
       </c>
       <c r="E20" s="66" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F20" s="49">
         <v>1</v>
@@ -50794,11 +50843,11 @@
         <v>46228</v>
       </c>
       <c r="H20" s="25">
-        <v>46213</v>
+        <v>46206</v>
       </c>
       <c r="I20" s="25"/>
       <c r="J20" s="25">
-        <v>46220</v>
+        <v>46213</v>
       </c>
       <c r="K20" s="25"/>
       <c r="L20" s="25" t="s">
@@ -50823,19 +50872,19 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="23">
-        <v>26641</v>
+        <v>26970</v>
       </c>
       <c r="B21" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="24" t="s">
         <v>174</v>
       </c>
       <c r="D21" s="23">
-        <v>299217</v>
+        <v>299209</v>
       </c>
       <c r="E21" s="66" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F21" s="49">
         <v>1</v>
@@ -50844,11 +50893,11 @@
         <v>46228</v>
       </c>
       <c r="H21" s="25">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="I21" s="25"/>
       <c r="J21" s="25">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="K21" s="25"/>
       <c r="L21" s="25" t="s">
@@ -50873,51 +50922,51 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="23">
-        <v>27547</v>
+        <v>26641</v>
       </c>
       <c r="B22" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D22" s="23">
-        <v>1573002</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>130</v>
+        <v>299217</v>
+      </c>
+      <c r="E22" s="66" t="s">
+        <v>212</v>
       </c>
       <c r="F22" s="49">
         <v>1</v>
       </c>
       <c r="G22" s="25">
-        <v>46233</v>
-      </c>
-      <c r="H22" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="I22" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="L22" s="25">
-        <v>46220</v>
-      </c>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25">
-        <v>46232</v>
-      </c>
-      <c r="O22" s="25"/>
+        <v>46228</v>
+      </c>
+      <c r="H22" s="25">
+        <v>46206</v>
+      </c>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25">
+        <v>46213</v>
+      </c>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N22" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O22" s="25" t="s">
+        <v>77</v>
+      </c>
       <c r="P22" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="Q22" s="23" t="s">
-        <v>189</v>
+      <c r="Q22" s="23">
+        <v>285</v>
       </c>
       <c r="R22" s="50"/>
     </row>
@@ -50926,16 +50975,16 @@
         <v>27547</v>
       </c>
       <c r="B23" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="24" t="s">
         <v>178</v>
       </c>
       <c r="D23" s="23">
-        <v>1573001</v>
+        <v>1573002</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F23" s="49">
         <v>1</v>
@@ -50973,25 +51022,25 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="23">
-        <v>27575</v>
+        <v>27547</v>
       </c>
       <c r="B24" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D24" s="23">
-        <v>774016</v>
+        <v>1573001</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>214</v>
+        <v>131</v>
       </c>
       <c r="F24" s="49">
         <v>1</v>
       </c>
       <c r="G24" s="25">
-        <v>46239</v>
+        <v>46233</v>
       </c>
       <c r="H24" s="25" t="s">
         <v>77</v>
@@ -51010,38 +51059,38 @@
       </c>
       <c r="M24" s="25"/>
       <c r="N24" s="25">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="O24" s="25"/>
       <c r="P24" s="25" t="s">
         <v>61</v>
       </c>
       <c r="Q24" s="23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R24" s="50"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="23">
-        <v>27575</v>
+        <v>27567</v>
       </c>
       <c r="B25" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>179</v>
+        <v>417</v>
       </c>
       <c r="D25" s="23">
-        <v>774016</v>
+        <v>112036</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>214</v>
+        <v>418</v>
       </c>
       <c r="F25" s="49">
         <v>1</v>
       </c>
       <c r="G25" s="25">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="H25" s="25" t="s">
         <v>77</v>
@@ -51056,18 +51105,18 @@
         <v>77</v>
       </c>
       <c r="L25" s="25">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="M25" s="25"/>
       <c r="N25" s="25">
-        <v>46238</v>
+        <v>46227</v>
       </c>
       <c r="O25" s="25"/>
       <c r="P25" s="25" t="s">
         <v>61</v>
       </c>
       <c r="Q25" s="23" t="s">
-        <v>190</v>
+        <v>419</v>
       </c>
       <c r="R25" s="50"/>
     </row>
@@ -51076,16 +51125,16 @@
         <v>27575</v>
       </c>
       <c r="B26" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" s="24" t="s">
         <v>179</v>
       </c>
       <c r="D26" s="23">
-        <v>774017</v>
+        <v>774016</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F26" s="49">
         <v>1</v>
@@ -51126,16 +51175,16 @@
         <v>27575</v>
       </c>
       <c r="B27" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="24" t="s">
         <v>179</v>
       </c>
       <c r="D27" s="23">
-        <v>774017</v>
+        <v>774016</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F27" s="49">
         <v>1</v>
@@ -51173,25 +51222,25 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="23">
-        <v>27524</v>
+        <v>27575</v>
       </c>
       <c r="B28" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D28" s="23">
-        <v>299528</v>
+        <v>774017</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F28" s="49">
         <v>1</v>
       </c>
       <c r="G28" s="25">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="H28" s="25" t="s">
         <v>77</v>
@@ -51206,118 +51255,118 @@
         <v>77</v>
       </c>
       <c r="L28" s="25">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="M28" s="25"/>
       <c r="N28" s="25">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="O28" s="25"/>
       <c r="P28" s="25" t="s">
         <v>61</v>
       </c>
       <c r="Q28" s="23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="R28" s="50"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="23">
-        <v>27587</v>
+        <v>27575</v>
       </c>
       <c r="B29" s="23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D29" s="23">
-        <v>1608001</v>
+        <v>774017</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F29" s="49">
         <v>1</v>
       </c>
       <c r="G29" s="25">
-        <v>46246</v>
-      </c>
-      <c r="H29" s="80">
-        <v>46213</v>
-      </c>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25">
-        <v>46226</v>
-      </c>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="M29" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N29" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="O29" s="25" t="s">
-        <v>77</v>
-      </c>
+        <v>46239</v>
+      </c>
+      <c r="H29" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="L29" s="25">
+        <v>46220</v>
+      </c>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25">
+        <v>46238</v>
+      </c>
+      <c r="O29" s="25"/>
       <c r="P29" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="Q29" s="23">
-        <v>124</v>
+      <c r="Q29" s="23" t="s">
+        <v>190</v>
       </c>
       <c r="R29" s="50"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="23">
-        <v>27587</v>
+        <v>27524</v>
       </c>
       <c r="B30" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D30" s="23">
-        <v>1608002</v>
+        <v>299528</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F30" s="49">
         <v>1</v>
       </c>
       <c r="G30" s="25">
-        <v>46246</v>
-      </c>
-      <c r="H30" s="80">
-        <v>46213</v>
-      </c>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25">
-        <v>46226</v>
-      </c>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="M30" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N30" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="O30" s="25" t="s">
-        <v>77</v>
-      </c>
+        <v>46245</v>
+      </c>
+      <c r="H30" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="J30" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="L30" s="25">
+        <v>46234</v>
+      </c>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25">
+        <v>46244</v>
+      </c>
+      <c r="O30" s="25"/>
       <c r="P30" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="Q30" s="23">
-        <v>124</v>
+      <c r="Q30" s="23" t="s">
+        <v>188</v>
       </c>
       <c r="R30" s="50"/>
     </row>
@@ -51326,13 +51375,13 @@
         <v>27587</v>
       </c>
       <c r="B31" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>183</v>
       </c>
       <c r="D31" s="23">
-        <v>1608002</v>
+        <v>1608001</v>
       </c>
       <c r="E31" s="24" t="s">
         <v>217</v>
@@ -51373,196 +51422,196 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
-        <v>27593</v>
+        <v>27587</v>
       </c>
       <c r="B32" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D32" s="23">
-        <v>1609001</v>
+        <v>1608002</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F32" s="49">
         <v>1</v>
       </c>
       <c r="G32" s="25">
-        <v>46253</v>
+        <v>46246</v>
       </c>
       <c r="H32" s="80">
         <v>46213</v>
       </c>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27">
-        <v>46228</v>
-      </c>
-      <c r="K32" s="27"/>
-      <c r="L32" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="M32" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="N32" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="O32" s="26" t="s">
+      <c r="I32" s="25"/>
+      <c r="J32" s="25">
+        <v>46226</v>
+      </c>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M32" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N32" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O32" s="25" t="s">
         <v>77</v>
       </c>
       <c r="P32" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="Q32" s="26" t="s">
-        <v>191</v>
+      <c r="Q32" s="23">
+        <v>124</v>
       </c>
       <c r="R32" s="50"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="23">
-        <v>27599</v>
+        <v>27587</v>
       </c>
       <c r="B33" s="23">
-        <v>1</v>
-      </c>
-      <c r="C33" s="48" t="s">
-        <v>174</v>
+        <v>3</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>183</v>
       </c>
       <c r="D33" s="23">
-        <v>299374</v>
+        <v>1608002</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F33" s="49">
         <v>1</v>
       </c>
       <c r="G33" s="25">
-        <v>46254</v>
-      </c>
-      <c r="H33" s="27">
-        <v>46220</v>
-      </c>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27">
-        <v>46234</v>
-      </c>
-      <c r="K33" s="27"/>
-      <c r="L33" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="M33" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="N33" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="O33" s="26" t="s">
+        <v>46246</v>
+      </c>
+      <c r="H33" s="80">
+        <v>46213</v>
+      </c>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25">
+        <v>46226</v>
+      </c>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M33" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N33" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O33" s="25" t="s">
         <v>77</v>
       </c>
       <c r="P33" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="Q33" s="26">
-        <v>285</v>
+      <c r="Q33" s="23">
+        <v>124</v>
       </c>
       <c r="R33" s="50"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="23">
-        <v>27542</v>
+        <v>27593</v>
       </c>
       <c r="B34" s="23">
         <v>1</v>
       </c>
-      <c r="C34" s="48" t="s">
-        <v>174</v>
+      <c r="C34" s="24" t="s">
+        <v>184</v>
       </c>
       <c r="D34" s="23">
-        <v>299528</v>
+        <v>1609001</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F34" s="49">
         <v>1</v>
       </c>
       <c r="G34" s="25">
-        <v>46255</v>
-      </c>
-      <c r="H34" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J34" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="K34" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="L34" s="27">
-        <v>46241</v>
-      </c>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27">
-        <v>46254</v>
-      </c>
-      <c r="O34" s="27"/>
+        <v>46253</v>
+      </c>
+      <c r="H34" s="80">
+        <v>46213</v>
+      </c>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27">
+        <v>46228</v>
+      </c>
+      <c r="K34" s="27"/>
+      <c r="L34" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M34" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="N34" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O34" s="26" t="s">
+        <v>77</v>
+      </c>
       <c r="P34" s="25" t="s">
         <v>61</v>
       </c>
       <c r="Q34" s="26" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R34" s="50"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="23">
-        <v>27600</v>
+        <v>27599</v>
       </c>
       <c r="B35" s="23">
         <v>1</v>
       </c>
-      <c r="C35" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>77</v>
+      <c r="C35" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" s="23">
+        <v>299374</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F35" s="49">
         <v>1</v>
       </c>
       <c r="G35" s="25">
-        <v>46259</v>
-      </c>
-      <c r="H35" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J35" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="K35" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="L35" s="27">
-        <v>46248</v>
-      </c>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27">
-        <v>46255</v>
-      </c>
-      <c r="O35" s="27"/>
+        <v>46254</v>
+      </c>
+      <c r="H35" s="27">
+        <v>46220</v>
+      </c>
+      <c r="I35" s="27"/>
+      <c r="J35" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K35" s="27"/>
+      <c r="L35" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M35" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="N35" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O35" s="26" t="s">
+        <v>77</v>
+      </c>
       <c r="P35" s="25" t="s">
         <v>61</v>
       </c>
@@ -51573,27 +51622,27 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
-        <v>27600</v>
+        <v>27542</v>
       </c>
       <c r="B36" s="23">
-        <v>5</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>77</v>
+        <v>1</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="D36" s="23">
+        <v>299528</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F36" s="49">
         <v>1</v>
       </c>
       <c r="G36" s="25">
-        <v>46259</v>
-      </c>
-      <c r="H36" s="27" t="s">
+        <v>46255</v>
+      </c>
+      <c r="H36" s="26" t="s">
         <v>77</v>
       </c>
       <c r="I36" s="26" t="s">
@@ -51606,18 +51655,18 @@
         <v>77</v>
       </c>
       <c r="L36" s="27">
-        <v>46248</v>
+        <v>46241</v>
       </c>
       <c r="M36" s="27"/>
       <c r="N36" s="27">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="O36" s="27"/>
       <c r="P36" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="Q36" s="26">
-        <v>285</v>
+      <c r="Q36" s="26" t="s">
+        <v>188</v>
       </c>
       <c r="R36" s="50"/>
     </row>
@@ -51626,7 +51675,7 @@
         <v>27600</v>
       </c>
       <c r="B37" s="23">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C37" s="24" t="s">
         <v>182</v>
@@ -51676,7 +51725,7 @@
         <v>27600</v>
       </c>
       <c r="B38" s="23">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>182</v>
@@ -51726,7 +51775,7 @@
         <v>27600</v>
       </c>
       <c r="B39" s="23">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C39" s="24" t="s">
         <v>182</v>
@@ -51741,7 +51790,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="25">
-        <v>46269</v>
+        <v>46259</v>
       </c>
       <c r="H39" s="27" t="s">
         <v>77</v>
@@ -51776,7 +51825,7 @@
         <v>27600</v>
       </c>
       <c r="B40" s="23">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C40" s="24" t="s">
         <v>182</v>
@@ -51791,7 +51840,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="25">
-        <v>46269</v>
+        <v>46259</v>
       </c>
       <c r="H40" s="27" t="s">
         <v>77</v>
@@ -51826,7 +51875,7 @@
         <v>27600</v>
       </c>
       <c r="B41" s="23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>182</v>
@@ -51876,7 +51925,7 @@
         <v>27600</v>
       </c>
       <c r="B42" s="23">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C42" s="24" t="s">
         <v>182</v>
@@ -51923,19 +51972,19 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="23">
-        <v>27496</v>
+        <v>27600</v>
       </c>
       <c r="B43" s="23">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="D43" s="23">
-        <v>299208</v>
+        <v>182</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F43" s="49">
         <v>1</v>
@@ -51943,26 +51992,26 @@
       <c r="G43" s="25">
         <v>46269</v>
       </c>
-      <c r="H43" s="27">
-        <v>46206</v>
-      </c>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27">
-        <v>46213</v>
-      </c>
-      <c r="K43" s="27"/>
-      <c r="L43" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="M43" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="N43" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="O43" s="26" t="s">
-        <v>77</v>
-      </c>
+      <c r="H43" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I43" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="J43" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K43" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="L43" s="27">
+        <v>46248</v>
+      </c>
+      <c r="M43" s="27"/>
+      <c r="N43" s="27">
+        <v>46255</v>
+      </c>
+      <c r="O43" s="27"/>
       <c r="P43" s="25" t="s">
         <v>61</v>
       </c>
@@ -51976,7 +52025,7 @@
         <v>27600</v>
       </c>
       <c r="B44" s="23">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C44" s="24" t="s">
         <v>182</v>
@@ -51985,24 +52034,24 @@
         <v>77</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F44" s="49">
         <v>1</v>
       </c>
       <c r="G44" s="25">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="H44" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I44" s="27" t="s">
+      <c r="I44" s="26" t="s">
         <v>77</v>
       </c>
       <c r="J44" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="K44" s="27" t="s">
+      <c r="K44" s="26" t="s">
         <v>77</v>
       </c>
       <c r="L44" s="27">
@@ -52023,46 +52072,46 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="23">
-        <v>27600</v>
+        <v>27496</v>
       </c>
       <c r="B45" s="23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>77</v>
+        <v>174</v>
+      </c>
+      <c r="D45" s="23">
+        <v>299208</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F45" s="49">
         <v>1</v>
       </c>
       <c r="G45" s="25">
-        <v>46279</v>
-      </c>
-      <c r="H45" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="I45" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="J45" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="K45" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="L45" s="27">
-        <v>46248</v>
-      </c>
-      <c r="M45" s="27"/>
-      <c r="N45" s="27">
-        <v>46255</v>
-      </c>
-      <c r="O45" s="27"/>
+        <v>46269</v>
+      </c>
+      <c r="H45" s="27">
+        <v>46206</v>
+      </c>
+      <c r="I45" s="27"/>
+      <c r="J45" s="27">
+        <v>46213</v>
+      </c>
+      <c r="K45" s="27"/>
+      <c r="L45" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M45" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="N45" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O45" s="26" t="s">
+        <v>77</v>
+      </c>
       <c r="P45" s="25" t="s">
         <v>61</v>
       </c>
@@ -52076,7 +52125,7 @@
         <v>27600</v>
       </c>
       <c r="B46" s="23">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C46" s="24" t="s">
         <v>182</v>
@@ -52126,7 +52175,7 @@
         <v>27600</v>
       </c>
       <c r="B47" s="23">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C47" s="24" t="s">
         <v>182</v>
@@ -52176,7 +52225,7 @@
         <v>27600</v>
       </c>
       <c r="B48" s="23">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C48" s="24" t="s">
         <v>182</v>
@@ -52191,7 +52240,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="25">
-        <v>46289</v>
+        <v>46279</v>
       </c>
       <c r="H48" s="27" t="s">
         <v>77</v>
@@ -52226,7 +52275,7 @@
         <v>27600</v>
       </c>
       <c r="B49" s="23">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C49" s="24" t="s">
         <v>182</v>
@@ -52241,7 +52290,7 @@
         <v>1</v>
       </c>
       <c r="G49" s="25">
-        <v>46289</v>
+        <v>46279</v>
       </c>
       <c r="H49" s="27" t="s">
         <v>77</v>
@@ -52276,7 +52325,7 @@
         <v>27600</v>
       </c>
       <c r="B50" s="23">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C50" s="24" t="s">
         <v>182</v>
@@ -52326,7 +52375,7 @@
         <v>27600</v>
       </c>
       <c r="B51" s="23">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C51" s="24" t="s">
         <v>182</v>
@@ -52373,56 +52422,159 @@
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="23">
-        <v>27597</v>
+        <v>27600</v>
       </c>
       <c r="B52" s="23">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="D52" s="23">
-        <v>299303</v>
+        <v>182</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F52" s="49">
         <v>1</v>
       </c>
       <c r="G52" s="25">
-        <v>46332</v>
-      </c>
-      <c r="H52" s="27">
-        <v>46297</v>
-      </c>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27">
-        <v>46307</v>
-      </c>
-      <c r="K52" s="27"/>
-      <c r="L52" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="M52" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="N52" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="O52" s="26" t="s">
-        <v>77</v>
-      </c>
+        <v>46289</v>
+      </c>
+      <c r="H52" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I52" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="J52" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K52" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L52" s="27">
+        <v>46248</v>
+      </c>
+      <c r="M52" s="27"/>
+      <c r="N52" s="27">
+        <v>46255</v>
+      </c>
+      <c r="O52" s="27"/>
       <c r="P52" s="25" t="s">
         <v>61</v>
       </c>
       <c r="Q52" s="26">
+        <v>285</v>
+      </c>
+      <c r="R52" s="50"/>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="23">
+        <v>27600</v>
+      </c>
+      <c r="B53" s="23">
+        <v>16</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="F53" s="49">
+        <v>1</v>
+      </c>
+      <c r="G53" s="25">
+        <v>46289</v>
+      </c>
+      <c r="H53" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I53" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="J53" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="K53" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="L53" s="27">
+        <v>46248</v>
+      </c>
+      <c r="M53" s="27"/>
+      <c r="N53" s="27">
+        <v>46255</v>
+      </c>
+      <c r="O53" s="27"/>
+      <c r="P53" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q53" s="26">
+        <v>285</v>
+      </c>
+      <c r="R53" s="50"/>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="23">
+        <v>27597</v>
+      </c>
+      <c r="B54" s="23">
+        <v>1</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" s="23">
+        <v>299303</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="F54" s="49">
+        <v>1</v>
+      </c>
+      <c r="G54" s="25">
+        <v>46332</v>
+      </c>
+      <c r="H54" s="27">
+        <v>46297</v>
+      </c>
+      <c r="I54" s="27"/>
+      <c r="J54" s="27">
+        <v>46307</v>
+      </c>
+      <c r="K54" s="27"/>
+      <c r="L54" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="M54" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="N54" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="O54" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="P54" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q54" s="26">
         <v>496</v>
       </c>
-      <c r="R52" s="50"/>
+      <c r="R54" s="50"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N52" xr:uid="{276B14C1-1A52-4B27-91DF-D329FDD63C7A}"/>
+  <autoFilter ref="A1:N54" xr:uid="{276B14C1-1A52-4B27-91DF-D329FDD63C7A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R54">
+    <sortCondition ref="G2:G54"/>
+  </sortState>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="39" orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094AC9D9-1AAE-4A1C-AB74-2208A1716180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E8A3DC-C881-4837-AC90-E2D34851FAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
@@ -1627,7 +1627,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1843,9 +1843,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -47003,11 +47000,11 @@
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="A30:A43">
-    <cfRule type="containsText" dxfId="41" priority="50" operator="containsText" text="encamisado">
+    <cfRule type="containsText" dxfId="41" priority="51" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",A30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="40" priority="50" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",A30)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="51" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",A30)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="39" priority="52">
       <formula>$P30="s"</formula>
@@ -47028,88 +47025,88 @@
     <cfRule type="containsText" dxfId="35" priority="29" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",C45)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="30" operator="containsText" text="pronto">
+    <cfRule type="expression" dxfId="34" priority="31">
+      <formula>$P45="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="30" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",C45)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="31">
-      <formula>$P45="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C55:C77">
-    <cfRule type="containsText" dxfId="32" priority="25" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="31" priority="26" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="32" priority="26" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",C55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="27">
+    <cfRule type="expression" dxfId="31" priority="27">
       <formula>$P55="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="25" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",C55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:D43">
     <cfRule type="containsText" dxfId="29" priority="47" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",D30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="48" operator="containsText" text="pronto">
+    <cfRule type="expression" dxfId="28" priority="49">
+      <formula>$P30="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="27" priority="48" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",D30)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="49">
-      <formula>$P30="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:D77">
-    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="encamisado">
+    <cfRule type="containsText" dxfId="26" priority="22" operator="containsText" text="pronto">
+      <formula>NOT(ISERROR(SEARCH("pronto",D55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="25" priority="21" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",D55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="22" operator="containsText" text="pronto">
-      <formula>NOT(ISERROR(SEARCH("pronto",D55)))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="23">
       <formula>$P55="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59:G60 G67">
-    <cfRule type="containsText" dxfId="23" priority="9" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
+    <cfRule type="expression" dxfId="23" priority="12">
+      <formula>$P59="s"</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="22" priority="10" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",G59)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="12">
-      <formula>$P59="s"</formula>
+    <cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",G59)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H58 H60 H62 H65:H66 H76">
-    <cfRule type="containsText" dxfId="20" priority="13" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="14" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="20" priority="14" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",H58)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="16">
+    <cfRule type="expression" dxfId="19" priority="16">
       <formula>$P58="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",H58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33:N45">
     <cfRule type="containsText" dxfId="17" priority="41" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",N33)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="42" operator="containsText" text="pronto">
+    <cfRule type="expression" dxfId="16" priority="43">
+      <formula>$P33="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="42" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",N33)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="43">
-      <formula>$P33="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N55:N77">
     <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="encamisado">
       <formula>NOT(ISERROR(SEARCH("encamisado",N55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="6" operator="containsText" text="pronto">
+    <cfRule type="expression" dxfId="13" priority="7">
+      <formula>$P55="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",N55)))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="7">
-      <formula>$P55="s"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O33:O35">
@@ -47146,14 +47143,14 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB55:AB77">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="encamisado">
-      <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="pronto">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="pronto">
       <formula>NOT(ISERROR(SEARCH("pronto",AB55)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$P55="s"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="encamisado">
+      <formula>NOT(ISERROR(SEARCH("encamisado",AB55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -50010,7 +50007,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="25">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="H4" s="25">
         <v>46196</v>
@@ -50064,7 +50061,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="25">
-        <v>46195</v>
+        <v>46211</v>
       </c>
       <c r="H5" s="25">
         <v>46196</v>
@@ -50116,7 +50113,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="25">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="H6" s="25">
         <v>46192</v>
@@ -50170,7 +50167,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="25">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="H7" s="25">
         <v>46192</v>
@@ -50224,7 +50221,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="25">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="H8" s="25">
         <v>46192</v>
@@ -50278,7 +50275,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="25">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="H9" s="25">
         <v>46192</v>
@@ -50332,7 +50329,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="25">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="H10" s="25">
         <v>46192</v>
@@ -50386,7 +50383,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="25">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="H11" s="25">
         <v>46192</v>
@@ -50440,7 +50437,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="25">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="H12" s="25">
         <v>46192</v>
@@ -50494,7 +50491,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="25">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="H13" s="25">
         <v>46192</v>
@@ -50589,7 +50586,7 @@
       <c r="F15" s="49">
         <v>1</v>
       </c>
-      <c r="G15" s="81">
+      <c r="G15" s="25">
         <v>46216</v>
       </c>
       <c r="H15" s="25" t="s">
@@ -50607,7 +50604,9 @@
       <c r="L15" s="27">
         <v>46202</v>
       </c>
-      <c r="M15" s="27"/>
+      <c r="M15" s="27">
+        <v>46202</v>
+      </c>
       <c r="N15" s="27">
         <v>46216</v>
       </c>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E8A3DC-C881-4837-AC90-E2D34851FAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC49F8CE-55AC-4639-AFE6-D7CB8FF09397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6833" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6833" uniqueCount="424">
   <si>
     <t>O.S.</t>
   </si>
@@ -1358,6 +1358,10 @@
   </si>
   <si>
     <t>USINAGEM ACABEMENTO CARCAÇA INF</t>
+  </si>
+  <si>
+    <t>Fund. Real
+(Acabamento)</t>
   </si>
 </sst>
 </file>
@@ -5153,9 +5157,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}" name="Tabela1" displayName="Tabela1" ref="A1:AI114" totalsRowShown="0" headerRowDxfId="215" dataDxfId="214">
   <autoFilter ref="A1:AI114" xr:uid="{0B979512-8F08-4F92-A755-B1320B33B48D}">
-    <filterColumn colId="0">
+    <filterColumn colId="4">
       <filters>
-        <filter val="2203"/>
+        <filter val="MS Internacional"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -8205,7 +8209,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15">
         <v>2203</v>
       </c>
@@ -8320,7 +8324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
         <v>2203</v>
       </c>
@@ -8435,7 +8439,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="15">
         <v>2227</v>
       </c>
@@ -8517,7 +8521,7 @@
         <v>69</v>
       </c>
       <c r="Z24" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AA24" s="10" t="s">
         <v>69</v>
@@ -8549,7 +8553,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>2227</v>
       </c>
@@ -8631,7 +8635,7 @@
         <v>69</v>
       </c>
       <c r="Z25" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AA25" s="10" t="s">
         <v>69</v>
@@ -8663,7 +8667,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="15">
         <v>2227</v>
       </c>
@@ -8745,7 +8749,7 @@
         <v>69</v>
       </c>
       <c r="Z26" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AA26" s="10" t="s">
         <v>69</v>
@@ -8777,7 +8781,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="15">
         <v>2227</v>
       </c>
@@ -8859,7 +8863,7 @@
         <v>69</v>
       </c>
       <c r="Z27" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AA27" s="10" t="s">
         <v>69</v>
@@ -8891,7 +8895,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="15">
         <v>2227</v>
       </c>
@@ -8973,7 +8977,7 @@
         <v>69</v>
       </c>
       <c r="Z28" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AA28" s="10" t="s">
         <v>69</v>
@@ -9005,7 +9009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="15">
         <v>2227</v>
       </c>
@@ -9087,7 +9091,7 @@
         <v>69</v>
       </c>
       <c r="Z29" s="10" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="AA29" s="10" t="s">
         <v>69</v>
@@ -9119,7 +9123,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
         <v>2203</v>
       </c>
@@ -10841,7 +10845,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
         <v>2203</v>
       </c>
@@ -10956,7 +10960,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15">
         <v>2203</v>
       </c>
@@ -11071,7 +11075,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <v>2203</v>
       </c>
@@ -14225,7 +14229,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="75" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A75" s="15">
         <v>2290</v>
       </c>
@@ -14337,7 +14341,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A76" s="15">
         <v>2290</v>
       </c>
@@ -14449,7 +14453,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="77" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A77" s="15">
         <v>2290</v>
       </c>
@@ -49865,7 +49869,7 @@
         <v>196</v>
       </c>
       <c r="M1" s="22" t="s">
-        <v>196</v>
+        <v>423</v>
       </c>
       <c r="N1" s="22" t="s">
         <v>197</v>

--- a/dados.xlsx
+++ b/dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\srv-fls\PCP Equipamentos\PCP AÇÚCAR E ETANOL 2026_2027\Programação\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC49F8CE-55AC-4639-AFE6-D7CB8FF09397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2257C7-18D2-4313-AC84-8018234CC831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{1CF907DD-3526-475F-8A93-BDC6F789D12C}"/>
   </bookViews>
   <sheets>
     <sheet name="BAGACEIRAS" sheetId="2" r:id="rId1"/>
@@ -21,9 +21,11 @@
     <sheet name="CAMISAS" sheetId="7" r:id="rId6"/>
     <sheet name="EIXOS" sheetId="12" r:id="rId7"/>
     <sheet name="VI DIVERSOS" sheetId="10" r:id="rId8"/>
-    <sheet name="PLANEJADO BAGACEIRA" sheetId="5" state="hidden" r:id="rId9"/>
+    <sheet name="Manganês" sheetId="13" r:id="rId9"/>
+    <sheet name="PLANEJADO BAGACEIRA" sheetId="5" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Manganês!$A$1:$J$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'VI DIVERSOS'!$A$1:$N$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">BAGACEIRAS!$A$1:$AI$113</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">BAGACEIRAS!$1:$1</definedName>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6833" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7181" uniqueCount="454">
   <si>
     <t>O.S.</t>
   </si>
@@ -1363,6 +1365,96 @@
     <t>Fund. Real
 (Acabamento)</t>
   </si>
+  <si>
+    <t>Prazo Contratual</t>
+  </si>
+  <si>
+    <t>Fusão</t>
+  </si>
+  <si>
+    <t>Metso Brasil Indústria e Comércio Ltda - 152</t>
+  </si>
+  <si>
+    <t>MANTA HP400 FUND. C/ USIN. (7055308385)</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO HP300 FUND. C/ USIN. (MM1601135)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO HP300 FUND. C/ USIN. (MM1670349)</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>MANTA HP400 FUND. C/ USIN. (N55308512)</t>
+  </si>
+  <si>
+    <t>MANTA HP400 FUND. C/ USIN. (7055308388)</t>
+  </si>
+  <si>
+    <t>Superior Industries do Brasil Ltda.</t>
+  </si>
+  <si>
+    <t>MANTA P500 FUND. C/ USIN (50-5P21M502-R01)</t>
+  </si>
+  <si>
+    <t>MANTA P400 FUND. C/ USIN (50-4P18M001)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P300 FUND. C/ USIN (50-3P21B006)</t>
+  </si>
+  <si>
+    <t>MANTA P300 FUND. C/ USIN (50-3P21M002)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P400 FUND. C/ USIN (50-4P21B002)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P400 FUND. C/ USIN (50-4P21B003)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P300 FUND. C/ USIN (50-3P18B004)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P500 FUND. C/ USIN (50-5P18B506)</t>
+  </si>
+  <si>
+    <t>MANTA P200 FUND. C/ USIN (50-2P18M002)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P500 FUND. C/ USIN (50-5P21B506)</t>
+  </si>
+  <si>
+    <t>MANTA P300 FUND. C/ USIN (50-3P21M001)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P200 FUND. C/ USIN (50-2P21B007)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P300 FUND. C/ USIN (50-3P21B003)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P400 FUND. C/ USIN (50-4P18B002)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P300 FUND. C/ USIN (50-3P18B003)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P400 FUND. C/ USIN (50-4P18B006)</t>
+  </si>
+  <si>
+    <t>REVESTIMENTO DO BOJO P400 FUND. C/ USIN (50-4P21B006)</t>
+  </si>
+  <si>
+    <t>MANTA P400 FUND. C/ USIN (50-4P21M002)</t>
+  </si>
+  <si>
+    <t>MANTA P300 FUND. C/ USIN (50-3P18M002)</t>
+  </si>
 </sst>
 </file>
 
@@ -1631,7 +1723,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1847,6 +1939,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -18396,6 +18506,854 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE2D677-2C60-498D-9118-7EBBADC442C8}">
+  <dimension ref="B2:AK7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="37" width="3.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:37" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3">
+        <v>23</v>
+      </c>
+      <c r="D2" s="3">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3">
+        <v>27</v>
+      </c>
+      <c r="H2" s="3">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3">
+        <v>29</v>
+      </c>
+      <c r="J2" s="3">
+        <v>30</v>
+      </c>
+      <c r="K2" s="3">
+        <v>31</v>
+      </c>
+      <c r="L2" s="3">
+        <v>32</v>
+      </c>
+      <c r="M2" s="3">
+        <v>33</v>
+      </c>
+      <c r="N2" s="3">
+        <v>34</v>
+      </c>
+      <c r="O2" s="3">
+        <v>35</v>
+      </c>
+      <c r="P2" s="3">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>37</v>
+      </c>
+      <c r="R2" s="3">
+        <v>38</v>
+      </c>
+      <c r="S2" s="3">
+        <v>39</v>
+      </c>
+      <c r="T2" s="3">
+        <v>40</v>
+      </c>
+      <c r="U2" s="3">
+        <v>41</v>
+      </c>
+      <c r="V2" s="3">
+        <v>42</v>
+      </c>
+      <c r="W2" s="3">
+        <v>43</v>
+      </c>
+      <c r="X2" s="3">
+        <v>44</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>45</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>46</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>47</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>48</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>49</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>50</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>51</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>52</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>53</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>2</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>3</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:37" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,C2,BAGACEIRAS!$I:$I)</f>
+        <v>4</v>
+      </c>
+      <c r="D3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,D2,BAGACEIRAS!$I:$I)</f>
+        <v>6</v>
+      </c>
+      <c r="E3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,E2,BAGACEIRAS!$I:$I)</f>
+        <v>8</v>
+      </c>
+      <c r="F3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,F2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="G3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,G2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="H3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,H2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="I3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,I2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="J3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,J2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="K3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,K2,BAGACEIRAS!$I:$I)</f>
+        <v>8</v>
+      </c>
+      <c r="L3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,L2,BAGACEIRAS!$I:$I)</f>
+        <v>6</v>
+      </c>
+      <c r="M3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,M2,BAGACEIRAS!$I:$I)</f>
+        <v>5</v>
+      </c>
+      <c r="N3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,N2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,O2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,P2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,Q2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,R2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,S2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,T2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="U3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,U2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,V2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,W2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,X2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,Y2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,Z2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AA3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AA2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AB3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AB2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AC2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AD3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AD2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AE3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AE2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AF3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AF2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AG3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AG2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AH2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AI2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AJ2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <f>SUMIF(BAGACEIRAS!$AE:$AE,AK2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:37" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,C2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,D2,BAGACEIRAS!$I:$I)</f>
+        <v>4</v>
+      </c>
+      <c r="E4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,E2,BAGACEIRAS!$I:$I)</f>
+        <v>6</v>
+      </c>
+      <c r="F4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,F2,BAGACEIRAS!$I:$I)</f>
+        <v>8</v>
+      </c>
+      <c r="G4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,G2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="H4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,H2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="I4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,I2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="J4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,J2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="K4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,K2,BAGACEIRAS!$I:$I)</f>
+        <v>3</v>
+      </c>
+      <c r="L4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,L2,BAGACEIRAS!$I:$I)</f>
+        <v>8</v>
+      </c>
+      <c r="M4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,M2,BAGACEIRAS!$I:$I)</f>
+        <v>6</v>
+      </c>
+      <c r="N4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,N2,BAGACEIRAS!$I:$I)</f>
+        <v>5</v>
+      </c>
+      <c r="O4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,O2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,P2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,Q2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,R2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,S2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="T4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,T2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="U4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,U2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="V4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,V2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="W4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,W2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="X4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,X2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,Y2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,Z2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AA4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AA2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AB4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AB2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AC2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AD2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AE4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AE2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AF4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AF2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AG2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AH2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AI2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AJ2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="4">
+        <f>SUMIF(BAGACEIRAS!$AF:$AF,AK2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:37" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,C2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,D2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,E2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,F2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,G2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,H2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,I2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,J2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,K2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,L2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,M2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,N2,BAGACEIRAS!$I:$I)</f>
+        <v>6</v>
+      </c>
+      <c r="O5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,O2,BAGACEIRAS!$I:$I)</f>
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,P2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,Q2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,R2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,S2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,T2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,U2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,V2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,W2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,X2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,Y2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,Z2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AA5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AA2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AB5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AB2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AC5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AC2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AD5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AD2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AE5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AE2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AF5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AF2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AG5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AG2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AH5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AH2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AI2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AJ2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AK5" s="4">
+        <f>SUMIF(BAGACEIRAS!$AG:$AG,AK2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:37" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,C2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,D2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,E2,BAGACEIRAS!$I:$I)</f>
+        <v>4</v>
+      </c>
+      <c r="F6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,F2,BAGACEIRAS!$I:$I)</f>
+        <v>6</v>
+      </c>
+      <c r="G6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,G2,BAGACEIRAS!$I:$I)</f>
+        <v>8</v>
+      </c>
+      <c r="H6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,H2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="I6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,I2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="J6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,J2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="K6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,K2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="L6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,L2,BAGACEIRAS!$I:$I)</f>
+        <v>3</v>
+      </c>
+      <c r="M6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,M2,BAGACEIRAS!$I:$I)</f>
+        <v>8</v>
+      </c>
+      <c r="N6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,N2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,O2,BAGACEIRAS!$I:$I)</f>
+        <v>6</v>
+      </c>
+      <c r="P6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,P2,BAGACEIRAS!$I:$I)</f>
+        <v>5</v>
+      </c>
+      <c r="Q6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,Q2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,R2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,S2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,T2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,U2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,V2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="W6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,W2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="X6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,X2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,Y2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,Z2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AA2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AB6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AB2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AC2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AD2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AE2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AF2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AG6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AG2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AH2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AI2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AJ2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="4">
+        <f>SUMIF(BAGACEIRAS!$AH:$AH,AK2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:37" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,C2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,D2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,E2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,F2,BAGACEIRAS!$I:$I)</f>
+        <v>4</v>
+      </c>
+      <c r="G7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,G2,BAGACEIRAS!$I:$I)</f>
+        <v>6</v>
+      </c>
+      <c r="H7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,H2,BAGACEIRAS!$I:$I)</f>
+        <v>8</v>
+      </c>
+      <c r="I7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,I2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="J7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,J2,BAGACEIRAS!$I:$I)</f>
+        <v>10</v>
+      </c>
+      <c r="K7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,K2,BAGACEIRAS!$I:$I)</f>
+        <v>15</v>
+      </c>
+      <c r="L7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,L2,BAGACEIRAS!$I:$I)</f>
+        <v>12</v>
+      </c>
+      <c r="M7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,M2,BAGACEIRAS!$I:$I)</f>
+        <v>3</v>
+      </c>
+      <c r="N7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,N2,BAGACEIRAS!$I:$I)</f>
+        <v>8</v>
+      </c>
+      <c r="O7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,O2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,P2,BAGACEIRAS!$I:$I)</f>
+        <v>6</v>
+      </c>
+      <c r="Q7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,Q2,BAGACEIRAS!$I:$I)</f>
+        <v>5</v>
+      </c>
+      <c r="R7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,R2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="S7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,S2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="T7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,T2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,U2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,V2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,W2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="X7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,X2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,Y2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,Z2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AA7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AA2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AB7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AB2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AC2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AD2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AE2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AF2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AG7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AG2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AH2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AI2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AJ2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="4">
+        <f>SUMIF(BAGACEIRAS!$AI:$AI,AK2,BAGACEIRAS!$I:$I)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F053A7-2FDA-4BCA-8A08-44A595E3BEFC}">
   <dimension ref="A1:V163"/>
@@ -52584,849 +53542,3670 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE2D677-2C60-498D-9118-7EBBADC442C8}">
-  <dimension ref="B2:AK7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7CFD24F-B3EF-4CA9-A951-03CC4269A17E}">
+  <dimension ref="A1:L113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="37" width="3.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" style="28" customWidth="1"/>
+    <col min="4" max="4" width="8" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.28515625" style="28" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" style="10" customWidth="1"/>
+    <col min="8" max="10" width="16.7109375" style="10" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:37" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B2" s="2"/>
-      <c r="C2" s="3">
-        <v>23</v>
-      </c>
-      <c r="D2" s="3">
-        <v>24</v>
-      </c>
-      <c r="E2" s="3">
-        <v>25</v>
-      </c>
-      <c r="F2" s="3">
-        <v>26</v>
-      </c>
-      <c r="G2" s="3">
-        <v>27</v>
-      </c>
-      <c r="H2" s="3">
-        <v>28</v>
-      </c>
-      <c r="I2" s="3">
-        <v>29</v>
-      </c>
-      <c r="J2" s="3">
-        <v>30</v>
-      </c>
-      <c r="K2" s="3">
-        <v>31</v>
-      </c>
-      <c r="L2" s="3">
-        <v>32</v>
-      </c>
-      <c r="M2" s="3">
-        <v>33</v>
-      </c>
-      <c r="N2" s="3">
-        <v>34</v>
-      </c>
-      <c r="O2" s="3">
-        <v>35</v>
-      </c>
-      <c r="P2" s="3">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>37</v>
-      </c>
-      <c r="R2" s="3">
-        <v>38</v>
-      </c>
-      <c r="S2" s="3">
-        <v>39</v>
-      </c>
-      <c r="T2" s="3">
-        <v>40</v>
-      </c>
-      <c r="U2" s="3">
-        <v>41</v>
-      </c>
-      <c r="V2" s="3">
-        <v>42</v>
-      </c>
-      <c r="W2" s="3">
-        <v>43</v>
-      </c>
-      <c r="X2" s="3">
-        <v>44</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>45</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>46</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>47</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>48</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>49</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>50</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>51</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>52</v>
-      </c>
-      <c r="AG2" s="3">
-        <v>53</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="3">
+    <row r="1" spans="1:12" s="10" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>423</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="23">
+        <v>27415</v>
+      </c>
+      <c r="B2" s="23">
+        <v>1</v>
+      </c>
+      <c r="C2" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D2" s="23">
+        <v>152652</v>
+      </c>
+      <c r="E2" s="81" t="s">
+        <v>427</v>
+      </c>
+      <c r="F2" s="25">
+        <v>46162</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="H2" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K2" s="50"/>
+      <c r="L2" s="23"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="23">
+        <v>27574</v>
+      </c>
+      <c r="B3" s="23">
+        <v>1</v>
+      </c>
+      <c r="C3" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" s="23">
+        <v>152655</v>
+      </c>
+      <c r="E3" s="81" t="s">
+        <v>429</v>
+      </c>
+      <c r="F3" s="25">
+        <v>46234</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="H3" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K3" s="50"/>
+      <c r="L3" s="23"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="23">
+        <v>27574</v>
+      </c>
+      <c r="B4" s="23">
         <v>2</v>
       </c>
-      <c r="AJ2" s="3">
+      <c r="C4" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D4" s="23">
+        <v>152655</v>
+      </c>
+      <c r="E4" s="81" t="s">
+        <v>429</v>
+      </c>
+      <c r="F4" s="25">
+        <v>46234</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="H4" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K4" s="50"/>
+      <c r="L4" s="23"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="23">
+        <v>27572</v>
+      </c>
+      <c r="B5" s="23">
+        <v>1</v>
+      </c>
+      <c r="C5" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D5" s="23">
+        <v>152654</v>
+      </c>
+      <c r="E5" s="81" t="s">
+        <v>430</v>
+      </c>
+      <c r="F5" s="25">
+        <v>46234</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H5" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K5" s="50"/>
+      <c r="L5" s="23"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="23">
+        <v>27572</v>
+      </c>
+      <c r="B6" s="23">
+        <v>2</v>
+      </c>
+      <c r="C6" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D6" s="23">
+        <v>152654</v>
+      </c>
+      <c r="E6" s="81" t="s">
+        <v>430</v>
+      </c>
+      <c r="F6" s="25">
+        <v>46234</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H6" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K6" s="50"/>
+      <c r="L6" s="23"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="23">
+        <v>27572</v>
+      </c>
+      <c r="B7" s="23">
         <v>3</v>
       </c>
-      <c r="AK2" s="3">
+      <c r="C7" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D7" s="23">
+        <v>152654</v>
+      </c>
+      <c r="E7" s="81" t="s">
+        <v>430</v>
+      </c>
+      <c r="F7" s="25">
+        <v>46234</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H7" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K7" s="50"/>
+      <c r="L7" s="23"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="23">
+        <v>27572</v>
+      </c>
+      <c r="B8" s="23">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="2:37" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="4">
-        <f>SUMIF(BAGACEIRAS!$AE:$AE,C2,BAGACEIRAS!$I:$I)</f>
+      <c r="C8" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D8" s="23">
+        <v>152654</v>
+      </c>
+      <c r="E8" s="81" t="s">
+        <v>430</v>
+      </c>
+      <c r="F8" s="25">
+        <v>46234</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H8" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K8" s="50"/>
+      <c r="L8" s="23"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="23">
+        <v>27595</v>
+      </c>
+      <c r="B9" s="23">
+        <v>1</v>
+      </c>
+      <c r="C9" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D9" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E9" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F9" s="25">
+        <v>46238</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H9" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I9" s="25">
+        <v>46210</v>
+      </c>
+      <c r="J9" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K9" s="50"/>
+      <c r="L9" s="23">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="23">
+        <v>27595</v>
+      </c>
+      <c r="B10" s="23">
+        <v>2</v>
+      </c>
+      <c r="C10" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D10" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E10" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F10" s="25">
+        <v>46238</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H10" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I10" s="25">
+        <v>46210</v>
+      </c>
+      <c r="J10" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K10" s="50"/>
+      <c r="L10" s="23">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="23">
+        <v>27595</v>
+      </c>
+      <c r="B11" s="23">
+        <v>3</v>
+      </c>
+      <c r="C11" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D11" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E11" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F11" s="25">
+        <v>46238</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H11" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I11" s="25">
+        <v>46210</v>
+      </c>
+      <c r="J11" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K11" s="50"/>
+      <c r="L11" s="23">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="23">
+        <v>27595</v>
+      </c>
+      <c r="B12" s="23">
         <v>4</v>
       </c>
-      <c r="D3" s="4">
-        <f>SUMIF(BAGACEIRAS!$AE:$AE,D2,BAGACEIRAS!$I:$I)</f>
+      <c r="C12" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D12" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E12" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F12" s="25">
+        <v>46238</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H12" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I12" s="25">
+        <v>46210</v>
+      </c>
+      <c r="J12" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K12" s="50"/>
+      <c r="L12" s="23">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="23">
+        <v>27595</v>
+      </c>
+      <c r="B13" s="23">
+        <v>5</v>
+      </c>
+      <c r="C13" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D13" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E13" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F13" s="25">
+        <v>46238</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H13" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I13" s="25">
+        <v>46210</v>
+      </c>
+      <c r="J13" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K13" s="50"/>
+      <c r="L13" s="23">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="23">
+        <v>27595</v>
+      </c>
+      <c r="B14" s="23">
         <v>6</v>
       </c>
-      <c r="E3" s="4">
-        <f>SUMIF(BAGACEIRAS!$AE:$AE,E2,BAGACEIRAS!$I:$I)</f>
+      <c r="C14" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D14" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E14" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F14" s="25">
+        <v>46238</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H14" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K14" s="50"/>
+      <c r="L14" s="23"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="23">
+        <v>27595</v>
+      </c>
+      <c r="B15" s="23">
+        <v>7</v>
+      </c>
+      <c r="C15" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D15" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E15" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F15" s="25">
+        <v>46238</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H15" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K15" s="50"/>
+      <c r="L15" s="23"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="23">
+        <v>27595</v>
+      </c>
+      <c r="B16" s="23">
         <v>8</v>
       </c>
-      <c r="F3" s="4">
-        <f>SUMIF(BAGACEIRAS!$AE:$AE,F2,BAGACEIRAS!$I:$I)</f>
+      <c r="C16" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D16" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E16" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F16" s="25">
+        <v>46238</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H16" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K16" s="50"/>
+      <c r="L16" s="23"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="23">
+        <v>27595</v>
+      </c>
+      <c r="B17" s="23">
+        <v>9</v>
+      </c>
+      <c r="C17" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D17" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E17" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F17" s="25">
+        <v>46238</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H17" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K17" s="50"/>
+      <c r="L17" s="23"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="23">
+        <v>27602</v>
+      </c>
+      <c r="B18" s="23">
+        <v>1</v>
+      </c>
+      <c r="C18" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D18" s="23">
+        <v>152655</v>
+      </c>
+      <c r="E18" s="81" t="s">
+        <v>429</v>
+      </c>
+      <c r="F18" s="25">
+        <v>46240</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H18" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K18" s="50"/>
+      <c r="L18" s="23"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="23">
+        <v>27602</v>
+      </c>
+      <c r="B19" s="23">
+        <v>2</v>
+      </c>
+      <c r="C19" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D19" s="23">
+        <v>152655</v>
+      </c>
+      <c r="E19" s="81" t="s">
+        <v>429</v>
+      </c>
+      <c r="F19" s="25">
+        <v>46240</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H19" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K19" s="50"/>
+      <c r="L19" s="23"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="23">
+        <v>27602</v>
+      </c>
+      <c r="B20" s="23">
+        <v>3</v>
+      </c>
+      <c r="C20" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D20" s="23">
+        <v>152655</v>
+      </c>
+      <c r="E20" s="81" t="s">
+        <v>429</v>
+      </c>
+      <c r="F20" s="25">
+        <v>46240</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H20" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K20" s="50"/>
+      <c r="L20" s="23"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="23">
+        <v>27602</v>
+      </c>
+      <c r="B21" s="23">
+        <v>4</v>
+      </c>
+      <c r="C21" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D21" s="23">
+        <v>152655</v>
+      </c>
+      <c r="E21" s="81" t="s">
+        <v>429</v>
+      </c>
+      <c r="F21" s="25">
+        <v>46240</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H21" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K21" s="50"/>
+      <c r="L21" s="23"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="23">
+        <v>27592</v>
+      </c>
+      <c r="B22" s="23">
+        <v>1</v>
+      </c>
+      <c r="C22" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D22" s="23">
+        <v>152655</v>
+      </c>
+      <c r="E22" s="81" t="s">
+        <v>429</v>
+      </c>
+      <c r="F22" s="25">
+        <v>46241</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H22" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K22" s="50"/>
+      <c r="L22" s="23"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="23">
+        <v>27592</v>
+      </c>
+      <c r="B23" s="23">
+        <v>2</v>
+      </c>
+      <c r="C23" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D23" s="23">
+        <v>152655</v>
+      </c>
+      <c r="E23" s="81" t="s">
+        <v>429</v>
+      </c>
+      <c r="F23" s="25">
+        <v>46241</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H23" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K23" s="50"/>
+      <c r="L23" s="23"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="23">
+        <v>27591</v>
+      </c>
+      <c r="B24" s="23">
+        <v>1</v>
+      </c>
+      <c r="C24" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D24" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E24" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F24" s="25">
+        <v>46241</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H24" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K24" s="50"/>
+      <c r="L24" s="23"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="23">
+        <v>27591</v>
+      </c>
+      <c r="B25" s="23">
+        <v>2</v>
+      </c>
+      <c r="C25" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D25" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E25" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F25" s="25">
+        <v>46241</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H25" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K25" s="50"/>
+      <c r="L25" s="23"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="23">
+        <v>27591</v>
+      </c>
+      <c r="B26" s="23">
+        <v>3</v>
+      </c>
+      <c r="C26" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D26" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E26" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F26" s="25">
+        <v>46241</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H26" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K26" s="50"/>
+      <c r="L26" s="23"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="23">
+        <v>27591</v>
+      </c>
+      <c r="B27" s="23">
+        <v>4</v>
+      </c>
+      <c r="C27" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D27" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E27" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F27" s="25">
+        <v>46241</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H27" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K27" s="50"/>
+      <c r="L27" s="23"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="23">
+        <v>27591</v>
+      </c>
+      <c r="B28" s="23">
+        <v>5</v>
+      </c>
+      <c r="C28" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D28" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E28" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F28" s="25">
+        <v>46241</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H28" s="25">
+        <v>46213</v>
+      </c>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25">
+        <v>46220</v>
+      </c>
+      <c r="K28" s="50"/>
+      <c r="L28" s="23"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B29" s="23">
+        <v>1</v>
+      </c>
+      <c r="C29" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D29" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E29" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F29" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H29" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K29" s="50"/>
+      <c r="L29" s="23"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B30" s="23">
+        <v>2</v>
+      </c>
+      <c r="C30" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D30" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E30" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F30" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H30" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K30" s="50"/>
+      <c r="L30" s="23"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B31" s="23">
+        <v>3</v>
+      </c>
+      <c r="C31" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D31" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E31" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F31" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H31" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K31" s="50"/>
+      <c r="L31" s="23"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B32" s="23">
+        <v>4</v>
+      </c>
+      <c r="C32" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D32" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E32" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F32" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H32" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K32" s="50"/>
+      <c r="L32" s="23"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B33" s="23">
+        <v>5</v>
+      </c>
+      <c r="C33" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D33" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E33" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F33" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H33" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K33" s="50"/>
+      <c r="L33" s="23"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B34" s="23">
+        <v>6</v>
+      </c>
+      <c r="C34" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D34" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E34" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F34" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H34" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K34" s="50"/>
+      <c r="L34" s="23"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B35" s="23">
+        <v>7</v>
+      </c>
+      <c r="C35" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D35" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E35" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F35" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G35" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H35" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K35" s="50"/>
+      <c r="L35" s="23"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B36" s="23">
+        <v>8</v>
+      </c>
+      <c r="C36" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D36" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E36" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F36" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H36" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K36" s="50"/>
+      <c r="L36" s="23"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B37" s="23">
+        <v>9</v>
+      </c>
+      <c r="C37" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D37" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E37" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F37" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G37" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H37" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K37" s="50"/>
+      <c r="L37" s="23"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B38" s="23">
         <v>10</v>
       </c>
-      <c r="G3" s="4">
-        <f>SUMIF(BAGACEIRAS!$AE:$AE,G2,BAGACEIRAS!$I:$I)</f>
+      <c r="C38" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D38" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E38" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F38" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H38" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K38" s="50"/>
+      <c r="L38" s="23"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B39" s="23">
+        <v>11</v>
+      </c>
+      <c r="C39" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D39" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E39" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F39" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H39" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K39" s="50"/>
+      <c r="L39" s="23"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B40" s="23">
+        <v>12</v>
+      </c>
+      <c r="C40" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D40" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E40" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F40" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G40" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H40" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K40" s="50"/>
+      <c r="L40" s="23"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="23">
+        <v>27594</v>
+      </c>
+      <c r="B41" s="23">
+        <v>13</v>
+      </c>
+      <c r="C41" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D41" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E41" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F41" s="25">
+        <v>46245</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H41" s="25">
+        <v>46220</v>
+      </c>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25">
+        <v>46227</v>
+      </c>
+      <c r="K41" s="50"/>
+      <c r="L41" s="23"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="23">
+        <v>27606</v>
+      </c>
+      <c r="B42" s="23">
+        <v>1</v>
+      </c>
+      <c r="C42" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D42" s="23">
+        <v>152653</v>
+      </c>
+      <c r="E42" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F42" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G42" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H42" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K42" s="50"/>
+      <c r="L42" s="23"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="23">
+        <v>27606</v>
+      </c>
+      <c r="B43" s="23">
+        <v>2</v>
+      </c>
+      <c r="C43" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D43" s="23">
+        <v>152653</v>
+      </c>
+      <c r="E43" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F43" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G43" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H43" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K43" s="50"/>
+      <c r="L43" s="23"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="23">
+        <v>27606</v>
+      </c>
+      <c r="B44" s="23">
+        <v>3</v>
+      </c>
+      <c r="C44" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D44" s="23">
+        <v>152653</v>
+      </c>
+      <c r="E44" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F44" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G44" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H44" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K44" s="50"/>
+      <c r="L44" s="23"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="23">
+        <v>27606</v>
+      </c>
+      <c r="B45" s="23">
+        <v>4</v>
+      </c>
+      <c r="C45" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D45" s="23">
+        <v>152653</v>
+      </c>
+      <c r="E45" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F45" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G45" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H45" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I45" s="27"/>
+      <c r="J45" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K45" s="50"/>
+      <c r="L45" s="23"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="23">
+        <v>27606</v>
+      </c>
+      <c r="B46" s="23">
+        <v>5</v>
+      </c>
+      <c r="C46" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D46" s="23">
+        <v>152653</v>
+      </c>
+      <c r="E46" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F46" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G46" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H46" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I46" s="27"/>
+      <c r="J46" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K46" s="50"/>
+      <c r="L46" s="23"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="23">
+        <v>27606</v>
+      </c>
+      <c r="B47" s="23">
+        <v>6</v>
+      </c>
+      <c r="C47" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D47" s="23">
+        <v>152653</v>
+      </c>
+      <c r="E47" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F47" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G47" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H47" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I47" s="27"/>
+      <c r="J47" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K47" s="50"/>
+      <c r="L47" s="23"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="23">
+        <v>27606</v>
+      </c>
+      <c r="B48" s="23">
+        <v>7</v>
+      </c>
+      <c r="C48" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D48" s="23">
+        <v>152653</v>
+      </c>
+      <c r="E48" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F48" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G48" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H48" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K48" s="50"/>
+      <c r="L48" s="23"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="23">
+        <v>27606</v>
+      </c>
+      <c r="B49" s="23">
+        <v>8</v>
+      </c>
+      <c r="C49" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D49" s="23">
+        <v>152653</v>
+      </c>
+      <c r="E49" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F49" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G49" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H49" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I49" s="27"/>
+      <c r="J49" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K49" s="50"/>
+      <c r="L49" s="23"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="23">
+        <v>27606</v>
+      </c>
+      <c r="B50" s="23">
+        <v>9</v>
+      </c>
+      <c r="C50" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D50" s="23">
+        <v>152653</v>
+      </c>
+      <c r="E50" s="81" t="s">
+        <v>433</v>
+      </c>
+      <c r="F50" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G50" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H50" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I50" s="27"/>
+      <c r="J50" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K50" s="50"/>
+      <c r="L50" s="23"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B51" s="23">
+        <v>1</v>
+      </c>
+      <c r="C51" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D51" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E51" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F51" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G51" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H51" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I51" s="27"/>
+      <c r="J51" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K51" s="50"/>
+      <c r="L51" s="23"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B52" s="23">
+        <v>2</v>
+      </c>
+      <c r="C52" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D52" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E52" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F52" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G52" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H52" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I52" s="27"/>
+      <c r="J52" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K52" s="50"/>
+      <c r="L52" s="23"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B53" s="23">
+        <v>3</v>
+      </c>
+      <c r="C53" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D53" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E53" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F53" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H53" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I53" s="27"/>
+      <c r="J53" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K53" s="50"/>
+      <c r="L53" s="23"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B54" s="23">
+        <v>4</v>
+      </c>
+      <c r="C54" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D54" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E54" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F54" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G54" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H54" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I54" s="27"/>
+      <c r="J54" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K54" s="50"/>
+      <c r="L54" s="23"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B55" s="23">
+        <v>5</v>
+      </c>
+      <c r="C55" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D55" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E55" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F55" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H55" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I55" s="27"/>
+      <c r="J55" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K55" s="50"/>
+      <c r="L55" s="23"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B56" s="23">
+        <v>6</v>
+      </c>
+      <c r="C56" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D56" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E56" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F56" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G56" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H56" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I56" s="27"/>
+      <c r="J56" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K56" s="50"/>
+      <c r="L56" s="23"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B57" s="23">
+        <v>7</v>
+      </c>
+      <c r="C57" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D57" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E57" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F57" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G57" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H57" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I57" s="27"/>
+      <c r="J57" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K57" s="50"/>
+      <c r="L57" s="23"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B58" s="23">
+        <v>8</v>
+      </c>
+      <c r="C58" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D58" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E58" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F58" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G58" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H58" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I58" s="27"/>
+      <c r="J58" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K58" s="50"/>
+      <c r="L58" s="23"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B59" s="23">
+        <v>9</v>
+      </c>
+      <c r="C59" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D59" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E59" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F59" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G59" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H59" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K59" s="50"/>
+      <c r="L59" s="23"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="23">
+        <v>27604</v>
+      </c>
+      <c r="B60" s="23">
         <v>10</v>
       </c>
-      <c r="H3" s="4">
-        <f>SUMIF(BAGACEIRAS!$AE:$AE,H2,BAGACEIRAS!$I:$I)</f>
+      <c r="C60" s="81" t="s">
+        <v>426</v>
+      </c>
+      <c r="D60" s="23">
+        <v>152650</v>
+      </c>
+      <c r="E60" s="81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F60" s="25">
+        <v>46253</v>
+      </c>
+      <c r="G60" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H60" s="27">
+        <v>46227</v>
+      </c>
+      <c r="I60" s="27"/>
+      <c r="J60" s="27">
+        <v>46234</v>
+      </c>
+      <c r="K60" s="50"/>
+      <c r="L60" s="23"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="23">
+        <v>27545</v>
+      </c>
+      <c r="B61" s="23">
+        <v>3</v>
+      </c>
+      <c r="C61" s="81" t="s">
+        <v>434</v>
+      </c>
+      <c r="D61" s="23">
+        <v>1425040</v>
+      </c>
+      <c r="E61" s="81" t="s">
+        <v>435</v>
+      </c>
+      <c r="F61" s="25">
+        <v>46244</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H61" s="27">
+        <v>46213</v>
+      </c>
+      <c r="I61" s="27"/>
+      <c r="J61" s="27">
+        <v>46220</v>
+      </c>
+      <c r="K61" s="50"/>
+      <c r="L61" s="26"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="23">
+        <v>27545</v>
+      </c>
+      <c r="B62" s="23">
+        <v>4</v>
+      </c>
+      <c r="C62" s="81" t="s">
+        <v>434</v>
+      </c>
+      <c r="D62" s="23">
+        <v>1425040</v>
+      </c>
+      <c r="E62" s="81" t="s">
+        <v>435</v>
+      </c>
+      <c r="F62" s="25">
+        <v>46244</v>
+      </c>
+      <c r="G62" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H62" s="27">
+        <v>46213</v>
+      </c>
+      <c r="I62" s="27"/>
+      <c r="J62" s="27">
+        <v>46220</v>
+      </c>
+      <c r="K62" s="50"/>
+      <c r="L62" s="26"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="23">
+        <v>27545</v>
+      </c>
+      <c r="B63" s="23">
+        <v>5</v>
+      </c>
+      <c r="C63" s="81" t="s">
+        <v>434</v>
+      </c>
+      <c r="D63" s="23">
+        <v>1425040</v>
+      </c>
+      <c r="E63" s="81" t="s">
+        <v>435</v>
+      </c>
+      <c r="F63" s="25">
+        <v>46244</v>
+      </c>
+      <c r="G63" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H63" s="27">
+        <v>46213</v>
+      </c>
+      <c r="I63" s="27"/>
+      <c r="J63" s="27">
+        <v>46220</v>
+      </c>
+      <c r="K63" s="50"/>
+      <c r="L63" s="26"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="23">
+        <v>27545</v>
+      </c>
+      <c r="B64" s="23">
+        <v>16</v>
+      </c>
+      <c r="C64" s="81" t="s">
+        <v>434</v>
+      </c>
+      <c r="D64" s="23">
+        <v>1425040</v>
+      </c>
+      <c r="E64" s="81" t="s">
+        <v>435</v>
+      </c>
+      <c r="F64" s="25">
+        <v>46244</v>
+      </c>
+      <c r="G64" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H64" s="27">
+        <v>46213</v>
+      </c>
+      <c r="I64" s="27"/>
+      <c r="J64" s="27">
+        <v>46220</v>
+      </c>
+      <c r="K64" s="50"/>
+      <c r="L64" s="26"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="23">
+        <v>27545</v>
+      </c>
+      <c r="B65" s="23">
+        <v>14</v>
+      </c>
+      <c r="C65" s="81" t="s">
+        <v>434</v>
+      </c>
+      <c r="D65" s="23">
+        <v>1425049</v>
+      </c>
+      <c r="E65" s="81" t="s">
+        <v>436</v>
+      </c>
+      <c r="F65" s="25">
+        <v>46244</v>
+      </c>
+      <c r="G65" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="H65" s="27">
+        <v>46213</v>
+      </c>
+      <c r="I65" s="27"/>
+      <c r="J65" s="27">
+        <v>46220</v>
+      </c>
+      <c r="K65" s="50"/>
+      <c r="L65" s="26"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="82">
+        <v>27456</v>
+      </c>
+      <c r="B66" s="82">
+        <v>4</v>
+      </c>
+      <c r="C66" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D66" s="82">
+        <v>1425031</v>
+      </c>
+      <c r="E66" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="F66" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G66" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H66" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I66" s="86"/>
+      <c r="J66" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K66" s="50"/>
+      <c r="L66" s="86"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="82">
+        <v>27456</v>
+      </c>
+      <c r="B67" s="82">
+        <v>5</v>
+      </c>
+      <c r="C67" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D67" s="82">
+        <v>1425031</v>
+      </c>
+      <c r="E67" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="F67" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G67" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H67" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I67" s="86"/>
+      <c r="J67" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K67" s="50"/>
+      <c r="L67" s="86"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="82">
+        <v>27456</v>
+      </c>
+      <c r="B68" s="82">
+        <v>6</v>
+      </c>
+      <c r="C68" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D68" s="82">
+        <v>1425032</v>
+      </c>
+      <c r="E68" s="83" t="s">
+        <v>438</v>
+      </c>
+      <c r="F68" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G68" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H68" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I68" s="86"/>
+      <c r="J68" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K68" s="50"/>
+      <c r="L68" s="86"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="82">
+        <v>27456</v>
+      </c>
+      <c r="B69" s="82">
+        <v>7</v>
+      </c>
+      <c r="C69" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D69" s="82">
+        <v>1425032</v>
+      </c>
+      <c r="E69" s="83" t="s">
+        <v>438</v>
+      </c>
+      <c r="F69" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G69" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H69" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I69" s="86"/>
+      <c r="J69" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K69" s="50"/>
+      <c r="L69" s="86"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="82">
+        <v>27456</v>
+      </c>
+      <c r="B70" s="82">
         <v>10</v>
       </c>
-      <c r="I3" s="4">
-        <f>SUMIF(BAGACEIRAS!$AE:$AE,I2,BAGACEIRAS!$I:$I)</f>
+      <c r="C70" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D70" s="82">
+        <v>1425034</v>
+      </c>
+      <c r="E70" s="83" t="s">
+        <v>439</v>
+      </c>
+      <c r="F70" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G70" s="82" t="s">
+        <v>428</v>
+      </c>
+      <c r="H70" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I70" s="86"/>
+      <c r="J70" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K70" s="50"/>
+      <c r="L70" s="86"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="82">
+        <v>27456</v>
+      </c>
+      <c r="B71" s="82">
+        <v>11</v>
+      </c>
+      <c r="C71" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D71" s="82">
+        <v>1425035</v>
+      </c>
+      <c r="E71" s="83" t="s">
+        <v>440</v>
+      </c>
+      <c r="F71" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G71" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H71" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I71" s="86"/>
+      <c r="J71" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K71" s="50"/>
+      <c r="L71" s="86"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="82">
+        <v>27465</v>
+      </c>
+      <c r="B72" s="82">
+        <v>1</v>
+      </c>
+      <c r="C72" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D72" s="82">
+        <v>1425031</v>
+      </c>
+      <c r="E72" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="F72" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G72" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H72" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I72" s="86"/>
+      <c r="J72" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K72" s="50"/>
+      <c r="L72" s="86"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="82">
+        <v>27465</v>
+      </c>
+      <c r="B73" s="82">
+        <v>2</v>
+      </c>
+      <c r="C73" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D73" s="82">
+        <v>1425032</v>
+      </c>
+      <c r="E73" s="83" t="s">
+        <v>438</v>
+      </c>
+      <c r="F73" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G73" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H73" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I73" s="86"/>
+      <c r="J73" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K73" s="50"/>
+      <c r="L73" s="86"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" s="82">
+        <v>27465</v>
+      </c>
+      <c r="B74" s="82">
+        <v>3</v>
+      </c>
+      <c r="C74" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D74" s="82">
+        <v>1425039</v>
+      </c>
+      <c r="E74" s="83" t="s">
+        <v>441</v>
+      </c>
+      <c r="F74" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G74" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H74" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I74" s="86"/>
+      <c r="J74" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K74" s="50"/>
+      <c r="L74" s="86"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="82">
+        <v>27465</v>
+      </c>
+      <c r="B75" s="82">
+        <v>9</v>
+      </c>
+      <c r="C75" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D75" s="82">
+        <v>1425046</v>
+      </c>
+      <c r="E75" s="83" t="s">
+        <v>442</v>
+      </c>
+      <c r="F75" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G75" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H75" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I75" s="86"/>
+      <c r="J75" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K75" s="50"/>
+      <c r="L75" s="86"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="82">
+        <v>27456</v>
+      </c>
+      <c r="B76" s="82">
+        <v>19</v>
+      </c>
+      <c r="C76" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D76" s="82">
+        <v>1425038</v>
+      </c>
+      <c r="E76" s="83" t="s">
+        <v>443</v>
+      </c>
+      <c r="F76" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G76" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H76" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I76" s="86"/>
+      <c r="J76" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K76" s="50"/>
+      <c r="L76" s="86"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" s="82">
+        <v>27506</v>
+      </c>
+      <c r="B77" s="82">
+        <v>1</v>
+      </c>
+      <c r="C77" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D77" s="82">
+        <v>1425031</v>
+      </c>
+      <c r="E77" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="F77" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G77" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H77" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I77" s="86"/>
+      <c r="J77" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K77" s="50"/>
+      <c r="L77" s="86"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="82">
+        <v>27506</v>
+      </c>
+      <c r="B78" s="82">
+        <v>2</v>
+      </c>
+      <c r="C78" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D78" s="82">
+        <v>1425031</v>
+      </c>
+      <c r="E78" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="F78" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G78" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H78" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I78" s="86"/>
+      <c r="J78" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K78" s="50"/>
+      <c r="L78" s="86"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="82">
+        <v>27506</v>
+      </c>
+      <c r="B79" s="82">
+        <v>3</v>
+      </c>
+      <c r="C79" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D79" s="82">
+        <v>1425031</v>
+      </c>
+      <c r="E79" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="F79" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G79" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H79" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I79" s="86"/>
+      <c r="J79" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K79" s="50"/>
+      <c r="L79" s="86"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="82">
+        <v>27506</v>
+      </c>
+      <c r="B80" s="82">
+        <v>4</v>
+      </c>
+      <c r="C80" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D80" s="82">
+        <v>1425031</v>
+      </c>
+      <c r="E80" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="F80" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G80" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H80" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I80" s="86"/>
+      <c r="J80" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K80" s="50"/>
+      <c r="L80" s="86"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" s="82">
+        <v>27474</v>
+      </c>
+      <c r="B81" s="82">
+        <v>1</v>
+      </c>
+      <c r="C81" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D81" s="82">
+        <v>1425039</v>
+      </c>
+      <c r="E81" s="83" t="s">
+        <v>441</v>
+      </c>
+      <c r="F81" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G81" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H81" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I81" s="86"/>
+      <c r="J81" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K81" s="50"/>
+      <c r="L81" s="86"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" s="82">
+        <v>27603</v>
+      </c>
+      <c r="B82" s="82">
+        <v>1</v>
+      </c>
+      <c r="C82" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D82" s="82">
+        <v>1425034</v>
+      </c>
+      <c r="E82" s="83" t="s">
+        <v>439</v>
+      </c>
+      <c r="F82" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G82" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H82" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I82" s="86"/>
+      <c r="J82" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K82" s="50"/>
+      <c r="L82" s="86"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" s="82">
+        <v>27603</v>
+      </c>
+      <c r="B83" s="82">
+        <v>2</v>
+      </c>
+      <c r="C83" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D83" s="82">
+        <v>1425034</v>
+      </c>
+      <c r="E83" s="83" t="s">
+        <v>439</v>
+      </c>
+      <c r="F83" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G83" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H83" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I83" s="86"/>
+      <c r="J83" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K83" s="50"/>
+      <c r="L83" s="86"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" s="82">
+        <v>27529</v>
+      </c>
+      <c r="B84" s="82">
+        <v>1</v>
+      </c>
+      <c r="C84" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D84" s="82">
+        <v>1425032</v>
+      </c>
+      <c r="E84" s="83" t="s">
+        <v>438</v>
+      </c>
+      <c r="F84" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G84" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H84" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I84" s="86"/>
+      <c r="J84" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K84" s="50"/>
+      <c r="L84" s="86"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="82">
+        <v>27529</v>
+      </c>
+      <c r="B85" s="82">
+        <v>2</v>
+      </c>
+      <c r="C85" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D85" s="82">
+        <v>1425032</v>
+      </c>
+      <c r="E85" s="83" t="s">
+        <v>438</v>
+      </c>
+      <c r="F85" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G85" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H85" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I85" s="86"/>
+      <c r="J85" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K85" s="50"/>
+      <c r="L85" s="86"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" s="82">
+        <v>27529</v>
+      </c>
+      <c r="B86" s="82">
+        <v>3</v>
+      </c>
+      <c r="C86" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D86" s="82">
+        <v>1425032</v>
+      </c>
+      <c r="E86" s="83" t="s">
+        <v>438</v>
+      </c>
+      <c r="F86" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G86" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H86" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I86" s="86"/>
+      <c r="J86" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K86" s="50"/>
+      <c r="L86" s="86"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" s="82">
+        <v>27529</v>
+      </c>
+      <c r="B87" s="82">
+        <v>4</v>
+      </c>
+      <c r="C87" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D87" s="82">
+        <v>1425032</v>
+      </c>
+      <c r="E87" s="83" t="s">
+        <v>438</v>
+      </c>
+      <c r="F87" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G87" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H87" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I87" s="86"/>
+      <c r="J87" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K87" s="50"/>
+      <c r="L87" s="86"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="82">
+        <v>27529</v>
+      </c>
+      <c r="B88" s="82">
+        <v>5</v>
+      </c>
+      <c r="C88" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D88" s="82">
+        <v>1425032</v>
+      </c>
+      <c r="E88" s="83" t="s">
+        <v>438</v>
+      </c>
+      <c r="F88" s="84">
+        <v>46295</v>
+      </c>
+      <c r="G88" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="H88" s="85">
+        <v>46275</v>
+      </c>
+      <c r="I88" s="86"/>
+      <c r="J88" s="85">
+        <v>46290</v>
+      </c>
+      <c r="K88" s="50"/>
+      <c r="L88" s="86"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="82">
+        <v>27529</v>
+      </c>
+      <c r="B89" s="82">
+        <v>6</v>
+      </c>
+      <c r="C89" s="83" t="s">
+        <v>434</v>
+      </c>
+      <c r="D89" s="82